--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -3687,11 +3687,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="ItemData" sheetId="5" r:id="rId6"/>
     <sheet name="TrainingRateConfig" sheetId="12" r:id="rId7"/>
     <sheet name="SlicerConfig" sheetId="6" r:id="rId8"/>
-    <sheet name="TrailConfig" sheetId="7" r:id="rId9"/>
+    <sheet name="AuraConfig" sheetId="7" r:id="rId9"/>
     <sheet name="LevelConfig" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="934">
   <si>
     <t>子配置键</t>
   </si>
@@ -101,7 +101,7 @@
     <t>TrainingRateConfig</t>
   </si>
   <si>
-    <t>TrailConfig</t>
+    <t>AuraConfig</t>
   </si>
   <si>
     <t>AreaRefreshData</t>
@@ -2321,19 +2321,19 @@
     <t>图片ID</t>
   </si>
   <si>
-    <t>TrailId</t>
-  </si>
-  <si>
-    <t>1星拖尾</t>
+    <t>AuraId</t>
+  </si>
+  <si>
+    <t>Common</t>
   </si>
   <si>
     <t>Effects.Trail1</t>
   </si>
   <si>
-    <t>sandboxId://UI/Icon/Trail/Trail1Img.png</t>
-  </si>
-  <si>
-    <t>2星拖尾</t>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["01_Common"]</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
   </si>
   <si>
     <t>1.38e+6</t>
@@ -2342,10 +2342,10 @@
     <t>Effects.Trail2</t>
   </si>
   <si>
-    <t>sandboxId://UI/Icon/Trail/Trail2Img.png</t>
-  </si>
-  <si>
-    <t>3星拖尾</t>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["02_Uncommon"]</t>
+  </si>
+  <si>
+    <t>Rare</t>
   </si>
   <si>
     <t>3.32e+8</t>
@@ -2354,10 +2354,10 @@
     <t>Effects.Trail3</t>
   </si>
   <si>
-    <t>sandboxId://UI/Icon/Trail/Trail3Img.png</t>
-  </si>
-  <si>
-    <t>4星拖尾</t>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["03_Rare"]</t>
+  </si>
+  <si>
+    <t>Epic</t>
   </si>
   <si>
     <t>7.30e+10</t>
@@ -2366,10 +2366,10 @@
     <t>Effects.Trail4</t>
   </si>
   <si>
-    <t>sandboxId://UI/Icon/Trail/Trail4Img.png</t>
-  </si>
-  <si>
-    <t>5星拖尾</t>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["04_Epic"]</t>
+  </si>
+  <si>
+    <t>Legendary</t>
   </si>
   <si>
     <t>1.42e+13</t>
@@ -2378,151 +2378,7 @@
     <t>Effects.Trail5</t>
   </si>
   <si>
-    <t>sandboxId://UI/Icon/Trail/Trail5Img.png</t>
-  </si>
-  <si>
-    <t>6星拖尾</t>
-  </si>
-  <si>
-    <t>2.67e+15</t>
-  </si>
-  <si>
-    <t>Effects.Trail6</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail6Img.png</t>
-  </si>
-  <si>
-    <t>7星拖尾</t>
-  </si>
-  <si>
-    <t>4.69e+17</t>
-  </si>
-  <si>
-    <t>Effects.Trail7</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail7Img.png</t>
-  </si>
-  <si>
-    <t>8星拖尾</t>
-  </si>
-  <si>
-    <t>7.56e+19</t>
-  </si>
-  <si>
-    <t>Effects.Trail8</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail8Img.png</t>
-  </si>
-  <si>
-    <t>9星拖尾</t>
-  </si>
-  <si>
-    <t>1.18e+22</t>
-  </si>
-  <si>
-    <t>Effects.Trail9</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail9Img.png</t>
-  </si>
-  <si>
-    <t>10星拖尾</t>
-  </si>
-  <si>
-    <t>1.65e+24</t>
-  </si>
-  <si>
-    <t>Effects.Trail10</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail10Img.png</t>
-  </si>
-  <si>
-    <t>11星拖尾</t>
-  </si>
-  <si>
-    <t>2.27e+26</t>
-  </si>
-  <si>
-    <t>Effects.Trail11</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail11Img.png</t>
-  </si>
-  <si>
-    <t>12星拖尾</t>
-  </si>
-  <si>
-    <t>3.00e+28</t>
-  </si>
-  <si>
-    <t>Effects.Trail12</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail12Img.png</t>
-  </si>
-  <si>
-    <t>13星拖尾</t>
-  </si>
-  <si>
-    <t>2.23e+31</t>
-  </si>
-  <si>
-    <t>Effects.Trail13</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail13Img.png</t>
-  </si>
-  <si>
-    <t>14星拖尾</t>
-  </si>
-  <si>
-    <t>3.29e+33</t>
-  </si>
-  <si>
-    <t>Effects.Trail14</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail14Img.png</t>
-  </si>
-  <si>
-    <t>15星拖尾</t>
-  </si>
-  <si>
-    <t>4.78e+35</t>
-  </si>
-  <si>
-    <t>Effects.Trail15</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail15Img.png</t>
-  </si>
-  <si>
-    <t>16星拖尾</t>
-  </si>
-  <si>
-    <t>6.72e+37</t>
-  </si>
-  <si>
-    <t>Effects.Trail16</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail16Img.png</t>
-  </si>
-  <si>
-    <t>17星拖尾</t>
-  </si>
-  <si>
-    <t>9.61e+39</t>
-  </si>
-  <si>
-    <t>Effects.Trail17</t>
-  </si>
-  <si>
-    <t>sandboxId://UI/Icon/Trail/Trail17Img.png</t>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["05_Legendary"]</t>
   </si>
   <si>
     <t>关卡Id</t>
@@ -3665,7 +3521,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3681,17 +3537,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="fill" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4081,62 +3934,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="26" customHeight="1" spans="1:6">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="21" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4153,7 +4006,7 @@
       <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="24" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
@@ -4173,7 +4026,7 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="24" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4207,7 +4060,7 @@
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="25" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
@@ -4227,7 +4080,7 @@
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="24" t="s">
         <v>21</v>
       </c>
       <c r="F8" t="s">
@@ -4247,7 +4100,7 @@
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="24" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
@@ -4267,7 +4120,7 @@
       <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="25" t="s">
         <v>25</v>
       </c>
       <c r="F10" t="s">
@@ -4278,7 +4131,7 @@
   <hyperlinks>
     <hyperlink ref="E2" location="CommonConfig!A1" display="CommonConfig"/>
     <hyperlink ref="E4" location="SlicerConfig!A1" display="SlicerConfig"/>
-    <hyperlink ref="E6" location="TrailConfig!A1" display="TrailConfig"/>
+    <hyperlink ref="E6" location="TrailConfig!A1" display="AuraConfig"/>
     <hyperlink ref="E7" location="AreaRefreshData!A1" display="AreaRefreshData"/>
     <hyperlink ref="E8" location="ItemData!A1" display="ItemData"/>
     <hyperlink ref="E9" location="AreaConfig!A1" display="AreaConfig"/>
@@ -4303,13 +4156,13 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>826</v>
+        <v>778</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>827</v>
+        <v>779</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>828</v>
+        <v>780</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:5">
@@ -4317,10 +4170,10 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>829</v>
+        <v>781</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>830</v>
+        <v>782</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
@@ -4336,576 +4189,576 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>831</v>
+        <v>783</v>
       </c>
       <c r="B4" s="2">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>832</v>
+        <v>784</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>833</v>
+        <v>785</v>
       </c>
       <c r="B5" s="2">
         <v>122</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>834</v>
+        <v>786</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>835</v>
+        <v>787</v>
       </c>
       <c r="B6" s="2">
         <v>520</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>836</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>837</v>
+        <v>789</v>
       </c>
       <c r="B7" s="2">
         <v>2176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>838</v>
+        <v>790</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>839</v>
+        <v>791</v>
       </c>
       <c r="B8" s="2">
         <v>9101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>840</v>
+        <v>792</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>842</v>
+        <v>793</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>794</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>843</v>
+        <v>795</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>845</v>
+        <v>796</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>797</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>846</v>
+        <v>798</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>848</v>
+        <v>799</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>800</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>849</v>
+        <v>801</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>851</v>
+        <v>802</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>803</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>852</v>
+        <v>804</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>854</v>
+        <v>805</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>806</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>855</v>
+        <v>807</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>857</v>
+        <v>808</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>809</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>858</v>
+        <v>810</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>859</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>860</v>
+        <v>811</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>812</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>861</v>
+        <v>813</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>863</v>
+        <v>814</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>815</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>864</v>
+        <v>816</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>865</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>866</v>
+        <v>817</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>818</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>867</v>
+        <v>819</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>869</v>
+        <v>820</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>821</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>870</v>
+        <v>822</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>872</v>
+        <v>823</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>824</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>873</v>
+        <v>825</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>875</v>
+        <v>826</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>827</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>876</v>
+        <v>828</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>878</v>
+        <v>829</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>830</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>879</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>880</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>881</v>
+        <v>832</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>833</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>882</v>
+        <v>834</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>884</v>
+        <v>835</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>836</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>885</v>
+        <v>837</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>887</v>
+        <v>838</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>839</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>888</v>
+        <v>840</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="B25" s="28" t="s">
-        <v>890</v>
+        <v>841</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>842</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>891</v>
+        <v>843</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>893</v>
+        <v>844</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>845</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>894</v>
+        <v>846</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>896</v>
+        <v>847</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>848</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>897</v>
+        <v>849</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>898</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>899</v>
+        <v>850</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>851</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>900</v>
+        <v>852</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="B29" s="28" t="s">
-        <v>902</v>
+        <v>853</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>854</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>903</v>
+        <v>855</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>905</v>
+        <v>856</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>857</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>906</v>
+        <v>858</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>908</v>
+        <v>859</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>860</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>909</v>
+        <v>861</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>911</v>
+        <v>862</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>863</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>912</v>
+        <v>864</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>914</v>
+        <v>865</v>
+      </c>
+      <c r="B33" s="27" t="s">
+        <v>866</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>915</v>
+        <v>867</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="B34" s="28" t="s">
-        <v>917</v>
+        <v>868</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>869</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>918</v>
+        <v>870</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="B35" s="28" t="s">
-        <v>920</v>
+        <v>871</v>
+      </c>
+      <c r="B35" s="27" t="s">
+        <v>872</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>921</v>
+        <v>873</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="B36" s="28" t="s">
-        <v>923</v>
+        <v>874</v>
+      </c>
+      <c r="B36" s="27" t="s">
+        <v>875</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>924</v>
+        <v>876</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="B37" s="28" t="s">
-        <v>926</v>
+        <v>877</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>878</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>927</v>
+        <v>879</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>928</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>929</v>
+        <v>880</v>
+      </c>
+      <c r="B38" s="27" t="s">
+        <v>881</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>930</v>
+        <v>882</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>932</v>
+        <v>883</v>
+      </c>
+      <c r="B39" s="27" t="s">
+        <v>884</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>933</v>
+        <v>885</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>934</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>935</v>
+        <v>886</v>
+      </c>
+      <c r="B40" s="27" t="s">
+        <v>887</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>936</v>
+        <v>888</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>937</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>938</v>
+        <v>889</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>890</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>939</v>
+        <v>891</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="B42" s="28" t="s">
-        <v>941</v>
+        <v>892</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>893</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>942</v>
+        <v>894</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>943</v>
-      </c>
-      <c r="B43" s="29" t="s">
-        <v>944</v>
+        <v>895</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>896</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>945</v>
+        <v>897</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>946</v>
-      </c>
-      <c r="B44" s="29" t="s">
-        <v>947</v>
+        <v>898</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>899</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>948</v>
+        <v>900</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>949</v>
-      </c>
-      <c r="B45" s="29" t="s">
-        <v>950</v>
+        <v>901</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>902</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>951</v>
+        <v>903</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>952</v>
-      </c>
-      <c r="B46" s="29" t="s">
-        <v>953</v>
+        <v>904</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>905</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>954</v>
+        <v>906</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="B47" s="29" t="s">
-        <v>956</v>
+        <v>907</v>
+      </c>
+      <c r="B47" s="28" t="s">
+        <v>908</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>957</v>
+        <v>909</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>958</v>
-      </c>
-      <c r="B48" s="29" t="s">
-        <v>959</v>
+        <v>910</v>
+      </c>
+      <c r="B48" s="28" t="s">
+        <v>911</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>960</v>
+        <v>912</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="B49" s="29" t="s">
-        <v>962</v>
+        <v>913</v>
+      </c>
+      <c r="B49" s="28" t="s">
+        <v>914</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>963</v>
+        <v>915</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>964</v>
-      </c>
-      <c r="B50" s="29" t="s">
-        <v>965</v>
+        <v>916</v>
+      </c>
+      <c r="B50" s="28" t="s">
+        <v>917</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>966</v>
+        <v>918</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>967</v>
-      </c>
-      <c r="B51" s="29" t="s">
-        <v>968</v>
+        <v>919</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>920</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>969</v>
+        <v>921</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>970</v>
-      </c>
-      <c r="B52" s="29" t="s">
-        <v>971</v>
+        <v>922</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>923</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>972</v>
+        <v>924</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="B53" s="29" t="s">
-        <v>974</v>
+        <v>925</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>926</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>975</v>
+        <v>927</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="B54" s="29" t="s">
-        <v>977</v>
+        <v>928</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>929</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>978</v>
+        <v>930</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>979</v>
-      </c>
-      <c r="B55" s="29" t="s">
-        <v>980</v>
+        <v>931</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>932</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>981</v>
+        <v>933</v>
       </c>
     </row>
   </sheetData>
@@ -4920,389 +4773,389 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="44.175" style="16" customWidth="1"/>
-    <col min="2" max="2" width="71.3583333333333" style="16" customWidth="1"/>
-    <col min="3" max="3" width="123.558333333333" style="16" customWidth="1"/>
-    <col min="4" max="4" width="82.8666666666667" style="16" customWidth="1"/>
-    <col min="5" max="6" width="9" style="16"/>
-    <col min="7" max="7" width="81.1833333333333" style="16" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="16"/>
+    <col min="1" max="1" width="44.175" style="15" customWidth="1"/>
+    <col min="2" max="2" width="71.3583333333333" style="15" customWidth="1"/>
+    <col min="3" max="3" width="123.558333333333" style="15" customWidth="1"/>
+    <col min="4" max="4" width="82.8666666666667" style="15" customWidth="1"/>
+    <col min="5" max="6" width="9" style="15"/>
+    <col min="7" max="7" width="81.1833333333333" style="15" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" s="16" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
-      <c r="A1" s="17" t="s">
+    <row r="1" s="15" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
+      <c r="A1" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
-    <row r="2" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+    <row r="2" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
-    <row r="3" s="16" customFormat="1" ht="91" customHeight="1" spans="1:7">
-      <c r="A3" s="17" t="s">
+    <row r="3" s="15" customFormat="1" ht="91" customHeight="1" spans="1:7">
+      <c r="A3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
-    <row r="4" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A4" s="17" t="s">
+    <row r="4" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A4" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
     </row>
-    <row r="5" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A5" s="17" t="s">
+    <row r="5" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="16">
         <v>10</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
-    <row r="6" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A6" s="17" t="s">
+    <row r="6" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
     </row>
-    <row r="7" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A7" s="19" t="s">
+    <row r="7" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A7" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
     </row>
-    <row r="8" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A8" s="19" t="s">
+    <row r="8" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A8" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
     </row>
-    <row r="9" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A9" s="19" t="s">
+    <row r="9" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A9" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
     </row>
-    <row r="10" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A10" s="17" t="s">
+    <row r="10" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A10" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
     </row>
-    <row r="11" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A11" s="17" t="s">
+    <row r="11" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A11" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
     </row>
-    <row r="12" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A12" s="17" t="s">
+    <row r="12" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
     </row>
-    <row r="13" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
+    <row r="13" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
     </row>
-    <row r="14" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+    <row r="14" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
     </row>
-    <row r="15" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+    <row r="15" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
     </row>
-    <row r="16" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
+    <row r="16" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
     </row>
-    <row r="17" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
+    <row r="17" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
     </row>
-    <row r="18" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
+    <row r="18" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
     </row>
-    <row r="19" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+    <row r="19" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
     </row>
-    <row r="20" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+    <row r="20" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
     </row>
-    <row r="21" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+    <row r="21" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
     </row>
-    <row r="22" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
+    <row r="22" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
     </row>
-    <row r="23" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
+    <row r="23" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
     </row>
-    <row r="24" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
+    <row r="24" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
-    <row r="25" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
+    <row r="25" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
     </row>
-    <row r="26" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
+    <row r="26" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
     </row>
-    <row r="27" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
+    <row r="27" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="C27" s="16"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
     </row>
-    <row r="28" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
+    <row r="28" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
     </row>
-    <row r="29" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
+    <row r="29" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
     </row>
-    <row r="30" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
+    <row r="30" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
     </row>
-    <row r="31" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
+    <row r="31" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
     </row>
-    <row r="32" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
+    <row r="32" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
     </row>
-    <row r="33" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
+    <row r="33" s="15" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
     </row>
-    <row r="34" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
+    <row r="34" s="15" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
     </row>
-    <row r="35" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
+    <row r="35" s="15" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
     </row>
-    <row r="36" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
+    <row r="36" s="15" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -5668,943 +5521,943 @@
   <dimension ref="A1:E55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" width="37.75" style="14" customWidth="1"/>
+    <col min="1" max="2" width="37.75" style="13" customWidth="1"/>
     <col min="3" max="3" width="33.0833333333333" customWidth="1"/>
     <col min="4" max="5" width="40.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="14" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="15">
+      <c r="A4" s="14">
         <v>1</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="14">
         <v>1</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="14">
         <v>80</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="14">
         <v>3</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="15">
+      <c r="A5" s="14">
         <v>2</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="14">
         <v>2</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="14">
         <v>4</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="14">
         <v>3</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="15">
+      <c r="A6" s="14">
         <v>3</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="14">
         <v>3</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="14">
         <v>4</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="14">
         <v>3</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="15">
+      <c r="A7" s="14">
         <v>4</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="14">
         <v>4</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="14">
         <v>4</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <v>3</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="15">
+      <c r="A8" s="14">
         <v>5</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="14">
         <v>5</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="14">
         <v>4</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="14">
         <v>3</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="15">
+      <c r="A9" s="14">
         <v>6</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="14">
         <v>6</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <v>4</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <v>3</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="15">
+      <c r="A10" s="14">
         <v>7</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="14">
         <v>7</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="14">
         <v>4</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <v>3</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="15">
+      <c r="A11" s="14">
         <v>8</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="14">
         <v>8</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="14">
         <v>4</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="14">
         <v>3</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="15">
+      <c r="A12" s="14">
         <v>9</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="14">
         <v>9</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <v>4</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <v>3</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="15">
+      <c r="A13" s="14">
         <v>10</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="14">
         <v>10</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="14">
         <v>4</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <v>3</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="15">
+      <c r="A14" s="14">
         <v>11</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="14">
         <v>11</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <v>4</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <v>3</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="15">
+      <c r="A15" s="14">
         <v>12</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="14">
         <v>12</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
         <v>4</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <v>3</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="15">
+      <c r="A16" s="14">
         <v>13</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <v>13</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="15">
+      <c r="A17" s="14">
         <v>14</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <v>14</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="14">
         <v>4</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="14">
         <v>3</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="15">
+      <c r="A18" s="14">
         <v>15</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <v>15</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="15">
+      <c r="A19" s="14">
         <v>16</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="14">
         <v>16</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="14">
         <v>4</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="14">
         <v>3</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="15">
+      <c r="A20" s="14">
         <v>17</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="14">
         <v>17</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="15">
+      <c r="A21" s="14">
         <v>18</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="14">
         <v>18</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="14">
         <v>4</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="14">
         <v>3</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="15">
+      <c r="A22" s="14">
         <v>19</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="14">
         <v>19</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="14">
         <v>4</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="14">
         <v>3</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="15">
+      <c r="A23" s="14">
         <v>20</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="14">
         <v>20</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="14">
         <v>4</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="15">
+      <c r="A24" s="14">
         <v>21</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="14">
         <v>21</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="14">
         <v>4</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="14">
         <v>3</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="15">
+      <c r="A25" s="14">
         <v>22</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="14">
         <v>22</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="14">
         <v>4</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="14">
         <v>3</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="15">
+      <c r="A26" s="14">
         <v>23</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="14">
         <v>23</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="14">
         <v>4</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="14">
         <v>3</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="15">
+      <c r="A27" s="14">
         <v>24</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="14">
         <v>24</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="14">
         <v>4</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="14">
         <v>3</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="15">
+      <c r="A28" s="14">
         <v>25</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="14">
         <v>25</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="14">
         <v>4</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="14">
         <v>3</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="15">
+      <c r="A29" s="14">
         <v>26</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="14">
         <v>26</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="14">
         <v>4</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="14">
         <v>3</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="15">
+      <c r="A30" s="14">
         <v>27</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="14">
         <v>27</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="14">
         <v>4</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="14">
         <v>3</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="15">
+      <c r="A31" s="14">
         <v>28</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="14">
         <v>28</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="14">
         <v>4</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="14">
         <v>3</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="15">
+      <c r="A32" s="14">
         <v>29</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="14">
         <v>29</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="14">
         <v>4</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="14">
         <v>3</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="15">
+      <c r="A33" s="14">
         <v>30</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="14">
         <v>30</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="14">
         <v>4</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="14">
         <v>3</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="15">
+      <c r="A34" s="14">
         <v>31</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="14">
         <v>31</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="14">
         <v>4</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="14">
         <v>3</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="15">
+      <c r="A35" s="14">
         <v>32</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="14">
         <v>32</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="14">
         <v>4</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="14">
         <v>3</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="15">
+      <c r="A36" s="14">
         <v>33</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="14">
         <v>33</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="14">
         <v>4</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="14">
         <v>3</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="15">
+      <c r="A37" s="14">
         <v>34</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="14">
         <v>34</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="14">
         <v>4</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="14">
         <v>3</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="15">
+      <c r="A38" s="14">
         <v>35</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="14">
         <v>35</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="14">
         <v>4</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="14">
         <v>3</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="15">
+      <c r="A39" s="14">
         <v>36</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="14">
         <v>36</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>4</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="14">
         <v>3</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="15">
+      <c r="A40" s="14">
         <v>37</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="14">
         <v>37</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>4</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="14">
         <v>3</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="15">
+      <c r="A41" s="14">
         <v>38</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="14">
         <v>38</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>4</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="14">
         <v>3</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="15">
+      <c r="A42" s="14">
         <v>39</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="14">
         <v>39</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>4</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="14">
         <v>3</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="15">
+      <c r="A43" s="14">
         <v>40</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="14">
         <v>40</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>4</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="14">
         <v>3</v>
       </c>
-      <c r="E43" s="15" t="s">
+      <c r="E43" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="15">
+      <c r="A44" s="14">
         <v>41</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="14">
         <v>41</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>4</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="14">
         <v>3</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="E44" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="15">
+      <c r="A45" s="14">
         <v>42</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="14">
         <v>42</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>4</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="14">
         <v>3</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="E45" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="15">
+      <c r="A46" s="14">
         <v>43</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="14">
         <v>43</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="14">
         <v>4</v>
       </c>
-      <c r="D46" s="15">
+      <c r="D46" s="14">
         <v>3</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="15">
+      <c r="A47" s="14">
         <v>44</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="14">
         <v>44</v>
       </c>
-      <c r="C47" s="15">
+      <c r="C47" s="14">
         <v>4</v>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="14">
         <v>3</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="15">
+      <c r="A48" s="14">
         <v>45</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48" s="14">
         <v>45</v>
       </c>
-      <c r="C48" s="15">
+      <c r="C48" s="14">
         <v>4</v>
       </c>
-      <c r="D48" s="15">
+      <c r="D48" s="14">
         <v>3</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="15">
+      <c r="A49" s="14">
         <v>46</v>
       </c>
-      <c r="B49" s="15">
+      <c r="B49" s="14">
         <v>46</v>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="14">
         <v>4</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="14">
         <v>3</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="15">
+      <c r="A50" s="14">
         <v>47</v>
       </c>
-      <c r="B50" s="15">
+      <c r="B50" s="14">
         <v>47</v>
       </c>
-      <c r="C50" s="15">
+      <c r="C50" s="14">
         <v>4</v>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="14">
         <v>3</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="15">
+      <c r="A51" s="14">
         <v>48</v>
       </c>
-      <c r="B51" s="15">
+      <c r="B51" s="14">
         <v>48</v>
       </c>
-      <c r="C51" s="15">
+      <c r="C51" s="14">
         <v>4</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="14">
         <v>3</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="15">
+      <c r="A52" s="14">
         <v>49</v>
       </c>
-      <c r="B52" s="15">
+      <c r="B52" s="14">
         <v>49</v>
       </c>
-      <c r="C52" s="15">
+      <c r="C52" s="14">
         <v>4</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="14">
         <v>3</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="15">
+      <c r="A53" s="14">
         <v>50</v>
       </c>
-      <c r="B53" s="15">
+      <c r="B53" s="14">
         <v>50</v>
       </c>
-      <c r="C53" s="15">
+      <c r="C53" s="14">
         <v>4</v>
       </c>
-      <c r="D53" s="15">
+      <c r="D53" s="14">
         <v>3</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="E53" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="15">
+      <c r="A54" s="14">
         <v>51</v>
       </c>
-      <c r="B54" s="15">
+      <c r="B54" s="14">
         <v>51</v>
       </c>
-      <c r="C54" s="15">
+      <c r="C54" s="14">
         <v>4</v>
       </c>
-      <c r="D54" s="15">
+      <c r="D54" s="14">
         <v>3</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="E54" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="15">
+      <c r="A55" s="14">
         <v>52</v>
       </c>
-      <c r="B55" s="15">
+      <c r="B55" s="14">
         <v>52</v>
       </c>
-      <c r="C55" s="15">
+      <c r="C55" s="14">
         <v>4</v>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="14">
         <v>3</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" s="14" t="s">
         <v>89</v>
       </c>
     </row>
@@ -6620,801 +6473,801 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="27.75" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="25.175" style="10" customWidth="1"/>
-    <col min="2" max="2" width="13.575" style="10" customWidth="1"/>
-    <col min="3" max="3" width="127.141666666667" style="10" customWidth="1"/>
-    <col min="4" max="4" width="49" style="10" customWidth="1"/>
-    <col min="5" max="5" width="92.9666666666667" style="11" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="25.175" style="9" customWidth="1"/>
+    <col min="2" max="2" width="13.575" style="9" customWidth="1"/>
+    <col min="3" max="3" width="127.141666666667" style="9" customWidth="1"/>
+    <col min="4" max="4" width="49" style="9" customWidth="1"/>
+    <col min="5" max="5" width="92.9666666666667" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="12">
+      <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="12">
+      <c r="A5" s="11">
         <v>2</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>2</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="12">
+      <c r="A6" s="11">
         <v>3</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="12">
+      <c r="A7" s="11">
         <v>4</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>4</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="12">
+      <c r="A8" s="11">
         <v>5</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>5</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="12">
+      <c r="A9" s="11">
         <v>6</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>6</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="12">
+      <c r="A10" s="11">
         <v>7</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>7</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="12">
+      <c r="A11" s="11">
         <v>8</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>8</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="12">
+      <c r="A12" s="11">
         <v>9</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>9</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="12">
+      <c r="A13" s="11">
         <v>10</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="11">
         <v>10</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="12">
+      <c r="A14" s="11">
         <v>11</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="11">
         <v>11</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="12">
+      <c r="A15" s="11">
         <v>12</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="11">
         <v>12</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="12">
+      <c r="A16" s="11">
         <v>13</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="11">
         <v>13</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="12">
+      <c r="A17" s="11">
         <v>14</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="11">
         <v>14</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="12">
+      <c r="A18" s="11">
         <v>15</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="11">
         <v>15</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="12">
+      <c r="A19" s="11">
         <v>16</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="11">
         <v>16</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="12">
+      <c r="A20" s="11">
         <v>17</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="11">
         <v>17</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="12">
+      <c r="A21" s="11">
         <v>18</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="11">
         <v>18</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="12">
+      <c r="A22" s="11">
         <v>19</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <v>19</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="12">
+      <c r="A23" s="11">
         <v>20</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="11">
         <v>20</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="12">
+      <c r="A24" s="11">
         <v>21</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="11">
         <v>21</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="12">
+      <c r="A25" s="11">
         <v>22</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="11">
         <v>22</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="12">
+      <c r="A26" s="11">
         <v>23</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="11">
         <v>23</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="12">
+      <c r="A27" s="11">
         <v>24</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="11">
         <v>24</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="12">
+      <c r="A28" s="11">
         <v>25</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="11">
         <v>25</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="12">
+      <c r="A29" s="11">
         <v>26</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="11">
         <v>26</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="12">
+      <c r="A30" s="11">
         <v>27</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="11">
         <v>27</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="12">
+      <c r="A31" s="11">
         <v>28</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="11">
         <v>28</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="12">
+      <c r="A32" s="11">
         <v>29</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="11">
         <v>29</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="12">
+      <c r="A33" s="11">
         <v>30</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="11">
         <v>30</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="12">
+      <c r="A34" s="11">
         <v>31</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="11">
         <v>31</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="12">
+      <c r="A35" s="11">
         <v>32</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="11">
         <v>32</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="12">
+      <c r="A36" s="11">
         <v>33</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="11">
         <v>33</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="12">
+      <c r="A37" s="11">
         <v>34</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="11">
         <v>34</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="12">
+      <c r="A38" s="11">
         <v>35</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="11">
         <v>35</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="12">
+      <c r="A39" s="11">
         <v>36</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="11">
         <v>36</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="12">
+      <c r="A40" s="11">
         <v>37</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="11">
         <v>37</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="12">
+      <c r="A41" s="11">
         <v>38</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="11">
         <v>38</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="12">
+      <c r="A42" s="11">
         <v>39</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="11">
         <v>39</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="11" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="13">
+      <c r="A43" s="12">
         <v>40</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="12">
         <v>40</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="13">
+      <c r="A44" s="12">
         <v>41</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="12">
         <v>41</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="13">
+      <c r="A45" s="12">
         <v>42</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="12">
         <v>42</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="13">
+      <c r="A46" s="12">
         <v>43</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="12">
         <v>43</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="13">
+      <c r="A47" s="12">
         <v>44</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="12">
         <v>44</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="13">
+      <c r="A48" s="12">
         <v>45</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="12">
         <v>45</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="13">
+      <c r="A49" s="12">
         <v>46</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="12">
         <v>46</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="13">
+      <c r="A50" s="12">
         <v>47</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="12">
         <v>47</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="13">
+      <c r="A51" s="12">
         <v>48</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="12">
         <v>48</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="13">
+      <c r="A52" s="12">
         <v>49</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="12">
         <v>49</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="13">
+      <c r="A53" s="12">
         <v>50</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="12">
         <v>50</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="13">
+      <c r="A54" s="12">
         <v>51</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="12">
         <v>51</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="13">
+      <c r="A55" s="12">
         <v>52</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="12">
         <v>52</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="13"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="13"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="C58" s="13"/>
+      <c r="C58" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7532,7 +7385,7 @@
         <f>CEILING(A4/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="8">
         <v>73689874069532</v>
       </c>
       <c r="G4" s="8" t="s">
@@ -7559,7 +7412,7 @@
         <f t="shared" ref="E5:E36" si="0">CEILING(A5/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <v>103338086714343</v>
       </c>
       <c r="G5" s="8" t="s">
@@ -7588,7 +7441,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <v>114468149232543</v>
       </c>
       <c r="G6" s="8" t="s">
@@ -7617,7 +7470,7 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <v>102034222005672</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -7646,7 +7499,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>83505287199254</v>
       </c>
       <c r="G8" s="8" t="s">
@@ -7673,7 +7526,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <v>82413393212572</v>
       </c>
       <c r="G9" s="8" t="s">
@@ -7701,7 +7554,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>93587171790136</v>
       </c>
       <c r="G10" s="8" t="s">
@@ -7729,7 +7582,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <v>98881391823727</v>
       </c>
       <c r="G11" s="8" t="s">
@@ -7757,7 +7610,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <v>140583336060167</v>
       </c>
       <c r="G12" s="8" t="s">
@@ -7784,7 +7637,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="8">
         <v>111194186656631</v>
       </c>
       <c r="G13" s="8" t="s">
@@ -7811,7 +7664,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="8">
         <v>133914186848952</v>
       </c>
       <c r="G14" s="8" t="s">
@@ -7838,7 +7691,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="8">
         <v>122198581325096</v>
       </c>
       <c r="G15" s="8" t="s">
@@ -7865,7 +7718,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="8">
         <v>137046890645413</v>
       </c>
       <c r="G16" s="8" t="s">
@@ -7896,7 +7749,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="8">
         <v>102352328211075</v>
       </c>
       <c r="G17" s="8" t="s">
@@ -7927,7 +7780,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="8">
         <v>82050572064304</v>
       </c>
       <c r="G18" s="8" t="s">
@@ -7958,7 +7811,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="8">
         <v>78831531789183</v>
       </c>
       <c r="G19" s="8" t="s">
@@ -7989,7 +7842,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="8">
         <v>108041083429458</v>
       </c>
       <c r="G20" s="8" t="s">
@@ -8020,7 +7873,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="8">
         <v>86299665819505</v>
       </c>
       <c r="G21" s="8" t="s">
@@ -8051,7 +7904,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="8">
         <v>123569723967761</v>
       </c>
       <c r="G22" s="8" t="s">
@@ -8082,7 +7935,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="8">
         <v>119546448004051</v>
       </c>
       <c r="G23" s="8" t="s">
@@ -8113,7 +7966,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="8">
         <v>91007101306341</v>
       </c>
       <c r="G24" s="8" t="s">
@@ -8144,7 +7997,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="8">
         <v>91391954516503</v>
       </c>
       <c r="G25" s="8" t="s">
@@ -8175,7 +8028,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="8">
         <v>109276220541606</v>
       </c>
       <c r="G26" s="8" t="s">
@@ -8206,7 +8059,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="8">
         <v>108792020810626</v>
       </c>
       <c r="G27" s="8" t="s">
@@ -8237,7 +8090,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="8">
         <v>94990895501990</v>
       </c>
       <c r="G28" s="8" t="s">
@@ -8268,7 +8121,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="8">
         <v>92053411642730</v>
       </c>
       <c r="G29" s="8" t="s">
@@ -8299,7 +8152,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="8">
         <v>129094955837159</v>
       </c>
       <c r="G30" s="8" t="s">
@@ -8330,7 +8183,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="8">
         <v>136720402016106</v>
       </c>
       <c r="G31" s="8" t="s">
@@ -8361,7 +8214,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="8">
         <v>103985740716894</v>
       </c>
       <c r="G32" s="8" t="s">
@@ -8392,7 +8245,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="8">
         <v>110363379748775</v>
       </c>
       <c r="G33" s="8" t="s">
@@ -8419,7 +8272,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="8">
         <v>130735151388109</v>
       </c>
       <c r="G34" s="8" t="s">
@@ -8446,7 +8299,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="8">
         <v>112469820699203</v>
       </c>
       <c r="G35" s="8" t="s">
@@ -8473,7 +8326,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="8">
         <v>104485794834544</v>
       </c>
       <c r="G36" s="8" t="s">
@@ -8504,7 +8357,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>6</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="8">
         <v>99220241284612</v>
       </c>
       <c r="G37" s="8" t="s">
@@ -8531,7 +8384,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>7</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="8">
         <v>80947939739818</v>
       </c>
       <c r="G38" s="8" t="s">
@@ -8558,7 +8411,7 @@
         <f t="shared" ref="E39:E72" si="1">CEILING(A39/4,1)</f>
         <v>9</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="8">
         <v>107316878006177</v>
       </c>
       <c r="G39" s="8" t="s">
@@ -8589,7 +8442,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="8">
         <v>81581045315216</v>
       </c>
       <c r="G40" s="8" t="s">
@@ -8620,7 +8473,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="8">
         <v>112660123650049</v>
       </c>
       <c r="G41" s="8" t="s">
@@ -8647,7 +8500,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="8">
         <v>105948548039431</v>
       </c>
       <c r="G42" s="8" t="s">
@@ -8674,7 +8527,7 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="8">
         <v>136608949835509</v>
       </c>
       <c r="G43" s="8" t="s">
@@ -8701,7 +8554,7 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="8">
         <v>123814344941081</v>
       </c>
       <c r="G44" s="8" t="s">
@@ -8728,7 +8581,7 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="8">
         <v>70631811357234</v>
       </c>
       <c r="G45" s="8" t="s">
@@ -8755,7 +8608,7 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="8">
         <v>121882306399734</v>
       </c>
       <c r="G46" s="8" t="s">
@@ -8782,7 +8635,7 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="8">
         <v>98362111955314</v>
       </c>
       <c r="G47" s="8" t="s">
@@ -8809,7 +8662,7 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="8">
         <v>87499152943626</v>
       </c>
       <c r="G48" s="8" t="s">
@@ -8836,7 +8689,7 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="8">
         <v>94526628741923</v>
       </c>
       <c r="G49" s="8" t="s">
@@ -8863,7 +8716,7 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50" s="8">
         <v>135071120477292</v>
       </c>
       <c r="G50" s="8" t="s">
@@ -8890,7 +8743,7 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="8">
         <v>73644651229136</v>
       </c>
       <c r="G51" s="8" t="s">
@@ -8917,7 +8770,7 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52" s="8">
         <v>77926265714695</v>
       </c>
       <c r="G52" s="8" t="s">
@@ -8944,7 +8797,7 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53" s="8">
         <v>82854353471706</v>
       </c>
       <c r="G53" s="8" t="s">
@@ -8971,7 +8824,7 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F54" s="8">
         <v>77671502371070</v>
       </c>
       <c r="G54" s="8" t="s">
@@ -8998,7 +8851,7 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F55" s="7">
+      <c r="F55" s="8">
         <v>70793360263168</v>
       </c>
       <c r="G55" s="8" t="s">
@@ -9025,7 +8878,7 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56" s="8">
         <v>84818213347817</v>
       </c>
       <c r="G56" s="8" t="s">
@@ -9052,7 +8905,7 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F57" s="8">
         <v>91851759457969</v>
       </c>
       <c r="G57" s="8" t="s">
@@ -9079,7 +8932,7 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F58" s="8">
         <v>121890208198805</v>
       </c>
       <c r="G58" s="8" t="s">
@@ -9106,7 +8959,7 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F59" s="7">
+      <c r="F59" s="8">
         <v>117985852407168</v>
       </c>
       <c r="G59" s="8" t="s">
@@ -9133,7 +8986,7 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F60" s="8">
         <v>97339206973141</v>
       </c>
       <c r="G60" s="8" t="s">
@@ -9160,7 +9013,7 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F61" s="8">
         <v>91021502703797</v>
       </c>
       <c r="G61" s="8" t="s">
@@ -9187,7 +9040,7 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F62" s="7">
+      <c r="F62" s="8">
         <v>118793829418414</v>
       </c>
       <c r="G62" s="8" t="s">
@@ -9214,7 +9067,7 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F63" s="7">
+      <c r="F63" s="8">
         <v>108919245506457</v>
       </c>
       <c r="G63" s="8" t="s">
@@ -9241,7 +9094,7 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F64" s="8">
         <v>135998992968408</v>
       </c>
       <c r="G64" s="8" t="s">
@@ -9268,7 +9121,7 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F65" s="8">
         <v>124995167587191</v>
       </c>
       <c r="G65" s="8" t="s">
@@ -9295,7 +9148,7 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66" s="8">
         <v>100207039759139</v>
       </c>
       <c r="G66" s="8" t="s">
@@ -9322,7 +9175,7 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F67" s="8">
         <v>117284808467540</v>
       </c>
       <c r="G67" s="8" t="s">
@@ -9349,7 +9202,7 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F68" s="8">
         <v>100856293823266</v>
       </c>
       <c r="G68" s="8" t="s">
@@ -9376,7 +9229,7 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F69" s="7">
+      <c r="F69" s="8">
         <v>131767978667574</v>
       </c>
       <c r="G69" s="8" t="s">
@@ -9403,7 +9256,7 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70" s="8">
         <v>137793066084531</v>
       </c>
       <c r="G70" s="8" t="s">
@@ -9430,7 +9283,7 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71" s="8">
         <v>89446188580427</v>
       </c>
       <c r="G71" s="8" t="s">
@@ -9457,7 +9310,7 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F72" s="8">
         <v>122719253084629</v>
       </c>
       <c r="G72" s="8" t="s">
@@ -9484,7 +9337,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>15</v>
       </c>
-      <c r="F73" s="7">
+      <c r="F73" s="8">
         <v>112549310275337</v>
       </c>
       <c r="G73" s="8" t="s">
@@ -9511,7 +9364,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F74" s="7">
+      <c r="F74" s="8">
         <v>88430290010781</v>
       </c>
       <c r="G74" s="8" t="s">
@@ -9538,7 +9391,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F75" s="7">
+      <c r="F75" s="8">
         <v>71786460797721</v>
       </c>
       <c r="G75" s="8" t="s">
@@ -9565,7 +9418,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F76" s="8">
         <v>97338088026484</v>
       </c>
       <c r="G76" s="8" t="s">
@@ -9592,7 +9445,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F77" s="8">
         <v>111210837018880</v>
       </c>
       <c r="G77" s="8" t="s">
@@ -9619,7 +9472,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F78" s="8">
         <v>91454753076661</v>
       </c>
       <c r="G78" s="8" t="s">
@@ -9646,7 +9499,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F79" s="8">
         <v>140372090697167</v>
       </c>
       <c r="G79" s="8" t="s">
@@ -9673,7 +9526,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F80" s="8">
         <v>85844805634635</v>
       </c>
       <c r="G80" s="8" t="s">
@@ -9700,7 +9553,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F81" s="7">
+      <c r="F81" s="8">
         <v>121461526979401</v>
       </c>
       <c r="G81" s="8" t="s">
@@ -9727,7 +9580,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F82" s="7">
+      <c r="F82" s="8">
         <v>119745475735524</v>
       </c>
       <c r="G82" s="8" t="s">
@@ -9754,7 +9607,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F83" s="7">
+      <c r="F83" s="8">
         <v>101894479505985</v>
       </c>
       <c r="G83" s="8" t="s">
@@ -9781,7 +9634,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F84" s="7">
+      <c r="F84" s="8">
         <v>130984354600200</v>
       </c>
       <c r="G84" s="8" t="s">
@@ -9808,7 +9661,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F85" s="7">
+      <c r="F85" s="8">
         <v>139575750428458</v>
       </c>
       <c r="G85" s="8" t="s">
@@ -9835,7 +9688,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F86" s="7">
+      <c r="F86" s="8">
         <v>111543784097462</v>
       </c>
       <c r="G86" s="8" t="s">
@@ -9862,7 +9715,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F87" s="7">
+      <c r="F87" s="8">
         <v>104244387773955</v>
       </c>
       <c r="G87" s="8" t="s">
@@ -9889,7 +9742,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F88" s="7">
+      <c r="F88" s="8">
         <v>136776890462387</v>
       </c>
       <c r="G88" s="8" t="s">
@@ -9916,7 +9769,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F89" s="7">
+      <c r="F89" s="8">
         <v>126165124926341</v>
       </c>
       <c r="G89" s="8" t="s">
@@ -9943,7 +9796,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F90" s="7">
+      <c r="F90" s="8">
         <v>76143760243972</v>
       </c>
       <c r="G90" s="8" t="s">
@@ -9970,7 +9823,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F91" s="7">
+      <c r="F91" s="8">
         <v>73975383470183</v>
       </c>
       <c r="G91" s="8" t="s">
@@ -9997,7 +9850,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F92" s="7">
+      <c r="F92" s="8">
         <v>110779582383706</v>
       </c>
       <c r="G92" s="8" t="s">
@@ -10024,7 +9877,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F93" s="7">
+      <c r="F93" s="8">
         <v>139231009266383</v>
       </c>
       <c r="G93" s="8" t="s">
@@ -10051,7 +9904,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F94" s="7">
+      <c r="F94" s="8">
         <v>122330740858585</v>
       </c>
       <c r="G94" s="8" t="s">
@@ -10078,7 +9931,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F95" s="7">
+      <c r="F95" s="8">
         <v>117103663687356</v>
       </c>
       <c r="G95" s="8" t="s">
@@ -10105,7 +9958,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F96" s="7">
+      <c r="F96" s="8">
         <v>103139070075508</v>
       </c>
       <c r="G96" s="8" t="s">
@@ -10132,7 +9985,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F97" s="7">
+      <c r="F97" s="8">
         <v>88725487654147</v>
       </c>
       <c r="G97" s="8" t="s">
@@ -10159,7 +10012,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F98" s="7">
+      <c r="F98" s="8">
         <v>72100736251601</v>
       </c>
       <c r="G98" s="8" t="s">
@@ -10186,7 +10039,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F99" s="7">
+      <c r="F99" s="8">
         <v>95625760850047</v>
       </c>
       <c r="G99" s="8" t="s">
@@ -10213,7 +10066,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F100" s="7">
+      <c r="F100" s="8">
         <v>110809850119673</v>
       </c>
       <c r="G100" s="8" t="s">
@@ -10240,7 +10093,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F101" s="7">
+      <c r="F101" s="8">
         <v>128268169997293</v>
       </c>
       <c r="G101" s="8" t="s">
@@ -10267,7 +10120,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F102" s="7">
+      <c r="F102" s="8">
         <v>81568443921942</v>
       </c>
       <c r="G102" s="8" t="s">
@@ -10294,7 +10147,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F103" s="8">
         <v>80275546299866</v>
       </c>
       <c r="G103" s="8" t="s">
@@ -10321,7 +10174,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F104" s="7">
+      <c r="F104" s="8">
         <v>104304476590207</v>
       </c>
       <c r="G104" s="8" t="s">
@@ -10348,7 +10201,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F105" s="7">
+      <c r="F105" s="8">
         <v>129658959682028</v>
       </c>
       <c r="G105" s="8" t="s">
@@ -10375,7 +10228,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F106" s="7">
+      <c r="F106" s="8">
         <v>91807501817775</v>
       </c>
       <c r="G106" s="8" t="s">
@@ -10402,7 +10255,7 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F107" s="7">
+      <c r="F107" s="8">
         <v>119033390105144</v>
       </c>
       <c r="G107" s="8" t="s">
@@ -10428,7 +10281,7 @@
       <c r="E108" s="1">
         <v>24</v>
       </c>
-      <c r="F108" s="7">
+      <c r="F108" s="8">
         <v>96459025721039</v>
       </c>
       <c r="G108" s="8" t="s">
@@ -10455,7 +10308,7 @@
       <c r="E109" s="1">
         <v>24</v>
       </c>
-      <c r="F109" s="7">
+      <c r="F109" s="8">
         <v>138981227536547</v>
       </c>
       <c r="G109" s="8" t="s">
@@ -10482,7 +10335,7 @@
       <c r="E110" s="1">
         <v>25</v>
       </c>
-      <c r="F110" s="7">
+      <c r="F110" s="8">
         <v>119423227657745</v>
       </c>
       <c r="G110" s="8" t="s">
@@ -10509,7 +10362,7 @@
       <c r="E111" s="1">
         <v>25</v>
       </c>
-      <c r="F111" s="7">
+      <c r="F111" s="8">
         <v>96126442221467</v>
       </c>
       <c r="G111" s="8" t="s">
@@ -10536,7 +10389,7 @@
       <c r="E112" s="1">
         <v>25</v>
       </c>
-      <c r="F112" s="7">
+      <c r="F112" s="8">
         <v>115960927208349</v>
       </c>
       <c r="G112" s="8" t="s">
@@ -10563,7 +10416,7 @@
       <c r="E113" s="1">
         <v>25</v>
       </c>
-      <c r="F113" s="7">
+      <c r="F113" s="8">
         <v>130983706534388</v>
       </c>
       <c r="G113" s="8" t="s">
@@ -10590,7 +10443,7 @@
       <c r="E114" s="1">
         <v>26</v>
       </c>
-      <c r="F114" s="7">
+      <c r="F114" s="8">
         <v>95831043321895</v>
       </c>
       <c r="G114" s="8" t="s">
@@ -10617,7 +10470,7 @@
       <c r="E115" s="1">
         <v>26</v>
       </c>
-      <c r="F115" s="7">
+      <c r="F115" s="8">
         <v>112143431254973</v>
       </c>
       <c r="G115" s="8" t="s">
@@ -10644,7 +10497,7 @@
       <c r="E116" s="1">
         <v>26</v>
       </c>
-      <c r="F116" s="7">
+      <c r="F116" s="8">
         <v>118258115873868</v>
       </c>
       <c r="G116" s="8" t="s">
@@ -10671,7 +10524,7 @@
       <c r="E117" s="1">
         <v>26</v>
       </c>
-      <c r="F117" s="7">
+      <c r="F117" s="8">
         <v>78313318872069</v>
       </c>
       <c r="G117" s="8" t="s">
@@ -10698,7 +10551,7 @@
       <c r="E118" s="1">
         <v>27</v>
       </c>
-      <c r="F118" s="7">
+      <c r="F118" s="8">
         <v>125592304728045</v>
       </c>
       <c r="G118" s="8" t="s">
@@ -10725,7 +10578,7 @@
       <c r="E119" s="1">
         <v>27</v>
       </c>
-      <c r="F119" s="7">
+      <c r="F119" s="8">
         <v>80137167951870</v>
       </c>
       <c r="G119" s="8" t="s">
@@ -10752,7 +10605,7 @@
       <c r="E120" s="1">
         <v>27</v>
       </c>
-      <c r="F120" s="7">
+      <c r="F120" s="8">
         <v>73282351047760</v>
       </c>
       <c r="G120" s="8" t="s">
@@ -10779,7 +10632,7 @@
       <c r="E121" s="1">
         <v>27</v>
       </c>
-      <c r="F121" s="7">
+      <c r="F121" s="8">
         <v>103255430368191</v>
       </c>
       <c r="G121" s="8" t="s">
@@ -10806,7 +10659,7 @@
       <c r="E122" s="1">
         <v>28</v>
       </c>
-      <c r="F122" s="7">
+      <c r="F122" s="8">
         <v>116294264954356</v>
       </c>
       <c r="G122" s="8" t="s">
@@ -10833,7 +10686,7 @@
       <c r="E123" s="1">
         <v>28</v>
       </c>
-      <c r="F123" s="7">
+      <c r="F123" s="8">
         <v>125743373452231</v>
       </c>
       <c r="G123" s="8" t="s">
@@ -10860,7 +10713,7 @@
       <c r="E124" s="1">
         <v>28</v>
       </c>
-      <c r="F124" s="7">
+      <c r="F124" s="8">
         <v>112421216883327</v>
       </c>
       <c r="G124" s="8" t="s">
@@ -10878,7 +10731,7 @@
       <c r="B125" s="1">
         <v>122</v>
       </c>
-      <c r="C125" s="9" t="s">
+      <c r="C125" s="8" t="s">
         <v>406</v>
       </c>
       <c r="D125" s="1">
@@ -10887,7 +10740,7 @@
       <c r="E125" s="1">
         <v>28</v>
       </c>
-      <c r="F125" s="7">
+      <c r="F125" s="8">
         <v>91269915478196</v>
       </c>
       <c r="G125" s="8" t="s">
@@ -10904,7 +10757,7 @@
       <c r="B126" s="1">
         <v>123</v>
       </c>
-      <c r="C126" s="9" t="s">
+      <c r="C126" s="8" t="s">
         <v>408</v>
       </c>
       <c r="D126" s="1">
@@ -10913,7 +10766,7 @@
       <c r="E126" s="1">
         <v>29</v>
       </c>
-      <c r="F126" s="7">
+      <c r="F126" s="8">
         <v>105465120437268</v>
       </c>
       <c r="G126" s="8" t="s">
@@ -10930,7 +10783,7 @@
       <c r="B127" s="1">
         <v>124</v>
       </c>
-      <c r="C127" s="9" t="s">
+      <c r="C127" s="8" t="s">
         <v>410</v>
       </c>
       <c r="D127" s="1">
@@ -10939,7 +10792,7 @@
       <c r="E127" s="1">
         <v>29</v>
       </c>
-      <c r="F127" s="7">
+      <c r="F127" s="8">
         <v>83111312306519</v>
       </c>
       <c r="G127" s="8" t="s">
@@ -10956,7 +10809,7 @@
       <c r="B128" s="1">
         <v>125</v>
       </c>
-      <c r="C128" s="9" t="s">
+      <c r="C128" s="8" t="s">
         <v>412</v>
       </c>
       <c r="D128" s="1">
@@ -10965,7 +10818,7 @@
       <c r="E128" s="1">
         <v>29</v>
       </c>
-      <c r="F128" s="7">
+      <c r="F128" s="8">
         <v>100761293408985</v>
       </c>
       <c r="G128" s="8" t="s">
@@ -10982,7 +10835,7 @@
       <c r="B129" s="1">
         <v>126</v>
       </c>
-      <c r="C129" s="9" t="s">
+      <c r="C129" s="8" t="s">
         <v>414</v>
       </c>
       <c r="D129" s="1">
@@ -10991,7 +10844,7 @@
       <c r="E129" s="1">
         <v>29</v>
       </c>
-      <c r="F129" s="7">
+      <c r="F129" s="8">
         <v>125949085124996</v>
       </c>
       <c r="G129" s="8" t="s">
@@ -11008,7 +10861,7 @@
       <c r="B130" s="1">
         <v>127</v>
       </c>
-      <c r="C130" s="9" t="s">
+      <c r="C130" s="8" t="s">
         <v>416</v>
       </c>
       <c r="D130" s="1">
@@ -11017,7 +10870,7 @@
       <c r="E130" s="1">
         <v>30</v>
       </c>
-      <c r="F130" s="7">
+      <c r="F130" s="8">
         <v>97905565242094</v>
       </c>
       <c r="G130" s="8" t="s">
@@ -11034,7 +10887,7 @@
       <c r="B131" s="1">
         <v>128</v>
       </c>
-      <c r="C131" s="9" t="s">
+      <c r="C131" s="8" t="s">
         <v>418</v>
       </c>
       <c r="D131" s="1">
@@ -11043,7 +10896,7 @@
       <c r="E131" s="1">
         <v>30</v>
       </c>
-      <c r="F131" s="7">
+      <c r="F131" s="8">
         <v>140476411551393</v>
       </c>
       <c r="G131" s="8" t="s">
@@ -11060,7 +10913,7 @@
       <c r="B132" s="1">
         <v>129</v>
       </c>
-      <c r="C132" s="9" t="s">
+      <c r="C132" s="8" t="s">
         <v>420</v>
       </c>
       <c r="D132" s="1">
@@ -11069,7 +10922,7 @@
       <c r="E132" s="1">
         <v>30</v>
       </c>
-      <c r="F132" s="7">
+      <c r="F132" s="8">
         <v>120018046835451</v>
       </c>
       <c r="G132" s="8" t="s">
@@ -11086,7 +10939,7 @@
       <c r="B133" s="1">
         <v>130</v>
       </c>
-      <c r="C133" s="9" t="s">
+      <c r="C133" s="8" t="s">
         <v>422</v>
       </c>
       <c r="D133" s="1">
@@ -11095,7 +10948,7 @@
       <c r="E133" s="1">
         <v>30</v>
       </c>
-      <c r="F133" s="7">
+      <c r="F133" s="8">
         <v>80251278207088</v>
       </c>
       <c r="G133" s="8" t="s">
@@ -11112,7 +10965,7 @@
       <c r="B134" s="1">
         <v>131</v>
       </c>
-      <c r="C134" s="9" t="s">
+      <c r="C134" s="8" t="s">
         <v>424</v>
       </c>
       <c r="D134" s="1">
@@ -11121,7 +10974,7 @@
       <c r="E134" s="1">
         <v>31</v>
       </c>
-      <c r="F134" s="7">
+      <c r="F134" s="8">
         <v>93241401911451</v>
       </c>
       <c r="G134" s="8" t="s">
@@ -11138,7 +10991,7 @@
       <c r="B135" s="1">
         <v>132</v>
       </c>
-      <c r="C135" s="9" t="s">
+      <c r="C135" s="8" t="s">
         <v>426</v>
       </c>
       <c r="D135" s="1">
@@ -11147,7 +11000,7 @@
       <c r="E135" s="1">
         <v>31</v>
       </c>
-      <c r="F135" s="7">
+      <c r="F135" s="8">
         <v>111428364476852</v>
       </c>
       <c r="G135" s="8" t="s">
@@ -11164,7 +11017,7 @@
       <c r="B136" s="1">
         <v>133</v>
       </c>
-      <c r="C136" s="9" t="s">
+      <c r="C136" s="8" t="s">
         <v>428</v>
       </c>
       <c r="D136" s="1">
@@ -11173,7 +11026,7 @@
       <c r="E136" s="1">
         <v>31</v>
       </c>
-      <c r="F136" s="7">
+      <c r="F136" s="8">
         <v>117739005088015</v>
       </c>
       <c r="G136" s="8" t="s">
@@ -11190,7 +11043,7 @@
       <c r="B137" s="1">
         <v>134</v>
       </c>
-      <c r="C137" s="9" t="s">
+      <c r="C137" s="8" t="s">
         <v>430</v>
       </c>
       <c r="D137" s="1">
@@ -11199,7 +11052,7 @@
       <c r="E137" s="1">
         <v>31</v>
       </c>
-      <c r="F137" s="7">
+      <c r="F137" s="8">
         <v>106059177546151</v>
       </c>
       <c r="G137" s="8" t="s">
@@ -11216,7 +11069,7 @@
       <c r="B138" s="1">
         <v>135</v>
       </c>
-      <c r="C138" s="9" t="s">
+      <c r="C138" s="8" t="s">
         <v>432</v>
       </c>
       <c r="D138" s="1">
@@ -11225,7 +11078,7 @@
       <c r="E138" s="1">
         <v>32</v>
       </c>
-      <c r="F138" s="7">
+      <c r="F138" s="8">
         <v>136795155731733</v>
       </c>
       <c r="G138" s="8" t="s">
@@ -11242,7 +11095,7 @@
       <c r="B139" s="1">
         <v>136</v>
       </c>
-      <c r="C139" s="9" t="s">
+      <c r="C139" s="8" t="s">
         <v>434</v>
       </c>
       <c r="D139" s="1">
@@ -11251,7 +11104,7 @@
       <c r="E139" s="1">
         <v>32</v>
       </c>
-      <c r="F139" s="7">
+      <c r="F139" s="8">
         <v>72644523405324</v>
       </c>
       <c r="G139" s="8" t="s">
@@ -11268,7 +11121,7 @@
       <c r="B140" s="1">
         <v>137</v>
       </c>
-      <c r="C140" s="9" t="s">
+      <c r="C140" s="8" t="s">
         <v>436</v>
       </c>
       <c r="D140" s="1">
@@ -11277,7 +11130,7 @@
       <c r="E140" s="1">
         <v>32</v>
       </c>
-      <c r="F140" s="7">
+      <c r="F140" s="8">
         <v>108937394146011</v>
       </c>
       <c r="G140" s="8" t="s">
@@ -11294,7 +11147,7 @@
       <c r="B141" s="1">
         <v>138</v>
       </c>
-      <c r="C141" s="9" t="s">
+      <c r="C141" s="8" t="s">
         <v>438</v>
       </c>
       <c r="D141" s="1">
@@ -11303,7 +11156,7 @@
       <c r="E141" s="1">
         <v>32</v>
       </c>
-      <c r="F141" s="7">
+      <c r="F141" s="8">
         <v>79433065873354</v>
       </c>
       <c r="G141" s="8" t="s">
@@ -11320,7 +11173,7 @@
       <c r="B142" s="1">
         <v>139</v>
       </c>
-      <c r="C142" s="9" t="s">
+      <c r="C142" s="8" t="s">
         <v>440</v>
       </c>
       <c r="D142" s="1">
@@ -11329,7 +11182,7 @@
       <c r="E142" s="1">
         <v>33</v>
       </c>
-      <c r="F142" s="7">
+      <c r="F142" s="8">
         <v>78433393917163</v>
       </c>
       <c r="G142" s="8" t="s">
@@ -11346,7 +11199,7 @@
       <c r="B143" s="1">
         <v>140</v>
       </c>
-      <c r="C143" s="9" t="s">
+      <c r="C143" s="8" t="s">
         <v>442</v>
       </c>
       <c r="D143" s="1">
@@ -11355,7 +11208,7 @@
       <c r="E143" s="1">
         <v>33</v>
       </c>
-      <c r="F143" s="7">
+      <c r="F143" s="8">
         <v>86723396142799</v>
       </c>
       <c r="G143" s="8" t="s">
@@ -11372,7 +11225,7 @@
       <c r="B144" s="1">
         <v>141</v>
       </c>
-      <c r="C144" s="9" t="s">
+      <c r="C144" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D144" s="1">
@@ -11381,7 +11234,7 @@
       <c r="E144" s="1">
         <v>33</v>
       </c>
-      <c r="F144" s="7">
+      <c r="F144" s="8">
         <v>116389499163956</v>
       </c>
       <c r="G144" s="8" t="s">
@@ -11398,7 +11251,7 @@
       <c r="B145" s="1">
         <v>142</v>
       </c>
-      <c r="C145" s="9" t="s">
+      <c r="C145" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D145" s="1">
@@ -11407,7 +11260,7 @@
       <c r="E145" s="1">
         <v>33</v>
       </c>
-      <c r="F145" s="7">
+      <c r="F145" s="8">
         <v>97264334614998</v>
       </c>
       <c r="G145" s="8" t="s">
@@ -11424,7 +11277,7 @@
       <c r="B146" s="1">
         <v>143</v>
       </c>
-      <c r="C146" s="9" t="s">
+      <c r="C146" s="8" t="s">
         <v>448</v>
       </c>
       <c r="D146" s="1">
@@ -11433,7 +11286,7 @@
       <c r="E146" s="1">
         <v>34</v>
       </c>
-      <c r="F146" s="7">
+      <c r="F146" s="8">
         <v>115791824258294</v>
       </c>
       <c r="G146" s="8" t="s">
@@ -11450,7 +11303,7 @@
       <c r="B147" s="1">
         <v>144</v>
       </c>
-      <c r="C147" s="9" t="s">
+      <c r="C147" s="8" t="s">
         <v>450</v>
       </c>
       <c r="D147" s="1">
@@ -11459,7 +11312,7 @@
       <c r="E147" s="1">
         <v>34</v>
       </c>
-      <c r="F147" s="7">
+      <c r="F147" s="8">
         <v>94398618924427</v>
       </c>
       <c r="G147" s="8" t="s">
@@ -11476,7 +11329,7 @@
       <c r="B148" s="1">
         <v>145</v>
       </c>
-      <c r="C148" s="9" t="s">
+      <c r="C148" s="8" t="s">
         <v>452</v>
       </c>
       <c r="D148" s="1">
@@ -11485,7 +11338,7 @@
       <c r="E148" s="1">
         <v>34</v>
       </c>
-      <c r="F148" s="7">
+      <c r="F148" s="8">
         <v>128273384481118</v>
       </c>
       <c r="G148" s="8" t="s">
@@ -11502,7 +11355,7 @@
       <c r="B149" s="1">
         <v>146</v>
       </c>
-      <c r="C149" s="9" t="s">
+      <c r="C149" s="8" t="s">
         <v>454</v>
       </c>
       <c r="D149" s="1">
@@ -11511,7 +11364,7 @@
       <c r="E149" s="1">
         <v>34</v>
       </c>
-      <c r="F149" s="7">
+      <c r="F149" s="8">
         <v>138000317292270</v>
       </c>
       <c r="G149" s="8" t="s">
@@ -11528,7 +11381,7 @@
       <c r="B150" s="1">
         <v>147</v>
       </c>
-      <c r="C150" s="9" t="s">
+      <c r="C150" s="8" t="s">
         <v>456</v>
       </c>
       <c r="D150" s="1">
@@ -11537,7 +11390,7 @@
       <c r="E150" s="1">
         <v>35</v>
       </c>
-      <c r="F150" s="7">
+      <c r="F150" s="8">
         <v>100641475547869</v>
       </c>
       <c r="G150" s="8" t="s">
@@ -11554,7 +11407,7 @@
       <c r="B151" s="1">
         <v>148</v>
       </c>
-      <c r="C151" s="9" t="s">
+      <c r="C151" s="8" t="s">
         <v>458</v>
       </c>
       <c r="D151" s="1">
@@ -11563,7 +11416,7 @@
       <c r="E151" s="1">
         <v>35</v>
       </c>
-      <c r="F151" s="7">
+      <c r="F151" s="8">
         <v>79371487434912</v>
       </c>
       <c r="G151" s="8" t="s">
@@ -11590,156 +11443,156 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>2</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>4</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7">
         <v>151</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>3</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>8</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>16</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>153</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>32</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>154</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>64</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A10" s="6">
+      <c r="A10" s="7">
         <v>7</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>128</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>156</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>8</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>256</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>157</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A12" s="6">
+      <c r="A12" s="7">
         <v>9</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>512</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>158</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A13" s="6">
+      <c r="A13" s="7">
         <v>10</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>1024</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>159</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A14" s="6">
+      <c r="A14" s="7">
         <v>11</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>2048</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>160</v>
       </c>
     </row>
@@ -11873,16 +11726,16 @@
         <v>1</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="J4" s="5"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" customFormat="1" ht="16.5" spans="1:10">
       <c r="A5" s="1">
@@ -11901,16 +11754,16 @@
         <v>39</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="J5" s="5"/>
+      <c r="J5" s="6"/>
     </row>
     <row r="6" customFormat="1" ht="16.5" spans="1:10">
       <c r="A6" s="1">
@@ -11929,16 +11782,16 @@
         <v>450</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="J6" s="5"/>
+      <c r="J6" s="6"/>
     </row>
     <row r="7" customFormat="1" ht="16.5" spans="1:10">
       <c r="A7" s="1">
@@ -11957,16 +11810,16 @@
         <v>3282</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="J7" s="5"/>
+      <c r="J7" s="6"/>
     </row>
     <row r="8" customFormat="1" ht="16.5" spans="1:10">
       <c r="A8" s="1">
@@ -11978,23 +11831,23 @@
       <c r="C8" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="26" t="s">
         <v>490</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="26" t="s">
         <v>491</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="J8" s="5"/>
+      <c r="J8" s="6"/>
     </row>
     <row r="9" customFormat="1" ht="16.5" spans="1:10">
       <c r="A9" s="1">
@@ -12006,23 +11859,23 @@
       <c r="C9" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="26" t="s">
         <v>496</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="26" t="s">
         <v>497</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="J9" s="5"/>
+      <c r="J9" s="6"/>
     </row>
     <row r="10" customFormat="1" ht="16.5" spans="1:10">
       <c r="A10" s="1">
@@ -12034,23 +11887,23 @@
       <c r="C10" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="26" t="s">
         <v>502</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="26" t="s">
         <v>503</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="J10" s="5"/>
+      <c r="J10" s="6"/>
     </row>
     <row r="11" customFormat="1" ht="16.5" spans="1:10">
       <c r="A11" s="1">
@@ -12062,23 +11915,23 @@
       <c r="C11" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="26" t="s">
         <v>508</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="26" t="s">
         <v>509</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>511</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="J11" s="5"/>
+      <c r="J11" s="6"/>
     </row>
     <row r="12" customFormat="1" ht="16.5" spans="1:10">
       <c r="A12" s="1">
@@ -12090,23 +11943,23 @@
       <c r="C12" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="26" t="s">
         <v>514</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="26" t="s">
         <v>515</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>517</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="J12" s="5"/>
+      <c r="J12" s="6"/>
     </row>
     <row r="13" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="1">
@@ -12118,23 +11971,23 @@
       <c r="C13" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="26" t="s">
         <v>520</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="26" t="s">
         <v>521</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="J13" s="5"/>
+      <c r="J13" s="6"/>
     </row>
     <row r="14" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="1">
@@ -12146,23 +11999,23 @@
       <c r="C14" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="26" t="s">
         <v>526</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="26" t="s">
         <v>527</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="J14" s="5"/>
+      <c r="J14" s="6"/>
     </row>
     <row r="15" customFormat="1" ht="16.5" spans="1:10">
       <c r="A15" s="1">
@@ -12174,23 +12027,23 @@
       <c r="C15" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="26" t="s">
         <v>532</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="26" t="s">
         <v>533</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="J15" s="5"/>
+      <c r="J15" s="6"/>
     </row>
     <row r="16" customFormat="1" ht="16.5" spans="1:10">
       <c r="A16" s="1">
@@ -12202,23 +12055,23 @@
       <c r="C16" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="26" t="s">
         <v>538</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="26" t="s">
         <v>539</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="J16" s="5"/>
+      <c r="J16" s="6"/>
     </row>
     <row r="17" customFormat="1" ht="16.5" spans="1:10">
       <c r="A17" s="1">
@@ -12230,23 +12083,23 @@
       <c r="C17" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>544</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>545</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="6" t="s">
         <v>546</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="J17" s="5"/>
+      <c r="J17" s="6"/>
     </row>
     <row r="18" customFormat="1" ht="16.5" spans="1:10">
       <c r="A18" s="1">
@@ -12258,23 +12111,23 @@
       <c r="C18" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="26" t="s">
         <v>550</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="26" t="s">
         <v>551</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="6" t="s">
         <v>552</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="6" t="s">
         <v>553</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="6" t="s">
         <v>554</v>
       </c>
-      <c r="J18" s="5"/>
+      <c r="J18" s="6"/>
     </row>
     <row r="19" customFormat="1" ht="16.5" spans="1:10">
       <c r="A19" s="1">
@@ -12286,23 +12139,23 @@
       <c r="C19" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="26" t="s">
         <v>556</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="26" t="s">
         <v>557</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="6" t="s">
         <v>558</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="6" t="s">
         <v>560</v>
       </c>
-      <c r="J19" s="5"/>
+      <c r="J19" s="6"/>
     </row>
     <row r="20" customFormat="1" ht="16.5" spans="1:10">
       <c r="A20" s="1">
@@ -12314,23 +12167,23 @@
       <c r="C20" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="26" t="s">
         <v>562</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="26" t="s">
         <v>563</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="6" t="s">
         <v>564</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="6" t="s">
         <v>565</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="6" t="s">
         <v>566</v>
       </c>
-      <c r="J20" s="5"/>
+      <c r="J20" s="6"/>
     </row>
     <row r="21" ht="16.5" spans="1:10">
       <c r="A21" s="1">
@@ -12342,23 +12195,23 @@
       <c r="C21" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="26" t="s">
         <v>568</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="26" t="s">
         <v>569</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="6" t="s">
         <v>570</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="6" t="s">
         <v>571</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="6" t="s">
         <v>572</v>
       </c>
-      <c r="J21" s="5"/>
+      <c r="J21" s="6"/>
     </row>
     <row r="22" ht="16.5" spans="1:10">
       <c r="A22" s="1">
@@ -12370,23 +12223,23 @@
       <c r="C22" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="26" t="s">
         <v>574</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="26" t="s">
         <v>575</v>
       </c>
       <c r="F22" s="1"/>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="6" t="s">
         <v>576</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="J22" s="5"/>
+      <c r="J22" s="6"/>
     </row>
     <row r="23" ht="16.5" spans="1:10">
       <c r="A23" s="1">
@@ -12398,23 +12251,23 @@
       <c r="C23" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="26" t="s">
         <v>580</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="26" t="s">
         <v>581</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="6" t="s">
         <v>582</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="6" t="s">
         <v>583</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="6" t="s">
         <v>584</v>
       </c>
-      <c r="J23" s="5"/>
+      <c r="J23" s="6"/>
     </row>
     <row r="24" ht="16.5" spans="1:10">
       <c r="A24" s="1">
@@ -12426,23 +12279,23 @@
       <c r="C24" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="26" t="s">
         <v>586</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="26" t="s">
         <v>587</v>
       </c>
       <c r="F24" s="1"/>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="6" t="s">
         <v>588</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="6" t="s">
         <v>589</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="6" t="s">
         <v>590</v>
       </c>
-      <c r="J24" s="5"/>
+      <c r="J24" s="6"/>
     </row>
     <row r="25" ht="16.5" spans="1:10">
       <c r="A25" s="1">
@@ -12454,23 +12307,23 @@
       <c r="C25" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="26" t="s">
         <v>592</v>
       </c>
-      <c r="E25" s="27" t="s">
+      <c r="E25" s="26" t="s">
         <v>593</v>
       </c>
       <c r="F25" s="1"/>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="6" t="s">
         <v>595</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="I25" s="6" t="s">
         <v>596</v>
       </c>
-      <c r="J25" s="5"/>
+      <c r="J25" s="6"/>
     </row>
     <row r="26" ht="16.5" spans="1:10">
       <c r="A26" s="1">
@@ -12482,23 +12335,23 @@
       <c r="C26" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="26" t="s">
         <v>598</v>
       </c>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="26" t="s">
         <v>599</v>
       </c>
       <c r="F26" s="1"/>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="6" t="s">
         <v>600</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="6" t="s">
         <v>601</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="I26" s="6" t="s">
         <v>602</v>
       </c>
-      <c r="J26" s="5"/>
+      <c r="J26" s="6"/>
     </row>
     <row r="27" ht="16.5" spans="1:10">
       <c r="A27" s="1">
@@ -12510,23 +12363,23 @@
       <c r="C27" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="26" t="s">
         <v>604</v>
       </c>
-      <c r="E27" s="27" t="s">
+      <c r="E27" s="26" t="s">
         <v>605</v>
       </c>
       <c r="F27" s="1"/>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="6" t="s">
         <v>606</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="I27" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="J27" s="5"/>
+      <c r="J27" s="6"/>
     </row>
     <row r="28" ht="16.5" spans="1:10">
       <c r="A28" s="1">
@@ -12538,23 +12391,23 @@
       <c r="C28" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="26" t="s">
         <v>610</v>
       </c>
-      <c r="E28" s="27" t="s">
+      <c r="E28" s="26" t="s">
         <v>611</v>
       </c>
       <c r="F28" s="1"/>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="6" t="s">
         <v>612</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="I28" s="5" t="s">
+      <c r="I28" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="J28" s="5"/>
+      <c r="J28" s="6"/>
     </row>
     <row r="29" ht="16.5" spans="1:10">
       <c r="A29" s="1">
@@ -12566,23 +12419,23 @@
       <c r="C29" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="26" t="s">
         <v>616</v>
       </c>
-      <c r="E29" s="27" t="s">
+      <c r="E29" s="26" t="s">
         <v>617</v>
       </c>
       <c r="F29" s="1"/>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="I29" s="5" t="s">
+      <c r="I29" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="J29" s="5"/>
+      <c r="J29" s="6"/>
     </row>
     <row r="30" ht="16.5" spans="1:10">
       <c r="A30" s="1">
@@ -12594,19 +12447,19 @@
       <c r="C30" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="26" t="s">
         <v>622</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="26" t="s">
         <v>623</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="H30" s="5" t="s">
+      <c r="H30" s="6" t="s">
         <v>625</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="I30" s="6" t="s">
         <v>626</v>
       </c>
     </row>
@@ -12620,19 +12473,19 @@
       <c r="C31" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="26" t="s">
         <v>628</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="26" t="s">
         <v>629</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="H31" s="5" t="s">
+      <c r="H31" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="I31" s="5" t="s">
+      <c r="I31" s="6" t="s">
         <v>632</v>
       </c>
     </row>
@@ -12646,19 +12499,19 @@
       <c r="C32" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="D32" s="27" t="s">
+      <c r="D32" s="26" t="s">
         <v>634</v>
       </c>
-      <c r="E32" s="27" t="s">
+      <c r="E32" s="26" t="s">
         <v>635</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="H32" s="5" t="s">
+      <c r="H32" s="6" t="s">
         <v>637</v>
       </c>
-      <c r="I32" s="5" t="s">
+      <c r="I32" s="6" t="s">
         <v>638</v>
       </c>
     </row>
@@ -12672,19 +12525,19 @@
       <c r="C33" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="D33" s="27" t="s">
+      <c r="D33" s="26" t="s">
         <v>640</v>
       </c>
-      <c r="E33" s="27" t="s">
+      <c r="E33" s="26" t="s">
         <v>641</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="6" t="s">
         <v>642</v>
       </c>
-      <c r="H33" s="5" t="s">
+      <c r="H33" s="6" t="s">
         <v>643</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="I33" s="6" t="s">
         <v>644</v>
       </c>
     </row>
@@ -12698,19 +12551,19 @@
       <c r="C34" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D34" s="26" t="s">
         <v>646</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="E34" s="26" t="s">
         <v>647</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="6" t="s">
         <v>648</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="6" t="s">
         <v>649</v>
       </c>
-      <c r="I34" s="5" t="s">
+      <c r="I34" s="6" t="s">
         <v>650</v>
       </c>
     </row>
@@ -12724,19 +12577,19 @@
       <c r="C35" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="D35" s="27" t="s">
+      <c r="D35" s="26" t="s">
         <v>652</v>
       </c>
-      <c r="E35" s="27" t="s">
+      <c r="E35" s="26" t="s">
         <v>653</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="6" t="s">
         <v>654</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="6" t="s">
         <v>655</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I35" s="6" t="s">
         <v>656</v>
       </c>
     </row>
@@ -12750,19 +12603,19 @@
       <c r="C36" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="D36" s="27" t="s">
+      <c r="D36" s="26" t="s">
         <v>658</v>
       </c>
-      <c r="E36" s="27" t="s">
+      <c r="E36" s="26" t="s">
         <v>659</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="6" t="s">
         <v>660</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="6" t="s">
         <v>661</v>
       </c>
-      <c r="I36" s="5" t="s">
+      <c r="I36" s="6" t="s">
         <v>662</v>
       </c>
     </row>
@@ -12776,19 +12629,19 @@
       <c r="C37" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D37" s="26" t="s">
         <v>664</v>
       </c>
-      <c r="E37" s="27" t="s">
+      <c r="E37" s="26" t="s">
         <v>665</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="6" t="s">
         <v>666</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="6" t="s">
         <v>667</v>
       </c>
-      <c r="I37" s="5" t="s">
+      <c r="I37" s="6" t="s">
         <v>668</v>
       </c>
     </row>
@@ -12802,19 +12655,19 @@
       <c r="C38" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="26" t="s">
         <v>670</v>
       </c>
-      <c r="E38" s="27" t="s">
+      <c r="E38" s="26" t="s">
         <v>671</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="6" t="s">
         <v>672</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="6" t="s">
         <v>673</v>
       </c>
-      <c r="I38" s="5" t="s">
+      <c r="I38" s="6" t="s">
         <v>674</v>
       </c>
     </row>
@@ -12828,19 +12681,19 @@
       <c r="C39" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="D39" s="26" t="s">
         <v>676</v>
       </c>
-      <c r="E39" s="27" t="s">
+      <c r="E39" s="26" t="s">
         <v>677</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="H39" s="5" t="s">
+      <c r="H39" s="6" t="s">
         <v>679</v>
       </c>
-      <c r="I39" s="5" t="s">
+      <c r="I39" s="6" t="s">
         <v>680</v>
       </c>
     </row>
@@ -12854,19 +12707,19 @@
       <c r="C40" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" s="26" t="s">
         <v>682</v>
       </c>
-      <c r="E40" s="27" t="s">
+      <c r="E40" s="26" t="s">
         <v>683</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="6" t="s">
         <v>684</v>
       </c>
-      <c r="H40" s="5" t="s">
+      <c r="H40" s="6" t="s">
         <v>685</v>
       </c>
-      <c r="I40" s="5" t="s">
+      <c r="I40" s="6" t="s">
         <v>686</v>
       </c>
     </row>
@@ -12880,19 +12733,19 @@
       <c r="C41" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="D41" s="26" t="s">
         <v>688</v>
       </c>
-      <c r="E41" s="27" t="s">
+      <c r="E41" s="26" t="s">
         <v>689</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="6" t="s">
         <v>690</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="H41" s="6" t="s">
         <v>691</v>
       </c>
-      <c r="I41" s="5" t="s">
+      <c r="I41" s="6" t="s">
         <v>692</v>
       </c>
     </row>
@@ -12906,19 +12759,19 @@
       <c r="C42" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="26" t="s">
         <v>694</v>
       </c>
-      <c r="E42" s="27" t="s">
+      <c r="E42" s="26" t="s">
         <v>695</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="6" t="s">
         <v>696</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="6" t="s">
         <v>697</v>
       </c>
-      <c r="I42" s="5" t="s">
+      <c r="I42" s="6" t="s">
         <v>698</v>
       </c>
     </row>
@@ -12932,19 +12785,19 @@
       <c r="C43" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="26" t="s">
         <v>700</v>
       </c>
-      <c r="E43" s="27" t="s">
+      <c r="E43" s="26" t="s">
         <v>701</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="G43" s="6" t="s">
         <v>702</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="6" t="s">
         <v>703</v>
       </c>
-      <c r="I43" s="5" t="s">
+      <c r="I43" s="6" t="s">
         <v>704</v>
       </c>
     </row>
@@ -13301,11 +13154,11 @@
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="38.6333333333333" style="2" customWidth="1"/>
     <col min="3" max="4" width="23.3833333333333" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="48.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="57.1333333333333" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="5" max="6" width="28" style="2" customWidth="1"/>
+    <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="48.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="57.1333333333333" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -13325,12 +13178,15 @@
         <v>465</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>757</v>
       </c>
     </row>
@@ -13351,13 +13207,16 @@
         <v>59</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>471</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -13377,12 +13236,15 @@
         <v>61</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -13402,11 +13264,14 @@
       <c r="E4" s="1">
         <v>1.5</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1" t="s">
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>761</v>
       </c>
     </row>
@@ -13420,17 +13285,20 @@
       <c r="C5" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="26" t="s">
         <v>763</v>
       </c>
       <c r="E5" s="1">
         <v>2.5</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>765</v>
       </c>
     </row>
@@ -13444,17 +13312,20 @@
       <c r="C6" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="26" t="s">
         <v>767</v>
       </c>
       <c r="E6" s="1">
         <v>3.5</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1" t="s">
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>769</v>
       </c>
     </row>
@@ -13468,17 +13339,20 @@
       <c r="C7" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="26" t="s">
         <v>771</v>
       </c>
       <c r="E7" s="1">
         <v>4.5</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1" t="s">
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>773</v>
       </c>
     </row>
@@ -13492,138 +13366,75 @@
       <c r="C8" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="26" t="s">
         <v>775</v>
       </c>
       <c r="E8" s="1">
         <v>5.5</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1" t="s">
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>777</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A9" s="1">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1">
-        <v>106</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>778</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>779</v>
-      </c>
-      <c r="E9" s="1">
-        <v>6.5</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="1" t="s">
-        <v>780</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>781</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A10" s="1">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1">
-        <v>107</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>782</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>783</v>
-      </c>
-      <c r="E10" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="1" t="s">
-        <v>784</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>785</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A11" s="1">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1">
-        <v>108</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>787</v>
-      </c>
-      <c r="E11" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>789</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A12" s="1">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1">
-        <v>109</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>791</v>
-      </c>
-      <c r="E12" s="4">
-        <v>9.5</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>793</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="5"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A13" s="1">
-        <v>10</v>
-      </c>
-      <c r="B13" s="1">
-        <v>110</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>795</v>
-      </c>
-      <c r="E13" s="1">
-        <v>12.5</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
       <c r="F13" s="1"/>
-      <c r="G13" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>797</v>
-      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -30002,28 +29813,14 @@
       <c r="XFD13" s="1"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A14" s="1">
-        <v>11</v>
-      </c>
-      <c r="B14" s="1">
-        <v>111</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>799</v>
-      </c>
-      <c r="E14" s="1">
-        <v>15.9</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
       <c r="F14" s="1"/>
-      <c r="G14" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>801</v>
-      </c>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -46402,28 +46199,14 @@
       <c r="XFD14" s="1"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A15" s="1">
-        <v>12</v>
-      </c>
-      <c r="B15" s="1">
-        <v>112</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>802</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>803</v>
-      </c>
-      <c r="E15" s="1">
-        <v>19.7</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>805</v>
-      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -62802,124 +62585,59 @@
       <c r="XFD15" s="1"/>
     </row>
     <row r="16" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A16" s="1">
-        <v>13</v>
-      </c>
-      <c r="B16" s="1">
-        <v>113</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>806</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>807</v>
-      </c>
-      <c r="E16" s="1">
-        <v>21.3</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
       <c r="F16" s="1"/>
-      <c r="G16" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>809</v>
-      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
     </row>
-    <row r="17" ht="16.5" spans="1:8">
-      <c r="A17" s="1">
-        <v>14</v>
-      </c>
-      <c r="B17" s="1">
-        <v>114</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>810</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>811</v>
-      </c>
-      <c r="E17" s="1">
-        <v>22.9</v>
-      </c>
+    <row r="17" ht="16.5" spans="1:9">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="1" t="s">
-        <v>812</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>813</v>
-      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
     </row>
-    <row r="18" ht="16.5" spans="1:8">
-      <c r="A18" s="1">
-        <v>15</v>
-      </c>
-      <c r="B18" s="1">
-        <v>115</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>814</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>815</v>
-      </c>
-      <c r="E18" s="1">
-        <v>24.5</v>
-      </c>
+    <row r="18" ht="16.5" spans="1:9">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>817</v>
-      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
     </row>
-    <row r="19" ht="16.5" spans="1:8">
-      <c r="A19" s="1">
-        <v>16</v>
-      </c>
-      <c r="B19" s="1">
-        <v>116</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>818</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>819</v>
-      </c>
-      <c r="E19" s="1">
-        <v>26.1</v>
-      </c>
+    <row r="19" ht="16.5" spans="1:9">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>821</v>
-      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
     </row>
-    <row r="20" ht="16.5" spans="1:8">
-      <c r="A20" s="1">
-        <v>17</v>
-      </c>
-      <c r="B20" s="1">
-        <v>117</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>823</v>
-      </c>
-      <c r="E20" s="1">
-        <v>27.7</v>
-      </c>
+    <row r="20" ht="16.5" spans="1:9">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>825</v>
-      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1303" uniqueCount="934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="720">
   <si>
     <t>子配置键</t>
   </si>
@@ -1448,9 +1448,6 @@
     <t>图片Id</t>
   </si>
   <si>
-    <t>贴图</t>
-  </si>
-  <si>
     <t>SlicerId</t>
   </si>
   <si>
@@ -1463,58 +1460,31 @@
     <t>ModelId</t>
   </si>
   <si>
-    <t>TextureId</t>
-  </si>
-  <si>
-    <t>荒木战棍</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Png/01_WildwoodWarclub.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/01_WildwoodWarclub/WildwoodWarclub.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/01_WildwoodWarclub/WildwoodWarclub.png</t>
-  </si>
-  <si>
-    <t>铁木战斧</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Png/02_IronwoodBattleaxe.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/02_IronwoodBattleaxe/IronwoodBattleaxe.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/02_IronwoodBattleaxe/IronwoodBattleaxe.png</t>
-  </si>
-  <si>
-    <t>霜钢剑</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Png/03_FroststeelSword.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/03_FroststeelSword/FroststeelSword.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/03_FroststeelSword/FroststeelSword.png</t>
-  </si>
-  <si>
-    <t>黑曜石手斧</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Png/04_ObsidianHandAxe.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/04_ObsidianHandAxe/ObsidianHandAxe.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/04_ObsidianHandAxe/ObsidianHandAxe.png</t>
-  </si>
-  <si>
-    <t>绯红晶格法杖</t>
+    <t>WornWoodenPickaxe</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["01WornWoodenPickaxe"]</t>
+  </si>
+  <si>
+    <t>HeavyWoodenHammer</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["02HeavyWoodenHammer"]</t>
+  </si>
+  <si>
+    <t>CrudeSilverPickaxe</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["03CrudeSilverPickaxe"]</t>
+  </si>
+  <si>
+    <t>CrudeSilverHammer</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["04CrudeSilverHammer"]</t>
+  </si>
+  <si>
+    <t>ReinforcedIronPickaxe</t>
   </si>
   <si>
     <t>3.50e+4</t>
@@ -1523,16 +1493,10 @@
     <t>1.90e+4</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/05_CrimsonLatticeStaff.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/05_CrimsonLatticeStaff/CrimsonLatticeStaff.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/05_CrimsonLatticeStaff/CrimsonLatticeStaff.png</t>
-  </si>
-  <si>
-    <t>夜影战斧</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["05ReinforcedIronPickaxe"]</t>
+  </si>
+  <si>
+    <t>ReinforcedIronHammer</t>
   </si>
   <si>
     <t>2.53e+5</t>
@@ -1541,16 +1505,10 @@
     <t>9.55e+4</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/06_NightshadeWarAxe.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/06_NightshadeWarAxe/NightshadeWarAxe.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/06_NightshadeWarAxe/NightshadeWarAxe.png</t>
-  </si>
-  <si>
-    <t>符文战锤</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["06ReinforcedIronHammer"]</t>
+  </si>
+  <si>
+    <t>FineSteelMiningPickaxe</t>
   </si>
   <si>
     <t>1.89e+6</t>
@@ -1559,16 +1517,10 @@
     <t>4.42e+5</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/07_RuneboundWarhammer.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/07_RuneboundWarhammer/RuneboundWarhammer.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/07_RuneboundWarhammer/RuneboundWarhammer.png</t>
-  </si>
-  <si>
-    <t>暗角钉头锤</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["07FineSteelMiningPickaxe"]</t>
+  </si>
+  <si>
+    <t>FineSteelMaul</t>
   </si>
   <si>
     <t>1.22e+7</t>
@@ -1577,16 +1529,10 @@
     <t>1.93e+6</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/08_DarkhornMace.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/08_DarkhornMace/DarkhornMace.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/08_DarkhornMace/DarkhornMace.png</t>
-  </si>
-  <si>
-    <t>白银匕首</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["08FineSteelMaul"]</t>
+  </si>
+  <si>
+    <t>BrassMechanicalPickaxe</t>
   </si>
   <si>
     <t>7.62e+7</t>
@@ -1595,16 +1541,10 @@
     <t>8.10e+6</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/09_SilverDagger.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/09_SilverDagger/SilverDagger.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/09_SilverDagger/SilverDagger.png</t>
-  </si>
-  <si>
-    <t>金辉日刃</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["09BrassMechanicalPickaxe"]</t>
+  </si>
+  <si>
+    <t>BrassMechanicalHammer</t>
   </si>
   <si>
     <t>4.65e+8</t>
@@ -1613,16 +1553,10 @@
     <t>3.31e+7</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/10_AuricSunblade.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/10_AuricSunblade/AuricSunblade.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/10_AuricSunblade/AuricSunblade.png</t>
-  </si>
-  <si>
-    <t>星界霜刃</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["10BrassMechanicalHammer"]</t>
+  </si>
+  <si>
+    <t>ObsidianBattlePickaxe</t>
   </si>
   <si>
     <t>2.78e+9</t>
@@ -1631,16 +1565,10 @@
     <t>1.33e+8</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/11_AstralFrostblade.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/11_AstralFrostblade/AstralFrostblade.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/11_AstralFrostblade/AstralFrostblade.png</t>
-  </si>
-  <si>
-    <t>炼狱弯刀</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["11ObsidianBattlePickaxe"]</t>
+  </si>
+  <si>
+    <t>ObsidianGreatHammer</t>
   </si>
   <si>
     <t>1.64e+10</t>
@@ -1649,16 +1577,10 @@
     <t>5.25e+8</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/12_InfernalScimitar.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/12_InfernalScimitar/InfernalScimitar.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/12_InfernalScimitar/InfernalScimitar.png</t>
-  </si>
-  <si>
-    <t>翠毒刃</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["12ObsidianGreatHammer"]</t>
+  </si>
+  <si>
+    <t>EmeraldGuardianPickaxe</t>
   </si>
   <si>
     <t>9.55e+10</t>
@@ -1667,16 +1589,10 @@
     <t>2.05e+9</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/13_VerdantVenomblade.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/13_VerdantVenomblade/VerdantVenomblade.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/13_VerdantVenomblade/VerdantVenomblade.png</t>
-  </si>
-  <si>
-    <t>翠绿三叉戟</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["13EmeraldGuardianPickaxe"]</t>
+  </si>
+  <si>
+    <t>EmeraldGuardianHammer</t>
   </si>
   <si>
     <t>5.49e+11</t>
@@ -1685,16 +1601,10 @@
     <t>7.99e+9</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/14_VerdantTrident.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/14_VerdantTrident/VerdantTrident.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/14_VerdantTrident/VerdantTrident.png</t>
-  </si>
-  <si>
-    <t>紫晶碎星枪</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["14EmeraldGuardianHammer"]</t>
+  </si>
+  <si>
+    <t>RedCrystalForgePickaxe</t>
   </si>
   <si>
     <t>3.13e+12</t>
@@ -1703,16 +1613,10 @@
     <t>3.10e+10</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/15_AmethystStarbreakerSpear.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/15_AmethystStarbreakerSpear/AmethystStarbreakerSpear.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/15_AmethystStarbreakerSpear/AmethystStarbreakerSpear.png</t>
-  </si>
-  <si>
-    <t>霜晶巨剑</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["15RedCrystalForgePickaxe"]</t>
+  </si>
+  <si>
+    <t>RedCrystalForgeHammer</t>
   </si>
   <si>
     <t>1.77e+13</t>
@@ -1721,16 +1625,10 @@
     <t>1.20e+11</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/16_FrostcrystalGreatsword.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/16_FrostcrystalGreatsword/FrostcrystalGreatsword.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/16_FrostcrystalGreatsword/FrostcrystalGreatsword.png</t>
-  </si>
-  <si>
-    <t>熔岩裂地斧</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["16RedCrystalForgeHammer"]</t>
+  </si>
+  <si>
+    <t>IceBlueStarCrystalPickaxe</t>
   </si>
   <si>
     <t>9.93e+13</t>
@@ -1739,16 +1637,10 @@
     <t>4.62e+11</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/17_MagmaEarthsplitter.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/17_MagmaEarthsplitter/MagmaEarthsplitter.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/17_MagmaEarthsplitter/MagmaEarthsplitter.png</t>
-  </si>
-  <si>
-    <t>烈焰之羽</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["17IceBlueStarCrystalPickaxe"]</t>
+  </si>
+  <si>
+    <t>IceBlueStarCrystalHammer</t>
   </si>
   <si>
     <t>5.54e+14</t>
@@ -1757,16 +1649,10 @@
     <t>1.78e+12</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/18_FlamingFeather.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/18_FlamingFeather/FlamingFeather.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/18_FlamingFeather/FlamingFeather.png</t>
-  </si>
-  <si>
-    <t>耀阳权杖</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["18IceBlueStarCrystalHammer"]</t>
+  </si>
+  <si>
+    <t>GildedCrownPickaxe</t>
   </si>
   <si>
     <t>3.07e+15</t>
@@ -1775,16 +1661,10 @@
     <t>6.90e+12</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/19_SunburstScepter.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/19_SunburstScepter/SunburstScepter.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/19_SunburstScepter/SunburstScepter.png</t>
-  </si>
-  <si>
-    <t>辉光天翼剑</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["19GildedCrownPickaxe"]</t>
+  </si>
+  <si>
+    <t>GildedCrownGreatHammer</t>
   </si>
   <si>
     <t>1.69e+16</t>
@@ -1793,529 +1673,7 @@
     <t>2.67e+13</t>
   </si>
   <si>
-    <t>sandboxId://Model/Slicer/Png/20_RadiantSkywingSword.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/20_RadiantSkywingSword/RadiantSkywingSword.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/20_RadiantSkywingSword/RadiantSkywingSword.png</t>
-  </si>
-  <si>
-    <t>凤凰翼剑</t>
-  </si>
-  <si>
-    <t>9.30e+16</t>
-  </si>
-  <si>
-    <t>1.04e+14</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Png/21_PhoenixwingSword.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/21_PhoenixwingSword/PhoenixwingSword.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/21_PhoenixwingSword/PhoenixwingSword.png</t>
-  </si>
-  <si>
-    <t>时轮齿刃</t>
-  </si>
-  <si>
-    <t>5.08e+17</t>
-  </si>
-  <si>
-    <t>4.03e+14</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Png/22_ChronoGearblade.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/22_ChronoGearblade/ChronoGearblade.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/22_ChronoGearblade/ChronoGearblade.png</t>
-  </si>
-  <si>
-    <t>裂魂镰刀</t>
-  </si>
-  <si>
-    <t>2.77e+18</t>
-  </si>
-  <si>
-    <t>1.57e+15</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Png/23_SoulrenderScythe.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/23_SoulrenderScythe/SoulrenderScythe.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/23_SoulrenderScythe/SoulrenderScythe.png</t>
-  </si>
-  <si>
-    <t>炼狱龙刃</t>
-  </si>
-  <si>
-    <t>1.45e+19</t>
-  </si>
-  <si>
-    <t>6.16e+15</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Png/24_InfernoDragonblade.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/24_InfernoDragonblade/InfernoDragonblade.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/24_InfernoDragonblade/InfernoDragonblade.png</t>
-  </si>
-  <si>
-    <t>虚空裂隙刃</t>
-  </si>
-  <si>
-    <t>7.84e+19</t>
-  </si>
-  <si>
-    <t>2.42e+16</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Png/25_VoidriftBlade.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/25_VoidriftBlade/VoidriftBlade.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/25_VoidriftBlade/VoidriftBlade.png</t>
-  </si>
-  <si>
-    <t>噬界魔刃</t>
-  </si>
-  <si>
-    <t>4.23e+20</t>
-  </si>
-  <si>
-    <t>9.54e+16</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Png/26_WorldeaterDemonblade.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/26_WorldeaterDemonblade/WorldeaterDemonblade.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/Slicer/Model/26_WorldeaterDemonblade/WorldeaterDemonblade.png</t>
-  </si>
-  <si>
-    <t>赤影刃</t>
-  </si>
-  <si>
-    <t>2.28e+21</t>
-  </si>
-  <si>
-    <t>1.50e+17</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/27Wp_Ansi.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/27Wp_Ansi_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/27Wp_Ansi_01.png</t>
-  </si>
-  <si>
-    <t>星渊圣锋</t>
-  </si>
-  <si>
-    <t>1.22e+22</t>
-  </si>
-  <si>
-    <t>3.00e+17</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/028_Wp_Ml_Sword_004.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/028_Wp_Ml_Sword_004.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/028_Wp_Ml_Sword_004_D.png</t>
-  </si>
-  <si>
-    <t>血月魔剑</t>
-  </si>
-  <si>
-    <t>6.35e+22</t>
-  </si>
-  <si>
-    <t>5.94e+17</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/029_Wp_Ml_Sword_003.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/029_Wp_Ml_Sword_003.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/029_Wp_Ml_Sword_003_D.png</t>
-  </si>
-  <si>
-    <t>紫晶灾厄</t>
-  </si>
-  <si>
-    <t>3.29e+23</t>
-  </si>
-  <si>
-    <t>1.17e+18</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/030_Wp_Dt_Sword_003.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/030_Wp_Dt_Sword_003.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/030_Wp_Dt_Sword_003_D.png</t>
-  </si>
-  <si>
-    <t>天穹裁决</t>
-  </si>
-  <si>
-    <t>1.70e+24</t>
-  </si>
-  <si>
-    <t>2.27e+18</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/031_Wp_Dt_Sword_004.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/031_Wp_Dt_Sword_004.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/031_Wp_Dt_Sword_004_D.png</t>
-  </si>
-  <si>
-    <t>赤焰龙牙</t>
-  </si>
-  <si>
-    <t>8.81e+24</t>
-  </si>
-  <si>
-    <t>4.37e+18</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/032_Wp_Dt_Sword_001.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/032_Wp_Dt_Sword_001.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/032_Wp_Dt_Sword_001_D.png</t>
-  </si>
-  <si>
-    <t>幽影月镰</t>
-  </si>
-  <si>
-    <t>4.55e+25</t>
-  </si>
-  <si>
-    <t>8.38e+18</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/033_Wp_Kris_Mn_DualBlades_01_1.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/033_Wp_Kris_Mn_DualBlades_01_1.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/033_Wp_Kris_Mn_DualBlades_01_1_D.png</t>
-  </si>
-  <si>
-    <t>曜金帝剑</t>
-  </si>
-  <si>
-    <t>2.35e+26</t>
-  </si>
-  <si>
-    <t>1.59e+19</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/034_Wp_Cc_Sword_003.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/034_Wp_Cc_Sword_003.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/034_Wp_Cc_Sword_003_D.png</t>
-  </si>
-  <si>
-    <t>苍蓝龙魂</t>
-  </si>
-  <si>
-    <t>1.21e+27</t>
-  </si>
-  <si>
-    <t>3.01e+19</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/035_Wp_Evan_Sword_01.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/035_Wp_Evan_Sword_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/035_Wp_Evan_Sword_01_D.png</t>
-  </si>
-  <si>
-    <t>暮光巨刃</t>
-  </si>
-  <si>
-    <t>6.23e+27</t>
-  </si>
-  <si>
-    <t>5.66e+19</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/036_Wp_Kris_Mn_GreatSword_01.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/036_Wp_Kris_Mn_GreatSword_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/036_Wp_Kris_Mn_GreatSword_01_D.png</t>
-  </si>
-  <si>
-    <t>血族王锋</t>
-  </si>
-  <si>
-    <t>3.20e+28</t>
-  </si>
-  <si>
-    <t>1.06e+20</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/037_WP_Boss_Vampire_01.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/037_WP_Boss_Vampire_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/037_WP_Boss_Vampire_01_D.png</t>
-  </si>
-  <si>
-    <t>绯翼魔剑</t>
-  </si>
-  <si>
-    <t>1.65e+29</t>
-  </si>
-  <si>
-    <t>1.97e+20</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/038_Wp_Shane_Avatar_R.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/038_Wp_Shane_Avatar_R.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/038_Wp_Shane_Avatar_R_D.png</t>
-  </si>
-  <si>
-    <t>灰烬锯刃</t>
-  </si>
-  <si>
-    <t>8.19e+29</t>
-  </si>
-  <si>
-    <t>3.64e+20</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/039_Wp_Serbinus_01.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/039_Wp_Serbinus_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/039_Wp_Serbinus_01_D.png</t>
-  </si>
-  <si>
-    <t>断魂鬼剑</t>
-  </si>
-  <si>
-    <t>4.20e+30</t>
-  </si>
-  <si>
-    <t>6.71e+20</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/040_Wp_Shane_Ghost_Sword_01.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/040_Wp_Shane_Ghost_Sword_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/040_Wp_Shane_Ghost_Sword_01_D.png</t>
-  </si>
-  <si>
-    <t>绯樱蛇影</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/041_Wp_Kagura_Mn_01.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/041_Wp_Kagura_Mn_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/041_Wp_Kagura_Mn_01_D.png</t>
-  </si>
-  <si>
-    <t>黑曜裁决</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/042_Wp_oscar_dagger_02.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/042_Wp_oscar_dagger_02.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/042_Wp_oscar_dagger_02_D.png</t>
-  </si>
-  <si>
-    <t>苍穹圣裁</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/043_Wp_GS_Sword_003.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/043_Wp_GS_Sword_003.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/043_Wp_GS_Sword_003_D.png</t>
-  </si>
-  <si>
-    <t>天翼辉光</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/044_Wp_GS_Sword_004.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/044_Wp_GS_Sword_004.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/044_Wp_GS_Sword_004_D.png</t>
-  </si>
-  <si>
-    <t>碧海云霄</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/045_Wp_Cc_Sword_002.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/045_Wp_Cc_Sword_002.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/045_Wp_Cc_Sword_002_D.png</t>
-  </si>
-  <si>
-    <t>王权天谴</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/046_Wp_Rudy_Mn_BigSword_01.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/046_Wp_Rudy_Mn_BigSword_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/046_Wp_Rudy_Mn_BigSword_01_D.png</t>
-  </si>
-  <si>
-    <t>寒渊狼牙</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/047_Wp_Teo_01.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/047_Wp_Teo_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/047_Wp_Teo_01_D.png</t>
-  </si>
-  <si>
-    <t>熔狱断罪</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/048_Wp_ML_sword_003_R.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/048_Wp_ML_sword_003_R.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/048_Wp_ML_sword_003_R_D.png</t>
-  </si>
-  <si>
-    <t>鸿运镇岳</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/049_Wp_Ml_Sword_002.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/049_Wp_Ml_Sword_002.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/049_Wp_Ml_Sword_002_D.png</t>
-  </si>
-  <si>
-    <t>影月血牙</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/050_Wp_oscar_dagger_01.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/050_Wp_oscar_dagger_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/050_Wp_oscar_dagger_01_D.png</t>
-  </si>
-  <si>
-    <t>幽冥锁刃</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/051_Wp_Shane_Ghost_Sword_Whip_01.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/051_Wp_Shane_Ghost_Sword_Whip_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/051_Wp_Shane_Ghost_Sword_Whip_01_D.png</t>
-  </si>
-  <si>
-    <t>赤焰龙魂</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/052_Wp_Cc_Sword_004.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/052_Wp_Cc_Sword_004.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/052_Wp_Cc_Sword_004_D.png</t>
-  </si>
-  <si>
-    <t>曜金赤锋</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Png/053_Wp_oscar_01.png</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Model/053_Wp_oscar_01.obj</t>
-  </si>
-  <si>
-    <t>sandboxId://Model/ExtraSlicer/Maps/053_Wp_oscar_01_D.png</t>
+    <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["20GildedCrownGreatHammer"]</t>
   </si>
   <si>
     <t>图片ID</t>
@@ -2885,15 +2243,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="MiSans"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3521,7 +2879,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3543,10 +2901,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="fill" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -3934,62 +3295,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="26" customHeight="1" spans="1:6">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="22" t="s">
         <v>14</v>
       </c>
     </row>
@@ -4006,7 +3367,7 @@
       <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="25" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
@@ -4026,7 +3387,7 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4043,7 +3404,7 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="26" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4060,7 +3421,7 @@
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="26" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
@@ -4080,7 +3441,7 @@
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="25" t="s">
         <v>21</v>
       </c>
       <c r="F8" t="s">
@@ -4100,7 +3461,7 @@
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="25" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
@@ -4120,7 +3481,7 @@
       <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="26" t="s">
         <v>25</v>
       </c>
       <c r="F10" t="s">
@@ -4156,13 +3517,13 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>778</v>
+        <v>564</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>779</v>
+        <v>565</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>780</v>
+        <v>566</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:5">
@@ -4170,10 +3531,10 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>781</v>
+        <v>567</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>782</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
@@ -4189,576 +3550,576 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>783</v>
+        <v>569</v>
       </c>
       <c r="B4" s="2">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>784</v>
+        <v>570</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>785</v>
+        <v>571</v>
       </c>
       <c r="B5" s="2">
         <v>122</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>786</v>
+        <v>572</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>787</v>
+        <v>573</v>
       </c>
       <c r="B6" s="2">
         <v>520</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>788</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>789</v>
+        <v>575</v>
       </c>
       <c r="B7" s="2">
         <v>2176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>790</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>791</v>
+        <v>577</v>
       </c>
       <c r="B8" s="2">
         <v>9101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>792</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>794</v>
+        <v>579</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>580</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>795</v>
+        <v>581</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>797</v>
+        <v>582</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>583</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>798</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>800</v>
+        <v>585</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>586</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>801</v>
+        <v>587</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>803</v>
+        <v>588</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>589</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>804</v>
+        <v>590</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>806</v>
+        <v>591</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>592</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>807</v>
+        <v>593</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>809</v>
+        <v>594</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>595</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>810</v>
+        <v>596</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>812</v>
+        <v>597</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>598</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>813</v>
+        <v>599</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>815</v>
+        <v>600</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>601</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>816</v>
+        <v>602</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>818</v>
+        <v>603</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>604</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>819</v>
+        <v>605</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>821</v>
+        <v>606</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>607</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>822</v>
+        <v>608</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>824</v>
+        <v>609</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>610</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>825</v>
+        <v>611</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>827</v>
+        <v>612</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>613</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>828</v>
+        <v>614</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="B21" s="27" t="s">
-        <v>830</v>
+        <v>615</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>616</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>831</v>
+        <v>617</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>833</v>
+        <v>618</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>619</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>834</v>
+        <v>620</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>836</v>
+        <v>621</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>622</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>837</v>
+        <v>623</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="B24" s="27" t="s">
-        <v>839</v>
+        <v>624</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>625</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>840</v>
+        <v>626</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="B25" s="27" t="s">
-        <v>842</v>
+        <v>627</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>628</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>843</v>
+        <v>629</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>845</v>
+        <v>630</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>631</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>846</v>
+        <v>632</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="B27" s="27" t="s">
-        <v>848</v>
+        <v>633</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>634</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>849</v>
+        <v>635</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="B28" s="27" t="s">
-        <v>851</v>
+        <v>636</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>637</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>852</v>
+        <v>638</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>854</v>
+        <v>639</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>640</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>855</v>
+        <v>641</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>857</v>
+        <v>642</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>643</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>858</v>
+        <v>644</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>859</v>
-      </c>
-      <c r="B31" s="27" t="s">
-        <v>860</v>
+        <v>645</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>646</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>861</v>
+        <v>647</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>862</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>863</v>
+        <v>648</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>649</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>864</v>
+        <v>650</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>865</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>866</v>
+        <v>651</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>652</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>867</v>
+        <v>653</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="B34" s="27" t="s">
-        <v>869</v>
+        <v>654</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>655</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>870</v>
+        <v>656</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>872</v>
+        <v>657</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>658</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>873</v>
+        <v>659</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="B36" s="27" t="s">
-        <v>875</v>
+        <v>660</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>661</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>876</v>
+        <v>662</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="B37" s="27" t="s">
-        <v>878</v>
+        <v>663</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>664</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>879</v>
+        <v>665</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>880</v>
-      </c>
-      <c r="B38" s="27" t="s">
-        <v>881</v>
+        <v>666</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>667</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>882</v>
+        <v>668</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="B39" s="27" t="s">
-        <v>884</v>
+        <v>669</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>670</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>885</v>
+        <v>671</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="B40" s="27" t="s">
-        <v>887</v>
+        <v>672</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>673</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>888</v>
+        <v>674</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="B41" s="27" t="s">
-        <v>890</v>
+        <v>675</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>676</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>891</v>
+        <v>677</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="B42" s="27" t="s">
-        <v>893</v>
+        <v>678</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>679</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>894</v>
+        <v>680</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="B43" s="28" t="s">
-        <v>896</v>
+        <v>681</v>
+      </c>
+      <c r="B43" s="29" t="s">
+        <v>682</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>897</v>
+        <v>683</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>898</v>
-      </c>
-      <c r="B44" s="28" t="s">
-        <v>899</v>
+        <v>684</v>
+      </c>
+      <c r="B44" s="29" t="s">
+        <v>685</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>900</v>
+        <v>686</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="B45" s="28" t="s">
-        <v>902</v>
+        <v>687</v>
+      </c>
+      <c r="B45" s="29" t="s">
+        <v>688</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>903</v>
+        <v>689</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="B46" s="28" t="s">
-        <v>905</v>
+        <v>690</v>
+      </c>
+      <c r="B46" s="29" t="s">
+        <v>691</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>906</v>
+        <v>692</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="B47" s="28" t="s">
-        <v>908</v>
+        <v>693</v>
+      </c>
+      <c r="B47" s="29" t="s">
+        <v>694</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>909</v>
+        <v>695</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="B48" s="28" t="s">
-        <v>911</v>
+        <v>696</v>
+      </c>
+      <c r="B48" s="29" t="s">
+        <v>697</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>912</v>
+        <v>698</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="B49" s="28" t="s">
-        <v>914</v>
+        <v>699</v>
+      </c>
+      <c r="B49" s="29" t="s">
+        <v>700</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>915</v>
+        <v>701</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>917</v>
+        <v>702</v>
+      </c>
+      <c r="B50" s="29" t="s">
+        <v>703</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>918</v>
+        <v>704</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="B51" s="28" t="s">
-        <v>920</v>
+        <v>705</v>
+      </c>
+      <c r="B51" s="29" t="s">
+        <v>706</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>921</v>
+        <v>707</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>923</v>
+        <v>708</v>
+      </c>
+      <c r="B52" s="29" t="s">
+        <v>709</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>924</v>
+        <v>710</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="B53" s="28" t="s">
-        <v>926</v>
+        <v>711</v>
+      </c>
+      <c r="B53" s="29" t="s">
+        <v>712</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>927</v>
+        <v>713</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>928</v>
-      </c>
-      <c r="B54" s="28" t="s">
-        <v>929</v>
+        <v>714</v>
+      </c>
+      <c r="B54" s="29" t="s">
+        <v>715</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>930</v>
+        <v>716</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="B55" s="28" t="s">
-        <v>932</v>
+        <v>717</v>
+      </c>
+      <c r="B55" s="29" t="s">
+        <v>718</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>933</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>
@@ -4773,389 +4134,389 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="44.175" style="15" customWidth="1"/>
-    <col min="2" max="2" width="71.3583333333333" style="15" customWidth="1"/>
-    <col min="3" max="3" width="123.558333333333" style="15" customWidth="1"/>
-    <col min="4" max="4" width="82.8666666666667" style="15" customWidth="1"/>
-    <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="81.1833333333333" style="15" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="15"/>
+    <col min="1" max="1" width="44.175" style="16" customWidth="1"/>
+    <col min="2" max="2" width="71.3583333333333" style="16" customWidth="1"/>
+    <col min="3" max="3" width="123.558333333333" style="16" customWidth="1"/>
+    <col min="4" max="4" width="82.8666666666667" style="16" customWidth="1"/>
+    <col min="5" max="6" width="9" style="16"/>
+    <col min="7" max="7" width="81.1833333333333" style="16" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" s="15" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
-      <c r="A1" s="16" t="s">
+    <row r="1" s="16" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
+      <c r="A1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
-    <row r="2" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+    <row r="2" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
-    <row r="3" s="15" customFormat="1" ht="91" customHeight="1" spans="1:7">
-      <c r="A3" s="16" t="s">
+    <row r="3" s="16" customFormat="1" ht="91" customHeight="1" spans="1:7">
+      <c r="A3" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
-    <row r="4" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A4" s="16" t="s">
+    <row r="4" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
     </row>
-    <row r="5" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A5" s="16" t="s">
+    <row r="5" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="17">
         <v>10</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
-    <row r="6" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A6" s="16" t="s">
+    <row r="6" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
     </row>
-    <row r="7" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A7" s="18" t="s">
+    <row r="7" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A7" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
     </row>
-    <row r="8" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A8" s="18" t="s">
+    <row r="8" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
     </row>
-    <row r="9" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A9" s="18" t="s">
+    <row r="9" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A9" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
     </row>
-    <row r="10" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A10" s="16" t="s">
+    <row r="10" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A10" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
     </row>
-    <row r="11" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A11" s="16" t="s">
+    <row r="11" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A11" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
     </row>
-    <row r="12" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A12" s="16" t="s">
+    <row r="12" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
     </row>
-    <row r="13" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
+    <row r="13" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
     </row>
-    <row r="14" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
+    <row r="14" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
     </row>
-    <row r="15" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+    <row r="15" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
     </row>
-    <row r="16" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+    <row r="16" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
     </row>
-    <row r="17" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
+    <row r="17" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
     </row>
-    <row r="18" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
+    <row r="18" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
     </row>
-    <row r="19" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+    <row r="19" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
     </row>
-    <row r="20" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
+    <row r="20" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
     </row>
-    <row r="21" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+    <row r="21" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
     </row>
-    <row r="22" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
+    <row r="22" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
     </row>
-    <row r="23" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
+    <row r="23" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
     </row>
-    <row r="24" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+    <row r="24" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
     </row>
-    <row r="25" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
+    <row r="25" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
     </row>
-    <row r="26" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+    <row r="26" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
     </row>
-    <row r="27" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="C27" s="16"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+    <row r="27" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
     </row>
-    <row r="28" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+    <row r="28" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
     </row>
-    <row r="29" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
+    <row r="29" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
     </row>
-    <row r="30" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+    <row r="30" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
     </row>
-    <row r="31" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
+    <row r="31" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
     </row>
-    <row r="32" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+    <row r="32" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
     </row>
-    <row r="33" s="15" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
+    <row r="33" s="16" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
     </row>
-    <row r="34" s="15" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
+    <row r="34" s="16" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
     </row>
-    <row r="35" s="15" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+    <row r="35" s="16" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
     </row>
-    <row r="36" s="15" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+    <row r="36" s="16" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -5521,943 +4882,943 @@
   <dimension ref="A1:E55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" width="37.75" style="13" customWidth="1"/>
+    <col min="1" max="2" width="37.75" style="14" customWidth="1"/>
     <col min="3" max="3" width="33.0833333333333" customWidth="1"/>
     <col min="4" max="5" width="40.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="15" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="14">
+      <c r="A4" s="15">
         <v>1</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="15">
         <v>1</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="15">
         <v>80</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="15">
         <v>3</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="14">
+      <c r="A5" s="15">
         <v>2</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="15">
         <v>2</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="15">
         <v>4</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="15">
         <v>3</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <v>3</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="15">
         <v>3</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="15">
         <v>4</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="15">
         <v>3</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="14">
+      <c r="A7" s="15">
         <v>4</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="15">
         <v>4</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="15">
         <v>4</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="15">
         <v>3</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="14">
+      <c r="A8" s="15">
         <v>5</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="15">
         <v>5</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="15">
         <v>4</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="15">
         <v>3</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <v>6</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="15">
         <v>6</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="15">
         <v>4</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="15">
         <v>3</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <v>7</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="15">
         <v>7</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="15">
         <v>4</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="15">
         <v>3</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <v>8</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="15">
         <v>8</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="15">
         <v>4</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="15">
         <v>3</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="14">
+      <c r="A12" s="15">
         <v>9</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="15">
         <v>9</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="15">
         <v>4</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="15">
         <v>3</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="14">
+      <c r="A13" s="15">
         <v>10</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="15">
         <v>10</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="15">
         <v>4</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="15">
         <v>3</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="14">
+      <c r="A14" s="15">
         <v>11</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="15">
         <v>11</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="15">
         <v>4</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="15">
         <v>3</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="14">
+      <c r="A15" s="15">
         <v>12</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="15">
         <v>12</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="15">
         <v>4</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="15">
         <v>3</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="14">
+      <c r="A16" s="15">
         <v>13</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="15">
         <v>13</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="15">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="15">
         <v>3</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="14">
+      <c r="A17" s="15">
         <v>14</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="15">
         <v>14</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="15">
         <v>4</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="15">
         <v>3</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="14">
+      <c r="A18" s="15">
         <v>15</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="15">
         <v>15</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="15">
         <v>4</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="15">
         <v>3</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="14">
+      <c r="A19" s="15">
         <v>16</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="15">
         <v>16</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="15">
         <v>4</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="15">
         <v>3</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="14">
+      <c r="A20" s="15">
         <v>17</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="15">
         <v>17</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="15">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="15">
         <v>3</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="14">
+      <c r="A21" s="15">
         <v>18</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="15">
         <v>18</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="15">
         <v>4</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="15">
         <v>3</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="14">
+      <c r="A22" s="15">
         <v>19</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="15">
         <v>19</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="15">
         <v>4</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="15">
         <v>3</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="14">
+      <c r="A23" s="15">
         <v>20</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="15">
         <v>20</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="15">
         <v>4</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="15">
         <v>3</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="14">
+      <c r="A24" s="15">
         <v>21</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="15">
         <v>21</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="15">
         <v>4</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="15">
         <v>3</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="14">
+      <c r="A25" s="15">
         <v>22</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="15">
         <v>22</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="15">
         <v>4</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="15">
         <v>3</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="14">
+      <c r="A26" s="15">
         <v>23</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="15">
         <v>23</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="15">
         <v>4</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="15">
         <v>3</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="14">
+      <c r="A27" s="15">
         <v>24</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="15">
         <v>24</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="15">
         <v>4</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="15">
         <v>3</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="14">
+      <c r="A28" s="15">
         <v>25</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="15">
         <v>25</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="15">
         <v>4</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="15">
         <v>3</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="14">
+      <c r="A29" s="15">
         <v>26</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="15">
         <v>26</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="15">
         <v>4</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="15">
         <v>3</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="14">
+      <c r="A30" s="15">
         <v>27</v>
       </c>
-      <c r="B30" s="14">
+      <c r="B30" s="15">
         <v>27</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="15">
         <v>4</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="15">
         <v>3</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="14">
+      <c r="A31" s="15">
         <v>28</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="15">
         <v>28</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="15">
         <v>4</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="15">
         <v>3</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="14">
+      <c r="A32" s="15">
         <v>29</v>
       </c>
-      <c r="B32" s="14">
+      <c r="B32" s="15">
         <v>29</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="15">
         <v>4</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="15">
         <v>3</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="14">
+      <c r="A33" s="15">
         <v>30</v>
       </c>
-      <c r="B33" s="14">
+      <c r="B33" s="15">
         <v>30</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="15">
         <v>4</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="15">
         <v>3</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="14">
+      <c r="A34" s="15">
         <v>31</v>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="15">
         <v>31</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="15">
         <v>4</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="15">
         <v>3</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="14">
+      <c r="A35" s="15">
         <v>32</v>
       </c>
-      <c r="B35" s="14">
+      <c r="B35" s="15">
         <v>32</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="15">
         <v>4</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="15">
         <v>3</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="14">
+      <c r="A36" s="15">
         <v>33</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="15">
         <v>33</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="15">
         <v>4</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="15">
         <v>3</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="14">
+      <c r="A37" s="15">
         <v>34</v>
       </c>
-      <c r="B37" s="14">
+      <c r="B37" s="15">
         <v>34</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="15">
         <v>4</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="15">
         <v>3</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="14">
+      <c r="A38" s="15">
         <v>35</v>
       </c>
-      <c r="B38" s="14">
+      <c r="B38" s="15">
         <v>35</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="15">
         <v>4</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="15">
         <v>3</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="14">
+      <c r="A39" s="15">
         <v>36</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="15">
         <v>36</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="15">
         <v>4</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="15">
         <v>3</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="14">
+      <c r="A40" s="15">
         <v>37</v>
       </c>
-      <c r="B40" s="14">
+      <c r="B40" s="15">
         <v>37</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="15">
         <v>4</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="15">
         <v>3</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="14">
+      <c r="A41" s="15">
         <v>38</v>
       </c>
-      <c r="B41" s="14">
+      <c r="B41" s="15">
         <v>38</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="15">
         <v>4</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D41" s="15">
         <v>3</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="14">
+      <c r="A42" s="15">
         <v>39</v>
       </c>
-      <c r="B42" s="14">
+      <c r="B42" s="15">
         <v>39</v>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="15">
         <v>4</v>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="15">
         <v>3</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="14">
+      <c r="A43" s="15">
         <v>40</v>
       </c>
-      <c r="B43" s="14">
+      <c r="B43" s="15">
         <v>40</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="15">
         <v>4</v>
       </c>
-      <c r="D43" s="14">
+      <c r="D43" s="15">
         <v>3</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="14">
+      <c r="A44" s="15">
         <v>41</v>
       </c>
-      <c r="B44" s="14">
+      <c r="B44" s="15">
         <v>41</v>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="15">
         <v>4</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="15">
         <v>3</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="14">
+      <c r="A45" s="15">
         <v>42</v>
       </c>
-      <c r="B45" s="14">
+      <c r="B45" s="15">
         <v>42</v>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="15">
         <v>4</v>
       </c>
-      <c r="D45" s="14">
+      <c r="D45" s="15">
         <v>3</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="14">
+      <c r="A46" s="15">
         <v>43</v>
       </c>
-      <c r="B46" s="14">
+      <c r="B46" s="15">
         <v>43</v>
       </c>
-      <c r="C46" s="14">
+      <c r="C46" s="15">
         <v>4</v>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="15">
         <v>3</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="14">
+      <c r="A47" s="15">
         <v>44</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="15">
         <v>44</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="15">
         <v>4</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D47" s="15">
         <v>3</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="14">
+      <c r="A48" s="15">
         <v>45</v>
       </c>
-      <c r="B48" s="14">
+      <c r="B48" s="15">
         <v>45</v>
       </c>
-      <c r="C48" s="14">
+      <c r="C48" s="15">
         <v>4</v>
       </c>
-      <c r="D48" s="14">
+      <c r="D48" s="15">
         <v>3</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="14">
+      <c r="A49" s="15">
         <v>46</v>
       </c>
-      <c r="B49" s="14">
+      <c r="B49" s="15">
         <v>46</v>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="15">
         <v>4</v>
       </c>
-      <c r="D49" s="14">
+      <c r="D49" s="15">
         <v>3</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="14">
+      <c r="A50" s="15">
         <v>47</v>
       </c>
-      <c r="B50" s="14">
+      <c r="B50" s="15">
         <v>47</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="15">
         <v>4</v>
       </c>
-      <c r="D50" s="14">
+      <c r="D50" s="15">
         <v>3</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="14">
+      <c r="A51" s="15">
         <v>48</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="15">
         <v>48</v>
       </c>
-      <c r="C51" s="14">
+      <c r="C51" s="15">
         <v>4</v>
       </c>
-      <c r="D51" s="14">
+      <c r="D51" s="15">
         <v>3</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="14">
+      <c r="A52" s="15">
         <v>49</v>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="15">
         <v>49</v>
       </c>
-      <c r="C52" s="14">
+      <c r="C52" s="15">
         <v>4</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="15">
         <v>3</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="14">
+      <c r="A53" s="15">
         <v>50</v>
       </c>
-      <c r="B53" s="14">
+      <c r="B53" s="15">
         <v>50</v>
       </c>
-      <c r="C53" s="14">
+      <c r="C53" s="15">
         <v>4</v>
       </c>
-      <c r="D53" s="14">
+      <c r="D53" s="15">
         <v>3</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="14">
+      <c r="A54" s="15">
         <v>51</v>
       </c>
-      <c r="B54" s="14">
+      <c r="B54" s="15">
         <v>51</v>
       </c>
-      <c r="C54" s="14">
+      <c r="C54" s="15">
         <v>4</v>
       </c>
-      <c r="D54" s="14">
+      <c r="D54" s="15">
         <v>3</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="14">
+      <c r="A55" s="15">
         <v>52</v>
       </c>
-      <c r="B55" s="14">
+      <c r="B55" s="15">
         <v>52</v>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="15">
         <v>4</v>
       </c>
-      <c r="D55" s="14">
+      <c r="D55" s="15">
         <v>3</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="15" t="s">
         <v>89</v>
       </c>
     </row>
@@ -6473,801 +5834,801 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="27.75" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="25.175" style="9" customWidth="1"/>
-    <col min="2" max="2" width="13.575" style="9" customWidth="1"/>
-    <col min="3" max="3" width="127.141666666667" style="9" customWidth="1"/>
-    <col min="4" max="4" width="49" style="9" customWidth="1"/>
-    <col min="5" max="5" width="92.9666666666667" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="25.175" style="10" customWidth="1"/>
+    <col min="2" max="2" width="13.575" style="10" customWidth="1"/>
+    <col min="3" max="3" width="127.141666666667" style="10" customWidth="1"/>
+    <col min="4" max="4" width="49" style="10" customWidth="1"/>
+    <col min="5" max="5" width="92.9666666666667" style="11" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="12" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="11">
+      <c r="A4" s="12">
         <v>1</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="12">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="11">
+      <c r="A5" s="12">
         <v>2</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="12">
         <v>2</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="11">
+      <c r="A6" s="12">
         <v>3</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="12">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="11">
+      <c r="A7" s="12">
         <v>4</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="12">
         <v>4</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="11">
+      <c r="A8" s="12">
         <v>5</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="12">
         <v>5</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="11">
+      <c r="A9" s="12">
         <v>6</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="12">
         <v>6</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="11">
+      <c r="A10" s="12">
         <v>7</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="12">
         <v>7</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="11">
+      <c r="A11" s="12">
         <v>8</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="12">
         <v>8</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="11">
+      <c r="A12" s="12">
         <v>9</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="12">
         <v>9</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="11">
+      <c r="A13" s="12">
         <v>10</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="12">
         <v>10</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="11">
+      <c r="A14" s="12">
         <v>11</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="12">
         <v>11</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="11">
+      <c r="A15" s="12">
         <v>12</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="12">
         <v>12</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="11">
+      <c r="A16" s="12">
         <v>13</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="12">
         <v>13</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="11">
+      <c r="A17" s="12">
         <v>14</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="12">
         <v>14</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="11">
+      <c r="A18" s="12">
         <v>15</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="12">
         <v>15</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="11">
+      <c r="A19" s="12">
         <v>16</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="12">
         <v>16</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="11">
+      <c r="A20" s="12">
         <v>17</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="12">
         <v>17</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="11">
+      <c r="A21" s="12">
         <v>18</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="12">
         <v>18</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="11">
+      <c r="A22" s="12">
         <v>19</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="12">
         <v>19</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="11">
+      <c r="A23" s="12">
         <v>20</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="12">
         <v>20</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="11">
+      <c r="A24" s="12">
         <v>21</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="12">
         <v>21</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="11">
+      <c r="A25" s="12">
         <v>22</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="12">
         <v>22</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="11">
+      <c r="A26" s="12">
         <v>23</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="12">
         <v>23</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="11">
+      <c r="A27" s="12">
         <v>24</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="12">
         <v>24</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="11">
+      <c r="A28" s="12">
         <v>25</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="12">
         <v>25</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="11">
+      <c r="A29" s="12">
         <v>26</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="12">
         <v>26</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="11">
+      <c r="A30" s="12">
         <v>27</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="12">
         <v>27</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="11">
+      <c r="A31" s="12">
         <v>28</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="12">
         <v>28</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="11">
+      <c r="A32" s="12">
         <v>29</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="12">
         <v>29</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="11">
+      <c r="A33" s="12">
         <v>30</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="12">
         <v>30</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="11">
+      <c r="A34" s="12">
         <v>31</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="12">
         <v>31</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="11">
+      <c r="A35" s="12">
         <v>32</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="12">
         <v>32</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="11">
+      <c r="A36" s="12">
         <v>33</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="12">
         <v>33</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="11">
+      <c r="A37" s="12">
         <v>34</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="12">
         <v>34</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="11">
+      <c r="A38" s="12">
         <v>35</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="12">
         <v>35</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="11">
+      <c r="A39" s="12">
         <v>36</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="12">
         <v>36</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="11">
+      <c r="A40" s="12">
         <v>37</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="12">
         <v>37</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="11">
+      <c r="A41" s="12">
         <v>38</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="12">
         <v>38</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="11">
+      <c r="A42" s="12">
         <v>39</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="12">
         <v>39</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="12" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="12">
+      <c r="A43" s="13">
         <v>40</v>
       </c>
-      <c r="B43" s="12">
+      <c r="B43" s="13">
         <v>40</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="12">
+      <c r="A44" s="13">
         <v>41</v>
       </c>
-      <c r="B44" s="12">
+      <c r="B44" s="13">
         <v>41</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="12">
+      <c r="A45" s="13">
         <v>42</v>
       </c>
-      <c r="B45" s="12">
+      <c r="B45" s="13">
         <v>42</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="12">
+      <c r="A46" s="13">
         <v>43</v>
       </c>
-      <c r="B46" s="12">
+      <c r="B46" s="13">
         <v>43</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="12">
+      <c r="A47" s="13">
         <v>44</v>
       </c>
-      <c r="B47" s="12">
+      <c r="B47" s="13">
         <v>44</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="12">
+      <c r="A48" s="13">
         <v>45</v>
       </c>
-      <c r="B48" s="12">
+      <c r="B48" s="13">
         <v>45</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="12">
+      <c r="A49" s="13">
         <v>46</v>
       </c>
-      <c r="B49" s="12">
+      <c r="B49" s="13">
         <v>46</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="12">
+      <c r="A50" s="13">
         <v>47</v>
       </c>
-      <c r="B50" s="12">
+      <c r="B50" s="13">
         <v>47</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="12">
+      <c r="A51" s="13">
         <v>48</v>
       </c>
-      <c r="B51" s="12">
+      <c r="B51" s="13">
         <v>48</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="12">
+      <c r="A52" s="13">
         <v>49</v>
       </c>
-      <c r="B52" s="12">
+      <c r="B52" s="13">
         <v>49</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="12">
+      <c r="A53" s="13">
         <v>50</v>
       </c>
-      <c r="B53" s="12">
+      <c r="B53" s="13">
         <v>50</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="12">
+      <c r="A54" s="13">
         <v>51</v>
       </c>
-      <c r="B54" s="12">
+      <c r="B54" s="13">
         <v>51</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="12">
+      <c r="A55" s="13">
         <v>52</v>
       </c>
-      <c r="B55" s="12">
+      <c r="B55" s="13">
         <v>52</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
+      <c r="A56" s="13"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="C58" s="12"/>
+      <c r="C58" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7385,10 +6746,10 @@
         <f>CEILING(A4/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="9">
         <v>73689874069532</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>164</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -7412,10 +6773,10 @@
         <f t="shared" ref="E5:E36" si="0">CEILING(A5/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="9">
         <v>103338086714343</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>167</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -7441,10 +6802,10 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <v>114468149232543</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
         <v>169</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -7470,10 +6831,10 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="9">
         <v>102034222005672</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>171</v>
       </c>
       <c r="H7" s="2" t="s">
@@ -7499,10 +6860,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <v>83505287199254</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>173</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -7526,10 +6887,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="9">
         <v>82413393212572</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>175</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -7554,10 +6915,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="9">
         <v>93587171790136</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="9" t="s">
         <v>177</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -7582,10 +6943,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="9">
         <v>98881391823727</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="9" t="s">
         <v>179</v>
       </c>
       <c r="H11" s="2" t="s">
@@ -7610,10 +6971,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="9">
         <v>140583336060167</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="9" t="s">
         <v>181</v>
       </c>
       <c r="H12" s="2" t="s">
@@ -7637,10 +6998,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="9">
         <v>111194186656631</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="9" t="s">
         <v>183</v>
       </c>
       <c r="H13" s="2" t="s">
@@ -7664,10 +7025,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <v>133914186848952</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="9" t="s">
         <v>185</v>
       </c>
       <c r="H14" s="2" t="s">
@@ -7691,10 +7052,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="9">
         <v>122198581325096</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="9" t="s">
         <v>187</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -7718,10 +7079,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F16" s="8">
+      <c r="F16" s="9">
         <v>137046890645413</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="9" t="s">
         <v>189</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -7749,10 +7110,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F17" s="8">
+      <c r="F17" s="9">
         <v>102352328211075</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="9" t="s">
         <v>191</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -7780,10 +7141,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="9">
         <v>82050572064304</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="9" t="s">
         <v>193</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -7811,10 +7172,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F19" s="8">
+      <c r="F19" s="9">
         <v>78831531789183</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="9" t="s">
         <v>195</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -7842,10 +7203,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F20" s="8">
+      <c r="F20" s="9">
         <v>108041083429458</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="9" t="s">
         <v>197</v>
       </c>
       <c r="H20" s="2" t="s">
@@ -7873,10 +7234,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F21" s="8">
+      <c r="F21" s="9">
         <v>86299665819505</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="9" t="s">
         <v>199</v>
       </c>
       <c r="H21" s="2" t="s">
@@ -7904,10 +7265,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F22" s="9">
         <v>123569723967761</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="9" t="s">
         <v>201</v>
       </c>
       <c r="H22" s="2" t="s">
@@ -7935,10 +7296,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="9">
         <v>119546448004051</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="9" t="s">
         <v>203</v>
       </c>
       <c r="H23" s="2" t="s">
@@ -7966,10 +7327,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F24" s="8">
+      <c r="F24" s="9">
         <v>91007101306341</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="9" t="s">
         <v>205</v>
       </c>
       <c r="H24" s="2" t="s">
@@ -7997,10 +7358,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F25" s="8">
+      <c r="F25" s="9">
         <v>91391954516503</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="9" t="s">
         <v>207</v>
       </c>
       <c r="H25" s="2" t="s">
@@ -8028,10 +7389,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F26" s="8">
+      <c r="F26" s="9">
         <v>109276220541606</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="9" t="s">
         <v>209</v>
       </c>
       <c r="H26" s="2" t="s">
@@ -8059,10 +7420,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F27" s="8">
+      <c r="F27" s="9">
         <v>108792020810626</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="9" t="s">
         <v>211</v>
       </c>
       <c r="H27" s="2" t="s">
@@ -8090,10 +7451,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F28" s="8">
+      <c r="F28" s="9">
         <v>94990895501990</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="9" t="s">
         <v>213</v>
       </c>
       <c r="H28" s="2" t="s">
@@ -8121,10 +7482,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F29" s="8">
+      <c r="F29" s="9">
         <v>92053411642730</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="9" t="s">
         <v>215</v>
       </c>
       <c r="H29" s="2" t="s">
@@ -8152,10 +7513,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F30" s="9">
         <v>129094955837159</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" s="9" t="s">
         <v>217</v>
       </c>
       <c r="H30" s="2" t="s">
@@ -8183,10 +7544,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F31" s="8">
+      <c r="F31" s="9">
         <v>136720402016106</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="9" t="s">
         <v>219</v>
       </c>
       <c r="H31" s="2" t="s">
@@ -8214,10 +7575,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F32" s="8">
+      <c r="F32" s="9">
         <v>103985740716894</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="9" t="s">
         <v>221</v>
       </c>
       <c r="H32" s="2" t="s">
@@ -8245,10 +7606,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F33" s="8">
+      <c r="F33" s="9">
         <v>110363379748775</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="9" t="s">
         <v>223</v>
       </c>
       <c r="H33" s="2" t="s">
@@ -8272,10 +7633,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F34" s="8">
+      <c r="F34" s="9">
         <v>130735151388109</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="9" t="s">
         <v>225</v>
       </c>
       <c r="H34" s="2" t="s">
@@ -8299,10 +7660,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="9">
         <v>112469820699203</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="9" t="s">
         <v>227</v>
       </c>
       <c r="H35" s="2" t="s">
@@ -8326,10 +7687,10 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F36" s="8">
+      <c r="F36" s="9">
         <v>104485794834544</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="9" t="s">
         <v>229</v>
       </c>
       <c r="H36" s="2" t="s">
@@ -8357,10 +7718,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>6</v>
       </c>
-      <c r="F37" s="8">
+      <c r="F37" s="9">
         <v>99220241284612</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="9" t="s">
         <v>231</v>
       </c>
       <c r="H37" s="2" t="s">
@@ -8384,10 +7745,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>7</v>
       </c>
-      <c r="F38" s="8">
+      <c r="F38" s="9">
         <v>80947939739818</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="9" t="s">
         <v>233</v>
       </c>
       <c r="H38" s="2" t="s">
@@ -8411,10 +7772,10 @@
         <f t="shared" ref="E39:E72" si="1">CEILING(A39/4,1)</f>
         <v>9</v>
       </c>
-      <c r="F39" s="8">
+      <c r="F39" s="9">
         <v>107316878006177</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="9" t="s">
         <v>235</v>
       </c>
       <c r="H39" s="2" t="s">
@@ -8442,10 +7803,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F40" s="8">
+      <c r="F40" s="9">
         <v>81581045315216</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="9" t="s">
         <v>237</v>
       </c>
       <c r="H40" s="2" t="s">
@@ -8473,10 +7834,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F41" s="8">
+      <c r="F41" s="9">
         <v>112660123650049</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G41" s="9" t="s">
         <v>239</v>
       </c>
       <c r="H41" s="2" t="s">
@@ -8500,10 +7861,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F42" s="8">
+      <c r="F42" s="9">
         <v>105948548039431</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="9" t="s">
         <v>241</v>
       </c>
       <c r="H42" s="2" t="s">
@@ -8527,10 +7888,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F43" s="8">
+      <c r="F43" s="9">
         <v>136608949835509</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="9" t="s">
         <v>243</v>
       </c>
       <c r="H43" s="2" t="s">
@@ -8554,10 +7915,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F44" s="8">
+      <c r="F44" s="9">
         <v>123814344941081</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="G44" s="9" t="s">
         <v>245</v>
       </c>
       <c r="H44" s="2" t="s">
@@ -8581,10 +7942,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F45" s="8">
+      <c r="F45" s="9">
         <v>70631811357234</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="G45" s="9" t="s">
         <v>247</v>
       </c>
       <c r="H45" s="2" t="s">
@@ -8608,10 +7969,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F46" s="8">
+      <c r="F46" s="9">
         <v>121882306399734</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" s="9" t="s">
         <v>249</v>
       </c>
       <c r="H46" s="2" t="s">
@@ -8635,10 +7996,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F47" s="8">
+      <c r="F47" s="9">
         <v>98362111955314</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" s="9" t="s">
         <v>251</v>
       </c>
       <c r="H47" s="2" t="s">
@@ -8662,10 +8023,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F48" s="8">
+      <c r="F48" s="9">
         <v>87499152943626</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="G48" s="9" t="s">
         <v>253</v>
       </c>
       <c r="H48" s="2" t="s">
@@ -8689,10 +8050,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F49" s="8">
+      <c r="F49" s="9">
         <v>94526628741923</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="G49" s="9" t="s">
         <v>255</v>
       </c>
       <c r="H49" s="2" t="s">
@@ -8716,10 +8077,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F50" s="8">
+      <c r="F50" s="9">
         <v>135071120477292</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" s="9" t="s">
         <v>257</v>
       </c>
       <c r="H50" s="2" t="s">
@@ -8743,10 +8104,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F51" s="8">
+      <c r="F51" s="9">
         <v>73644651229136</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="G51" s="9" t="s">
         <v>259</v>
       </c>
       <c r="H51" s="2" t="s">
@@ -8770,10 +8131,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F52" s="8">
+      <c r="F52" s="9">
         <v>77926265714695</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G52" s="9" t="s">
         <v>261</v>
       </c>
       <c r="H52" s="2" t="s">
@@ -8797,10 +8158,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F53" s="8">
+      <c r="F53" s="9">
         <v>82854353471706</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="G53" s="9" t="s">
         <v>263</v>
       </c>
       <c r="H53" s="2" t="s">
@@ -8824,10 +8185,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F54" s="8">
+      <c r="F54" s="9">
         <v>77671502371070</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="G54" s="9" t="s">
         <v>265</v>
       </c>
       <c r="H54" s="2" t="s">
@@ -8851,10 +8212,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F55" s="8">
+      <c r="F55" s="9">
         <v>70793360263168</v>
       </c>
-      <c r="G55" s="8" t="s">
+      <c r="G55" s="9" t="s">
         <v>267</v>
       </c>
       <c r="H55" s="2" t="s">
@@ -8878,10 +8239,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F56" s="8">
+      <c r="F56" s="9">
         <v>84818213347817</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="G56" s="9" t="s">
         <v>269</v>
       </c>
       <c r="H56" s="2" t="s">
@@ -8905,10 +8266,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F57" s="8">
+      <c r="F57" s="9">
         <v>91851759457969</v>
       </c>
-      <c r="G57" s="8" t="s">
+      <c r="G57" s="9" t="s">
         <v>271</v>
       </c>
       <c r="H57" s="2" t="s">
@@ -8932,10 +8293,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F58" s="8">
+      <c r="F58" s="9">
         <v>121890208198805</v>
       </c>
-      <c r="G58" s="8" t="s">
+      <c r="G58" s="9" t="s">
         <v>273</v>
       </c>
       <c r="H58" s="2" t="s">
@@ -8959,10 +8320,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F59" s="8">
+      <c r="F59" s="9">
         <v>117985852407168</v>
       </c>
-      <c r="G59" s="8" t="s">
+      <c r="G59" s="9" t="s">
         <v>275</v>
       </c>
       <c r="H59" s="2" t="s">
@@ -8986,10 +8347,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F60" s="8">
+      <c r="F60" s="9">
         <v>97339206973141</v>
       </c>
-      <c r="G60" s="8" t="s">
+      <c r="G60" s="9" t="s">
         <v>277</v>
       </c>
       <c r="H60" s="2" t="s">
@@ -9013,10 +8374,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="9">
         <v>91021502703797</v>
       </c>
-      <c r="G61" s="8" t="s">
+      <c r="G61" s="9" t="s">
         <v>279</v>
       </c>
       <c r="H61" s="2" t="s">
@@ -9040,10 +8401,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F62" s="8">
+      <c r="F62" s="9">
         <v>118793829418414</v>
       </c>
-      <c r="G62" s="8" t="s">
+      <c r="G62" s="9" t="s">
         <v>281</v>
       </c>
       <c r="H62" s="2" t="s">
@@ -9067,10 +8428,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F63" s="8">
+      <c r="F63" s="9">
         <v>108919245506457</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="G63" s="9" t="s">
         <v>283</v>
       </c>
       <c r="H63" s="2" t="s">
@@ -9094,10 +8455,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F64" s="8">
+      <c r="F64" s="9">
         <v>135998992968408</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="G64" s="9" t="s">
         <v>285</v>
       </c>
       <c r="H64" s="2" t="s">
@@ -9121,10 +8482,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F65" s="8">
+      <c r="F65" s="9">
         <v>124995167587191</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="G65" s="9" t="s">
         <v>287</v>
       </c>
       <c r="H65" s="2" t="s">
@@ -9148,10 +8509,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F66" s="8">
+      <c r="F66" s="9">
         <v>100207039759139</v>
       </c>
-      <c r="G66" s="8" t="s">
+      <c r="G66" s="9" t="s">
         <v>289</v>
       </c>
       <c r="H66" s="2" t="s">
@@ -9175,10 +8536,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F67" s="8">
+      <c r="F67" s="9">
         <v>117284808467540</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="G67" s="9" t="s">
         <v>291</v>
       </c>
       <c r="H67" s="2" t="s">
@@ -9202,10 +8563,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="9">
         <v>100856293823266</v>
       </c>
-      <c r="G68" s="8" t="s">
+      <c r="G68" s="9" t="s">
         <v>293</v>
       </c>
       <c r="H68" s="2" t="s">
@@ -9229,10 +8590,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F69" s="8">
+      <c r="F69" s="9">
         <v>131767978667574</v>
       </c>
-      <c r="G69" s="8" t="s">
+      <c r="G69" s="9" t="s">
         <v>295</v>
       </c>
       <c r="H69" s="2" t="s">
@@ -9256,10 +8617,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F70" s="8">
+      <c r="F70" s="9">
         <v>137793066084531</v>
       </c>
-      <c r="G70" s="8" t="s">
+      <c r="G70" s="9" t="s">
         <v>297</v>
       </c>
       <c r="H70" s="2" t="s">
@@ -9283,10 +8644,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F71" s="8">
+      <c r="F71" s="9">
         <v>89446188580427</v>
       </c>
-      <c r="G71" s="8" t="s">
+      <c r="G71" s="9" t="s">
         <v>299</v>
       </c>
       <c r="H71" s="2" t="s">
@@ -9310,10 +8671,10 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="F72" s="8">
+      <c r="F72" s="9">
         <v>122719253084629</v>
       </c>
-      <c r="G72" s="8" t="s">
+      <c r="G72" s="9" t="s">
         <v>301</v>
       </c>
       <c r="H72" s="2" t="s">
@@ -9337,10 +8698,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>15</v>
       </c>
-      <c r="F73" s="8">
+      <c r="F73" s="9">
         <v>112549310275337</v>
       </c>
-      <c r="G73" s="8" t="s">
+      <c r="G73" s="9" t="s">
         <v>303</v>
       </c>
       <c r="H73" s="2" t="s">
@@ -9364,10 +8725,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F74" s="8">
+      <c r="F74" s="9">
         <v>88430290010781</v>
       </c>
-      <c r="G74" s="8" t="s">
+      <c r="G74" s="9" t="s">
         <v>305</v>
       </c>
       <c r="H74" s="2" t="s">
@@ -9391,10 +8752,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F75" s="8">
+      <c r="F75" s="9">
         <v>71786460797721</v>
       </c>
-      <c r="G75" s="8" t="s">
+      <c r="G75" s="9" t="s">
         <v>307</v>
       </c>
       <c r="H75" s="2" t="s">
@@ -9418,10 +8779,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F76" s="8">
+      <c r="F76" s="9">
         <v>97338088026484</v>
       </c>
-      <c r="G76" s="8" t="s">
+      <c r="G76" s="9" t="s">
         <v>309</v>
       </c>
       <c r="H76" s="2" t="s">
@@ -9445,10 +8806,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F77" s="8">
+      <c r="F77" s="9">
         <v>111210837018880</v>
       </c>
-      <c r="G77" s="8" t="s">
+      <c r="G77" s="9" t="s">
         <v>311</v>
       </c>
       <c r="H77" s="2" t="s">
@@ -9472,10 +8833,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F78" s="8">
+      <c r="F78" s="9">
         <v>91454753076661</v>
       </c>
-      <c r="G78" s="8" t="s">
+      <c r="G78" s="9" t="s">
         <v>313</v>
       </c>
       <c r="H78" s="2" t="s">
@@ -9499,10 +8860,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F79" s="8">
+      <c r="F79" s="9">
         <v>140372090697167</v>
       </c>
-      <c r="G79" s="8" t="s">
+      <c r="G79" s="9" t="s">
         <v>315</v>
       </c>
       <c r="H79" s="2" t="s">
@@ -9526,10 +8887,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F80" s="8">
+      <c r="F80" s="9">
         <v>85844805634635</v>
       </c>
-      <c r="G80" s="8" t="s">
+      <c r="G80" s="9" t="s">
         <v>317</v>
       </c>
       <c r="H80" s="2" t="s">
@@ -9553,10 +8914,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F81" s="8">
+      <c r="F81" s="9">
         <v>121461526979401</v>
       </c>
-      <c r="G81" s="8" t="s">
+      <c r="G81" s="9" t="s">
         <v>319</v>
       </c>
       <c r="H81" s="2" t="s">
@@ -9580,10 +8941,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F82" s="8">
+      <c r="F82" s="9">
         <v>119745475735524</v>
       </c>
-      <c r="G82" s="8" t="s">
+      <c r="G82" s="9" t="s">
         <v>321</v>
       </c>
       <c r="H82" s="2" t="s">
@@ -9607,10 +8968,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F83" s="8">
+      <c r="F83" s="9">
         <v>101894479505985</v>
       </c>
-      <c r="G83" s="8" t="s">
+      <c r="G83" s="9" t="s">
         <v>323</v>
       </c>
       <c r="H83" s="2" t="s">
@@ -9634,10 +8995,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F84" s="8">
+      <c r="F84" s="9">
         <v>130984354600200</v>
       </c>
-      <c r="G84" s="8" t="s">
+      <c r="G84" s="9" t="s">
         <v>325</v>
       </c>
       <c r="H84" s="2" t="s">
@@ -9661,10 +9022,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F85" s="8">
+      <c r="F85" s="9">
         <v>139575750428458</v>
       </c>
-      <c r="G85" s="8" t="s">
+      <c r="G85" s="9" t="s">
         <v>327</v>
       </c>
       <c r="H85" s="2" t="s">
@@ -9688,10 +9049,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F86" s="8">
+      <c r="F86" s="9">
         <v>111543784097462</v>
       </c>
-      <c r="G86" s="8" t="s">
+      <c r="G86" s="9" t="s">
         <v>329</v>
       </c>
       <c r="H86" s="2" t="s">
@@ -9715,10 +9076,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F87" s="8">
+      <c r="F87" s="9">
         <v>104244387773955</v>
       </c>
-      <c r="G87" s="8" t="s">
+      <c r="G87" s="9" t="s">
         <v>331</v>
       </c>
       <c r="H87" s="2" t="s">
@@ -9742,10 +9103,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F88" s="8">
+      <c r="F88" s="9">
         <v>136776890462387</v>
       </c>
-      <c r="G88" s="8" t="s">
+      <c r="G88" s="9" t="s">
         <v>333</v>
       </c>
       <c r="H88" s="2" t="s">
@@ -9769,10 +9130,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F89" s="8">
+      <c r="F89" s="9">
         <v>126165124926341</v>
       </c>
-      <c r="G89" s="8" t="s">
+      <c r="G89" s="9" t="s">
         <v>335</v>
       </c>
       <c r="H89" s="2" t="s">
@@ -9796,10 +9157,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F90" s="8">
+      <c r="F90" s="9">
         <v>76143760243972</v>
       </c>
-      <c r="G90" s="8" t="s">
+      <c r="G90" s="9" t="s">
         <v>337</v>
       </c>
       <c r="H90" s="2" t="s">
@@ -9823,10 +9184,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F91" s="8">
+      <c r="F91" s="9">
         <v>73975383470183</v>
       </c>
-      <c r="G91" s="8" t="s">
+      <c r="G91" s="9" t="s">
         <v>339</v>
       </c>
       <c r="H91" s="2" t="s">
@@ -9850,10 +9211,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F92" s="8">
+      <c r="F92" s="9">
         <v>110779582383706</v>
       </c>
-      <c r="G92" s="8" t="s">
+      <c r="G92" s="9" t="s">
         <v>341</v>
       </c>
       <c r="H92" s="2" t="s">
@@ -9877,10 +9238,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F93" s="8">
+      <c r="F93" s="9">
         <v>139231009266383</v>
       </c>
-      <c r="G93" s="8" t="s">
+      <c r="G93" s="9" t="s">
         <v>343</v>
       </c>
       <c r="H93" s="2" t="s">
@@ -9904,10 +9265,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F94" s="8">
+      <c r="F94" s="9">
         <v>122330740858585</v>
       </c>
-      <c r="G94" s="8" t="s">
+      <c r="G94" s="9" t="s">
         <v>345</v>
       </c>
       <c r="H94" s="2" t="s">
@@ -9931,10 +9292,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F95" s="8">
+      <c r="F95" s="9">
         <v>117103663687356</v>
       </c>
-      <c r="G95" s="8" t="s">
+      <c r="G95" s="9" t="s">
         <v>347</v>
       </c>
       <c r="H95" s="2" t="s">
@@ -9958,10 +9319,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F96" s="8">
+      <c r="F96" s="9">
         <v>103139070075508</v>
       </c>
-      <c r="G96" s="8" t="s">
+      <c r="G96" s="9" t="s">
         <v>349</v>
       </c>
       <c r="H96" s="2" t="s">
@@ -9985,10 +9346,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F97" s="8">
+      <c r="F97" s="9">
         <v>88725487654147</v>
       </c>
-      <c r="G97" s="8" t="s">
+      <c r="G97" s="9" t="s">
         <v>351</v>
       </c>
       <c r="H97" s="2" t="s">
@@ -10012,10 +9373,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F98" s="8">
+      <c r="F98" s="9">
         <v>72100736251601</v>
       </c>
-      <c r="G98" s="8" t="s">
+      <c r="G98" s="9" t="s">
         <v>353</v>
       </c>
       <c r="H98" s="2" t="s">
@@ -10039,10 +9400,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F99" s="8">
+      <c r="F99" s="9">
         <v>95625760850047</v>
       </c>
-      <c r="G99" s="8" t="s">
+      <c r="G99" s="9" t="s">
         <v>355</v>
       </c>
       <c r="H99" s="2" t="s">
@@ -10066,10 +9427,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F100" s="8">
+      <c r="F100" s="9">
         <v>110809850119673</v>
       </c>
-      <c r="G100" s="8" t="s">
+      <c r="G100" s="9" t="s">
         <v>357</v>
       </c>
       <c r="H100" s="2" t="s">
@@ -10093,10 +9454,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F101" s="8">
+      <c r="F101" s="9">
         <v>128268169997293</v>
       </c>
-      <c r="G101" s="8" t="s">
+      <c r="G101" s="9" t="s">
         <v>359</v>
       </c>
       <c r="H101" s="2" t="s">
@@ -10120,10 +9481,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F102" s="8">
+      <c r="F102" s="9">
         <v>81568443921942</v>
       </c>
-      <c r="G102" s="8" t="s">
+      <c r="G102" s="9" t="s">
         <v>361</v>
       </c>
       <c r="H102" s="2" t="s">
@@ -10147,10 +9508,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F103" s="8">
+      <c r="F103" s="9">
         <v>80275546299866</v>
       </c>
-      <c r="G103" s="8" t="s">
+      <c r="G103" s="9" t="s">
         <v>363</v>
       </c>
       <c r="H103" s="2" t="s">
@@ -10174,10 +9535,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F104" s="8">
+      <c r="F104" s="9">
         <v>104304476590207</v>
       </c>
-      <c r="G104" s="8" t="s">
+      <c r="G104" s="9" t="s">
         <v>365</v>
       </c>
       <c r="H104" s="2" t="s">
@@ -10201,10 +9562,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F105" s="8">
+      <c r="F105" s="9">
         <v>129658959682028</v>
       </c>
-      <c r="G105" s="8" t="s">
+      <c r="G105" s="9" t="s">
         <v>367</v>
       </c>
       <c r="H105" s="2" t="s">
@@ -10228,10 +9589,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F106" s="8">
+      <c r="F106" s="9">
         <v>91807501817775</v>
       </c>
-      <c r="G106" s="8" t="s">
+      <c r="G106" s="9" t="s">
         <v>369</v>
       </c>
       <c r="H106" s="2" t="s">
@@ -10255,10 +9616,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F107" s="8">
+      <c r="F107" s="9">
         <v>119033390105144</v>
       </c>
-      <c r="G107" s="8" t="s">
+      <c r="G107" s="9" t="s">
         <v>371</v>
       </c>
       <c r="H107" s="2" t="s">
@@ -10281,10 +9642,10 @@
       <c r="E108" s="1">
         <v>24</v>
       </c>
-      <c r="F108" s="8">
+      <c r="F108" s="9">
         <v>96459025721039</v>
       </c>
-      <c r="G108" s="8" t="s">
+      <c r="G108" s="9" t="s">
         <v>373</v>
       </c>
       <c r="H108" s="2" t="s">
@@ -10308,10 +9669,10 @@
       <c r="E109" s="1">
         <v>24</v>
       </c>
-      <c r="F109" s="8">
+      <c r="F109" s="9">
         <v>138981227536547</v>
       </c>
-      <c r="G109" s="8" t="s">
+      <c r="G109" s="9" t="s">
         <v>375</v>
       </c>
       <c r="H109" s="2" t="s">
@@ -10335,10 +9696,10 @@
       <c r="E110" s="1">
         <v>25</v>
       </c>
-      <c r="F110" s="8">
+      <c r="F110" s="9">
         <v>119423227657745</v>
       </c>
-      <c r="G110" s="8" t="s">
+      <c r="G110" s="9" t="s">
         <v>377</v>
       </c>
       <c r="H110" s="2" t="s">
@@ -10362,10 +9723,10 @@
       <c r="E111" s="1">
         <v>25</v>
       </c>
-      <c r="F111" s="8">
+      <c r="F111" s="9">
         <v>96126442221467</v>
       </c>
-      <c r="G111" s="8" t="s">
+      <c r="G111" s="9" t="s">
         <v>379</v>
       </c>
       <c r="H111" s="2" t="s">
@@ -10389,10 +9750,10 @@
       <c r="E112" s="1">
         <v>25</v>
       </c>
-      <c r="F112" s="8">
+      <c r="F112" s="9">
         <v>115960927208349</v>
       </c>
-      <c r="G112" s="8" t="s">
+      <c r="G112" s="9" t="s">
         <v>381</v>
       </c>
       <c r="H112" s="2" t="s">
@@ -10416,10 +9777,10 @@
       <c r="E113" s="1">
         <v>25</v>
       </c>
-      <c r="F113" s="8">
+      <c r="F113" s="9">
         <v>130983706534388</v>
       </c>
-      <c r="G113" s="8" t="s">
+      <c r="G113" s="9" t="s">
         <v>383</v>
       </c>
       <c r="H113" s="2" t="s">
@@ -10443,10 +9804,10 @@
       <c r="E114" s="1">
         <v>26</v>
       </c>
-      <c r="F114" s="8">
+      <c r="F114" s="9">
         <v>95831043321895</v>
       </c>
-      <c r="G114" s="8" t="s">
+      <c r="G114" s="9" t="s">
         <v>385</v>
       </c>
       <c r="H114" s="2" t="s">
@@ -10470,10 +9831,10 @@
       <c r="E115" s="1">
         <v>26</v>
       </c>
-      <c r="F115" s="8">
+      <c r="F115" s="9">
         <v>112143431254973</v>
       </c>
-      <c r="G115" s="8" t="s">
+      <c r="G115" s="9" t="s">
         <v>387</v>
       </c>
       <c r="H115" s="2" t="s">
@@ -10497,10 +9858,10 @@
       <c r="E116" s="1">
         <v>26</v>
       </c>
-      <c r="F116" s="8">
+      <c r="F116" s="9">
         <v>118258115873868</v>
       </c>
-      <c r="G116" s="8" t="s">
+      <c r="G116" s="9" t="s">
         <v>389</v>
       </c>
       <c r="H116" s="2" t="s">
@@ -10524,10 +9885,10 @@
       <c r="E117" s="1">
         <v>26</v>
       </c>
-      <c r="F117" s="8">
+      <c r="F117" s="9">
         <v>78313318872069</v>
       </c>
-      <c r="G117" s="8" t="s">
+      <c r="G117" s="9" t="s">
         <v>391</v>
       </c>
       <c r="H117" s="2" t="s">
@@ -10551,10 +9912,10 @@
       <c r="E118" s="1">
         <v>27</v>
       </c>
-      <c r="F118" s="8">
+      <c r="F118" s="9">
         <v>125592304728045</v>
       </c>
-      <c r="G118" s="8" t="s">
+      <c r="G118" s="9" t="s">
         <v>393</v>
       </c>
       <c r="H118" s="2" t="s">
@@ -10578,10 +9939,10 @@
       <c r="E119" s="1">
         <v>27</v>
       </c>
-      <c r="F119" s="8">
+      <c r="F119" s="9">
         <v>80137167951870</v>
       </c>
-      <c r="G119" s="8" t="s">
+      <c r="G119" s="9" t="s">
         <v>395</v>
       </c>
       <c r="H119" s="2" t="s">
@@ -10605,10 +9966,10 @@
       <c r="E120" s="1">
         <v>27</v>
       </c>
-      <c r="F120" s="8">
+      <c r="F120" s="9">
         <v>73282351047760</v>
       </c>
-      <c r="G120" s="8" t="s">
+      <c r="G120" s="9" t="s">
         <v>397</v>
       </c>
       <c r="H120" s="2" t="s">
@@ -10632,10 +9993,10 @@
       <c r="E121" s="1">
         <v>27</v>
       </c>
-      <c r="F121" s="8">
+      <c r="F121" s="9">
         <v>103255430368191</v>
       </c>
-      <c r="G121" s="8" t="s">
+      <c r="G121" s="9" t="s">
         <v>399</v>
       </c>
       <c r="H121" s="2" t="s">
@@ -10659,10 +10020,10 @@
       <c r="E122" s="1">
         <v>28</v>
       </c>
-      <c r="F122" s="8">
+      <c r="F122" s="9">
         <v>116294264954356</v>
       </c>
-      <c r="G122" s="8" t="s">
+      <c r="G122" s="9" t="s">
         <v>401</v>
       </c>
       <c r="H122" s="2" t="s">
@@ -10686,10 +10047,10 @@
       <c r="E123" s="1">
         <v>28</v>
       </c>
-      <c r="F123" s="8">
+      <c r="F123" s="9">
         <v>125743373452231</v>
       </c>
-      <c r="G123" s="8" t="s">
+      <c r="G123" s="9" t="s">
         <v>403</v>
       </c>
       <c r="H123" s="2" t="s">
@@ -10713,10 +10074,10 @@
       <c r="E124" s="1">
         <v>28</v>
       </c>
-      <c r="F124" s="8">
+      <c r="F124" s="9">
         <v>112421216883327</v>
       </c>
-      <c r="G124" s="8" t="s">
+      <c r="G124" s="9" t="s">
         <v>405</v>
       </c>
       <c r="H124" s="2" t="s">
@@ -10731,7 +10092,7 @@
       <c r="B125" s="1">
         <v>122</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="9" t="s">
         <v>406</v>
       </c>
       <c r="D125" s="1">
@@ -10740,10 +10101,10 @@
       <c r="E125" s="1">
         <v>28</v>
       </c>
-      <c r="F125" s="8">
+      <c r="F125" s="9">
         <v>91269915478196</v>
       </c>
-      <c r="G125" s="8" t="s">
+      <c r="G125" s="9" t="s">
         <v>407</v>
       </c>
       <c r="H125" s="2" t="s">
@@ -10757,7 +10118,7 @@
       <c r="B126" s="1">
         <v>123</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C126" s="9" t="s">
         <v>408</v>
       </c>
       <c r="D126" s="1">
@@ -10766,10 +10127,10 @@
       <c r="E126" s="1">
         <v>29</v>
       </c>
-      <c r="F126" s="8">
+      <c r="F126" s="9">
         <v>105465120437268</v>
       </c>
-      <c r="G126" s="8" t="s">
+      <c r="G126" s="9" t="s">
         <v>409</v>
       </c>
       <c r="H126" s="2" t="s">
@@ -10783,7 +10144,7 @@
       <c r="B127" s="1">
         <v>124</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="9" t="s">
         <v>410</v>
       </c>
       <c r="D127" s="1">
@@ -10792,10 +10153,10 @@
       <c r="E127" s="1">
         <v>29</v>
       </c>
-      <c r="F127" s="8">
+      <c r="F127" s="9">
         <v>83111312306519</v>
       </c>
-      <c r="G127" s="8" t="s">
+      <c r="G127" s="9" t="s">
         <v>411</v>
       </c>
       <c r="H127" s="2" t="s">
@@ -10809,7 +10170,7 @@
       <c r="B128" s="1">
         <v>125</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="9" t="s">
         <v>412</v>
       </c>
       <c r="D128" s="1">
@@ -10818,10 +10179,10 @@
       <c r="E128" s="1">
         <v>29</v>
       </c>
-      <c r="F128" s="8">
+      <c r="F128" s="9">
         <v>100761293408985</v>
       </c>
-      <c r="G128" s="8" t="s">
+      <c r="G128" s="9" t="s">
         <v>413</v>
       </c>
       <c r="H128" s="2" t="s">
@@ -10835,7 +10196,7 @@
       <c r="B129" s="1">
         <v>126</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="9" t="s">
         <v>414</v>
       </c>
       <c r="D129" s="1">
@@ -10844,10 +10205,10 @@
       <c r="E129" s="1">
         <v>29</v>
       </c>
-      <c r="F129" s="8">
+      <c r="F129" s="9">
         <v>125949085124996</v>
       </c>
-      <c r="G129" s="8" t="s">
+      <c r="G129" s="9" t="s">
         <v>415</v>
       </c>
       <c r="H129" s="2" t="s">
@@ -10861,7 +10222,7 @@
       <c r="B130" s="1">
         <v>127</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="9" t="s">
         <v>416</v>
       </c>
       <c r="D130" s="1">
@@ -10870,10 +10231,10 @@
       <c r="E130" s="1">
         <v>30</v>
       </c>
-      <c r="F130" s="8">
+      <c r="F130" s="9">
         <v>97905565242094</v>
       </c>
-      <c r="G130" s="8" t="s">
+      <c r="G130" s="9" t="s">
         <v>417</v>
       </c>
       <c r="H130" s="2" t="s">
@@ -10887,7 +10248,7 @@
       <c r="B131" s="1">
         <v>128</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="9" t="s">
         <v>418</v>
       </c>
       <c r="D131" s="1">
@@ -10896,10 +10257,10 @@
       <c r="E131" s="1">
         <v>30</v>
       </c>
-      <c r="F131" s="8">
+      <c r="F131" s="9">
         <v>140476411551393</v>
       </c>
-      <c r="G131" s="8" t="s">
+      <c r="G131" s="9" t="s">
         <v>419</v>
       </c>
       <c r="H131" s="2" t="s">
@@ -10913,7 +10274,7 @@
       <c r="B132" s="1">
         <v>129</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="9" t="s">
         <v>420</v>
       </c>
       <c r="D132" s="1">
@@ -10922,10 +10283,10 @@
       <c r="E132" s="1">
         <v>30</v>
       </c>
-      <c r="F132" s="8">
+      <c r="F132" s="9">
         <v>120018046835451</v>
       </c>
-      <c r="G132" s="8" t="s">
+      <c r="G132" s="9" t="s">
         <v>421</v>
       </c>
       <c r="H132" s="2" t="s">
@@ -10939,7 +10300,7 @@
       <c r="B133" s="1">
         <v>130</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="9" t="s">
         <v>422</v>
       </c>
       <c r="D133" s="1">
@@ -10948,10 +10309,10 @@
       <c r="E133" s="1">
         <v>30</v>
       </c>
-      <c r="F133" s="8">
+      <c r="F133" s="9">
         <v>80251278207088</v>
       </c>
-      <c r="G133" s="8" t="s">
+      <c r="G133" s="9" t="s">
         <v>423</v>
       </c>
       <c r="H133" s="2" t="s">
@@ -10965,7 +10326,7 @@
       <c r="B134" s="1">
         <v>131</v>
       </c>
-      <c r="C134" s="8" t="s">
+      <c r="C134" s="9" t="s">
         <v>424</v>
       </c>
       <c r="D134" s="1">
@@ -10974,10 +10335,10 @@
       <c r="E134" s="1">
         <v>31</v>
       </c>
-      <c r="F134" s="8">
+      <c r="F134" s="9">
         <v>93241401911451</v>
       </c>
-      <c r="G134" s="8" t="s">
+      <c r="G134" s="9" t="s">
         <v>425</v>
       </c>
       <c r="H134" s="2" t="s">
@@ -10991,7 +10352,7 @@
       <c r="B135" s="1">
         <v>132</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="9" t="s">
         <v>426</v>
       </c>
       <c r="D135" s="1">
@@ -11000,10 +10361,10 @@
       <c r="E135" s="1">
         <v>31</v>
       </c>
-      <c r="F135" s="8">
+      <c r="F135" s="9">
         <v>111428364476852</v>
       </c>
-      <c r="G135" s="8" t="s">
+      <c r="G135" s="9" t="s">
         <v>427</v>
       </c>
       <c r="H135" s="2" t="s">
@@ -11017,7 +10378,7 @@
       <c r="B136" s="1">
         <v>133</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="C136" s="9" t="s">
         <v>428</v>
       </c>
       <c r="D136" s="1">
@@ -11026,10 +10387,10 @@
       <c r="E136" s="1">
         <v>31</v>
       </c>
-      <c r="F136" s="8">
+      <c r="F136" s="9">
         <v>117739005088015</v>
       </c>
-      <c r="G136" s="8" t="s">
+      <c r="G136" s="9" t="s">
         <v>429</v>
       </c>
       <c r="H136" s="2" t="s">
@@ -11043,7 +10404,7 @@
       <c r="B137" s="1">
         <v>134</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="9" t="s">
         <v>430</v>
       </c>
       <c r="D137" s="1">
@@ -11052,10 +10413,10 @@
       <c r="E137" s="1">
         <v>31</v>
       </c>
-      <c r="F137" s="8">
+      <c r="F137" s="9">
         <v>106059177546151</v>
       </c>
-      <c r="G137" s="8" t="s">
+      <c r="G137" s="9" t="s">
         <v>431</v>
       </c>
       <c r="H137" s="2" t="s">
@@ -11069,7 +10430,7 @@
       <c r="B138" s="1">
         <v>135</v>
       </c>
-      <c r="C138" s="8" t="s">
+      <c r="C138" s="9" t="s">
         <v>432</v>
       </c>
       <c r="D138" s="1">
@@ -11078,10 +10439,10 @@
       <c r="E138" s="1">
         <v>32</v>
       </c>
-      <c r="F138" s="8">
+      <c r="F138" s="9">
         <v>136795155731733</v>
       </c>
-      <c r="G138" s="8" t="s">
+      <c r="G138" s="9" t="s">
         <v>433</v>
       </c>
       <c r="H138" s="2" t="s">
@@ -11095,7 +10456,7 @@
       <c r="B139" s="1">
         <v>136</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="9" t="s">
         <v>434</v>
       </c>
       <c r="D139" s="1">
@@ -11104,10 +10465,10 @@
       <c r="E139" s="1">
         <v>32</v>
       </c>
-      <c r="F139" s="8">
+      <c r="F139" s="9">
         <v>72644523405324</v>
       </c>
-      <c r="G139" s="8" t="s">
+      <c r="G139" s="9" t="s">
         <v>435</v>
       </c>
       <c r="H139" s="2" t="s">
@@ -11121,7 +10482,7 @@
       <c r="B140" s="1">
         <v>137</v>
       </c>
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="9" t="s">
         <v>436</v>
       </c>
       <c r="D140" s="1">
@@ -11130,10 +10491,10 @@
       <c r="E140" s="1">
         <v>32</v>
       </c>
-      <c r="F140" s="8">
+      <c r="F140" s="9">
         <v>108937394146011</v>
       </c>
-      <c r="G140" s="8" t="s">
+      <c r="G140" s="9" t="s">
         <v>437</v>
       </c>
       <c r="H140" s="2" t="s">
@@ -11147,7 +10508,7 @@
       <c r="B141" s="1">
         <v>138</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="9" t="s">
         <v>438</v>
       </c>
       <c r="D141" s="1">
@@ -11156,10 +10517,10 @@
       <c r="E141" s="1">
         <v>32</v>
       </c>
-      <c r="F141" s="8">
+      <c r="F141" s="9">
         <v>79433065873354</v>
       </c>
-      <c r="G141" s="8" t="s">
+      <c r="G141" s="9" t="s">
         <v>439</v>
       </c>
       <c r="H141" s="2" t="s">
@@ -11173,7 +10534,7 @@
       <c r="B142" s="1">
         <v>139</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="9" t="s">
         <v>440</v>
       </c>
       <c r="D142" s="1">
@@ -11182,10 +10543,10 @@
       <c r="E142" s="1">
         <v>33</v>
       </c>
-      <c r="F142" s="8">
+      <c r="F142" s="9">
         <v>78433393917163</v>
       </c>
-      <c r="G142" s="8" t="s">
+      <c r="G142" s="9" t="s">
         <v>441</v>
       </c>
       <c r="H142" s="2" t="s">
@@ -11199,7 +10560,7 @@
       <c r="B143" s="1">
         <v>140</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="9" t="s">
         <v>442</v>
       </c>
       <c r="D143" s="1">
@@ -11208,10 +10569,10 @@
       <c r="E143" s="1">
         <v>33</v>
       </c>
-      <c r="F143" s="8">
+      <c r="F143" s="9">
         <v>86723396142799</v>
       </c>
-      <c r="G143" s="8" t="s">
+      <c r="G143" s="9" t="s">
         <v>443</v>
       </c>
       <c r="H143" s="2" t="s">
@@ -11225,7 +10586,7 @@
       <c r="B144" s="1">
         <v>141</v>
       </c>
-      <c r="C144" s="8" t="s">
+      <c r="C144" s="9" t="s">
         <v>444</v>
       </c>
       <c r="D144" s="1">
@@ -11234,10 +10595,10 @@
       <c r="E144" s="1">
         <v>33</v>
       </c>
-      <c r="F144" s="8">
+      <c r="F144" s="9">
         <v>116389499163956</v>
       </c>
-      <c r="G144" s="8" t="s">
+      <c r="G144" s="9" t="s">
         <v>445</v>
       </c>
       <c r="H144" s="2" t="s">
@@ -11251,7 +10612,7 @@
       <c r="B145" s="1">
         <v>142</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="9" t="s">
         <v>446</v>
       </c>
       <c r="D145" s="1">
@@ -11260,10 +10621,10 @@
       <c r="E145" s="1">
         <v>33</v>
       </c>
-      <c r="F145" s="8">
+      <c r="F145" s="9">
         <v>97264334614998</v>
       </c>
-      <c r="G145" s="8" t="s">
+      <c r="G145" s="9" t="s">
         <v>447</v>
       </c>
       <c r="H145" s="2" t="s">
@@ -11277,7 +10638,7 @@
       <c r="B146" s="1">
         <v>143</v>
       </c>
-      <c r="C146" s="8" t="s">
+      <c r="C146" s="9" t="s">
         <v>448</v>
       </c>
       <c r="D146" s="1">
@@ -11286,10 +10647,10 @@
       <c r="E146" s="1">
         <v>34</v>
       </c>
-      <c r="F146" s="8">
+      <c r="F146" s="9">
         <v>115791824258294</v>
       </c>
-      <c r="G146" s="8" t="s">
+      <c r="G146" s="9" t="s">
         <v>449</v>
       </c>
       <c r="H146" s="2" t="s">
@@ -11303,7 +10664,7 @@
       <c r="B147" s="1">
         <v>144</v>
       </c>
-      <c r="C147" s="8" t="s">
+      <c r="C147" s="9" t="s">
         <v>450</v>
       </c>
       <c r="D147" s="1">
@@ -11312,10 +10673,10 @@
       <c r="E147" s="1">
         <v>34</v>
       </c>
-      <c r="F147" s="8">
+      <c r="F147" s="9">
         <v>94398618924427</v>
       </c>
-      <c r="G147" s="8" t="s">
+      <c r="G147" s="9" t="s">
         <v>451</v>
       </c>
       <c r="H147" s="2" t="s">
@@ -11329,7 +10690,7 @@
       <c r="B148" s="1">
         <v>145</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="C148" s="9" t="s">
         <v>452</v>
       </c>
       <c r="D148" s="1">
@@ -11338,10 +10699,10 @@
       <c r="E148" s="1">
         <v>34</v>
       </c>
-      <c r="F148" s="8">
+      <c r="F148" s="9">
         <v>128273384481118</v>
       </c>
-      <c r="G148" s="8" t="s">
+      <c r="G148" s="9" t="s">
         <v>453</v>
       </c>
       <c r="H148" s="2" t="s">
@@ -11355,7 +10716,7 @@
       <c r="B149" s="1">
         <v>146</v>
       </c>
-      <c r="C149" s="8" t="s">
+      <c r="C149" s="9" t="s">
         <v>454</v>
       </c>
       <c r="D149" s="1">
@@ -11364,10 +10725,10 @@
       <c r="E149" s="1">
         <v>34</v>
       </c>
-      <c r="F149" s="8">
+      <c r="F149" s="9">
         <v>138000317292270</v>
       </c>
-      <c r="G149" s="8" t="s">
+      <c r="G149" s="9" t="s">
         <v>455</v>
       </c>
       <c r="H149" s="2" t="s">
@@ -11381,7 +10742,7 @@
       <c r="B150" s="1">
         <v>147</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C150" s="9" t="s">
         <v>456</v>
       </c>
       <c r="D150" s="1">
@@ -11390,10 +10751,10 @@
       <c r="E150" s="1">
         <v>35</v>
       </c>
-      <c r="F150" s="8">
+      <c r="F150" s="9">
         <v>100641475547869</v>
       </c>
-      <c r="G150" s="8" t="s">
+      <c r="G150" s="9" t="s">
         <v>457</v>
       </c>
       <c r="H150" s="2" t="s">
@@ -11407,7 +10768,7 @@
       <c r="B151" s="1">
         <v>148</v>
       </c>
-      <c r="C151" s="8" t="s">
+      <c r="C151" s="9" t="s">
         <v>458</v>
       </c>
       <c r="D151" s="1">
@@ -11416,10 +10777,10 @@
       <c r="E151" s="1">
         <v>35</v>
       </c>
-      <c r="F151" s="8">
+      <c r="F151" s="9">
         <v>79371487434912</v>
       </c>
-      <c r="G151" s="8" t="s">
+      <c r="G151" s="9" t="s">
         <v>459</v>
       </c>
       <c r="H151" s="2" t="s">
@@ -11443,156 +10804,156 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A4" s="7">
+      <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="8">
         <v>2</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="8">
         <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A5" s="7">
+      <c r="A5" s="8">
         <v>2</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <v>4</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="8">
         <v>151</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A6" s="7">
+      <c r="A6" s="8">
         <v>3</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <v>8</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A7" s="7">
+      <c r="A7" s="8">
         <v>4</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <v>16</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <v>153</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A8" s="7">
+      <c r="A8" s="8">
         <v>5</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="8">
         <v>32</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>154</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A9" s="7">
+      <c r="A9" s="8">
         <v>6</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="8">
         <v>64</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A10" s="7">
+      <c r="A10" s="8">
         <v>7</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="8">
         <v>128</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>156</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A11" s="7">
+      <c r="A11" s="8">
         <v>8</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <v>256</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <v>157</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A12" s="7">
+      <c r="A12" s="8">
         <v>9</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <v>512</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>158</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A13" s="7">
+      <c r="A13" s="8">
         <v>10</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="8">
         <v>1024</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <v>159</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A14" s="7">
+      <c r="A14" s="8">
         <v>11</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="8">
         <v>2048</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <v>160</v>
       </c>
     </row>
@@ -11610,7 +10971,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="38.6333333333333" customWidth="1"/>
@@ -11619,10 +10980,9 @@
     <col min="6" max="6" width="22.9333333333333" customWidth="1"/>
     <col min="7" max="7" width="55" customWidth="1"/>
     <col min="8" max="8" width="44.5583333333333" customWidth="1"/>
-    <col min="9" max="9" width="44.8833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="16.5" spans="1:10">
+    <row r="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -11647,22 +11007,19 @@
       <c r="H1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="I1" t="s">
-        <v>467</v>
-      </c>
     </row>
-    <row r="2" customFormat="1" ht="16.5" spans="1:10">
+    <row r="2" customFormat="1" ht="16.5" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>156</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>59</v>
@@ -11671,16 +11028,13 @@
         <v>58</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>472</v>
-      </c>
     </row>
-    <row r="3" customFormat="1" ht="16.5" spans="1:10">
+    <row r="3" customFormat="1" ht="16.5" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>61</v>
       </c>
@@ -11700,16 +11054,13 @@
         <v>62</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>7</v>
+        <v>162</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="4" customFormat="1" ht="16.5" spans="1:10">
+    <row r="4" customFormat="1" ht="16.5" spans="1:9">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -11717,7 +11068,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -11726,18 +11077,13 @@
         <v>1</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="J4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="I4" s="6"/>
     </row>
-    <row r="5" customFormat="1" ht="16.5" spans="1:10">
+    <row r="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -11745,7 +11091,7 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D5" s="1">
         <v>25</v>
@@ -11754,18 +11100,13 @@
         <v>39</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="6" t="s">
-        <v>478</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>480</v>
-      </c>
-      <c r="J5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="I5" s="6"/>
     </row>
-    <row r="6" customFormat="1" ht="16.5" spans="1:10">
+    <row r="6" customFormat="1" ht="16.5" spans="1:9">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -11773,7 +11114,7 @@
         <v>103</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="D6" s="1">
         <v>450</v>
@@ -11782,18 +11123,13 @@
         <v>450</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>483</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>484</v>
-      </c>
-      <c r="J6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="I6" s="6"/>
     </row>
-    <row r="7" customFormat="1" ht="16.5" spans="1:10">
+    <row r="7" customFormat="1" ht="16.5" spans="1:9">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -11801,7 +11137,7 @@
         <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D7" s="1">
         <v>4375</v>
@@ -11810,18 +11146,13 @@
         <v>3282</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="J7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="I7" s="6"/>
     </row>
-    <row r="8" customFormat="1" ht="16.5" spans="1:10">
+    <row r="8" customFormat="1" ht="16.5" spans="1:9">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -11829,27 +11160,22 @@
         <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>490</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>491</v>
+        <v>479</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>480</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>481</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="6" t="s">
-        <v>492</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="J8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="I8" s="6"/>
     </row>
-    <row r="9" customFormat="1" ht="16.5" spans="1:10">
+    <row r="9" customFormat="1" ht="16.5" spans="1:9">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -11857,27 +11183,22 @@
         <v>106</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>496</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>497</v>
+        <v>483</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>484</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>485</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="J9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="I9" s="6"/>
     </row>
-    <row r="10" customFormat="1" ht="16.5" spans="1:10">
+    <row r="10" customFormat="1" ht="16.5" spans="1:9">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -11885,27 +11206,22 @@
         <v>107</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>502</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>503</v>
+        <v>487</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>488</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>489</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="J10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="I10" s="6"/>
     </row>
-    <row r="11" customFormat="1" ht="16.5" spans="1:10">
+    <row r="11" customFormat="1" ht="16.5" spans="1:9">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -11913,27 +11229,22 @@
         <v>108</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>508</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>509</v>
+        <v>491</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>492</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>493</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="J11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="I11" s="6"/>
     </row>
-    <row r="12" customFormat="1" ht="16.5" spans="1:10">
+    <row r="12" customFormat="1" ht="16.5" spans="1:9">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -11941,27 +11252,22 @@
         <v>109</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>514</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>515</v>
+        <v>495</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>497</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="6" t="s">
-        <v>516</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="J12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="I12" s="6"/>
     </row>
-    <row r="13" customFormat="1" ht="16.5" spans="1:10">
+    <row r="13" customFormat="1" ht="16.5" spans="1:9">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -11969,27 +11275,22 @@
         <v>110</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>520</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>521</v>
+        <v>499</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>501</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="6" t="s">
-        <v>522</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="J13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="I13" s="6"/>
     </row>
-    <row r="14" customFormat="1" ht="16.5" spans="1:10">
+    <row r="14" customFormat="1" ht="16.5" spans="1:9">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -11997,27 +11298,22 @@
         <v>111</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>526</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>527</v>
+        <v>503</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>504</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>505</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="6" t="s">
-        <v>528</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>529</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="J14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="I14" s="6"/>
     </row>
-    <row r="15" customFormat="1" ht="16.5" spans="1:10">
+    <row r="15" customFormat="1" ht="16.5" spans="1:9">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -12025,27 +11321,22 @@
         <v>112</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="D15" s="26" t="s">
-        <v>532</v>
-      </c>
-      <c r="E15" s="26" t="s">
-        <v>533</v>
+        <v>507</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>508</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>509</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="6" t="s">
-        <v>534</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>536</v>
-      </c>
-      <c r="J15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="I15" s="6"/>
     </row>
-    <row r="16" customFormat="1" ht="16.5" spans="1:10">
+    <row r="16" customFormat="1" ht="16.5" spans="1:9">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -12053,27 +11344,22 @@
         <v>113</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D16" s="26" t="s">
-        <v>538</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>539</v>
+        <v>511</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>512</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>513</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="6" t="s">
-        <v>540</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>541</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>542</v>
-      </c>
-      <c r="J16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="I16" s="6"/>
     </row>
-    <row r="17" customFormat="1" ht="16.5" spans="1:10">
+    <row r="17" customFormat="1" ht="16.5" spans="1:9">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -12081,27 +11367,22 @@
         <v>114</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>544</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>545</v>
+        <v>515</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>516</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>517</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="6" t="s">
-        <v>546</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>548</v>
-      </c>
-      <c r="J17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="I17" s="6"/>
     </row>
-    <row r="18" customFormat="1" ht="16.5" spans="1:10">
+    <row r="18" customFormat="1" ht="16.5" spans="1:9">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -12109,27 +11390,22 @@
         <v>115</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>550</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>551</v>
+        <v>519</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>520</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>521</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="G18" s="6" t="s">
-        <v>552</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>553</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>554</v>
-      </c>
-      <c r="J18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="I18" s="6"/>
     </row>
-    <row r="19" customFormat="1" ht="16.5" spans="1:10">
+    <row r="19" customFormat="1" ht="16.5" spans="1:9">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -12137,27 +11413,22 @@
         <v>116</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>556</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>557</v>
+        <v>523</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>524</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>525</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="J19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="I19" s="6"/>
     </row>
-    <row r="20" customFormat="1" ht="16.5" spans="1:10">
+    <row r="20" customFormat="1" ht="16.5" spans="1:9">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -12165,27 +11436,22 @@
         <v>117</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>562</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>563</v>
+        <v>527</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>529</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="6" t="s">
-        <v>564</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="J20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="I20" s="6"/>
     </row>
-    <row r="21" ht="16.5" spans="1:10">
+    <row r="21" ht="16.5" spans="1:9">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -12193,27 +11459,22 @@
         <v>118</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>568</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>569</v>
+        <v>531</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>532</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>533</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="6" t="s">
-        <v>570</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>571</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>572</v>
-      </c>
-      <c r="J21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="I21" s="6"/>
     </row>
-    <row r="22" ht="16.5" spans="1:10">
+    <row r="22" ht="16.5" spans="1:9">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -12221,27 +11482,22 @@
         <v>119</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>574</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>575</v>
+        <v>535</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>536</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>537</v>
       </c>
       <c r="F22" s="1"/>
-      <c r="G22" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>577</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>578</v>
-      </c>
-      <c r="J22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="I22" s="6"/>
     </row>
-    <row r="23" ht="16.5" spans="1:10">
+    <row r="23" ht="16.5" spans="1:9">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -12249,895 +11505,20 @@
         <v>120</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>580</v>
-      </c>
-      <c r="E23" s="26" t="s">
-        <v>581</v>
+        <v>539</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>541</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>583</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>584</v>
-      </c>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24" ht="16.5" spans="1:10">
-      <c r="A24" s="1">
-        <v>21</v>
-      </c>
-      <c r="B24" s="1">
-        <v>121</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>585</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>586</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>587</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="6" t="s">
-        <v>588</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>589</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="J24" s="6"/>
-    </row>
-    <row r="25" ht="16.5" spans="1:10">
-      <c r="A25" s="1">
-        <v>22</v>
-      </c>
-      <c r="B25" s="1">
-        <v>122</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>592</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>593</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>595</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="J25" s="6"/>
-    </row>
-    <row r="26" ht="16.5" spans="1:10">
-      <c r="A26" s="1">
-        <v>23</v>
-      </c>
-      <c r="B26" s="1">
-        <v>123</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>598</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>599</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="6" t="s">
-        <v>600</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>601</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>602</v>
-      </c>
-      <c r="J26" s="6"/>
-    </row>
-    <row r="27" ht="16.5" spans="1:10">
-      <c r="A27" s="1">
-        <v>24</v>
-      </c>
-      <c r="B27" s="1">
-        <v>124</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>603</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>604</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>605</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="6" t="s">
-        <v>606</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>607</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>608</v>
-      </c>
-      <c r="J27" s="6"/>
-    </row>
-    <row r="28" ht="16.5" spans="1:10">
-      <c r="A28" s="1">
-        <v>25</v>
-      </c>
-      <c r="B28" s="1">
-        <v>125</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>610</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>611</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>614</v>
-      </c>
-      <c r="J28" s="6"/>
-    </row>
-    <row r="29" ht="16.5" spans="1:10">
-      <c r="A29" s="1">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1">
-        <v>126</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>616</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>617</v>
-      </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="6" t="s">
-        <v>618</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>619</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="J29" s="6"/>
-    </row>
-    <row r="30" ht="16.5" spans="1:10">
-      <c r="A30" s="1">
-        <v>27</v>
-      </c>
-      <c r="B30" s="1">
-        <v>127</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>622</v>
-      </c>
-      <c r="E30" s="26" t="s">
-        <v>623</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>624</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>625</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:10">
-      <c r="A31" s="1">
-        <v>28</v>
-      </c>
-      <c r="B31" s="1">
-        <v>128</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>628</v>
-      </c>
-      <c r="E31" s="26" t="s">
-        <v>629</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>630</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>631</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:10">
-      <c r="A32" s="1">
-        <v>29</v>
-      </c>
-      <c r="B32" s="1">
-        <v>129</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>634</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>635</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>637</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" spans="1:9">
-      <c r="A33" s="1">
-        <v>30</v>
-      </c>
-      <c r="B33" s="1">
-        <v>130</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>640</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>641</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>642</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>643</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:9">
-      <c r="A34" s="1">
-        <v>31</v>
-      </c>
-      <c r="B34" s="1">
-        <v>131</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>646</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>647</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>648</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>649</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:9">
-      <c r="A35" s="1">
-        <v>32</v>
-      </c>
-      <c r="B35" s="1">
-        <v>132</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>652</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>653</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>654</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>655</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" spans="1:9">
-      <c r="A36" s="1">
-        <v>33</v>
-      </c>
-      <c r="B36" s="1">
-        <v>133</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>658</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>659</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>660</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>661</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" spans="1:9">
-      <c r="A37" s="1">
-        <v>34</v>
-      </c>
-      <c r="B37" s="1">
-        <v>134</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>664</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>665</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>666</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>667</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:9">
-      <c r="A38" s="1">
-        <v>35</v>
-      </c>
-      <c r="B38" s="1">
-        <v>135</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>670</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>671</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>672</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>673</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="39" ht="16.5" spans="1:9">
-      <c r="A39" s="1">
-        <v>36</v>
-      </c>
-      <c r="B39" s="1">
-        <v>136</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>676</v>
-      </c>
-      <c r="E39" s="26" t="s">
-        <v>677</v>
-      </c>
-      <c r="G39" s="6" t="s">
-        <v>678</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>679</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="40" ht="16.5" spans="1:9">
-      <c r="A40" s="1">
-        <v>37</v>
-      </c>
-      <c r="B40" s="1">
-        <v>137</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>682</v>
-      </c>
-      <c r="E40" s="26" t="s">
-        <v>683</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>684</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>685</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="41" ht="16.5" spans="1:9">
-      <c r="A41" s="1">
-        <v>38</v>
-      </c>
-      <c r="B41" s="1">
-        <v>138</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="D41" s="26" t="s">
-        <v>688</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>689</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>690</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>691</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="42" ht="16.5" spans="1:9">
-      <c r="A42" s="1">
-        <v>39</v>
-      </c>
-      <c r="B42" s="1">
-        <v>139</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="D42" s="26" t="s">
-        <v>694</v>
-      </c>
-      <c r="E42" s="26" t="s">
-        <v>695</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>696</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>697</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="43" ht="16.5" spans="1:9">
-      <c r="A43" s="1">
-        <v>40</v>
-      </c>
-      <c r="B43" s="1">
-        <v>140</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="D43" s="26" t="s">
-        <v>700</v>
-      </c>
-      <c r="E43" s="26" t="s">
-        <v>701</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>702</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>703</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="44" ht="16.5" spans="1:9">
-      <c r="A44" s="1">
-        <v>41</v>
-      </c>
-      <c r="B44" s="1">
-        <v>141</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>705</v>
-      </c>
-      <c r="D44" s="1">
-        <v>2.23e+31</v>
-      </c>
-      <c r="E44" s="1">
-        <v>9.25e+20</v>
-      </c>
-      <c r="G44" t="s">
-        <v>706</v>
-      </c>
-      <c r="H44" t="s">
-        <v>707</v>
-      </c>
-      <c r="I44" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:9">
-      <c r="A45" s="1">
-        <v>42</v>
-      </c>
-      <c r="B45" s="1">
-        <v>142</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>709</v>
-      </c>
-      <c r="D45" s="1">
-        <v>1.14e+32</v>
-      </c>
-      <c r="E45" s="1">
-        <v>1.27e+21</v>
-      </c>
-      <c r="G45" t="s">
-        <v>710</v>
-      </c>
-      <c r="H45" t="s">
-        <v>711</v>
-      </c>
-      <c r="I45" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:9">
-      <c r="A46" s="1">
-        <v>43</v>
-      </c>
-      <c r="B46" s="1">
-        <v>143</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="D46" s="1">
-        <v>6.04e+32</v>
-      </c>
-      <c r="E46" s="1">
-        <v>1.72e+21</v>
-      </c>
-      <c r="G46" t="s">
-        <v>714</v>
-      </c>
-      <c r="H46" t="s">
-        <v>715</v>
-      </c>
-      <c r="I46" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="47" ht="16.5" spans="1:9">
-      <c r="A47" s="1">
-        <v>44</v>
-      </c>
-      <c r="B47" s="1">
-        <v>144</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>717</v>
-      </c>
-      <c r="D47" s="1">
-        <v>3.19e+33</v>
-      </c>
-      <c r="E47" s="1">
-        <v>2.32e+21</v>
-      </c>
-      <c r="G47" t="s">
-        <v>718</v>
-      </c>
-      <c r="H47" t="s">
-        <v>719</v>
-      </c>
-      <c r="I47" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:9">
-      <c r="A48" s="1">
-        <v>45</v>
-      </c>
-      <c r="B48" s="1">
-        <v>145</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>721</v>
-      </c>
-      <c r="D48" s="1">
-        <v>1.63e+34</v>
-      </c>
-      <c r="E48" s="1">
-        <v>3.1e+21</v>
-      </c>
-      <c r="G48" t="s">
-        <v>722</v>
-      </c>
-      <c r="H48" t="s">
-        <v>723</v>
-      </c>
-      <c r="I48" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="49" ht="16.5" spans="1:9">
-      <c r="A49" s="1">
-        <v>46</v>
-      </c>
-      <c r="B49" s="1">
-        <v>146</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="D49" s="1">
-        <v>8.6e+34</v>
-      </c>
-      <c r="E49" s="1">
-        <v>4.13e+21</v>
-      </c>
-      <c r="G49" t="s">
-        <v>726</v>
-      </c>
-      <c r="H49" t="s">
-        <v>727</v>
-      </c>
-      <c r="I49" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="50" ht="16.5" spans="1:9">
-      <c r="A50" s="1">
-        <v>47</v>
-      </c>
-      <c r="B50" s="1">
-        <v>147</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="D50" s="1">
-        <v>4.4e+35</v>
-      </c>
-      <c r="E50" s="1">
-        <v>5.46e+21</v>
-      </c>
-      <c r="G50" t="s">
-        <v>730</v>
-      </c>
-      <c r="H50" t="s">
-        <v>731</v>
-      </c>
-      <c r="I50" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="51" ht="16.5" spans="1:9">
-      <c r="A51" s="1">
-        <v>48</v>
-      </c>
-      <c r="B51" s="1">
-        <v>148</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="D51" s="1">
-        <v>2.31e+36</v>
-      </c>
-      <c r="E51" s="1">
-        <v>7.18e+21</v>
-      </c>
-      <c r="G51" t="s">
-        <v>734</v>
-      </c>
-      <c r="H51" t="s">
-        <v>735</v>
-      </c>
-      <c r="I51" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="52" ht="16.5" spans="1:9">
-      <c r="A52" s="1">
-        <v>49</v>
-      </c>
-      <c r="B52" s="1">
-        <v>149</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="D52" s="1">
-        <v>1.22e+37</v>
-      </c>
-      <c r="E52" s="1">
-        <v>9.39e+21</v>
-      </c>
-      <c r="G52" t="s">
-        <v>738</v>
-      </c>
-      <c r="H52" t="s">
-        <v>739</v>
-      </c>
-      <c r="I52" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="53" ht="16.5" spans="1:9">
-      <c r="A53" s="1">
-        <v>50</v>
-      </c>
-      <c r="B53" s="1">
-        <v>150</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="D53" s="1">
-        <v>6.2e+37</v>
-      </c>
-      <c r="E53" s="1">
-        <v>1.22e+22</v>
-      </c>
-      <c r="G53" t="s">
-        <v>742</v>
-      </c>
-      <c r="H53" t="s">
-        <v>743</v>
-      </c>
-      <c r="I53" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="54" ht="16.5" spans="1:9">
-      <c r="A54" s="1">
-        <v>51</v>
-      </c>
-      <c r="B54" s="1">
-        <v>151</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="D54" s="1">
-        <v>3.25e+38</v>
-      </c>
-      <c r="E54" s="1">
-        <v>1.58e+22</v>
-      </c>
-      <c r="G54" t="s">
-        <v>746</v>
-      </c>
-      <c r="H54" t="s">
-        <v>747</v>
-      </c>
-      <c r="I54" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="55" ht="16.5" spans="1:9">
-      <c r="A55" s="1">
-        <v>52</v>
-      </c>
-      <c r="B55" s="1">
-        <v>152</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="D55" s="1">
-        <v>1.7e+39</v>
-      </c>
-      <c r="E55" s="1">
-        <v>2.03e+22</v>
-      </c>
-      <c r="G55" t="s">
-        <v>750</v>
-      </c>
-      <c r="H55" t="s">
-        <v>751</v>
-      </c>
-      <c r="I55" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="56" ht="16.5" spans="1:9">
-      <c r="A56" s="1">
-        <v>53</v>
-      </c>
-      <c r="B56" s="1">
-        <v>153</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>753</v>
-      </c>
-      <c r="D56" s="1">
-        <v>8.69e+39</v>
-      </c>
-      <c r="E56" s="1">
-        <v>2.6e+22</v>
-      </c>
-      <c r="G56" t="s">
-        <v>754</v>
-      </c>
-      <c r="H56" t="s">
-        <v>755</v>
-      </c>
-      <c r="I56" t="s">
-        <v>756</v>
-      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="I23" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13187,7 +11568,7 @@
         <v>153</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>757</v>
+        <v>543</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -13195,13 +11576,13 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>758</v>
+        <v>544</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>156</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>59</v>
@@ -13213,10 +11594,10 @@
         <v>58</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -13256,7 +11637,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>759</v>
+        <v>545</v>
       </c>
       <c r="D4" s="1">
         <v>3750</v>
@@ -13269,10 +11650,10 @@
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1" t="s">
-        <v>760</v>
+        <v>546</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>761</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -13283,10 +11664,10 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>763</v>
+        <v>548</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>549</v>
       </c>
       <c r="E5" s="1">
         <v>2.5</v>
@@ -13296,10 +11677,10 @@
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>764</v>
+        <v>550</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>765</v>
+        <v>551</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -13310,10 +11691,10 @@
         <v>103</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>767</v>
+        <v>552</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>553</v>
       </c>
       <c r="E6" s="1">
         <v>3.5</v>
@@ -13323,10 +11704,10 @@
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
-        <v>768</v>
+        <v>554</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>769</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -13337,10 +11718,10 @@
         <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>771</v>
+        <v>556</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>557</v>
       </c>
       <c r="E7" s="1">
         <v>4.5</v>
@@ -13350,10 +11731,10 @@
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>772</v>
+        <v>558</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>773</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -13364,10 +11745,10 @@
         <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>775</v>
+        <v>560</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>561</v>
       </c>
       <c r="E8" s="1">
         <v>5.5</v>
@@ -13377,10 +11758,10 @@
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>776</v>
+        <v>562</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>777</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="715">
   <si>
     <t>子配置键</t>
   </si>
@@ -1685,9 +1685,6 @@
     <t>Common</t>
   </si>
   <si>
-    <t>Effects.Trail1</t>
-  </si>
-  <si>
     <t>game.ReplicatedStorage.Assets.Effects.Aura["01_Common"]</t>
   </si>
   <si>
@@ -1697,9 +1694,6 @@
     <t>1.38e+6</t>
   </si>
   <si>
-    <t>Effects.Trail2</t>
-  </si>
-  <si>
     <t>game.ReplicatedStorage.Assets.Effects.Aura["02_Uncommon"]</t>
   </si>
   <si>
@@ -1709,9 +1703,6 @@
     <t>3.32e+8</t>
   </si>
   <si>
-    <t>Effects.Trail3</t>
-  </si>
-  <si>
     <t>game.ReplicatedStorage.Assets.Effects.Aura["03_Rare"]</t>
   </si>
   <si>
@@ -1721,9 +1712,6 @@
     <t>7.30e+10</t>
   </si>
   <si>
-    <t>Effects.Trail4</t>
-  </si>
-  <si>
     <t>game.ReplicatedStorage.Assets.Effects.Aura["04_Epic"]</t>
   </si>
   <si>
@@ -1731,9 +1719,6 @@
   </si>
   <si>
     <t>1.42e+13</t>
-  </si>
-  <si>
-    <t>Effects.Trail5</t>
   </si>
   <si>
     <t>game.ReplicatedStorage.Assets.Effects.Aura["05_Legendary"]</t>
@@ -3517,13 +3502,13 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:5">
@@ -3531,10 +3516,10 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
@@ -3550,576 +3535,576 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B4" s="2">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B5" s="2">
         <v>122</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B6" s="2">
         <v>520</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B7" s="2">
         <v>2176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B8" s="2">
         <v>9101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="B50" s="29" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="B52" s="29" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="B53" s="29" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="B54" s="29" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B55" s="29" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
     </row>
   </sheetData>
@@ -11649,11 +11634,11 @@
         <v>1</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="1" t="s">
+      <c r="H4">
+        <v>91469233823349</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11664,10 +11649,10 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D5" s="27" t="s">
         <v>548</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>549</v>
       </c>
       <c r="E5" s="1">
         <v>2.5</v>
@@ -11676,11 +11661,11 @@
         <v>1</v>
       </c>
       <c r="G5" s="1"/>
-      <c r="H5" s="1" t="s">
-        <v>550</v>
+      <c r="H5">
+        <v>112048940124762</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11691,10 +11676,10 @@
         <v>103</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E6" s="1">
         <v>3.5</v>
@@ -11703,11 +11688,11 @@
         <v>1</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
-        <v>554</v>
+      <c r="H6">
+        <v>114920101659350</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11718,10 +11703,10 @@
         <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E7" s="1">
         <v>4.5</v>
@@ -11730,11 +11715,11 @@
         <v>1</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
-        <v>558</v>
+      <c r="H7">
+        <v>76680071023422</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11745,10 +11730,10 @@
         <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E8" s="1">
         <v>5.5</v>
@@ -11757,11 +11742,11 @@
         <v>1</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8" s="1" t="s">
-        <v>562</v>
+      <c r="H8">
+        <v>98163950325063</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" firstSheet="1" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="AreaRefreshData" sheetId="8" r:id="rId5"/>
     <sheet name="ItemData" sheetId="5" r:id="rId6"/>
     <sheet name="TrainingRateConfig" sheetId="12" r:id="rId7"/>
-    <sheet name="SlicerConfig" sheetId="6" r:id="rId8"/>
+    <sheet name="ToolConfig" sheetId="6" r:id="rId8"/>
     <sheet name="AuraConfig" sheetId="7" r:id="rId9"/>
     <sheet name="LevelConfig" sheetId="10" r:id="rId10"/>
   </sheets>
@@ -92,10 +92,10 @@
     <t>训练场地数据</t>
   </si>
   <si>
-    <t>SlicerConfig</t>
-  </si>
-  <si>
-    <t>切割器</t>
+    <t>ToolConfig</t>
+  </si>
+  <si>
+    <t>工具表</t>
   </si>
   <si>
     <t>TrainingRateConfig</t>
@@ -1448,7 +1448,7 @@
     <t>图片Id</t>
   </si>
   <si>
-    <t>SlicerId</t>
+    <t>ToolId</t>
   </si>
   <si>
     <t>Price</t>
@@ -2222,15 +2222,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2883,16 +2883,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="fill" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -2940,10 +2940,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -3372,7 +3372,7 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="26" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3389,7 +3389,7 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="25" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="25" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
@@ -3426,7 +3426,7 @@
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="26" t="s">
         <v>21</v>
       </c>
       <c r="F8" t="s">
@@ -3446,7 +3446,7 @@
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="26" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
@@ -3466,7 +3466,7 @@
       <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="25" t="s">
         <v>25</v>
       </c>
       <c r="F10" t="s">
@@ -3476,7 +3476,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" location="CommonConfig!A1" display="CommonConfig"/>
-    <hyperlink ref="E4" location="SlicerConfig!A1" display="SlicerConfig"/>
+    <hyperlink ref="E4" location="SlicerConfig!A1" display="ToolConfig"/>
     <hyperlink ref="E6" location="TrailConfig!A1" display="AuraConfig"/>
     <hyperlink ref="E7" location="AreaRefreshData!A1" display="AreaRefreshData"/>
     <hyperlink ref="E8" location="ItemData!A1" display="ItemData"/>
@@ -11062,11 +11062,13 @@
         <v>1</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4">
+        <v>99853650045862</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="I4" s="7"/>
     </row>
     <row r="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A5" s="1">
@@ -11085,11 +11087,13 @@
         <v>39</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="7" t="s">
+      <c r="G5">
+        <v>116225665846279</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="I5" s="6"/>
+      <c r="I5" s="7"/>
     </row>
     <row r="6" customFormat="1" ht="16.5" spans="1:9">
       <c r="A6" s="1">
@@ -11108,11 +11112,13 @@
         <v>450</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="7" t="s">
+      <c r="G6">
+        <v>136956773152573</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="I6" s="6"/>
+      <c r="I6" s="7"/>
     </row>
     <row r="7" customFormat="1" ht="16.5" spans="1:9">
       <c r="A7" s="1">
@@ -11131,11 +11137,13 @@
         <v>3282</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="7" t="s">
+      <c r="G7">
+        <v>97553870039023</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="I7" s="6"/>
+      <c r="I7" s="7"/>
     </row>
     <row r="8" customFormat="1" ht="16.5" spans="1:9">
       <c r="A8" s="1">
@@ -11154,11 +11162,13 @@
         <v>481</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="7" t="s">
+      <c r="G8">
+        <v>118090700645855</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="I8" s="6"/>
+      <c r="I8" s="7"/>
     </row>
     <row r="9" customFormat="1" ht="16.5" spans="1:9">
       <c r="A9" s="1">
@@ -11177,11 +11187,13 @@
         <v>485</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="7" t="s">
+      <c r="G9">
+        <v>138508042210191</v>
+      </c>
+      <c r="H9" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="I9" s="6"/>
+      <c r="I9" s="7"/>
     </row>
     <row r="10" customFormat="1" ht="16.5" spans="1:9">
       <c r="A10" s="1">
@@ -11200,11 +11212,13 @@
         <v>489</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="7" t="s">
+      <c r="G10">
+        <v>78371166922896</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="I10" s="6"/>
+      <c r="I10" s="7"/>
     </row>
     <row r="11" customFormat="1" ht="16.5" spans="1:9">
       <c r="A11" s="1">
@@ -11223,11 +11237,13 @@
         <v>493</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="7" t="s">
+      <c r="G11">
+        <v>132966760008713</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="I11" s="6"/>
+      <c r="I11" s="7"/>
     </row>
     <row r="12" customFormat="1" ht="16.5" spans="1:9">
       <c r="A12" s="1">
@@ -11246,11 +11262,13 @@
         <v>497</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="7" t="s">
+      <c r="G12">
+        <v>133927008310944</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>498</v>
       </c>
-      <c r="I12" s="6"/>
+      <c r="I12" s="7"/>
     </row>
     <row r="13" customFormat="1" ht="16.5" spans="1:9">
       <c r="A13" s="1">
@@ -11269,11 +11287,13 @@
         <v>501</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="7" t="s">
+      <c r="G13">
+        <v>98415179467911</v>
+      </c>
+      <c r="H13" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="I13" s="6"/>
+      <c r="I13" s="7"/>
     </row>
     <row r="14" customFormat="1" ht="16.5" spans="1:9">
       <c r="A14" s="1">
@@ -11292,11 +11312,13 @@
         <v>505</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="7" t="s">
+      <c r="G14">
+        <v>79276409476682</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>506</v>
       </c>
-      <c r="I14" s="6"/>
+      <c r="I14" s="7"/>
     </row>
     <row r="15" customFormat="1" ht="16.5" spans="1:9">
       <c r="A15" s="1">
@@ -11315,11 +11337,13 @@
         <v>509</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="7" t="s">
+      <c r="G15">
+        <v>86184044773576</v>
+      </c>
+      <c r="H15" s="6" t="s">
         <v>510</v>
       </c>
-      <c r="I15" s="6"/>
+      <c r="I15" s="7"/>
     </row>
     <row r="16" customFormat="1" ht="16.5" spans="1:9">
       <c r="A16" s="1">
@@ -11338,11 +11362,13 @@
         <v>513</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="7" t="s">
+      <c r="G16">
+        <v>85964386896273</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="I16" s="6"/>
+      <c r="I16" s="7"/>
     </row>
     <row r="17" customFormat="1" ht="16.5" spans="1:9">
       <c r="A17" s="1">
@@ -11361,11 +11387,13 @@
         <v>517</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="7" t="s">
+      <c r="G17">
+        <v>121813166897471</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>518</v>
       </c>
-      <c r="I17" s="6"/>
+      <c r="I17" s="7"/>
     </row>
     <row r="18" customFormat="1" ht="16.5" spans="1:9">
       <c r="A18" s="1">
@@ -11384,11 +11412,13 @@
         <v>521</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="7" t="s">
+      <c r="G18">
+        <v>107669574278873</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>522</v>
       </c>
-      <c r="I18" s="6"/>
+      <c r="I18" s="7"/>
     </row>
     <row r="19" customFormat="1" ht="16.5" spans="1:9">
       <c r="A19" s="1">
@@ -11407,11 +11437,13 @@
         <v>525</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="7" t="s">
+      <c r="G19">
+        <v>98723580431394</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="I19" s="6"/>
+      <c r="I19" s="7"/>
     </row>
     <row r="20" customFormat="1" ht="16.5" spans="1:9">
       <c r="A20" s="1">
@@ -11430,11 +11462,13 @@
         <v>529</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="7" t="s">
+      <c r="G20">
+        <v>126241505230536</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="I20" s="6"/>
+      <c r="I20" s="7"/>
     </row>
     <row r="21" ht="16.5" spans="1:9">
       <c r="A21" s="1">
@@ -11453,11 +11487,13 @@
         <v>533</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="7" t="s">
+      <c r="G21">
+        <v>78092021290844</v>
+      </c>
+      <c r="H21" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="I21" s="6"/>
+      <c r="I21" s="7"/>
     </row>
     <row r="22" ht="16.5" spans="1:9">
       <c r="A22" s="1">
@@ -11476,11 +11512,13 @@
         <v>537</v>
       </c>
       <c r="F22" s="1"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="7" t="s">
+      <c r="G22">
+        <v>138731887343821</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="I22" s="6"/>
+      <c r="I22" s="7"/>
     </row>
     <row r="23" ht="16.5" spans="1:9">
       <c r="A23" s="1">
@@ -11499,11 +11537,13 @@
         <v>541</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="7" t="s">
+      <c r="G23">
+        <v>113127149166000</v>
+      </c>
+      <c r="H23" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="I23" s="6"/>
+      <c r="I23" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -2864,7 +2864,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2890,6 +2890,9 @@
       <alignment horizontal="fill" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3280,62 +3283,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="23" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="26" customHeight="1" spans="1:6">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="23" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3352,7 +3355,7 @@
       <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="26" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
@@ -3372,7 +3375,7 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="27" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3389,7 +3392,7 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="26" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3406,7 +3409,7 @@
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="26" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
@@ -3426,7 +3429,7 @@
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="27" t="s">
         <v>21</v>
       </c>
       <c r="F8" t="s">
@@ -3446,7 +3449,7 @@
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="27" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
@@ -3466,7 +3469,7 @@
       <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="26" t="s">
         <v>25</v>
       </c>
       <c r="F10" t="s">
@@ -3594,7 +3597,7 @@
       <c r="A9" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="29" t="s">
         <v>575</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3605,7 +3608,7 @@
       <c r="A10" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="29" t="s">
         <v>578</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3616,7 +3619,7 @@
       <c r="A11" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="29" t="s">
         <v>581</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3627,7 +3630,7 @@
       <c r="A12" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="29" t="s">
         <v>584</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3638,7 +3641,7 @@
       <c r="A13" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="29" t="s">
         <v>587</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3649,7 +3652,7 @@
       <c r="A14" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="29" t="s">
         <v>590</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3660,7 +3663,7 @@
       <c r="A15" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="29" t="s">
         <v>593</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3671,7 +3674,7 @@
       <c r="A16" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="29" t="s">
         <v>596</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3682,7 +3685,7 @@
       <c r="A17" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="29" t="s">
         <v>599</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3693,7 +3696,7 @@
       <c r="A18" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="29" t="s">
         <v>602</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3704,7 +3707,7 @@
       <c r="A19" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="29" t="s">
         <v>605</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3715,7 +3718,7 @@
       <c r="A20" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="29" t="s">
         <v>608</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3726,7 +3729,7 @@
       <c r="A21" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="29" t="s">
         <v>611</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3737,7 +3740,7 @@
       <c r="A22" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="29" t="s">
         <v>614</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3748,7 +3751,7 @@
       <c r="A23" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="29" t="s">
         <v>617</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3759,7 +3762,7 @@
       <c r="A24" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="29" t="s">
         <v>620</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3770,7 +3773,7 @@
       <c r="A25" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="29" t="s">
         <v>623</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -3781,7 +3784,7 @@
       <c r="A26" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="29" t="s">
         <v>626</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -3792,7 +3795,7 @@
       <c r="A27" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="29" t="s">
         <v>629</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -3803,7 +3806,7 @@
       <c r="A28" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="29" t="s">
         <v>632</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -3814,7 +3817,7 @@
       <c r="A29" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="29" t="s">
         <v>635</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -3825,7 +3828,7 @@
       <c r="A30" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="29" t="s">
         <v>638</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -3836,7 +3839,7 @@
       <c r="A31" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="29" t="s">
         <v>641</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -3847,7 +3850,7 @@
       <c r="A32" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="29" t="s">
         <v>644</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -3858,7 +3861,7 @@
       <c r="A33" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="29" t="s">
         <v>647</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -3869,7 +3872,7 @@
       <c r="A34" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="29" t="s">
         <v>650</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -3880,7 +3883,7 @@
       <c r="A35" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="29" t="s">
         <v>653</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -3891,7 +3894,7 @@
       <c r="A36" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="29" t="s">
         <v>656</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -3902,7 +3905,7 @@
       <c r="A37" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="29" t="s">
         <v>659</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -3913,7 +3916,7 @@
       <c r="A38" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="29" t="s">
         <v>662</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -3924,7 +3927,7 @@
       <c r="A39" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="B39" s="28" t="s">
+      <c r="B39" s="29" t="s">
         <v>665</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -3935,7 +3938,7 @@
       <c r="A40" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B40" s="29" t="s">
         <v>668</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -3946,7 +3949,7 @@
       <c r="A41" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="29" t="s">
         <v>671</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -3957,7 +3960,7 @@
       <c r="A42" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="B42" s="28" t="s">
+      <c r="B42" s="29" t="s">
         <v>674</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -3968,7 +3971,7 @@
       <c r="A43" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="30" t="s">
         <v>677</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -3979,7 +3982,7 @@
       <c r="A44" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="30" t="s">
         <v>680</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -3990,7 +3993,7 @@
       <c r="A45" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="30" t="s">
         <v>683</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -4001,7 +4004,7 @@
       <c r="A46" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B46" s="29" t="s">
+      <c r="B46" s="30" t="s">
         <v>686</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -4012,7 +4015,7 @@
       <c r="A47" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="30" t="s">
         <v>689</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -4023,7 +4026,7 @@
       <c r="A48" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="B48" s="29" t="s">
+      <c r="B48" s="30" t="s">
         <v>692</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -4034,7 +4037,7 @@
       <c r="A49" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="B49" s="29" t="s">
+      <c r="B49" s="30" t="s">
         <v>695</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -4045,7 +4048,7 @@
       <c r="A50" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="B50" s="29" t="s">
+      <c r="B50" s="30" t="s">
         <v>698</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -4056,7 +4059,7 @@
       <c r="A51" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="B51" s="29" t="s">
+      <c r="B51" s="30" t="s">
         <v>701</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -4067,7 +4070,7 @@
       <c r="A52" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="B52" s="29" t="s">
+      <c r="B52" s="30" t="s">
         <v>704</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -4078,7 +4081,7 @@
       <c r="A53" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="B53" s="29" t="s">
+      <c r="B53" s="30" t="s">
         <v>707</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -4089,7 +4092,7 @@
       <c r="A54" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="B54" s="29" t="s">
+      <c r="B54" s="30" t="s">
         <v>710</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -4100,7 +4103,7 @@
       <c r="A55" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="B55" s="29" t="s">
+      <c r="B55" s="30" t="s">
         <v>713</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -4119,389 +4122,389 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="44.175" style="16" customWidth="1"/>
-    <col min="2" max="2" width="71.3583333333333" style="16" customWidth="1"/>
-    <col min="3" max="3" width="123.558333333333" style="16" customWidth="1"/>
-    <col min="4" max="4" width="82.8666666666667" style="16" customWidth="1"/>
-    <col min="5" max="6" width="9" style="16"/>
-    <col min="7" max="7" width="81.1833333333333" style="16" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="16"/>
+    <col min="1" max="1" width="44.175" style="17" customWidth="1"/>
+    <col min="2" max="2" width="71.3583333333333" style="17" customWidth="1"/>
+    <col min="3" max="3" width="123.558333333333" style="17" customWidth="1"/>
+    <col min="4" max="4" width="82.8666666666667" style="17" customWidth="1"/>
+    <col min="5" max="6" width="9" style="17"/>
+    <col min="7" max="7" width="81.1833333333333" style="17" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" s="16" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
-      <c r="A1" s="17" t="s">
+    <row r="1" s="17" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
+      <c r="A1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
-    <row r="2" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+    <row r="2" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
     </row>
-    <row r="3" s="16" customFormat="1" ht="91" customHeight="1" spans="1:7">
-      <c r="A3" s="17" t="s">
+    <row r="3" s="17" customFormat="1" ht="91" customHeight="1" spans="1:7">
+      <c r="A3" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
     </row>
-    <row r="4" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A4" s="17" t="s">
+    <row r="4" s="17" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A4" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
-    <row r="5" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A5" s="17" t="s">
+    <row r="5" s="17" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A5" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <v>10</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
     </row>
-    <row r="6" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A6" s="17" t="s">
+    <row r="6" s="17" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A6" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
     </row>
-    <row r="7" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A7" s="19" t="s">
+    <row r="7" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A7" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
     </row>
-    <row r="8" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A8" s="19" t="s">
+    <row r="8" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A8" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
     </row>
-    <row r="9" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A9" s="19" t="s">
+    <row r="9" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A9" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
     </row>
-    <row r="10" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A10" s="17" t="s">
+    <row r="10" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
     </row>
-    <row r="11" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A11" s="17" t="s">
+    <row r="11" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A11" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
     </row>
-    <row r="12" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A12" s="17" t="s">
+    <row r="12" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A12" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
     </row>
-    <row r="13" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
+    <row r="13" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
     </row>
-    <row r="14" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+    <row r="14" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
     </row>
-    <row r="15" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+    <row r="15" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
     </row>
-    <row r="16" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
+    <row r="16" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
     </row>
-    <row r="17" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
+    <row r="17" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
     </row>
-    <row r="18" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
+    <row r="18" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
     </row>
-    <row r="19" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+    <row r="19" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
     </row>
-    <row r="20" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+    <row r="20" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
     </row>
-    <row r="21" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+    <row r="21" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
     </row>
-    <row r="22" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
+    <row r="22" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
     </row>
-    <row r="23" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
+    <row r="23" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
     </row>
-    <row r="24" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
+    <row r="24" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
     </row>
-    <row r="25" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
+    <row r="25" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
     </row>
-    <row r="26" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
+    <row r="26" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
     </row>
-    <row r="27" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
+    <row r="27" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="C27" s="18"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
     </row>
-    <row r="28" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
+    <row r="28" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
     </row>
-    <row r="29" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
+    <row r="29" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
     </row>
-    <row r="30" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
+    <row r="30" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
     </row>
-    <row r="31" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
+    <row r="31" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
     </row>
-    <row r="32" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
+    <row r="32" s="17" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
     </row>
-    <row r="33" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
+    <row r="33" s="17" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
     </row>
-    <row r="34" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
+    <row r="34" s="17" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
     </row>
-    <row r="35" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
+    <row r="35" s="17" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
     </row>
-    <row r="36" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
+    <row r="36" s="17" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -4867,943 +4870,943 @@
   <dimension ref="A1:E55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" width="37.75" style="14" customWidth="1"/>
+    <col min="1" max="2" width="37.75" style="15" customWidth="1"/>
     <col min="3" max="3" width="33.0833333333333" customWidth="1"/>
     <col min="4" max="5" width="40.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="16" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="16" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="15">
+      <c r="A4" s="16">
         <v>1</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="16">
         <v>1</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="16">
         <v>80</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="16">
         <v>3</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <v>2</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="16">
         <v>2</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="16">
         <v>4</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <v>3</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="15">
+      <c r="A6" s="16">
         <v>3</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="16">
         <v>3</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="16">
         <v>4</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="16">
         <v>3</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="15">
+      <c r="A7" s="16">
         <v>4</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="16">
         <v>4</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="16">
         <v>4</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="16">
         <v>3</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="15">
+      <c r="A8" s="16">
         <v>5</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="16">
         <v>5</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="16">
         <v>4</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="16">
         <v>3</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="15">
+      <c r="A9" s="16">
         <v>6</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="16">
         <v>6</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="16">
         <v>4</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="16">
         <v>3</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="15">
+      <c r="A10" s="16">
         <v>7</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="16">
         <v>7</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="16">
         <v>4</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="16">
         <v>3</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="15">
+      <c r="A11" s="16">
         <v>8</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="16">
         <v>8</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="16">
         <v>4</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="16">
         <v>3</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="15">
+      <c r="A12" s="16">
         <v>9</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="16">
         <v>9</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="16">
         <v>4</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="16">
         <v>3</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="15">
+      <c r="A13" s="16">
         <v>10</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="16">
         <v>10</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="16">
         <v>4</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="16">
         <v>3</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="15">
+      <c r="A14" s="16">
         <v>11</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="16">
         <v>11</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="16">
         <v>4</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="16">
         <v>3</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="15">
+      <c r="A15" s="16">
         <v>12</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="16">
         <v>12</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="16">
         <v>4</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="16">
         <v>3</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="15">
+      <c r="A16" s="16">
         <v>13</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="16">
         <v>13</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="16">
         <v>4</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="16">
         <v>3</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="15">
+      <c r="A17" s="16">
         <v>14</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="16">
         <v>14</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="16">
         <v>4</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="16">
         <v>3</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="15">
+      <c r="A18" s="16">
         <v>15</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="16">
         <v>15</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="16">
         <v>4</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="16">
         <v>3</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="15">
+      <c r="A19" s="16">
         <v>16</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="16">
         <v>16</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="16">
         <v>4</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="16">
         <v>3</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="15">
+      <c r="A20" s="16">
         <v>17</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="16">
         <v>17</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="16">
         <v>4</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="16">
         <v>3</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="15">
+      <c r="A21" s="16">
         <v>18</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="16">
         <v>18</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="16">
         <v>4</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="16">
         <v>3</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="15">
+      <c r="A22" s="16">
         <v>19</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="16">
         <v>19</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="16">
         <v>4</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="16">
         <v>3</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="15">
+      <c r="A23" s="16">
         <v>20</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="16">
         <v>20</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="16">
         <v>4</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="16">
         <v>3</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="15">
+      <c r="A24" s="16">
         <v>21</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="16">
         <v>21</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="16">
         <v>4</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="16">
         <v>3</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="15">
+      <c r="A25" s="16">
         <v>22</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="16">
         <v>22</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="16">
         <v>4</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="16">
         <v>3</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="15">
+      <c r="A26" s="16">
         <v>23</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="16">
         <v>23</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="16">
         <v>4</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="16">
         <v>3</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="15">
+      <c r="A27" s="16">
         <v>24</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="16">
         <v>24</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="16">
         <v>4</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="16">
         <v>3</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="15">
+      <c r="A28" s="16">
         <v>25</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="16">
         <v>25</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="16">
         <v>4</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="16">
         <v>3</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="15">
+      <c r="A29" s="16">
         <v>26</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="16">
         <v>26</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="16">
         <v>4</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="16">
         <v>3</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="15">
+      <c r="A30" s="16">
         <v>27</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="16">
         <v>27</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="16">
         <v>4</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="16">
         <v>3</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="15">
+      <c r="A31" s="16">
         <v>28</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="16">
         <v>28</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="16">
         <v>4</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="16">
         <v>3</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="15">
+      <c r="A32" s="16">
         <v>29</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="16">
         <v>29</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="16">
         <v>4</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="16">
         <v>3</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="15">
+      <c r="A33" s="16">
         <v>30</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="16">
         <v>30</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="16">
         <v>4</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="16">
         <v>3</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="15">
+      <c r="A34" s="16">
         <v>31</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="16">
         <v>31</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="16">
         <v>4</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="16">
         <v>3</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="15">
+      <c r="A35" s="16">
         <v>32</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="16">
         <v>32</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="16">
         <v>4</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="16">
         <v>3</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="15">
+      <c r="A36" s="16">
         <v>33</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="16">
         <v>33</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="16">
         <v>4</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="16">
         <v>3</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="15">
+      <c r="A37" s="16">
         <v>34</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="16">
         <v>34</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="16">
         <v>4</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="16">
         <v>3</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="15">
+      <c r="A38" s="16">
         <v>35</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="16">
         <v>35</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="16">
         <v>4</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="16">
         <v>3</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="15">
+      <c r="A39" s="16">
         <v>36</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="16">
         <v>36</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="16">
         <v>4</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="16">
         <v>3</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="15">
+      <c r="A40" s="16">
         <v>37</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="16">
         <v>37</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="16">
         <v>4</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="16">
         <v>3</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="15">
+      <c r="A41" s="16">
         <v>38</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="16">
         <v>38</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="16">
         <v>4</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="16">
         <v>3</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="15">
+      <c r="A42" s="16">
         <v>39</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="16">
         <v>39</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="16">
         <v>4</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="16">
         <v>3</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="15">
+      <c r="A43" s="16">
         <v>40</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="16">
         <v>40</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="16">
         <v>4</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="16">
         <v>3</v>
       </c>
-      <c r="E43" s="15" t="s">
+      <c r="E43" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="15">
+      <c r="A44" s="16">
         <v>41</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="16">
         <v>41</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="16">
         <v>4</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="16">
         <v>3</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="E44" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="15">
+      <c r="A45" s="16">
         <v>42</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="16">
         <v>42</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="16">
         <v>4</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="16">
         <v>3</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="E45" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="15">
+      <c r="A46" s="16">
         <v>43</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="16">
         <v>43</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="16">
         <v>4</v>
       </c>
-      <c r="D46" s="15">
+      <c r="D46" s="16">
         <v>3</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="15">
+      <c r="A47" s="16">
         <v>44</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="16">
         <v>44</v>
       </c>
-      <c r="C47" s="15">
+      <c r="C47" s="16">
         <v>4</v>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="16">
         <v>3</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="15">
+      <c r="A48" s="16">
         <v>45</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48" s="16">
         <v>45</v>
       </c>
-      <c r="C48" s="15">
+      <c r="C48" s="16">
         <v>4</v>
       </c>
-      <c r="D48" s="15">
+      <c r="D48" s="16">
         <v>3</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="15">
+      <c r="A49" s="16">
         <v>46</v>
       </c>
-      <c r="B49" s="15">
+      <c r="B49" s="16">
         <v>46</v>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="16">
         <v>4</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="16">
         <v>3</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="15">
+      <c r="A50" s="16">
         <v>47</v>
       </c>
-      <c r="B50" s="15">
+      <c r="B50" s="16">
         <v>47</v>
       </c>
-      <c r="C50" s="15">
+      <c r="C50" s="16">
         <v>4</v>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="16">
         <v>3</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="15">
+      <c r="A51" s="16">
         <v>48</v>
       </c>
-      <c r="B51" s="15">
+      <c r="B51" s="16">
         <v>48</v>
       </c>
-      <c r="C51" s="15">
+      <c r="C51" s="16">
         <v>4</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="16">
         <v>3</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="15">
+      <c r="A52" s="16">
         <v>49</v>
       </c>
-      <c r="B52" s="15">
+      <c r="B52" s="16">
         <v>49</v>
       </c>
-      <c r="C52" s="15">
+      <c r="C52" s="16">
         <v>4</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="16">
         <v>3</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="15">
+      <c r="A53" s="16">
         <v>50</v>
       </c>
-      <c r="B53" s="15">
+      <c r="B53" s="16">
         <v>50</v>
       </c>
-      <c r="C53" s="15">
+      <c r="C53" s="16">
         <v>4</v>
       </c>
-      <c r="D53" s="15">
+      <c r="D53" s="16">
         <v>3</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="E53" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="15">
+      <c r="A54" s="16">
         <v>51</v>
       </c>
-      <c r="B54" s="15">
+      <c r="B54" s="16">
         <v>51</v>
       </c>
-      <c r="C54" s="15">
+      <c r="C54" s="16">
         <v>4</v>
       </c>
-      <c r="D54" s="15">
+      <c r="D54" s="16">
         <v>3</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="E54" s="16" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="15">
+      <c r="A55" s="16">
         <v>52</v>
       </c>
-      <c r="B55" s="15">
+      <c r="B55" s="16">
         <v>52</v>
       </c>
-      <c r="C55" s="15">
+      <c r="C55" s="16">
         <v>4</v>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="16">
         <v>3</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" s="16" t="s">
         <v>89</v>
       </c>
     </row>
@@ -5819,801 +5822,801 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="27.75" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="25.175" style="10" customWidth="1"/>
-    <col min="2" max="2" width="13.575" style="10" customWidth="1"/>
-    <col min="3" max="3" width="127.141666666667" style="10" customWidth="1"/>
-    <col min="4" max="4" width="49" style="10" customWidth="1"/>
-    <col min="5" max="5" width="92.9666666666667" style="11" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="25.175" style="11" customWidth="1"/>
+    <col min="2" max="2" width="13.575" style="11" customWidth="1"/>
+    <col min="3" max="3" width="127.141666666667" style="11" customWidth="1"/>
+    <col min="4" max="4" width="49" style="11" customWidth="1"/>
+    <col min="5" max="5" width="92.9666666666667" style="12" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="12">
+      <c r="A4" s="13">
         <v>1</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="13">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="12">
+      <c r="A5" s="13">
         <v>2</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="13">
         <v>2</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="12">
+      <c r="A6" s="13">
         <v>3</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="13">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="12">
+      <c r="A7" s="13">
         <v>4</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="13">
         <v>4</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="12">
+      <c r="A8" s="13">
         <v>5</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="13">
         <v>5</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="12">
+      <c r="A9" s="13">
         <v>6</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="13">
         <v>6</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="12">
+      <c r="A10" s="13">
         <v>7</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="13">
         <v>7</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="12">
+      <c r="A11" s="13">
         <v>8</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="13">
         <v>8</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="12">
+      <c r="A12" s="13">
         <v>9</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="13">
         <v>9</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="12">
+      <c r="A13" s="13">
         <v>10</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="13">
         <v>10</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="12">
+      <c r="A14" s="13">
         <v>11</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="13">
         <v>11</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="12">
+      <c r="A15" s="13">
         <v>12</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="13">
         <v>12</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="12">
+      <c r="A16" s="13">
         <v>13</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="13">
         <v>13</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="12">
+      <c r="A17" s="13">
         <v>14</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="13">
         <v>14</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="12">
+      <c r="A18" s="13">
         <v>15</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="13">
         <v>15</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="12">
+      <c r="A19" s="13">
         <v>16</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="13">
         <v>16</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="12">
+      <c r="A20" s="13">
         <v>17</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="13">
         <v>17</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="12">
+      <c r="A21" s="13">
         <v>18</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="13">
         <v>18</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="12">
+      <c r="A22" s="13">
         <v>19</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="13">
         <v>19</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="12">
+      <c r="A23" s="13">
         <v>20</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="13">
         <v>20</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="12">
+      <c r="A24" s="13">
         <v>21</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="13">
         <v>21</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="12">
+      <c r="A25" s="13">
         <v>22</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="13">
         <v>22</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="12">
+      <c r="A26" s="13">
         <v>23</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="13">
         <v>23</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="12">
+      <c r="A27" s="13">
         <v>24</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="13">
         <v>24</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="12">
+      <c r="A28" s="13">
         <v>25</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="13">
         <v>25</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="12">
+      <c r="A29" s="13">
         <v>26</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="13">
         <v>26</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="12">
+      <c r="A30" s="13">
         <v>27</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="13">
         <v>27</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="12">
+      <c r="A31" s="13">
         <v>28</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="13">
         <v>28</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="12">
+      <c r="A32" s="13">
         <v>29</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="13">
         <v>29</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="12">
+      <c r="A33" s="13">
         <v>30</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="13">
         <v>30</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="12">
+      <c r="A34" s="13">
         <v>31</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="13">
         <v>31</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="12">
+      <c r="A35" s="13">
         <v>32</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="13">
         <v>32</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="12">
+      <c r="A36" s="13">
         <v>33</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="13">
         <v>33</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="12">
+      <c r="A37" s="13">
         <v>34</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="13">
         <v>34</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="12">
+      <c r="A38" s="13">
         <v>35</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="13">
         <v>35</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="12">
+      <c r="A39" s="13">
         <v>36</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="13">
         <v>36</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="12">
+      <c r="A40" s="13">
         <v>37</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="13">
         <v>37</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="12">
+      <c r="A41" s="13">
         <v>38</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="13">
         <v>38</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="12">
+      <c r="A42" s="13">
         <v>39</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="13">
         <v>39</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="13">
+      <c r="A43" s="14">
         <v>40</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="14">
         <v>40</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="13">
+      <c r="A44" s="14">
         <v>41</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="14">
         <v>41</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="13">
+      <c r="A45" s="14">
         <v>42</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="14">
         <v>42</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="13">
+      <c r="A46" s="14">
         <v>43</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="14">
         <v>43</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="13">
+      <c r="A47" s="14">
         <v>44</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="14">
         <v>44</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="13">
+      <c r="A48" s="14">
         <v>45</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="14">
         <v>45</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="13">
+      <c r="A49" s="14">
         <v>46</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="14">
         <v>46</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="13">
+      <c r="A50" s="14">
         <v>47</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="14">
         <v>47</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="13">
+      <c r="A51" s="14">
         <v>48</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="14">
         <v>48</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="13">
+      <c r="A52" s="14">
         <v>49</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="14">
         <v>49</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="13">
+      <c r="A53" s="14">
         <v>50</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="14">
         <v>50</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="13">
+      <c r="A54" s="14">
         <v>51</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="14">
         <v>51</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="13">
+      <c r="A55" s="14">
         <v>52</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="14">
         <v>52</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="14" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="13"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
+      <c r="A56" s="14"/>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="13"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="C58" s="13"/>
+      <c r="C58" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6732,9 +6735,9 @@
         <v>1</v>
       </c>
       <c r="F4" s="9">
-        <v>73689874069532</v>
-      </c>
-      <c r="G4" s="9" t="s">
+        <v>113244405937302</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>164</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -6759,9 +6762,9 @@
         <v>1</v>
       </c>
       <c r="F5" s="9">
-        <v>103338086714343</v>
-      </c>
-      <c r="G5" s="9" t="s">
+        <v>105711056874756</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>167</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -6788,9 +6791,9 @@
         <v>1</v>
       </c>
       <c r="F6" s="9">
-        <v>114468149232543</v>
-      </c>
-      <c r="G6" s="9" t="s">
+        <v>82693303214454</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>169</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -6817,9 +6820,9 @@
         <v>1</v>
       </c>
       <c r="F7" s="9">
-        <v>102034222005672</v>
-      </c>
-      <c r="G7" s="9" t="s">
+        <v>102504658102706</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>171</v>
       </c>
       <c r="H7" s="2" t="s">
@@ -6846,9 +6849,9 @@
         <v>2</v>
       </c>
       <c r="F8" s="9">
-        <v>83505287199254</v>
-      </c>
-      <c r="G8" s="9" t="s">
+        <v>83069096807916</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>173</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -6873,9 +6876,9 @@
         <v>2</v>
       </c>
       <c r="F9" s="9">
-        <v>82413393212572</v>
-      </c>
-      <c r="G9" s="9" t="s">
+        <v>80534536398974</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>175</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -6901,9 +6904,9 @@
         <v>2</v>
       </c>
       <c r="F10" s="9">
-        <v>93587171790136</v>
-      </c>
-      <c r="G10" s="9" t="s">
+        <v>74246671448525</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>177</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -6929,9 +6932,9 @@
         <v>2</v>
       </c>
       <c r="F11" s="9">
-        <v>98881391823727</v>
-      </c>
-      <c r="G11" s="9" t="s">
+        <v>71499702430100</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>179</v>
       </c>
       <c r="H11" s="2" t="s">
@@ -6957,9 +6960,9 @@
         <v>3</v>
       </c>
       <c r="F12" s="9">
-        <v>140583336060167</v>
-      </c>
-      <c r="G12" s="9" t="s">
+        <v>122909083001205</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>181</v>
       </c>
       <c r="H12" s="2" t="s">
@@ -6984,9 +6987,9 @@
         <v>3</v>
       </c>
       <c r="F13" s="9">
-        <v>111194186656631</v>
-      </c>
-      <c r="G13" s="9" t="s">
+        <v>128658267266293</v>
+      </c>
+      <c r="G13" s="10" t="s">
         <v>183</v>
       </c>
       <c r="H13" s="2" t="s">
@@ -7011,9 +7014,9 @@
         <v>3</v>
       </c>
       <c r="F14" s="9">
-        <v>133914186848952</v>
-      </c>
-      <c r="G14" s="9" t="s">
+        <v>134748387119946</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>185</v>
       </c>
       <c r="H14" s="2" t="s">
@@ -7038,9 +7041,9 @@
         <v>3</v>
       </c>
       <c r="F15" s="9">
-        <v>122198581325096</v>
-      </c>
-      <c r="G15" s="9" t="s">
+        <v>131559815185521</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>187</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -7065,9 +7068,9 @@
         <v>4</v>
       </c>
       <c r="F16" s="9">
-        <v>137046890645413</v>
-      </c>
-      <c r="G16" s="9" t="s">
+        <v>135406755438948</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>189</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -7096,9 +7099,9 @@
         <v>4</v>
       </c>
       <c r="F17" s="9">
-        <v>102352328211075</v>
-      </c>
-      <c r="G17" s="9" t="s">
+        <v>128433990441931</v>
+      </c>
+      <c r="G17" s="10" t="s">
         <v>191</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -7127,9 +7130,9 @@
         <v>4</v>
       </c>
       <c r="F18" s="9">
-        <v>82050572064304</v>
-      </c>
-      <c r="G18" s="9" t="s">
+        <v>86357992624263</v>
+      </c>
+      <c r="G18" s="10" t="s">
         <v>193</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -7158,9 +7161,9 @@
         <v>4</v>
       </c>
       <c r="F19" s="9">
-        <v>78831531789183</v>
-      </c>
-      <c r="G19" s="9" t="s">
+        <v>96128137486525</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>195</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -7189,9 +7192,9 @@
         <v>5</v>
       </c>
       <c r="F20" s="9">
-        <v>108041083429458</v>
-      </c>
-      <c r="G20" s="9" t="s">
+        <v>131913492630514</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>197</v>
       </c>
       <c r="H20" s="2" t="s">
@@ -7220,9 +7223,9 @@
         <v>5</v>
       </c>
       <c r="F21" s="9">
-        <v>86299665819505</v>
-      </c>
-      <c r="G21" s="9" t="s">
+        <v>119579899338192</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>199</v>
       </c>
       <c r="H21" s="2" t="s">
@@ -7251,9 +7254,9 @@
         <v>5</v>
       </c>
       <c r="F22" s="9">
-        <v>123569723967761</v>
-      </c>
-      <c r="G22" s="9" t="s">
+        <v>82472089572732</v>
+      </c>
+      <c r="G22" s="10" t="s">
         <v>201</v>
       </c>
       <c r="H22" s="2" t="s">
@@ -7282,9 +7285,9 @@
         <v>5</v>
       </c>
       <c r="F23" s="9">
-        <v>119546448004051</v>
-      </c>
-      <c r="G23" s="9" t="s">
+        <v>104108852156434</v>
+      </c>
+      <c r="G23" s="10" t="s">
         <v>203</v>
       </c>
       <c r="H23" s="2" t="s">
@@ -7313,9 +7316,9 @@
         <v>6</v>
       </c>
       <c r="F24" s="9">
-        <v>91007101306341</v>
-      </c>
-      <c r="G24" s="9" t="s">
+        <v>79005623120233</v>
+      </c>
+      <c r="G24" s="10" t="s">
         <v>205</v>
       </c>
       <c r="H24" s="2" t="s">
@@ -7344,9 +7347,9 @@
         <v>6</v>
       </c>
       <c r="F25" s="9">
-        <v>91391954516503</v>
-      </c>
-      <c r="G25" s="9" t="s">
+        <v>97611938478078</v>
+      </c>
+      <c r="G25" s="10" t="s">
         <v>207</v>
       </c>
       <c r="H25" s="2" t="s">
@@ -7375,9 +7378,9 @@
         <v>6</v>
       </c>
       <c r="F26" s="9">
-        <v>109276220541606</v>
-      </c>
-      <c r="G26" s="9" t="s">
+        <v>81806655827798</v>
+      </c>
+      <c r="G26" s="10" t="s">
         <v>209</v>
       </c>
       <c r="H26" s="2" t="s">
@@ -7406,9 +7409,9 @@
         <v>6</v>
       </c>
       <c r="F27" s="9">
-        <v>108792020810626</v>
-      </c>
-      <c r="G27" s="9" t="s">
+        <v>105716218867716</v>
+      </c>
+      <c r="G27" s="10" t="s">
         <v>211</v>
       </c>
       <c r="H27" s="2" t="s">
@@ -7437,9 +7440,9 @@
         <v>7</v>
       </c>
       <c r="F28" s="9">
-        <v>94990895501990</v>
-      </c>
-      <c r="G28" s="9" t="s">
+        <v>128411546772202</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>213</v>
       </c>
       <c r="H28" s="2" t="s">
@@ -7468,9 +7471,9 @@
         <v>7</v>
       </c>
       <c r="F29" s="9">
-        <v>92053411642730</v>
-      </c>
-      <c r="G29" s="9" t="s">
+        <v>139465058617680</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>215</v>
       </c>
       <c r="H29" s="2" t="s">
@@ -7499,9 +7502,9 @@
         <v>7</v>
       </c>
       <c r="F30" s="9">
-        <v>129094955837159</v>
-      </c>
-      <c r="G30" s="9" t="s">
+        <v>81737011057690</v>
+      </c>
+      <c r="G30" s="10" t="s">
         <v>217</v>
       </c>
       <c r="H30" s="2" t="s">
@@ -7530,9 +7533,9 @@
         <v>7</v>
       </c>
       <c r="F31" s="9">
-        <v>136720402016106</v>
-      </c>
-      <c r="G31" s="9" t="s">
+        <v>81445862907930</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>219</v>
       </c>
       <c r="H31" s="2" t="s">
@@ -7561,9 +7564,9 @@
         <v>8</v>
       </c>
       <c r="F32" s="9">
-        <v>103985740716894</v>
-      </c>
-      <c r="G32" s="9" t="s">
+        <v>123098432383687</v>
+      </c>
+      <c r="G32" s="10" t="s">
         <v>221</v>
       </c>
       <c r="H32" s="2" t="s">
@@ -7592,9 +7595,9 @@
         <v>8</v>
       </c>
       <c r="F33" s="9">
-        <v>110363379748775</v>
-      </c>
-      <c r="G33" s="9" t="s">
+        <v>131796260838154</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>223</v>
       </c>
       <c r="H33" s="2" t="s">
@@ -7619,9 +7622,9 @@
         <v>8</v>
       </c>
       <c r="F34" s="9">
-        <v>130735151388109</v>
-      </c>
-      <c r="G34" s="9" t="s">
+        <v>116376878683736</v>
+      </c>
+      <c r="G34" s="10" t="s">
         <v>225</v>
       </c>
       <c r="H34" s="2" t="s">
@@ -7646,9 +7649,9 @@
         <v>8</v>
       </c>
       <c r="F35" s="9">
-        <v>112469820699203</v>
-      </c>
-      <c r="G35" s="9" t="s">
+        <v>100558097057142</v>
+      </c>
+      <c r="G35" s="10" t="s">
         <v>227</v>
       </c>
       <c r="H35" s="2" t="s">
@@ -7673,9 +7676,9 @@
         <v>9</v>
       </c>
       <c r="F36" s="9">
-        <v>104485794834544</v>
-      </c>
-      <c r="G36" s="9" t="s">
+        <v>92332707761527</v>
+      </c>
+      <c r="G36" s="10" t="s">
         <v>229</v>
       </c>
       <c r="H36" s="2" t="s">
@@ -7704,9 +7707,9 @@
         <v>6</v>
       </c>
       <c r="F37" s="9">
-        <v>99220241284612</v>
-      </c>
-      <c r="G37" s="9" t="s">
+        <v>108895787734224</v>
+      </c>
+      <c r="G37" s="10" t="s">
         <v>231</v>
       </c>
       <c r="H37" s="2" t="s">
@@ -7731,9 +7734,9 @@
         <v>7</v>
       </c>
       <c r="F38" s="9">
-        <v>80947939739818</v>
-      </c>
-      <c r="G38" s="9" t="s">
+        <v>95471681056681</v>
+      </c>
+      <c r="G38" s="10" t="s">
         <v>233</v>
       </c>
       <c r="H38" s="2" t="s">
@@ -7758,9 +7761,9 @@
         <v>9</v>
       </c>
       <c r="F39" s="9">
-        <v>107316878006177</v>
-      </c>
-      <c r="G39" s="9" t="s">
+        <v>104955598295323</v>
+      </c>
+      <c r="G39" s="10" t="s">
         <v>235</v>
       </c>
       <c r="H39" s="2" t="s">
@@ -7789,9 +7792,9 @@
         <v>10</v>
       </c>
       <c r="F40" s="9">
-        <v>81581045315216</v>
-      </c>
-      <c r="G40" s="9" t="s">
+        <v>103175883366340</v>
+      </c>
+      <c r="G40" s="10" t="s">
         <v>237</v>
       </c>
       <c r="H40" s="2" t="s">
@@ -7820,9 +7823,9 @@
         <v>10</v>
       </c>
       <c r="F41" s="9">
-        <v>112660123650049</v>
-      </c>
-      <c r="G41" s="9" t="s">
+        <v>114247164745798</v>
+      </c>
+      <c r="G41" s="10" t="s">
         <v>239</v>
       </c>
       <c r="H41" s="2" t="s">
@@ -7847,9 +7850,9 @@
         <v>10</v>
       </c>
       <c r="F42" s="9">
-        <v>105948548039431</v>
-      </c>
-      <c r="G42" s="9" t="s">
+        <v>86017047390182</v>
+      </c>
+      <c r="G42" s="10" t="s">
         <v>241</v>
       </c>
       <c r="H42" s="2" t="s">
@@ -7874,9 +7877,9 @@
         <v>10</v>
       </c>
       <c r="F43" s="9">
-        <v>136608949835509</v>
-      </c>
-      <c r="G43" s="9" t="s">
+        <v>81373582816266</v>
+      </c>
+      <c r="G43" s="10" t="s">
         <v>243</v>
       </c>
       <c r="H43" s="2" t="s">
@@ -7901,9 +7904,9 @@
         <v>11</v>
       </c>
       <c r="F44" s="9">
-        <v>123814344941081</v>
-      </c>
-      <c r="G44" s="9" t="s">
+        <v>132788281080826</v>
+      </c>
+      <c r="G44" s="10" t="s">
         <v>245</v>
       </c>
       <c r="H44" s="2" t="s">
@@ -7928,9 +7931,9 @@
         <v>11</v>
       </c>
       <c r="F45" s="9">
-        <v>70631811357234</v>
-      </c>
-      <c r="G45" s="9" t="s">
+        <v>95162444285252</v>
+      </c>
+      <c r="G45" s="10" t="s">
         <v>247</v>
       </c>
       <c r="H45" s="2" t="s">
@@ -7955,9 +7958,9 @@
         <v>11</v>
       </c>
       <c r="F46" s="9">
-        <v>121882306399734</v>
-      </c>
-      <c r="G46" s="9" t="s">
+        <v>95953438126479</v>
+      </c>
+      <c r="G46" s="10" t="s">
         <v>249</v>
       </c>
       <c r="H46" s="2" t="s">
@@ -7982,9 +7985,9 @@
         <v>11</v>
       </c>
       <c r="F47" s="9">
-        <v>98362111955314</v>
-      </c>
-      <c r="G47" s="9" t="s">
+        <v>112039222887887</v>
+      </c>
+      <c r="G47" s="10" t="s">
         <v>251</v>
       </c>
       <c r="H47" s="2" t="s">
@@ -8009,9 +8012,9 @@
         <v>12</v>
       </c>
       <c r="F48" s="9">
-        <v>87499152943626</v>
-      </c>
-      <c r="G48" s="9" t="s">
+        <v>95377459606647</v>
+      </c>
+      <c r="G48" s="10" t="s">
         <v>253</v>
       </c>
       <c r="H48" s="2" t="s">
@@ -8036,9 +8039,9 @@
         <v>12</v>
       </c>
       <c r="F49" s="9">
-        <v>94526628741923</v>
-      </c>
-      <c r="G49" s="9" t="s">
+        <v>113983796605688</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>255</v>
       </c>
       <c r="H49" s="2" t="s">
@@ -8063,9 +8066,9 @@
         <v>12</v>
       </c>
       <c r="F50" s="9">
-        <v>135071120477292</v>
-      </c>
-      <c r="G50" s="9" t="s">
+        <v>117157716541352</v>
+      </c>
+      <c r="G50" s="10" t="s">
         <v>257</v>
       </c>
       <c r="H50" s="2" t="s">
@@ -8090,9 +8093,9 @@
         <v>12</v>
       </c>
       <c r="F51" s="9">
-        <v>73644651229136</v>
-      </c>
-      <c r="G51" s="9" t="s">
+        <v>100893051807474</v>
+      </c>
+      <c r="G51" s="10" t="s">
         <v>259</v>
       </c>
       <c r="H51" s="2" t="s">
@@ -8117,9 +8120,9 @@
         <v>13</v>
       </c>
       <c r="F52" s="9">
-        <v>77926265714695</v>
-      </c>
-      <c r="G52" s="9" t="s">
+        <v>137999782231090</v>
+      </c>
+      <c r="G52" s="10" t="s">
         <v>261</v>
       </c>
       <c r="H52" s="2" t="s">
@@ -8144,9 +8147,9 @@
         <v>13</v>
       </c>
       <c r="F53" s="9">
-        <v>82854353471706</v>
-      </c>
-      <c r="G53" s="9" t="s">
+        <v>127007149281218</v>
+      </c>
+      <c r="G53" s="10" t="s">
         <v>263</v>
       </c>
       <c r="H53" s="2" t="s">
@@ -8171,9 +8174,9 @@
         <v>13</v>
       </c>
       <c r="F54" s="9">
-        <v>77671502371070</v>
-      </c>
-      <c r="G54" s="9" t="s">
+        <v>85273469740405</v>
+      </c>
+      <c r="G54" s="10" t="s">
         <v>265</v>
       </c>
       <c r="H54" s="2" t="s">
@@ -8198,9 +8201,9 @@
         <v>13</v>
       </c>
       <c r="F55" s="9">
-        <v>70793360263168</v>
-      </c>
-      <c r="G55" s="9" t="s">
+        <v>85750403977754</v>
+      </c>
+      <c r="G55" s="10" t="s">
         <v>267</v>
       </c>
       <c r="H55" s="2" t="s">
@@ -8225,9 +8228,9 @@
         <v>14</v>
       </c>
       <c r="F56" s="9">
-        <v>84818213347817</v>
-      </c>
-      <c r="G56" s="9" t="s">
+        <v>87658125570749</v>
+      </c>
+      <c r="G56" s="10" t="s">
         <v>269</v>
       </c>
       <c r="H56" s="2" t="s">
@@ -8252,9 +8255,9 @@
         <v>14</v>
       </c>
       <c r="F57" s="9">
-        <v>91851759457969</v>
-      </c>
-      <c r="G57" s="9" t="s">
+        <v>71386503893388</v>
+      </c>
+      <c r="G57" s="10" t="s">
         <v>271</v>
       </c>
       <c r="H57" s="2" t="s">
@@ -8279,9 +8282,9 @@
         <v>14</v>
       </c>
       <c r="F58" s="9">
-        <v>121890208198805</v>
-      </c>
-      <c r="G58" s="9" t="s">
+        <v>117660867991736</v>
+      </c>
+      <c r="G58" s="10" t="s">
         <v>273</v>
       </c>
       <c r="H58" s="2" t="s">
@@ -8306,9 +8309,9 @@
         <v>14</v>
       </c>
       <c r="F59" s="9">
-        <v>117985852407168</v>
-      </c>
-      <c r="G59" s="9" t="s">
+        <v>75602786825729</v>
+      </c>
+      <c r="G59" s="10" t="s">
         <v>275</v>
       </c>
       <c r="H59" s="2" t="s">
@@ -8333,9 +8336,9 @@
         <v>15</v>
       </c>
       <c r="F60" s="9">
-        <v>97339206973141</v>
-      </c>
-      <c r="G60" s="9" t="s">
+        <v>97494295137425</v>
+      </c>
+      <c r="G60" s="10" t="s">
         <v>277</v>
       </c>
       <c r="H60" s="2" t="s">
@@ -8360,9 +8363,9 @@
         <v>15</v>
       </c>
       <c r="F61" s="9">
-        <v>91021502703797</v>
-      </c>
-      <c r="G61" s="9" t="s">
+        <v>121387106380169</v>
+      </c>
+      <c r="G61" s="10" t="s">
         <v>279</v>
       </c>
       <c r="H61" s="2" t="s">
@@ -8387,9 +8390,9 @@
         <v>15</v>
       </c>
       <c r="F62" s="9">
-        <v>118793829418414</v>
-      </c>
-      <c r="G62" s="9" t="s">
+        <v>77703154963129</v>
+      </c>
+      <c r="G62" s="10" t="s">
         <v>281</v>
       </c>
       <c r="H62" s="2" t="s">
@@ -8414,9 +8417,9 @@
         <v>15</v>
       </c>
       <c r="F63" s="9">
-        <v>108919245506457</v>
-      </c>
-      <c r="G63" s="9" t="s">
+        <v>82745313217810</v>
+      </c>
+      <c r="G63" s="10" t="s">
         <v>283</v>
       </c>
       <c r="H63" s="2" t="s">
@@ -8441,9 +8444,9 @@
         <v>16</v>
       </c>
       <c r="F64" s="9">
-        <v>135998992968408</v>
-      </c>
-      <c r="G64" s="9" t="s">
+        <v>78702263483439</v>
+      </c>
+      <c r="G64" s="10" t="s">
         <v>285</v>
       </c>
       <c r="H64" s="2" t="s">
@@ -8468,9 +8471,9 @@
         <v>16</v>
       </c>
       <c r="F65" s="9">
-        <v>124995167587191</v>
-      </c>
-      <c r="G65" s="9" t="s">
+        <v>103252845267522</v>
+      </c>
+      <c r="G65" s="10" t="s">
         <v>287</v>
       </c>
       <c r="H65" s="2" t="s">
@@ -8495,9 +8498,9 @@
         <v>16</v>
       </c>
       <c r="F66" s="9">
-        <v>100207039759139</v>
-      </c>
-      <c r="G66" s="9" t="s">
+        <v>93380659059014</v>
+      </c>
+      <c r="G66" s="10" t="s">
         <v>289</v>
       </c>
       <c r="H66" s="2" t="s">
@@ -8522,9 +8525,9 @@
         <v>16</v>
       </c>
       <c r="F67" s="9">
-        <v>117284808467540</v>
-      </c>
-      <c r="G67" s="9" t="s">
+        <v>124070618735034</v>
+      </c>
+      <c r="G67" s="10" t="s">
         <v>291</v>
       </c>
       <c r="H67" s="2" t="s">
@@ -8549,9 +8552,9 @@
         <v>17</v>
       </c>
       <c r="F68" s="9">
-        <v>100856293823266</v>
-      </c>
-      <c r="G68" s="9" t="s">
+        <v>82229267783572</v>
+      </c>
+      <c r="G68" s="10" t="s">
         <v>293</v>
       </c>
       <c r="H68" s="2" t="s">
@@ -8576,9 +8579,9 @@
         <v>17</v>
       </c>
       <c r="F69" s="9">
-        <v>131767978667574</v>
-      </c>
-      <c r="G69" s="9" t="s">
+        <v>90764663625426</v>
+      </c>
+      <c r="G69" s="10" t="s">
         <v>295</v>
       </c>
       <c r="H69" s="2" t="s">
@@ -8603,9 +8606,9 @@
         <v>17</v>
       </c>
       <c r="F70" s="9">
-        <v>137793066084531</v>
-      </c>
-      <c r="G70" s="9" t="s">
+        <v>89592774326120</v>
+      </c>
+      <c r="G70" s="10" t="s">
         <v>297</v>
       </c>
       <c r="H70" s="2" t="s">
@@ -8630,9 +8633,9 @@
         <v>17</v>
       </c>
       <c r="F71" s="9">
-        <v>89446188580427</v>
-      </c>
-      <c r="G71" s="9" t="s">
+        <v>96498729983354</v>
+      </c>
+      <c r="G71" s="10" t="s">
         <v>299</v>
       </c>
       <c r="H71" s="2" t="s">
@@ -8657,9 +8660,9 @@
         <v>18</v>
       </c>
       <c r="F72" s="9">
-        <v>122719253084629</v>
-      </c>
-      <c r="G72" s="9" t="s">
+        <v>137402232463633</v>
+      </c>
+      <c r="G72" s="10" t="s">
         <v>301</v>
       </c>
       <c r="H72" s="2" t="s">
@@ -8684,9 +8687,9 @@
         <v>15</v>
       </c>
       <c r="F73" s="9">
-        <v>112549310275337</v>
-      </c>
-      <c r="G73" s="9" t="s">
+        <v>79717469784936</v>
+      </c>
+      <c r="G73" s="10" t="s">
         <v>303</v>
       </c>
       <c r="H73" s="2" t="s">
@@ -8711,9 +8714,9 @@
         <v>16</v>
       </c>
       <c r="F74" s="9">
-        <v>88430290010781</v>
-      </c>
-      <c r="G74" s="9" t="s">
+        <v>86646811474956</v>
+      </c>
+      <c r="G74" s="10" t="s">
         <v>305</v>
       </c>
       <c r="H74" s="2" t="s">
@@ -8738,9 +8741,9 @@
         <v>16</v>
       </c>
       <c r="F75" s="9">
-        <v>71786460797721</v>
-      </c>
-      <c r="G75" s="9" t="s">
+        <v>128217347353354</v>
+      </c>
+      <c r="G75" s="10" t="s">
         <v>307</v>
       </c>
       <c r="H75" s="2" t="s">
@@ -8765,9 +8768,9 @@
         <v>16</v>
       </c>
       <c r="F76" s="9">
-        <v>97338088026484</v>
-      </c>
-      <c r="G76" s="9" t="s">
+        <v>126321668579357</v>
+      </c>
+      <c r="G76" s="10" t="s">
         <v>309</v>
       </c>
       <c r="H76" s="2" t="s">
@@ -8792,9 +8795,9 @@
         <v>16</v>
       </c>
       <c r="F77" s="9">
-        <v>111210837018880</v>
-      </c>
-      <c r="G77" s="9" t="s">
+        <v>98351529529203</v>
+      </c>
+      <c r="G77" s="10" t="s">
         <v>311</v>
       </c>
       <c r="H77" s="2" t="s">
@@ -8819,9 +8822,9 @@
         <v>17</v>
       </c>
       <c r="F78" s="9">
-        <v>91454753076661</v>
-      </c>
-      <c r="G78" s="9" t="s">
+        <v>81048668172712</v>
+      </c>
+      <c r="G78" s="10" t="s">
         <v>313</v>
       </c>
       <c r="H78" s="2" t="s">
@@ -8846,9 +8849,9 @@
         <v>17</v>
       </c>
       <c r="F79" s="9">
-        <v>140372090697167</v>
-      </c>
-      <c r="G79" s="9" t="s">
+        <v>127615544859575</v>
+      </c>
+      <c r="G79" s="10" t="s">
         <v>315</v>
       </c>
       <c r="H79" s="2" t="s">
@@ -8873,9 +8876,9 @@
         <v>17</v>
       </c>
       <c r="F80" s="9">
-        <v>85844805634635</v>
-      </c>
-      <c r="G80" s="9" t="s">
+        <v>70656304136373</v>
+      </c>
+      <c r="G80" s="10" t="s">
         <v>317</v>
       </c>
       <c r="H80" s="2" t="s">
@@ -8900,9 +8903,9 @@
         <v>17</v>
       </c>
       <c r="F81" s="9">
-        <v>121461526979401</v>
-      </c>
-      <c r="G81" s="9" t="s">
+        <v>134424174805013</v>
+      </c>
+      <c r="G81" s="10" t="s">
         <v>319</v>
       </c>
       <c r="H81" s="2" t="s">
@@ -8927,9 +8930,9 @@
         <v>18</v>
       </c>
       <c r="F82" s="9">
-        <v>119745475735524</v>
-      </c>
-      <c r="G82" s="9" t="s">
+        <v>127255485663084</v>
+      </c>
+      <c r="G82" s="10" t="s">
         <v>321</v>
       </c>
       <c r="H82" s="2" t="s">
@@ -8954,9 +8957,9 @@
         <v>18</v>
       </c>
       <c r="F83" s="9">
-        <v>101894479505985</v>
-      </c>
-      <c r="G83" s="9" t="s">
+        <v>134027683373658</v>
+      </c>
+      <c r="G83" s="10" t="s">
         <v>323</v>
       </c>
       <c r="H83" s="2" t="s">
@@ -8981,9 +8984,9 @@
         <v>18</v>
       </c>
       <c r="F84" s="9">
-        <v>130984354600200</v>
-      </c>
-      <c r="G84" s="9" t="s">
+        <v>112447657334137</v>
+      </c>
+      <c r="G84" s="10" t="s">
         <v>325</v>
       </c>
       <c r="H84" s="2" t="s">
@@ -9008,9 +9011,9 @@
         <v>18</v>
       </c>
       <c r="F85" s="9">
-        <v>139575750428458</v>
-      </c>
-      <c r="G85" s="9" t="s">
+        <v>104595008892706</v>
+      </c>
+      <c r="G85" s="10" t="s">
         <v>327</v>
       </c>
       <c r="H85" s="2" t="s">
@@ -9035,9 +9038,9 @@
         <v>19</v>
       </c>
       <c r="F86" s="9">
-        <v>111543784097462</v>
-      </c>
-      <c r="G86" s="9" t="s">
+        <v>82759045606098</v>
+      </c>
+      <c r="G86" s="10" t="s">
         <v>329</v>
       </c>
       <c r="H86" s="2" t="s">
@@ -9062,9 +9065,9 @@
         <v>19</v>
       </c>
       <c r="F87" s="9">
-        <v>104244387773955</v>
-      </c>
-      <c r="G87" s="9" t="s">
+        <v>105620837789519</v>
+      </c>
+      <c r="G87" s="10" t="s">
         <v>331</v>
       </c>
       <c r="H87" s="2" t="s">
@@ -9089,9 +9092,9 @@
         <v>19</v>
       </c>
       <c r="F88" s="9">
-        <v>136776890462387</v>
-      </c>
-      <c r="G88" s="9" t="s">
+        <v>111024567754480</v>
+      </c>
+      <c r="G88" s="10" t="s">
         <v>333</v>
       </c>
       <c r="H88" s="2" t="s">
@@ -9116,9 +9119,9 @@
         <v>19</v>
       </c>
       <c r="F89" s="9">
-        <v>126165124926341</v>
-      </c>
-      <c r="G89" s="9" t="s">
+        <v>137153989969007</v>
+      </c>
+      <c r="G89" s="10" t="s">
         <v>335</v>
       </c>
       <c r="H89" s="2" t="s">
@@ -9143,9 +9146,9 @@
         <v>20</v>
       </c>
       <c r="F90" s="9">
-        <v>76143760243972</v>
-      </c>
-      <c r="G90" s="9" t="s">
+        <v>74496996195913</v>
+      </c>
+      <c r="G90" s="10" t="s">
         <v>337</v>
       </c>
       <c r="H90" s="2" t="s">
@@ -9170,9 +9173,9 @@
         <v>20</v>
       </c>
       <c r="F91" s="9">
-        <v>73975383470183</v>
-      </c>
-      <c r="G91" s="9" t="s">
+        <v>132785860315163</v>
+      </c>
+      <c r="G91" s="10" t="s">
         <v>339</v>
       </c>
       <c r="H91" s="2" t="s">
@@ -9197,9 +9200,9 @@
         <v>20</v>
       </c>
       <c r="F92" s="9">
-        <v>110779582383706</v>
-      </c>
-      <c r="G92" s="9" t="s">
+        <v>117198962948319</v>
+      </c>
+      <c r="G92" s="10" t="s">
         <v>341</v>
       </c>
       <c r="H92" s="2" t="s">
@@ -9224,9 +9227,9 @@
         <v>20</v>
       </c>
       <c r="F93" s="9">
-        <v>139231009266383</v>
-      </c>
-      <c r="G93" s="9" t="s">
+        <v>124449160476895</v>
+      </c>
+      <c r="G93" s="10" t="s">
         <v>343</v>
       </c>
       <c r="H93" s="2" t="s">
@@ -9251,9 +9254,9 @@
         <v>21</v>
       </c>
       <c r="F94" s="9">
-        <v>122330740858585</v>
-      </c>
-      <c r="G94" s="9" t="s">
+        <v>125887863438527</v>
+      </c>
+      <c r="G94" s="10" t="s">
         <v>345</v>
       </c>
       <c r="H94" s="2" t="s">
@@ -9278,9 +9281,9 @@
         <v>21</v>
       </c>
       <c r="F95" s="9">
-        <v>117103663687356</v>
-      </c>
-      <c r="G95" s="9" t="s">
+        <v>137692564728429</v>
+      </c>
+      <c r="G95" s="10" t="s">
         <v>347</v>
       </c>
       <c r="H95" s="2" t="s">
@@ -9305,9 +9308,9 @@
         <v>21</v>
       </c>
       <c r="F96" s="9">
-        <v>103139070075508</v>
-      </c>
-      <c r="G96" s="9" t="s">
+        <v>82350951870220</v>
+      </c>
+      <c r="G96" s="10" t="s">
         <v>349</v>
       </c>
       <c r="H96" s="2" t="s">
@@ -9332,9 +9335,9 @@
         <v>21</v>
       </c>
       <c r="F97" s="9">
-        <v>88725487654147</v>
-      </c>
-      <c r="G97" s="9" t="s">
+        <v>133019385929561</v>
+      </c>
+      <c r="G97" s="10" t="s">
         <v>351</v>
       </c>
       <c r="H97" s="2" t="s">
@@ -9359,9 +9362,9 @@
         <v>22</v>
       </c>
       <c r="F98" s="9">
-        <v>72100736251601</v>
-      </c>
-      <c r="G98" s="9" t="s">
+        <v>82714807302588</v>
+      </c>
+      <c r="G98" s="10" t="s">
         <v>353</v>
       </c>
       <c r="H98" s="2" t="s">
@@ -9386,9 +9389,9 @@
         <v>22</v>
       </c>
       <c r="F99" s="9">
-        <v>95625760850047</v>
-      </c>
-      <c r="G99" s="9" t="s">
+        <v>120409278538446</v>
+      </c>
+      <c r="G99" s="10" t="s">
         <v>355</v>
       </c>
       <c r="H99" s="2" t="s">
@@ -9413,9 +9416,9 @@
         <v>22</v>
       </c>
       <c r="F100" s="9">
-        <v>110809850119673</v>
-      </c>
-      <c r="G100" s="9" t="s">
+        <v>136303201068741</v>
+      </c>
+      <c r="G100" s="10" t="s">
         <v>357</v>
       </c>
       <c r="H100" s="2" t="s">
@@ -9440,9 +9443,9 @@
         <v>22</v>
       </c>
       <c r="F101" s="9">
-        <v>128268169997293</v>
-      </c>
-      <c r="G101" s="9" t="s">
+        <v>76724781858184</v>
+      </c>
+      <c r="G101" s="10" t="s">
         <v>359</v>
       </c>
       <c r="H101" s="2" t="s">
@@ -9467,9 +9470,9 @@
         <v>23</v>
       </c>
       <c r="F102" s="9">
-        <v>81568443921942</v>
-      </c>
-      <c r="G102" s="9" t="s">
+        <v>120125979830927</v>
+      </c>
+      <c r="G102" s="10" t="s">
         <v>361</v>
       </c>
       <c r="H102" s="2" t="s">
@@ -9494,9 +9497,9 @@
         <v>23</v>
       </c>
       <c r="F103" s="9">
-        <v>80275546299866</v>
-      </c>
-      <c r="G103" s="9" t="s">
+        <v>86921870572603</v>
+      </c>
+      <c r="G103" s="10" t="s">
         <v>363</v>
       </c>
       <c r="H103" s="2" t="s">
@@ -9521,9 +9524,9 @@
         <v>23</v>
       </c>
       <c r="F104" s="9">
-        <v>104304476590207</v>
-      </c>
-      <c r="G104" s="9" t="s">
+        <v>126355990231048</v>
+      </c>
+      <c r="G104" s="10" t="s">
         <v>365</v>
       </c>
       <c r="H104" s="2" t="s">
@@ -9548,9 +9551,9 @@
         <v>23</v>
       </c>
       <c r="F105" s="9">
-        <v>129658959682028</v>
-      </c>
-      <c r="G105" s="9" t="s">
+        <v>72326444062448</v>
+      </c>
+      <c r="G105" s="10" t="s">
         <v>367</v>
       </c>
       <c r="H105" s="2" t="s">
@@ -9575,9 +9578,9 @@
         <v>24</v>
       </c>
       <c r="F106" s="9">
-        <v>91807501817775</v>
-      </c>
-      <c r="G106" s="9" t="s">
+        <v>72257499044823</v>
+      </c>
+      <c r="G106" s="10" t="s">
         <v>369</v>
       </c>
       <c r="H106" s="2" t="s">
@@ -9602,9 +9605,9 @@
         <v>24</v>
       </c>
       <c r="F107" s="9">
-        <v>119033390105144</v>
-      </c>
-      <c r="G107" s="9" t="s">
+        <v>74695865349139</v>
+      </c>
+      <c r="G107" s="10" t="s">
         <v>371</v>
       </c>
       <c r="H107" s="2" t="s">
@@ -9628,9 +9631,9 @@
         <v>24</v>
       </c>
       <c r="F108" s="9">
-        <v>96459025721039</v>
-      </c>
-      <c r="G108" s="9" t="s">
+        <v>98358488442985</v>
+      </c>
+      <c r="G108" s="10" t="s">
         <v>373</v>
       </c>
       <c r="H108" s="2" t="s">
@@ -9655,9 +9658,9 @@
         <v>24</v>
       </c>
       <c r="F109" s="9">
-        <v>138981227536547</v>
-      </c>
-      <c r="G109" s="9" t="s">
+        <v>113636295509693</v>
+      </c>
+      <c r="G109" s="10" t="s">
         <v>375</v>
       </c>
       <c r="H109" s="2" t="s">
@@ -9682,9 +9685,9 @@
         <v>25</v>
       </c>
       <c r="F110" s="9">
-        <v>119423227657745</v>
-      </c>
-      <c r="G110" s="9" t="s">
+        <v>114047124407739</v>
+      </c>
+      <c r="G110" s="10" t="s">
         <v>377</v>
       </c>
       <c r="H110" s="2" t="s">
@@ -9709,9 +9712,9 @@
         <v>25</v>
       </c>
       <c r="F111" s="9">
-        <v>96126442221467</v>
-      </c>
-      <c r="G111" s="9" t="s">
+        <v>95771403493939</v>
+      </c>
+      <c r="G111" s="10" t="s">
         <v>379</v>
       </c>
       <c r="H111" s="2" t="s">
@@ -9736,9 +9739,9 @@
         <v>25</v>
       </c>
       <c r="F112" s="9">
-        <v>115960927208349</v>
-      </c>
-      <c r="G112" s="9" t="s">
+        <v>140393673870516</v>
+      </c>
+      <c r="G112" s="10" t="s">
         <v>381</v>
       </c>
       <c r="H112" s="2" t="s">
@@ -9763,9 +9766,9 @@
         <v>25</v>
       </c>
       <c r="F113" s="9">
-        <v>130983706534388</v>
-      </c>
-      <c r="G113" s="9" t="s">
+        <v>123109322631502</v>
+      </c>
+      <c r="G113" s="10" t="s">
         <v>383</v>
       </c>
       <c r="H113" s="2" t="s">
@@ -9790,9 +9793,9 @@
         <v>26</v>
       </c>
       <c r="F114" s="9">
-        <v>95831043321895</v>
-      </c>
-      <c r="G114" s="9" t="s">
+        <v>98614967981417</v>
+      </c>
+      <c r="G114" s="10" t="s">
         <v>385</v>
       </c>
       <c r="H114" s="2" t="s">
@@ -9817,9 +9820,9 @@
         <v>26</v>
       </c>
       <c r="F115" s="9">
-        <v>112143431254973</v>
-      </c>
-      <c r="G115" s="9" t="s">
+        <v>127369769981706</v>
+      </c>
+      <c r="G115" s="10" t="s">
         <v>387</v>
       </c>
       <c r="H115" s="2" t="s">
@@ -9844,9 +9847,9 @@
         <v>26</v>
       </c>
       <c r="F116" s="9">
-        <v>118258115873868</v>
-      </c>
-      <c r="G116" s="9" t="s">
+        <v>134574393827781</v>
+      </c>
+      <c r="G116" s="10" t="s">
         <v>389</v>
       </c>
       <c r="H116" s="2" t="s">
@@ -9871,9 +9874,9 @@
         <v>26</v>
       </c>
       <c r="F117" s="9">
-        <v>78313318872069</v>
-      </c>
-      <c r="G117" s="9" t="s">
+        <v>130258203281991</v>
+      </c>
+      <c r="G117" s="10" t="s">
         <v>391</v>
       </c>
       <c r="H117" s="2" t="s">
@@ -9898,9 +9901,9 @@
         <v>27</v>
       </c>
       <c r="F118" s="9">
-        <v>125592304728045</v>
-      </c>
-      <c r="G118" s="9" t="s">
+        <v>93953823085119</v>
+      </c>
+      <c r="G118" s="10" t="s">
         <v>393</v>
       </c>
       <c r="H118" s="2" t="s">
@@ -9925,9 +9928,9 @@
         <v>27</v>
       </c>
       <c r="F119" s="9">
-        <v>80137167951870</v>
-      </c>
-      <c r="G119" s="9" t="s">
+        <v>109802560542166</v>
+      </c>
+      <c r="G119" s="10" t="s">
         <v>395</v>
       </c>
       <c r="H119" s="2" t="s">
@@ -9952,9 +9955,9 @@
         <v>27</v>
       </c>
       <c r="F120" s="9">
-        <v>73282351047760</v>
-      </c>
-      <c r="G120" s="9" t="s">
+        <v>130989494782889</v>
+      </c>
+      <c r="G120" s="10" t="s">
         <v>397</v>
       </c>
       <c r="H120" s="2" t="s">
@@ -9979,9 +9982,9 @@
         <v>27</v>
       </c>
       <c r="F121" s="9">
-        <v>103255430368191</v>
-      </c>
-      <c r="G121" s="9" t="s">
+        <v>129408716253336</v>
+      </c>
+      <c r="G121" s="10" t="s">
         <v>399</v>
       </c>
       <c r="H121" s="2" t="s">
@@ -10006,9 +10009,9 @@
         <v>28</v>
       </c>
       <c r="F122" s="9">
-        <v>116294264954356</v>
-      </c>
-      <c r="G122" s="9" t="s">
+        <v>127772866805590</v>
+      </c>
+      <c r="G122" s="10" t="s">
         <v>401</v>
       </c>
       <c r="H122" s="2" t="s">
@@ -10033,9 +10036,9 @@
         <v>28</v>
       </c>
       <c r="F123" s="9">
-        <v>125743373452231</v>
-      </c>
-      <c r="G123" s="9" t="s">
+        <v>91938109188463</v>
+      </c>
+      <c r="G123" s="10" t="s">
         <v>403</v>
       </c>
       <c r="H123" s="2" t="s">
@@ -10060,9 +10063,9 @@
         <v>28</v>
       </c>
       <c r="F124" s="9">
-        <v>112421216883327</v>
-      </c>
-      <c r="G124" s="9" t="s">
+        <v>85077262752129</v>
+      </c>
+      <c r="G124" s="10" t="s">
         <v>405</v>
       </c>
       <c r="H124" s="2" t="s">
@@ -10077,7 +10080,7 @@
       <c r="B125" s="1">
         <v>122</v>
       </c>
-      <c r="C125" s="9" t="s">
+      <c r="C125" s="10" t="s">
         <v>406</v>
       </c>
       <c r="D125" s="1">
@@ -10087,9 +10090,9 @@
         <v>28</v>
       </c>
       <c r="F125" s="9">
-        <v>91269915478196</v>
-      </c>
-      <c r="G125" s="9" t="s">
+        <v>140335958193244</v>
+      </c>
+      <c r="G125" s="10" t="s">
         <v>407</v>
       </c>
       <c r="H125" s="2" t="s">
@@ -10103,7 +10106,7 @@
       <c r="B126" s="1">
         <v>123</v>
       </c>
-      <c r="C126" s="9" t="s">
+      <c r="C126" s="10" t="s">
         <v>408</v>
       </c>
       <c r="D126" s="1">
@@ -10113,9 +10116,9 @@
         <v>29</v>
       </c>
       <c r="F126" s="9">
-        <v>105465120437268</v>
-      </c>
-      <c r="G126" s="9" t="s">
+        <v>86732012145983</v>
+      </c>
+      <c r="G126" s="10" t="s">
         <v>409</v>
       </c>
       <c r="H126" s="2" t="s">
@@ -10129,7 +10132,7 @@
       <c r="B127" s="1">
         <v>124</v>
       </c>
-      <c r="C127" s="9" t="s">
+      <c r="C127" s="10" t="s">
         <v>410</v>
       </c>
       <c r="D127" s="1">
@@ -10139,9 +10142,9 @@
         <v>29</v>
       </c>
       <c r="F127" s="9">
-        <v>83111312306519</v>
-      </c>
-      <c r="G127" s="9" t="s">
+        <v>78044122276865</v>
+      </c>
+      <c r="G127" s="10" t="s">
         <v>411</v>
       </c>
       <c r="H127" s="2" t="s">
@@ -10155,7 +10158,7 @@
       <c r="B128" s="1">
         <v>125</v>
       </c>
-      <c r="C128" s="9" t="s">
+      <c r="C128" s="10" t="s">
         <v>412</v>
       </c>
       <c r="D128" s="1">
@@ -10165,9 +10168,9 @@
         <v>29</v>
       </c>
       <c r="F128" s="9">
-        <v>100761293408985</v>
-      </c>
-      <c r="G128" s="9" t="s">
+        <v>114974638199136</v>
+      </c>
+      <c r="G128" s="10" t="s">
         <v>413</v>
       </c>
       <c r="H128" s="2" t="s">
@@ -10181,7 +10184,7 @@
       <c r="B129" s="1">
         <v>126</v>
       </c>
-      <c r="C129" s="9" t="s">
+      <c r="C129" s="10" t="s">
         <v>414</v>
       </c>
       <c r="D129" s="1">
@@ -10191,9 +10194,9 @@
         <v>29</v>
       </c>
       <c r="F129" s="9">
-        <v>125949085124996</v>
-      </c>
-      <c r="G129" s="9" t="s">
+        <v>83652207307759</v>
+      </c>
+      <c r="G129" s="10" t="s">
         <v>415</v>
       </c>
       <c r="H129" s="2" t="s">
@@ -10207,7 +10210,7 @@
       <c r="B130" s="1">
         <v>127</v>
       </c>
-      <c r="C130" s="9" t="s">
+      <c r="C130" s="10" t="s">
         <v>416</v>
       </c>
       <c r="D130" s="1">
@@ -10217,9 +10220,9 @@
         <v>30</v>
       </c>
       <c r="F130" s="9">
-        <v>97905565242094</v>
-      </c>
-      <c r="G130" s="9" t="s">
+        <v>131787091355052</v>
+      </c>
+      <c r="G130" s="10" t="s">
         <v>417</v>
       </c>
       <c r="H130" s="2" t="s">
@@ -10233,7 +10236,7 @@
       <c r="B131" s="1">
         <v>128</v>
       </c>
-      <c r="C131" s="9" t="s">
+      <c r="C131" s="10" t="s">
         <v>418</v>
       </c>
       <c r="D131" s="1">
@@ -10243,9 +10246,9 @@
         <v>30</v>
       </c>
       <c r="F131" s="9">
-        <v>140476411551393</v>
-      </c>
-      <c r="G131" s="9" t="s">
+        <v>99348381699835</v>
+      </c>
+      <c r="G131" s="10" t="s">
         <v>419</v>
       </c>
       <c r="H131" s="2" t="s">
@@ -10259,7 +10262,7 @@
       <c r="B132" s="1">
         <v>129</v>
       </c>
-      <c r="C132" s="9" t="s">
+      <c r="C132" s="10" t="s">
         <v>420</v>
       </c>
       <c r="D132" s="1">
@@ -10269,9 +10272,9 @@
         <v>30</v>
       </c>
       <c r="F132" s="9">
-        <v>120018046835451</v>
-      </c>
-      <c r="G132" s="9" t="s">
+        <v>75412160560516</v>
+      </c>
+      <c r="G132" s="10" t="s">
         <v>421</v>
       </c>
       <c r="H132" s="2" t="s">
@@ -10285,7 +10288,7 @@
       <c r="B133" s="1">
         <v>130</v>
       </c>
-      <c r="C133" s="9" t="s">
+      <c r="C133" s="10" t="s">
         <v>422</v>
       </c>
       <c r="D133" s="1">
@@ -10295,9 +10298,9 @@
         <v>30</v>
       </c>
       <c r="F133" s="9">
-        <v>80251278207088</v>
-      </c>
-      <c r="G133" s="9" t="s">
+        <v>105475505052937</v>
+      </c>
+      <c r="G133" s="10" t="s">
         <v>423</v>
       </c>
       <c r="H133" s="2" t="s">
@@ -10311,7 +10314,7 @@
       <c r="B134" s="1">
         <v>131</v>
       </c>
-      <c r="C134" s="9" t="s">
+      <c r="C134" s="10" t="s">
         <v>424</v>
       </c>
       <c r="D134" s="1">
@@ -10321,9 +10324,9 @@
         <v>31</v>
       </c>
       <c r="F134" s="9">
-        <v>93241401911451</v>
-      </c>
-      <c r="G134" s="9" t="s">
+        <v>125484119033793</v>
+      </c>
+      <c r="G134" s="10" t="s">
         <v>425</v>
       </c>
       <c r="H134" s="2" t="s">
@@ -10337,7 +10340,7 @@
       <c r="B135" s="1">
         <v>132</v>
       </c>
-      <c r="C135" s="9" t="s">
+      <c r="C135" s="10" t="s">
         <v>426</v>
       </c>
       <c r="D135" s="1">
@@ -10347,9 +10350,9 @@
         <v>31</v>
       </c>
       <c r="F135" s="9">
-        <v>111428364476852</v>
-      </c>
-      <c r="G135" s="9" t="s">
+        <v>140608831780254</v>
+      </c>
+      <c r="G135" s="10" t="s">
         <v>427</v>
       </c>
       <c r="H135" s="2" t="s">
@@ -10363,7 +10366,7 @@
       <c r="B136" s="1">
         <v>133</v>
       </c>
-      <c r="C136" s="9" t="s">
+      <c r="C136" s="10" t="s">
         <v>428</v>
       </c>
       <c r="D136" s="1">
@@ -10373,9 +10376,9 @@
         <v>31</v>
       </c>
       <c r="F136" s="9">
-        <v>117739005088015</v>
-      </c>
-      <c r="G136" s="9" t="s">
+        <v>124177358025481</v>
+      </c>
+      <c r="G136" s="10" t="s">
         <v>429</v>
       </c>
       <c r="H136" s="2" t="s">
@@ -10389,7 +10392,7 @@
       <c r="B137" s="1">
         <v>134</v>
       </c>
-      <c r="C137" s="9" t="s">
+      <c r="C137" s="10" t="s">
         <v>430</v>
       </c>
       <c r="D137" s="1">
@@ -10399,9 +10402,9 @@
         <v>31</v>
       </c>
       <c r="F137" s="9">
-        <v>106059177546151</v>
-      </c>
-      <c r="G137" s="9" t="s">
+        <v>129385390119523</v>
+      </c>
+      <c r="G137" s="10" t="s">
         <v>431</v>
       </c>
       <c r="H137" s="2" t="s">
@@ -10415,7 +10418,7 @@
       <c r="B138" s="1">
         <v>135</v>
       </c>
-      <c r="C138" s="9" t="s">
+      <c r="C138" s="10" t="s">
         <v>432</v>
       </c>
       <c r="D138" s="1">
@@ -10425,9 +10428,9 @@
         <v>32</v>
       </c>
       <c r="F138" s="9">
-        <v>136795155731733</v>
-      </c>
-      <c r="G138" s="9" t="s">
+        <v>84940520003035</v>
+      </c>
+      <c r="G138" s="10" t="s">
         <v>433</v>
       </c>
       <c r="H138" s="2" t="s">
@@ -10441,7 +10444,7 @@
       <c r="B139" s="1">
         <v>136</v>
       </c>
-      <c r="C139" s="9" t="s">
+      <c r="C139" s="10" t="s">
         <v>434</v>
       </c>
       <c r="D139" s="1">
@@ -10451,9 +10454,9 @@
         <v>32</v>
       </c>
       <c r="F139" s="9">
-        <v>72644523405324</v>
-      </c>
-      <c r="G139" s="9" t="s">
+        <v>90031364711610</v>
+      </c>
+      <c r="G139" s="10" t="s">
         <v>435</v>
       </c>
       <c r="H139" s="2" t="s">
@@ -10467,7 +10470,7 @@
       <c r="B140" s="1">
         <v>137</v>
       </c>
-      <c r="C140" s="9" t="s">
+      <c r="C140" s="10" t="s">
         <v>436</v>
       </c>
       <c r="D140" s="1">
@@ -10477,9 +10480,9 @@
         <v>32</v>
       </c>
       <c r="F140" s="9">
-        <v>108937394146011</v>
-      </c>
-      <c r="G140" s="9" t="s">
+        <v>84418341821320</v>
+      </c>
+      <c r="G140" s="10" t="s">
         <v>437</v>
       </c>
       <c r="H140" s="2" t="s">
@@ -10493,7 +10496,7 @@
       <c r="B141" s="1">
         <v>138</v>
       </c>
-      <c r="C141" s="9" t="s">
+      <c r="C141" s="10" t="s">
         <v>438</v>
       </c>
       <c r="D141" s="1">
@@ -10503,9 +10506,9 @@
         <v>32</v>
       </c>
       <c r="F141" s="9">
-        <v>79433065873354</v>
-      </c>
-      <c r="G141" s="9" t="s">
+        <v>130255705800444</v>
+      </c>
+      <c r="G141" s="10" t="s">
         <v>439</v>
       </c>
       <c r="H141" s="2" t="s">
@@ -10519,7 +10522,7 @@
       <c r="B142" s="1">
         <v>139</v>
       </c>
-      <c r="C142" s="9" t="s">
+      <c r="C142" s="10" t="s">
         <v>440</v>
       </c>
       <c r="D142" s="1">
@@ -10529,9 +10532,9 @@
         <v>33</v>
       </c>
       <c r="F142" s="9">
-        <v>78433393917163</v>
-      </c>
-      <c r="G142" s="9" t="s">
+        <v>123568265278671</v>
+      </c>
+      <c r="G142" s="10" t="s">
         <v>441</v>
       </c>
       <c r="H142" s="2" t="s">
@@ -10545,7 +10548,7 @@
       <c r="B143" s="1">
         <v>140</v>
       </c>
-      <c r="C143" s="9" t="s">
+      <c r="C143" s="10" t="s">
         <v>442</v>
       </c>
       <c r="D143" s="1">
@@ -10555,9 +10558,9 @@
         <v>33</v>
       </c>
       <c r="F143" s="9">
-        <v>86723396142799</v>
-      </c>
-      <c r="G143" s="9" t="s">
+        <v>75689117044416</v>
+      </c>
+      <c r="G143" s="10" t="s">
         <v>443</v>
       </c>
       <c r="H143" s="2" t="s">
@@ -10571,7 +10574,7 @@
       <c r="B144" s="1">
         <v>141</v>
       </c>
-      <c r="C144" s="9" t="s">
+      <c r="C144" s="10" t="s">
         <v>444</v>
       </c>
       <c r="D144" s="1">
@@ -10581,9 +10584,9 @@
         <v>33</v>
       </c>
       <c r="F144" s="9">
-        <v>116389499163956</v>
-      </c>
-      <c r="G144" s="9" t="s">
+        <v>92309488435591</v>
+      </c>
+      <c r="G144" s="10" t="s">
         <v>445</v>
       </c>
       <c r="H144" s="2" t="s">
@@ -10597,7 +10600,7 @@
       <c r="B145" s="1">
         <v>142</v>
       </c>
-      <c r="C145" s="9" t="s">
+      <c r="C145" s="10" t="s">
         <v>446</v>
       </c>
       <c r="D145" s="1">
@@ -10607,9 +10610,9 @@
         <v>33</v>
       </c>
       <c r="F145" s="9">
-        <v>97264334614998</v>
-      </c>
-      <c r="G145" s="9" t="s">
+        <v>106319308889290</v>
+      </c>
+      <c r="G145" s="10" t="s">
         <v>447</v>
       </c>
       <c r="H145" s="2" t="s">
@@ -10623,7 +10626,7 @@
       <c r="B146" s="1">
         <v>143</v>
       </c>
-      <c r="C146" s="9" t="s">
+      <c r="C146" s="10" t="s">
         <v>448</v>
       </c>
       <c r="D146" s="1">
@@ -10633,9 +10636,9 @@
         <v>34</v>
       </c>
       <c r="F146" s="9">
-        <v>115791824258294</v>
-      </c>
-      <c r="G146" s="9" t="s">
+        <v>123120949699520</v>
+      </c>
+      <c r="G146" s="10" t="s">
         <v>449</v>
       </c>
       <c r="H146" s="2" t="s">
@@ -10649,7 +10652,7 @@
       <c r="B147" s="1">
         <v>144</v>
       </c>
-      <c r="C147" s="9" t="s">
+      <c r="C147" s="10" t="s">
         <v>450</v>
       </c>
       <c r="D147" s="1">
@@ -10659,9 +10662,9 @@
         <v>34</v>
       </c>
       <c r="F147" s="9">
-        <v>94398618924427</v>
-      </c>
-      <c r="G147" s="9" t="s">
+        <v>111674856010497</v>
+      </c>
+      <c r="G147" s="10" t="s">
         <v>451</v>
       </c>
       <c r="H147" s="2" t="s">
@@ -10675,7 +10678,7 @@
       <c r="B148" s="1">
         <v>145</v>
       </c>
-      <c r="C148" s="9" t="s">
+      <c r="C148" s="10" t="s">
         <v>452</v>
       </c>
       <c r="D148" s="1">
@@ -10685,9 +10688,9 @@
         <v>34</v>
       </c>
       <c r="F148" s="9">
-        <v>128273384481118</v>
-      </c>
-      <c r="G148" s="9" t="s">
+        <v>118080816505555</v>
+      </c>
+      <c r="G148" s="10" t="s">
         <v>453</v>
       </c>
       <c r="H148" s="2" t="s">
@@ -10701,7 +10704,7 @@
       <c r="B149" s="1">
         <v>146</v>
       </c>
-      <c r="C149" s="9" t="s">
+      <c r="C149" s="10" t="s">
         <v>454</v>
       </c>
       <c r="D149" s="1">
@@ -10711,9 +10714,9 @@
         <v>34</v>
       </c>
       <c r="F149" s="9">
-        <v>138000317292270</v>
-      </c>
-      <c r="G149" s="9" t="s">
+        <v>105021574817966</v>
+      </c>
+      <c r="G149" s="10" t="s">
         <v>455</v>
       </c>
       <c r="H149" s="2" t="s">
@@ -10727,7 +10730,7 @@
       <c r="B150" s="1">
         <v>147</v>
       </c>
-      <c r="C150" s="9" t="s">
+      <c r="C150" s="10" t="s">
         <v>456</v>
       </c>
       <c r="D150" s="1">
@@ -10737,9 +10740,9 @@
         <v>35</v>
       </c>
       <c r="F150" s="9">
-        <v>100641475547869</v>
-      </c>
-      <c r="G150" s="9" t="s">
+        <v>72690180103558</v>
+      </c>
+      <c r="G150" s="10" t="s">
         <v>457</v>
       </c>
       <c r="H150" s="2" t="s">
@@ -10753,7 +10756,7 @@
       <c r="B151" s="1">
         <v>148</v>
       </c>
-      <c r="C151" s="9" t="s">
+      <c r="C151" s="10" t="s">
         <v>458</v>
       </c>
       <c r="D151" s="1">
@@ -10763,9 +10766,9 @@
         <v>35</v>
       </c>
       <c r="F151" s="9">
-        <v>79371487434912</v>
-      </c>
-      <c r="G151" s="9" t="s">
+        <v>94914272618995</v>
+      </c>
+      <c r="G151" s="10" t="s">
         <v>459</v>
       </c>
       <c r="H151" s="2" t="s">
@@ -11155,10 +11158,10 @@
       <c r="C8" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="28" t="s">
         <v>480</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="28" t="s">
         <v>481</v>
       </c>
       <c r="F8" s="1"/>
@@ -11180,10 +11183,10 @@
       <c r="C9" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="28" t="s">
         <v>484</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="28" t="s">
         <v>485</v>
       </c>
       <c r="F9" s="1"/>
@@ -11205,10 +11208,10 @@
       <c r="C10" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="28" t="s">
         <v>488</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="28" t="s">
         <v>489</v>
       </c>
       <c r="F10" s="1"/>
@@ -11230,10 +11233,10 @@
       <c r="C11" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="28" t="s">
         <v>492</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="28" t="s">
         <v>493</v>
       </c>
       <c r="F11" s="1"/>
@@ -11255,10 +11258,10 @@
       <c r="C12" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="28" t="s">
         <v>496</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="28" t="s">
         <v>497</v>
       </c>
       <c r="F12" s="1"/>
@@ -11280,10 +11283,10 @@
       <c r="C13" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="28" t="s">
         <v>500</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="28" t="s">
         <v>501</v>
       </c>
       <c r="F13" s="1"/>
@@ -11305,10 +11308,10 @@
       <c r="C14" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="28" t="s">
         <v>504</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="28" t="s">
         <v>505</v>
       </c>
       <c r="F14" s="1"/>
@@ -11330,10 +11333,10 @@
       <c r="C15" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="28" t="s">
         <v>508</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="28" t="s">
         <v>509</v>
       </c>
       <c r="F15" s="1"/>
@@ -11355,10 +11358,10 @@
       <c r="C16" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="28" t="s">
         <v>512</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="28" t="s">
         <v>513</v>
       </c>
       <c r="F16" s="1"/>
@@ -11380,10 +11383,10 @@
       <c r="C17" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="28" t="s">
         <v>516</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="28" t="s">
         <v>517</v>
       </c>
       <c r="F17" s="1"/>
@@ -11405,10 +11408,10 @@
       <c r="C18" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="28" t="s">
         <v>520</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="28" t="s">
         <v>521</v>
       </c>
       <c r="F18" s="1"/>
@@ -11430,10 +11433,10 @@
       <c r="C19" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="28" t="s">
         <v>524</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="28" t="s">
         <v>525</v>
       </c>
       <c r="F19" s="1"/>
@@ -11455,10 +11458,10 @@
       <c r="C20" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="28" t="s">
         <v>528</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="28" t="s">
         <v>529</v>
       </c>
       <c r="F20" s="1"/>
@@ -11480,10 +11483,10 @@
       <c r="C21" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="28" t="s">
         <v>532</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="28" t="s">
         <v>533</v>
       </c>
       <c r="F21" s="1"/>
@@ -11505,10 +11508,10 @@
       <c r="C22" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="28" t="s">
         <v>536</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="28" t="s">
         <v>537</v>
       </c>
       <c r="F22" s="1"/>
@@ -11530,10 +11533,10 @@
       <c r="C23" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="28" t="s">
         <v>540</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="28" t="s">
         <v>541</v>
       </c>
       <c r="F23" s="1"/>
@@ -11691,7 +11694,7 @@
       <c r="C5" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="28" t="s">
         <v>548</v>
       </c>
       <c r="E5" s="1">
@@ -11718,7 +11721,7 @@
       <c r="C6" s="1" t="s">
         <v>550</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="28" t="s">
         <v>551</v>
       </c>
       <c r="E6" s="1">
@@ -11745,7 +11748,7 @@
       <c r="C7" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="28" t="s">
         <v>554</v>
       </c>
       <c r="E7" s="1">
@@ -11772,7 +11775,7 @@
       <c r="C8" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="28" t="s">
         <v>557</v>
       </c>
       <c r="E8" s="1">

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="5"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="703">
   <si>
     <t>子配置键</t>
   </si>
@@ -236,55 +236,19 @@
     <t>number_option</t>
   </si>
   <si>
-    <t>BlockModels.TrainingField1.Field4</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField1.Field3</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField1.Field2</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField1.Field1</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField1.Field0</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField2.Field4</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField2.Field3</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField2.Field2</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField2.Field1</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField3.Field4</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField3.Field3</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField3.Field2</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField3.Field1</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField4.Field4</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField4.Field3</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField4.Field2</t>
-  </si>
-  <si>
-    <t>BlockModels.TrainingField4.Field1</t>
+    <t>game.Workspace.BlockMeshs["世界1"].TrainingCenter.Training1</t>
+  </si>
+  <si>
+    <t>game.Workspace.BlockMeshs["世界1"].TrainingCenter.Training2</t>
+  </si>
+  <si>
+    <t>game.Workspace.BlockMeshs["世界1"].TrainingCenter.Training3</t>
+  </si>
+  <si>
+    <t>game.Workspace.BlockMeshs["世界1"].TrainingCenter.Training4</t>
+  </si>
+  <si>
+    <t>game.Workspace.BlockMeshs["世界1"].TrainingCenter.Training5</t>
   </si>
   <si>
     <t>组ID</t>
@@ -2864,7 +2828,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2890,9 +2854,6 @@
       <alignment horizontal="fill" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3283,62 +3244,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="22" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="26" customHeight="1" spans="1:6">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="22" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3355,7 +3316,7 @@
       <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="25" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
@@ -3375,7 +3336,7 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="26" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3392,7 +3353,7 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="25" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3409,7 +3370,7 @@
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="25" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
@@ -3429,7 +3390,7 @@
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="26" t="s">
         <v>21</v>
       </c>
       <c r="F8" t="s">
@@ -3449,7 +3410,7 @@
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="26" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
@@ -3469,7 +3430,7 @@
       <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="25" t="s">
         <v>25</v>
       </c>
       <c r="F10" t="s">
@@ -3505,13 +3466,13 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:5">
@@ -3519,10 +3480,10 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
@@ -3538,576 +3499,576 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
       <c r="B4" s="2">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="B5" s="2">
         <v>122</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="B6" s="2">
         <v>520</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="B7" s="2">
         <v>2176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="B8" s="2">
         <v>9101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>575</v>
+        <v>562</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>563</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>578</v>
+        <v>565</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>566</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>581</v>
+        <v>568</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>569</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>584</v>
+        <v>571</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>572</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>587</v>
+        <v>574</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>575</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>590</v>
+        <v>577</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>578</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>593</v>
+        <v>580</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>581</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>596</v>
+        <v>583</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>584</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>599</v>
+        <v>586</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>587</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>602</v>
+        <v>589</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>590</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>605</v>
+        <v>592</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>593</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>608</v>
+        <v>595</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>596</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>611</v>
+        <v>598</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>599</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="B22" s="29" t="s">
-        <v>614</v>
+        <v>601</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>602</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>617</v>
+        <v>604</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>605</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="B24" s="29" t="s">
-        <v>620</v>
+        <v>607</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>608</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="B25" s="29" t="s">
-        <v>623</v>
+        <v>610</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>611</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="B26" s="29" t="s">
-        <v>626</v>
+        <v>613</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>614</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>629</v>
+        <v>616</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>617</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="B28" s="29" t="s">
-        <v>632</v>
+        <v>619</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>620</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="B29" s="29" t="s">
-        <v>635</v>
+        <v>622</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>623</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="B30" s="29" t="s">
-        <v>638</v>
+        <v>625</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>626</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="B31" s="29" t="s">
-        <v>641</v>
+        <v>628</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>629</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="B32" s="29" t="s">
-        <v>644</v>
+        <v>631</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>632</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="B33" s="29" t="s">
-        <v>647</v>
+        <v>634</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>635</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="B34" s="29" t="s">
-        <v>650</v>
+        <v>637</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>638</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="B35" s="29" t="s">
-        <v>653</v>
+        <v>640</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>641</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="B36" s="29" t="s">
-        <v>656</v>
+        <v>643</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>644</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="B37" s="29" t="s">
-        <v>659</v>
+        <v>646</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>647</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="B38" s="29" t="s">
-        <v>662</v>
+        <v>649</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>650</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="B39" s="29" t="s">
-        <v>665</v>
+        <v>652</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>653</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="B40" s="29" t="s">
-        <v>668</v>
+        <v>655</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>656</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="B41" s="29" t="s">
-        <v>671</v>
+        <v>658</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>659</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="B42" s="29" t="s">
-        <v>674</v>
+        <v>661</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>662</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="B43" s="30" t="s">
-        <v>677</v>
+        <v>664</v>
+      </c>
+      <c r="B43" s="29" t="s">
+        <v>665</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="B44" s="30" t="s">
-        <v>680</v>
+        <v>667</v>
+      </c>
+      <c r="B44" s="29" t="s">
+        <v>668</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="B45" s="30" t="s">
-        <v>683</v>
+        <v>670</v>
+      </c>
+      <c r="B45" s="29" t="s">
+        <v>671</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="B46" s="30" t="s">
-        <v>686</v>
+        <v>673</v>
+      </c>
+      <c r="B46" s="29" t="s">
+        <v>674</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="B47" s="30" t="s">
-        <v>689</v>
+        <v>676</v>
+      </c>
+      <c r="B47" s="29" t="s">
+        <v>677</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="B48" s="30" t="s">
-        <v>692</v>
+        <v>679</v>
+      </c>
+      <c r="B48" s="29" t="s">
+        <v>680</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="B49" s="30" t="s">
-        <v>695</v>
+        <v>682</v>
+      </c>
+      <c r="B49" s="29" t="s">
+        <v>683</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="B50" s="30" t="s">
-        <v>698</v>
+        <v>685</v>
+      </c>
+      <c r="B50" s="29" t="s">
+        <v>686</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="B51" s="30" t="s">
-        <v>701</v>
+        <v>688</v>
+      </c>
+      <c r="B51" s="29" t="s">
+        <v>689</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="B52" s="30" t="s">
-        <v>704</v>
+        <v>691</v>
+      </c>
+      <c r="B52" s="29" t="s">
+        <v>692</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="B53" s="30" t="s">
-        <v>707</v>
+        <v>694</v>
+      </c>
+      <c r="B53" s="29" t="s">
+        <v>695</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B54" s="30" t="s">
-        <v>710</v>
+        <v>697</v>
+      </c>
+      <c r="B54" s="29" t="s">
+        <v>698</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="B55" s="30" t="s">
-        <v>713</v>
+        <v>700</v>
+      </c>
+      <c r="B55" s="29" t="s">
+        <v>701</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>
@@ -4122,389 +4083,389 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="44.175" style="17" customWidth="1"/>
-    <col min="2" max="2" width="71.3583333333333" style="17" customWidth="1"/>
-    <col min="3" max="3" width="123.558333333333" style="17" customWidth="1"/>
-    <col min="4" max="4" width="82.8666666666667" style="17" customWidth="1"/>
-    <col min="5" max="6" width="9" style="17"/>
-    <col min="7" max="7" width="81.1833333333333" style="17" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="17"/>
+    <col min="1" max="1" width="44.175" style="16" customWidth="1"/>
+    <col min="2" max="2" width="71.3583333333333" style="16" customWidth="1"/>
+    <col min="3" max="3" width="123.558333333333" style="16" customWidth="1"/>
+    <col min="4" max="4" width="82.8666666666667" style="16" customWidth="1"/>
+    <col min="5" max="6" width="9" style="16"/>
+    <col min="7" max="7" width="81.1833333333333" style="16" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" s="17" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
-      <c r="A1" s="18" t="s">
+    <row r="1" s="16" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
+      <c r="A1" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
-    <row r="2" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+    <row r="2" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
-    <row r="3" s="17" customFormat="1" ht="91" customHeight="1" spans="1:7">
-      <c r="A3" s="18" t="s">
+    <row r="3" s="16" customFormat="1" ht="91" customHeight="1" spans="1:7">
+      <c r="A3" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
-    <row r="4" s="17" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A4" s="18" t="s">
+    <row r="4" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
     </row>
-    <row r="5" s="17" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A5" s="18" t="s">
+    <row r="5" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A5" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="17">
         <v>10</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
     </row>
-    <row r="6" s="17" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A6" s="18" t="s">
+    <row r="6" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A6" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
     </row>
-    <row r="7" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A7" s="20" t="s">
+    <row r="7" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A7" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
     </row>
-    <row r="8" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A8" s="20" t="s">
+    <row r="8" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A8" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
     </row>
-    <row r="9" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A9" s="20" t="s">
+    <row r="9" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A9" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
     </row>
-    <row r="10" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A10" s="18" t="s">
+    <row r="10" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A10" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
     </row>
-    <row r="11" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A11" s="18" t="s">
+    <row r="11" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A11" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
     </row>
-    <row r="12" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A12" s="18" t="s">
+    <row r="12" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A12" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
     </row>
-    <row r="13" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
+    <row r="13" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
     </row>
-    <row r="14" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
+    <row r="14" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
     </row>
-    <row r="15" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
+    <row r="15" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
     </row>
-    <row r="16" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
+    <row r="16" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
     </row>
-    <row r="17" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
+    <row r="17" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
     </row>
-    <row r="18" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
+    <row r="18" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
     </row>
-    <row r="19" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
+    <row r="19" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
     </row>
-    <row r="20" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
+    <row r="20" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
     </row>
-    <row r="21" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
+    <row r="21" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
     </row>
-    <row r="22" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
+    <row r="22" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
     </row>
-    <row r="23" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
+    <row r="23" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
     </row>
-    <row r="24" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
+    <row r="24" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
     </row>
-    <row r="25" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
+    <row r="25" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
     </row>
-    <row r="26" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B26" s="18"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
+    <row r="26" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
     </row>
-    <row r="27" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="C27" s="18"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
+    <row r="27" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="C27" s="17"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
     </row>
-    <row r="28" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B28" s="18"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
+    <row r="28" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
     </row>
-    <row r="29" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
+    <row r="29" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
     </row>
-    <row r="30" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
+    <row r="30" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
     </row>
-    <row r="31" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
+    <row r="31" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
     </row>
-    <row r="32" s="17" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
+    <row r="32" s="16" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
     </row>
-    <row r="33" s="17" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
+    <row r="33" s="16" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
     </row>
-    <row r="34" s="17" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
+    <row r="34" s="16" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
     </row>
-    <row r="35" s="17" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B35" s="18"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
+    <row r="35" s="16" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
     </row>
-    <row r="36" s="17" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
+    <row r="36" s="16" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -4546,8 +4507,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12.3833333333333" style="2" customWidth="1"/>
     <col min="2" max="3" width="27.4333333333333" style="2" customWidth="1"/>
@@ -4680,182 +4641,6 @@
       </c>
       <c r="E8" s="1" t="s">
         <v>67</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A9" s="1">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1">
-        <v>15</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:5">
-      <c r="A10" s="1">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1">
-        <v>18</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:5">
-      <c r="A11" s="1">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
-        <v>35</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:5">
-      <c r="A12" s="1">
-        <v>9</v>
-      </c>
-      <c r="B12" s="1">
-        <v>24</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1">
-        <v>44</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:5">
-      <c r="A13" s="1">
-        <v>10</v>
-      </c>
-      <c r="B13" s="1">
-        <v>27</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1">
-        <v>54</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:5">
-      <c r="A14" s="1">
-        <v>11</v>
-      </c>
-      <c r="B14" s="1">
-        <v>30</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
-        <v>65</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:5">
-      <c r="A15" s="1">
-        <v>12</v>
-      </c>
-      <c r="B15" s="1">
-        <v>33</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1">
-        <v>76</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:5">
-      <c r="A16" s="1">
-        <v>13</v>
-      </c>
-      <c r="B16" s="1">
-        <v>36</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1">
-        <v>89</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:5">
-      <c r="A17" s="1">
-        <v>14</v>
-      </c>
-      <c r="B17" s="1">
-        <v>39</v>
-      </c>
-      <c r="D17" s="1">
-        <v>103</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" spans="1:5">
-      <c r="A18" s="1">
-        <v>15</v>
-      </c>
-      <c r="B18" s="1">
-        <v>42</v>
-      </c>
-      <c r="D18" s="1">
-        <v>117</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:5">
-      <c r="A19" s="1">
-        <v>16</v>
-      </c>
-      <c r="B19" s="1">
-        <v>45</v>
-      </c>
-      <c r="D19" s="1">
-        <v>132</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:5">
-      <c r="A20" s="1">
-        <v>17</v>
-      </c>
-      <c r="B20" s="1">
-        <v>48</v>
-      </c>
-      <c r="D20" s="1">
-        <v>149</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4870,944 +4655,944 @@
   <dimension ref="A1:E55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" width="37.75" style="15" customWidth="1"/>
+    <col min="1" max="2" width="37.75" style="14" customWidth="1"/>
     <col min="3" max="3" width="33.0833333333333" customWidth="1"/>
     <col min="4" max="5" width="40.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>83</v>
+      <c r="B1" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="16" t="s">
-        <v>87</v>
+      <c r="B2" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>88</v>
+      <c r="E3" s="15" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="16">
+      <c r="A4" s="15">
         <v>1</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="15">
         <v>1</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="15">
         <v>80</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <v>3</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>89</v>
+      <c r="E4" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>2</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="15">
         <v>2</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="15">
         <v>4</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>3</v>
       </c>
-      <c r="E5" s="16" t="s">
-        <v>89</v>
+      <c r="E5" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="16">
+      <c r="A6" s="15">
         <v>3</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="15">
         <v>3</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="15">
         <v>4</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="15">
         <v>3</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>89</v>
+      <c r="E6" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="16">
+      <c r="A7" s="15">
         <v>4</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="15">
         <v>4</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="15">
         <v>4</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="15">
         <v>3</v>
       </c>
-      <c r="E7" s="16" t="s">
-        <v>89</v>
+      <c r="E7" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="16">
+      <c r="A8" s="15">
         <v>5</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="15">
         <v>5</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="15">
         <v>4</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="15">
         <v>3</v>
       </c>
-      <c r="E8" s="16" t="s">
-        <v>89</v>
+      <c r="E8" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="16">
+      <c r="A9" s="15">
         <v>6</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="15">
         <v>6</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="15">
         <v>4</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="15">
         <v>3</v>
       </c>
-      <c r="E9" s="16" t="s">
-        <v>89</v>
+      <c r="E9" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="16">
+      <c r="A10" s="15">
         <v>7</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="15">
         <v>7</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="15">
         <v>4</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="15">
         <v>3</v>
       </c>
-      <c r="E10" s="16" t="s">
-        <v>89</v>
+      <c r="E10" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="16">
+      <c r="A11" s="15">
         <v>8</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="15">
         <v>8</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="15">
         <v>4</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="15">
         <v>3</v>
       </c>
-      <c r="E11" s="16" t="s">
-        <v>89</v>
+      <c r="E11" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="16">
+      <c r="A12" s="15">
         <v>9</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="15">
         <v>9</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="15">
         <v>4</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="15">
         <v>3</v>
       </c>
-      <c r="E12" s="16" t="s">
-        <v>89</v>
+      <c r="E12" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="16">
+      <c r="A13" s="15">
         <v>10</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="15">
         <v>10</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="15">
         <v>4</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="15">
         <v>3</v>
       </c>
-      <c r="E13" s="16" t="s">
-        <v>89</v>
+      <c r="E13" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="16">
+      <c r="A14" s="15">
         <v>11</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="15">
         <v>11</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="15">
         <v>4</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="15">
         <v>3</v>
       </c>
-      <c r="E14" s="16" t="s">
-        <v>89</v>
+      <c r="E14" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="16">
+      <c r="A15" s="15">
         <v>12</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="15">
         <v>12</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="15">
         <v>4</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="15">
         <v>3</v>
       </c>
-      <c r="E15" s="16" t="s">
-        <v>89</v>
+      <c r="E15" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="16">
+      <c r="A16" s="15">
         <v>13</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="15">
         <v>13</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="15">
         <v>4</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="15">
         <v>3</v>
       </c>
-      <c r="E16" s="16" t="s">
-        <v>89</v>
+      <c r="E16" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="16">
+      <c r="A17" s="15">
         <v>14</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="15">
         <v>14</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="15">
         <v>4</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="15">
         <v>3</v>
       </c>
-      <c r="E17" s="16" t="s">
-        <v>89</v>
+      <c r="E17" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="16">
+      <c r="A18" s="15">
         <v>15</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="15">
         <v>15</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="15">
         <v>4</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="15">
         <v>3</v>
       </c>
-      <c r="E18" s="16" t="s">
-        <v>89</v>
+      <c r="E18" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="16">
+      <c r="A19" s="15">
         <v>16</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="15">
         <v>16</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="15">
         <v>4</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="15">
         <v>3</v>
       </c>
-      <c r="E19" s="16" t="s">
-        <v>89</v>
+      <c r="E19" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="16">
+      <c r="A20" s="15">
         <v>17</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="15">
         <v>17</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="15">
         <v>4</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <v>3</v>
       </c>
-      <c r="E20" s="16" t="s">
-        <v>89</v>
+      <c r="E20" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="16">
+      <c r="A21" s="15">
         <v>18</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="15">
         <v>18</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="15">
         <v>4</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="15">
         <v>3</v>
       </c>
-      <c r="E21" s="16" t="s">
-        <v>89</v>
+      <c r="E21" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="16">
+      <c r="A22" s="15">
         <v>19</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="15">
         <v>19</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="15">
         <v>4</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="15">
         <v>3</v>
       </c>
-      <c r="E22" s="16" t="s">
-        <v>89</v>
+      <c r="E22" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="16">
+      <c r="A23" s="15">
         <v>20</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="15">
         <v>20</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="15">
         <v>4</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="15">
         <v>3</v>
       </c>
-      <c r="E23" s="16" t="s">
-        <v>89</v>
+      <c r="E23" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="16">
+      <c r="A24" s="15">
         <v>21</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="15">
         <v>21</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="15">
         <v>4</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="15">
         <v>3</v>
       </c>
-      <c r="E24" s="16" t="s">
-        <v>89</v>
+      <c r="E24" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="16">
+      <c r="A25" s="15">
         <v>22</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="15">
         <v>22</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="15">
         <v>4</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="15">
         <v>3</v>
       </c>
-      <c r="E25" s="16" t="s">
-        <v>89</v>
+      <c r="E25" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="16">
+      <c r="A26" s="15">
         <v>23</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="15">
         <v>23</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="15">
         <v>4</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="15">
         <v>3</v>
       </c>
-      <c r="E26" s="16" t="s">
-        <v>89</v>
+      <c r="E26" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="16">
+      <c r="A27" s="15">
         <v>24</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="15">
         <v>24</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="15">
         <v>4</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="15">
         <v>3</v>
       </c>
-      <c r="E27" s="16" t="s">
-        <v>89</v>
+      <c r="E27" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="16">
+      <c r="A28" s="15">
         <v>25</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="15">
         <v>25</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="15">
         <v>4</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="15">
         <v>3</v>
       </c>
-      <c r="E28" s="16" t="s">
-        <v>89</v>
+      <c r="E28" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="16">
+      <c r="A29" s="15">
         <v>26</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="15">
         <v>26</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="15">
         <v>4</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="15">
         <v>3</v>
       </c>
-      <c r="E29" s="16" t="s">
-        <v>89</v>
+      <c r="E29" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="16">
+      <c r="A30" s="15">
         <v>27</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="15">
         <v>27</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="15">
         <v>4</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="15">
         <v>3</v>
       </c>
-      <c r="E30" s="16" t="s">
-        <v>89</v>
+      <c r="E30" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="16">
+      <c r="A31" s="15">
         <v>28</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="15">
         <v>28</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="15">
         <v>4</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="15">
         <v>3</v>
       </c>
-      <c r="E31" s="16" t="s">
-        <v>89</v>
+      <c r="E31" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="16">
+      <c r="A32" s="15">
         <v>29</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="15">
         <v>29</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="15">
         <v>4</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="15">
         <v>3</v>
       </c>
-      <c r="E32" s="16" t="s">
-        <v>89</v>
+      <c r="E32" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="16">
+      <c r="A33" s="15">
         <v>30</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="15">
         <v>30</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="15">
         <v>4</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="15">
         <v>3</v>
       </c>
-      <c r="E33" s="16" t="s">
-        <v>89</v>
+      <c r="E33" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="16">
+      <c r="A34" s="15">
         <v>31</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="15">
         <v>31</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="15">
         <v>4</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="15">
         <v>3</v>
       </c>
-      <c r="E34" s="16" t="s">
-        <v>89</v>
+      <c r="E34" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="16">
+      <c r="A35" s="15">
         <v>32</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="15">
         <v>32</v>
       </c>
-      <c r="C35" s="16">
+      <c r="C35" s="15">
         <v>4</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D35" s="15">
         <v>3</v>
       </c>
-      <c r="E35" s="16" t="s">
-        <v>89</v>
+      <c r="E35" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="16">
+      <c r="A36" s="15">
         <v>33</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="15">
         <v>33</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="15">
         <v>4</v>
       </c>
-      <c r="D36" s="16">
+      <c r="D36" s="15">
         <v>3</v>
       </c>
-      <c r="E36" s="16" t="s">
-        <v>89</v>
+      <c r="E36" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="16">
+      <c r="A37" s="15">
         <v>34</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="15">
         <v>34</v>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="15">
         <v>4</v>
       </c>
-      <c r="D37" s="16">
+      <c r="D37" s="15">
         <v>3</v>
       </c>
-      <c r="E37" s="16" t="s">
-        <v>89</v>
+      <c r="E37" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="16">
+      <c r="A38" s="15">
         <v>35</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="15">
         <v>35</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="15">
         <v>4</v>
       </c>
-      <c r="D38" s="16">
+      <c r="D38" s="15">
         <v>3</v>
       </c>
-      <c r="E38" s="16" t="s">
-        <v>89</v>
+      <c r="E38" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="16">
+      <c r="A39" s="15">
         <v>36</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="15">
         <v>36</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="15">
         <v>4</v>
       </c>
-      <c r="D39" s="16">
+      <c r="D39" s="15">
         <v>3</v>
       </c>
-      <c r="E39" s="16" t="s">
-        <v>89</v>
+      <c r="E39" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="16">
+      <c r="A40" s="15">
         <v>37</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="15">
         <v>37</v>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="15">
         <v>4</v>
       </c>
-      <c r="D40" s="16">
+      <c r="D40" s="15">
         <v>3</v>
       </c>
-      <c r="E40" s="16" t="s">
-        <v>89</v>
+      <c r="E40" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="16">
+      <c r="A41" s="15">
         <v>38</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="15">
         <v>38</v>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="15">
         <v>4</v>
       </c>
-      <c r="D41" s="16">
+      <c r="D41" s="15">
         <v>3</v>
       </c>
-      <c r="E41" s="16" t="s">
-        <v>89</v>
+      <c r="E41" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="16">
+      <c r="A42" s="15">
         <v>39</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="15">
         <v>39</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="15">
         <v>4</v>
       </c>
-      <c r="D42" s="16">
+      <c r="D42" s="15">
         <v>3</v>
       </c>
-      <c r="E42" s="16" t="s">
-        <v>89</v>
+      <c r="E42" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="16">
+      <c r="A43" s="15">
         <v>40</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="15">
         <v>40</v>
       </c>
-      <c r="C43" s="16">
+      <c r="C43" s="15">
         <v>4</v>
       </c>
-      <c r="D43" s="16">
+      <c r="D43" s="15">
         <v>3</v>
       </c>
-      <c r="E43" s="16" t="s">
-        <v>89</v>
+      <c r="E43" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="16">
+      <c r="A44" s="15">
         <v>41</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="15">
         <v>41</v>
       </c>
-      <c r="C44" s="16">
+      <c r="C44" s="15">
         <v>4</v>
       </c>
-      <c r="D44" s="16">
+      <c r="D44" s="15">
         <v>3</v>
       </c>
-      <c r="E44" s="16" t="s">
-        <v>89</v>
+      <c r="E44" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="16">
+      <c r="A45" s="15">
         <v>42</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="15">
         <v>42</v>
       </c>
-      <c r="C45" s="16">
+      <c r="C45" s="15">
         <v>4</v>
       </c>
-      <c r="D45" s="16">
+      <c r="D45" s="15">
         <v>3</v>
       </c>
-      <c r="E45" s="16" t="s">
-        <v>89</v>
+      <c r="E45" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="16">
+      <c r="A46" s="15">
         <v>43</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="15">
         <v>43</v>
       </c>
-      <c r="C46" s="16">
+      <c r="C46" s="15">
         <v>4</v>
       </c>
-      <c r="D46" s="16">
+      <c r="D46" s="15">
         <v>3</v>
       </c>
-      <c r="E46" s="16" t="s">
-        <v>89</v>
+      <c r="E46" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="16">
+      <c r="A47" s="15">
         <v>44</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="15">
         <v>44</v>
       </c>
-      <c r="C47" s="16">
+      <c r="C47" s="15">
         <v>4</v>
       </c>
-      <c r="D47" s="16">
+      <c r="D47" s="15">
         <v>3</v>
       </c>
-      <c r="E47" s="16" t="s">
-        <v>89</v>
+      <c r="E47" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="16">
+      <c r="A48" s="15">
         <v>45</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="15">
         <v>45</v>
       </c>
-      <c r="C48" s="16">
+      <c r="C48" s="15">
         <v>4</v>
       </c>
-      <c r="D48" s="16">
+      <c r="D48" s="15">
         <v>3</v>
       </c>
-      <c r="E48" s="16" t="s">
-        <v>89</v>
+      <c r="E48" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="16">
+      <c r="A49" s="15">
         <v>46</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="15">
         <v>46</v>
       </c>
-      <c r="C49" s="16">
+      <c r="C49" s="15">
         <v>4</v>
       </c>
-      <c r="D49" s="16">
+      <c r="D49" s="15">
         <v>3</v>
       </c>
-      <c r="E49" s="16" t="s">
-        <v>89</v>
+      <c r="E49" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="16">
+      <c r="A50" s="15">
         <v>47</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="15">
         <v>47</v>
       </c>
-      <c r="C50" s="16">
+      <c r="C50" s="15">
         <v>4</v>
       </c>
-      <c r="D50" s="16">
+      <c r="D50" s="15">
         <v>3</v>
       </c>
-      <c r="E50" s="16" t="s">
-        <v>89</v>
+      <c r="E50" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="16">
+      <c r="A51" s="15">
         <v>48</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="15">
         <v>48</v>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="15">
         <v>4</v>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="15">
         <v>3</v>
       </c>
-      <c r="E51" s="16" t="s">
-        <v>89</v>
+      <c r="E51" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="16">
+      <c r="A52" s="15">
         <v>49</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="15">
         <v>49</v>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="15">
         <v>4</v>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="15">
         <v>3</v>
       </c>
-      <c r="E52" s="16" t="s">
-        <v>89</v>
+      <c r="E52" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="16">
+      <c r="A53" s="15">
         <v>50</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="15">
         <v>50</v>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="15">
         <v>4</v>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="15">
         <v>3</v>
       </c>
-      <c r="E53" s="16" t="s">
-        <v>89</v>
+      <c r="E53" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="16">
+      <c r="A54" s="15">
         <v>51</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="15">
         <v>51</v>
       </c>
-      <c r="C54" s="16">
+      <c r="C54" s="15">
         <v>4</v>
       </c>
-      <c r="D54" s="16">
+      <c r="D54" s="15">
         <v>3</v>
       </c>
-      <c r="E54" s="16" t="s">
-        <v>89</v>
+      <c r="E54" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="16">
+      <c r="A55" s="15">
         <v>52</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="15">
         <v>52</v>
       </c>
-      <c r="C55" s="16">
+      <c r="C55" s="15">
         <v>4</v>
       </c>
-      <c r="D55" s="16">
+      <c r="D55" s="15">
         <v>3</v>
       </c>
-      <c r="E55" s="16" t="s">
-        <v>89</v>
+      <c r="E55" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -5822,801 +5607,801 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="27.75" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="25.175" style="11" customWidth="1"/>
-    <col min="2" max="2" width="13.575" style="11" customWidth="1"/>
-    <col min="3" max="3" width="127.141666666667" style="11" customWidth="1"/>
-    <col min="4" max="4" width="49" style="11" customWidth="1"/>
-    <col min="5" max="5" width="92.9666666666667" style="12" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="11"/>
+    <col min="1" max="1" width="25.175" style="10" customWidth="1"/>
+    <col min="2" max="2" width="13.575" style="10" customWidth="1"/>
+    <col min="3" max="3" width="127.141666666667" style="10" customWidth="1"/>
+    <col min="4" max="4" width="49" style="10" customWidth="1"/>
+    <col min="5" max="5" width="92.9666666666667" style="11" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E1" s="12" t="s">
+      <c r="B1" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>93</v>
+      <c r="B2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="C3" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>1</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="12">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>96</v>
+      <c r="C4" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="13">
+      <c r="A5" s="12">
         <v>2</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="12">
         <v>2</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>96</v>
+      <c r="C5" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="13">
+      <c r="A6" s="12">
         <v>3</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="12">
         <v>3</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>96</v>
+      <c r="C6" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="13">
+      <c r="A7" s="12">
         <v>4</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="12">
         <v>4</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>96</v>
+      <c r="C7" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="13">
+      <c r="A8" s="12">
         <v>5</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="12">
         <v>5</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>96</v>
+      <c r="C8" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="13">
+      <c r="A9" s="12">
         <v>6</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <v>6</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>96</v>
+      <c r="C9" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="13">
+      <c r="A10" s="12">
         <v>7</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="12">
         <v>7</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>96</v>
+      <c r="C10" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="13">
+      <c r="A11" s="12">
         <v>8</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="12">
         <v>8</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>96</v>
+      <c r="C11" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="13">
+      <c r="A12" s="12">
         <v>9</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="12">
         <v>9</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>96</v>
+      <c r="C12" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="13">
+      <c r="A13" s="12">
         <v>10</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <v>10</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>96</v>
+      <c r="C13" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="13">
+      <c r="A14" s="12">
         <v>11</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="12">
         <v>11</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>96</v>
+      <c r="C14" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="13">
+      <c r="A15" s="12">
         <v>12</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="12">
         <v>12</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>96</v>
+      <c r="C15" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="13">
+      <c r="A16" s="12">
         <v>13</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="12">
         <v>13</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" s="13" t="s">
+      <c r="C16" s="13" t="s">
         <v>96</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="13">
+      <c r="A17" s="12">
         <v>14</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="12">
         <v>14</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>96</v>
+      <c r="C17" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="13">
+      <c r="A18" s="12">
         <v>15</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="12">
         <v>15</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>96</v>
+      <c r="C18" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="13">
+      <c r="A19" s="12">
         <v>16</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="12">
         <v>16</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>96</v>
+      <c r="C19" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="13">
+      <c r="A20" s="12">
         <v>17</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="12">
         <v>17</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>96</v>
+      <c r="C20" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="13">
+      <c r="A21" s="12">
         <v>18</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="12">
         <v>18</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>96</v>
+      <c r="C21" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="13">
+      <c r="A22" s="12">
         <v>19</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="12">
         <v>19</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>96</v>
+      <c r="C22" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="13">
+      <c r="A23" s="12">
         <v>20</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="12">
         <v>20</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>96</v>
+      <c r="C23" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="13">
+      <c r="A24" s="12">
         <v>21</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="12">
         <v>21</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>96</v>
+      <c r="C24" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="13">
+      <c r="A25" s="12">
         <v>22</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="12">
         <v>22</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>96</v>
+      <c r="C25" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="13">
+      <c r="A26" s="12">
         <v>23</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="12">
         <v>23</v>
       </c>
-      <c r="C26" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>96</v>
+      <c r="C26" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="13">
+      <c r="A27" s="12">
         <v>24</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="12">
         <v>24</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>96</v>
+      <c r="C27" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="13">
+      <c r="A28" s="12">
         <v>25</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="12">
         <v>25</v>
       </c>
-      <c r="C28" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>96</v>
+      <c r="C28" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="13">
+      <c r="A29" s="12">
         <v>26</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="12">
         <v>26</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>96</v>
+      <c r="C29" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="13">
+      <c r="A30" s="12">
         <v>27</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="12">
         <v>27</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>96</v>
+      <c r="C30" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="13">
+      <c r="A31" s="12">
         <v>28</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="12">
         <v>28</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>96</v>
+      <c r="C31" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="13">
+      <c r="A32" s="12">
         <v>29</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="12">
         <v>29</v>
       </c>
-      <c r="C32" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>96</v>
+      <c r="C32" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="13">
+      <c r="A33" s="12">
         <v>30</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="12">
         <v>30</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>96</v>
+      <c r="C33" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="13">
+      <c r="A34" s="12">
         <v>31</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="12">
         <v>31</v>
       </c>
-      <c r="C34" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>96</v>
+      <c r="C34" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="13">
+      <c r="A35" s="12">
         <v>32</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="12">
         <v>32</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>96</v>
+      <c r="C35" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="13">
+      <c r="A36" s="12">
         <v>33</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="12">
         <v>33</v>
       </c>
-      <c r="C36" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>96</v>
+      <c r="C36" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="13">
+      <c r="A37" s="12">
         <v>34</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="12">
         <v>34</v>
       </c>
-      <c r="C37" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>96</v>
+      <c r="C37" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="13">
+      <c r="A38" s="12">
         <v>35</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="12">
         <v>35</v>
       </c>
-      <c r="C38" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>96</v>
+      <c r="C38" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="13">
+      <c r="A39" s="12">
         <v>36</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="12">
         <v>36</v>
       </c>
-      <c r="C39" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>96</v>
+      <c r="C39" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="13">
+      <c r="A40" s="12">
         <v>37</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="12">
         <v>37</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="D40" s="13" t="s">
-        <v>96</v>
+      <c r="C40" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="13">
+      <c r="A41" s="12">
         <v>38</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="12">
         <v>38</v>
       </c>
-      <c r="C41" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>96</v>
+      <c r="C41" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="13">
+      <c r="A42" s="12">
         <v>39</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="12">
         <v>39</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>96</v>
+      <c r="C42" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="14">
+      <c r="A43" s="13">
         <v>40</v>
       </c>
-      <c r="B43" s="14">
+      <c r="B43" s="13">
         <v>40</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>96</v>
+      <c r="C43" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="14">
+      <c r="A44" s="13">
         <v>41</v>
       </c>
-      <c r="B44" s="14">
+      <c r="B44" s="13">
         <v>41</v>
       </c>
-      <c r="C44" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>96</v>
+      <c r="C44" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="14">
+      <c r="A45" s="13">
         <v>42</v>
       </c>
-      <c r="B45" s="14">
+      <c r="B45" s="13">
         <v>42</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>96</v>
+      <c r="C45" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="14">
+      <c r="A46" s="13">
         <v>43</v>
       </c>
-      <c r="B46" s="14">
+      <c r="B46" s="13">
         <v>43</v>
       </c>
-      <c r="C46" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>96</v>
+      <c r="C46" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="14">
+      <c r="A47" s="13">
         <v>44</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="13">
         <v>44</v>
       </c>
-      <c r="C47" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>96</v>
+      <c r="C47" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="14">
+      <c r="A48" s="13">
         <v>45</v>
       </c>
-      <c r="B48" s="14">
+      <c r="B48" s="13">
         <v>45</v>
       </c>
-      <c r="C48" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>96</v>
+      <c r="C48" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="14">
+      <c r="A49" s="13">
         <v>46</v>
       </c>
-      <c r="B49" s="14">
+      <c r="B49" s="13">
         <v>46</v>
       </c>
-      <c r="C49" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>96</v>
+      <c r="C49" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="14">
+      <c r="A50" s="13">
         <v>47</v>
       </c>
-      <c r="B50" s="14">
+      <c r="B50" s="13">
         <v>47</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>96</v>
+      <c r="C50" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="14">
+      <c r="A51" s="13">
         <v>48</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="13">
         <v>48</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>96</v>
+      <c r="C51" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="14">
+      <c r="A52" s="13">
         <v>49</v>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="13">
         <v>49</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>96</v>
+      <c r="C52" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="14">
+      <c r="A53" s="13">
         <v>50</v>
       </c>
-      <c r="B53" s="14">
+      <c r="B53" s="13">
         <v>50</v>
       </c>
-      <c r="C53" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>96</v>
+      <c r="C53" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="14">
+      <c r="A54" s="13">
         <v>51</v>
       </c>
-      <c r="B54" s="14">
+      <c r="B54" s="13">
         <v>51</v>
       </c>
-      <c r="C54" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>96</v>
+      <c r="C54" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="14">
+      <c r="A55" s="13">
         <v>52</v>
       </c>
-      <c r="B55" s="14">
+      <c r="B55" s="13">
         <v>52</v>
       </c>
-      <c r="C55" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>96</v>
+      <c r="C55" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
+      <c r="A56" s="13"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="14"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="C58" s="14"/>
+      <c r="C58" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6644,25 +6429,25 @@
         <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:12">
@@ -6670,25 +6455,25 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:12">
@@ -6711,7 +6496,7 @@
         <v>7</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>7</v>
@@ -6725,7 +6510,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -6734,14 +6519,14 @@
         <f>CEILING(A4/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="6">
         <v>113244405937302</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>164</v>
+      <c r="G4" s="9" t="s">
+        <v>152</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:12">
@@ -6752,7 +6537,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -6761,14 +6546,14 @@
         <f t="shared" ref="E5:E36" si="0">CEILING(A5/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="6">
         <v>105711056874756</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>167</v>
+      <c r="G5" s="9" t="s">
+        <v>155</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -6781,7 +6566,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="D6" s="1">
         <v>6</v>
@@ -6790,14 +6575,14 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="6">
         <v>82693303214454</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>169</v>
+      <c r="G6" s="9" t="s">
+        <v>157</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -6810,7 +6595,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="D7" s="1">
         <v>8</v>
@@ -6819,14 +6604,14 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="6">
         <v>102504658102706</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>171</v>
+      <c r="G7" s="9" t="s">
+        <v>159</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -6839,7 +6624,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="D8" s="1">
         <v>13</v>
@@ -6848,14 +6633,14 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="6">
         <v>83069096807916</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>173</v>
+      <c r="G8" s="9" t="s">
+        <v>161</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:12">
@@ -6866,7 +6651,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D9" s="1">
         <v>20</v>
@@ -6875,14 +6660,14 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="6">
         <v>80534536398974</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>175</v>
+      <c r="G9" s="9" t="s">
+        <v>163</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I9" s="3"/>
     </row>
@@ -6894,7 +6679,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D10" s="1">
         <v>30</v>
@@ -6903,14 +6688,14 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="6">
         <v>74246671448525</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>177</v>
+      <c r="G10" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I10" s="3"/>
     </row>
@@ -6922,7 +6707,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D11" s="1">
         <v>38</v>
@@ -6931,14 +6716,14 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="6">
         <v>71499702430100</v>
       </c>
-      <c r="G11" s="10" t="s">
-        <v>179</v>
+      <c r="G11" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I11" s="3"/>
     </row>
@@ -6950,7 +6735,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D12" s="1">
         <v>63</v>
@@ -6959,14 +6744,14 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="6">
         <v>122909083001205</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>181</v>
+      <c r="G12" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -6977,7 +6762,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
@@ -6986,14 +6771,14 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="6">
         <v>128658267266293</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>183</v>
+      <c r="G13" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7004,7 +6789,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="D14" s="1">
         <v>150</v>
@@ -7013,14 +6798,14 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="6">
         <v>134748387119946</v>
       </c>
-      <c r="G14" s="10" t="s">
-        <v>185</v>
+      <c r="G14" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7031,7 +6816,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D15" s="1">
         <v>188</v>
@@ -7040,14 +6825,14 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="6">
         <v>131559815185521</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>187</v>
+      <c r="G15" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:12">
@@ -7058,7 +6843,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D16" s="1">
         <v>313</v>
@@ -7067,14 +6852,14 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="6">
         <v>135406755438948</v>
       </c>
-      <c r="G16" s="10" t="s">
-        <v>189</v>
+      <c r="G16" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -7089,7 +6874,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D17" s="1">
         <v>500</v>
@@ -7098,14 +6883,14 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="6">
         <v>128433990441931</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>191</v>
+      <c r="G17" s="9" t="s">
+        <v>179</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -7120,7 +6905,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="D18" s="1">
         <v>750</v>
@@ -7129,14 +6914,14 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="6">
         <v>86357992624263</v>
       </c>
-      <c r="G18" s="10" t="s">
-        <v>193</v>
+      <c r="G18" s="9" t="s">
+        <v>181</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
@@ -7151,7 +6936,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D19" s="1">
         <v>938</v>
@@ -7160,14 +6945,14 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="6">
         <v>96128137486525</v>
       </c>
-      <c r="G19" s="10" t="s">
-        <v>195</v>
+      <c r="G19" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -7182,7 +6967,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="D20" s="1">
         <v>1563</v>
@@ -7191,14 +6976,14 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="6">
         <v>131913492630514</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>197</v>
+      <c r="G20" s="9" t="s">
+        <v>185</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -7213,7 +6998,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="D21" s="1">
         <v>2500</v>
@@ -7222,14 +7007,14 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="6">
         <v>119579899338192</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>199</v>
+      <c r="G21" s="9" t="s">
+        <v>187</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -7244,7 +7029,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="D22" s="1">
         <v>3750</v>
@@ -7253,14 +7038,14 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="6">
         <v>82472089572732</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>201</v>
+      <c r="G22" s="9" t="s">
+        <v>189</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -7275,7 +7060,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D23" s="1">
         <v>4688</v>
@@ -7284,14 +7069,14 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="6">
         <v>104108852156434</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>203</v>
+      <c r="G23" s="9" t="s">
+        <v>191</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -7306,7 +7091,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="D24" s="1">
         <v>7800</v>
@@ -7315,14 +7100,14 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="6">
         <v>79005623120233</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>205</v>
+      <c r="G24" s="9" t="s">
+        <v>193</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -7337,7 +7122,7 @@
         <v>22</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D25" s="1">
         <v>12480</v>
@@ -7346,14 +7131,14 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="6">
         <v>97611938478078</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>207</v>
+      <c r="G25" s="9" t="s">
+        <v>195</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -7368,7 +7153,7 @@
         <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="D26" s="1">
         <v>18720</v>
@@ -7377,14 +7162,14 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="6">
         <v>81806655827798</v>
       </c>
-      <c r="G26" s="10" t="s">
-        <v>209</v>
+      <c r="G26" s="9" t="s">
+        <v>197</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
@@ -7399,7 +7184,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D27" s="1">
         <v>23400</v>
@@ -7408,14 +7193,14 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="6">
         <v>105716218867716</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>211</v>
+      <c r="G27" s="9" t="s">
+        <v>199</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
@@ -7430,7 +7215,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="D28" s="1">
         <v>39050</v>
@@ -7439,14 +7224,14 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="6">
         <v>128411546772202</v>
       </c>
-      <c r="G28" s="10" t="s">
-        <v>213</v>
+      <c r="G28" s="9" t="s">
+        <v>201</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -7461,7 +7246,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D29" s="1">
         <v>62480</v>
@@ -7470,14 +7255,14 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="6">
         <v>139465058617680</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>215</v>
+      <c r="G29" s="9" t="s">
+        <v>203</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -7492,7 +7277,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="D30" s="1">
         <v>93720</v>
@@ -7501,14 +7286,14 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="6">
         <v>81737011057690</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>217</v>
+      <c r="G30" s="9" t="s">
+        <v>205</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -7523,7 +7308,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D31" s="1">
         <v>117150</v>
@@ -7532,14 +7317,14 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="6">
         <v>81445862907930</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>219</v>
+      <c r="G31" s="9" t="s">
+        <v>207</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -7554,7 +7339,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D32" s="1">
         <v>195500</v>
@@ -7563,14 +7348,14 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="6">
         <v>123098432383687</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>221</v>
+      <c r="G32" s="9" t="s">
+        <v>209</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -7585,7 +7370,7 @@
         <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="D33" s="1">
         <v>312800</v>
@@ -7594,14 +7379,14 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="6">
         <v>131796260838154</v>
       </c>
-      <c r="G33" s="10" t="s">
-        <v>223</v>
+      <c r="G33" s="9" t="s">
+        <v>211</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7612,7 +7397,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="D34" s="1">
         <v>469200</v>
@@ -7621,14 +7406,14 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="6">
         <v>116376878683736</v>
       </c>
-      <c r="G34" s="10" t="s">
-        <v>225</v>
+      <c r="G34" s="9" t="s">
+        <v>213</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7639,7 +7424,7 @@
         <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="D35" s="1">
         <v>586500</v>
@@ -7648,14 +7433,14 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="6">
         <v>100558097057142</v>
       </c>
-      <c r="G35" s="10" t="s">
-        <v>227</v>
+      <c r="G35" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:12">
@@ -7666,7 +7451,7 @@
         <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="D36" s="1">
         <v>975000</v>
@@ -7675,14 +7460,14 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="6">
         <v>92332707761527</v>
       </c>
-      <c r="G36" s="10" t="s">
-        <v>229</v>
+      <c r="G36" s="9" t="s">
+        <v>217</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -7697,7 +7482,7 @@
         <v>34</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="D37" s="1">
         <v>1560000</v>
@@ -7706,14 +7491,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>6</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="6">
         <v>108895787734224</v>
       </c>
-      <c r="G37" s="10" t="s">
-        <v>231</v>
+      <c r="G37" s="9" t="s">
+        <v>219</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7724,7 +7509,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D38" s="1">
         <v>2340000</v>
@@ -7733,14 +7518,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>7</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="6">
         <v>95471681056681</v>
       </c>
-      <c r="G38" s="10" t="s">
-        <v>233</v>
+      <c r="G38" s="9" t="s">
+        <v>221</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:12">
@@ -7751,7 +7536,7 @@
         <v>36</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D39" s="1">
         <v>2925000</v>
@@ -7760,14 +7545,14 @@
         <f t="shared" ref="E39:E72" si="1">CEILING(A39/4,1)</f>
         <v>9</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="6">
         <v>104955598295323</v>
       </c>
-      <c r="G39" s="10" t="s">
-        <v>235</v>
+      <c r="G39" s="9" t="s">
+        <v>223</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
@@ -7782,7 +7567,7 @@
         <v>37</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="D40" s="1">
         <v>4885000</v>
@@ -7791,14 +7576,14 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="6">
         <v>103175883366340</v>
       </c>
-      <c r="G40" s="10" t="s">
-        <v>237</v>
+      <c r="G40" s="9" t="s">
+        <v>225</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
@@ -7813,7 +7598,7 @@
         <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="D41" s="1">
         <v>7816000</v>
@@ -7822,14 +7607,14 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="6">
         <v>114247164745798</v>
       </c>
-      <c r="G41" s="10" t="s">
-        <v>239</v>
+      <c r="G41" s="9" t="s">
+        <v>227</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7840,7 +7625,7 @@
         <v>39</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D42" s="1">
         <v>11724000</v>
@@ -7849,14 +7634,14 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="6">
         <v>86017047390182</v>
       </c>
-      <c r="G42" s="10" t="s">
-        <v>241</v>
+      <c r="G42" s="9" t="s">
+        <v>229</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7867,7 +7652,7 @@
         <v>40</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="D43" s="1">
         <v>14655000</v>
@@ -7876,14 +7661,14 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="6">
         <v>81373582816266</v>
       </c>
-      <c r="G43" s="10" t="s">
-        <v>243</v>
+      <c r="G43" s="9" t="s">
+        <v>231</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7894,7 +7679,7 @@
         <v>41</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="D44" s="1">
         <v>24400000</v>
@@ -7903,14 +7688,14 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="6">
         <v>132788281080826</v>
       </c>
-      <c r="G44" s="10" t="s">
-        <v>245</v>
+      <c r="G44" s="9" t="s">
+        <v>233</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7921,7 +7706,7 @@
         <v>42</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D45" s="1">
         <v>39040000</v>
@@ -7930,14 +7715,14 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="6">
         <v>95162444285252</v>
       </c>
-      <c r="G45" s="10" t="s">
-        <v>247</v>
+      <c r="G45" s="9" t="s">
+        <v>235</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7948,7 +7733,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D46" s="1">
         <v>58560000</v>
@@ -7957,14 +7742,14 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="6">
         <v>95953438126479</v>
       </c>
-      <c r="G46" s="10" t="s">
-        <v>249</v>
+      <c r="G46" s="9" t="s">
+        <v>237</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7975,7 +7760,7 @@
         <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D47" s="1">
         <v>73200000</v>
@@ -7984,14 +7769,14 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="6">
         <v>112039222887887</v>
       </c>
-      <c r="G47" s="10" t="s">
-        <v>251</v>
+      <c r="G47" s="9" t="s">
+        <v>239</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -8002,7 +7787,7 @@
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D48" s="1">
         <v>122000000</v>
@@ -8011,14 +7796,14 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="6">
         <v>95377459606647</v>
       </c>
-      <c r="G48" s="10" t="s">
-        <v>253</v>
+      <c r="G48" s="9" t="s">
+        <v>241</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8029,7 +7814,7 @@
         <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="D49" s="1">
         <v>195200000</v>
@@ -8038,14 +7823,14 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F49" s="6">
         <v>113983796605688</v>
       </c>
-      <c r="G49" s="10" t="s">
-        <v>255</v>
+      <c r="G49" s="9" t="s">
+        <v>243</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8056,7 +7841,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="D50" s="1">
         <v>292800000</v>
@@ -8065,14 +7850,14 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="6">
         <v>117157716541352</v>
       </c>
-      <c r="G50" s="10" t="s">
-        <v>257</v>
+      <c r="G50" s="9" t="s">
+        <v>245</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="51" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8083,7 +7868,7 @@
         <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="D51" s="1">
         <v>366000000</v>
@@ -8092,14 +7877,14 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F51" s="6">
         <v>100893051807474</v>
       </c>
-      <c r="G51" s="10" t="s">
-        <v>259</v>
+      <c r="G51" s="9" t="s">
+        <v>247</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8110,7 +7895,7 @@
         <v>49</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D52" s="1">
         <v>610000000</v>
@@ -8119,14 +7904,14 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="6">
         <v>137999782231090</v>
       </c>
-      <c r="G52" s="10" t="s">
-        <v>261</v>
+      <c r="G52" s="9" t="s">
+        <v>249</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8137,7 +7922,7 @@
         <v>50</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D53" s="1">
         <v>976000000</v>
@@ -8146,14 +7931,14 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="6">
         <v>127007149281218</v>
       </c>
-      <c r="G53" s="10" t="s">
-        <v>263</v>
+      <c r="G53" s="9" t="s">
+        <v>251</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8164,7 +7949,7 @@
         <v>51</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D54" s="1">
         <v>1464000000</v>
@@ -8173,14 +7958,14 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F54" s="9">
+      <c r="F54" s="6">
         <v>85273469740405</v>
       </c>
-      <c r="G54" s="10" t="s">
-        <v>265</v>
+      <c r="G54" s="9" t="s">
+        <v>253</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8191,7 +7976,7 @@
         <v>52</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="D55" s="1">
         <v>1830000000</v>
@@ -8200,14 +7985,14 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="6">
         <v>85750403977754</v>
       </c>
-      <c r="G55" s="10" t="s">
-        <v>267</v>
+      <c r="G55" s="9" t="s">
+        <v>255</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8218,7 +8003,7 @@
         <v>53</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="D56" s="1">
         <v>3050000000</v>
@@ -8227,14 +8012,14 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56" s="6">
         <v>87658125570749</v>
       </c>
-      <c r="G56" s="10" t="s">
-        <v>269</v>
+      <c r="G56" s="9" t="s">
+        <v>257</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8245,7 +8030,7 @@
         <v>54</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D57" s="1">
         <v>4880000000</v>
@@ -8254,14 +8039,14 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F57" s="6">
         <v>71386503893388</v>
       </c>
-      <c r="G57" s="10" t="s">
-        <v>271</v>
+      <c r="G57" s="9" t="s">
+        <v>259</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8272,7 +8057,7 @@
         <v>55</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="D58" s="1">
         <v>7320000000</v>
@@ -8281,14 +8066,14 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F58" s="9">
+      <c r="F58" s="6">
         <v>117660867991736</v>
       </c>
-      <c r="G58" s="10" t="s">
-        <v>273</v>
+      <c r="G58" s="9" t="s">
+        <v>261</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8299,7 +8084,7 @@
         <v>56</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="D59" s="1">
         <v>9150000000</v>
@@ -8308,14 +8093,14 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F59" s="9">
+      <c r="F59" s="6">
         <v>75602786825729</v>
       </c>
-      <c r="G59" s="10" t="s">
-        <v>275</v>
+      <c r="G59" s="9" t="s">
+        <v>263</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8326,7 +8111,7 @@
         <v>57</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="D60" s="1">
         <v>15250000000</v>
@@ -8335,14 +8120,14 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F60" s="9">
+      <c r="F60" s="6">
         <v>97494295137425</v>
       </c>
-      <c r="G60" s="10" t="s">
-        <v>277</v>
+      <c r="G60" s="9" t="s">
+        <v>265</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8353,7 +8138,7 @@
         <v>58</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="D61" s="1">
         <v>24400000000</v>
@@ -8362,14 +8147,14 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F61" s="9">
+      <c r="F61" s="6">
         <v>121387106380169</v>
       </c>
-      <c r="G61" s="10" t="s">
-        <v>279</v>
+      <c r="G61" s="9" t="s">
+        <v>267</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8380,7 +8165,7 @@
         <v>59</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D62" s="1">
         <v>36600000000</v>
@@ -8389,14 +8174,14 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F62" s="9">
+      <c r="F62" s="6">
         <v>77703154963129</v>
       </c>
-      <c r="G62" s="10" t="s">
-        <v>281</v>
+      <c r="G62" s="9" t="s">
+        <v>269</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8407,7 +8192,7 @@
         <v>60</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="D63" s="1">
         <v>45750000000</v>
@@ -8416,14 +8201,14 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F63" s="9">
+      <c r="F63" s="6">
         <v>82745313217810</v>
       </c>
-      <c r="G63" s="10" t="s">
-        <v>283</v>
+      <c r="G63" s="9" t="s">
+        <v>271</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8434,7 +8219,7 @@
         <v>61</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="D64" s="1">
         <v>76500000000</v>
@@ -8443,14 +8228,14 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F64" s="9">
+      <c r="F64" s="6">
         <v>78702263483439</v>
       </c>
-      <c r="G64" s="10" t="s">
-        <v>285</v>
+      <c r="G64" s="9" t="s">
+        <v>273</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8461,7 +8246,7 @@
         <v>62</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="D65" s="1">
         <v>122400000000</v>
@@ -8470,14 +8255,14 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F65" s="9">
+      <c r="F65" s="6">
         <v>103252845267522</v>
       </c>
-      <c r="G65" s="10" t="s">
-        <v>287</v>
+      <c r="G65" s="9" t="s">
+        <v>275</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="66" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8488,7 +8273,7 @@
         <v>63</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="D66" s="1">
         <v>183600000000</v>
@@ -8497,14 +8282,14 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F66" s="9">
+      <c r="F66" s="6">
         <v>93380659059014</v>
       </c>
-      <c r="G66" s="10" t="s">
-        <v>289</v>
+      <c r="G66" s="9" t="s">
+        <v>277</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="67" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8515,7 +8300,7 @@
         <v>64</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="D67" s="1">
         <v>229500000000</v>
@@ -8524,14 +8309,14 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F67" s="9">
+      <c r="F67" s="6">
         <v>124070618735034</v>
       </c>
-      <c r="G67" s="10" t="s">
-        <v>291</v>
+      <c r="G67" s="9" t="s">
+        <v>279</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8542,7 +8327,7 @@
         <v>65</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D68" s="1">
         <v>381500000000</v>
@@ -8551,14 +8336,14 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F68" s="9">
+      <c r="F68" s="6">
         <v>82229267783572</v>
       </c>
-      <c r="G68" s="10" t="s">
-        <v>293</v>
+      <c r="G68" s="9" t="s">
+        <v>281</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="69" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8569,7 +8354,7 @@
         <v>66</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D69" s="1">
         <v>610400000000</v>
@@ -8578,14 +8363,14 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F69" s="9">
+      <c r="F69" s="6">
         <v>90764663625426</v>
       </c>
-      <c r="G69" s="10" t="s">
-        <v>295</v>
+      <c r="G69" s="9" t="s">
+        <v>283</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8596,7 +8381,7 @@
         <v>67</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="D70" s="1">
         <v>915600000000</v>
@@ -8605,14 +8390,14 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F70" s="9">
+      <c r="F70" s="6">
         <v>89592774326120</v>
       </c>
-      <c r="G70" s="10" t="s">
-        <v>297</v>
+      <c r="G70" s="9" t="s">
+        <v>285</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8623,7 +8408,7 @@
         <v>68</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D71" s="1">
         <v>1144500000000</v>
@@ -8632,14 +8417,14 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F71" s="9">
+      <c r="F71" s="6">
         <v>96498729983354</v>
       </c>
-      <c r="G71" s="10" t="s">
-        <v>299</v>
+      <c r="G71" s="9" t="s">
+        <v>287</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8650,7 +8435,7 @@
         <v>69</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="D72" s="1">
         <v>1905000000000</v>
@@ -8659,14 +8444,14 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="F72" s="9">
+      <c r="F72" s="6">
         <v>137402232463633</v>
       </c>
-      <c r="G72" s="10" t="s">
-        <v>301</v>
+      <c r="G72" s="9" t="s">
+        <v>289</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="73" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8677,7 +8462,7 @@
         <v>70</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="D73" s="1">
         <v>3048000000000</v>
@@ -8686,14 +8471,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>15</v>
       </c>
-      <c r="F73" s="9">
+      <c r="F73" s="6">
         <v>79717469784936</v>
       </c>
-      <c r="G73" s="10" t="s">
-        <v>303</v>
+      <c r="G73" s="9" t="s">
+        <v>291</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8704,7 +8489,7 @@
         <v>71</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="D74" s="1">
         <v>4572000000000</v>
@@ -8713,14 +8498,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F74" s="9">
+      <c r="F74" s="6">
         <v>86646811474956</v>
       </c>
-      <c r="G74" s="10" t="s">
-        <v>305</v>
+      <c r="G74" s="9" t="s">
+        <v>293</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8731,7 +8516,7 @@
         <v>72</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="D75" s="1">
         <v>5715000000000</v>
@@ -8740,14 +8525,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F75" s="9">
+      <c r="F75" s="6">
         <v>128217347353354</v>
       </c>
-      <c r="G75" s="10" t="s">
-        <v>307</v>
+      <c r="G75" s="9" t="s">
+        <v>295</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8758,7 +8543,7 @@
         <v>73</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D76" s="1">
         <v>9550000000000</v>
@@ -8767,14 +8552,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F76" s="9">
+      <c r="F76" s="6">
         <v>126321668579357</v>
       </c>
-      <c r="G76" s="10" t="s">
-        <v>309</v>
+      <c r="G76" s="9" t="s">
+        <v>297</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="77" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8785,7 +8570,7 @@
         <v>74</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D77" s="1">
         <v>15280000000000</v>
@@ -8794,14 +8579,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77" s="6">
         <v>98351529529203</v>
       </c>
-      <c r="G77" s="10" t="s">
-        <v>311</v>
+      <c r="G77" s="9" t="s">
+        <v>299</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8812,7 +8597,7 @@
         <v>75</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="D78" s="1">
         <v>22920000000000</v>
@@ -8821,14 +8606,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F78" s="9">
+      <c r="F78" s="6">
         <v>81048668172712</v>
       </c>
-      <c r="G78" s="10" t="s">
-        <v>313</v>
+      <c r="G78" s="9" t="s">
+        <v>301</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="79" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8839,7 +8624,7 @@
         <v>76</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="D79" s="1">
         <v>28650000000000</v>
@@ -8848,14 +8633,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79" s="6">
         <v>127615544859575</v>
       </c>
-      <c r="G79" s="10" t="s">
-        <v>315</v>
+      <c r="G79" s="9" t="s">
+        <v>303</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="80" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8866,7 +8651,7 @@
         <v>77</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="D80" s="1">
         <v>47700000000000</v>
@@ -8875,14 +8660,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F80" s="9">
+      <c r="F80" s="6">
         <v>70656304136373</v>
       </c>
-      <c r="G80" s="10" t="s">
-        <v>317</v>
+      <c r="G80" s="9" t="s">
+        <v>305</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="81" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8893,7 +8678,7 @@
         <v>78</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="D81" s="1">
         <v>76320000000000</v>
@@ -8902,14 +8687,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F81" s="9">
+      <c r="F81" s="6">
         <v>134424174805013</v>
       </c>
-      <c r="G81" s="10" t="s">
-        <v>319</v>
+      <c r="G81" s="9" t="s">
+        <v>307</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="82" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8920,7 +8705,7 @@
         <v>79</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D82" s="1">
         <v>114480000000000</v>
@@ -8929,14 +8714,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F82" s="9">
+      <c r="F82" s="6">
         <v>127255485663084</v>
       </c>
-      <c r="G82" s="10" t="s">
-        <v>321</v>
+      <c r="G82" s="9" t="s">
+        <v>309</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="83" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8947,7 +8732,7 @@
         <v>80</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="D83" s="1">
         <v>143100000000000</v>
@@ -8956,14 +8741,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F83" s="9">
+      <c r="F83" s="6">
         <v>134027683373658</v>
       </c>
-      <c r="G83" s="10" t="s">
-        <v>323</v>
+      <c r="G83" s="9" t="s">
+        <v>311</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="84" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8974,7 +8759,7 @@
         <v>81</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="D84" s="1">
         <v>238500000000000</v>
@@ -8983,14 +8768,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F84" s="9">
+      <c r="F84" s="6">
         <v>112447657334137</v>
       </c>
-      <c r="G84" s="10" t="s">
-        <v>325</v>
+      <c r="G84" s="9" t="s">
+        <v>313</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="85" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9001,7 +8786,7 @@
         <v>82</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D85" s="1">
         <v>381600000000000</v>
@@ -9010,14 +8795,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F85" s="9">
+      <c r="F85" s="6">
         <v>104595008892706</v>
       </c>
-      <c r="G85" s="10" t="s">
-        <v>327</v>
+      <c r="G85" s="9" t="s">
+        <v>315</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9028,7 +8813,7 @@
         <v>83</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="D86" s="1">
         <v>572400000000000</v>
@@ -9037,14 +8822,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F86" s="9">
+      <c r="F86" s="6">
         <v>82759045606098</v>
       </c>
-      <c r="G86" s="10" t="s">
-        <v>329</v>
+      <c r="G86" s="9" t="s">
+        <v>317</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="87" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9055,7 +8840,7 @@
         <v>84</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="D87" s="1">
         <v>715500000000000</v>
@@ -9064,14 +8849,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F87" s="9">
+      <c r="F87" s="6">
         <v>105620837789519</v>
       </c>
-      <c r="G87" s="10" t="s">
-        <v>331</v>
+      <c r="G87" s="9" t="s">
+        <v>319</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9082,7 +8867,7 @@
         <v>85</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="D88" s="1">
         <v>1190000000000000</v>
@@ -9091,14 +8876,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F88" s="9">
+      <c r="F88" s="6">
         <v>111024567754480</v>
       </c>
-      <c r="G88" s="10" t="s">
-        <v>333</v>
+      <c r="G88" s="9" t="s">
+        <v>321</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="89" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9109,7 +8894,7 @@
         <v>86</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="D89" s="1">
         <v>1904000000000000</v>
@@ -9118,14 +8903,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F89" s="9">
+      <c r="F89" s="6">
         <v>137153989969007</v>
       </c>
-      <c r="G89" s="10" t="s">
-        <v>335</v>
+      <c r="G89" s="9" t="s">
+        <v>323</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="90" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9136,7 +8921,7 @@
         <v>87</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="D90" s="1">
         <v>2856000000000000</v>
@@ -9145,14 +8930,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F90" s="9">
+      <c r="F90" s="6">
         <v>74496996195913</v>
       </c>
-      <c r="G90" s="10" t="s">
-        <v>337</v>
+      <c r="G90" s="9" t="s">
+        <v>325</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="91" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9163,7 +8948,7 @@
         <v>88</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="D91" s="1">
         <v>3570000000000000</v>
@@ -9172,14 +8957,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F91" s="9">
+      <c r="F91" s="6">
         <v>132785860315163</v>
       </c>
-      <c r="G91" s="10" t="s">
-        <v>339</v>
+      <c r="G91" s="9" t="s">
+        <v>327</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="92" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9190,7 +8975,7 @@
         <v>89</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="D92" s="1">
         <v>5950000000000000</v>
@@ -9199,14 +8984,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F92" s="9">
+      <c r="F92" s="6">
         <v>117198962948319</v>
       </c>
-      <c r="G92" s="10" t="s">
-        <v>341</v>
+      <c r="G92" s="9" t="s">
+        <v>329</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="93" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9217,7 +9002,7 @@
         <v>90</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="D93" s="1">
         <v>9520000000000000</v>
@@ -9226,14 +9011,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F93" s="9">
+      <c r="F93" s="6">
         <v>124449160476895</v>
       </c>
-      <c r="G93" s="10" t="s">
-        <v>343</v>
+      <c r="G93" s="9" t="s">
+        <v>331</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="94" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9244,7 +9029,7 @@
         <v>91</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="D94" s="1">
         <v>1.428e+16</v>
@@ -9253,14 +9038,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F94" s="9">
+      <c r="F94" s="6">
         <v>125887863438527</v>
       </c>
-      <c r="G94" s="10" t="s">
-        <v>345</v>
+      <c r="G94" s="9" t="s">
+        <v>333</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="95" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9271,7 +9056,7 @@
         <v>92</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="D95" s="1">
         <v>1.785e+16</v>
@@ -9280,14 +9065,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F95" s="9">
+      <c r="F95" s="6">
         <v>137692564728429</v>
       </c>
-      <c r="G95" s="10" t="s">
-        <v>347</v>
+      <c r="G95" s="9" t="s">
+        <v>335</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="96" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9298,7 +9083,7 @@
         <v>93</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="D96" s="1">
         <v>2.98e+16</v>
@@ -9307,14 +9092,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F96" s="9">
+      <c r="F96" s="6">
         <v>82350951870220</v>
       </c>
-      <c r="G96" s="10" t="s">
-        <v>349</v>
+      <c r="G96" s="9" t="s">
+        <v>337</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="97" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9325,7 +9110,7 @@
         <v>94</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="D97" s="1">
         <v>4.768e+16</v>
@@ -9334,14 +9119,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F97" s="9">
+      <c r="F97" s="6">
         <v>133019385929561</v>
       </c>
-      <c r="G97" s="10" t="s">
-        <v>351</v>
+      <c r="G97" s="9" t="s">
+        <v>339</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="98" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9352,7 +9137,7 @@
         <v>95</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="D98" s="1">
         <v>7.152e+16</v>
@@ -9361,14 +9146,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F98" s="9">
+      <c r="F98" s="6">
         <v>82714807302588</v>
       </c>
-      <c r="G98" s="10" t="s">
-        <v>353</v>
+      <c r="G98" s="9" t="s">
+        <v>341</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="99" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9379,7 +9164,7 @@
         <v>96</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="D99" s="1">
         <v>8.94e+16</v>
@@ -9388,14 +9173,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F99" s="9">
+      <c r="F99" s="6">
         <v>120409278538446</v>
       </c>
-      <c r="G99" s="10" t="s">
-        <v>355</v>
+      <c r="G99" s="9" t="s">
+        <v>343</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="100" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9406,7 +9191,7 @@
         <v>97</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D100" s="1">
         <v>1.49e+17</v>
@@ -9415,14 +9200,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F100" s="9">
+      <c r="F100" s="6">
         <v>136303201068741</v>
       </c>
-      <c r="G100" s="10" t="s">
-        <v>357</v>
+      <c r="G100" s="9" t="s">
+        <v>345</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="101" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9433,7 +9218,7 @@
         <v>98</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="D101" s="1">
         <v>2.384e+17</v>
@@ -9442,14 +9227,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F101" s="9">
+      <c r="F101" s="6">
         <v>76724781858184</v>
       </c>
-      <c r="G101" s="10" t="s">
-        <v>359</v>
+      <c r="G101" s="9" t="s">
+        <v>347</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="102" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9460,7 +9245,7 @@
         <v>99</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="D102" s="1">
         <v>3.576e+17</v>
@@ -9469,14 +9254,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F102" s="9">
+      <c r="F102" s="6">
         <v>120125979830927</v>
       </c>
-      <c r="G102" s="10" t="s">
-        <v>361</v>
+      <c r="G102" s="9" t="s">
+        <v>349</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="103" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9487,7 +9272,7 @@
         <v>100</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="D103" s="1">
         <v>4.47e+17</v>
@@ -9496,14 +9281,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F103" s="9">
+      <c r="F103" s="6">
         <v>86921870572603</v>
       </c>
-      <c r="G103" s="10" t="s">
-        <v>363</v>
+      <c r="G103" s="9" t="s">
+        <v>351</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="104" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9514,7 +9299,7 @@
         <v>101</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="D104" s="1">
         <v>7.45e+17</v>
@@ -9523,14 +9308,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F104" s="9">
+      <c r="F104" s="6">
         <v>126355990231048</v>
       </c>
-      <c r="G104" s="10" t="s">
-        <v>365</v>
+      <c r="G104" s="9" t="s">
+        <v>353</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="105" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9541,7 +9326,7 @@
         <v>102</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D105" s="1">
         <v>1.192e+18</v>
@@ -9550,14 +9335,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F105" s="9">
+      <c r="F105" s="6">
         <v>72326444062448</v>
       </c>
-      <c r="G105" s="10" t="s">
-        <v>367</v>
+      <c r="G105" s="9" t="s">
+        <v>355</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="106" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9568,7 +9353,7 @@
         <v>103</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="D106" s="1">
         <v>1.788e+18</v>
@@ -9577,14 +9362,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F106" s="9">
+      <c r="F106" s="6">
         <v>72257499044823</v>
       </c>
-      <c r="G106" s="10" t="s">
-        <v>369</v>
+      <c r="G106" s="9" t="s">
+        <v>357</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="107" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9595,7 +9380,7 @@
         <v>104</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="D107" s="1">
         <v>2.235e+18</v>
@@ -9604,14 +9389,14 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F107" s="9">
+      <c r="F107" s="6">
         <v>74695865349139</v>
       </c>
-      <c r="G107" s="10" t="s">
-        <v>371</v>
+      <c r="G107" s="9" t="s">
+        <v>359</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:9">
@@ -9622,7 +9407,7 @@
         <v>105</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="D108" s="1">
         <v>3.725e+18</v>
@@ -9630,14 +9415,14 @@
       <c r="E108" s="1">
         <v>24</v>
       </c>
-      <c r="F108" s="9">
+      <c r="F108" s="6">
         <v>98358488442985</v>
       </c>
-      <c r="G108" s="10" t="s">
-        <v>373</v>
+      <c r="G108" s="9" t="s">
+        <v>361</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I108" s="3"/>
     </row>
@@ -9649,7 +9434,7 @@
         <v>106</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="D109" s="1">
         <v>5.96e+18</v>
@@ -9657,14 +9442,14 @@
       <c r="E109" s="1">
         <v>24</v>
       </c>
-      <c r="F109" s="9">
+      <c r="F109" s="6">
         <v>113636295509693</v>
       </c>
-      <c r="G109" s="10" t="s">
-        <v>375</v>
+      <c r="G109" s="9" t="s">
+        <v>363</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I109" s="3"/>
     </row>
@@ -9676,7 +9461,7 @@
         <v>107</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="D110" s="1">
         <v>8.94e+18</v>
@@ -9684,14 +9469,14 @@
       <c r="E110" s="1">
         <v>25</v>
       </c>
-      <c r="F110" s="9">
+      <c r="F110" s="6">
         <v>114047124407739</v>
       </c>
-      <c r="G110" s="10" t="s">
-        <v>377</v>
+      <c r="G110" s="9" t="s">
+        <v>365</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I110" s="3"/>
     </row>
@@ -9703,7 +9488,7 @@
         <v>108</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="D111" s="1">
         <v>1.1175e+19</v>
@@ -9711,14 +9496,14 @@
       <c r="E111" s="1">
         <v>25</v>
       </c>
-      <c r="F111" s="9">
+      <c r="F111" s="6">
         <v>95771403493939</v>
       </c>
-      <c r="G111" s="10" t="s">
-        <v>379</v>
+      <c r="G111" s="9" t="s">
+        <v>367</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I111" s="3"/>
     </row>
@@ -9730,7 +9515,7 @@
         <v>109</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D112" s="1">
         <v>1.865e+19</v>
@@ -9738,14 +9523,14 @@
       <c r="E112" s="1">
         <v>25</v>
       </c>
-      <c r="F112" s="9">
+      <c r="F112" s="6">
         <v>140393673870516</v>
       </c>
-      <c r="G112" s="10" t="s">
-        <v>381</v>
+      <c r="G112" s="9" t="s">
+        <v>369</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I112" s="3"/>
     </row>
@@ -9757,7 +9542,7 @@
         <v>110</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="D113" s="1">
         <v>2.984e+19</v>
@@ -9765,14 +9550,14 @@
       <c r="E113" s="1">
         <v>25</v>
       </c>
-      <c r="F113" s="9">
+      <c r="F113" s="6">
         <v>123109322631502</v>
       </c>
-      <c r="G113" s="10" t="s">
-        <v>383</v>
+      <c r="G113" s="9" t="s">
+        <v>371</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I113" s="3"/>
     </row>
@@ -9784,7 +9569,7 @@
         <v>111</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="D114" s="1">
         <v>4.476e+19</v>
@@ -9792,14 +9577,14 @@
       <c r="E114" s="1">
         <v>26</v>
       </c>
-      <c r="F114" s="9">
+      <c r="F114" s="6">
         <v>98614967981417</v>
       </c>
-      <c r="G114" s="10" t="s">
-        <v>385</v>
+      <c r="G114" s="9" t="s">
+        <v>373</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I114" s="3"/>
     </row>
@@ -9811,7 +9596,7 @@
         <v>112</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="D115" s="1">
         <v>5.595e+19</v>
@@ -9819,14 +9604,14 @@
       <c r="E115" s="1">
         <v>26</v>
       </c>
-      <c r="F115" s="9">
+      <c r="F115" s="6">
         <v>127369769981706</v>
       </c>
-      <c r="G115" s="10" t="s">
-        <v>387</v>
+      <c r="G115" s="9" t="s">
+        <v>375</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I115" s="3"/>
     </row>
@@ -9838,7 +9623,7 @@
         <v>113</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="D116" s="1">
         <v>9.3e+19</v>
@@ -9846,14 +9631,14 @@
       <c r="E116" s="1">
         <v>26</v>
       </c>
-      <c r="F116" s="9">
+      <c r="F116" s="6">
         <v>134574393827781</v>
       </c>
-      <c r="G116" s="10" t="s">
-        <v>389</v>
+      <c r="G116" s="9" t="s">
+        <v>377</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I116" s="3"/>
     </row>
@@ -9865,7 +9650,7 @@
         <v>114</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="D117" s="1">
         <v>1.488e+20</v>
@@ -9873,14 +9658,14 @@
       <c r="E117" s="1">
         <v>26</v>
       </c>
-      <c r="F117" s="9">
+      <c r="F117" s="6">
         <v>130258203281991</v>
       </c>
-      <c r="G117" s="10" t="s">
-        <v>391</v>
+      <c r="G117" s="9" t="s">
+        <v>379</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I117" s="3"/>
     </row>
@@ -9892,7 +9677,7 @@
         <v>115</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D118" s="1">
         <v>2.232e+20</v>
@@ -9900,14 +9685,14 @@
       <c r="E118" s="1">
         <v>27</v>
       </c>
-      <c r="F118" s="9">
+      <c r="F118" s="6">
         <v>93953823085119</v>
       </c>
-      <c r="G118" s="10" t="s">
-        <v>393</v>
+      <c r="G118" s="9" t="s">
+        <v>381</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I118" s="3"/>
     </row>
@@ -9919,7 +9704,7 @@
         <v>116</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="D119" s="1">
         <v>2.79e+20</v>
@@ -9927,14 +9712,14 @@
       <c r="E119" s="1">
         <v>27</v>
       </c>
-      <c r="F119" s="9">
+      <c r="F119" s="6">
         <v>109802560542166</v>
       </c>
-      <c r="G119" s="10" t="s">
-        <v>395</v>
+      <c r="G119" s="9" t="s">
+        <v>383</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I119" s="3"/>
     </row>
@@ -9946,7 +9731,7 @@
         <v>117</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="D120" s="1">
         <v>4.655e+20</v>
@@ -9954,14 +9739,14 @@
       <c r="E120" s="1">
         <v>27</v>
       </c>
-      <c r="F120" s="9">
+      <c r="F120" s="6">
         <v>130989494782889</v>
       </c>
-      <c r="G120" s="10" t="s">
-        <v>397</v>
+      <c r="G120" s="9" t="s">
+        <v>385</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I120" s="3"/>
     </row>
@@ -9973,7 +9758,7 @@
         <v>118</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="D121" s="1">
         <v>7.448e+20</v>
@@ -9981,14 +9766,14 @@
       <c r="E121" s="1">
         <v>27</v>
       </c>
-      <c r="F121" s="9">
+      <c r="F121" s="6">
         <v>129408716253336</v>
       </c>
-      <c r="G121" s="10" t="s">
-        <v>399</v>
+      <c r="G121" s="9" t="s">
+        <v>387</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I121" s="3"/>
     </row>
@@ -10000,7 +9785,7 @@
         <v>119</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="D122" s="1">
         <v>1.1172e+21</v>
@@ -10008,14 +9793,14 @@
       <c r="E122" s="1">
         <v>28</v>
       </c>
-      <c r="F122" s="9">
+      <c r="F122" s="6">
         <v>127772866805590</v>
       </c>
-      <c r="G122" s="10" t="s">
-        <v>401</v>
+      <c r="G122" s="9" t="s">
+        <v>389</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I122" s="3"/>
     </row>
@@ -10027,7 +9812,7 @@
         <v>120</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="D123" s="1">
         <v>1.3965e+21</v>
@@ -10035,14 +9820,14 @@
       <c r="E123" s="1">
         <v>28</v>
       </c>
-      <c r="F123" s="9">
+      <c r="F123" s="6">
         <v>91938109188463</v>
       </c>
-      <c r="G123" s="10" t="s">
-        <v>403</v>
+      <c r="G123" s="9" t="s">
+        <v>391</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I123" s="3"/>
     </row>
@@ -10054,7 +9839,7 @@
         <v>121</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="D124" s="1">
         <v>2.33e+21</v>
@@ -10062,14 +9847,14 @@
       <c r="E124" s="1">
         <v>28</v>
       </c>
-      <c r="F124" s="9">
+      <c r="F124" s="6">
         <v>85077262752129</v>
       </c>
-      <c r="G124" s="10" t="s">
-        <v>405</v>
+      <c r="G124" s="9" t="s">
+        <v>393</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="I124" s="3"/>
     </row>
@@ -10080,8 +9865,8 @@
       <c r="B125" s="1">
         <v>122</v>
       </c>
-      <c r="C125" s="10" t="s">
-        <v>406</v>
+      <c r="C125" s="9" t="s">
+        <v>394</v>
       </c>
       <c r="D125" s="1">
         <v>3.728e+21</v>
@@ -10089,14 +9874,14 @@
       <c r="E125" s="1">
         <v>28</v>
       </c>
-      <c r="F125" s="9">
+      <c r="F125" s="6">
         <v>140335958193244</v>
       </c>
-      <c r="G125" s="10" t="s">
-        <v>407</v>
+      <c r="G125" s="9" t="s">
+        <v>395</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="1:9">
@@ -10106,8 +9891,8 @@
       <c r="B126" s="1">
         <v>123</v>
       </c>
-      <c r="C126" s="10" t="s">
-        <v>408</v>
+      <c r="C126" s="9" t="s">
+        <v>396</v>
       </c>
       <c r="D126" s="1">
         <v>5.592e+21</v>
@@ -10115,14 +9900,14 @@
       <c r="E126" s="1">
         <v>29</v>
       </c>
-      <c r="F126" s="9">
+      <c r="F126" s="6">
         <v>86732012145983</v>
       </c>
-      <c r="G126" s="10" t="s">
-        <v>409</v>
+      <c r="G126" s="9" t="s">
+        <v>397</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="1:9">
@@ -10132,8 +9917,8 @@
       <c r="B127" s="1">
         <v>124</v>
       </c>
-      <c r="C127" s="10" t="s">
-        <v>410</v>
+      <c r="C127" s="9" t="s">
+        <v>398</v>
       </c>
       <c r="D127" s="1">
         <v>6.99e+21</v>
@@ -10141,14 +9926,14 @@
       <c r="E127" s="1">
         <v>29</v>
       </c>
-      <c r="F127" s="9">
+      <c r="F127" s="6">
         <v>78044122276865</v>
       </c>
-      <c r="G127" s="10" t="s">
-        <v>411</v>
+      <c r="G127" s="9" t="s">
+        <v>399</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="1:9">
@@ -10158,8 +9943,8 @@
       <c r="B128" s="1">
         <v>125</v>
       </c>
-      <c r="C128" s="10" t="s">
-        <v>412</v>
+      <c r="C128" s="9" t="s">
+        <v>400</v>
       </c>
       <c r="D128" s="1">
         <v>1.165e+22</v>
@@ -10167,14 +9952,14 @@
       <c r="E128" s="1">
         <v>29</v>
       </c>
-      <c r="F128" s="9">
+      <c r="F128" s="6">
         <v>114974638199136</v>
       </c>
-      <c r="G128" s="10" t="s">
-        <v>413</v>
+      <c r="G128" s="9" t="s">
+        <v>401</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="1:8">
@@ -10184,8 +9969,8 @@
       <c r="B129" s="1">
         <v>126</v>
       </c>
-      <c r="C129" s="10" t="s">
-        <v>414</v>
+      <c r="C129" s="9" t="s">
+        <v>402</v>
       </c>
       <c r="D129" s="1">
         <v>1.864e+22</v>
@@ -10193,14 +9978,14 @@
       <c r="E129" s="1">
         <v>29</v>
       </c>
-      <c r="F129" s="9">
+      <c r="F129" s="6">
         <v>83652207307759</v>
       </c>
-      <c r="G129" s="10" t="s">
-        <v>415</v>
+      <c r="G129" s="9" t="s">
+        <v>403</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="1:8">
@@ -10210,8 +9995,8 @@
       <c r="B130" s="1">
         <v>127</v>
       </c>
-      <c r="C130" s="10" t="s">
-        <v>416</v>
+      <c r="C130" s="9" t="s">
+        <v>404</v>
       </c>
       <c r="D130" s="1">
         <v>2.796e+22</v>
@@ -10219,14 +10004,14 @@
       <c r="E130" s="1">
         <v>30</v>
       </c>
-      <c r="F130" s="9">
+      <c r="F130" s="6">
         <v>131787091355052</v>
       </c>
-      <c r="G130" s="10" t="s">
-        <v>417</v>
+      <c r="G130" s="9" t="s">
+        <v>405</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="1:8">
@@ -10236,8 +10021,8 @@
       <c r="B131" s="1">
         <v>128</v>
       </c>
-      <c r="C131" s="10" t="s">
-        <v>418</v>
+      <c r="C131" s="9" t="s">
+        <v>406</v>
       </c>
       <c r="D131" s="1">
         <v>3.495e+22</v>
@@ -10245,14 +10030,14 @@
       <c r="E131" s="1">
         <v>30</v>
       </c>
-      <c r="F131" s="9">
+      <c r="F131" s="6">
         <v>99348381699835</v>
       </c>
-      <c r="G131" s="10" t="s">
-        <v>419</v>
+      <c r="G131" s="9" t="s">
+        <v>407</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="1:8">
@@ -10262,8 +10047,8 @@
       <c r="B132" s="1">
         <v>129</v>
       </c>
-      <c r="C132" s="10" t="s">
-        <v>420</v>
+      <c r="C132" s="9" t="s">
+        <v>408</v>
       </c>
       <c r="D132" s="1">
         <v>5.8e+22</v>
@@ -10271,14 +10056,14 @@
       <c r="E132" s="1">
         <v>30</v>
       </c>
-      <c r="F132" s="9">
+      <c r="F132" s="6">
         <v>75412160560516</v>
       </c>
-      <c r="G132" s="10" t="s">
-        <v>421</v>
+      <c r="G132" s="9" t="s">
+        <v>409</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="1:8">
@@ -10288,8 +10073,8 @@
       <c r="B133" s="1">
         <v>130</v>
       </c>
-      <c r="C133" s="10" t="s">
-        <v>422</v>
+      <c r="C133" s="9" t="s">
+        <v>410</v>
       </c>
       <c r="D133" s="1">
         <v>9.28e+22</v>
@@ -10297,14 +10082,14 @@
       <c r="E133" s="1">
         <v>30</v>
       </c>
-      <c r="F133" s="9">
+      <c r="F133" s="6">
         <v>105475505052937</v>
       </c>
-      <c r="G133" s="10" t="s">
-        <v>423</v>
+      <c r="G133" s="9" t="s">
+        <v>411</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="1:8">
@@ -10314,8 +10099,8 @@
       <c r="B134" s="1">
         <v>131</v>
       </c>
-      <c r="C134" s="10" t="s">
-        <v>424</v>
+      <c r="C134" s="9" t="s">
+        <v>412</v>
       </c>
       <c r="D134" s="1">
         <v>1.392e+23</v>
@@ -10323,14 +10108,14 @@
       <c r="E134" s="1">
         <v>31</v>
       </c>
-      <c r="F134" s="9">
+      <c r="F134" s="6">
         <v>125484119033793</v>
       </c>
-      <c r="G134" s="10" t="s">
-        <v>425</v>
+      <c r="G134" s="9" t="s">
+        <v>413</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="1:8">
@@ -10340,8 +10125,8 @@
       <c r="B135" s="1">
         <v>132</v>
       </c>
-      <c r="C135" s="10" t="s">
-        <v>426</v>
+      <c r="C135" s="9" t="s">
+        <v>414</v>
       </c>
       <c r="D135" s="1">
         <v>1.74e+23</v>
@@ -10349,14 +10134,14 @@
       <c r="E135" s="1">
         <v>31</v>
       </c>
-      <c r="F135" s="9">
+      <c r="F135" s="6">
         <v>140608831780254</v>
       </c>
-      <c r="G135" s="10" t="s">
-        <v>427</v>
+      <c r="G135" s="9" t="s">
+        <v>415</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="1:8">
@@ -10366,8 +10151,8 @@
       <c r="B136" s="1">
         <v>133</v>
       </c>
-      <c r="C136" s="10" t="s">
-        <v>428</v>
+      <c r="C136" s="9" t="s">
+        <v>416</v>
       </c>
       <c r="D136" s="1">
         <v>2.91e+23</v>
@@ -10375,14 +10160,14 @@
       <c r="E136" s="1">
         <v>31</v>
       </c>
-      <c r="F136" s="9">
+      <c r="F136" s="6">
         <v>124177358025481</v>
       </c>
-      <c r="G136" s="10" t="s">
-        <v>429</v>
+      <c r="G136" s="9" t="s">
+        <v>417</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="1:8">
@@ -10392,8 +10177,8 @@
       <c r="B137" s="1">
         <v>134</v>
       </c>
-      <c r="C137" s="10" t="s">
-        <v>430</v>
+      <c r="C137" s="9" t="s">
+        <v>418</v>
       </c>
       <c r="D137" s="1">
         <v>4.656e+23</v>
@@ -10401,14 +10186,14 @@
       <c r="E137" s="1">
         <v>31</v>
       </c>
-      <c r="F137" s="9">
+      <c r="F137" s="6">
         <v>129385390119523</v>
       </c>
-      <c r="G137" s="10" t="s">
-        <v>431</v>
+      <c r="G137" s="9" t="s">
+        <v>419</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="1:8">
@@ -10418,8 +10203,8 @@
       <c r="B138" s="1">
         <v>135</v>
       </c>
-      <c r="C138" s="10" t="s">
-        <v>432</v>
+      <c r="C138" s="9" t="s">
+        <v>420</v>
       </c>
       <c r="D138" s="1">
         <v>6.984e+23</v>
@@ -10427,14 +10212,14 @@
       <c r="E138" s="1">
         <v>32</v>
       </c>
-      <c r="F138" s="9">
+      <c r="F138" s="6">
         <v>84940520003035</v>
       </c>
-      <c r="G138" s="10" t="s">
-        <v>433</v>
+      <c r="G138" s="9" t="s">
+        <v>421</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="139" ht="16.5" spans="1:8">
@@ -10444,8 +10229,8 @@
       <c r="B139" s="1">
         <v>136</v>
       </c>
-      <c r="C139" s="10" t="s">
-        <v>434</v>
+      <c r="C139" s="9" t="s">
+        <v>422</v>
       </c>
       <c r="D139" s="1">
         <v>8.73e+23</v>
@@ -10453,14 +10238,14 @@
       <c r="E139" s="1">
         <v>32</v>
       </c>
-      <c r="F139" s="9">
+      <c r="F139" s="6">
         <v>90031364711610</v>
       </c>
-      <c r="G139" s="10" t="s">
-        <v>435</v>
+      <c r="G139" s="9" t="s">
+        <v>423</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="140" ht="16.5" spans="1:8">
@@ -10470,8 +10255,8 @@
       <c r="B140" s="1">
         <v>137</v>
       </c>
-      <c r="C140" s="10" t="s">
-        <v>436</v>
+      <c r="C140" s="9" t="s">
+        <v>424</v>
       </c>
       <c r="D140" s="1">
         <v>1.455e+24</v>
@@ -10479,14 +10264,14 @@
       <c r="E140" s="1">
         <v>32</v>
       </c>
-      <c r="F140" s="9">
+      <c r="F140" s="6">
         <v>84418341821320</v>
       </c>
-      <c r="G140" s="10" t="s">
-        <v>437</v>
+      <c r="G140" s="9" t="s">
+        <v>425</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="1:8">
@@ -10496,8 +10281,8 @@
       <c r="B141" s="1">
         <v>138</v>
       </c>
-      <c r="C141" s="10" t="s">
-        <v>438</v>
+      <c r="C141" s="9" t="s">
+        <v>426</v>
       </c>
       <c r="D141" s="1">
         <v>2.328e+24</v>
@@ -10505,14 +10290,14 @@
       <c r="E141" s="1">
         <v>32</v>
       </c>
-      <c r="F141" s="9">
+      <c r="F141" s="6">
         <v>130255705800444</v>
       </c>
-      <c r="G141" s="10" t="s">
-        <v>439</v>
+      <c r="G141" s="9" t="s">
+        <v>427</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="1:8">
@@ -10522,8 +10307,8 @@
       <c r="B142" s="1">
         <v>139</v>
       </c>
-      <c r="C142" s="10" t="s">
-        <v>440</v>
+      <c r="C142" s="9" t="s">
+        <v>428</v>
       </c>
       <c r="D142" s="1">
         <v>3.492e+24</v>
@@ -10531,14 +10316,14 @@
       <c r="E142" s="1">
         <v>33</v>
       </c>
-      <c r="F142" s="9">
+      <c r="F142" s="6">
         <v>123568265278671</v>
       </c>
-      <c r="G142" s="10" t="s">
-        <v>441</v>
+      <c r="G142" s="9" t="s">
+        <v>429</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="1:8">
@@ -10548,8 +10333,8 @@
       <c r="B143" s="1">
         <v>140</v>
       </c>
-      <c r="C143" s="10" t="s">
-        <v>442</v>
+      <c r="C143" s="9" t="s">
+        <v>430</v>
       </c>
       <c r="D143" s="1">
         <v>4.365e+24</v>
@@ -10557,14 +10342,14 @@
       <c r="E143" s="1">
         <v>33</v>
       </c>
-      <c r="F143" s="9">
+      <c r="F143" s="6">
         <v>75689117044416</v>
       </c>
-      <c r="G143" s="10" t="s">
-        <v>443</v>
+      <c r="G143" s="9" t="s">
+        <v>431</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="1:8">
@@ -10574,8 +10359,8 @@
       <c r="B144" s="1">
         <v>141</v>
       </c>
-      <c r="C144" s="10" t="s">
-        <v>444</v>
+      <c r="C144" s="9" t="s">
+        <v>432</v>
       </c>
       <c r="D144" s="1">
         <v>7.3e+24</v>
@@ -10583,14 +10368,14 @@
       <c r="E144" s="1">
         <v>33</v>
       </c>
-      <c r="F144" s="9">
+      <c r="F144" s="6">
         <v>92309488435591</v>
       </c>
-      <c r="G144" s="10" t="s">
-        <v>445</v>
+      <c r="G144" s="9" t="s">
+        <v>433</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="1:8">
@@ -10600,8 +10385,8 @@
       <c r="B145" s="1">
         <v>142</v>
       </c>
-      <c r="C145" s="10" t="s">
-        <v>446</v>
+      <c r="C145" s="9" t="s">
+        <v>434</v>
       </c>
       <c r="D145" s="1">
         <v>1.168e+25</v>
@@ -10609,14 +10394,14 @@
       <c r="E145" s="1">
         <v>33</v>
       </c>
-      <c r="F145" s="9">
+      <c r="F145" s="6">
         <v>106319308889290</v>
       </c>
-      <c r="G145" s="10" t="s">
-        <v>447</v>
+      <c r="G145" s="9" t="s">
+        <v>435</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="1:8">
@@ -10626,8 +10411,8 @@
       <c r="B146" s="1">
         <v>143</v>
       </c>
-      <c r="C146" s="10" t="s">
-        <v>448</v>
+      <c r="C146" s="9" t="s">
+        <v>436</v>
       </c>
       <c r="D146" s="1">
         <v>1.752e+25</v>
@@ -10635,14 +10420,14 @@
       <c r="E146" s="1">
         <v>34</v>
       </c>
-      <c r="F146" s="9">
+      <c r="F146" s="6">
         <v>123120949699520</v>
       </c>
-      <c r="G146" s="10" t="s">
-        <v>449</v>
+      <c r="G146" s="9" t="s">
+        <v>437</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="1:8">
@@ -10652,8 +10437,8 @@
       <c r="B147" s="1">
         <v>144</v>
       </c>
-      <c r="C147" s="10" t="s">
-        <v>450</v>
+      <c r="C147" s="9" t="s">
+        <v>438</v>
       </c>
       <c r="D147" s="1">
         <v>2.19e+25</v>
@@ -10661,14 +10446,14 @@
       <c r="E147" s="1">
         <v>34</v>
       </c>
-      <c r="F147" s="9">
+      <c r="F147" s="6">
         <v>111674856010497</v>
       </c>
-      <c r="G147" s="10" t="s">
-        <v>451</v>
+      <c r="G147" s="9" t="s">
+        <v>439</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="1:8">
@@ -10678,8 +10463,8 @@
       <c r="B148" s="1">
         <v>145</v>
       </c>
-      <c r="C148" s="10" t="s">
-        <v>452</v>
+      <c r="C148" s="9" t="s">
+        <v>440</v>
       </c>
       <c r="D148" s="1">
         <v>3.64e+25</v>
@@ -10687,14 +10472,14 @@
       <c r="E148" s="1">
         <v>34</v>
       </c>
-      <c r="F148" s="9">
+      <c r="F148" s="6">
         <v>118080816505555</v>
       </c>
-      <c r="G148" s="10" t="s">
-        <v>453</v>
+      <c r="G148" s="9" t="s">
+        <v>441</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="1:8">
@@ -10704,8 +10489,8 @@
       <c r="B149" s="1">
         <v>146</v>
       </c>
-      <c r="C149" s="10" t="s">
-        <v>454</v>
+      <c r="C149" s="9" t="s">
+        <v>442</v>
       </c>
       <c r="D149" s="1">
         <v>5.824e+25</v>
@@ -10713,14 +10498,14 @@
       <c r="E149" s="1">
         <v>34</v>
       </c>
-      <c r="F149" s="9">
+      <c r="F149" s="6">
         <v>105021574817966</v>
       </c>
-      <c r="G149" s="10" t="s">
-        <v>455</v>
+      <c r="G149" s="9" t="s">
+        <v>443</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="1:8">
@@ -10730,8 +10515,8 @@
       <c r="B150" s="1">
         <v>147</v>
       </c>
-      <c r="C150" s="10" t="s">
-        <v>456</v>
+      <c r="C150" s="9" t="s">
+        <v>444</v>
       </c>
       <c r="D150" s="1">
         <v>8.736e+25</v>
@@ -10739,14 +10524,14 @@
       <c r="E150" s="1">
         <v>35</v>
       </c>
-      <c r="F150" s="9">
+      <c r="F150" s="6">
         <v>72690180103558</v>
       </c>
-      <c r="G150" s="10" t="s">
-        <v>457</v>
+      <c r="G150" s="9" t="s">
+        <v>445</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="1:8">
@@ -10756,8 +10541,8 @@
       <c r="B151" s="1">
         <v>148</v>
       </c>
-      <c r="C151" s="10" t="s">
-        <v>458</v>
+      <c r="C151" s="9" t="s">
+        <v>446</v>
       </c>
       <c r="D151" s="1">
         <v>1.092e+26</v>
@@ -10765,14 +10550,14 @@
       <c r="E151" s="1">
         <v>35</v>
       </c>
-      <c r="F151" s="9">
+      <c r="F151" s="6">
         <v>94914272618995</v>
       </c>
-      <c r="G151" s="10" t="s">
-        <v>459</v>
+      <c r="G151" s="9" t="s">
+        <v>447</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -10796,10 +10581,10 @@
         <v>52</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="16.5" spans="1:3">
@@ -10807,10 +10592,10 @@
         <v>13</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="16.5" spans="1:3">
@@ -10975,25 +10760,25 @@
         <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="16.5" spans="1:9">
@@ -11001,13 +10786,13 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>59</v>
@@ -11016,10 +10801,10 @@
         <v>58</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="16.5" spans="1:9">
@@ -11042,7 +10827,7 @@
         <v>62</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>7</v>
@@ -11056,7 +10841,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -11069,7 +10854,7 @@
         <v>99853650045862</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="I4" s="7"/>
     </row>
@@ -11081,7 +10866,7 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="D5" s="1">
         <v>25</v>
@@ -11094,7 +10879,7 @@
         <v>116225665846279</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="I5" s="7"/>
     </row>
@@ -11106,7 +10891,7 @@
         <v>103</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="D6" s="1">
         <v>450</v>
@@ -11119,7 +10904,7 @@
         <v>136956773152573</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="I6" s="7"/>
     </row>
@@ -11131,7 +10916,7 @@
         <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="D7" s="1">
         <v>4375</v>
@@ -11144,7 +10929,7 @@
         <v>97553870039023</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="I7" s="7"/>
     </row>
@@ -11156,20 +10941,20 @@
         <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>480</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>481</v>
+        <v>467</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>468</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>469</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8">
         <v>118090700645855</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="I8" s="7"/>
     </row>
@@ -11181,20 +10966,20 @@
         <v>106</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>484</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>485</v>
+        <v>471</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>472</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>473</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9">
         <v>138508042210191</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="I9" s="7"/>
     </row>
@@ -11206,20 +10991,20 @@
         <v>107</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>488</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>489</v>
+        <v>475</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>476</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>477</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10">
         <v>78371166922896</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="I10" s="7"/>
     </row>
@@ -11231,20 +11016,20 @@
         <v>108</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>492</v>
-      </c>
-      <c r="E11" s="28" t="s">
-        <v>493</v>
+        <v>479</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>480</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>481</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11">
         <v>132966760008713</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="I11" s="7"/>
     </row>
@@ -11256,20 +11041,20 @@
         <v>109</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>496</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>497</v>
+        <v>483</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>484</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>485</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12">
         <v>133927008310944</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="I12" s="7"/>
     </row>
@@ -11281,20 +11066,20 @@
         <v>110</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>500</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>501</v>
+        <v>487</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>488</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>489</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13">
         <v>98415179467911</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="I13" s="7"/>
     </row>
@@ -11306,20 +11091,20 @@
         <v>111</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>504</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>505</v>
+        <v>491</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>492</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>493</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14">
         <v>79276409476682</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="I14" s="7"/>
     </row>
@@ -11331,20 +11116,20 @@
         <v>112</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>508</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>509</v>
+        <v>495</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>496</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>497</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15">
         <v>86184044773576</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="I15" s="7"/>
     </row>
@@ -11356,20 +11141,20 @@
         <v>113</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>513</v>
+        <v>499</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>501</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16">
         <v>85964386896273</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="I16" s="7"/>
     </row>
@@ -11381,20 +11166,20 @@
         <v>114</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>517</v>
+        <v>503</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>504</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>505</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17">
         <v>121813166897471</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -11406,20 +11191,20 @@
         <v>115</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>520</v>
-      </c>
-      <c r="E18" s="28" t="s">
-        <v>521</v>
+        <v>507</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>508</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>509</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18">
         <v>107669574278873</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="I18" s="7"/>
     </row>
@@ -11431,20 +11216,20 @@
         <v>116</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>524</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>525</v>
+        <v>511</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>512</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>513</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19">
         <v>98723580431394</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="I19" s="7"/>
     </row>
@@ -11456,20 +11241,20 @@
         <v>117</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>528</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>529</v>
+        <v>515</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>516</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>517</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20">
         <v>126241505230536</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="I20" s="7"/>
     </row>
@@ -11481,20 +11266,20 @@
         <v>118</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="D21" s="28" t="s">
-        <v>532</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>533</v>
+        <v>519</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>520</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>521</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21">
         <v>78092021290844</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="I21" s="7"/>
     </row>
@@ -11506,20 +11291,20 @@
         <v>119</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="D22" s="28" t="s">
-        <v>536</v>
-      </c>
-      <c r="E22" s="28" t="s">
-        <v>537</v>
+        <v>523</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>524</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>525</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22">
         <v>138731887343821</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="I22" s="7"/>
     </row>
@@ -11531,20 +11316,20 @@
         <v>120</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="D23" s="28" t="s">
-        <v>540</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>541</v>
+        <v>527</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>528</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>529</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23">
         <v>113127149166000</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="I23" s="7"/>
     </row>
@@ -11575,28 +11360,28 @@
         <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>54</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11604,28 +11389,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>58</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11665,7 +11450,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="D4" s="1">
         <v>3750</v>
@@ -11681,7 +11466,7 @@
         <v>91469233823349</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11692,10 +11477,10 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>548</v>
+        <v>535</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>536</v>
       </c>
       <c r="E5" s="1">
         <v>2.5</v>
@@ -11708,7 +11493,7 @@
         <v>112048940124762</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11719,10 +11504,10 @@
         <v>103</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>551</v>
+        <v>538</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>539</v>
       </c>
       <c r="E6" s="1">
         <v>3.5</v>
@@ -11735,7 +11520,7 @@
         <v>114920101659350</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11746,10 +11531,10 @@
         <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>554</v>
+        <v>541</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>542</v>
       </c>
       <c r="E7" s="1">
         <v>4.5</v>
@@ -11762,7 +11547,7 @@
         <v>76680071023422</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11773,10 +11558,10 @@
         <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>557</v>
+        <v>544</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>545</v>
       </c>
       <c r="E8" s="1">
         <v>5.5</v>
@@ -11789,7 +11574,7 @@
         <v>98163950325063</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="2"/>
+    <workbookView windowWidth="23760" windowHeight="10305" tabRatio="642" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23760" windowHeight="10305" tabRatio="642" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="705">
   <si>
     <t>子配置键</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t>GemCount=5</t>
+  </si>
+  <si>
+    <t>GiftData</t>
+  </si>
+  <si>
+    <t>Gem=5,Count=5,Time=10</t>
   </si>
   <si>
     <t>索引</t>
@@ -3466,13 +3472,13 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:5">
@@ -3480,10 +3486,10 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
@@ -3491,7 +3497,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -3499,576 +3505,576 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B4" s="2">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B5" s="2">
         <v>122</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B6" s="2">
         <v>520</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B7" s="2">
         <v>2176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B8" s="2">
         <v>9101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B30" s="28" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B33" s="28" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B34" s="28" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B35" s="28" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B36" s="28" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B37" s="28" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B38" s="28" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B39" s="28" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B43" s="29" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B47" s="29" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B49" s="29" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B50" s="29" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B52" s="29" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B53" s="29" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B54" s="29" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B55" s="29" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
   </sheetData>
@@ -4272,9 +4278,15 @@
       <c r="G12" s="17"/>
     </row>
     <row r="13" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="21"/>
+      <c r="A13" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>53</v>
+      </c>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
@@ -4519,19 +4531,19 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.5" spans="1:5">
@@ -4539,30 +4551,30 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.5" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>7</v>
@@ -4580,7 +4592,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:5">
@@ -4595,7 +4607,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.5" spans="1:5">
@@ -4610,7 +4622,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:5">
@@ -4625,7 +4637,7 @@
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:5">
@@ -4640,7 +4652,7 @@
         <v>14</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -4662,19 +4674,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4682,33 +4694,33 @@
         <v>13</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4725,7 +4737,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4742,7 +4754,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4759,7 +4771,7 @@
         <v>3</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4776,7 +4788,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4793,7 +4805,7 @@
         <v>3</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4810,7 +4822,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4827,7 +4839,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4844,7 +4856,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4861,7 +4873,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4878,7 +4890,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4895,7 +4907,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4912,7 +4924,7 @@
         <v>3</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4929,7 +4941,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4946,7 +4958,7 @@
         <v>3</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -4963,7 +4975,7 @@
         <v>3</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -4980,7 +4992,7 @@
         <v>3</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -4997,7 +5009,7 @@
         <v>3</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5014,7 +5026,7 @@
         <v>3</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5031,7 +5043,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5048,7 +5060,7 @@
         <v>3</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -5065,7 +5077,7 @@
         <v>3</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5082,7 +5094,7 @@
         <v>3</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -5099,7 +5111,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5116,7 +5128,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -5133,7 +5145,7 @@
         <v>3</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5150,7 +5162,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5167,7 +5179,7 @@
         <v>3</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -5184,7 +5196,7 @@
         <v>3</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -5201,7 +5213,7 @@
         <v>3</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -5218,7 +5230,7 @@
         <v>3</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -5235,7 +5247,7 @@
         <v>3</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -5252,7 +5264,7 @@
         <v>3</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -5269,7 +5281,7 @@
         <v>3</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -5286,7 +5298,7 @@
         <v>3</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -5303,7 +5315,7 @@
         <v>3</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -5320,7 +5332,7 @@
         <v>3</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -5337,7 +5349,7 @@
         <v>3</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -5354,7 +5366,7 @@
         <v>3</v>
       </c>
       <c r="E41" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -5371,7 +5383,7 @@
         <v>3</v>
       </c>
       <c r="E42" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -5388,7 +5400,7 @@
         <v>3</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -5405,7 +5417,7 @@
         <v>3</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -5422,7 +5434,7 @@
         <v>3</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -5439,7 +5451,7 @@
         <v>3</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -5456,7 +5468,7 @@
         <v>3</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -5473,7 +5485,7 @@
         <v>3</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -5490,7 +5502,7 @@
         <v>3</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -5507,7 +5519,7 @@
         <v>3</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -5524,7 +5536,7 @@
         <v>3</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -5541,7 +5553,7 @@
         <v>3</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -5558,7 +5570,7 @@
         <v>3</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -5575,7 +5587,7 @@
         <v>3</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -5592,7 +5604,7 @@
         <v>3</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -5617,16 +5629,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>5</v>
@@ -5637,24 +5649,24 @@
         <v>13</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>7</v>
@@ -5668,10 +5680,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5682,10 +5694,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5696,10 +5708,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>86</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5710,10 +5722,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5724,10 +5736,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5738,10 +5750,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5752,10 +5764,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5766,10 +5778,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -5780,10 +5792,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5794,10 +5806,10 @@
         <v>10</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5808,10 +5820,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5822,10 +5834,10 @@
         <v>12</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5836,10 +5848,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -5850,10 +5862,10 @@
         <v>14</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -5864,10 +5876,10 @@
         <v>15</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -5878,10 +5890,10 @@
         <v>16</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -5892,10 +5904,10 @@
         <v>17</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5906,10 +5918,10 @@
         <v>18</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -5920,10 +5932,10 @@
         <v>19</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5934,10 +5946,10 @@
         <v>20</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5948,10 +5960,10 @@
         <v>21</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -5962,10 +5974,10 @@
         <v>22</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5976,10 +5988,10 @@
         <v>23</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5990,10 +6002,10 @@
         <v>24</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6004,10 +6016,10 @@
         <v>25</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -6018,10 +6030,10 @@
         <v>26</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -6032,10 +6044,10 @@
         <v>27</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6046,10 +6058,10 @@
         <v>28</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6060,10 +6072,10 @@
         <v>29</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -6074,10 +6086,10 @@
         <v>30</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -6088,10 +6100,10 @@
         <v>31</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -6102,10 +6114,10 @@
         <v>32</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -6116,10 +6128,10 @@
         <v>33</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -6130,10 +6142,10 @@
         <v>34</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -6144,10 +6156,10 @@
         <v>35</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -6158,10 +6170,10 @@
         <v>36</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -6172,10 +6184,10 @@
         <v>37</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -6186,10 +6198,10 @@
         <v>38</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -6200,10 +6212,10 @@
         <v>39</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -6214,10 +6226,10 @@
         <v>40</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -6228,10 +6240,10 @@
         <v>41</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -6242,10 +6254,10 @@
         <v>42</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -6256,10 +6268,10 @@
         <v>43</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -6270,10 +6282,10 @@
         <v>44</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -6284,10 +6296,10 @@
         <v>45</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -6298,10 +6310,10 @@
         <v>46</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -6312,10 +6324,10 @@
         <v>47</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -6326,10 +6338,10 @@
         <v>48</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -6340,10 +6352,10 @@
         <v>49</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -6354,10 +6366,10 @@
         <v>50</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -6368,10 +6380,10 @@
         <v>51</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -6382,10 +6394,10 @@
         <v>52</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -6426,28 +6438,28 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:12">
@@ -6455,48 +6467,48 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>7</v>
@@ -6510,7 +6522,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D4" s="1">
         <v>3</v>
@@ -6523,10 +6535,10 @@
         <v>113244405937302</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:12">
@@ -6537,7 +6549,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D5" s="1">
         <v>4</v>
@@ -6550,10 +6562,10 @@
         <v>105711056874756</v>
       </c>
       <c r="G5" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -6566,7 +6578,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D6" s="1">
         <v>6</v>
@@ -6579,10 +6591,10 @@
         <v>82693303214454</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -6595,7 +6607,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D7" s="1">
         <v>8</v>
@@ -6608,10 +6620,10 @@
         <v>102504658102706</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -6624,7 +6636,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D8" s="1">
         <v>13</v>
@@ -6637,10 +6649,10 @@
         <v>83069096807916</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:12">
@@ -6651,7 +6663,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D9" s="1">
         <v>20</v>
@@ -6664,10 +6676,10 @@
         <v>80534536398974</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I9" s="3"/>
     </row>
@@ -6679,7 +6691,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D10" s="1">
         <v>30</v>
@@ -6692,10 +6704,10 @@
         <v>74246671448525</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I10" s="3"/>
     </row>
@@ -6707,7 +6719,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D11" s="1">
         <v>38</v>
@@ -6720,10 +6732,10 @@
         <v>71499702430100</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I11" s="3"/>
     </row>
@@ -6735,7 +6747,7 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D12" s="1">
         <v>63</v>
@@ -6748,10 +6760,10 @@
         <v>122909083001205</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -6762,7 +6774,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
@@ -6775,10 +6787,10 @@
         <v>128658267266293</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -6789,7 +6801,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D14" s="1">
         <v>150</v>
@@ -6802,10 +6814,10 @@
         <v>134748387119946</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -6816,7 +6828,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D15" s="1">
         <v>188</v>
@@ -6829,10 +6841,10 @@
         <v>131559815185521</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:12">
@@ -6843,7 +6855,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D16" s="1">
         <v>313</v>
@@ -6856,10 +6868,10 @@
         <v>135406755438948</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
@@ -6874,7 +6886,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D17" s="1">
         <v>500</v>
@@ -6887,10 +6899,10 @@
         <v>128433990441931</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
@@ -6905,7 +6917,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D18" s="1">
         <v>750</v>
@@ -6918,10 +6930,10 @@
         <v>86357992624263</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
@@ -6936,7 +6948,7 @@
         <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D19" s="1">
         <v>938</v>
@@ -6949,10 +6961,10 @@
         <v>96128137486525</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -6967,7 +6979,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D20" s="1">
         <v>1563</v>
@@ -6980,10 +6992,10 @@
         <v>131913492630514</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -6998,7 +7010,7 @@
         <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D21" s="1">
         <v>2500</v>
@@ -7011,10 +7023,10 @@
         <v>119579899338192</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -7029,7 +7041,7 @@
         <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D22" s="1">
         <v>3750</v>
@@ -7042,10 +7054,10 @@
         <v>82472089572732</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -7060,7 +7072,7 @@
         <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D23" s="1">
         <v>4688</v>
@@ -7073,10 +7085,10 @@
         <v>104108852156434</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -7091,7 +7103,7 @@
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D24" s="1">
         <v>7800</v>
@@ -7104,10 +7116,10 @@
         <v>79005623120233</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -7122,7 +7134,7 @@
         <v>22</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D25" s="1">
         <v>12480</v>
@@ -7135,10 +7147,10 @@
         <v>97611938478078</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -7153,7 +7165,7 @@
         <v>23</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D26" s="1">
         <v>18720</v>
@@ -7166,10 +7178,10 @@
         <v>81806655827798</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
@@ -7184,7 +7196,7 @@
         <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D27" s="1">
         <v>23400</v>
@@ -7197,10 +7209,10 @@
         <v>105716218867716</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
@@ -7215,7 +7227,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D28" s="1">
         <v>39050</v>
@@ -7228,10 +7240,10 @@
         <v>128411546772202</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -7246,7 +7258,7 @@
         <v>26</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D29" s="1">
         <v>62480</v>
@@ -7259,10 +7271,10 @@
         <v>139465058617680</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -7277,7 +7289,7 @@
         <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D30" s="1">
         <v>93720</v>
@@ -7290,10 +7302,10 @@
         <v>81737011057690</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -7308,7 +7320,7 @@
         <v>28</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D31" s="1">
         <v>117150</v>
@@ -7321,10 +7333,10 @@
         <v>81445862907930</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -7339,7 +7351,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D32" s="1">
         <v>195500</v>
@@ -7352,10 +7364,10 @@
         <v>123098432383687</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -7370,7 +7382,7 @@
         <v>30</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D33" s="1">
         <v>312800</v>
@@ -7383,10 +7395,10 @@
         <v>131796260838154</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7397,7 +7409,7 @@
         <v>31</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D34" s="1">
         <v>469200</v>
@@ -7410,10 +7422,10 @@
         <v>116376878683736</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7424,7 +7436,7 @@
         <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D35" s="1">
         <v>586500</v>
@@ -7437,10 +7449,10 @@
         <v>100558097057142</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:12">
@@ -7451,7 +7463,7 @@
         <v>33</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D36" s="1">
         <v>975000</v>
@@ -7464,10 +7476,10 @@
         <v>92332707761527</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
@@ -7482,7 +7494,7 @@
         <v>34</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D37" s="1">
         <v>1560000</v>
@@ -7495,10 +7507,10 @@
         <v>108895787734224</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7509,7 +7521,7 @@
         <v>35</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D38" s="1">
         <v>2340000</v>
@@ -7522,10 +7534,10 @@
         <v>95471681056681</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" ht="16.5" spans="1:12">
@@ -7536,7 +7548,7 @@
         <v>36</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D39" s="1">
         <v>2925000</v>
@@ -7549,10 +7561,10 @@
         <v>104955598295323</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
@@ -7567,7 +7579,7 @@
         <v>37</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D40" s="1">
         <v>4885000</v>
@@ -7580,10 +7592,10 @@
         <v>103175883366340</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
@@ -7598,7 +7610,7 @@
         <v>38</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D41" s="1">
         <v>7816000</v>
@@ -7611,10 +7623,10 @@
         <v>114247164745798</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7625,7 +7637,7 @@
         <v>39</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D42" s="1">
         <v>11724000</v>
@@ -7638,10 +7650,10 @@
         <v>86017047390182</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7652,7 +7664,7 @@
         <v>40</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D43" s="1">
         <v>14655000</v>
@@ -7665,10 +7677,10 @@
         <v>81373582816266</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7679,7 +7691,7 @@
         <v>41</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D44" s="1">
         <v>24400000</v>
@@ -7692,10 +7704,10 @@
         <v>132788281080826</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7706,7 +7718,7 @@
         <v>42</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D45" s="1">
         <v>39040000</v>
@@ -7719,10 +7731,10 @@
         <v>95162444285252</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7733,7 +7745,7 @@
         <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D46" s="1">
         <v>58560000</v>
@@ -7746,10 +7758,10 @@
         <v>95953438126479</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7760,7 +7772,7 @@
         <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D47" s="1">
         <v>73200000</v>
@@ -7773,10 +7785,10 @@
         <v>112039222887887</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" ht="16.5" spans="1:12">
@@ -7787,7 +7799,7 @@
         <v>45</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D48" s="1">
         <v>122000000</v>
@@ -7800,10 +7812,10 @@
         <v>95377459606647</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -7814,7 +7826,7 @@
         <v>46</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D49" s="1">
         <v>195200000</v>
@@ -7827,10 +7839,10 @@
         <v>113983796605688</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -7841,7 +7853,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D50" s="1">
         <v>292800000</v>
@@ -7854,10 +7866,10 @@
         <v>117157716541352</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -7868,7 +7880,7 @@
         <v>48</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D51" s="1">
         <v>366000000</v>
@@ -7881,10 +7893,10 @@
         <v>100893051807474</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="52" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -7895,7 +7907,7 @@
         <v>49</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D52" s="1">
         <v>610000000</v>
@@ -7908,10 +7920,10 @@
         <v>137999782231090</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -7922,7 +7934,7 @@
         <v>50</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D53" s="1">
         <v>976000000</v>
@@ -7935,10 +7947,10 @@
         <v>127007149281218</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -7949,7 +7961,7 @@
         <v>51</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D54" s="1">
         <v>1464000000</v>
@@ -7962,10 +7974,10 @@
         <v>85273469740405</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -7976,7 +7988,7 @@
         <v>52</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D55" s="1">
         <v>1830000000</v>
@@ -7989,10 +8001,10 @@
         <v>85750403977754</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8003,7 +8015,7 @@
         <v>53</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D56" s="1">
         <v>3050000000</v>
@@ -8016,10 +8028,10 @@
         <v>87658125570749</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8030,7 +8042,7 @@
         <v>54</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D57" s="1">
         <v>4880000000</v>
@@ -8043,10 +8055,10 @@
         <v>71386503893388</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8057,7 +8069,7 @@
         <v>55</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D58" s="1">
         <v>7320000000</v>
@@ -8070,10 +8082,10 @@
         <v>117660867991736</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8084,7 +8096,7 @@
         <v>56</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D59" s="1">
         <v>9150000000</v>
@@ -8097,10 +8109,10 @@
         <v>75602786825729</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8111,7 +8123,7 @@
         <v>57</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D60" s="1">
         <v>15250000000</v>
@@ -8124,10 +8136,10 @@
         <v>97494295137425</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="61" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8138,7 +8150,7 @@
         <v>58</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D61" s="1">
         <v>24400000000</v>
@@ -8151,10 +8163,10 @@
         <v>121387106380169</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="62" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8165,7 +8177,7 @@
         <v>59</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D62" s="1">
         <v>36600000000</v>
@@ -8178,10 +8190,10 @@
         <v>77703154963129</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8192,7 +8204,7 @@
         <v>60</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D63" s="1">
         <v>45750000000</v>
@@ -8205,10 +8217,10 @@
         <v>82745313217810</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8219,7 +8231,7 @@
         <v>61</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D64" s="1">
         <v>76500000000</v>
@@ -8232,10 +8244,10 @@
         <v>78702263483439</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8246,7 +8258,7 @@
         <v>62</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D65" s="1">
         <v>122400000000</v>
@@ -8259,10 +8271,10 @@
         <v>103252845267522</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="66" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8273,7 +8285,7 @@
         <v>63</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D66" s="1">
         <v>183600000000</v>
@@ -8286,10 +8298,10 @@
         <v>93380659059014</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8300,7 +8312,7 @@
         <v>64</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D67" s="1">
         <v>229500000000</v>
@@ -8313,10 +8325,10 @@
         <v>124070618735034</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="68" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8327,7 +8339,7 @@
         <v>65</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D68" s="1">
         <v>381500000000</v>
@@ -8340,10 +8352,10 @@
         <v>82229267783572</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8354,7 +8366,7 @@
         <v>66</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D69" s="1">
         <v>610400000000</v>
@@ -8367,10 +8379,10 @@
         <v>90764663625426</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="70" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8381,7 +8393,7 @@
         <v>67</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D70" s="1">
         <v>915600000000</v>
@@ -8394,10 +8406,10 @@
         <v>89592774326120</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="71" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8408,7 +8420,7 @@
         <v>68</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D71" s="1">
         <v>1144500000000</v>
@@ -8421,10 +8433,10 @@
         <v>96498729983354</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="72" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8435,7 +8447,7 @@
         <v>69</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D72" s="1">
         <v>1905000000000</v>
@@ -8448,10 +8460,10 @@
         <v>137402232463633</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="73" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8462,7 +8474,7 @@
         <v>70</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D73" s="1">
         <v>3048000000000</v>
@@ -8475,10 +8487,10 @@
         <v>79717469784936</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8489,7 +8501,7 @@
         <v>71</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D74" s="1">
         <v>4572000000000</v>
@@ -8502,10 +8514,10 @@
         <v>86646811474956</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="75" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8516,7 +8528,7 @@
         <v>72</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D75" s="1">
         <v>5715000000000</v>
@@ -8529,10 +8541,10 @@
         <v>128217347353354</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8543,7 +8555,7 @@
         <v>73</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D76" s="1">
         <v>9550000000000</v>
@@ -8556,10 +8568,10 @@
         <v>126321668579357</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="77" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8570,7 +8582,7 @@
         <v>74</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D77" s="1">
         <v>15280000000000</v>
@@ -8583,10 +8595,10 @@
         <v>98351529529203</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="78" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8597,7 +8609,7 @@
         <v>75</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D78" s="1">
         <v>22920000000000</v>
@@ -8610,10 +8622,10 @@
         <v>81048668172712</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="79" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8624,7 +8636,7 @@
         <v>76</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D79" s="1">
         <v>28650000000000</v>
@@ -8637,10 +8649,10 @@
         <v>127615544859575</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8651,7 +8663,7 @@
         <v>77</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D80" s="1">
         <v>47700000000000</v>
@@ -8664,10 +8676,10 @@
         <v>70656304136373</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8678,7 +8690,7 @@
         <v>78</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D81" s="1">
         <v>76320000000000</v>
@@ -8691,10 +8703,10 @@
         <v>134424174805013</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="82" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8705,7 +8717,7 @@
         <v>79</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D82" s="1">
         <v>114480000000000</v>
@@ -8718,10 +8730,10 @@
         <v>127255485663084</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="83" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8732,7 +8744,7 @@
         <v>80</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D83" s="1">
         <v>143100000000000</v>
@@ -8745,10 +8757,10 @@
         <v>134027683373658</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="84" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8759,7 +8771,7 @@
         <v>81</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D84" s="1">
         <v>238500000000000</v>
@@ -8772,10 +8784,10 @@
         <v>112447657334137</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="85" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8786,7 +8798,7 @@
         <v>82</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D85" s="1">
         <v>381600000000000</v>
@@ -8799,10 +8811,10 @@
         <v>104595008892706</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="86" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8813,7 +8825,7 @@
         <v>83</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D86" s="1">
         <v>572400000000000</v>
@@ -8826,10 +8838,10 @@
         <v>82759045606098</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="87" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8840,7 +8852,7 @@
         <v>84</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D87" s="1">
         <v>715500000000000</v>
@@ -8853,10 +8865,10 @@
         <v>105620837789519</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="88" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8867,7 +8879,7 @@
         <v>85</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D88" s="1">
         <v>1190000000000000</v>
@@ -8880,10 +8892,10 @@
         <v>111024567754480</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="89" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8894,7 +8906,7 @@
         <v>86</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D89" s="1">
         <v>1904000000000000</v>
@@ -8907,10 +8919,10 @@
         <v>137153989969007</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="90" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8921,7 +8933,7 @@
         <v>87</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D90" s="1">
         <v>2856000000000000</v>
@@ -8934,10 +8946,10 @@
         <v>74496996195913</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="91" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8948,7 +8960,7 @@
         <v>88</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D91" s="1">
         <v>3570000000000000</v>
@@ -8961,10 +8973,10 @@
         <v>132785860315163</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="92" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -8975,7 +8987,7 @@
         <v>89</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D92" s="1">
         <v>5950000000000000</v>
@@ -8988,10 +9000,10 @@
         <v>117198962948319</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="93" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9002,7 +9014,7 @@
         <v>90</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D93" s="1">
         <v>9520000000000000</v>
@@ -9015,10 +9027,10 @@
         <v>124449160476895</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="94" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9029,7 +9041,7 @@
         <v>91</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D94" s="1">
         <v>1.428e+16</v>
@@ -9042,10 +9054,10 @@
         <v>125887863438527</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="95" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9056,7 +9068,7 @@
         <v>92</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D95" s="1">
         <v>1.785e+16</v>
@@ -9069,10 +9081,10 @@
         <v>137692564728429</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="96" s="3" customFormat="1" ht="16.5" spans="1:8">
@@ -9083,7 +9095,7 @@
         <v>93</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D96" s="1">
         <v>2.98e+16</v>
@@ -9096,10 +9108,10 @@
         <v>82350951870220</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9110,7 +9122,7 @@
         <v>94</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D97" s="1">
         <v>4.768e+16</v>
@@ -9123,10 +9135,10 @@
         <v>133019385929561</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="98" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9137,7 +9149,7 @@
         <v>95</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D98" s="1">
         <v>7.152e+16</v>
@@ -9150,10 +9162,10 @@
         <v>82714807302588</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="99" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9164,7 +9176,7 @@
         <v>96</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D99" s="1">
         <v>8.94e+16</v>
@@ -9177,10 +9189,10 @@
         <v>120409278538446</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="100" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9191,7 +9203,7 @@
         <v>97</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D100" s="1">
         <v>1.49e+17</v>
@@ -9204,10 +9216,10 @@
         <v>136303201068741</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="101" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9218,7 +9230,7 @@
         <v>98</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D101" s="1">
         <v>2.384e+17</v>
@@ -9231,10 +9243,10 @@
         <v>76724781858184</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="102" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9245,7 +9257,7 @@
         <v>99</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D102" s="1">
         <v>3.576e+17</v>
@@ -9258,10 +9270,10 @@
         <v>120125979830927</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="103" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9272,7 +9284,7 @@
         <v>100</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D103" s="1">
         <v>4.47e+17</v>
@@ -9285,10 +9297,10 @@
         <v>86921870572603</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="104" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9299,7 +9311,7 @@
         <v>101</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D104" s="1">
         <v>7.45e+17</v>
@@ -9312,10 +9324,10 @@
         <v>126355990231048</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="105" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9326,7 +9338,7 @@
         <v>102</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D105" s="1">
         <v>1.192e+18</v>
@@ -9339,10 +9351,10 @@
         <v>72326444062448</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="106" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9353,7 +9365,7 @@
         <v>103</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D106" s="1">
         <v>1.788e+18</v>
@@ -9366,10 +9378,10 @@
         <v>72257499044823</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="107" s="3" customFormat="1" ht="16.5" spans="1:9">
@@ -9380,7 +9392,7 @@
         <v>104</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D107" s="1">
         <v>2.235e+18</v>
@@ -9393,10 +9405,10 @@
         <v>74695865349139</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="108" ht="16.5" spans="1:9">
@@ -9407,7 +9419,7 @@
         <v>105</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D108" s="1">
         <v>3.725e+18</v>
@@ -9419,10 +9431,10 @@
         <v>98358488442985</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I108" s="3"/>
     </row>
@@ -9434,7 +9446,7 @@
         <v>106</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D109" s="1">
         <v>5.96e+18</v>
@@ -9446,10 +9458,10 @@
         <v>113636295509693</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I109" s="3"/>
     </row>
@@ -9461,7 +9473,7 @@
         <v>107</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D110" s="1">
         <v>8.94e+18</v>
@@ -9473,10 +9485,10 @@
         <v>114047124407739</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I110" s="3"/>
     </row>
@@ -9488,7 +9500,7 @@
         <v>108</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D111" s="1">
         <v>1.1175e+19</v>
@@ -9500,10 +9512,10 @@
         <v>95771403493939</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I111" s="3"/>
     </row>
@@ -9515,7 +9527,7 @@
         <v>109</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D112" s="1">
         <v>1.865e+19</v>
@@ -9527,10 +9539,10 @@
         <v>140393673870516</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I112" s="3"/>
     </row>
@@ -9542,7 +9554,7 @@
         <v>110</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D113" s="1">
         <v>2.984e+19</v>
@@ -9554,10 +9566,10 @@
         <v>123109322631502</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I113" s="3"/>
     </row>
@@ -9569,7 +9581,7 @@
         <v>111</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D114" s="1">
         <v>4.476e+19</v>
@@ -9581,10 +9593,10 @@
         <v>98614967981417</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I114" s="3"/>
     </row>
@@ -9596,7 +9608,7 @@
         <v>112</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D115" s="1">
         <v>5.595e+19</v>
@@ -9608,10 +9620,10 @@
         <v>127369769981706</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I115" s="3"/>
     </row>
@@ -9623,7 +9635,7 @@
         <v>113</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D116" s="1">
         <v>9.3e+19</v>
@@ -9635,10 +9647,10 @@
         <v>134574393827781</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I116" s="3"/>
     </row>
@@ -9650,7 +9662,7 @@
         <v>114</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D117" s="1">
         <v>1.488e+20</v>
@@ -9662,10 +9674,10 @@
         <v>130258203281991</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I117" s="3"/>
     </row>
@@ -9677,7 +9689,7 @@
         <v>115</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D118" s="1">
         <v>2.232e+20</v>
@@ -9689,10 +9701,10 @@
         <v>93953823085119</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I118" s="3"/>
     </row>
@@ -9704,7 +9716,7 @@
         <v>116</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D119" s="1">
         <v>2.79e+20</v>
@@ -9716,10 +9728,10 @@
         <v>109802560542166</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I119" s="3"/>
     </row>
@@ -9731,7 +9743,7 @@
         <v>117</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D120" s="1">
         <v>4.655e+20</v>
@@ -9743,10 +9755,10 @@
         <v>130989494782889</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I120" s="3"/>
     </row>
@@ -9758,7 +9770,7 @@
         <v>118</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D121" s="1">
         <v>7.448e+20</v>
@@ -9770,10 +9782,10 @@
         <v>129408716253336</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I121" s="3"/>
     </row>
@@ -9785,7 +9797,7 @@
         <v>119</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D122" s="1">
         <v>1.1172e+21</v>
@@ -9797,10 +9809,10 @@
         <v>127772866805590</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I122" s="3"/>
     </row>
@@ -9812,7 +9824,7 @@
         <v>120</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D123" s="1">
         <v>1.3965e+21</v>
@@ -9824,10 +9836,10 @@
         <v>91938109188463</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I123" s="3"/>
     </row>
@@ -9839,7 +9851,7 @@
         <v>121</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D124" s="1">
         <v>2.33e+21</v>
@@ -9851,10 +9863,10 @@
         <v>85077262752129</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I124" s="3"/>
     </row>
@@ -9866,7 +9878,7 @@
         <v>122</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D125" s="1">
         <v>3.728e+21</v>
@@ -9878,10 +9890,10 @@
         <v>140335958193244</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126" ht="16.5" spans="1:9">
@@ -9892,7 +9904,7 @@
         <v>123</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D126" s="1">
         <v>5.592e+21</v>
@@ -9904,10 +9916,10 @@
         <v>86732012145983</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="127" ht="16.5" spans="1:9">
@@ -9918,7 +9930,7 @@
         <v>124</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D127" s="1">
         <v>6.99e+21</v>
@@ -9930,10 +9942,10 @@
         <v>78044122276865</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="128" ht="16.5" spans="1:9">
@@ -9944,7 +9956,7 @@
         <v>125</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D128" s="1">
         <v>1.165e+22</v>
@@ -9956,10 +9968,10 @@
         <v>114974638199136</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="129" ht="16.5" spans="1:8">
@@ -9970,7 +9982,7 @@
         <v>126</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D129" s="1">
         <v>1.864e+22</v>
@@ -9982,10 +9994,10 @@
         <v>83652207307759</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="130" ht="16.5" spans="1:8">
@@ -9996,7 +10008,7 @@
         <v>127</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D130" s="1">
         <v>2.796e+22</v>
@@ -10008,10 +10020,10 @@
         <v>131787091355052</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="131" ht="16.5" spans="1:8">
@@ -10022,7 +10034,7 @@
         <v>128</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D131" s="1">
         <v>3.495e+22</v>
@@ -10034,10 +10046,10 @@
         <v>99348381699835</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="132" ht="16.5" spans="1:8">
@@ -10048,7 +10060,7 @@
         <v>129</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D132" s="1">
         <v>5.8e+22</v>
@@ -10060,10 +10072,10 @@
         <v>75412160560516</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="133" ht="16.5" spans="1:8">
@@ -10074,7 +10086,7 @@
         <v>130</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D133" s="1">
         <v>9.28e+22</v>
@@ -10086,10 +10098,10 @@
         <v>105475505052937</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="134" ht="16.5" spans="1:8">
@@ -10100,7 +10112,7 @@
         <v>131</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D134" s="1">
         <v>1.392e+23</v>
@@ -10112,10 +10124,10 @@
         <v>125484119033793</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="135" ht="16.5" spans="1:8">
@@ -10126,7 +10138,7 @@
         <v>132</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D135" s="1">
         <v>1.74e+23</v>
@@ -10138,10 +10150,10 @@
         <v>140608831780254</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="136" ht="16.5" spans="1:8">
@@ -10152,7 +10164,7 @@
         <v>133</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D136" s="1">
         <v>2.91e+23</v>
@@ -10164,10 +10176,10 @@
         <v>124177358025481</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="137" ht="16.5" spans="1:8">
@@ -10178,7 +10190,7 @@
         <v>134</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D137" s="1">
         <v>4.656e+23</v>
@@ -10190,10 +10202,10 @@
         <v>129385390119523</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="138" ht="16.5" spans="1:8">
@@ -10204,7 +10216,7 @@
         <v>135</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D138" s="1">
         <v>6.984e+23</v>
@@ -10216,10 +10228,10 @@
         <v>84940520003035</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="139" ht="16.5" spans="1:8">
@@ -10230,7 +10242,7 @@
         <v>136</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D139" s="1">
         <v>8.73e+23</v>
@@ -10242,10 +10254,10 @@
         <v>90031364711610</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="140" ht="16.5" spans="1:8">
@@ -10256,7 +10268,7 @@
         <v>137</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D140" s="1">
         <v>1.455e+24</v>
@@ -10268,10 +10280,10 @@
         <v>84418341821320</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="141" ht="16.5" spans="1:8">
@@ -10282,7 +10294,7 @@
         <v>138</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D141" s="1">
         <v>2.328e+24</v>
@@ -10294,10 +10306,10 @@
         <v>130255705800444</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="142" ht="16.5" spans="1:8">
@@ -10308,7 +10320,7 @@
         <v>139</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D142" s="1">
         <v>3.492e+24</v>
@@ -10320,10 +10332,10 @@
         <v>123568265278671</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="143" ht="16.5" spans="1:8">
@@ -10334,7 +10346,7 @@
         <v>140</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D143" s="1">
         <v>4.365e+24</v>
@@ -10346,10 +10358,10 @@
         <v>75689117044416</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="144" ht="16.5" spans="1:8">
@@ -10360,7 +10372,7 @@
         <v>141</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D144" s="1">
         <v>7.3e+24</v>
@@ -10372,10 +10384,10 @@
         <v>92309488435591</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="145" ht="16.5" spans="1:8">
@@ -10386,7 +10398,7 @@
         <v>142</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D145" s="1">
         <v>1.168e+25</v>
@@ -10398,10 +10410,10 @@
         <v>106319308889290</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="146" ht="16.5" spans="1:8">
@@ -10412,7 +10424,7 @@
         <v>143</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D146" s="1">
         <v>1.752e+25</v>
@@ -10424,10 +10436,10 @@
         <v>123120949699520</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="147" ht="16.5" spans="1:8">
@@ -10438,7 +10450,7 @@
         <v>144</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D147" s="1">
         <v>2.19e+25</v>
@@ -10450,10 +10462,10 @@
         <v>111674856010497</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="148" ht="16.5" spans="1:8">
@@ -10464,7 +10476,7 @@
         <v>145</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D148" s="1">
         <v>3.64e+25</v>
@@ -10476,10 +10488,10 @@
         <v>118080816505555</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="149" ht="16.5" spans="1:8">
@@ -10490,7 +10502,7 @@
         <v>146</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D149" s="1">
         <v>5.824e+25</v>
@@ -10502,10 +10514,10 @@
         <v>105021574817966</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="150" ht="16.5" spans="1:8">
@@ -10516,7 +10528,7 @@
         <v>147</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D150" s="1">
         <v>8.736e+25</v>
@@ -10528,10 +10540,10 @@
         <v>72690180103558</v>
       </c>
       <c r="G150" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="151" ht="16.5" spans="1:8">
@@ -10542,7 +10554,7 @@
         <v>148</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D151" s="1">
         <v>1.092e+26</v>
@@ -10554,10 +10566,10 @@
         <v>94914272618995</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -10578,13 +10590,13 @@
   <sheetData>
     <row r="1" customFormat="1" ht="16.5" spans="1:3">
       <c r="A1" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="16.5" spans="1:3">
@@ -10592,21 +10604,21 @@
         <v>13</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="16.5" spans="1:3">
       <c r="A3" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="16.5" spans="1:3">
@@ -10757,28 +10769,28 @@
   <sheetData>
     <row r="1" customFormat="1" ht="16.5" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="16.5" spans="1:9">
@@ -10786,48 +10798,48 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="16.5" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>7</v>
@@ -10841,7 +10853,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -10854,7 +10866,7 @@
         <v>99853650045862</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I4" s="7"/>
     </row>
@@ -10866,7 +10878,7 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D5" s="1">
         <v>25</v>
@@ -10879,7 +10891,7 @@
         <v>116225665846279</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="I5" s="7"/>
     </row>
@@ -10891,7 +10903,7 @@
         <v>103</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D6" s="1">
         <v>450</v>
@@ -10904,7 +10916,7 @@
         <v>136956773152573</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I6" s="7"/>
     </row>
@@ -10916,7 +10928,7 @@
         <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D7" s="1">
         <v>4375</v>
@@ -10929,7 +10941,7 @@
         <v>97553870039023</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="I7" s="7"/>
     </row>
@@ -10941,20 +10953,20 @@
         <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8">
         <v>118090700645855</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="I8" s="7"/>
     </row>
@@ -10966,20 +10978,20 @@
         <v>106</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9">
         <v>138508042210191</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="I9" s="7"/>
     </row>
@@ -10991,20 +11003,20 @@
         <v>107</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10">
         <v>78371166922896</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="I10" s="7"/>
     </row>
@@ -11016,20 +11028,20 @@
         <v>108</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11">
         <v>132966760008713</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="I11" s="7"/>
     </row>
@@ -11041,20 +11053,20 @@
         <v>109</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12">
         <v>133927008310944</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="I12" s="7"/>
     </row>
@@ -11066,20 +11078,20 @@
         <v>110</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13">
         <v>98415179467911</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="I13" s="7"/>
     </row>
@@ -11091,20 +11103,20 @@
         <v>111</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14">
         <v>79276409476682</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="I14" s="7"/>
     </row>
@@ -11116,20 +11128,20 @@
         <v>112</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E15" s="27" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15">
         <v>86184044773576</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I15" s="7"/>
     </row>
@@ -11141,20 +11153,20 @@
         <v>113</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E16" s="27" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16">
         <v>85964386896273</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="I16" s="7"/>
     </row>
@@ -11166,20 +11178,20 @@
         <v>114</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17">
         <v>121813166897471</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -11191,20 +11203,20 @@
         <v>115</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18">
         <v>107669574278873</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="I18" s="7"/>
     </row>
@@ -11216,20 +11228,20 @@
         <v>116</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E19" s="27" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19">
         <v>98723580431394</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="I19" s="7"/>
     </row>
@@ -11241,20 +11253,20 @@
         <v>117</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E20" s="27" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20">
         <v>126241505230536</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="I20" s="7"/>
     </row>
@@ -11266,20 +11278,20 @@
         <v>118</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21">
         <v>78092021290844</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="I21" s="7"/>
     </row>
@@ -11291,20 +11303,20 @@
         <v>119</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E22" s="27" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22">
         <v>138731887343821</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="I22" s="7"/>
     </row>
@@ -11316,20 +11328,20 @@
         <v>120</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23">
         <v>113127149166000</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I23" s="7"/>
     </row>
@@ -11357,31 +11369,31 @@
   <sheetData>
     <row r="1" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11389,51 +11401,51 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>7</v>
@@ -11450,7 +11462,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D4" s="1">
         <v>3750</v>
@@ -11466,7 +11478,7 @@
         <v>91469233823349</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11477,10 +11489,10 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E5" s="1">
         <v>2.5</v>
@@ -11493,7 +11505,7 @@
         <v>112048940124762</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11504,10 +11516,10 @@
         <v>103</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E6" s="1">
         <v>3.5</v>
@@ -11520,7 +11532,7 @@
         <v>114920101659350</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11531,10 +11543,10 @@
         <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E7" s="1">
         <v>4.5</v>
@@ -11547,7 +11559,7 @@
         <v>76680071023422</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11558,10 +11570,10 @@
         <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E8" s="1">
         <v>5.5</v>
@@ -11574,7 +11586,7 @@
         <v>98163950325063</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -242,19 +242,19 @@
     <t>number_option</t>
   </si>
   <si>
-    <t>game.Workspace.BlockMeshs["世界1"].TrainingCenter.Training1</t>
-  </si>
-  <si>
-    <t>game.Workspace.BlockMeshs["世界1"].TrainingCenter.Training2</t>
-  </si>
-  <si>
-    <t>game.Workspace.BlockMeshs["世界1"].TrainingCenter.Training3</t>
-  </si>
-  <si>
-    <t>game.Workspace.BlockMeshs["世界1"].TrainingCenter.Training4</t>
-  </si>
-  <si>
-    <t>game.Workspace.BlockMeshs["世界1"].TrainingCenter.Training5</t>
+    <t>game.Workspace.BlockMeshs.World1Root.TrainingCenter.Training1</t>
+  </si>
+  <si>
+    <t>game.Workspace.BlockMeshs.World1Root.TrainingCenter.Training2</t>
+  </si>
+  <si>
+    <t>game.Workspace.BlockMeshs.World1Root.TrainingCenter.Training3</t>
+  </si>
+  <si>
+    <t>game.Workspace.BlockMeshs.World1Root.TrainingCenter.Training4</t>
+  </si>
+  <si>
+    <t>game.Workspace.BlockMeshs.World1Root.TrainingCenter.Training5</t>
   </si>
   <si>
     <t>组ID</t>

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="742">
   <si>
     <t>子配置键</t>
   </si>
@@ -1646,6 +1646,9 @@
     <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["20GildedCrownGreatHammer"]</t>
   </si>
   <si>
+    <t>图片</t>
+  </si>
+  <si>
     <t>图片ID</t>
   </si>
   <si>
@@ -1661,37 +1664,145 @@
     <t>Uncommon</t>
   </si>
   <si>
-    <t>1.38e+6</t>
-  </si>
-  <si>
     <t>game.ReplicatedStorage.Assets.Effects.Aura["02_Uncommon"]</t>
   </si>
   <si>
+    <t>Toxic</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["03_Toxic"]</t>
+  </si>
+  <si>
     <t>Rare</t>
   </si>
   <si>
-    <t>3.32e+8</t>
-  </si>
-  <si>
-    <t>game.ReplicatedStorage.Assets.Effects.Aura["03_Rare"]</t>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["04_Rare"]</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["05_Bronze"]</t>
+  </si>
+  <si>
+    <t>Abyss</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["06_Abyss"]</t>
+  </si>
+  <si>
+    <t>Void</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["07_Void"]</t>
+  </si>
+  <si>
+    <t>Crimson</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["08_Crimson"]</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["09_Silver"]</t>
   </si>
   <si>
     <t>Epic</t>
   </si>
   <si>
-    <t>7.30e+10</t>
-  </si>
-  <si>
-    <t>game.ReplicatedStorage.Assets.Effects.Aura["04_Epic"]</t>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["10_Epic"]</t>
+  </si>
+  <si>
+    <t>Ocean</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["11_Ocean"]</t>
+  </si>
+  <si>
+    <t>Lunar</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["12_Lunar"]</t>
   </si>
   <si>
     <t>Legendary</t>
   </si>
   <si>
-    <t>1.42e+13</t>
-  </si>
-  <si>
-    <t>game.ReplicatedStorage.Assets.Effects.Aura["05_Legendary"]</t>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["13_Legendary"]</t>
+  </si>
+  <si>
+    <t>Emerald</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["14_Emerald"]</t>
+  </si>
+  <si>
+    <t>Sapphire</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["15_Sapphire"]</t>
+  </si>
+  <si>
+    <t>Ruby</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["16_Ruby"]</t>
+  </si>
+  <si>
+    <t>Sakura</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["17_Sakura"]</t>
+  </si>
+  <si>
+    <t>Sunset</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["18_Sunset"]</t>
+  </si>
+  <si>
+    <t>Frost</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["19_Frost"]</t>
+  </si>
+  <si>
+    <t>Inferno</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["20_Inferno"]</t>
+  </si>
+  <si>
+    <t>Storm</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["21_Storm"]</t>
+  </si>
+  <si>
+    <t>Solar</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["22_Solar"]</t>
+  </si>
+  <si>
+    <t>Neon</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["23_Neon"]</t>
+  </si>
+  <si>
+    <t>Prismatic</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["24_Prismatic"]</t>
+  </si>
+  <si>
+    <t>Astral</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.Effects.Aura["25_Astral"]</t>
   </si>
   <si>
     <t>关卡Id</t>
@@ -2172,7 +2283,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2184,11 +2295,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2704,13 +2810,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2719,122 +2828,119 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2847,73 +2953,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="fill" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="fill" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -3250,62 +3350,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="20" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="26" customHeight="1" spans="1:6">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="20" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3322,7 +3422,7 @@
       <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="23" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
@@ -3342,7 +3442,7 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="24" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3359,7 +3459,7 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="23" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3376,7 +3476,7 @@
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="23" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
@@ -3396,7 +3496,7 @@
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="24" t="s">
         <v>21</v>
       </c>
       <c r="F8" t="s">
@@ -3416,7 +3516,7 @@
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="24" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
@@ -3436,7 +3536,7 @@
       <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="23" t="s">
         <v>25</v>
       </c>
       <c r="F10" t="s">
@@ -3472,13 +3572,13 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>549</v>
+        <v>586</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>550</v>
+        <v>587</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>551</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:5">
@@ -3486,10 +3586,10 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>552</v>
+        <v>589</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>553</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
@@ -3505,576 +3605,576 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>554</v>
+        <v>591</v>
       </c>
       <c r="B4" s="2">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>555</v>
+        <v>592</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>556</v>
+        <v>593</v>
       </c>
       <c r="B5" s="2">
         <v>122</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>558</v>
+        <v>595</v>
       </c>
       <c r="B6" s="2">
         <v>520</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>559</v>
+        <v>596</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>560</v>
+        <v>597</v>
       </c>
       <c r="B7" s="2">
         <v>2176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>561</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>562</v>
+        <v>599</v>
       </c>
       <c r="B8" s="2">
         <v>9101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>563</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>565</v>
+        <v>601</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>602</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>566</v>
+        <v>603</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>568</v>
+        <v>604</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>605</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>569</v>
+        <v>606</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>571</v>
+        <v>607</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>608</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>572</v>
+        <v>609</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>574</v>
+        <v>610</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>611</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>575</v>
+        <v>612</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>577</v>
+        <v>613</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>614</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>578</v>
+        <v>615</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>580</v>
+        <v>616</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>617</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>581</v>
+        <v>618</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>583</v>
+        <v>619</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>620</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>584</v>
+        <v>621</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>586</v>
+        <v>622</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>623</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>587</v>
+        <v>624</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>589</v>
+        <v>625</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>626</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>590</v>
+        <v>627</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>592</v>
+        <v>628</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>629</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>593</v>
+        <v>630</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>595</v>
+        <v>631</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>632</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>596</v>
+        <v>633</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>598</v>
+        <v>634</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>635</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>599</v>
+        <v>636</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>601</v>
+        <v>637</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>638</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>602</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="B22" s="28" t="s">
-        <v>604</v>
+        <v>640</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>641</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>605</v>
+        <v>642</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>607</v>
+        <v>643</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>644</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>608</v>
+        <v>645</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>610</v>
+        <v>646</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>647</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>611</v>
+        <v>648</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="B25" s="28" t="s">
-        <v>613</v>
+        <v>649</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>650</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>614</v>
+        <v>651</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>616</v>
+        <v>652</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>653</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>617</v>
+        <v>654</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>619</v>
+        <v>655</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>656</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>620</v>
+        <v>657</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>622</v>
+        <v>658</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>659</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>623</v>
+        <v>660</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="B29" s="28" t="s">
-        <v>625</v>
+        <v>661</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>662</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>626</v>
+        <v>663</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>628</v>
+        <v>664</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>665</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>629</v>
+        <v>666</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>631</v>
+        <v>667</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>668</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>632</v>
+        <v>669</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>634</v>
+        <v>670</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>671</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>635</v>
+        <v>672</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>637</v>
+        <v>673</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>674</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>638</v>
+        <v>675</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="B34" s="28" t="s">
-        <v>640</v>
+        <v>676</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>677</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>641</v>
+        <v>678</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="B35" s="28" t="s">
-        <v>643</v>
+        <v>679</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>680</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>644</v>
+        <v>681</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="B36" s="28" t="s">
-        <v>646</v>
+        <v>682</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>683</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>647</v>
+        <v>684</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="B37" s="28" t="s">
-        <v>649</v>
+        <v>685</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>686</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>652</v>
+        <v>688</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>689</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>653</v>
+        <v>690</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>655</v>
+        <v>691</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>692</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>656</v>
+        <v>693</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="B40" s="28" t="s">
-        <v>658</v>
+        <v>694</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>695</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>659</v>
+        <v>696</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>661</v>
+        <v>697</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>698</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>662</v>
+        <v>699</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="B42" s="28" t="s">
-        <v>664</v>
+        <v>700</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>701</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>665</v>
+        <v>702</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="B43" s="29" t="s">
-        <v>667</v>
+        <v>703</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>704</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="B44" s="29" t="s">
-        <v>670</v>
+        <v>706</v>
+      </c>
+      <c r="B44" s="27" t="s">
+        <v>707</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>671</v>
+        <v>708</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="B45" s="29" t="s">
-        <v>673</v>
+        <v>709</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>710</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>674</v>
+        <v>711</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B46" s="29" t="s">
-        <v>676</v>
+        <v>712</v>
+      </c>
+      <c r="B46" s="27" t="s">
+        <v>713</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="B47" s="29" t="s">
-        <v>679</v>
+        <v>715</v>
+      </c>
+      <c r="B47" s="27" t="s">
+        <v>716</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="B48" s="29" t="s">
-        <v>682</v>
+        <v>718</v>
+      </c>
+      <c r="B48" s="27" t="s">
+        <v>719</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>683</v>
+        <v>720</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>684</v>
-      </c>
-      <c r="B49" s="29" t="s">
-        <v>685</v>
+        <v>721</v>
+      </c>
+      <c r="B49" s="27" t="s">
+        <v>722</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>686</v>
+        <v>723</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="B50" s="29" t="s">
-        <v>688</v>
+        <v>724</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>725</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>689</v>
+        <v>726</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="B51" s="29" t="s">
-        <v>691</v>
+        <v>727</v>
+      </c>
+      <c r="B51" s="27" t="s">
+        <v>728</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>692</v>
+        <v>729</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="B52" s="29" t="s">
-        <v>694</v>
+        <v>730</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>731</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>695</v>
+        <v>732</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="B53" s="29" t="s">
-        <v>697</v>
+        <v>733</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>734</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>698</v>
+        <v>735</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="B54" s="29" t="s">
-        <v>700</v>
+        <v>736</v>
+      </c>
+      <c r="B54" s="27" t="s">
+        <v>737</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>701</v>
+        <v>738</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="B55" s="29" t="s">
-        <v>703</v>
+        <v>739</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>740</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>704</v>
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -4089,395 +4189,395 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="44.175" style="16" customWidth="1"/>
-    <col min="2" max="2" width="71.3583333333333" style="16" customWidth="1"/>
-    <col min="3" max="3" width="123.558333333333" style="16" customWidth="1"/>
-    <col min="4" max="4" width="82.8666666666667" style="16" customWidth="1"/>
-    <col min="5" max="6" width="9" style="16"/>
-    <col min="7" max="7" width="81.1833333333333" style="16" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="16"/>
+    <col min="1" max="1" width="44.175" style="14" customWidth="1"/>
+    <col min="2" max="2" width="71.3583333333333" style="14" customWidth="1"/>
+    <col min="3" max="3" width="123.558333333333" style="14" customWidth="1"/>
+    <col min="4" max="4" width="82.8666666666667" style="14" customWidth="1"/>
+    <col min="5" max="6" width="9" style="14"/>
+    <col min="7" max="7" width="81.1833333333333" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" s="16" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
-      <c r="A1" s="17" t="s">
+    <row r="1" s="14" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
+      <c r="A1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
-    <row r="2" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+    <row r="2" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
-    <row r="3" s="16" customFormat="1" ht="91" customHeight="1" spans="1:7">
-      <c r="A3" s="17" t="s">
+    <row r="3" s="14" customFormat="1" ht="91" customHeight="1" spans="1:7">
+      <c r="A3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
     </row>
-    <row r="4" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A4" s="17" t="s">
+    <row r="4" s="14" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A4" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
     </row>
-    <row r="5" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A5" s="17" t="s">
+    <row r="5" s="14" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A5" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="15">
         <v>10</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
     </row>
-    <row r="6" s="16" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A6" s="17" t="s">
+    <row r="6" s="14" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A6" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
     </row>
-    <row r="7" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A7" s="19" t="s">
+    <row r="7" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
     </row>
-    <row r="8" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A8" s="19" t="s">
+    <row r="8" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A8" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
     </row>
-    <row r="9" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A9" s="19" t="s">
+    <row r="9" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A9" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
     </row>
-    <row r="10" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A10" s="17" t="s">
+    <row r="10" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A10" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
     </row>
-    <row r="11" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A11" s="17" t="s">
+    <row r="11" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A11" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
     </row>
-    <row r="12" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A12" s="17" t="s">
+    <row r="12" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A12" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
     </row>
-    <row r="13" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A13" s="17" t="s">
+    <row r="13" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A13" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
     </row>
-    <row r="14" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
+    <row r="14" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
     </row>
-    <row r="15" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+    <row r="15" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
     </row>
-    <row r="16" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
+    <row r="16" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
     </row>
-    <row r="17" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
+    <row r="17" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
     </row>
-    <row r="18" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
+    <row r="18" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
     </row>
-    <row r="19" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+    <row r="19" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
     </row>
-    <row r="20" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+    <row r="20" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
     </row>
-    <row r="21" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
+    <row r="21" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
     </row>
-    <row r="22" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
+    <row r="22" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
     </row>
-    <row r="23" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
+    <row r="23" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
     </row>
-    <row r="24" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
+    <row r="24" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
     </row>
-    <row r="25" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
+    <row r="25" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
     </row>
-    <row r="26" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
+    <row r="26" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
     </row>
-    <row r="27" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="C27" s="17"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
+    <row r="27" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="C27" s="15"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
     </row>
-    <row r="28" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
+    <row r="28" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
     </row>
-    <row r="29" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
+    <row r="29" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
     </row>
-    <row r="30" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
+    <row r="30" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
     </row>
-    <row r="31" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
+    <row r="31" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
     </row>
-    <row r="32" s="16" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
+    <row r="32" s="14" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
     </row>
-    <row r="33" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
+    <row r="33" s="14" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
     </row>
-    <row r="34" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
+    <row r="34" s="14" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
     </row>
-    <row r="35" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
+    <row r="35" s="14" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
     </row>
-    <row r="36" s="16" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
+    <row r="36" s="14" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -4667,943 +4767,943 @@
   <dimension ref="A1:E55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" width="37.75" style="14" customWidth="1"/>
+    <col min="1" max="2" width="37.75" style="12" customWidth="1"/>
     <col min="3" max="3" width="33.0833333333333" customWidth="1"/>
     <col min="4" max="5" width="40.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="15">
+      <c r="A4" s="13">
         <v>1</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="13">
         <v>1</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <v>80</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="13">
         <v>3</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="15">
+      <c r="A5" s="13">
         <v>2</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="13">
         <v>2</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="13">
         <v>4</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="13">
         <v>3</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="15">
+      <c r="A6" s="13">
         <v>3</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="13">
         <v>3</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="13">
         <v>4</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="13">
         <v>3</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="15">
+      <c r="A7" s="13">
         <v>4</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="13">
         <v>4</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="13">
         <v>4</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="13">
         <v>3</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="15">
+      <c r="A8" s="13">
         <v>5</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="13">
         <v>5</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="13">
         <v>4</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="13">
         <v>3</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="15">
+      <c r="A9" s="13">
         <v>6</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="13">
         <v>6</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="13">
         <v>4</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="13">
         <v>3</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="15">
+      <c r="A10" s="13">
         <v>7</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="13">
         <v>7</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="13">
         <v>4</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="13">
         <v>3</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="15">
+      <c r="A11" s="13">
         <v>8</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="13">
         <v>8</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="13">
         <v>4</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="13">
         <v>3</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="15">
+      <c r="A12" s="13">
         <v>9</v>
       </c>
-      <c r="B12" s="15">
+      <c r="B12" s="13">
         <v>9</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="13">
         <v>4</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="13">
         <v>3</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="15">
+      <c r="A13" s="13">
         <v>10</v>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="13">
         <v>10</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="13">
         <v>4</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="13">
         <v>3</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="15">
+      <c r="A14" s="13">
         <v>11</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="13">
         <v>11</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="13">
         <v>4</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="13">
         <v>3</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="15">
+      <c r="A15" s="13">
         <v>12</v>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="13">
         <v>12</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13">
         <v>4</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13">
         <v>3</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="15">
+      <c r="A16" s="13">
         <v>13</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="13">
         <v>13</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="13">
         <v>4</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="13">
         <v>3</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="15">
+      <c r="A17" s="13">
         <v>14</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="13">
         <v>14</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="13">
         <v>4</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="13">
         <v>3</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="15">
+      <c r="A18" s="13">
         <v>15</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="13">
         <v>15</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13">
         <v>4</v>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="13">
         <v>3</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="15">
+      <c r="A19" s="13">
         <v>16</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="13">
         <v>16</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="13">
         <v>4</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="13">
         <v>3</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="15">
+      <c r="A20" s="13">
         <v>17</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="13">
         <v>17</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13">
         <v>4</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="13">
         <v>3</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="15">
+      <c r="A21" s="13">
         <v>18</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="13">
         <v>18</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="13">
         <v>4</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="13">
         <v>3</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="15">
+      <c r="A22" s="13">
         <v>19</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="13">
         <v>19</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="13">
         <v>4</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="13">
         <v>3</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="15">
+      <c r="A23" s="13">
         <v>20</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="13">
         <v>20</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="13">
         <v>4</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="13">
         <v>3</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="15">
+      <c r="A24" s="13">
         <v>21</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="13">
         <v>21</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="13">
         <v>4</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="13">
         <v>3</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="15">
+      <c r="A25" s="13">
         <v>22</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="13">
         <v>22</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="13">
         <v>4</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="13">
         <v>3</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="15">
+      <c r="A26" s="13">
         <v>23</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="13">
         <v>23</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="13">
         <v>4</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="13">
         <v>3</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="15">
+      <c r="A27" s="13">
         <v>24</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="13">
         <v>24</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13">
         <v>4</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13">
         <v>3</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="15">
+      <c r="A28" s="13">
         <v>25</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="13">
         <v>25</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13">
         <v>4</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="13">
         <v>3</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="15">
+      <c r="A29" s="13">
         <v>26</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="13">
         <v>26</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="13">
         <v>4</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="13">
         <v>3</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="15">
+      <c r="A30" s="13">
         <v>27</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="13">
         <v>27</v>
       </c>
-      <c r="C30" s="15">
+      <c r="C30" s="13">
         <v>4</v>
       </c>
-      <c r="D30" s="15">
+      <c r="D30" s="13">
         <v>3</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="15">
+      <c r="A31" s="13">
         <v>28</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="13">
         <v>28</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="13">
         <v>4</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="13">
         <v>3</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="15">
+      <c r="A32" s="13">
         <v>29</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="13">
         <v>29</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="13">
         <v>4</v>
       </c>
-      <c r="D32" s="15">
+      <c r="D32" s="13">
         <v>3</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="15">
+      <c r="A33" s="13">
         <v>30</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="13">
         <v>30</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="13">
         <v>4</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="13">
         <v>3</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="15">
+      <c r="A34" s="13">
         <v>31</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="13">
         <v>31</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="13">
         <v>4</v>
       </c>
-      <c r="D34" s="15">
+      <c r="D34" s="13">
         <v>3</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="15">
+      <c r="A35" s="13">
         <v>32</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="13">
         <v>32</v>
       </c>
-      <c r="C35" s="15">
+      <c r="C35" s="13">
         <v>4</v>
       </c>
-      <c r="D35" s="15">
+      <c r="D35" s="13">
         <v>3</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="15">
+      <c r="A36" s="13">
         <v>33</v>
       </c>
-      <c r="B36" s="15">
+      <c r="B36" s="13">
         <v>33</v>
       </c>
-      <c r="C36" s="15">
+      <c r="C36" s="13">
         <v>4</v>
       </c>
-      <c r="D36" s="15">
+      <c r="D36" s="13">
         <v>3</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="15">
+      <c r="A37" s="13">
         <v>34</v>
       </c>
-      <c r="B37" s="15">
+      <c r="B37" s="13">
         <v>34</v>
       </c>
-      <c r="C37" s="15">
+      <c r="C37" s="13">
         <v>4</v>
       </c>
-      <c r="D37" s="15">
+      <c r="D37" s="13">
         <v>3</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="15">
+      <c r="A38" s="13">
         <v>35</v>
       </c>
-      <c r="B38" s="15">
+      <c r="B38" s="13">
         <v>35</v>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="13">
         <v>4</v>
       </c>
-      <c r="D38" s="15">
+      <c r="D38" s="13">
         <v>3</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="15">
+      <c r="A39" s="13">
         <v>36</v>
       </c>
-      <c r="B39" s="15">
+      <c r="B39" s="13">
         <v>36</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="13">
         <v>4</v>
       </c>
-      <c r="D39" s="15">
+      <c r="D39" s="13">
         <v>3</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="15">
+      <c r="A40" s="13">
         <v>37</v>
       </c>
-      <c r="B40" s="15">
+      <c r="B40" s="13">
         <v>37</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="13">
         <v>4</v>
       </c>
-      <c r="D40" s="15">
+      <c r="D40" s="13">
         <v>3</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="15">
+      <c r="A41" s="13">
         <v>38</v>
       </c>
-      <c r="B41" s="15">
+      <c r="B41" s="13">
         <v>38</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="13">
         <v>4</v>
       </c>
-      <c r="D41" s="15">
+      <c r="D41" s="13">
         <v>3</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="15">
+      <c r="A42" s="13">
         <v>39</v>
       </c>
-      <c r="B42" s="15">
+      <c r="B42" s="13">
         <v>39</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="13">
         <v>4</v>
       </c>
-      <c r="D42" s="15">
+      <c r="D42" s="13">
         <v>3</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="15">
+      <c r="A43" s="13">
         <v>40</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B43" s="13">
         <v>40</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="13">
         <v>4</v>
       </c>
-      <c r="D43" s="15">
+      <c r="D43" s="13">
         <v>3</v>
       </c>
-      <c r="E43" s="15" t="s">
+      <c r="E43" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="15">
+      <c r="A44" s="13">
         <v>41</v>
       </c>
-      <c r="B44" s="15">
+      <c r="B44" s="13">
         <v>41</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="13">
         <v>4</v>
       </c>
-      <c r="D44" s="15">
+      <c r="D44" s="13">
         <v>3</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="E44" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="15">
+      <c r="A45" s="13">
         <v>42</v>
       </c>
-      <c r="B45" s="15">
+      <c r="B45" s="13">
         <v>42</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="13">
         <v>4</v>
       </c>
-      <c r="D45" s="15">
+      <c r="D45" s="13">
         <v>3</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="E45" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="15">
+      <c r="A46" s="13">
         <v>43</v>
       </c>
-      <c r="B46" s="15">
+      <c r="B46" s="13">
         <v>43</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="13">
         <v>4</v>
       </c>
-      <c r="D46" s="15">
+      <c r="D46" s="13">
         <v>3</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="15">
+      <c r="A47" s="13">
         <v>44</v>
       </c>
-      <c r="B47" s="15">
+      <c r="B47" s="13">
         <v>44</v>
       </c>
-      <c r="C47" s="15">
+      <c r="C47" s="13">
         <v>4</v>
       </c>
-      <c r="D47" s="15">
+      <c r="D47" s="13">
         <v>3</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="15">
+      <c r="A48" s="13">
         <v>45</v>
       </c>
-      <c r="B48" s="15">
+      <c r="B48" s="13">
         <v>45</v>
       </c>
-      <c r="C48" s="15">
+      <c r="C48" s="13">
         <v>4</v>
       </c>
-      <c r="D48" s="15">
+      <c r="D48" s="13">
         <v>3</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="15">
+      <c r="A49" s="13">
         <v>46</v>
       </c>
-      <c r="B49" s="15">
+      <c r="B49" s="13">
         <v>46</v>
       </c>
-      <c r="C49" s="15">
+      <c r="C49" s="13">
         <v>4</v>
       </c>
-      <c r="D49" s="15">
+      <c r="D49" s="13">
         <v>3</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="15">
+      <c r="A50" s="13">
         <v>47</v>
       </c>
-      <c r="B50" s="15">
+      <c r="B50" s="13">
         <v>47</v>
       </c>
-      <c r="C50" s="15">
+      <c r="C50" s="13">
         <v>4</v>
       </c>
-      <c r="D50" s="15">
+      <c r="D50" s="13">
         <v>3</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="15">
+      <c r="A51" s="13">
         <v>48</v>
       </c>
-      <c r="B51" s="15">
+      <c r="B51" s="13">
         <v>48</v>
       </c>
-      <c r="C51" s="15">
+      <c r="C51" s="13">
         <v>4</v>
       </c>
-      <c r="D51" s="15">
+      <c r="D51" s="13">
         <v>3</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E51" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="15">
+      <c r="A52" s="13">
         <v>49</v>
       </c>
-      <c r="B52" s="15">
+      <c r="B52" s="13">
         <v>49</v>
       </c>
-      <c r="C52" s="15">
+      <c r="C52" s="13">
         <v>4</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="13">
         <v>3</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E52" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="15">
+      <c r="A53" s="13">
         <v>50</v>
       </c>
-      <c r="B53" s="15">
+      <c r="B53" s="13">
         <v>50</v>
       </c>
-      <c r="C53" s="15">
+      <c r="C53" s="13">
         <v>4</v>
       </c>
-      <c r="D53" s="15">
+      <c r="D53" s="13">
         <v>3</v>
       </c>
-      <c r="E53" s="15" t="s">
+      <c r="E53" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="15">
+      <c r="A54" s="13">
         <v>51</v>
       </c>
-      <c r="B54" s="15">
+      <c r="B54" s="13">
         <v>51</v>
       </c>
-      <c r="C54" s="15">
+      <c r="C54" s="13">
         <v>4</v>
       </c>
-      <c r="D54" s="15">
+      <c r="D54" s="13">
         <v>3</v>
       </c>
-      <c r="E54" s="15" t="s">
+      <c r="E54" s="13" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="15">
+      <c r="A55" s="13">
         <v>52</v>
       </c>
-      <c r="B55" s="15">
+      <c r="B55" s="13">
         <v>52</v>
       </c>
-      <c r="C55" s="15">
+      <c r="C55" s="13">
         <v>4</v>
       </c>
-      <c r="D55" s="15">
+      <c r="D55" s="13">
         <v>3</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E55" s="13" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5619,801 +5719,801 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="27.75" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="25.175" style="10" customWidth="1"/>
-    <col min="2" max="2" width="13.575" style="10" customWidth="1"/>
-    <col min="3" max="3" width="127.141666666667" style="10" customWidth="1"/>
-    <col min="4" max="4" width="49" style="10" customWidth="1"/>
-    <col min="5" max="5" width="92.9666666666667" style="11" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="10"/>
+    <col min="1" max="1" width="25.175" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13.575" style="8" customWidth="1"/>
+    <col min="3" max="3" width="127.141666666667" style="8" customWidth="1"/>
+    <col min="4" max="4" width="49" style="8" customWidth="1"/>
+    <col min="5" max="5" width="92.9666666666667" style="9" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>1</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="10">
         <v>1</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>2</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>2</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>3</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>4</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="10">
         <v>4</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>5</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="10">
         <v>5</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>6</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="10">
         <v>6</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="12">
+      <c r="A10" s="10">
         <v>7</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="10">
         <v>7</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="12">
+      <c r="A11" s="10">
         <v>8</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="10">
         <v>8</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="12">
+      <c r="A12" s="10">
         <v>9</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="10">
         <v>9</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="12">
+      <c r="A13" s="10">
         <v>10</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="10">
         <v>10</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="12">
+      <c r="A14" s="10">
         <v>11</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="10">
         <v>11</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="12">
+      <c r="A15" s="10">
         <v>12</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="10">
         <v>12</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="12">
+      <c r="A16" s="10">
         <v>13</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="10">
         <v>13</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="12">
+      <c r="A17" s="10">
         <v>14</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="10">
         <v>14</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="12">
+      <c r="A18" s="10">
         <v>15</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="10">
         <v>15</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="12">
+      <c r="A19" s="10">
         <v>16</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="10">
         <v>16</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="12">
+      <c r="A20" s="10">
         <v>17</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="10">
         <v>17</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="12">
+      <c r="A21" s="10">
         <v>18</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="10">
         <v>18</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="12">
+      <c r="A22" s="10">
         <v>19</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="10">
         <v>19</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="12">
+      <c r="A23" s="10">
         <v>20</v>
       </c>
-      <c r="B23" s="12">
+      <c r="B23" s="10">
         <v>20</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="12">
+      <c r="A24" s="10">
         <v>21</v>
       </c>
-      <c r="B24" s="12">
+      <c r="B24" s="10">
         <v>21</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="12">
+      <c r="A25" s="10">
         <v>22</v>
       </c>
-      <c r="B25" s="12">
+      <c r="B25" s="10">
         <v>22</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="12">
+      <c r="A26" s="10">
         <v>23</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B26" s="10">
         <v>23</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="12">
+      <c r="A27" s="10">
         <v>24</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="10">
         <v>24</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="12">
+      <c r="A28" s="10">
         <v>25</v>
       </c>
-      <c r="B28" s="12">
+      <c r="B28" s="10">
         <v>25</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="12">
+      <c r="A29" s="10">
         <v>26</v>
       </c>
-      <c r="B29" s="12">
+      <c r="B29" s="10">
         <v>26</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="12">
+      <c r="A30" s="10">
         <v>27</v>
       </c>
-      <c r="B30" s="12">
+      <c r="B30" s="10">
         <v>27</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="12">
+      <c r="A31" s="10">
         <v>28</v>
       </c>
-      <c r="B31" s="12">
+      <c r="B31" s="10">
         <v>28</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="12">
+      <c r="A32" s="10">
         <v>29</v>
       </c>
-      <c r="B32" s="12">
+      <c r="B32" s="10">
         <v>29</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="12">
+      <c r="A33" s="10">
         <v>30</v>
       </c>
-      <c r="B33" s="12">
+      <c r="B33" s="10">
         <v>30</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="12">
+      <c r="A34" s="10">
         <v>31</v>
       </c>
-      <c r="B34" s="12">
+      <c r="B34" s="10">
         <v>31</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="12">
+      <c r="A35" s="10">
         <v>32</v>
       </c>
-      <c r="B35" s="12">
+      <c r="B35" s="10">
         <v>32</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="12">
+      <c r="A36" s="10">
         <v>33</v>
       </c>
-      <c r="B36" s="12">
+      <c r="B36" s="10">
         <v>33</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="12">
+      <c r="A37" s="10">
         <v>34</v>
       </c>
-      <c r="B37" s="12">
+      <c r="B37" s="10">
         <v>34</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="12">
+      <c r="A38" s="10">
         <v>35</v>
       </c>
-      <c r="B38" s="12">
+      <c r="B38" s="10">
         <v>35</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="12">
+      <c r="A39" s="10">
         <v>36</v>
       </c>
-      <c r="B39" s="12">
+      <c r="B39" s="10">
         <v>36</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="12">
+      <c r="A40" s="10">
         <v>37</v>
       </c>
-      <c r="B40" s="12">
+      <c r="B40" s="10">
         <v>37</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="12">
+      <c r="A41" s="10">
         <v>38</v>
       </c>
-      <c r="B41" s="12">
+      <c r="B41" s="10">
         <v>38</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="12">
+      <c r="A42" s="10">
         <v>39</v>
       </c>
-      <c r="B42" s="12">
+      <c r="B42" s="10">
         <v>39</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="10" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="13">
+      <c r="A43" s="11">
         <v>40</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="11">
         <v>40</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="13">
+      <c r="A44" s="11">
         <v>41</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="11">
         <v>41</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="13">
+      <c r="A45" s="11">
         <v>42</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="11">
         <v>42</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="13">
+      <c r="A46" s="11">
         <v>43</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="11">
         <v>43</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="13">
+      <c r="A47" s="11">
         <v>44</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="11">
         <v>44</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="13">
+      <c r="A48" s="11">
         <v>45</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="11">
         <v>45</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="13">
+      <c r="A49" s="11">
         <v>46</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="11">
         <v>46</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="13">
+      <c r="A50" s="11">
         <v>47</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="11">
         <v>47</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="13">
+      <c r="A51" s="11">
         <v>48</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="11">
         <v>48</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="13">
+      <c r="A52" s="11">
         <v>49</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="11">
         <v>49</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="13">
+      <c r="A53" s="11">
         <v>50</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="11">
         <v>50</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="13">
+      <c r="A54" s="11">
         <v>51</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="11">
         <v>51</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="13">
+      <c r="A55" s="11">
         <v>52</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="11">
         <v>52</v>
       </c>
-      <c r="C55" s="13" t="s">
+      <c r="C55" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="13" t="s">
+      <c r="D55" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="13"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="13"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="C58" s="13"/>
+      <c r="C58" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6531,10 +6631,10 @@
         <f>CEILING(A4/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>113244405937302</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="7" t="s">
         <v>154</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -6558,10 +6658,10 @@
         <f t="shared" ref="E5:E36" si="0">CEILING(A5/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>105711056874756</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="7" t="s">
         <v>157</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -6587,10 +6687,10 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <v>82693303214454</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="7" t="s">
         <v>159</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -6616,10 +6716,10 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>102504658102706</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="7" t="s">
         <v>161</v>
       </c>
       <c r="H7" s="2" t="s">
@@ -6645,10 +6745,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="4">
         <v>83069096807916</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="7" t="s">
         <v>163</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -6672,10 +6772,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="4">
         <v>80534536398974</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="7" t="s">
         <v>165</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -6700,10 +6800,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="4">
         <v>74246671448525</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="7" t="s">
         <v>167</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -6728,10 +6828,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="4">
         <v>71499702430100</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="7" t="s">
         <v>169</v>
       </c>
       <c r="H11" s="2" t="s">
@@ -6756,10 +6856,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="4">
         <v>122909083001205</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="7" t="s">
         <v>171</v>
       </c>
       <c r="H12" s="2" t="s">
@@ -6783,10 +6883,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="4">
         <v>128658267266293</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="7" t="s">
         <v>173</v>
       </c>
       <c r="H13" s="2" t="s">
@@ -6810,10 +6910,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="4">
         <v>134748387119946</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="7" t="s">
         <v>175</v>
       </c>
       <c r="H14" s="2" t="s">
@@ -6837,10 +6937,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="4">
         <v>131559815185521</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="7" t="s">
         <v>177</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -6864,10 +6964,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="4">
         <v>135406755438948</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="7" t="s">
         <v>179</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -6895,10 +6995,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="4">
         <v>128433990441931</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="7" t="s">
         <v>181</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -6926,10 +7026,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="4">
         <v>86357992624263</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="7" t="s">
         <v>183</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -6957,10 +7057,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="4">
         <v>96128137486525</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="7" t="s">
         <v>185</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -6988,10 +7088,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="4">
         <v>131913492630514</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="7" t="s">
         <v>187</v>
       </c>
       <c r="H20" s="2" t="s">
@@ -7019,10 +7119,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="4">
         <v>119579899338192</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="7" t="s">
         <v>189</v>
       </c>
       <c r="H21" s="2" t="s">
@@ -7050,10 +7150,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="4">
         <v>82472089572732</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="7" t="s">
         <v>191</v>
       </c>
       <c r="H22" s="2" t="s">
@@ -7081,10 +7181,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="4">
         <v>104108852156434</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="7" t="s">
         <v>193</v>
       </c>
       <c r="H23" s="2" t="s">
@@ -7112,10 +7212,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="4">
         <v>79005623120233</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="7" t="s">
         <v>195</v>
       </c>
       <c r="H24" s="2" t="s">
@@ -7143,10 +7243,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="4">
         <v>97611938478078</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="7" t="s">
         <v>197</v>
       </c>
       <c r="H25" s="2" t="s">
@@ -7174,10 +7274,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="4">
         <v>81806655827798</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="7" t="s">
         <v>199</v>
       </c>
       <c r="H26" s="2" t="s">
@@ -7205,10 +7305,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="4">
         <v>105716218867716</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="7" t="s">
         <v>201</v>
       </c>
       <c r="H27" s="2" t="s">
@@ -7236,10 +7336,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="4">
         <v>128411546772202</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="7" t="s">
         <v>203</v>
       </c>
       <c r="H28" s="2" t="s">
@@ -7267,10 +7367,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="4">
         <v>139465058617680</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="7" t="s">
         <v>205</v>
       </c>
       <c r="H29" s="2" t="s">
@@ -7298,10 +7398,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="4">
         <v>81737011057690</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="7" t="s">
         <v>207</v>
       </c>
       <c r="H30" s="2" t="s">
@@ -7329,10 +7429,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="4">
         <v>81445862907930</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="7" t="s">
         <v>209</v>
       </c>
       <c r="H31" s="2" t="s">
@@ -7360,10 +7460,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="4">
         <v>123098432383687</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="7" t="s">
         <v>211</v>
       </c>
       <c r="H32" s="2" t="s">
@@ -7391,10 +7491,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="4">
         <v>131796260838154</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="7" t="s">
         <v>213</v>
       </c>
       <c r="H33" s="2" t="s">
@@ -7418,10 +7518,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="4">
         <v>116376878683736</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="7" t="s">
         <v>215</v>
       </c>
       <c r="H34" s="2" t="s">
@@ -7445,10 +7545,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="4">
         <v>100558097057142</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="7" t="s">
         <v>217</v>
       </c>
       <c r="H35" s="2" t="s">
@@ -7472,10 +7572,10 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="4">
         <v>92332707761527</v>
       </c>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="7" t="s">
         <v>219</v>
       </c>
       <c r="H36" s="2" t="s">
@@ -7503,10 +7603,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>6</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="4">
         <v>108895787734224</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" s="7" t="s">
         <v>221</v>
       </c>
       <c r="H37" s="2" t="s">
@@ -7530,10 +7630,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>7</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="4">
         <v>95471681056681</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="7" t="s">
         <v>223</v>
       </c>
       <c r="H38" s="2" t="s">
@@ -7557,10 +7657,10 @@
         <f t="shared" ref="E39:E72" si="1">CEILING(A39/4,1)</f>
         <v>9</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="4">
         <v>104955598295323</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="7" t="s">
         <v>225</v>
       </c>
       <c r="H39" s="2" t="s">
@@ -7588,10 +7688,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="4">
         <v>103175883366340</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="7" t="s">
         <v>227</v>
       </c>
       <c r="H40" s="2" t="s">
@@ -7619,10 +7719,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41" s="4">
         <v>114247164745798</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="7" t="s">
         <v>229</v>
       </c>
       <c r="H41" s="2" t="s">
@@ -7646,10 +7746,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42" s="4">
         <v>86017047390182</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="7" t="s">
         <v>231</v>
       </c>
       <c r="H42" s="2" t="s">
@@ -7673,10 +7773,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F43" s="6">
+      <c r="F43" s="4">
         <v>81373582816266</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G43" s="7" t="s">
         <v>233</v>
       </c>
       <c r="H43" s="2" t="s">
@@ -7700,10 +7800,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44" s="4">
         <v>132788281080826</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="7" t="s">
         <v>235</v>
       </c>
       <c r="H44" s="2" t="s">
@@ -7727,10 +7827,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F45" s="4">
         <v>95162444285252</v>
       </c>
-      <c r="G45" s="9" t="s">
+      <c r="G45" s="7" t="s">
         <v>237</v>
       </c>
       <c r="H45" s="2" t="s">
@@ -7754,10 +7854,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F46" s="6">
+      <c r="F46" s="4">
         <v>95953438126479</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="7" t="s">
         <v>239</v>
       </c>
       <c r="H46" s="2" t="s">
@@ -7781,10 +7881,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47" s="4">
         <v>112039222887887</v>
       </c>
-      <c r="G47" s="9" t="s">
+      <c r="G47" s="7" t="s">
         <v>241</v>
       </c>
       <c r="H47" s="2" t="s">
@@ -7808,10 +7908,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48" s="4">
         <v>95377459606647</v>
       </c>
-      <c r="G48" s="9" t="s">
+      <c r="G48" s="7" t="s">
         <v>243</v>
       </c>
       <c r="H48" s="2" t="s">
@@ -7835,10 +7935,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49" s="4">
         <v>113983796605688</v>
       </c>
-      <c r="G49" s="9" t="s">
+      <c r="G49" s="7" t="s">
         <v>245</v>
       </c>
       <c r="H49" s="2" t="s">
@@ -7862,10 +7962,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50" s="4">
         <v>117157716541352</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="7" t="s">
         <v>247</v>
       </c>
       <c r="H50" s="2" t="s">
@@ -7889,10 +7989,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51" s="4">
         <v>100893051807474</v>
       </c>
-      <c r="G51" s="9" t="s">
+      <c r="G51" s="7" t="s">
         <v>249</v>
       </c>
       <c r="H51" s="2" t="s">
@@ -7916,10 +8016,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52" s="4">
         <v>137999782231090</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="7" t="s">
         <v>251</v>
       </c>
       <c r="H52" s="2" t="s">
@@ -7943,10 +8043,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53" s="4">
         <v>127007149281218</v>
       </c>
-      <c r="G53" s="9" t="s">
+      <c r="G53" s="7" t="s">
         <v>253</v>
       </c>
       <c r="H53" s="2" t="s">
@@ -7970,10 +8070,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="4">
         <v>85273469740405</v>
       </c>
-      <c r="G54" s="9" t="s">
+      <c r="G54" s="7" t="s">
         <v>255</v>
       </c>
       <c r="H54" s="2" t="s">
@@ -7997,10 +8097,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F55" s="4">
         <v>85750403977754</v>
       </c>
-      <c r="G55" s="9" t="s">
+      <c r="G55" s="7" t="s">
         <v>257</v>
       </c>
       <c r="H55" s="2" t="s">
@@ -8024,10 +8124,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56" s="4">
         <v>87658125570749</v>
       </c>
-      <c r="G56" s="9" t="s">
+      <c r="G56" s="7" t="s">
         <v>259</v>
       </c>
       <c r="H56" s="2" t="s">
@@ -8051,10 +8151,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F57" s="4">
         <v>71386503893388</v>
       </c>
-      <c r="G57" s="9" t="s">
+      <c r="G57" s="7" t="s">
         <v>261</v>
       </c>
       <c r="H57" s="2" t="s">
@@ -8078,10 +8178,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58" s="4">
         <v>117660867991736</v>
       </c>
-      <c r="G58" s="9" t="s">
+      <c r="G58" s="7" t="s">
         <v>263</v>
       </c>
       <c r="H58" s="2" t="s">
@@ -8105,10 +8205,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59" s="4">
         <v>75602786825729</v>
       </c>
-      <c r="G59" s="9" t="s">
+      <c r="G59" s="7" t="s">
         <v>265</v>
       </c>
       <c r="H59" s="2" t="s">
@@ -8132,10 +8232,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F60" s="4">
         <v>97494295137425</v>
       </c>
-      <c r="G60" s="9" t="s">
+      <c r="G60" s="7" t="s">
         <v>267</v>
       </c>
       <c r="H60" s="2" t="s">
@@ -8159,10 +8259,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F61" s="4">
         <v>121387106380169</v>
       </c>
-      <c r="G61" s="9" t="s">
+      <c r="G61" s="7" t="s">
         <v>269</v>
       </c>
       <c r="H61" s="2" t="s">
@@ -8186,10 +8286,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F62" s="4">
         <v>77703154963129</v>
       </c>
-      <c r="G62" s="9" t="s">
+      <c r="G62" s="7" t="s">
         <v>271</v>
       </c>
       <c r="H62" s="2" t="s">
@@ -8213,10 +8313,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F63" s="4">
         <v>82745313217810</v>
       </c>
-      <c r="G63" s="9" t="s">
+      <c r="G63" s="7" t="s">
         <v>273</v>
       </c>
       <c r="H63" s="2" t="s">
@@ -8240,10 +8340,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64" s="4">
         <v>78702263483439</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="G64" s="7" t="s">
         <v>275</v>
       </c>
       <c r="H64" s="2" t="s">
@@ -8267,10 +8367,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65" s="4">
         <v>103252845267522</v>
       </c>
-      <c r="G65" s="9" t="s">
+      <c r="G65" s="7" t="s">
         <v>277</v>
       </c>
       <c r="H65" s="2" t="s">
@@ -8294,10 +8394,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66" s="4">
         <v>93380659059014</v>
       </c>
-      <c r="G66" s="9" t="s">
+      <c r="G66" s="7" t="s">
         <v>279</v>
       </c>
       <c r="H66" s="2" t="s">
@@ -8321,10 +8421,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F67" s="4">
         <v>124070618735034</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="G67" s="7" t="s">
         <v>281</v>
       </c>
       <c r="H67" s="2" t="s">
@@ -8348,10 +8448,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F68" s="4">
         <v>82229267783572</v>
       </c>
-      <c r="G68" s="9" t="s">
+      <c r="G68" s="7" t="s">
         <v>283</v>
       </c>
       <c r="H68" s="2" t="s">
@@ -8375,10 +8475,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F69" s="6">
+      <c r="F69" s="4">
         <v>90764663625426</v>
       </c>
-      <c r="G69" s="9" t="s">
+      <c r="G69" s="7" t="s">
         <v>285</v>
       </c>
       <c r="H69" s="2" t="s">
@@ -8402,10 +8502,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70" s="4">
         <v>89592774326120</v>
       </c>
-      <c r="G70" s="9" t="s">
+      <c r="G70" s="7" t="s">
         <v>287</v>
       </c>
       <c r="H70" s="2" t="s">
@@ -8429,10 +8529,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="4">
         <v>96498729983354</v>
       </c>
-      <c r="G71" s="9" t="s">
+      <c r="G71" s="7" t="s">
         <v>289</v>
       </c>
       <c r="H71" s="2" t="s">
@@ -8456,10 +8556,10 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72" s="4">
         <v>137402232463633</v>
       </c>
-      <c r="G72" s="9" t="s">
+      <c r="G72" s="7" t="s">
         <v>291</v>
       </c>
       <c r="H72" s="2" t="s">
@@ -8483,10 +8583,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>15</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F73" s="4">
         <v>79717469784936</v>
       </c>
-      <c r="G73" s="9" t="s">
+      <c r="G73" s="7" t="s">
         <v>293</v>
       </c>
       <c r="H73" s="2" t="s">
@@ -8510,10 +8610,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F74" s="4">
         <v>86646811474956</v>
       </c>
-      <c r="G74" s="9" t="s">
+      <c r="G74" s="7" t="s">
         <v>295</v>
       </c>
       <c r="H74" s="2" t="s">
@@ -8537,10 +8637,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F75" s="4">
         <v>128217347353354</v>
       </c>
-      <c r="G75" s="9" t="s">
+      <c r="G75" s="7" t="s">
         <v>297</v>
       </c>
       <c r="H75" s="2" t="s">
@@ -8564,10 +8664,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F76" s="4">
         <v>126321668579357</v>
       </c>
-      <c r="G76" s="9" t="s">
+      <c r="G76" s="7" t="s">
         <v>299</v>
       </c>
       <c r="H76" s="2" t="s">
@@ -8591,10 +8691,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F77" s="6">
+      <c r="F77" s="4">
         <v>98351529529203</v>
       </c>
-      <c r="G77" s="9" t="s">
+      <c r="G77" s="7" t="s">
         <v>301</v>
       </c>
       <c r="H77" s="2" t="s">
@@ -8618,10 +8718,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F78" s="4">
         <v>81048668172712</v>
       </c>
-      <c r="G78" s="9" t="s">
+      <c r="G78" s="7" t="s">
         <v>303</v>
       </c>
       <c r="H78" s="2" t="s">
@@ -8645,10 +8745,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="4">
         <v>127615544859575</v>
       </c>
-      <c r="G79" s="9" t="s">
+      <c r="G79" s="7" t="s">
         <v>305</v>
       </c>
       <c r="H79" s="2" t="s">
@@ -8672,10 +8772,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80" s="4">
         <v>70656304136373</v>
       </c>
-      <c r="G80" s="9" t="s">
+      <c r="G80" s="7" t="s">
         <v>307</v>
       </c>
       <c r="H80" s="2" t="s">
@@ -8699,10 +8799,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F81" s="6">
+      <c r="F81" s="4">
         <v>134424174805013</v>
       </c>
-      <c r="G81" s="9" t="s">
+      <c r="G81" s="7" t="s">
         <v>309</v>
       </c>
       <c r="H81" s="2" t="s">
@@ -8726,10 +8826,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82" s="4">
         <v>127255485663084</v>
       </c>
-      <c r="G82" s="9" t="s">
+      <c r="G82" s="7" t="s">
         <v>311</v>
       </c>
       <c r="H82" s="2" t="s">
@@ -8753,10 +8853,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F83" s="4">
         <v>134027683373658</v>
       </c>
-      <c r="G83" s="9" t="s">
+      <c r="G83" s="7" t="s">
         <v>313</v>
       </c>
       <c r="H83" s="2" t="s">
@@ -8780,10 +8880,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F84" s="4">
         <v>112447657334137</v>
       </c>
-      <c r="G84" s="9" t="s">
+      <c r="G84" s="7" t="s">
         <v>315</v>
       </c>
       <c r="H84" s="2" t="s">
@@ -8807,10 +8907,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F85" s="4">
         <v>104595008892706</v>
       </c>
-      <c r="G85" s="9" t="s">
+      <c r="G85" s="7" t="s">
         <v>317</v>
       </c>
       <c r="H85" s="2" t="s">
@@ -8834,10 +8934,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F86" s="4">
         <v>82759045606098</v>
       </c>
-      <c r="G86" s="9" t="s">
+      <c r="G86" s="7" t="s">
         <v>319</v>
       </c>
       <c r="H86" s="2" t="s">
@@ -8861,10 +8961,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="4">
         <v>105620837789519</v>
       </c>
-      <c r="G87" s="9" t="s">
+      <c r="G87" s="7" t="s">
         <v>321</v>
       </c>
       <c r="H87" s="2" t="s">
@@ -8888,10 +8988,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="4">
         <v>111024567754480</v>
       </c>
-      <c r="G88" s="9" t="s">
+      <c r="G88" s="7" t="s">
         <v>323</v>
       </c>
       <c r="H88" s="2" t="s">
@@ -8915,10 +9015,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F89" s="4">
         <v>137153989969007</v>
       </c>
-      <c r="G89" s="9" t="s">
+      <c r="G89" s="7" t="s">
         <v>325</v>
       </c>
       <c r="H89" s="2" t="s">
@@ -8942,10 +9042,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F90" s="6">
+      <c r="F90" s="4">
         <v>74496996195913</v>
       </c>
-      <c r="G90" s="9" t="s">
+      <c r="G90" s="7" t="s">
         <v>327</v>
       </c>
       <c r="H90" s="2" t="s">
@@ -8969,10 +9069,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F91" s="4">
         <v>132785860315163</v>
       </c>
-      <c r="G91" s="9" t="s">
+      <c r="G91" s="7" t="s">
         <v>329</v>
       </c>
       <c r="H91" s="2" t="s">
@@ -8996,10 +9096,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="4">
         <v>117198962948319</v>
       </c>
-      <c r="G92" s="9" t="s">
+      <c r="G92" s="7" t="s">
         <v>331</v>
       </c>
       <c r="H92" s="2" t="s">
@@ -9023,10 +9123,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F93" s="4">
         <v>124449160476895</v>
       </c>
-      <c r="G93" s="9" t="s">
+      <c r="G93" s="7" t="s">
         <v>333</v>
       </c>
       <c r="H93" s="2" t="s">
@@ -9050,10 +9150,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="4">
         <v>125887863438527</v>
       </c>
-      <c r="G94" s="9" t="s">
+      <c r="G94" s="7" t="s">
         <v>335</v>
       </c>
       <c r="H94" s="2" t="s">
@@ -9077,10 +9177,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F95" s="6">
+      <c r="F95" s="4">
         <v>137692564728429</v>
       </c>
-      <c r="G95" s="9" t="s">
+      <c r="G95" s="7" t="s">
         <v>337</v>
       </c>
       <c r="H95" s="2" t="s">
@@ -9104,10 +9204,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F96" s="6">
+      <c r="F96" s="4">
         <v>82350951870220</v>
       </c>
-      <c r="G96" s="9" t="s">
+      <c r="G96" s="7" t="s">
         <v>339</v>
       </c>
       <c r="H96" s="2" t="s">
@@ -9131,10 +9231,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="4">
         <v>133019385929561</v>
       </c>
-      <c r="G97" s="9" t="s">
+      <c r="G97" s="7" t="s">
         <v>341</v>
       </c>
       <c r="H97" s="2" t="s">
@@ -9158,10 +9258,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F98" s="4">
         <v>82714807302588</v>
       </c>
-      <c r="G98" s="9" t="s">
+      <c r="G98" s="7" t="s">
         <v>343</v>
       </c>
       <c r="H98" s="2" t="s">
@@ -9185,10 +9285,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F99" s="4">
         <v>120409278538446</v>
       </c>
-      <c r="G99" s="9" t="s">
+      <c r="G99" s="7" t="s">
         <v>345</v>
       </c>
       <c r="H99" s="2" t="s">
@@ -9212,10 +9312,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F100" s="4">
         <v>136303201068741</v>
       </c>
-      <c r="G100" s="9" t="s">
+      <c r="G100" s="7" t="s">
         <v>347</v>
       </c>
       <c r="H100" s="2" t="s">
@@ -9239,10 +9339,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F101" s="4">
         <v>76724781858184</v>
       </c>
-      <c r="G101" s="9" t="s">
+      <c r="G101" s="7" t="s">
         <v>349</v>
       </c>
       <c r="H101" s="2" t="s">
@@ -9266,10 +9366,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F102" s="4">
         <v>120125979830927</v>
       </c>
-      <c r="G102" s="9" t="s">
+      <c r="G102" s="7" t="s">
         <v>351</v>
       </c>
       <c r="H102" s="2" t="s">
@@ -9293,10 +9393,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F103" s="4">
         <v>86921870572603</v>
       </c>
-      <c r="G103" s="9" t="s">
+      <c r="G103" s="7" t="s">
         <v>353</v>
       </c>
       <c r="H103" s="2" t="s">
@@ -9320,10 +9420,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F104" s="4">
         <v>126355990231048</v>
       </c>
-      <c r="G104" s="9" t="s">
+      <c r="G104" s="7" t="s">
         <v>355</v>
       </c>
       <c r="H104" s="2" t="s">
@@ -9347,10 +9447,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F105" s="4">
         <v>72326444062448</v>
       </c>
-      <c r="G105" s="9" t="s">
+      <c r="G105" s="7" t="s">
         <v>357</v>
       </c>
       <c r="H105" s="2" t="s">
@@ -9374,10 +9474,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F106" s="4">
         <v>72257499044823</v>
       </c>
-      <c r="G106" s="9" t="s">
+      <c r="G106" s="7" t="s">
         <v>359</v>
       </c>
       <c r="H106" s="2" t="s">
@@ -9401,10 +9501,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F107" s="4">
         <v>74695865349139</v>
       </c>
-      <c r="G107" s="9" t="s">
+      <c r="G107" s="7" t="s">
         <v>361</v>
       </c>
       <c r="H107" s="2" t="s">
@@ -9427,10 +9527,10 @@
       <c r="E108" s="1">
         <v>24</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F108" s="4">
         <v>98358488442985</v>
       </c>
-      <c r="G108" s="9" t="s">
+      <c r="G108" s="7" t="s">
         <v>363</v>
       </c>
       <c r="H108" s="2" t="s">
@@ -9454,10 +9554,10 @@
       <c r="E109" s="1">
         <v>24</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F109" s="4">
         <v>113636295509693</v>
       </c>
-      <c r="G109" s="9" t="s">
+      <c r="G109" s="7" t="s">
         <v>365</v>
       </c>
       <c r="H109" s="2" t="s">
@@ -9481,10 +9581,10 @@
       <c r="E110" s="1">
         <v>25</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F110" s="4">
         <v>114047124407739</v>
       </c>
-      <c r="G110" s="9" t="s">
+      <c r="G110" s="7" t="s">
         <v>367</v>
       </c>
       <c r="H110" s="2" t="s">
@@ -9508,10 +9608,10 @@
       <c r="E111" s="1">
         <v>25</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F111" s="4">
         <v>95771403493939</v>
       </c>
-      <c r="G111" s="9" t="s">
+      <c r="G111" s="7" t="s">
         <v>369</v>
       </c>
       <c r="H111" s="2" t="s">
@@ -9535,10 +9635,10 @@
       <c r="E112" s="1">
         <v>25</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F112" s="4">
         <v>140393673870516</v>
       </c>
-      <c r="G112" s="9" t="s">
+      <c r="G112" s="7" t="s">
         <v>371</v>
       </c>
       <c r="H112" s="2" t="s">
@@ -9562,10 +9662,10 @@
       <c r="E113" s="1">
         <v>25</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F113" s="4">
         <v>123109322631502</v>
       </c>
-      <c r="G113" s="9" t="s">
+      <c r="G113" s="7" t="s">
         <v>373</v>
       </c>
       <c r="H113" s="2" t="s">
@@ -9589,10 +9689,10 @@
       <c r="E114" s="1">
         <v>26</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F114" s="4">
         <v>98614967981417</v>
       </c>
-      <c r="G114" s="9" t="s">
+      <c r="G114" s="7" t="s">
         <v>375</v>
       </c>
       <c r="H114" s="2" t="s">
@@ -9616,10 +9716,10 @@
       <c r="E115" s="1">
         <v>26</v>
       </c>
-      <c r="F115" s="6">
+      <c r="F115" s="4">
         <v>127369769981706</v>
       </c>
-      <c r="G115" s="9" t="s">
+      <c r="G115" s="7" t="s">
         <v>377</v>
       </c>
       <c r="H115" s="2" t="s">
@@ -9643,10 +9743,10 @@
       <c r="E116" s="1">
         <v>26</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F116" s="4">
         <v>134574393827781</v>
       </c>
-      <c r="G116" s="9" t="s">
+      <c r="G116" s="7" t="s">
         <v>379</v>
       </c>
       <c r="H116" s="2" t="s">
@@ -9670,10 +9770,10 @@
       <c r="E117" s="1">
         <v>26</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117" s="4">
         <v>130258203281991</v>
       </c>
-      <c r="G117" s="9" t="s">
+      <c r="G117" s="7" t="s">
         <v>381</v>
       </c>
       <c r="H117" s="2" t="s">
@@ -9697,10 +9797,10 @@
       <c r="E118" s="1">
         <v>27</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F118" s="4">
         <v>93953823085119</v>
       </c>
-      <c r="G118" s="9" t="s">
+      <c r="G118" s="7" t="s">
         <v>383</v>
       </c>
       <c r="H118" s="2" t="s">
@@ -9724,10 +9824,10 @@
       <c r="E119" s="1">
         <v>27</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F119" s="4">
         <v>109802560542166</v>
       </c>
-      <c r="G119" s="9" t="s">
+      <c r="G119" s="7" t="s">
         <v>385</v>
       </c>
       <c r="H119" s="2" t="s">
@@ -9751,10 +9851,10 @@
       <c r="E120" s="1">
         <v>27</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F120" s="4">
         <v>130989494782889</v>
       </c>
-      <c r="G120" s="9" t="s">
+      <c r="G120" s="7" t="s">
         <v>387</v>
       </c>
       <c r="H120" s="2" t="s">
@@ -9778,10 +9878,10 @@
       <c r="E121" s="1">
         <v>27</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F121" s="4">
         <v>129408716253336</v>
       </c>
-      <c r="G121" s="9" t="s">
+      <c r="G121" s="7" t="s">
         <v>389</v>
       </c>
       <c r="H121" s="2" t="s">
@@ -9805,10 +9905,10 @@
       <c r="E122" s="1">
         <v>28</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F122" s="4">
         <v>127772866805590</v>
       </c>
-      <c r="G122" s="9" t="s">
+      <c r="G122" s="7" t="s">
         <v>391</v>
       </c>
       <c r="H122" s="2" t="s">
@@ -9832,10 +9932,10 @@
       <c r="E123" s="1">
         <v>28</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F123" s="4">
         <v>91938109188463</v>
       </c>
-      <c r="G123" s="9" t="s">
+      <c r="G123" s="7" t="s">
         <v>393</v>
       </c>
       <c r="H123" s="2" t="s">
@@ -9859,10 +9959,10 @@
       <c r="E124" s="1">
         <v>28</v>
       </c>
-      <c r="F124" s="6">
+      <c r="F124" s="4">
         <v>85077262752129</v>
       </c>
-      <c r="G124" s="9" t="s">
+      <c r="G124" s="7" t="s">
         <v>395</v>
       </c>
       <c r="H124" s="2" t="s">
@@ -9877,7 +9977,7 @@
       <c r="B125" s="1">
         <v>122</v>
       </c>
-      <c r="C125" s="9" t="s">
+      <c r="C125" s="7" t="s">
         <v>396</v>
       </c>
       <c r="D125" s="1">
@@ -9886,10 +9986,10 @@
       <c r="E125" s="1">
         <v>28</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F125" s="4">
         <v>140335958193244</v>
       </c>
-      <c r="G125" s="9" t="s">
+      <c r="G125" s="7" t="s">
         <v>397</v>
       </c>
       <c r="H125" s="2" t="s">
@@ -9903,7 +10003,7 @@
       <c r="B126" s="1">
         <v>123</v>
       </c>
-      <c r="C126" s="9" t="s">
+      <c r="C126" s="7" t="s">
         <v>398</v>
       </c>
       <c r="D126" s="1">
@@ -9912,10 +10012,10 @@
       <c r="E126" s="1">
         <v>29</v>
       </c>
-      <c r="F126" s="6">
+      <c r="F126" s="4">
         <v>86732012145983</v>
       </c>
-      <c r="G126" s="9" t="s">
+      <c r="G126" s="7" t="s">
         <v>399</v>
       </c>
       <c r="H126" s="2" t="s">
@@ -9929,7 +10029,7 @@
       <c r="B127" s="1">
         <v>124</v>
       </c>
-      <c r="C127" s="9" t="s">
+      <c r="C127" s="7" t="s">
         <v>400</v>
       </c>
       <c r="D127" s="1">
@@ -9938,10 +10038,10 @@
       <c r="E127" s="1">
         <v>29</v>
       </c>
-      <c r="F127" s="6">
+      <c r="F127" s="4">
         <v>78044122276865</v>
       </c>
-      <c r="G127" s="9" t="s">
+      <c r="G127" s="7" t="s">
         <v>401</v>
       </c>
       <c r="H127" s="2" t="s">
@@ -9955,7 +10055,7 @@
       <c r="B128" s="1">
         <v>125</v>
       </c>
-      <c r="C128" s="9" t="s">
+      <c r="C128" s="7" t="s">
         <v>402</v>
       </c>
       <c r="D128" s="1">
@@ -9964,10 +10064,10 @@
       <c r="E128" s="1">
         <v>29</v>
       </c>
-      <c r="F128" s="6">
+      <c r="F128" s="4">
         <v>114974638199136</v>
       </c>
-      <c r="G128" s="9" t="s">
+      <c r="G128" s="7" t="s">
         <v>403</v>
       </c>
       <c r="H128" s="2" t="s">
@@ -9981,7 +10081,7 @@
       <c r="B129" s="1">
         <v>126</v>
       </c>
-      <c r="C129" s="9" t="s">
+      <c r="C129" s="7" t="s">
         <v>404</v>
       </c>
       <c r="D129" s="1">
@@ -9990,10 +10090,10 @@
       <c r="E129" s="1">
         <v>29</v>
       </c>
-      <c r="F129" s="6">
+      <c r="F129" s="4">
         <v>83652207307759</v>
       </c>
-      <c r="G129" s="9" t="s">
+      <c r="G129" s="7" t="s">
         <v>405</v>
       </c>
       <c r="H129" s="2" t="s">
@@ -10007,7 +10107,7 @@
       <c r="B130" s="1">
         <v>127</v>
       </c>
-      <c r="C130" s="9" t="s">
+      <c r="C130" s="7" t="s">
         <v>406</v>
       </c>
       <c r="D130" s="1">
@@ -10016,10 +10116,10 @@
       <c r="E130" s="1">
         <v>30</v>
       </c>
-      <c r="F130" s="6">
+      <c r="F130" s="4">
         <v>131787091355052</v>
       </c>
-      <c r="G130" s="9" t="s">
+      <c r="G130" s="7" t="s">
         <v>407</v>
       </c>
       <c r="H130" s="2" t="s">
@@ -10033,7 +10133,7 @@
       <c r="B131" s="1">
         <v>128</v>
       </c>
-      <c r="C131" s="9" t="s">
+      <c r="C131" s="7" t="s">
         <v>408</v>
       </c>
       <c r="D131" s="1">
@@ -10042,10 +10142,10 @@
       <c r="E131" s="1">
         <v>30</v>
       </c>
-      <c r="F131" s="6">
+      <c r="F131" s="4">
         <v>99348381699835</v>
       </c>
-      <c r="G131" s="9" t="s">
+      <c r="G131" s="7" t="s">
         <v>409</v>
       </c>
       <c r="H131" s="2" t="s">
@@ -10059,7 +10159,7 @@
       <c r="B132" s="1">
         <v>129</v>
       </c>
-      <c r="C132" s="9" t="s">
+      <c r="C132" s="7" t="s">
         <v>410</v>
       </c>
       <c r="D132" s="1">
@@ -10068,10 +10168,10 @@
       <c r="E132" s="1">
         <v>30</v>
       </c>
-      <c r="F132" s="6">
+      <c r="F132" s="4">
         <v>75412160560516</v>
       </c>
-      <c r="G132" s="9" t="s">
+      <c r="G132" s="7" t="s">
         <v>411</v>
       </c>
       <c r="H132" s="2" t="s">
@@ -10085,7 +10185,7 @@
       <c r="B133" s="1">
         <v>130</v>
       </c>
-      <c r="C133" s="9" t="s">
+      <c r="C133" s="7" t="s">
         <v>412</v>
       </c>
       <c r="D133" s="1">
@@ -10094,10 +10194,10 @@
       <c r="E133" s="1">
         <v>30</v>
       </c>
-      <c r="F133" s="6">
+      <c r="F133" s="4">
         <v>105475505052937</v>
       </c>
-      <c r="G133" s="9" t="s">
+      <c r="G133" s="7" t="s">
         <v>413</v>
       </c>
       <c r="H133" s="2" t="s">
@@ -10111,7 +10211,7 @@
       <c r="B134" s="1">
         <v>131</v>
       </c>
-      <c r="C134" s="9" t="s">
+      <c r="C134" s="7" t="s">
         <v>414</v>
       </c>
       <c r="D134" s="1">
@@ -10120,10 +10220,10 @@
       <c r="E134" s="1">
         <v>31</v>
       </c>
-      <c r="F134" s="6">
+      <c r="F134" s="4">
         <v>125484119033793</v>
       </c>
-      <c r="G134" s="9" t="s">
+      <c r="G134" s="7" t="s">
         <v>415</v>
       </c>
       <c r="H134" s="2" t="s">
@@ -10137,7 +10237,7 @@
       <c r="B135" s="1">
         <v>132</v>
       </c>
-      <c r="C135" s="9" t="s">
+      <c r="C135" s="7" t="s">
         <v>416</v>
       </c>
       <c r="D135" s="1">
@@ -10146,10 +10246,10 @@
       <c r="E135" s="1">
         <v>31</v>
       </c>
-      <c r="F135" s="6">
+      <c r="F135" s="4">
         <v>140608831780254</v>
       </c>
-      <c r="G135" s="9" t="s">
+      <c r="G135" s="7" t="s">
         <v>417</v>
       </c>
       <c r="H135" s="2" t="s">
@@ -10163,7 +10263,7 @@
       <c r="B136" s="1">
         <v>133</v>
       </c>
-      <c r="C136" s="9" t="s">
+      <c r="C136" s="7" t="s">
         <v>418</v>
       </c>
       <c r="D136" s="1">
@@ -10172,10 +10272,10 @@
       <c r="E136" s="1">
         <v>31</v>
       </c>
-      <c r="F136" s="6">
+      <c r="F136" s="4">
         <v>124177358025481</v>
       </c>
-      <c r="G136" s="9" t="s">
+      <c r="G136" s="7" t="s">
         <v>419</v>
       </c>
       <c r="H136" s="2" t="s">
@@ -10189,7 +10289,7 @@
       <c r="B137" s="1">
         <v>134</v>
       </c>
-      <c r="C137" s="9" t="s">
+      <c r="C137" s="7" t="s">
         <v>420</v>
       </c>
       <c r="D137" s="1">
@@ -10198,10 +10298,10 @@
       <c r="E137" s="1">
         <v>31</v>
       </c>
-      <c r="F137" s="6">
+      <c r="F137" s="4">
         <v>129385390119523</v>
       </c>
-      <c r="G137" s="9" t="s">
+      <c r="G137" s="7" t="s">
         <v>421</v>
       </c>
       <c r="H137" s="2" t="s">
@@ -10215,7 +10315,7 @@
       <c r="B138" s="1">
         <v>135</v>
       </c>
-      <c r="C138" s="9" t="s">
+      <c r="C138" s="7" t="s">
         <v>422</v>
       </c>
       <c r="D138" s="1">
@@ -10224,10 +10324,10 @@
       <c r="E138" s="1">
         <v>32</v>
       </c>
-      <c r="F138" s="6">
+      <c r="F138" s="4">
         <v>84940520003035</v>
       </c>
-      <c r="G138" s="9" t="s">
+      <c r="G138" s="7" t="s">
         <v>423</v>
       </c>
       <c r="H138" s="2" t="s">
@@ -10241,7 +10341,7 @@
       <c r="B139" s="1">
         <v>136</v>
       </c>
-      <c r="C139" s="9" t="s">
+      <c r="C139" s="7" t="s">
         <v>424</v>
       </c>
       <c r="D139" s="1">
@@ -10250,10 +10350,10 @@
       <c r="E139" s="1">
         <v>32</v>
       </c>
-      <c r="F139" s="6">
+      <c r="F139" s="4">
         <v>90031364711610</v>
       </c>
-      <c r="G139" s="9" t="s">
+      <c r="G139" s="7" t="s">
         <v>425</v>
       </c>
       <c r="H139" s="2" t="s">
@@ -10267,7 +10367,7 @@
       <c r="B140" s="1">
         <v>137</v>
       </c>
-      <c r="C140" s="9" t="s">
+      <c r="C140" s="7" t="s">
         <v>426</v>
       </c>
       <c r="D140" s="1">
@@ -10276,10 +10376,10 @@
       <c r="E140" s="1">
         <v>32</v>
       </c>
-      <c r="F140" s="6">
+      <c r="F140" s="4">
         <v>84418341821320</v>
       </c>
-      <c r="G140" s="9" t="s">
+      <c r="G140" s="7" t="s">
         <v>427</v>
       </c>
       <c r="H140" s="2" t="s">
@@ -10293,7 +10393,7 @@
       <c r="B141" s="1">
         <v>138</v>
       </c>
-      <c r="C141" s="9" t="s">
+      <c r="C141" s="7" t="s">
         <v>428</v>
       </c>
       <c r="D141" s="1">
@@ -10302,10 +10402,10 @@
       <c r="E141" s="1">
         <v>32</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F141" s="4">
         <v>130255705800444</v>
       </c>
-      <c r="G141" s="9" t="s">
+      <c r="G141" s="7" t="s">
         <v>429</v>
       </c>
       <c r="H141" s="2" t="s">
@@ -10319,7 +10419,7 @@
       <c r="B142" s="1">
         <v>139</v>
       </c>
-      <c r="C142" s="9" t="s">
+      <c r="C142" s="7" t="s">
         <v>430</v>
       </c>
       <c r="D142" s="1">
@@ -10328,10 +10428,10 @@
       <c r="E142" s="1">
         <v>33</v>
       </c>
-      <c r="F142" s="6">
+      <c r="F142" s="4">
         <v>123568265278671</v>
       </c>
-      <c r="G142" s="9" t="s">
+      <c r="G142" s="7" t="s">
         <v>431</v>
       </c>
       <c r="H142" s="2" t="s">
@@ -10345,7 +10445,7 @@
       <c r="B143" s="1">
         <v>140</v>
       </c>
-      <c r="C143" s="9" t="s">
+      <c r="C143" s="7" t="s">
         <v>432</v>
       </c>
       <c r="D143" s="1">
@@ -10354,10 +10454,10 @@
       <c r="E143" s="1">
         <v>33</v>
       </c>
-      <c r="F143" s="6">
+      <c r="F143" s="4">
         <v>75689117044416</v>
       </c>
-      <c r="G143" s="9" t="s">
+      <c r="G143" s="7" t="s">
         <v>433</v>
       </c>
       <c r="H143" s="2" t="s">
@@ -10371,7 +10471,7 @@
       <c r="B144" s="1">
         <v>141</v>
       </c>
-      <c r="C144" s="9" t="s">
+      <c r="C144" s="7" t="s">
         <v>434</v>
       </c>
       <c r="D144" s="1">
@@ -10380,10 +10480,10 @@
       <c r="E144" s="1">
         <v>33</v>
       </c>
-      <c r="F144" s="6">
+      <c r="F144" s="4">
         <v>92309488435591</v>
       </c>
-      <c r="G144" s="9" t="s">
+      <c r="G144" s="7" t="s">
         <v>435</v>
       </c>
       <c r="H144" s="2" t="s">
@@ -10397,7 +10497,7 @@
       <c r="B145" s="1">
         <v>142</v>
       </c>
-      <c r="C145" s="9" t="s">
+      <c r="C145" s="7" t="s">
         <v>436</v>
       </c>
       <c r="D145" s="1">
@@ -10406,10 +10506,10 @@
       <c r="E145" s="1">
         <v>33</v>
       </c>
-      <c r="F145" s="6">
+      <c r="F145" s="4">
         <v>106319308889290</v>
       </c>
-      <c r="G145" s="9" t="s">
+      <c r="G145" s="7" t="s">
         <v>437</v>
       </c>
       <c r="H145" s="2" t="s">
@@ -10423,7 +10523,7 @@
       <c r="B146" s="1">
         <v>143</v>
       </c>
-      <c r="C146" s="9" t="s">
+      <c r="C146" s="7" t="s">
         <v>438</v>
       </c>
       <c r="D146" s="1">
@@ -10432,10 +10532,10 @@
       <c r="E146" s="1">
         <v>34</v>
       </c>
-      <c r="F146" s="6">
+      <c r="F146" s="4">
         <v>123120949699520</v>
       </c>
-      <c r="G146" s="9" t="s">
+      <c r="G146" s="7" t="s">
         <v>439</v>
       </c>
       <c r="H146" s="2" t="s">
@@ -10449,7 +10549,7 @@
       <c r="B147" s="1">
         <v>144</v>
       </c>
-      <c r="C147" s="9" t="s">
+      <c r="C147" s="7" t="s">
         <v>440</v>
       </c>
       <c r="D147" s="1">
@@ -10458,10 +10558,10 @@
       <c r="E147" s="1">
         <v>34</v>
       </c>
-      <c r="F147" s="6">
+      <c r="F147" s="4">
         <v>111674856010497</v>
       </c>
-      <c r="G147" s="9" t="s">
+      <c r="G147" s="7" t="s">
         <v>441</v>
       </c>
       <c r="H147" s="2" t="s">
@@ -10475,7 +10575,7 @@
       <c r="B148" s="1">
         <v>145</v>
       </c>
-      <c r="C148" s="9" t="s">
+      <c r="C148" s="7" t="s">
         <v>442</v>
       </c>
       <c r="D148" s="1">
@@ -10484,10 +10584,10 @@
       <c r="E148" s="1">
         <v>34</v>
       </c>
-      <c r="F148" s="6">
+      <c r="F148" s="4">
         <v>118080816505555</v>
       </c>
-      <c r="G148" s="9" t="s">
+      <c r="G148" s="7" t="s">
         <v>443</v>
       </c>
       <c r="H148" s="2" t="s">
@@ -10501,7 +10601,7 @@
       <c r="B149" s="1">
         <v>146</v>
       </c>
-      <c r="C149" s="9" t="s">
+      <c r="C149" s="7" t="s">
         <v>444</v>
       </c>
       <c r="D149" s="1">
@@ -10510,10 +10610,10 @@
       <c r="E149" s="1">
         <v>34</v>
       </c>
-      <c r="F149" s="6">
+      <c r="F149" s="4">
         <v>105021574817966</v>
       </c>
-      <c r="G149" s="9" t="s">
+      <c r="G149" s="7" t="s">
         <v>445</v>
       </c>
       <c r="H149" s="2" t="s">
@@ -10527,7 +10627,7 @@
       <c r="B150" s="1">
         <v>147</v>
       </c>
-      <c r="C150" s="9" t="s">
+      <c r="C150" s="7" t="s">
         <v>446</v>
       </c>
       <c r="D150" s="1">
@@ -10536,10 +10636,10 @@
       <c r="E150" s="1">
         <v>35</v>
       </c>
-      <c r="F150" s="6">
+      <c r="F150" s="4">
         <v>72690180103558</v>
       </c>
-      <c r="G150" s="9" t="s">
+      <c r="G150" s="7" t="s">
         <v>447</v>
       </c>
       <c r="H150" s="2" t="s">
@@ -10553,7 +10653,7 @@
       <c r="B151" s="1">
         <v>148</v>
       </c>
-      <c r="C151" s="9" t="s">
+      <c r="C151" s="7" t="s">
         <v>448</v>
       </c>
       <c r="D151" s="1">
@@ -10562,10 +10662,10 @@
       <c r="E151" s="1">
         <v>35</v>
       </c>
-      <c r="F151" s="6">
+      <c r="F151" s="4">
         <v>94914272618995</v>
       </c>
-      <c r="G151" s="9" t="s">
+      <c r="G151" s="7" t="s">
         <v>449</v>
       </c>
       <c r="H151" s="2" t="s">
@@ -10589,156 +10689,156 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A4" s="8">
+      <c r="A4" s="6">
         <v>1</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="6">
         <v>2</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A5" s="8">
+      <c r="A5" s="6">
         <v>2</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="6">
         <v>4</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <v>151</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A6" s="8">
+      <c r="A6" s="6">
         <v>3</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>8</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A7" s="8">
+      <c r="A7" s="6">
         <v>4</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>16</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <v>153</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A8" s="8">
+      <c r="A8" s="6">
         <v>5</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>32</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <v>154</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A9" s="8">
+      <c r="A9" s="6">
         <v>6</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>64</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="6">
         <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A10" s="8">
+      <c r="A10" s="6">
         <v>7</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>128</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="6">
         <v>156</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A11" s="8">
+      <c r="A11" s="6">
         <v>8</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <v>256</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="6">
         <v>157</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A12" s="8">
+      <c r="A12" s="6">
         <v>9</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <v>512</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="6">
         <v>158</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A13" s="8">
+      <c r="A13" s="6">
         <v>10</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="6">
         <v>1024</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="6">
         <v>159</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A14" s="8">
+      <c r="A14" s="6">
         <v>11</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>2048</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>160</v>
       </c>
     </row>
@@ -10865,10 +10965,10 @@
       <c r="G4">
         <v>99853650045862</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="I4" s="7"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A5" s="1">
@@ -10890,10 +10990,10 @@
       <c r="G5">
         <v>116225665846279</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="I5" s="7"/>
+      <c r="I5" s="5"/>
     </row>
     <row r="6" customFormat="1" ht="16.5" spans="1:9">
       <c r="A6" s="1">
@@ -10915,10 +11015,10 @@
       <c r="G6">
         <v>136956773152573</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="I6" s="7"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" customFormat="1" ht="16.5" spans="1:9">
       <c r="A7" s="1">
@@ -10940,10 +11040,10 @@
       <c r="G7">
         <v>97553870039023</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="I7" s="7"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8" customFormat="1" ht="16.5" spans="1:9">
       <c r="A8" s="1">
@@ -10955,20 +11055,20 @@
       <c r="C8" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="25" t="s">
         <v>470</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="25" t="s">
         <v>471</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8">
         <v>118090700645855</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="I8" s="7"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" customFormat="1" ht="16.5" spans="1:9">
       <c r="A9" s="1">
@@ -10980,20 +11080,20 @@
       <c r="C9" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="25" t="s">
         <v>474</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="25" t="s">
         <v>475</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9">
         <v>138508042210191</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="I9" s="7"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" customFormat="1" ht="16.5" spans="1:9">
       <c r="A10" s="1">
@@ -11005,20 +11105,20 @@
       <c r="C10" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="25" t="s">
         <v>478</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="25" t="s">
         <v>479</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10">
         <v>78371166922896</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="I10" s="7"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" customFormat="1" ht="16.5" spans="1:9">
       <c r="A11" s="1">
@@ -11030,20 +11130,20 @@
       <c r="C11" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="25" t="s">
         <v>482</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="25" t="s">
         <v>483</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11">
         <v>132966760008713</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="I11" s="7"/>
+      <c r="I11" s="5"/>
     </row>
     <row r="12" customFormat="1" ht="16.5" spans="1:9">
       <c r="A12" s="1">
@@ -11055,20 +11155,20 @@
       <c r="C12" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="25" t="s">
         <v>486</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="25" t="s">
         <v>487</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12">
         <v>133927008310944</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="I12" s="7"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="13" customFormat="1" ht="16.5" spans="1:9">
       <c r="A13" s="1">
@@ -11080,20 +11180,20 @@
       <c r="C13" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="25" t="s">
         <v>490</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="25" t="s">
         <v>491</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13">
         <v>98415179467911</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="I13" s="7"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" customFormat="1" ht="16.5" spans="1:9">
       <c r="A14" s="1">
@@ -11105,20 +11205,20 @@
       <c r="C14" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="25" t="s">
         <v>494</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="25" t="s">
         <v>495</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14">
         <v>79276409476682</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="4" t="s">
         <v>496</v>
       </c>
-      <c r="I14" s="7"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15" customFormat="1" ht="16.5" spans="1:9">
       <c r="A15" s="1">
@@ -11130,20 +11230,20 @@
       <c r="C15" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="25" t="s">
         <v>498</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="25" t="s">
         <v>499</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15">
         <v>86184044773576</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="I15" s="7"/>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" customFormat="1" ht="16.5" spans="1:9">
       <c r="A16" s="1">
@@ -11155,20 +11255,20 @@
       <c r="C16" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="25" t="s">
         <v>502</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="25" t="s">
         <v>503</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16">
         <v>85964386896273</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="I16" s="7"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" customFormat="1" ht="16.5" spans="1:9">
       <c r="A17" s="1">
@@ -11180,20 +11280,20 @@
       <c r="C17" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="25" t="s">
         <v>506</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="25" t="s">
         <v>507</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17">
         <v>121813166897471</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="I17" s="7"/>
+      <c r="I17" s="5"/>
     </row>
     <row r="18" customFormat="1" ht="16.5" spans="1:9">
       <c r="A18" s="1">
@@ -11205,20 +11305,20 @@
       <c r="C18" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="25" t="s">
         <v>510</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="25" t="s">
         <v>511</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18">
         <v>107669574278873</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="I18" s="7"/>
+      <c r="I18" s="5"/>
     </row>
     <row r="19" customFormat="1" ht="16.5" spans="1:9">
       <c r="A19" s="1">
@@ -11230,20 +11330,20 @@
       <c r="C19" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="25" t="s">
         <v>514</v>
       </c>
-      <c r="E19" s="27" t="s">
+      <c r="E19" s="25" t="s">
         <v>515</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19">
         <v>98723580431394</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="I19" s="7"/>
+      <c r="I19" s="5"/>
     </row>
     <row r="20" customFormat="1" ht="16.5" spans="1:9">
       <c r="A20" s="1">
@@ -11255,20 +11355,20 @@
       <c r="C20" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="25" t="s">
         <v>518</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="25" t="s">
         <v>519</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20">
         <v>126241505230536</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="I20" s="7"/>
+      <c r="I20" s="5"/>
     </row>
     <row r="21" ht="16.5" spans="1:9">
       <c r="A21" s="1">
@@ -11280,20 +11380,20 @@
       <c r="C21" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="25" t="s">
         <v>522</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="25" t="s">
         <v>523</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21">
         <v>78092021290844</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="I21" s="7"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" ht="16.5" spans="1:9">
       <c r="A22" s="1">
@@ -11305,20 +11405,20 @@
       <c r="C22" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="25" t="s">
         <v>526</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="25" t="s">
         <v>527</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22">
         <v>138731887343821</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="I22" s="7"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23" ht="16.5" spans="1:9">
       <c r="A23" s="1">
@@ -11330,20 +11430,20 @@
       <c r="C23" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="25" t="s">
         <v>530</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="25" t="s">
         <v>531</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23">
         <v>113127149166000</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="I23" s="7"/>
+      <c r="I23" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11354,7 +11454,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD20"/>
+  <dimension ref="A1:XFD28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -11362,8 +11462,8 @@
     <col min="3" max="4" width="23.3833333333333" style="2" customWidth="1"/>
     <col min="5" max="6" width="28" style="2" customWidth="1"/>
     <col min="7" max="7" width="13.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="48.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="57.1333333333333" style="2" customWidth="1"/>
+    <col min="8" max="8" width="24.4583333333333" style="2" customWidth="1"/>
+    <col min="9" max="9" width="42.6416666666667" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -11372,7 +11472,7 @@
         <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>454</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>139</v>
@@ -11390,10 +11490,10 @@
         <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>143</v>
+        <v>533</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11401,7 +11501,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>146</v>
@@ -11462,10 +11562,10 @@
         <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D4" s="1">
-        <v>3750</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1">
         <v>1.5</v>
@@ -11478,7 +11578,7 @@
         <v>91469233823349</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11489,16 +11589,16 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="D5" s="27" t="s">
         <v>538</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2</v>
       </c>
       <c r="E5" s="1">
         <v>2.5</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5">
@@ -11518,21 +11618,21 @@
       <c r="C6" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="D6" s="27" t="s">
-        <v>541</v>
+      <c r="D6" s="1">
+        <v>3</v>
       </c>
       <c r="E6" s="1">
         <v>3.5</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6">
         <v>114920101659350</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11543,23 +11643,23 @@
         <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>544</v>
+        <v>542</v>
+      </c>
+      <c r="D7" s="1">
+        <v>4</v>
       </c>
       <c r="E7" s="1">
         <v>4.5</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7">
         <v>76680071023422</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11570,78 +11670,158 @@
         <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>547</v>
+        <v>544</v>
+      </c>
+      <c r="D8" s="1">
+        <v>5</v>
       </c>
       <c r="E8" s="1">
         <v>5.5</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8">
         <v>98163950325063</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>106</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D9" s="1">
+        <v>6</v>
+      </c>
+      <c r="E9" s="1">
+        <v>6.5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>6</v>
+      </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="H9">
+        <v>98163950325063</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>107</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D10" s="1">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1">
+        <v>7.5</v>
+      </c>
+      <c r="F10" s="1">
+        <v>7</v>
+      </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="H10">
+        <v>98163950325063</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>549</v>
+      </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>108</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="D11" s="1">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1">
+        <v>8.5</v>
+      </c>
+      <c r="F11" s="1">
+        <v>8</v>
+      </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="H11">
+        <v>98163950325063</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>551</v>
+      </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="5"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>109</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9</v>
+      </c>
+      <c r="E12" s="1">
+        <v>9.5</v>
+      </c>
+      <c r="F12" s="1">
+        <v>9</v>
+      </c>
+      <c r="H12">
+        <v>98163950325063</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>553</v>
+      </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>110</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D13" s="1">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1">
+        <v>10.5</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10</v>
+      </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="H13">
+        <v>98163950325063</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>555</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -28019,15 +28199,31 @@
       <c r="XFD13" s="1"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>111</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D14" s="1">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="F14" s="1">
+        <v>11</v>
+      </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="H14">
+        <v>98163950325063</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>557</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -44405,15 +44601,31 @@
       <c r="XFD14" s="1"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>112</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D15" s="1">
+        <v>12</v>
+      </c>
+      <c r="E15" s="1">
+        <v>12.5</v>
+      </c>
+      <c r="F15" s="1">
+        <v>12</v>
+      </c>
       <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="H15">
+        <v>98163950325063</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>559</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -60791,59 +61003,347 @@
       <c r="XFD15" s="1"/>
     </row>
     <row r="16" ht="16.5" spans="1:1024 1025:16384">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>113</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D16" s="1">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1">
+        <v>13.5</v>
+      </c>
+      <c r="F16" s="1">
+        <v>13</v>
+      </c>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="H16">
+        <v>98163950325063</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>561</v>
+      </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>114</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="D17" s="1">
+        <v>14</v>
+      </c>
+      <c r="E17" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="F17" s="1">
+        <v>14</v>
+      </c>
       <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="H17">
+        <v>98163950325063</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>563</v>
+      </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
+      <c r="A18" s="1">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>115</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D18" s="1">
+        <v>15</v>
+      </c>
+      <c r="E18" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="F18" s="1">
+        <v>15</v>
+      </c>
       <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
+      <c r="H18">
+        <v>98163950325063</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>565</v>
+      </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="A19" s="1">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>116</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="D19" s="1">
+        <v>16</v>
+      </c>
+      <c r="E19" s="1">
+        <v>16.5</v>
+      </c>
+      <c r="F19" s="1">
+        <v>16</v>
+      </c>
       <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
+      <c r="H19">
+        <v>98163950325063</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>567</v>
+      </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="A20" s="1">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>117</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="D20" s="1">
+        <v>17</v>
+      </c>
+      <c r="E20" s="1">
+        <v>17.5</v>
+      </c>
+      <c r="F20" s="1">
+        <v>17</v>
+      </c>
       <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+      <c r="H20">
+        <v>98163950325063</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:9">
+      <c r="A21" s="1">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>118</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D21" s="1">
+        <v>18</v>
+      </c>
+      <c r="E21" s="1">
+        <v>18.5</v>
+      </c>
+      <c r="F21" s="1">
+        <v>18</v>
+      </c>
+      <c r="H21">
+        <v>98163950325063</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:9">
+      <c r="A22" s="1">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>119</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="D22" s="1">
+        <v>19</v>
+      </c>
+      <c r="E22" s="1">
+        <v>19.5</v>
+      </c>
+      <c r="F22" s="1">
+        <v>19</v>
+      </c>
+      <c r="H22">
+        <v>98163950325063</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:9">
+      <c r="A23" s="1">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1">
+        <v>120</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="D23" s="1">
+        <v>20</v>
+      </c>
+      <c r="E23" s="1">
+        <v>20.5</v>
+      </c>
+      <c r="F23" s="1">
+        <v>20</v>
+      </c>
+      <c r="H23">
+        <v>98163950325063</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:9">
+      <c r="A24" s="1">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>121</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="D24" s="1">
+        <v>21</v>
+      </c>
+      <c r="E24" s="1">
+        <v>21.5</v>
+      </c>
+      <c r="F24" s="1">
+        <v>21</v>
+      </c>
+      <c r="H24">
+        <v>98163950325063</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:9">
+      <c r="A25" s="1">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>122</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D25" s="1">
+        <v>22</v>
+      </c>
+      <c r="E25" s="1">
+        <v>22.5</v>
+      </c>
+      <c r="F25" s="1">
+        <v>22</v>
+      </c>
+      <c r="H25">
+        <v>98163950325063</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:9">
+      <c r="A26" s="1">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>123</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="D26" s="1">
+        <v>23</v>
+      </c>
+      <c r="E26" s="1">
+        <v>23.5</v>
+      </c>
+      <c r="F26" s="1">
+        <v>23</v>
+      </c>
+      <c r="H26">
+        <v>98163950325063</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:9">
+      <c r="A27" s="1">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>124</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="D27" s="1">
+        <v>24</v>
+      </c>
+      <c r="E27" s="1">
+        <v>24.5</v>
+      </c>
+      <c r="F27" s="1">
+        <v>24</v>
+      </c>
+      <c r="H27">
+        <v>98163950325063</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:9">
+      <c r="A28" s="1">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>125</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="D28" s="1">
+        <v>25</v>
+      </c>
+      <c r="E28" s="1">
+        <v>25.5</v>
+      </c>
+      <c r="F28" s="1">
+        <v>25</v>
+      </c>
+      <c r="H28">
+        <v>98163950325063</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>585</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -2940,7 +2940,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2951,6 +2951,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -3350,62 +3353,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="26" customHeight="1" spans="1:6">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3422,7 +3425,7 @@
       <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="24" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
@@ -3442,7 +3445,7 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="25" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3459,7 +3462,7 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="24" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3476,7 +3479,7 @@
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="24" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
@@ -3496,7 +3499,7 @@
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="25" t="s">
         <v>21</v>
       </c>
       <c r="F8" t="s">
@@ -3516,7 +3519,7 @@
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="25" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
@@ -3536,7 +3539,7 @@
       <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="24" t="s">
         <v>25</v>
       </c>
       <c r="F10" t="s">
@@ -3664,7 +3667,7 @@
       <c r="A9" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="27" t="s">
         <v>602</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3675,7 +3678,7 @@
       <c r="A10" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="27" t="s">
         <v>605</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3686,7 +3689,7 @@
       <c r="A11" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="27" t="s">
         <v>608</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -3697,7 +3700,7 @@
       <c r="A12" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="27" t="s">
         <v>611</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -3708,7 +3711,7 @@
       <c r="A13" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="27" t="s">
         <v>614</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -3719,7 +3722,7 @@
       <c r="A14" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="27" t="s">
         <v>617</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3730,7 +3733,7 @@
       <c r="A15" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="27" t="s">
         <v>620</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -3741,7 +3744,7 @@
       <c r="A16" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="27" t="s">
         <v>623</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -3752,7 +3755,7 @@
       <c r="A17" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="27" t="s">
         <v>626</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -3763,7 +3766,7 @@
       <c r="A18" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="27" t="s">
         <v>629</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -3774,7 +3777,7 @@
       <c r="A19" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="27" t="s">
         <v>632</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -3785,7 +3788,7 @@
       <c r="A20" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="27" t="s">
         <v>635</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3796,7 +3799,7 @@
       <c r="A21" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="27" t="s">
         <v>638</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -3807,7 +3810,7 @@
       <c r="A22" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="27" t="s">
         <v>641</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -3818,7 +3821,7 @@
       <c r="A23" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="27" t="s">
         <v>644</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -3829,7 +3832,7 @@
       <c r="A24" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="27" t="s">
         <v>647</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -3840,7 +3843,7 @@
       <c r="A25" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="27" t="s">
         <v>650</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -3851,7 +3854,7 @@
       <c r="A26" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="27" t="s">
         <v>653</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -3862,7 +3865,7 @@
       <c r="A27" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="27" t="s">
         <v>656</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -3873,7 +3876,7 @@
       <c r="A28" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="27" t="s">
         <v>659</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -3884,7 +3887,7 @@
       <c r="A29" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="27" t="s">
         <v>662</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -3895,7 +3898,7 @@
       <c r="A30" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="B30" s="26" t="s">
+      <c r="B30" s="27" t="s">
         <v>665</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -3906,7 +3909,7 @@
       <c r="A31" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="27" t="s">
         <v>668</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -3917,7 +3920,7 @@
       <c r="A32" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="27" t="s">
         <v>671</v>
       </c>
       <c r="C32" s="2" t="s">
@@ -3928,7 +3931,7 @@
       <c r="A33" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="27" t="s">
         <v>674</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -3939,7 +3942,7 @@
       <c r="A34" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="27" t="s">
         <v>677</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -3950,7 +3953,7 @@
       <c r="A35" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="27" t="s">
         <v>680</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -3961,7 +3964,7 @@
       <c r="A36" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="B36" s="26" t="s">
+      <c r="B36" s="27" t="s">
         <v>683</v>
       </c>
       <c r="C36" s="2" t="s">
@@ -3972,7 +3975,7 @@
       <c r="A37" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="27" t="s">
         <v>686</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -3983,7 +3986,7 @@
       <c r="A38" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="B38" s="26" t="s">
+      <c r="B38" s="27" t="s">
         <v>689</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -3994,7 +3997,7 @@
       <c r="A39" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="27" t="s">
         <v>692</v>
       </c>
       <c r="C39" s="2" t="s">
@@ -4005,7 +4008,7 @@
       <c r="A40" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="27" t="s">
         <v>695</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -4016,7 +4019,7 @@
       <c r="A41" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="27" t="s">
         <v>698</v>
       </c>
       <c r="C41" s="2" t="s">
@@ -4027,7 +4030,7 @@
       <c r="A42" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="27" t="s">
         <v>701</v>
       </c>
       <c r="C42" s="2" t="s">
@@ -4038,7 +4041,7 @@
       <c r="A43" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="28" t="s">
         <v>704</v>
       </c>
       <c r="C43" s="2" t="s">
@@ -4049,7 +4052,7 @@
       <c r="A44" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="28" t="s">
         <v>707</v>
       </c>
       <c r="C44" s="2" t="s">
@@ -4060,7 +4063,7 @@
       <c r="A45" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="28" t="s">
         <v>710</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -4071,7 +4074,7 @@
       <c r="A46" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="B46" s="27" t="s">
+      <c r="B46" s="28" t="s">
         <v>713</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -4082,7 +4085,7 @@
       <c r="A47" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="28" t="s">
         <v>716</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -4093,7 +4096,7 @@
       <c r="A48" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="28" t="s">
         <v>719</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -4104,7 +4107,7 @@
       <c r="A49" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="28" t="s">
         <v>722</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -4115,7 +4118,7 @@
       <c r="A50" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="28" t="s">
         <v>725</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -4126,7 +4129,7 @@
       <c r="A51" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="28" t="s">
         <v>728</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -4137,7 +4140,7 @@
       <c r="A52" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="28" t="s">
         <v>731</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -4148,7 +4151,7 @@
       <c r="A53" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="28" t="s">
         <v>734</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -4159,7 +4162,7 @@
       <c r="A54" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="28" t="s">
         <v>737</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -4170,7 +4173,7 @@
       <c r="A55" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="28" t="s">
         <v>740</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -4189,395 +4192,395 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="44.175" style="14" customWidth="1"/>
-    <col min="2" max="2" width="71.3583333333333" style="14" customWidth="1"/>
-    <col min="3" max="3" width="123.558333333333" style="14" customWidth="1"/>
-    <col min="4" max="4" width="82.8666666666667" style="14" customWidth="1"/>
-    <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="81.1833333333333" style="14" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="14"/>
+    <col min="1" max="1" width="44.175" style="15" customWidth="1"/>
+    <col min="2" max="2" width="71.3583333333333" style="15" customWidth="1"/>
+    <col min="3" max="3" width="123.558333333333" style="15" customWidth="1"/>
+    <col min="4" max="4" width="82.8666666666667" style="15" customWidth="1"/>
+    <col min="5" max="6" width="9" style="15"/>
+    <col min="7" max="7" width="81.1833333333333" style="15" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" s="14" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
-      <c r="A1" s="15" t="s">
+    <row r="1" s="15" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
+      <c r="A1" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
-    <row r="2" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+    <row r="2" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
-    <row r="3" s="14" customFormat="1" ht="91" customHeight="1" spans="1:7">
-      <c r="A3" s="15" t="s">
+    <row r="3" s="15" customFormat="1" ht="91" customHeight="1" spans="1:7">
+      <c r="A3" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
     </row>
-    <row r="4" s="14" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A4" s="15" t="s">
+    <row r="4" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A4" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
     </row>
-    <row r="5" s="14" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A5" s="15" t="s">
+    <row r="5" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="16">
         <v>10</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
     </row>
-    <row r="6" s="14" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A6" s="15" t="s">
+    <row r="6" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
     </row>
-    <row r="7" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A7" s="17" t="s">
+    <row r="7" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A7" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
     </row>
-    <row r="8" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A8" s="17" t="s">
+    <row r="8" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A8" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
     </row>
-    <row r="9" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A9" s="17" t="s">
+    <row r="9" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A9" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
     </row>
-    <row r="10" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A10" s="15" t="s">
+    <row r="10" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A10" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
     </row>
-    <row r="11" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A11" s="15" t="s">
+    <row r="11" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A11" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
     </row>
-    <row r="12" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A12" s="15" t="s">
+    <row r="12" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
     </row>
-    <row r="13" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A13" s="15" t="s">
+    <row r="13" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A13" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
     </row>
-    <row r="14" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
+    <row r="14" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
     </row>
-    <row r="15" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
+    <row r="15" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
     </row>
-    <row r="16" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
+    <row r="16" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
     </row>
-    <row r="17" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
+    <row r="17" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
     </row>
-    <row r="18" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+    <row r="18" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
     </row>
-    <row r="19" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
+    <row r="19" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
     </row>
-    <row r="20" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
+    <row r="20" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
     </row>
-    <row r="21" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
+    <row r="21" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
     </row>
-    <row r="22" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+    <row r="22" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
     </row>
-    <row r="23" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+    <row r="23" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
     </row>
-    <row r="24" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
+    <row r="24" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
-    <row r="25" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
+    <row r="25" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
     </row>
-    <row r="26" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
+    <row r="26" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
     </row>
-    <row r="27" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="C27" s="15"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
+    <row r="27" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="C27" s="16"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
     </row>
-    <row r="28" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
+    <row r="28" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
     </row>
-    <row r="29" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
+    <row r="29" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
     </row>
-    <row r="30" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
+    <row r="30" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
     </row>
-    <row r="31" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
+    <row r="31" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
     </row>
-    <row r="32" s="14" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
+    <row r="32" s="15" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
     </row>
-    <row r="33" s="14" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
+    <row r="33" s="15" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
     </row>
-    <row r="34" s="14" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
+    <row r="34" s="15" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
     </row>
-    <row r="35" s="14" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
+    <row r="35" s="15" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
     </row>
-    <row r="36" s="14" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
+    <row r="36" s="15" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -4767,943 +4770,943 @@
   <dimension ref="A1:E55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" width="37.75" style="12" customWidth="1"/>
+    <col min="1" max="2" width="37.75" style="13" customWidth="1"/>
     <col min="3" max="3" width="33.0833333333333" customWidth="1"/>
     <col min="4" max="5" width="40.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <v>1</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="14">
         <v>1</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="14">
         <v>80</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="14">
         <v>3</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>2</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="14">
         <v>2</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="14">
         <v>4</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="14">
         <v>3</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>3</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="14">
         <v>3</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="14">
         <v>4</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="14">
         <v>3</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="13">
+      <c r="A7" s="14">
         <v>4</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="14">
         <v>4</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="14">
         <v>4</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="14">
         <v>3</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>5</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="14">
         <v>5</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="14">
         <v>4</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="14">
         <v>3</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>6</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="14">
         <v>6</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="14">
         <v>4</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="14">
         <v>3</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>7</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="14">
         <v>7</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="14">
         <v>4</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="14">
         <v>3</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>8</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="14">
         <v>8</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="14">
         <v>4</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="14">
         <v>3</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>9</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <v>9</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="14">
         <v>4</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="14">
         <v>3</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>10</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="14">
         <v>10</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="14">
         <v>4</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="14">
         <v>3</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>11</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <v>11</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="14">
         <v>4</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="14">
         <v>3</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>12</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="14">
         <v>12</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="14">
         <v>4</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="14">
         <v>3</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>13</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="14">
         <v>13</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="14">
         <v>4</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="13">
+      <c r="A17" s="14">
         <v>14</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="14">
         <v>14</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="14">
         <v>4</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="14">
         <v>3</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>15</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="14">
         <v>15</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="14">
         <v>4</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="13">
+      <c r="A19" s="14">
         <v>16</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="14">
         <v>16</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="14">
         <v>4</v>
       </c>
-      <c r="D19" s="13">
+      <c r="D19" s="14">
         <v>3</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <v>17</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="14">
         <v>17</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="14">
         <v>4</v>
       </c>
-      <c r="D20" s="13">
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="13">
+      <c r="A21" s="14">
         <v>18</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="14">
         <v>18</v>
       </c>
-      <c r="C21" s="13">
+      <c r="C21" s="14">
         <v>4</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="14">
         <v>3</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="13">
+      <c r="A22" s="14">
         <v>19</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="14">
         <v>19</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="14">
         <v>4</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="14">
         <v>3</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="13">
+      <c r="A23" s="14">
         <v>20</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="14">
         <v>20</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="14">
         <v>4</v>
       </c>
-      <c r="D23" s="13">
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="13">
+      <c r="A24" s="14">
         <v>21</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="14">
         <v>21</v>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="14">
         <v>4</v>
       </c>
-      <c r="D24" s="13">
+      <c r="D24" s="14">
         <v>3</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="13">
+      <c r="A25" s="14">
         <v>22</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="14">
         <v>22</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="14">
         <v>4</v>
       </c>
-      <c r="D25" s="13">
+      <c r="D25" s="14">
         <v>3</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="13">
+      <c r="A26" s="14">
         <v>23</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="14">
         <v>23</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="14">
         <v>4</v>
       </c>
-      <c r="D26" s="13">
+      <c r="D26" s="14">
         <v>3</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="13">
+      <c r="A27" s="14">
         <v>24</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="14">
         <v>24</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="14">
         <v>4</v>
       </c>
-      <c r="D27" s="13">
+      <c r="D27" s="14">
         <v>3</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="13">
+      <c r="A28" s="14">
         <v>25</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="14">
         <v>25</v>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="14">
         <v>4</v>
       </c>
-      <c r="D28" s="13">
+      <c r="D28" s="14">
         <v>3</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="13">
+      <c r="A29" s="14">
         <v>26</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="14">
         <v>26</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="14">
         <v>4</v>
       </c>
-      <c r="D29" s="13">
+      <c r="D29" s="14">
         <v>3</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="13">
+      <c r="A30" s="14">
         <v>27</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="14">
         <v>27</v>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="14">
         <v>4</v>
       </c>
-      <c r="D30" s="13">
+      <c r="D30" s="14">
         <v>3</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="13">
+      <c r="A31" s="14">
         <v>28</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="14">
         <v>28</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="14">
         <v>4</v>
       </c>
-      <c r="D31" s="13">
+      <c r="D31" s="14">
         <v>3</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="13">
+      <c r="A32" s="14">
         <v>29</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="14">
         <v>29</v>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="14">
         <v>4</v>
       </c>
-      <c r="D32" s="13">
+      <c r="D32" s="14">
         <v>3</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="13">
+      <c r="A33" s="14">
         <v>30</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="14">
         <v>30</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="14">
         <v>4</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D33" s="14">
         <v>3</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="13">
+      <c r="A34" s="14">
         <v>31</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="14">
         <v>31</v>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="14">
         <v>4</v>
       </c>
-      <c r="D34" s="13">
+      <c r="D34" s="14">
         <v>3</v>
       </c>
-      <c r="E34" s="13" t="s">
+      <c r="E34" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="13">
+      <c r="A35" s="14">
         <v>32</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="14">
         <v>32</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="14">
         <v>4</v>
       </c>
-      <c r="D35" s="13">
+      <c r="D35" s="14">
         <v>3</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="13">
+      <c r="A36" s="14">
         <v>33</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <v>33</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="14">
         <v>4</v>
       </c>
-      <c r="D36" s="13">
+      <c r="D36" s="14">
         <v>3</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="13">
+      <c r="A37" s="14">
         <v>34</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="14">
         <v>34</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="14">
         <v>4</v>
       </c>
-      <c r="D37" s="13">
+      <c r="D37" s="14">
         <v>3</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="13">
+      <c r="A38" s="14">
         <v>35</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="14">
         <v>35</v>
       </c>
-      <c r="C38" s="13">
+      <c r="C38" s="14">
         <v>4</v>
       </c>
-      <c r="D38" s="13">
+      <c r="D38" s="14">
         <v>3</v>
       </c>
-      <c r="E38" s="13" t="s">
+      <c r="E38" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="13">
+      <c r="A39" s="14">
         <v>36</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="14">
         <v>36</v>
       </c>
-      <c r="C39" s="13">
+      <c r="C39" s="14">
         <v>4</v>
       </c>
-      <c r="D39" s="13">
+      <c r="D39" s="14">
         <v>3</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E39" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="13">
+      <c r="A40" s="14">
         <v>37</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="14">
         <v>37</v>
       </c>
-      <c r="C40" s="13">
+      <c r="C40" s="14">
         <v>4</v>
       </c>
-      <c r="D40" s="13">
+      <c r="D40" s="14">
         <v>3</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="13">
+      <c r="A41" s="14">
         <v>38</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="14">
         <v>38</v>
       </c>
-      <c r="C41" s="13">
+      <c r="C41" s="14">
         <v>4</v>
       </c>
-      <c r="D41" s="13">
+      <c r="D41" s="14">
         <v>3</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="13">
+      <c r="A42" s="14">
         <v>39</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="14">
         <v>39</v>
       </c>
-      <c r="C42" s="13">
+      <c r="C42" s="14">
         <v>4</v>
       </c>
-      <c r="D42" s="13">
+      <c r="D42" s="14">
         <v>3</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="13">
+      <c r="A43" s="14">
         <v>40</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="14">
         <v>40</v>
       </c>
-      <c r="C43" s="13">
+      <c r="C43" s="14">
         <v>4</v>
       </c>
-      <c r="D43" s="13">
+      <c r="D43" s="14">
         <v>3</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="13">
+      <c r="A44" s="14">
         <v>41</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="14">
         <v>41</v>
       </c>
-      <c r="C44" s="13">
+      <c r="C44" s="14">
         <v>4</v>
       </c>
-      <c r="D44" s="13">
+      <c r="D44" s="14">
         <v>3</v>
       </c>
-      <c r="E44" s="13" t="s">
+      <c r="E44" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="13">
+      <c r="A45" s="14">
         <v>42</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="14">
         <v>42</v>
       </c>
-      <c r="C45" s="13">
+      <c r="C45" s="14">
         <v>4</v>
       </c>
-      <c r="D45" s="13">
+      <c r="D45" s="14">
         <v>3</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E45" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="13">
+      <c r="A46" s="14">
         <v>43</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="14">
         <v>43</v>
       </c>
-      <c r="C46" s="13">
+      <c r="C46" s="14">
         <v>4</v>
       </c>
-      <c r="D46" s="13">
+      <c r="D46" s="14">
         <v>3</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="13">
+      <c r="A47" s="14">
         <v>44</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="14">
         <v>44</v>
       </c>
-      <c r="C47" s="13">
+      <c r="C47" s="14">
         <v>4</v>
       </c>
-      <c r="D47" s="13">
+      <c r="D47" s="14">
         <v>3</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="E47" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="13">
+      <c r="A48" s="14">
         <v>45</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="14">
         <v>45</v>
       </c>
-      <c r="C48" s="13">
+      <c r="C48" s="14">
         <v>4</v>
       </c>
-      <c r="D48" s="13">
+      <c r="D48" s="14">
         <v>3</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E48" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="13">
+      <c r="A49" s="14">
         <v>46</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="14">
         <v>46</v>
       </c>
-      <c r="C49" s="13">
+      <c r="C49" s="14">
         <v>4</v>
       </c>
-      <c r="D49" s="13">
+      <c r="D49" s="14">
         <v>3</v>
       </c>
-      <c r="E49" s="13" t="s">
+      <c r="E49" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="13">
+      <c r="A50" s="14">
         <v>47</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="14">
         <v>47</v>
       </c>
-      <c r="C50" s="13">
+      <c r="C50" s="14">
         <v>4</v>
       </c>
-      <c r="D50" s="13">
+      <c r="D50" s="14">
         <v>3</v>
       </c>
-      <c r="E50" s="13" t="s">
+      <c r="E50" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="13">
+      <c r="A51" s="14">
         <v>48</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="14">
         <v>48</v>
       </c>
-      <c r="C51" s="13">
+      <c r="C51" s="14">
         <v>4</v>
       </c>
-      <c r="D51" s="13">
+      <c r="D51" s="14">
         <v>3</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="13">
+      <c r="A52" s="14">
         <v>49</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="14">
         <v>49</v>
       </c>
-      <c r="C52" s="13">
+      <c r="C52" s="14">
         <v>4</v>
       </c>
-      <c r="D52" s="13">
+      <c r="D52" s="14">
         <v>3</v>
       </c>
-      <c r="E52" s="13" t="s">
+      <c r="E52" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="13">
+      <c r="A53" s="14">
         <v>50</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="14">
         <v>50</v>
       </c>
-      <c r="C53" s="13">
+      <c r="C53" s="14">
         <v>4</v>
       </c>
-      <c r="D53" s="13">
+      <c r="D53" s="14">
         <v>3</v>
       </c>
-      <c r="E53" s="13" t="s">
+      <c r="E53" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="13">
+      <c r="A54" s="14">
         <v>51</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="14">
         <v>51</v>
       </c>
-      <c r="C54" s="13">
+      <c r="C54" s="14">
         <v>4</v>
       </c>
-      <c r="D54" s="13">
+      <c r="D54" s="14">
         <v>3</v>
       </c>
-      <c r="E54" s="13" t="s">
+      <c r="E54" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="13">
+      <c r="A55" s="14">
         <v>52</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="14">
         <v>52</v>
       </c>
-      <c r="C55" s="13">
+      <c r="C55" s="14">
         <v>4</v>
       </c>
-      <c r="D55" s="13">
+      <c r="D55" s="14">
         <v>3</v>
       </c>
-      <c r="E55" s="13" t="s">
+      <c r="E55" s="14" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5719,801 +5722,801 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="27.75" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="25.175" style="8" customWidth="1"/>
-    <col min="2" max="2" width="13.575" style="8" customWidth="1"/>
-    <col min="3" max="3" width="127.141666666667" style="8" customWidth="1"/>
-    <col min="4" max="4" width="49" style="8" customWidth="1"/>
-    <col min="5" max="5" width="92.9666666666667" style="9" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="25.175" style="9" customWidth="1"/>
+    <col min="2" max="2" width="13.575" style="9" customWidth="1"/>
+    <col min="3" max="3" width="127.141666666667" style="9" customWidth="1"/>
+    <col min="4" max="4" width="49" style="9" customWidth="1"/>
+    <col min="5" max="5" width="92.9666666666667" style="10" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="10">
+      <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="11">
         <v>1</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="10">
+      <c r="A5" s="11">
         <v>2</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="11">
         <v>2</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="10">
+      <c r="A6" s="11">
         <v>3</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <v>3</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="10">
+      <c r="A7" s="11">
         <v>4</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <v>4</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="10">
+      <c r="A8" s="11">
         <v>5</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <v>5</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="10">
+      <c r="A9" s="11">
         <v>6</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="11">
         <v>6</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="10">
+      <c r="A10" s="11">
         <v>7</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <v>7</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="10">
+      <c r="A11" s="11">
         <v>8</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <v>8</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="10">
+      <c r="A12" s="11">
         <v>9</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <v>9</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="10">
+      <c r="A13" s="11">
         <v>10</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="11">
         <v>10</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="10">
+      <c r="A14" s="11">
         <v>11</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="11">
         <v>11</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="10">
+      <c r="A15" s="11">
         <v>12</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="11">
         <v>12</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="10">
+      <c r="A16" s="11">
         <v>13</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="11">
         <v>13</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="10">
+      <c r="A17" s="11">
         <v>14</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="11">
         <v>14</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="10">
+      <c r="A18" s="11">
         <v>15</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="11">
         <v>15</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="10">
+      <c r="A19" s="11">
         <v>16</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="11">
         <v>16</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="10">
+      <c r="A20" s="11">
         <v>17</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="11">
         <v>17</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="10">
+      <c r="A21" s="11">
         <v>18</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="11">
         <v>18</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="10">
+      <c r="A22" s="11">
         <v>19</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="11">
         <v>19</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="10">
+      <c r="A23" s="11">
         <v>20</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="11">
         <v>20</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="10">
+      <c r="A24" s="11">
         <v>21</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="11">
         <v>21</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="10">
+      <c r="A25" s="11">
         <v>22</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="11">
         <v>22</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="10">
+      <c r="A26" s="11">
         <v>23</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="11">
         <v>23</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="10">
+      <c r="A27" s="11">
         <v>24</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="11">
         <v>24</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="10">
+      <c r="A28" s="11">
         <v>25</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="11">
         <v>25</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="10">
+      <c r="A29" s="11">
         <v>26</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="11">
         <v>26</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="10">
+      <c r="A30" s="11">
         <v>27</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="11">
         <v>27</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="10">
+      <c r="A31" s="11">
         <v>28</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="11">
         <v>28</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="10">
+      <c r="A32" s="11">
         <v>29</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="11">
         <v>29</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="10">
+      <c r="A33" s="11">
         <v>30</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="11">
         <v>30</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="10">
+      <c r="A34" s="11">
         <v>31</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="11">
         <v>31</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="10">
+      <c r="A35" s="11">
         <v>32</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="11">
         <v>32</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="10">
+      <c r="A36" s="11">
         <v>33</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="11">
         <v>33</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="10">
+      <c r="A37" s="11">
         <v>34</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="11">
         <v>34</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="10">
+      <c r="A38" s="11">
         <v>35</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="11">
         <v>35</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="10">
+      <c r="A39" s="11">
         <v>36</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="11">
         <v>36</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="10">
+      <c r="A40" s="11">
         <v>37</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="11">
         <v>37</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="10">
+      <c r="A41" s="11">
         <v>38</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="11">
         <v>38</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="10">
+      <c r="A42" s="11">
         <v>39</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="11">
         <v>39</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="11" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="11">
+      <c r="A43" s="12">
         <v>40</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="12">
         <v>40</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="11">
+      <c r="A44" s="12">
         <v>41</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="12">
         <v>41</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="D44" s="11" t="s">
+      <c r="D44" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="11">
+      <c r="A45" s="12">
         <v>42</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="12">
         <v>42</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="11">
+      <c r="A46" s="12">
         <v>43</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="12">
         <v>43</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="11">
+      <c r="A47" s="12">
         <v>44</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="12">
         <v>44</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="11">
+      <c r="A48" s="12">
         <v>45</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="12">
         <v>45</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="11">
+      <c r="A49" s="12">
         <v>46</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="12">
         <v>46</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="11">
+      <c r="A50" s="12">
         <v>47</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="12">
         <v>47</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="11">
+      <c r="A51" s="12">
         <v>48</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="12">
         <v>48</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="11">
+      <c r="A52" s="12">
         <v>49</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="12">
         <v>49</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="11">
+      <c r="A53" s="12">
         <v>50</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="12">
         <v>50</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="11">
+      <c r="A54" s="12">
         <v>51</v>
       </c>
-      <c r="B54" s="11">
+      <c r="B54" s="12">
         <v>51</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="11">
+      <c r="A55" s="12">
         <v>52</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55" s="12">
         <v>52</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="12" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="C58" s="11"/>
+      <c r="C58" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6631,10 +6634,10 @@
         <f>CEILING(A4/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <v>113244405937302</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="8" t="s">
         <v>154</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -6658,10 +6661,10 @@
         <f t="shared" ref="E5:E36" si="0">CEILING(A5/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <v>105711056874756</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>157</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -6687,10 +6690,10 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>82693303214454</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="8" t="s">
         <v>159</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -6716,10 +6719,10 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>102504658102706</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>161</v>
       </c>
       <c r="H7" s="2" t="s">
@@ -6745,10 +6748,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>83069096807916</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -6772,10 +6775,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>80534536398974</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="8" t="s">
         <v>165</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -6800,10 +6803,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <v>74246671448525</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>167</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -6828,10 +6831,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>71499702430100</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="8" t="s">
         <v>169</v>
       </c>
       <c r="H11" s="2" t="s">
@@ -6856,10 +6859,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>122909083001205</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="8" t="s">
         <v>171</v>
       </c>
       <c r="H12" s="2" t="s">
@@ -6883,10 +6886,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <v>128658267266293</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="8" t="s">
         <v>173</v>
       </c>
       <c r="H13" s="2" t="s">
@@ -6910,10 +6913,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="5">
         <v>134748387119946</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="8" t="s">
         <v>175</v>
       </c>
       <c r="H14" s="2" t="s">
@@ -6937,10 +6940,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="5">
         <v>131559815185521</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="8" t="s">
         <v>177</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -6964,10 +6967,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="5">
         <v>135406755438948</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="8" t="s">
         <v>179</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -6995,10 +6998,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="5">
         <v>128433990441931</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="8" t="s">
         <v>181</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -7026,10 +7029,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="5">
         <v>86357992624263</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="8" t="s">
         <v>183</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -7057,10 +7060,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="5">
         <v>96128137486525</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>185</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -7088,10 +7091,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="5">
         <v>131913492630514</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="8" t="s">
         <v>187</v>
       </c>
       <c r="H20" s="2" t="s">
@@ -7119,10 +7122,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="5">
         <v>119579899338192</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="8" t="s">
         <v>189</v>
       </c>
       <c r="H21" s="2" t="s">
@@ -7150,10 +7153,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="5">
         <v>82472089572732</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="8" t="s">
         <v>191</v>
       </c>
       <c r="H22" s="2" t="s">
@@ -7181,10 +7184,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="5">
         <v>104108852156434</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="8" t="s">
         <v>193</v>
       </c>
       <c r="H23" s="2" t="s">
@@ -7212,10 +7215,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="5">
         <v>79005623120233</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="8" t="s">
         <v>195</v>
       </c>
       <c r="H24" s="2" t="s">
@@ -7243,10 +7246,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="5">
         <v>97611938478078</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="8" t="s">
         <v>197</v>
       </c>
       <c r="H25" s="2" t="s">
@@ -7274,10 +7277,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="5">
         <v>81806655827798</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="8" t="s">
         <v>199</v>
       </c>
       <c r="H26" s="2" t="s">
@@ -7305,10 +7308,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F27" s="5">
         <v>105716218867716</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="8" t="s">
         <v>201</v>
       </c>
       <c r="H27" s="2" t="s">
@@ -7336,10 +7339,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="5">
         <v>128411546772202</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="8" t="s">
         <v>203</v>
       </c>
       <c r="H28" s="2" t="s">
@@ -7367,10 +7370,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="5">
         <v>139465058617680</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="8" t="s">
         <v>205</v>
       </c>
       <c r="H29" s="2" t="s">
@@ -7398,10 +7401,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="5">
         <v>81737011057690</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="G30" s="8" t="s">
         <v>207</v>
       </c>
       <c r="H30" s="2" t="s">
@@ -7429,10 +7432,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F31" s="4">
+      <c r="F31" s="5">
         <v>81445862907930</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="8" t="s">
         <v>209</v>
       </c>
       <c r="H31" s="2" t="s">
@@ -7460,10 +7463,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="5">
         <v>123098432383687</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="8" t="s">
         <v>211</v>
       </c>
       <c r="H32" s="2" t="s">
@@ -7491,10 +7494,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="5">
         <v>131796260838154</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="8" t="s">
         <v>213</v>
       </c>
       <c r="H33" s="2" t="s">
@@ -7518,10 +7521,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="5">
         <v>116376878683736</v>
       </c>
-      <c r="G34" s="7" t="s">
+      <c r="G34" s="8" t="s">
         <v>215</v>
       </c>
       <c r="H34" s="2" t="s">
@@ -7545,10 +7548,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="5">
         <v>100558097057142</v>
       </c>
-      <c r="G35" s="7" t="s">
+      <c r="G35" s="8" t="s">
         <v>217</v>
       </c>
       <c r="H35" s="2" t="s">
@@ -7572,10 +7575,10 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="5">
         <v>92332707761527</v>
       </c>
-      <c r="G36" s="7" t="s">
+      <c r="G36" s="8" t="s">
         <v>219</v>
       </c>
       <c r="H36" s="2" t="s">
@@ -7603,10 +7606,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>6</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="5">
         <v>108895787734224</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G37" s="8" t="s">
         <v>221</v>
       </c>
       <c r="H37" s="2" t="s">
@@ -7630,10 +7633,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>7</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="5">
         <v>95471681056681</v>
       </c>
-      <c r="G38" s="7" t="s">
+      <c r="G38" s="8" t="s">
         <v>223</v>
       </c>
       <c r="H38" s="2" t="s">
@@ -7657,10 +7660,10 @@
         <f t="shared" ref="E39:E72" si="1">CEILING(A39/4,1)</f>
         <v>9</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="5">
         <v>104955598295323</v>
       </c>
-      <c r="G39" s="7" t="s">
+      <c r="G39" s="8" t="s">
         <v>225</v>
       </c>
       <c r="H39" s="2" t="s">
@@ -7688,10 +7691,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="5">
         <v>103175883366340</v>
       </c>
-      <c r="G40" s="7" t="s">
+      <c r="G40" s="8" t="s">
         <v>227</v>
       </c>
       <c r="H40" s="2" t="s">
@@ -7719,10 +7722,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="5">
         <v>114247164745798</v>
       </c>
-      <c r="G41" s="7" t="s">
+      <c r="G41" s="8" t="s">
         <v>229</v>
       </c>
       <c r="H41" s="2" t="s">
@@ -7746,10 +7749,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F42" s="5">
         <v>86017047390182</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="G42" s="8" t="s">
         <v>231</v>
       </c>
       <c r="H42" s="2" t="s">
@@ -7773,10 +7776,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F43" s="4">
+      <c r="F43" s="5">
         <v>81373582816266</v>
       </c>
-      <c r="G43" s="7" t="s">
+      <c r="G43" s="8" t="s">
         <v>233</v>
       </c>
       <c r="H43" s="2" t="s">
@@ -7800,10 +7803,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F44" s="4">
+      <c r="F44" s="5">
         <v>132788281080826</v>
       </c>
-      <c r="G44" s="7" t="s">
+      <c r="G44" s="8" t="s">
         <v>235</v>
       </c>
       <c r="H44" s="2" t="s">
@@ -7827,10 +7830,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F45" s="4">
+      <c r="F45" s="5">
         <v>95162444285252</v>
       </c>
-      <c r="G45" s="7" t="s">
+      <c r="G45" s="8" t="s">
         <v>237</v>
       </c>
       <c r="H45" s="2" t="s">
@@ -7854,10 +7857,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="5">
         <v>95953438126479</v>
       </c>
-      <c r="G46" s="7" t="s">
+      <c r="G46" s="8" t="s">
         <v>239</v>
       </c>
       <c r="H46" s="2" t="s">
@@ -7881,10 +7884,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="5">
         <v>112039222887887</v>
       </c>
-      <c r="G47" s="7" t="s">
+      <c r="G47" s="8" t="s">
         <v>241</v>
       </c>
       <c r="H47" s="2" t="s">
@@ -7908,10 +7911,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F48" s="4">
+      <c r="F48" s="5">
         <v>95377459606647</v>
       </c>
-      <c r="G48" s="7" t="s">
+      <c r="G48" s="8" t="s">
         <v>243</v>
       </c>
       <c r="H48" s="2" t="s">
@@ -7935,10 +7938,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F49" s="4">
+      <c r="F49" s="5">
         <v>113983796605688</v>
       </c>
-      <c r="G49" s="7" t="s">
+      <c r="G49" s="8" t="s">
         <v>245</v>
       </c>
       <c r="H49" s="2" t="s">
@@ -7962,10 +7965,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F50" s="4">
+      <c r="F50" s="5">
         <v>117157716541352</v>
       </c>
-      <c r="G50" s="7" t="s">
+      <c r="G50" s="8" t="s">
         <v>247</v>
       </c>
       <c r="H50" s="2" t="s">
@@ -7989,10 +7992,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F51" s="4">
+      <c r="F51" s="5">
         <v>100893051807474</v>
       </c>
-      <c r="G51" s="7" t="s">
+      <c r="G51" s="8" t="s">
         <v>249</v>
       </c>
       <c r="H51" s="2" t="s">
@@ -8016,10 +8019,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F52" s="4">
+      <c r="F52" s="5">
         <v>137999782231090</v>
       </c>
-      <c r="G52" s="7" t="s">
+      <c r="G52" s="8" t="s">
         <v>251</v>
       </c>
       <c r="H52" s="2" t="s">
@@ -8043,10 +8046,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F53" s="4">
+      <c r="F53" s="5">
         <v>127007149281218</v>
       </c>
-      <c r="G53" s="7" t="s">
+      <c r="G53" s="8" t="s">
         <v>253</v>
       </c>
       <c r="H53" s="2" t="s">
@@ -8070,10 +8073,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F54" s="4">
+      <c r="F54" s="5">
         <v>85273469740405</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G54" s="8" t="s">
         <v>255</v>
       </c>
       <c r="H54" s="2" t="s">
@@ -8097,10 +8100,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55" s="5">
         <v>85750403977754</v>
       </c>
-      <c r="G55" s="7" t="s">
+      <c r="G55" s="8" t="s">
         <v>257</v>
       </c>
       <c r="H55" s="2" t="s">
@@ -8124,10 +8127,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F56" s="4">
+      <c r="F56" s="5">
         <v>87658125570749</v>
       </c>
-      <c r="G56" s="7" t="s">
+      <c r="G56" s="8" t="s">
         <v>259</v>
       </c>
       <c r="H56" s="2" t="s">
@@ -8151,10 +8154,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F57" s="4">
+      <c r="F57" s="5">
         <v>71386503893388</v>
       </c>
-      <c r="G57" s="7" t="s">
+      <c r="G57" s="8" t="s">
         <v>261</v>
       </c>
       <c r="H57" s="2" t="s">
@@ -8178,10 +8181,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F58" s="4">
+      <c r="F58" s="5">
         <v>117660867991736</v>
       </c>
-      <c r="G58" s="7" t="s">
+      <c r="G58" s="8" t="s">
         <v>263</v>
       </c>
       <c r="H58" s="2" t="s">
@@ -8205,10 +8208,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F59" s="4">
+      <c r="F59" s="5">
         <v>75602786825729</v>
       </c>
-      <c r="G59" s="7" t="s">
+      <c r="G59" s="8" t="s">
         <v>265</v>
       </c>
       <c r="H59" s="2" t="s">
@@ -8232,10 +8235,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="5">
         <v>97494295137425</v>
       </c>
-      <c r="G60" s="7" t="s">
+      <c r="G60" s="8" t="s">
         <v>267</v>
       </c>
       <c r="H60" s="2" t="s">
@@ -8259,10 +8262,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="5">
         <v>121387106380169</v>
       </c>
-      <c r="G61" s="7" t="s">
+      <c r="G61" s="8" t="s">
         <v>269</v>
       </c>
       <c r="H61" s="2" t="s">
@@ -8286,10 +8289,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F62" s="4">
+      <c r="F62" s="5">
         <v>77703154963129</v>
       </c>
-      <c r="G62" s="7" t="s">
+      <c r="G62" s="8" t="s">
         <v>271</v>
       </c>
       <c r="H62" s="2" t="s">
@@ -8313,10 +8316,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="5">
         <v>82745313217810</v>
       </c>
-      <c r="G63" s="7" t="s">
+      <c r="G63" s="8" t="s">
         <v>273</v>
       </c>
       <c r="H63" s="2" t="s">
@@ -8340,10 +8343,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F64" s="5">
         <v>78702263483439</v>
       </c>
-      <c r="G64" s="7" t="s">
+      <c r="G64" s="8" t="s">
         <v>275</v>
       </c>
       <c r="H64" s="2" t="s">
@@ -8367,10 +8370,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F65" s="5">
         <v>103252845267522</v>
       </c>
-      <c r="G65" s="7" t="s">
+      <c r="G65" s="8" t="s">
         <v>277</v>
       </c>
       <c r="H65" s="2" t="s">
@@ -8394,10 +8397,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F66" s="5">
         <v>93380659059014</v>
       </c>
-      <c r="G66" s="7" t="s">
+      <c r="G66" s="8" t="s">
         <v>279</v>
       </c>
       <c r="H66" s="2" t="s">
@@ -8421,10 +8424,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="5">
         <v>124070618735034</v>
       </c>
-      <c r="G67" s="7" t="s">
+      <c r="G67" s="8" t="s">
         <v>281</v>
       </c>
       <c r="H67" s="2" t="s">
@@ -8448,10 +8451,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F68" s="5">
         <v>82229267783572</v>
       </c>
-      <c r="G68" s="7" t="s">
+      <c r="G68" s="8" t="s">
         <v>283</v>
       </c>
       <c r="H68" s="2" t="s">
@@ -8475,10 +8478,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F69" s="5">
         <v>90764663625426</v>
       </c>
-      <c r="G69" s="7" t="s">
+      <c r="G69" s="8" t="s">
         <v>285</v>
       </c>
       <c r="H69" s="2" t="s">
@@ -8502,10 +8505,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F70" s="4">
+      <c r="F70" s="5">
         <v>89592774326120</v>
       </c>
-      <c r="G70" s="7" t="s">
+      <c r="G70" s="8" t="s">
         <v>287</v>
       </c>
       <c r="H70" s="2" t="s">
@@ -8529,10 +8532,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F71" s="4">
+      <c r="F71" s="5">
         <v>96498729983354</v>
       </c>
-      <c r="G71" s="7" t="s">
+      <c r="G71" s="8" t="s">
         <v>289</v>
       </c>
       <c r="H71" s="2" t="s">
@@ -8556,10 +8559,10 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F72" s="5">
         <v>137402232463633</v>
       </c>
-      <c r="G72" s="7" t="s">
+      <c r="G72" s="8" t="s">
         <v>291</v>
       </c>
       <c r="H72" s="2" t="s">
@@ -8583,10 +8586,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>15</v>
       </c>
-      <c r="F73" s="4">
+      <c r="F73" s="5">
         <v>79717469784936</v>
       </c>
-      <c r="G73" s="7" t="s">
+      <c r="G73" s="8" t="s">
         <v>293</v>
       </c>
       <c r="H73" s="2" t="s">
@@ -8610,10 +8613,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F74" s="5">
         <v>86646811474956</v>
       </c>
-      <c r="G74" s="7" t="s">
+      <c r="G74" s="8" t="s">
         <v>295</v>
       </c>
       <c r="H74" s="2" t="s">
@@ -8637,10 +8640,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F75" s="4">
+      <c r="F75" s="5">
         <v>128217347353354</v>
       </c>
-      <c r="G75" s="7" t="s">
+      <c r="G75" s="8" t="s">
         <v>297</v>
       </c>
       <c r="H75" s="2" t="s">
@@ -8664,10 +8667,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F76" s="5">
         <v>126321668579357</v>
       </c>
-      <c r="G76" s="7" t="s">
+      <c r="G76" s="8" t="s">
         <v>299</v>
       </c>
       <c r="H76" s="2" t="s">
@@ -8691,10 +8694,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F77" s="4">
+      <c r="F77" s="5">
         <v>98351529529203</v>
       </c>
-      <c r="G77" s="7" t="s">
+      <c r="G77" s="8" t="s">
         <v>301</v>
       </c>
       <c r="H77" s="2" t="s">
@@ -8718,10 +8721,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F78" s="4">
+      <c r="F78" s="5">
         <v>81048668172712</v>
       </c>
-      <c r="G78" s="7" t="s">
+      <c r="G78" s="8" t="s">
         <v>303</v>
       </c>
       <c r="H78" s="2" t="s">
@@ -8745,10 +8748,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F79" s="4">
+      <c r="F79" s="5">
         <v>127615544859575</v>
       </c>
-      <c r="G79" s="7" t="s">
+      <c r="G79" s="8" t="s">
         <v>305</v>
       </c>
       <c r="H79" s="2" t="s">
@@ -8772,10 +8775,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F80" s="4">
+      <c r="F80" s="5">
         <v>70656304136373</v>
       </c>
-      <c r="G80" s="7" t="s">
+      <c r="G80" s="8" t="s">
         <v>307</v>
       </c>
       <c r="H80" s="2" t="s">
@@ -8799,10 +8802,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F81" s="4">
+      <c r="F81" s="5">
         <v>134424174805013</v>
       </c>
-      <c r="G81" s="7" t="s">
+      <c r="G81" s="8" t="s">
         <v>309</v>
       </c>
       <c r="H81" s="2" t="s">
@@ -8826,10 +8829,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F82" s="4">
+      <c r="F82" s="5">
         <v>127255485663084</v>
       </c>
-      <c r="G82" s="7" t="s">
+      <c r="G82" s="8" t="s">
         <v>311</v>
       </c>
       <c r="H82" s="2" t="s">
@@ -8853,10 +8856,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F83" s="5">
         <v>134027683373658</v>
       </c>
-      <c r="G83" s="7" t="s">
+      <c r="G83" s="8" t="s">
         <v>313</v>
       </c>
       <c r="H83" s="2" t="s">
@@ -8880,10 +8883,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F84" s="5">
         <v>112447657334137</v>
       </c>
-      <c r="G84" s="7" t="s">
+      <c r="G84" s="8" t="s">
         <v>315</v>
       </c>
       <c r="H84" s="2" t="s">
@@ -8907,10 +8910,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F85" s="4">
+      <c r="F85" s="5">
         <v>104595008892706</v>
       </c>
-      <c r="G85" s="7" t="s">
+      <c r="G85" s="8" t="s">
         <v>317</v>
       </c>
       <c r="H85" s="2" t="s">
@@ -8934,10 +8937,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F86" s="5">
         <v>82759045606098</v>
       </c>
-      <c r="G86" s="7" t="s">
+      <c r="G86" s="8" t="s">
         <v>319</v>
       </c>
       <c r="H86" s="2" t="s">
@@ -8961,10 +8964,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F87" s="4">
+      <c r="F87" s="5">
         <v>105620837789519</v>
       </c>
-      <c r="G87" s="7" t="s">
+      <c r="G87" s="8" t="s">
         <v>321</v>
       </c>
       <c r="H87" s="2" t="s">
@@ -8988,10 +8991,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F88" s="5">
         <v>111024567754480</v>
       </c>
-      <c r="G88" s="7" t="s">
+      <c r="G88" s="8" t="s">
         <v>323</v>
       </c>
       <c r="H88" s="2" t="s">
@@ -9015,10 +9018,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F89" s="5">
         <v>137153989969007</v>
       </c>
-      <c r="G89" s="7" t="s">
+      <c r="G89" s="8" t="s">
         <v>325</v>
       </c>
       <c r="H89" s="2" t="s">
@@ -9042,10 +9045,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F90" s="4">
+      <c r="F90" s="5">
         <v>74496996195913</v>
       </c>
-      <c r="G90" s="7" t="s">
+      <c r="G90" s="8" t="s">
         <v>327</v>
       </c>
       <c r="H90" s="2" t="s">
@@ -9069,10 +9072,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="5">
         <v>132785860315163</v>
       </c>
-      <c r="G91" s="7" t="s">
+      <c r="G91" s="8" t="s">
         <v>329</v>
       </c>
       <c r="H91" s="2" t="s">
@@ -9096,10 +9099,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F92" s="4">
+      <c r="F92" s="5">
         <v>117198962948319</v>
       </c>
-      <c r="G92" s="7" t="s">
+      <c r="G92" s="8" t="s">
         <v>331</v>
       </c>
       <c r="H92" s="2" t="s">
@@ -9123,10 +9126,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F93" s="4">
+      <c r="F93" s="5">
         <v>124449160476895</v>
       </c>
-      <c r="G93" s="7" t="s">
+      <c r="G93" s="8" t="s">
         <v>333</v>
       </c>
       <c r="H93" s="2" t="s">
@@ -9150,10 +9153,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F94" s="4">
+      <c r="F94" s="5">
         <v>125887863438527</v>
       </c>
-      <c r="G94" s="7" t="s">
+      <c r="G94" s="8" t="s">
         <v>335</v>
       </c>
       <c r="H94" s="2" t="s">
@@ -9177,10 +9180,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F95" s="4">
+      <c r="F95" s="5">
         <v>137692564728429</v>
       </c>
-      <c r="G95" s="7" t="s">
+      <c r="G95" s="8" t="s">
         <v>337</v>
       </c>
       <c r="H95" s="2" t="s">
@@ -9204,10 +9207,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F96" s="4">
+      <c r="F96" s="5">
         <v>82350951870220</v>
       </c>
-      <c r="G96" s="7" t="s">
+      <c r="G96" s="8" t="s">
         <v>339</v>
       </c>
       <c r="H96" s="2" t="s">
@@ -9231,10 +9234,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F97" s="4">
+      <c r="F97" s="5">
         <v>133019385929561</v>
       </c>
-      <c r="G97" s="7" t="s">
+      <c r="G97" s="8" t="s">
         <v>341</v>
       </c>
       <c r="H97" s="2" t="s">
@@ -9258,10 +9261,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F98" s="4">
+      <c r="F98" s="5">
         <v>82714807302588</v>
       </c>
-      <c r="G98" s="7" t="s">
+      <c r="G98" s="8" t="s">
         <v>343</v>
       </c>
       <c r="H98" s="2" t="s">
@@ -9285,10 +9288,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F99" s="4">
+      <c r="F99" s="5">
         <v>120409278538446</v>
       </c>
-      <c r="G99" s="7" t="s">
+      <c r="G99" s="8" t="s">
         <v>345</v>
       </c>
       <c r="H99" s="2" t="s">
@@ -9312,10 +9315,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F100" s="4">
+      <c r="F100" s="5">
         <v>136303201068741</v>
       </c>
-      <c r="G100" s="7" t="s">
+      <c r="G100" s="8" t="s">
         <v>347</v>
       </c>
       <c r="H100" s="2" t="s">
@@ -9339,10 +9342,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F101" s="4">
+      <c r="F101" s="5">
         <v>76724781858184</v>
       </c>
-      <c r="G101" s="7" t="s">
+      <c r="G101" s="8" t="s">
         <v>349</v>
       </c>
       <c r="H101" s="2" t="s">
@@ -9366,10 +9369,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F102" s="4">
+      <c r="F102" s="5">
         <v>120125979830927</v>
       </c>
-      <c r="G102" s="7" t="s">
+      <c r="G102" s="8" t="s">
         <v>351</v>
       </c>
       <c r="H102" s="2" t="s">
@@ -9393,10 +9396,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F103" s="4">
+      <c r="F103" s="5">
         <v>86921870572603</v>
       </c>
-      <c r="G103" s="7" t="s">
+      <c r="G103" s="8" t="s">
         <v>353</v>
       </c>
       <c r="H103" s="2" t="s">
@@ -9420,10 +9423,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F104" s="4">
+      <c r="F104" s="5">
         <v>126355990231048</v>
       </c>
-      <c r="G104" s="7" t="s">
+      <c r="G104" s="8" t="s">
         <v>355</v>
       </c>
       <c r="H104" s="2" t="s">
@@ -9447,10 +9450,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F105" s="4">
+      <c r="F105" s="5">
         <v>72326444062448</v>
       </c>
-      <c r="G105" s="7" t="s">
+      <c r="G105" s="8" t="s">
         <v>357</v>
       </c>
       <c r="H105" s="2" t="s">
@@ -9474,10 +9477,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F106" s="4">
+      <c r="F106" s="5">
         <v>72257499044823</v>
       </c>
-      <c r="G106" s="7" t="s">
+      <c r="G106" s="8" t="s">
         <v>359</v>
       </c>
       <c r="H106" s="2" t="s">
@@ -9501,10 +9504,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F107" s="4">
+      <c r="F107" s="5">
         <v>74695865349139</v>
       </c>
-      <c r="G107" s="7" t="s">
+      <c r="G107" s="8" t="s">
         <v>361</v>
       </c>
       <c r="H107" s="2" t="s">
@@ -9527,10 +9530,10 @@
       <c r="E108" s="1">
         <v>24</v>
       </c>
-      <c r="F108" s="4">
+      <c r="F108" s="5">
         <v>98358488442985</v>
       </c>
-      <c r="G108" s="7" t="s">
+      <c r="G108" s="8" t="s">
         <v>363</v>
       </c>
       <c r="H108" s="2" t="s">
@@ -9554,10 +9557,10 @@
       <c r="E109" s="1">
         <v>24</v>
       </c>
-      <c r="F109" s="4">
+      <c r="F109" s="5">
         <v>113636295509693</v>
       </c>
-      <c r="G109" s="7" t="s">
+      <c r="G109" s="8" t="s">
         <v>365</v>
       </c>
       <c r="H109" s="2" t="s">
@@ -9581,10 +9584,10 @@
       <c r="E110" s="1">
         <v>25</v>
       </c>
-      <c r="F110" s="4">
+      <c r="F110" s="5">
         <v>114047124407739</v>
       </c>
-      <c r="G110" s="7" t="s">
+      <c r="G110" s="8" t="s">
         <v>367</v>
       </c>
       <c r="H110" s="2" t="s">
@@ -9608,10 +9611,10 @@
       <c r="E111" s="1">
         <v>25</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="5">
         <v>95771403493939</v>
       </c>
-      <c r="G111" s="7" t="s">
+      <c r="G111" s="8" t="s">
         <v>369</v>
       </c>
       <c r="H111" s="2" t="s">
@@ -9635,10 +9638,10 @@
       <c r="E112" s="1">
         <v>25</v>
       </c>
-      <c r="F112" s="4">
+      <c r="F112" s="5">
         <v>140393673870516</v>
       </c>
-      <c r="G112" s="7" t="s">
+      <c r="G112" s="8" t="s">
         <v>371</v>
       </c>
       <c r="H112" s="2" t="s">
@@ -9662,10 +9665,10 @@
       <c r="E113" s="1">
         <v>25</v>
       </c>
-      <c r="F113" s="4">
+      <c r="F113" s="5">
         <v>123109322631502</v>
       </c>
-      <c r="G113" s="7" t="s">
+      <c r="G113" s="8" t="s">
         <v>373</v>
       </c>
       <c r="H113" s="2" t="s">
@@ -9689,10 +9692,10 @@
       <c r="E114" s="1">
         <v>26</v>
       </c>
-      <c r="F114" s="4">
+      <c r="F114" s="5">
         <v>98614967981417</v>
       </c>
-      <c r="G114" s="7" t="s">
+      <c r="G114" s="8" t="s">
         <v>375</v>
       </c>
       <c r="H114" s="2" t="s">
@@ -9716,10 +9719,10 @@
       <c r="E115" s="1">
         <v>26</v>
       </c>
-      <c r="F115" s="4">
+      <c r="F115" s="5">
         <v>127369769981706</v>
       </c>
-      <c r="G115" s="7" t="s">
+      <c r="G115" s="8" t="s">
         <v>377</v>
       </c>
       <c r="H115" s="2" t="s">
@@ -9743,10 +9746,10 @@
       <c r="E116" s="1">
         <v>26</v>
       </c>
-      <c r="F116" s="4">
+      <c r="F116" s="5">
         <v>134574393827781</v>
       </c>
-      <c r="G116" s="7" t="s">
+      <c r="G116" s="8" t="s">
         <v>379</v>
       </c>
       <c r="H116" s="2" t="s">
@@ -9770,10 +9773,10 @@
       <c r="E117" s="1">
         <v>26</v>
       </c>
-      <c r="F117" s="4">
+      <c r="F117" s="5">
         <v>130258203281991</v>
       </c>
-      <c r="G117" s="7" t="s">
+      <c r="G117" s="8" t="s">
         <v>381</v>
       </c>
       <c r="H117" s="2" t="s">
@@ -9797,10 +9800,10 @@
       <c r="E118" s="1">
         <v>27</v>
       </c>
-      <c r="F118" s="4">
+      <c r="F118" s="5">
         <v>93953823085119</v>
       </c>
-      <c r="G118" s="7" t="s">
+      <c r="G118" s="8" t="s">
         <v>383</v>
       </c>
       <c r="H118" s="2" t="s">
@@ -9824,10 +9827,10 @@
       <c r="E119" s="1">
         <v>27</v>
       </c>
-      <c r="F119" s="4">
+      <c r="F119" s="5">
         <v>109802560542166</v>
       </c>
-      <c r="G119" s="7" t="s">
+      <c r="G119" s="8" t="s">
         <v>385</v>
       </c>
       <c r="H119" s="2" t="s">
@@ -9851,10 +9854,10 @@
       <c r="E120" s="1">
         <v>27</v>
       </c>
-      <c r="F120" s="4">
+      <c r="F120" s="5">
         <v>130989494782889</v>
       </c>
-      <c r="G120" s="7" t="s">
+      <c r="G120" s="8" t="s">
         <v>387</v>
       </c>
       <c r="H120" s="2" t="s">
@@ -9878,10 +9881,10 @@
       <c r="E121" s="1">
         <v>27</v>
       </c>
-      <c r="F121" s="4">
+      <c r="F121" s="5">
         <v>129408716253336</v>
       </c>
-      <c r="G121" s="7" t="s">
+      <c r="G121" s="8" t="s">
         <v>389</v>
       </c>
       <c r="H121" s="2" t="s">
@@ -9905,10 +9908,10 @@
       <c r="E122" s="1">
         <v>28</v>
       </c>
-      <c r="F122" s="4">
+      <c r="F122" s="5">
         <v>127772866805590</v>
       </c>
-      <c r="G122" s="7" t="s">
+      <c r="G122" s="8" t="s">
         <v>391</v>
       </c>
       <c r="H122" s="2" t="s">
@@ -9932,10 +9935,10 @@
       <c r="E123" s="1">
         <v>28</v>
       </c>
-      <c r="F123" s="4">
+      <c r="F123" s="5">
         <v>91938109188463</v>
       </c>
-      <c r="G123" s="7" t="s">
+      <c r="G123" s="8" t="s">
         <v>393</v>
       </c>
       <c r="H123" s="2" t="s">
@@ -9959,10 +9962,10 @@
       <c r="E124" s="1">
         <v>28</v>
       </c>
-      <c r="F124" s="4">
+      <c r="F124" s="5">
         <v>85077262752129</v>
       </c>
-      <c r="G124" s="7" t="s">
+      <c r="G124" s="8" t="s">
         <v>395</v>
       </c>
       <c r="H124" s="2" t="s">
@@ -9977,7 +9980,7 @@
       <c r="B125" s="1">
         <v>122</v>
       </c>
-      <c r="C125" s="7" t="s">
+      <c r="C125" s="8" t="s">
         <v>396</v>
       </c>
       <c r="D125" s="1">
@@ -9986,10 +9989,10 @@
       <c r="E125" s="1">
         <v>28</v>
       </c>
-      <c r="F125" s="4">
+      <c r="F125" s="5">
         <v>140335958193244</v>
       </c>
-      <c r="G125" s="7" t="s">
+      <c r="G125" s="8" t="s">
         <v>397</v>
       </c>
       <c r="H125" s="2" t="s">
@@ -10003,7 +10006,7 @@
       <c r="B126" s="1">
         <v>123</v>
       </c>
-      <c r="C126" s="7" t="s">
+      <c r="C126" s="8" t="s">
         <v>398</v>
       </c>
       <c r="D126" s="1">
@@ -10012,10 +10015,10 @@
       <c r="E126" s="1">
         <v>29</v>
       </c>
-      <c r="F126" s="4">
+      <c r="F126" s="5">
         <v>86732012145983</v>
       </c>
-      <c r="G126" s="7" t="s">
+      <c r="G126" s="8" t="s">
         <v>399</v>
       </c>
       <c r="H126" s="2" t="s">
@@ -10029,7 +10032,7 @@
       <c r="B127" s="1">
         <v>124</v>
       </c>
-      <c r="C127" s="7" t="s">
+      <c r="C127" s="8" t="s">
         <v>400</v>
       </c>
       <c r="D127" s="1">
@@ -10038,10 +10041,10 @@
       <c r="E127" s="1">
         <v>29</v>
       </c>
-      <c r="F127" s="4">
+      <c r="F127" s="5">
         <v>78044122276865</v>
       </c>
-      <c r="G127" s="7" t="s">
+      <c r="G127" s="8" t="s">
         <v>401</v>
       </c>
       <c r="H127" s="2" t="s">
@@ -10055,7 +10058,7 @@
       <c r="B128" s="1">
         <v>125</v>
       </c>
-      <c r="C128" s="7" t="s">
+      <c r="C128" s="8" t="s">
         <v>402</v>
       </c>
       <c r="D128" s="1">
@@ -10064,10 +10067,10 @@
       <c r="E128" s="1">
         <v>29</v>
       </c>
-      <c r="F128" s="4">
+      <c r="F128" s="5">
         <v>114974638199136</v>
       </c>
-      <c r="G128" s="7" t="s">
+      <c r="G128" s="8" t="s">
         <v>403</v>
       </c>
       <c r="H128" s="2" t="s">
@@ -10081,7 +10084,7 @@
       <c r="B129" s="1">
         <v>126</v>
       </c>
-      <c r="C129" s="7" t="s">
+      <c r="C129" s="8" t="s">
         <v>404</v>
       </c>
       <c r="D129" s="1">
@@ -10090,10 +10093,10 @@
       <c r="E129" s="1">
         <v>29</v>
       </c>
-      <c r="F129" s="4">
+      <c r="F129" s="5">
         <v>83652207307759</v>
       </c>
-      <c r="G129" s="7" t="s">
+      <c r="G129" s="8" t="s">
         <v>405</v>
       </c>
       <c r="H129" s="2" t="s">
@@ -10107,7 +10110,7 @@
       <c r="B130" s="1">
         <v>127</v>
       </c>
-      <c r="C130" s="7" t="s">
+      <c r="C130" s="8" t="s">
         <v>406</v>
       </c>
       <c r="D130" s="1">
@@ -10116,10 +10119,10 @@
       <c r="E130" s="1">
         <v>30</v>
       </c>
-      <c r="F130" s="4">
+      <c r="F130" s="5">
         <v>131787091355052</v>
       </c>
-      <c r="G130" s="7" t="s">
+      <c r="G130" s="8" t="s">
         <v>407</v>
       </c>
       <c r="H130" s="2" t="s">
@@ -10133,7 +10136,7 @@
       <c r="B131" s="1">
         <v>128</v>
       </c>
-      <c r="C131" s="7" t="s">
+      <c r="C131" s="8" t="s">
         <v>408</v>
       </c>
       <c r="D131" s="1">
@@ -10142,10 +10145,10 @@
       <c r="E131" s="1">
         <v>30</v>
       </c>
-      <c r="F131" s="4">
+      <c r="F131" s="5">
         <v>99348381699835</v>
       </c>
-      <c r="G131" s="7" t="s">
+      <c r="G131" s="8" t="s">
         <v>409</v>
       </c>
       <c r="H131" s="2" t="s">
@@ -10159,7 +10162,7 @@
       <c r="B132" s="1">
         <v>129</v>
       </c>
-      <c r="C132" s="7" t="s">
+      <c r="C132" s="8" t="s">
         <v>410</v>
       </c>
       <c r="D132" s="1">
@@ -10168,10 +10171,10 @@
       <c r="E132" s="1">
         <v>30</v>
       </c>
-      <c r="F132" s="4">
+      <c r="F132" s="5">
         <v>75412160560516</v>
       </c>
-      <c r="G132" s="7" t="s">
+      <c r="G132" s="8" t="s">
         <v>411</v>
       </c>
       <c r="H132" s="2" t="s">
@@ -10185,7 +10188,7 @@
       <c r="B133" s="1">
         <v>130</v>
       </c>
-      <c r="C133" s="7" t="s">
+      <c r="C133" s="8" t="s">
         <v>412</v>
       </c>
       <c r="D133" s="1">
@@ -10194,10 +10197,10 @@
       <c r="E133" s="1">
         <v>30</v>
       </c>
-      <c r="F133" s="4">
+      <c r="F133" s="5">
         <v>105475505052937</v>
       </c>
-      <c r="G133" s="7" t="s">
+      <c r="G133" s="8" t="s">
         <v>413</v>
       </c>
       <c r="H133" s="2" t="s">
@@ -10211,7 +10214,7 @@
       <c r="B134" s="1">
         <v>131</v>
       </c>
-      <c r="C134" s="7" t="s">
+      <c r="C134" s="8" t="s">
         <v>414</v>
       </c>
       <c r="D134" s="1">
@@ -10220,10 +10223,10 @@
       <c r="E134" s="1">
         <v>31</v>
       </c>
-      <c r="F134" s="4">
+      <c r="F134" s="5">
         <v>125484119033793</v>
       </c>
-      <c r="G134" s="7" t="s">
+      <c r="G134" s="8" t="s">
         <v>415</v>
       </c>
       <c r="H134" s="2" t="s">
@@ -10237,7 +10240,7 @@
       <c r="B135" s="1">
         <v>132</v>
       </c>
-      <c r="C135" s="7" t="s">
+      <c r="C135" s="8" t="s">
         <v>416</v>
       </c>
       <c r="D135" s="1">
@@ -10246,10 +10249,10 @@
       <c r="E135" s="1">
         <v>31</v>
       </c>
-      <c r="F135" s="4">
+      <c r="F135" s="5">
         <v>140608831780254</v>
       </c>
-      <c r="G135" s="7" t="s">
+      <c r="G135" s="8" t="s">
         <v>417</v>
       </c>
       <c r="H135" s="2" t="s">
@@ -10263,7 +10266,7 @@
       <c r="B136" s="1">
         <v>133</v>
       </c>
-      <c r="C136" s="7" t="s">
+      <c r="C136" s="8" t="s">
         <v>418</v>
       </c>
       <c r="D136" s="1">
@@ -10272,10 +10275,10 @@
       <c r="E136" s="1">
         <v>31</v>
       </c>
-      <c r="F136" s="4">
+      <c r="F136" s="5">
         <v>124177358025481</v>
       </c>
-      <c r="G136" s="7" t="s">
+      <c r="G136" s="8" t="s">
         <v>419</v>
       </c>
       <c r="H136" s="2" t="s">
@@ -10289,7 +10292,7 @@
       <c r="B137" s="1">
         <v>134</v>
       </c>
-      <c r="C137" s="7" t="s">
+      <c r="C137" s="8" t="s">
         <v>420</v>
       </c>
       <c r="D137" s="1">
@@ -10298,10 +10301,10 @@
       <c r="E137" s="1">
         <v>31</v>
       </c>
-      <c r="F137" s="4">
+      <c r="F137" s="5">
         <v>129385390119523</v>
       </c>
-      <c r="G137" s="7" t="s">
+      <c r="G137" s="8" t="s">
         <v>421</v>
       </c>
       <c r="H137" s="2" t="s">
@@ -10315,7 +10318,7 @@
       <c r="B138" s="1">
         <v>135</v>
       </c>
-      <c r="C138" s="7" t="s">
+      <c r="C138" s="8" t="s">
         <v>422</v>
       </c>
       <c r="D138" s="1">
@@ -10324,10 +10327,10 @@
       <c r="E138" s="1">
         <v>32</v>
       </c>
-      <c r="F138" s="4">
+      <c r="F138" s="5">
         <v>84940520003035</v>
       </c>
-      <c r="G138" s="7" t="s">
+      <c r="G138" s="8" t="s">
         <v>423</v>
       </c>
       <c r="H138" s="2" t="s">
@@ -10341,7 +10344,7 @@
       <c r="B139" s="1">
         <v>136</v>
       </c>
-      <c r="C139" s="7" t="s">
+      <c r="C139" s="8" t="s">
         <v>424</v>
       </c>
       <c r="D139" s="1">
@@ -10350,10 +10353,10 @@
       <c r="E139" s="1">
         <v>32</v>
       </c>
-      <c r="F139" s="4">
+      <c r="F139" s="5">
         <v>90031364711610</v>
       </c>
-      <c r="G139" s="7" t="s">
+      <c r="G139" s="8" t="s">
         <v>425</v>
       </c>
       <c r="H139" s="2" t="s">
@@ -10367,7 +10370,7 @@
       <c r="B140" s="1">
         <v>137</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="C140" s="8" t="s">
         <v>426</v>
       </c>
       <c r="D140" s="1">
@@ -10376,10 +10379,10 @@
       <c r="E140" s="1">
         <v>32</v>
       </c>
-      <c r="F140" s="4">
+      <c r="F140" s="5">
         <v>84418341821320</v>
       </c>
-      <c r="G140" s="7" t="s">
+      <c r="G140" s="8" t="s">
         <v>427</v>
       </c>
       <c r="H140" s="2" t="s">
@@ -10393,7 +10396,7 @@
       <c r="B141" s="1">
         <v>138</v>
       </c>
-      <c r="C141" s="7" t="s">
+      <c r="C141" s="8" t="s">
         <v>428</v>
       </c>
       <c r="D141" s="1">
@@ -10402,10 +10405,10 @@
       <c r="E141" s="1">
         <v>32</v>
       </c>
-      <c r="F141" s="4">
+      <c r="F141" s="5">
         <v>130255705800444</v>
       </c>
-      <c r="G141" s="7" t="s">
+      <c r="G141" s="8" t="s">
         <v>429</v>
       </c>
       <c r="H141" s="2" t="s">
@@ -10419,7 +10422,7 @@
       <c r="B142" s="1">
         <v>139</v>
       </c>
-      <c r="C142" s="7" t="s">
+      <c r="C142" s="8" t="s">
         <v>430</v>
       </c>
       <c r="D142" s="1">
@@ -10428,10 +10431,10 @@
       <c r="E142" s="1">
         <v>33</v>
       </c>
-      <c r="F142" s="4">
+      <c r="F142" s="5">
         <v>123568265278671</v>
       </c>
-      <c r="G142" s="7" t="s">
+      <c r="G142" s="8" t="s">
         <v>431</v>
       </c>
       <c r="H142" s="2" t="s">
@@ -10445,7 +10448,7 @@
       <c r="B143" s="1">
         <v>140</v>
       </c>
-      <c r="C143" s="7" t="s">
+      <c r="C143" s="8" t="s">
         <v>432</v>
       </c>
       <c r="D143" s="1">
@@ -10454,10 +10457,10 @@
       <c r="E143" s="1">
         <v>33</v>
       </c>
-      <c r="F143" s="4">
+      <c r="F143" s="5">
         <v>75689117044416</v>
       </c>
-      <c r="G143" s="7" t="s">
+      <c r="G143" s="8" t="s">
         <v>433</v>
       </c>
       <c r="H143" s="2" t="s">
@@ -10471,7 +10474,7 @@
       <c r="B144" s="1">
         <v>141</v>
       </c>
-      <c r="C144" s="7" t="s">
+      <c r="C144" s="8" t="s">
         <v>434</v>
       </c>
       <c r="D144" s="1">
@@ -10480,10 +10483,10 @@
       <c r="E144" s="1">
         <v>33</v>
       </c>
-      <c r="F144" s="4">
+      <c r="F144" s="5">
         <v>92309488435591</v>
       </c>
-      <c r="G144" s="7" t="s">
+      <c r="G144" s="8" t="s">
         <v>435</v>
       </c>
       <c r="H144" s="2" t="s">
@@ -10497,7 +10500,7 @@
       <c r="B145" s="1">
         <v>142</v>
       </c>
-      <c r="C145" s="7" t="s">
+      <c r="C145" s="8" t="s">
         <v>436</v>
       </c>
       <c r="D145" s="1">
@@ -10506,10 +10509,10 @@
       <c r="E145" s="1">
         <v>33</v>
       </c>
-      <c r="F145" s="4">
+      <c r="F145" s="5">
         <v>106319308889290</v>
       </c>
-      <c r="G145" s="7" t="s">
+      <c r="G145" s="8" t="s">
         <v>437</v>
       </c>
       <c r="H145" s="2" t="s">
@@ -10523,7 +10526,7 @@
       <c r="B146" s="1">
         <v>143</v>
       </c>
-      <c r="C146" s="7" t="s">
+      <c r="C146" s="8" t="s">
         <v>438</v>
       </c>
       <c r="D146" s="1">
@@ -10532,10 +10535,10 @@
       <c r="E146" s="1">
         <v>34</v>
       </c>
-      <c r="F146" s="4">
+      <c r="F146" s="5">
         <v>123120949699520</v>
       </c>
-      <c r="G146" s="7" t="s">
+      <c r="G146" s="8" t="s">
         <v>439</v>
       </c>
       <c r="H146" s="2" t="s">
@@ -10549,7 +10552,7 @@
       <c r="B147" s="1">
         <v>144</v>
       </c>
-      <c r="C147" s="7" t="s">
+      <c r="C147" s="8" t="s">
         <v>440</v>
       </c>
       <c r="D147" s="1">
@@ -10558,10 +10561,10 @@
       <c r="E147" s="1">
         <v>34</v>
       </c>
-      <c r="F147" s="4">
+      <c r="F147" s="5">
         <v>111674856010497</v>
       </c>
-      <c r="G147" s="7" t="s">
+      <c r="G147" s="8" t="s">
         <v>441</v>
       </c>
       <c r="H147" s="2" t="s">
@@ -10575,7 +10578,7 @@
       <c r="B148" s="1">
         <v>145</v>
       </c>
-      <c r="C148" s="7" t="s">
+      <c r="C148" s="8" t="s">
         <v>442</v>
       </c>
       <c r="D148" s="1">
@@ -10584,10 +10587,10 @@
       <c r="E148" s="1">
         <v>34</v>
       </c>
-      <c r="F148" s="4">
+      <c r="F148" s="5">
         <v>118080816505555</v>
       </c>
-      <c r="G148" s="7" t="s">
+      <c r="G148" s="8" t="s">
         <v>443</v>
       </c>
       <c r="H148" s="2" t="s">
@@ -10601,7 +10604,7 @@
       <c r="B149" s="1">
         <v>146</v>
       </c>
-      <c r="C149" s="7" t="s">
+      <c r="C149" s="8" t="s">
         <v>444</v>
       </c>
       <c r="D149" s="1">
@@ -10610,10 +10613,10 @@
       <c r="E149" s="1">
         <v>34</v>
       </c>
-      <c r="F149" s="4">
+      <c r="F149" s="5">
         <v>105021574817966</v>
       </c>
-      <c r="G149" s="7" t="s">
+      <c r="G149" s="8" t="s">
         <v>445</v>
       </c>
       <c r="H149" s="2" t="s">
@@ -10627,7 +10630,7 @@
       <c r="B150" s="1">
         <v>147</v>
       </c>
-      <c r="C150" s="7" t="s">
+      <c r="C150" s="8" t="s">
         <v>446</v>
       </c>
       <c r="D150" s="1">
@@ -10636,10 +10639,10 @@
       <c r="E150" s="1">
         <v>35</v>
       </c>
-      <c r="F150" s="4">
+      <c r="F150" s="5">
         <v>72690180103558</v>
       </c>
-      <c r="G150" s="7" t="s">
+      <c r="G150" s="8" t="s">
         <v>447</v>
       </c>
       <c r="H150" s="2" t="s">
@@ -10653,7 +10656,7 @@
       <c r="B151" s="1">
         <v>148</v>
       </c>
-      <c r="C151" s="7" t="s">
+      <c r="C151" s="8" t="s">
         <v>448</v>
       </c>
       <c r="D151" s="1">
@@ -10662,10 +10665,10 @@
       <c r="E151" s="1">
         <v>35</v>
       </c>
-      <c r="F151" s="4">
+      <c r="F151" s="5">
         <v>94914272618995</v>
       </c>
-      <c r="G151" s="7" t="s">
+      <c r="G151" s="8" t="s">
         <v>449</v>
       </c>
       <c r="H151" s="2" t="s">
@@ -10689,156 +10692,156 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A4" s="6">
+      <c r="A4" s="7">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="7">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="7">
         <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>2</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="7">
         <v>4</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="7">
         <v>151</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A6" s="6">
+      <c r="A6" s="7">
         <v>3</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>8</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>16</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>153</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A8" s="6">
+      <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>32</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="7">
         <v>154</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A9" s="6">
+      <c r="A9" s="7">
         <v>6</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>64</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A10" s="6">
+      <c r="A10" s="7">
         <v>7</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>128</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>156</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>8</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>256</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>157</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A12" s="6">
+      <c r="A12" s="7">
         <v>9</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>512</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>158</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A13" s="6">
+      <c r="A13" s="7">
         <v>10</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>1024</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>159</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A14" s="6">
+      <c r="A14" s="7">
         <v>11</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>2048</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>160</v>
       </c>
     </row>
@@ -10965,10 +10968,10 @@
       <c r="G4">
         <v>99853650045862</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A5" s="1">
@@ -10990,10 +10993,10 @@
       <c r="G5">
         <v>116225665846279</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="I5" s="5"/>
+      <c r="I5" s="6"/>
     </row>
     <row r="6" customFormat="1" ht="16.5" spans="1:9">
       <c r="A6" s="1">
@@ -11015,10 +11018,10 @@
       <c r="G6">
         <v>136956773152573</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="6"/>
     </row>
     <row r="7" customFormat="1" ht="16.5" spans="1:9">
       <c r="A7" s="1">
@@ -11040,10 +11043,10 @@
       <c r="G7">
         <v>97553870039023</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="I7" s="5"/>
+      <c r="I7" s="6"/>
     </row>
     <row r="8" customFormat="1" ht="16.5" spans="1:9">
       <c r="A8" s="1">
@@ -11055,20 +11058,20 @@
       <c r="C8" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="26" t="s">
         <v>470</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="26" t="s">
         <v>471</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8">
         <v>118090700645855</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="I8" s="5"/>
+      <c r="I8" s="6"/>
     </row>
     <row r="9" customFormat="1" ht="16.5" spans="1:9">
       <c r="A9" s="1">
@@ -11080,20 +11083,20 @@
       <c r="C9" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="26" t="s">
         <v>474</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="26" t="s">
         <v>475</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9">
         <v>138508042210191</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="I9" s="5"/>
+      <c r="I9" s="6"/>
     </row>
     <row r="10" customFormat="1" ht="16.5" spans="1:9">
       <c r="A10" s="1">
@@ -11105,20 +11108,20 @@
       <c r="C10" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="26" t="s">
         <v>478</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="26" t="s">
         <v>479</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10">
         <v>78371166922896</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="I10" s="5"/>
+      <c r="I10" s="6"/>
     </row>
     <row r="11" customFormat="1" ht="16.5" spans="1:9">
       <c r="A11" s="1">
@@ -11130,20 +11133,20 @@
       <c r="C11" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="26" t="s">
         <v>482</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="26" t="s">
         <v>483</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11">
         <v>132966760008713</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>484</v>
       </c>
-      <c r="I11" s="5"/>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" customFormat="1" ht="16.5" spans="1:9">
       <c r="A12" s="1">
@@ -11155,20 +11158,20 @@
       <c r="C12" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="26" t="s">
         <v>486</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="26" t="s">
         <v>487</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12">
         <v>133927008310944</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="I12" s="5"/>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" customFormat="1" ht="16.5" spans="1:9">
       <c r="A13" s="1">
@@ -11180,20 +11183,20 @@
       <c r="C13" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="26" t="s">
         <v>490</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="26" t="s">
         <v>491</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13">
         <v>98415179467911</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="I13" s="5"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" customFormat="1" ht="16.5" spans="1:9">
       <c r="A14" s="1">
@@ -11205,20 +11208,20 @@
       <c r="C14" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="D14" s="25" t="s">
+      <c r="D14" s="26" t="s">
         <v>494</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="26" t="s">
         <v>495</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14">
         <v>79276409476682</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="5" t="s">
         <v>496</v>
       </c>
-      <c r="I14" s="5"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" customFormat="1" ht="16.5" spans="1:9">
       <c r="A15" s="1">
@@ -11230,20 +11233,20 @@
       <c r="C15" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="26" t="s">
         <v>498</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="26" t="s">
         <v>499</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15">
         <v>86184044773576</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="5" t="s">
         <v>500</v>
       </c>
-      <c r="I15" s="5"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" customFormat="1" ht="16.5" spans="1:9">
       <c r="A16" s="1">
@@ -11255,20 +11258,20 @@
       <c r="C16" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="26" t="s">
         <v>502</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="26" t="s">
         <v>503</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16">
         <v>85964386896273</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="I16" s="5"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" customFormat="1" ht="16.5" spans="1:9">
       <c r="A17" s="1">
@@ -11280,20 +11283,20 @@
       <c r="C17" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="26" t="s">
         <v>506</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="26" t="s">
         <v>507</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17">
         <v>121813166897471</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="I17" s="5"/>
+      <c r="I17" s="6"/>
     </row>
     <row r="18" customFormat="1" ht="16.5" spans="1:9">
       <c r="A18" s="1">
@@ -11305,20 +11308,20 @@
       <c r="C18" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D18" s="25" t="s">
+      <c r="D18" s="26" t="s">
         <v>510</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="26" t="s">
         <v>511</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18">
         <v>107669574278873</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="5" t="s">
         <v>512</v>
       </c>
-      <c r="I18" s="5"/>
+      <c r="I18" s="6"/>
     </row>
     <row r="19" customFormat="1" ht="16.5" spans="1:9">
       <c r="A19" s="1">
@@ -11330,20 +11333,20 @@
       <c r="C19" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="D19" s="25" t="s">
+      <c r="D19" s="26" t="s">
         <v>514</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="26" t="s">
         <v>515</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19">
         <v>98723580431394</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="I19" s="5"/>
+      <c r="I19" s="6"/>
     </row>
     <row r="20" customFormat="1" ht="16.5" spans="1:9">
       <c r="A20" s="1">
@@ -11355,20 +11358,20 @@
       <c r="C20" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D20" s="25" t="s">
+      <c r="D20" s="26" t="s">
         <v>518</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="26" t="s">
         <v>519</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20">
         <v>126241505230536</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="I20" s="5"/>
+      <c r="I20" s="6"/>
     </row>
     <row r="21" ht="16.5" spans="1:9">
       <c r="A21" s="1">
@@ -11380,20 +11383,20 @@
       <c r="C21" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="26" t="s">
         <v>522</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="26" t="s">
         <v>523</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21">
         <v>78092021290844</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="I21" s="5"/>
+      <c r="I21" s="6"/>
     </row>
     <row r="22" ht="16.5" spans="1:9">
       <c r="A22" s="1">
@@ -11405,20 +11408,20 @@
       <c r="C22" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="26" t="s">
         <v>526</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="26" t="s">
         <v>527</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22">
         <v>138731887343821</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="I22" s="5"/>
+      <c r="I22" s="6"/>
     </row>
     <row r="23" ht="16.5" spans="1:9">
       <c r="A23" s="1">
@@ -11430,20 +11433,20 @@
       <c r="C23" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="26" t="s">
         <v>530</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="26" t="s">
         <v>531</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23">
         <v>113127149166000</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="I23" s="5"/>
+      <c r="I23" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11574,8 +11577,8 @@
         <v>1</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4">
-        <v>91469233823349</v>
+      <c r="H4" s="4">
+        <v>88151748923443</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>537</v>
@@ -11601,8 +11604,8 @@
         <v>2</v>
       </c>
       <c r="G5" s="1"/>
-      <c r="H5">
-        <v>112048940124762</v>
+      <c r="H5" s="4">
+        <v>130646097070957</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>539</v>
@@ -11628,8 +11631,8 @@
         <v>3</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6">
-        <v>114920101659350</v>
+      <c r="H6" s="4">
+        <v>86124893237823</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>541</v>
@@ -11655,8 +11658,8 @@
         <v>4</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7">
-        <v>76680071023422</v>
+      <c r="H7" s="4">
+        <v>117901666423784</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>543</v>
@@ -11682,8 +11685,8 @@
         <v>5</v>
       </c>
       <c r="G8" s="1"/>
-      <c r="H8">
-        <v>98163950325063</v>
+      <c r="H8" s="4">
+        <v>133168932011408</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>545</v>
@@ -11709,8 +11712,8 @@
         <v>6</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9">
-        <v>98163950325063</v>
+      <c r="H9" s="4">
+        <v>71089861609803</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>547</v>
@@ -11736,8 +11739,8 @@
         <v>7</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10">
-        <v>98163950325063</v>
+      <c r="H10" s="4">
+        <v>71622349623563</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>549</v>
@@ -11763,8 +11766,8 @@
         <v>8</v>
       </c>
       <c r="G11" s="2"/>
-      <c r="H11">
-        <v>98163950325063</v>
+      <c r="H11" s="4">
+        <v>126547452796781</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>551</v>
@@ -11789,8 +11792,8 @@
       <c r="F12" s="1">
         <v>9</v>
       </c>
-      <c r="H12">
-        <v>98163950325063</v>
+      <c r="H12" s="4">
+        <v>111693433253936</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>553</v>
@@ -11816,8 +11819,8 @@
         <v>10</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="H13">
-        <v>98163950325063</v>
+      <c r="H13" s="4">
+        <v>126721700266409</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>555</v>
@@ -28218,8 +28221,8 @@
         <v>11</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14">
-        <v>98163950325063</v>
+      <c r="H14" s="4">
+        <v>92711027530571</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>557</v>
@@ -44620,8 +44623,8 @@
         <v>12</v>
       </c>
       <c r="G15" s="1"/>
-      <c r="H15">
-        <v>98163950325063</v>
+      <c r="H15" s="4">
+        <v>140129159429440</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>559</v>
@@ -61022,8 +61025,8 @@
         <v>13</v>
       </c>
       <c r="G16" s="1"/>
-      <c r="H16">
-        <v>98163950325063</v>
+      <c r="H16" s="4">
+        <v>125903398380406</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>561</v>
@@ -61049,8 +61052,8 @@
         <v>14</v>
       </c>
       <c r="G17" s="1"/>
-      <c r="H17">
-        <v>98163950325063</v>
+      <c r="H17" s="4">
+        <v>110859814667398</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>563</v>
@@ -61076,8 +61079,8 @@
         <v>15</v>
       </c>
       <c r="G18" s="1"/>
-      <c r="H18">
-        <v>98163950325063</v>
+      <c r="H18" s="4">
+        <v>71778195177377</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>565</v>
@@ -61103,8 +61106,8 @@
         <v>16</v>
       </c>
       <c r="G19" s="1"/>
-      <c r="H19">
-        <v>98163950325063</v>
+      <c r="H19" s="4">
+        <v>82261970902739</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>567</v>
@@ -61130,8 +61133,8 @@
         <v>17</v>
       </c>
       <c r="G20" s="1"/>
-      <c r="H20">
-        <v>98163950325063</v>
+      <c r="H20" s="4">
+        <v>84969691879555</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>569</v>
@@ -61156,8 +61159,8 @@
       <c r="F21" s="1">
         <v>18</v>
       </c>
-      <c r="H21">
-        <v>98163950325063</v>
+      <c r="H21" s="4">
+        <v>135431835703650</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>571</v>
@@ -61182,8 +61185,8 @@
       <c r="F22" s="1">
         <v>19</v>
       </c>
-      <c r="H22">
-        <v>98163950325063</v>
+      <c r="H22" s="4">
+        <v>84363202598659</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>573</v>
@@ -61208,8 +61211,8 @@
       <c r="F23" s="1">
         <v>20</v>
       </c>
-      <c r="H23">
-        <v>98163950325063</v>
+      <c r="H23" s="4">
+        <v>140502552004582</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>575</v>
@@ -61234,8 +61237,8 @@
       <c r="F24" s="1">
         <v>21</v>
       </c>
-      <c r="H24">
-        <v>98163950325063</v>
+      <c r="H24" s="4">
+        <v>110544423490869</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>577</v>
@@ -61260,8 +61263,8 @@
       <c r="F25" s="1">
         <v>22</v>
       </c>
-      <c r="H25">
-        <v>98163950325063</v>
+      <c r="H25" s="4">
+        <v>88436670368181</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>579</v>
@@ -61286,8 +61289,8 @@
       <c r="F26" s="1">
         <v>23</v>
       </c>
-      <c r="H26">
-        <v>98163950325063</v>
+      <c r="H26" s="4">
+        <v>101523513603326</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>581</v>
@@ -61312,8 +61315,8 @@
       <c r="F27" s="1">
         <v>24</v>
       </c>
-      <c r="H27">
-        <v>98163950325063</v>
+      <c r="H27" s="4">
+        <v>117557339704806</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>583</v>
@@ -61338,8 +61341,8 @@
       <c r="F28" s="1">
         <v>25</v>
       </c>
-      <c r="H28">
-        <v>98163950325063</v>
+      <c r="H28" s="4">
+        <v>94281665600637</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>585</v>

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="642" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Rule" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="754">
   <si>
     <t>子配置键</t>
   </si>
@@ -1644,6 +1644,42 @@
   </si>
   <si>
     <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["20GildedCrownGreatHammer"]</t>
+  </si>
+  <si>
+    <t>HolyCrownPickaxe</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.AITools["01-holy-crown-pickaxe"]</t>
+  </si>
+  <si>
+    <t>HolyCrownHammer</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.AITools["02-holy-crown-hammer"]</t>
+  </si>
+  <si>
+    <t>DragonFlamePickaxe</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.AITools["03-dragon-flame-pickaxe"]</t>
+  </si>
+  <si>
+    <t>DragonFlameHammer</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.AITools["04-dragon-flame-hammer"]</t>
+  </si>
+  <si>
+    <t>ThunderPickaxe</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.AITools["05-thunder-pickaxe"]</t>
+  </si>
+  <si>
+    <t>ThunderHammer</t>
+  </si>
+  <si>
+    <t>game.ReplicatedStorage.Assets.AITools["06-thunder-hammer"]</t>
   </si>
   <si>
     <t>图片</t>
@@ -2940,7 +2976,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2956,11 +2992,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="fill" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3353,62 +3398,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="24" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="26" customHeight="1" spans="1:6">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="24" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3425,7 +3470,7 @@
       <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="27" t="s">
         <v>15</v>
       </c>
       <c r="F4" t="s">
@@ -3445,7 +3490,7 @@
       <c r="D5" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="28" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3462,7 +3507,7 @@
       <c r="D6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="27" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3479,7 +3524,7 @@
       <c r="D7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="27" t="s">
         <v>19</v>
       </c>
       <c r="F7" t="s">
@@ -3499,7 +3544,7 @@
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="28" t="s">
         <v>21</v>
       </c>
       <c r="F8" t="s">
@@ -3519,7 +3564,7 @@
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="28" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
@@ -3539,7 +3584,7 @@
       <c r="D10" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="27" t="s">
         <v>25</v>
       </c>
       <c r="F10" t="s">
@@ -3575,13 +3620,13 @@
   <sheetData>
     <row r="1" ht="16.5" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:5">
@@ -3589,10 +3634,10 @@
         <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:5">
@@ -3608,576 +3653,576 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="B4" s="2">
         <v>29</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="B5" s="2">
         <v>122</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="B6" s="2">
         <v>520</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="B7" s="2">
         <v>2176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="B8" s="2">
         <v>9101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>602</v>
+        <v>613</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>614</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>605</v>
+        <v>616</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>617</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>608</v>
+        <v>619</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>620</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>611</v>
+        <v>622</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>623</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>614</v>
+        <v>625</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>626</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>617</v>
+        <v>628</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>629</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="B15" s="27" t="s">
-        <v>620</v>
+        <v>631</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>632</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>623</v>
+        <v>634</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>635</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>626</v>
+        <v>637</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>638</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>629</v>
+        <v>640</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>641</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>632</v>
+        <v>643</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>644</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="B20" s="27" t="s">
-        <v>635</v>
+        <v>646</v>
+      </c>
+      <c r="B20" s="30" t="s">
+        <v>647</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="B21" s="27" t="s">
-        <v>638</v>
+        <v>649</v>
+      </c>
+      <c r="B21" s="30" t="s">
+        <v>650</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>641</v>
+        <v>652</v>
+      </c>
+      <c r="B22" s="30" t="s">
+        <v>653</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>644</v>
+        <v>655</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>656</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="B24" s="27" t="s">
-        <v>647</v>
+        <v>658</v>
+      </c>
+      <c r="B24" s="30" t="s">
+        <v>659</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="B25" s="27" t="s">
-        <v>650</v>
+        <v>661</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>662</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>653</v>
+        <v>664</v>
+      </c>
+      <c r="B26" s="30" t="s">
+        <v>665</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="2" t="s">
-        <v>655</v>
-      </c>
-      <c r="B27" s="27" t="s">
-        <v>656</v>
+        <v>667</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>668</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="B28" s="27" t="s">
-        <v>659</v>
+        <v>670</v>
+      </c>
+      <c r="B28" s="30" t="s">
+        <v>671</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>662</v>
+        <v>673</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>674</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>665</v>
+        <v>676</v>
+      </c>
+      <c r="B30" s="30" t="s">
+        <v>677</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="B31" s="27" t="s">
-        <v>668</v>
+        <v>679</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>680</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>671</v>
+        <v>682</v>
+      </c>
+      <c r="B32" s="30" t="s">
+        <v>683</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="B33" s="27" t="s">
-        <v>674</v>
+        <v>685</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>686</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="B34" s="27" t="s">
-        <v>677</v>
+        <v>688</v>
+      </c>
+      <c r="B34" s="30" t="s">
+        <v>689</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="B35" s="27" t="s">
-        <v>680</v>
+        <v>691</v>
+      </c>
+      <c r="B35" s="30" t="s">
+        <v>692</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="B36" s="27" t="s">
-        <v>683</v>
+        <v>694</v>
+      </c>
+      <c r="B36" s="30" t="s">
+        <v>695</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="B37" s="27" t="s">
-        <v>686</v>
+        <v>697</v>
+      </c>
+      <c r="B37" s="30" t="s">
+        <v>698</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="B38" s="27" t="s">
-        <v>689</v>
+        <v>700</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>701</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="B39" s="27" t="s">
-        <v>692</v>
+        <v>703</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>704</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="B40" s="27" t="s">
-        <v>695</v>
+        <v>706</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>707</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="B41" s="27" t="s">
-        <v>698</v>
+        <v>709</v>
+      </c>
+      <c r="B41" s="30" t="s">
+        <v>710</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="B42" s="27" t="s">
-        <v>701</v>
+        <v>712</v>
+      </c>
+      <c r="B42" s="30" t="s">
+        <v>713</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="B43" s="28" t="s">
-        <v>704</v>
+        <v>715</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>716</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="B44" s="28" t="s">
-        <v>707</v>
+        <v>718</v>
+      </c>
+      <c r="B44" s="31" t="s">
+        <v>719</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B45" s="28" t="s">
-        <v>710</v>
+        <v>721</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>722</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="B46" s="28" t="s">
-        <v>713</v>
+        <v>724</v>
+      </c>
+      <c r="B46" s="31" t="s">
+        <v>725</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="B47" s="28" t="s">
-        <v>716</v>
+        <v>727</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>728</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="B48" s="28" t="s">
-        <v>719</v>
+        <v>730</v>
+      </c>
+      <c r="B48" s="31" t="s">
+        <v>731</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="B49" s="28" t="s">
-        <v>722</v>
+        <v>733</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>734</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>725</v>
+        <v>736</v>
+      </c>
+      <c r="B50" s="31" t="s">
+        <v>737</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="B51" s="28" t="s">
-        <v>728</v>
+        <v>739</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>740</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>731</v>
+        <v>742</v>
+      </c>
+      <c r="B52" s="31" t="s">
+        <v>743</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="B53" s="28" t="s">
-        <v>734</v>
+        <v>745</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>746</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="B54" s="28" t="s">
-        <v>737</v>
+        <v>748</v>
+      </c>
+      <c r="B54" s="31" t="s">
+        <v>749</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="B55" s="28" t="s">
-        <v>740</v>
+        <v>751</v>
+      </c>
+      <c r="B55" s="31" t="s">
+        <v>752</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
     </row>
   </sheetData>
@@ -4192,395 +4237,395 @@
   <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="44.175" style="15" customWidth="1"/>
-    <col min="2" max="2" width="71.3583333333333" style="15" customWidth="1"/>
-    <col min="3" max="3" width="123.558333333333" style="15" customWidth="1"/>
-    <col min="4" max="4" width="82.8666666666667" style="15" customWidth="1"/>
-    <col min="5" max="6" width="9" style="15"/>
-    <col min="7" max="7" width="81.1833333333333" style="15" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="15"/>
+    <col min="1" max="1" width="44.175" style="18" customWidth="1"/>
+    <col min="2" max="2" width="71.3583333333333" style="18" customWidth="1"/>
+    <col min="3" max="3" width="123.558333333333" style="18" customWidth="1"/>
+    <col min="4" max="4" width="82.8666666666667" style="18" customWidth="1"/>
+    <col min="5" max="6" width="9" style="18"/>
+    <col min="7" max="7" width="81.1833333333333" style="18" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" s="15" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
-      <c r="A1" s="16" t="s">
+    <row r="1" s="18" customFormat="1" ht="22.25" customHeight="1" spans="1:7">
+      <c r="A1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
-    <row r="2" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+    <row r="2" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
-    <row r="3" s="15" customFormat="1" ht="91" customHeight="1" spans="1:7">
-      <c r="A3" s="16" t="s">
+    <row r="3" s="18" customFormat="1" ht="91" customHeight="1" spans="1:7">
+      <c r="A3" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="17"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
     </row>
-    <row r="4" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A4" s="16" t="s">
+    <row r="4" s="18" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A4" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
     </row>
-    <row r="5" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A5" s="16" t="s">
+    <row r="5" s="18" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A5" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="19">
         <v>10</v>
       </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
     </row>
-    <row r="6" s="15" customFormat="1" ht="60" customHeight="1" spans="1:7">
-      <c r="A6" s="16" t="s">
+    <row r="6" s="18" customFormat="1" ht="60" customHeight="1" spans="1:7">
+      <c r="A6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
     </row>
-    <row r="7" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A7" s="18" t="s">
+    <row r="7" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A7" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
     </row>
-    <row r="8" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A8" s="18" t="s">
+    <row r="8" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A8" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
     </row>
-    <row r="9" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A9" s="18" t="s">
+    <row r="9" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A9" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
     </row>
-    <row r="10" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A10" s="16" t="s">
+    <row r="10" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
     </row>
-    <row r="11" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A11" s="16" t="s">
+    <row r="11" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A11" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
     </row>
-    <row r="12" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A12" s="16" t="s">
+    <row r="12" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
     </row>
-    <row r="13" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A13" s="16" t="s">
+    <row r="13" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A13" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
     </row>
-    <row r="14" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
+    <row r="14" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
     </row>
-    <row r="15" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+    <row r="15" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
     </row>
-    <row r="16" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+    <row r="16" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
     </row>
-    <row r="17" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
+    <row r="17" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
     </row>
-    <row r="18" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
+    <row r="18" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
     </row>
-    <row r="19" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+    <row r="19" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
     </row>
-    <row r="20" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
+    <row r="20" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
     </row>
-    <row r="21" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+    <row r="21" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
     </row>
-    <row r="22" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
+    <row r="22" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
     </row>
-    <row r="23" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
+    <row r="23" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
     </row>
-    <row r="24" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+    <row r="24" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
     </row>
-    <row r="25" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
+    <row r="25" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
     </row>
-    <row r="26" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+    <row r="26" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
     </row>
-    <row r="27" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="C27" s="16"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+    <row r="27" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="C27" s="19"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
     </row>
-    <row r="28" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+    <row r="28" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
     </row>
-    <row r="29" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
+    <row r="29" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
     </row>
-    <row r="30" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
+    <row r="30" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
     </row>
-    <row r="31" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
+    <row r="31" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
     </row>
-    <row r="32" s="15" customFormat="1" ht="24.75" spans="1:7">
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+    <row r="32" s="18" customFormat="1" ht="24.75" spans="1:7">
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
     </row>
-    <row r="33" s="15" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
+    <row r="33" s="18" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
     </row>
-    <row r="34" s="15" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
+    <row r="34" s="18" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
     </row>
-    <row r="35" s="15" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+    <row r="35" s="18" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
     </row>
-    <row r="36" s="15" customFormat="1" ht="24.75" spans="2:7">
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+    <row r="36" s="18" customFormat="1" ht="24.75" spans="2:7">
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -4770,943 +4815,943 @@
   <dimension ref="A1:E55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" width="37.75" style="13" customWidth="1"/>
+    <col min="1" max="2" width="37.75" style="16" customWidth="1"/>
     <col min="3" max="3" width="33.0833333333333" customWidth="1"/>
     <col min="4" max="5" width="40.4416666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="17" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="17" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="17" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="14">
+      <c r="A4" s="17">
         <v>1</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="17">
         <v>1</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="17">
         <v>80</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="17">
         <v>3</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="14">
+      <c r="A5" s="17">
         <v>2</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="17">
         <v>2</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="17">
         <v>4</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="17">
         <v>3</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="14">
+      <c r="A6" s="17">
         <v>3</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="17">
         <v>3</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="17">
         <v>4</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="17">
         <v>3</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="14">
+      <c r="A7" s="17">
         <v>4</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="17">
         <v>4</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="17">
         <v>4</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="17">
         <v>3</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="14">
+      <c r="A8" s="17">
         <v>5</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="17">
         <v>5</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="17">
         <v>4</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="17">
         <v>3</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="14">
+      <c r="A9" s="17">
         <v>6</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="17">
         <v>6</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="17">
         <v>4</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="17">
         <v>3</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="14">
+      <c r="A10" s="17">
         <v>7</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="17">
         <v>7</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="17">
         <v>4</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="17">
         <v>3</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="14">
+      <c r="A11" s="17">
         <v>8</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="17">
         <v>8</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="17">
         <v>4</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="17">
         <v>3</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="14">
+      <c r="A12" s="17">
         <v>9</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="17">
         <v>9</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="17">
         <v>4</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="17">
         <v>3</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="14">
+      <c r="A13" s="17">
         <v>10</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="17">
         <v>10</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="17">
         <v>4</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="17">
         <v>3</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="14">
+      <c r="A14" s="17">
         <v>11</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="17">
         <v>11</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="17">
         <v>4</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="17">
         <v>3</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="14">
+      <c r="A15" s="17">
         <v>12</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="17">
         <v>12</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="17">
         <v>4</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="17">
         <v>3</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="14">
+      <c r="A16" s="17">
         <v>13</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="17">
         <v>13</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C16" s="17">
         <v>4</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="17">
         <v>3</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="14">
+      <c r="A17" s="17">
         <v>14</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="17">
         <v>14</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="17">
         <v>4</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="17">
         <v>3</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="14">
+      <c r="A18" s="17">
         <v>15</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="17">
         <v>15</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="17">
         <v>4</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="17">
         <v>3</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="14">
+      <c r="A19" s="17">
         <v>16</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B19" s="17">
         <v>16</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="17">
         <v>4</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="17">
         <v>3</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="14">
+      <c r="A20" s="17">
         <v>17</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="17">
         <v>17</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="17">
         <v>4</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="17">
         <v>3</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="14">
+      <c r="A21" s="17">
         <v>18</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="17">
         <v>18</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="17">
         <v>4</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="17">
         <v>3</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="14">
+      <c r="A22" s="17">
         <v>19</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="17">
         <v>19</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="17">
         <v>4</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="17">
         <v>3</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="14">
+      <c r="A23" s="17">
         <v>20</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B23" s="17">
         <v>20</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="17">
         <v>4</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="17">
         <v>3</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="14">
+      <c r="A24" s="17">
         <v>21</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B24" s="17">
         <v>21</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="17">
         <v>4</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="17">
         <v>3</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="14">
+      <c r="A25" s="17">
         <v>22</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="17">
         <v>22</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="17">
         <v>4</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="17">
         <v>3</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="14">
+      <c r="A26" s="17">
         <v>23</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B26" s="17">
         <v>23</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C26" s="17">
         <v>4</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="17">
         <v>3</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="14">
+      <c r="A27" s="17">
         <v>24</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="17">
         <v>24</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="17">
         <v>4</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="17">
         <v>3</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="14">
+      <c r="A28" s="17">
         <v>25</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="17">
         <v>25</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="17">
         <v>4</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="17">
         <v>3</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="14">
+      <c r="A29" s="17">
         <v>26</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="17">
         <v>26</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="17">
         <v>4</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="17">
         <v>3</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="14">
+      <c r="A30" s="17">
         <v>27</v>
       </c>
-      <c r="B30" s="14">
+      <c r="B30" s="17">
         <v>27</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="17">
         <v>4</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="17">
         <v>3</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="14">
+      <c r="A31" s="17">
         <v>28</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="17">
         <v>28</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="17">
         <v>4</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="17">
         <v>3</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="14">
+      <c r="A32" s="17">
         <v>29</v>
       </c>
-      <c r="B32" s="14">
+      <c r="B32" s="17">
         <v>29</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="17">
         <v>4</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="17">
         <v>3</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="14">
+      <c r="A33" s="17">
         <v>30</v>
       </c>
-      <c r="B33" s="14">
+      <c r="B33" s="17">
         <v>30</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="17">
         <v>4</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="17">
         <v>3</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="14">
+      <c r="A34" s="17">
         <v>31</v>
       </c>
-      <c r="B34" s="14">
+      <c r="B34" s="17">
         <v>31</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="17">
         <v>4</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="17">
         <v>3</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="14">
+      <c r="A35" s="17">
         <v>32</v>
       </c>
-      <c r="B35" s="14">
+      <c r="B35" s="17">
         <v>32</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="17">
         <v>4</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="17">
         <v>3</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="14">
+      <c r="A36" s="17">
         <v>33</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B36" s="17">
         <v>33</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C36" s="17">
         <v>4</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="17">
         <v>3</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="14">
+      <c r="A37" s="17">
         <v>34</v>
       </c>
-      <c r="B37" s="14">
+      <c r="B37" s="17">
         <v>34</v>
       </c>
-      <c r="C37" s="14">
+      <c r="C37" s="17">
         <v>4</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="17">
         <v>3</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="14">
+      <c r="A38" s="17">
         <v>35</v>
       </c>
-      <c r="B38" s="14">
+      <c r="B38" s="17">
         <v>35</v>
       </c>
-      <c r="C38" s="14">
+      <c r="C38" s="17">
         <v>4</v>
       </c>
-      <c r="D38" s="14">
+      <c r="D38" s="17">
         <v>3</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="14">
+      <c r="A39" s="17">
         <v>36</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="17">
         <v>36</v>
       </c>
-      <c r="C39" s="14">
+      <c r="C39" s="17">
         <v>4</v>
       </c>
-      <c r="D39" s="14">
+      <c r="D39" s="17">
         <v>3</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="14">
+      <c r="A40" s="17">
         <v>37</v>
       </c>
-      <c r="B40" s="14">
+      <c r="B40" s="17">
         <v>37</v>
       </c>
-      <c r="C40" s="14">
+      <c r="C40" s="17">
         <v>4</v>
       </c>
-      <c r="D40" s="14">
+      <c r="D40" s="17">
         <v>3</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="14">
+      <c r="A41" s="17">
         <v>38</v>
       </c>
-      <c r="B41" s="14">
+      <c r="B41" s="17">
         <v>38</v>
       </c>
-      <c r="C41" s="14">
+      <c r="C41" s="17">
         <v>4</v>
       </c>
-      <c r="D41" s="14">
+      <c r="D41" s="17">
         <v>3</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="14">
+      <c r="A42" s="17">
         <v>39</v>
       </c>
-      <c r="B42" s="14">
+      <c r="B42" s="17">
         <v>39</v>
       </c>
-      <c r="C42" s="14">
+      <c r="C42" s="17">
         <v>4</v>
       </c>
-      <c r="D42" s="14">
+      <c r="D42" s="17">
         <v>3</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="14">
+      <c r="A43" s="17">
         <v>40</v>
       </c>
-      <c r="B43" s="14">
+      <c r="B43" s="17">
         <v>40</v>
       </c>
-      <c r="C43" s="14">
+      <c r="C43" s="17">
         <v>4</v>
       </c>
-      <c r="D43" s="14">
+      <c r="D43" s="17">
         <v>3</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:5">
-      <c r="A44" s="14">
+      <c r="A44" s="17">
         <v>41</v>
       </c>
-      <c r="B44" s="14">
+      <c r="B44" s="17">
         <v>41</v>
       </c>
-      <c r="C44" s="14">
+      <c r="C44" s="17">
         <v>4</v>
       </c>
-      <c r="D44" s="14">
+      <c r="D44" s="17">
         <v>3</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="14">
+      <c r="A45" s="17">
         <v>42</v>
       </c>
-      <c r="B45" s="14">
+      <c r="B45" s="17">
         <v>42</v>
       </c>
-      <c r="C45" s="14">
+      <c r="C45" s="17">
         <v>4</v>
       </c>
-      <c r="D45" s="14">
+      <c r="D45" s="17">
         <v>3</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:5">
-      <c r="A46" s="14">
+      <c r="A46" s="17">
         <v>43</v>
       </c>
-      <c r="B46" s="14">
+      <c r="B46" s="17">
         <v>43</v>
       </c>
-      <c r="C46" s="14">
+      <c r="C46" s="17">
         <v>4</v>
       </c>
-      <c r="D46" s="14">
+      <c r="D46" s="17">
         <v>3</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="14">
+      <c r="A47" s="17">
         <v>44</v>
       </c>
-      <c r="B47" s="14">
+      <c r="B47" s="17">
         <v>44</v>
       </c>
-      <c r="C47" s="14">
+      <c r="C47" s="17">
         <v>4</v>
       </c>
-      <c r="D47" s="14">
+      <c r="D47" s="17">
         <v>3</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="14">
+      <c r="A48" s="17">
         <v>45</v>
       </c>
-      <c r="B48" s="14">
+      <c r="B48" s="17">
         <v>45</v>
       </c>
-      <c r="C48" s="14">
+      <c r="C48" s="17">
         <v>4</v>
       </c>
-      <c r="D48" s="14">
+      <c r="D48" s="17">
         <v>3</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:5">
-      <c r="A49" s="14">
+      <c r="A49" s="17">
         <v>46</v>
       </c>
-      <c r="B49" s="14">
+      <c r="B49" s="17">
         <v>46</v>
       </c>
-      <c r="C49" s="14">
+      <c r="C49" s="17">
         <v>4</v>
       </c>
-      <c r="D49" s="14">
+      <c r="D49" s="17">
         <v>3</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:5">
-      <c r="A50" s="14">
+      <c r="A50" s="17">
         <v>47</v>
       </c>
-      <c r="B50" s="14">
+      <c r="B50" s="17">
         <v>47</v>
       </c>
-      <c r="C50" s="14">
+      <c r="C50" s="17">
         <v>4</v>
       </c>
-      <c r="D50" s="14">
+      <c r="D50" s="17">
         <v>3</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="14">
+      <c r="A51" s="17">
         <v>48</v>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="17">
         <v>48</v>
       </c>
-      <c r="C51" s="14">
+      <c r="C51" s="17">
         <v>4</v>
       </c>
-      <c r="D51" s="14">
+      <c r="D51" s="17">
         <v>3</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="14">
+      <c r="A52" s="17">
         <v>49</v>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="17">
         <v>49</v>
       </c>
-      <c r="C52" s="14">
+      <c r="C52" s="17">
         <v>4</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="17">
         <v>3</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="14">
+      <c r="A53" s="17">
         <v>50</v>
       </c>
-      <c r="B53" s="14">
+      <c r="B53" s="17">
         <v>50</v>
       </c>
-      <c r="C53" s="14">
+      <c r="C53" s="17">
         <v>4</v>
       </c>
-      <c r="D53" s="14">
+      <c r="D53" s="17">
         <v>3</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="14">
+      <c r="A54" s="17">
         <v>51</v>
       </c>
-      <c r="B54" s="14">
+      <c r="B54" s="17">
         <v>51</v>
       </c>
-      <c r="C54" s="14">
+      <c r="C54" s="17">
         <v>4</v>
       </c>
-      <c r="D54" s="14">
+      <c r="D54" s="17">
         <v>3</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="17" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="14">
+      <c r="A55" s="17">
         <v>52</v>
       </c>
-      <c r="B55" s="14">
+      <c r="B55" s="17">
         <v>52</v>
       </c>
-      <c r="C55" s="14">
+      <c r="C55" s="17">
         <v>4</v>
       </c>
-      <c r="D55" s="14">
+      <c r="D55" s="17">
         <v>3</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="17" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5722,801 +5767,801 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="27.75" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="25.175" style="9" customWidth="1"/>
-    <col min="2" max="2" width="13.575" style="9" customWidth="1"/>
-    <col min="3" max="3" width="127.141666666667" style="9" customWidth="1"/>
-    <col min="4" max="4" width="49" style="9" customWidth="1"/>
-    <col min="5" max="5" width="92.9666666666667" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="25.175" style="12" customWidth="1"/>
+    <col min="2" max="2" width="13.575" style="12" customWidth="1"/>
+    <col min="3" max="3" width="127.141666666667" style="12" customWidth="1"/>
+    <col min="4" max="4" width="49" style="12" customWidth="1"/>
+    <col min="5" max="5" width="92.9666666666667" style="13" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="14" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="14" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="11">
+      <c r="A4" s="14">
         <v>1</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="14">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="11">
+      <c r="A5" s="14">
         <v>2</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="14">
         <v>2</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="11">
+      <c r="A6" s="14">
         <v>3</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="14">
         <v>3</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="11">
+      <c r="A7" s="14">
         <v>4</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="14">
         <v>4</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="11">
+      <c r="A8" s="14">
         <v>5</v>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="14">
         <v>5</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="11">
+      <c r="A9" s="14">
         <v>6</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="14">
         <v>6</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="11">
+      <c r="A10" s="14">
         <v>7</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="14">
         <v>7</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="11">
+      <c r="A11" s="14">
         <v>8</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="14">
         <v>8</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="11">
+      <c r="A12" s="14">
         <v>9</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="14">
         <v>9</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="11">
+      <c r="A13" s="14">
         <v>10</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="14">
         <v>10</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="11">
+      <c r="A14" s="14">
         <v>11</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="14">
         <v>11</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="11">
+      <c r="A15" s="14">
         <v>12</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="14">
         <v>12</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="11">
+      <c r="A16" s="14">
         <v>13</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="14">
         <v>13</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="11">
+      <c r="A17" s="14">
         <v>14</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="14">
         <v>14</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="11">
+      <c r="A18" s="14">
         <v>15</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="14">
         <v>15</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="11">
+      <c r="A19" s="14">
         <v>16</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="14">
         <v>16</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="11">
+      <c r="A20" s="14">
         <v>17</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="14">
         <v>17</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="11">
+      <c r="A21" s="14">
         <v>18</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="14">
         <v>18</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="11">
+      <c r="A22" s="14">
         <v>19</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="14">
         <v>19</v>
       </c>
-      <c r="C22" s="12" t="s">
+      <c r="C22" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="11">
+      <c r="A23" s="14">
         <v>20</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="14">
         <v>20</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="11">
+      <c r="A24" s="14">
         <v>21</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="14">
         <v>21</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="11">
+      <c r="A25" s="14">
         <v>22</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="14">
         <v>22</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="11">
+      <c r="A26" s="14">
         <v>23</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="14">
         <v>23</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="11">
+      <c r="A27" s="14">
         <v>24</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="14">
         <v>24</v>
       </c>
-      <c r="C27" s="12" t="s">
+      <c r="C27" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="11">
+      <c r="A28" s="14">
         <v>25</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="14">
         <v>25</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="11">
+      <c r="A29" s="14">
         <v>26</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="14">
         <v>26</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="11">
+      <c r="A30" s="14">
         <v>27</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="14">
         <v>27</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="11">
+      <c r="A31" s="14">
         <v>28</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="14">
         <v>28</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="11">
+      <c r="A32" s="14">
         <v>29</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="14">
         <v>29</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="11">
+      <c r="A33" s="14">
         <v>30</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="14">
         <v>30</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="11">
+      <c r="A34" s="14">
         <v>31</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="14">
         <v>31</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="11">
+      <c r="A35" s="14">
         <v>32</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="14">
         <v>32</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="11">
+      <c r="A36" s="14">
         <v>33</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="14">
         <v>33</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="11">
+      <c r="A37" s="14">
         <v>34</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="14">
         <v>34</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="11">
+      <c r="A38" s="14">
         <v>35</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="14">
         <v>35</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="11">
+      <c r="A39" s="14">
         <v>36</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="14">
         <v>36</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="11">
+      <c r="A40" s="14">
         <v>37</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="14">
         <v>37</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="11">
+      <c r="A41" s="14">
         <v>38</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="14">
         <v>38</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="11">
+      <c r="A42" s="14">
         <v>39</v>
       </c>
-      <c r="B42" s="11">
+      <c r="B42" s="14">
         <v>39</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="D42" s="11" t="s">
+      <c r="D42" s="14" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="12">
+      <c r="A43" s="15">
         <v>40</v>
       </c>
-      <c r="B43" s="12">
+      <c r="B43" s="15">
         <v>40</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="D43" s="12" t="s">
+      <c r="D43" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="12">
+      <c r="A44" s="15">
         <v>41</v>
       </c>
-      <c r="B44" s="12">
+      <c r="B44" s="15">
         <v>41</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="12">
+      <c r="A45" s="15">
         <v>42</v>
       </c>
-      <c r="B45" s="12">
+      <c r="B45" s="15">
         <v>42</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="12">
+      <c r="A46" s="15">
         <v>43</v>
       </c>
-      <c r="B46" s="12">
+      <c r="B46" s="15">
         <v>43</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="12">
+      <c r="A47" s="15">
         <v>44</v>
       </c>
-      <c r="B47" s="12">
+      <c r="B47" s="15">
         <v>44</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D47" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="12">
+      <c r="A48" s="15">
         <v>45</v>
       </c>
-      <c r="B48" s="12">
+      <c r="B48" s="15">
         <v>45</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D48" s="12" t="s">
+      <c r="D48" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="12">
+      <c r="A49" s="15">
         <v>46</v>
       </c>
-      <c r="B49" s="12">
+      <c r="B49" s="15">
         <v>46</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="D49" s="12" t="s">
+      <c r="D49" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="12">
+      <c r="A50" s="15">
         <v>47</v>
       </c>
-      <c r="B50" s="12">
+      <c r="B50" s="15">
         <v>47</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="12">
+      <c r="A51" s="15">
         <v>48</v>
       </c>
-      <c r="B51" s="12">
+      <c r="B51" s="15">
         <v>48</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="12">
+      <c r="A52" s="15">
         <v>49</v>
       </c>
-      <c r="B52" s="12">
+      <c r="B52" s="15">
         <v>49</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="12">
+      <c r="A53" s="15">
         <v>50</v>
       </c>
-      <c r="B53" s="12">
+      <c r="B53" s="15">
         <v>50</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="12">
+      <c r="A54" s="15">
         <v>51</v>
       </c>
-      <c r="B54" s="12">
+      <c r="B54" s="15">
         <v>51</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="12">
+      <c r="A55" s="15">
         <v>52</v>
       </c>
-      <c r="B55" s="12">
+      <c r="B55" s="15">
         <v>52</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="15" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
+      <c r="A56" s="15"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
+      <c r="A57" s="15"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="C58" s="12"/>
+      <c r="C58" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6634,10 +6679,10 @@
         <f>CEILING(A4/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>113244405937302</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="11" t="s">
         <v>154</v>
       </c>
       <c r="H4" s="2" t="s">
@@ -6661,10 +6706,10 @@
         <f t="shared" ref="E5:E36" si="0">CEILING(A5/4,1)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>105711056874756</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="11" t="s">
         <v>157</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -6690,10 +6735,10 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>82693303214454</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="11" t="s">
         <v>159</v>
       </c>
       <c r="H6" s="2" t="s">
@@ -6719,10 +6764,10 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>102504658102706</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="11" t="s">
         <v>161</v>
       </c>
       <c r="H7" s="2" t="s">
@@ -6748,10 +6793,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>83069096807916</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="11" t="s">
         <v>163</v>
       </c>
       <c r="H8" s="2" t="s">
@@ -6775,10 +6820,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>80534536398974</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="11" t="s">
         <v>165</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -6803,10 +6848,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>74246671448525</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="11" t="s">
         <v>167</v>
       </c>
       <c r="H10" s="2" t="s">
@@ -6831,10 +6876,10 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>71499702430100</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="11" t="s">
         <v>169</v>
       </c>
       <c r="H11" s="2" t="s">
@@ -6859,10 +6904,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>122909083001205</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="11" t="s">
         <v>171</v>
       </c>
       <c r="H12" s="2" t="s">
@@ -6886,10 +6931,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>128658267266293</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="11" t="s">
         <v>173</v>
       </c>
       <c r="H13" s="2" t="s">
@@ -6913,10 +6958,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>134748387119946</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="11" t="s">
         <v>175</v>
       </c>
       <c r="H14" s="2" t="s">
@@ -6940,10 +6985,10 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>131559815185521</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="11" t="s">
         <v>177</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -6967,10 +7012,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <v>135406755438948</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="11" t="s">
         <v>179</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -6998,10 +7043,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="4">
         <v>128433990441931</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="11" t="s">
         <v>181</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -7029,10 +7074,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <v>86357992624263</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="11" t="s">
         <v>183</v>
       </c>
       <c r="H18" s="2" t="s">
@@ -7060,10 +7105,10 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <v>96128137486525</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="11" t="s">
         <v>185</v>
       </c>
       <c r="H19" s="2" t="s">
@@ -7091,10 +7136,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="4">
         <v>131913492630514</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="11" t="s">
         <v>187</v>
       </c>
       <c r="H20" s="2" t="s">
@@ -7122,10 +7167,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="4">
         <v>119579899338192</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="11" t="s">
         <v>189</v>
       </c>
       <c r="H21" s="2" t="s">
@@ -7153,10 +7198,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="4">
         <v>82472089572732</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="11" t="s">
         <v>191</v>
       </c>
       <c r="H22" s="2" t="s">
@@ -7184,10 +7229,10 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="4">
         <v>104108852156434</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="11" t="s">
         <v>193</v>
       </c>
       <c r="H23" s="2" t="s">
@@ -7215,10 +7260,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="4">
         <v>79005623120233</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="11" t="s">
         <v>195</v>
       </c>
       <c r="H24" s="2" t="s">
@@ -7246,10 +7291,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="4">
         <v>97611938478078</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="11" t="s">
         <v>197</v>
       </c>
       <c r="H25" s="2" t="s">
@@ -7277,10 +7322,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="4">
         <v>81806655827798</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="11" t="s">
         <v>199</v>
       </c>
       <c r="H26" s="2" t="s">
@@ -7308,10 +7353,10 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="4">
         <v>105716218867716</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="11" t="s">
         <v>201</v>
       </c>
       <c r="H27" s="2" t="s">
@@ -7339,10 +7384,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="4">
         <v>128411546772202</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="11" t="s">
         <v>203</v>
       </c>
       <c r="H28" s="2" t="s">
@@ -7370,10 +7415,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="4">
         <v>139465058617680</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="11" t="s">
         <v>205</v>
       </c>
       <c r="H29" s="2" t="s">
@@ -7401,10 +7446,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="4">
         <v>81737011057690</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" s="11" t="s">
         <v>207</v>
       </c>
       <c r="H30" s="2" t="s">
@@ -7432,10 +7477,10 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="4">
         <v>81445862907930</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="11" t="s">
         <v>209</v>
       </c>
       <c r="H31" s="2" t="s">
@@ -7463,10 +7508,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="4">
         <v>123098432383687</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="11" t="s">
         <v>211</v>
       </c>
       <c r="H32" s="2" t="s">
@@ -7494,10 +7539,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="4">
         <v>131796260838154</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="11" t="s">
         <v>213</v>
       </c>
       <c r="H33" s="2" t="s">
@@ -7521,10 +7566,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="4">
         <v>116376878683736</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="11" t="s">
         <v>215</v>
       </c>
       <c r="H34" s="2" t="s">
@@ -7548,10 +7593,10 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="4">
         <v>100558097057142</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="11" t="s">
         <v>217</v>
       </c>
       <c r="H35" s="2" t="s">
@@ -7575,10 +7620,10 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="4">
         <v>92332707761527</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="11" t="s">
         <v>219</v>
       </c>
       <c r="H36" s="2" t="s">
@@ -7606,10 +7651,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>6</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="4">
         <v>108895787734224</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="11" t="s">
         <v>221</v>
       </c>
       <c r="H37" s="2" t="s">
@@ -7633,10 +7678,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>7</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="4">
         <v>95471681056681</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="11" t="s">
         <v>223</v>
       </c>
       <c r="H38" s="2" t="s">
@@ -7660,10 +7705,10 @@
         <f t="shared" ref="E39:E72" si="1">CEILING(A39/4,1)</f>
         <v>9</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="4">
         <v>104955598295323</v>
       </c>
-      <c r="G39" s="8" t="s">
+      <c r="G39" s="11" t="s">
         <v>225</v>
       </c>
       <c r="H39" s="2" t="s">
@@ -7691,10 +7736,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="4">
         <v>103175883366340</v>
       </c>
-      <c r="G40" s="8" t="s">
+      <c r="G40" s="11" t="s">
         <v>227</v>
       </c>
       <c r="H40" s="2" t="s">
@@ -7722,10 +7767,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="4">
         <v>114247164745798</v>
       </c>
-      <c r="G41" s="8" t="s">
+      <c r="G41" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H41" s="2" t="s">
@@ -7749,10 +7794,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="4">
         <v>86017047390182</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="11" t="s">
         <v>231</v>
       </c>
       <c r="H42" s="2" t="s">
@@ -7776,10 +7821,10 @@
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="4">
         <v>81373582816266</v>
       </c>
-      <c r="G43" s="8" t="s">
+      <c r="G43" s="11" t="s">
         <v>233</v>
       </c>
       <c r="H43" s="2" t="s">
@@ -7803,10 +7848,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="4">
         <v>132788281080826</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="G44" s="11" t="s">
         <v>235</v>
       </c>
       <c r="H44" s="2" t="s">
@@ -7830,10 +7875,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="4">
         <v>95162444285252</v>
       </c>
-      <c r="G45" s="8" t="s">
+      <c r="G45" s="11" t="s">
         <v>237</v>
       </c>
       <c r="H45" s="2" t="s">
@@ -7857,10 +7902,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46" s="4">
         <v>95953438126479</v>
       </c>
-      <c r="G46" s="8" t="s">
+      <c r="G46" s="11" t="s">
         <v>239</v>
       </c>
       <c r="H46" s="2" t="s">
@@ -7884,10 +7929,10 @@
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="4">
         <v>112039222887887</v>
       </c>
-      <c r="G47" s="8" t="s">
+      <c r="G47" s="11" t="s">
         <v>241</v>
       </c>
       <c r="H47" s="2" t="s">
@@ -7911,10 +7956,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="4">
         <v>95377459606647</v>
       </c>
-      <c r="G48" s="8" t="s">
+      <c r="G48" s="11" t="s">
         <v>243</v>
       </c>
       <c r="H48" s="2" t="s">
@@ -7938,10 +7983,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="4">
         <v>113983796605688</v>
       </c>
-      <c r="G49" s="8" t="s">
+      <c r="G49" s="11" t="s">
         <v>245</v>
       </c>
       <c r="H49" s="2" t="s">
@@ -7965,10 +8010,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="4">
         <v>117157716541352</v>
       </c>
-      <c r="G50" s="8" t="s">
+      <c r="G50" s="11" t="s">
         <v>247</v>
       </c>
       <c r="H50" s="2" t="s">
@@ -7992,10 +8037,10 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="4">
         <v>100893051807474</v>
       </c>
-      <c r="G51" s="8" t="s">
+      <c r="G51" s="11" t="s">
         <v>249</v>
       </c>
       <c r="H51" s="2" t="s">
@@ -8019,10 +8064,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="4">
         <v>137999782231090</v>
       </c>
-      <c r="G52" s="8" t="s">
+      <c r="G52" s="11" t="s">
         <v>251</v>
       </c>
       <c r="H52" s="2" t="s">
@@ -8046,10 +8091,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="4">
         <v>127007149281218</v>
       </c>
-      <c r="G53" s="8" t="s">
+      <c r="G53" s="11" t="s">
         <v>253</v>
       </c>
       <c r="H53" s="2" t="s">
@@ -8073,10 +8118,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="4">
         <v>85273469740405</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="G54" s="11" t="s">
         <v>255</v>
       </c>
       <c r="H54" s="2" t="s">
@@ -8100,10 +8145,10 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F55" s="4">
         <v>85750403977754</v>
       </c>
-      <c r="G55" s="8" t="s">
+      <c r="G55" s="11" t="s">
         <v>257</v>
       </c>
       <c r="H55" s="2" t="s">
@@ -8127,10 +8172,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="4">
         <v>87658125570749</v>
       </c>
-      <c r="G56" s="8" t="s">
+      <c r="G56" s="11" t="s">
         <v>259</v>
       </c>
       <c r="H56" s="2" t="s">
@@ -8154,10 +8199,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57" s="4">
         <v>71386503893388</v>
       </c>
-      <c r="G57" s="8" t="s">
+      <c r="G57" s="11" t="s">
         <v>261</v>
       </c>
       <c r="H57" s="2" t="s">
@@ -8181,10 +8226,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="4">
         <v>117660867991736</v>
       </c>
-      <c r="G58" s="8" t="s">
+      <c r="G58" s="11" t="s">
         <v>263</v>
       </c>
       <c r="H58" s="2" t="s">
@@ -8208,10 +8253,10 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="4">
         <v>75602786825729</v>
       </c>
-      <c r="G59" s="8" t="s">
+      <c r="G59" s="11" t="s">
         <v>265</v>
       </c>
       <c r="H59" s="2" t="s">
@@ -8235,10 +8280,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="4">
         <v>97494295137425</v>
       </c>
-      <c r="G60" s="8" t="s">
+      <c r="G60" s="11" t="s">
         <v>267</v>
       </c>
       <c r="H60" s="2" t="s">
@@ -8262,10 +8307,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="4">
         <v>121387106380169</v>
       </c>
-      <c r="G61" s="8" t="s">
+      <c r="G61" s="11" t="s">
         <v>269</v>
       </c>
       <c r="H61" s="2" t="s">
@@ -8289,10 +8334,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F62" s="5">
+      <c r="F62" s="4">
         <v>77703154963129</v>
       </c>
-      <c r="G62" s="8" t="s">
+      <c r="G62" s="11" t="s">
         <v>271</v>
       </c>
       <c r="H62" s="2" t="s">
@@ -8316,10 +8361,10 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F63" s="5">
+      <c r="F63" s="4">
         <v>82745313217810</v>
       </c>
-      <c r="G63" s="8" t="s">
+      <c r="G63" s="11" t="s">
         <v>273</v>
       </c>
       <c r="H63" s="2" t="s">
@@ -8343,10 +8388,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64" s="4">
         <v>78702263483439</v>
       </c>
-      <c r="G64" s="8" t="s">
+      <c r="G64" s="11" t="s">
         <v>275</v>
       </c>
       <c r="H64" s="2" t="s">
@@ -8370,10 +8415,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="4">
         <v>103252845267522</v>
       </c>
-      <c r="G65" s="8" t="s">
+      <c r="G65" s="11" t="s">
         <v>277</v>
       </c>
       <c r="H65" s="2" t="s">
@@ -8397,10 +8442,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F66" s="5">
+      <c r="F66" s="4">
         <v>93380659059014</v>
       </c>
-      <c r="G66" s="8" t="s">
+      <c r="G66" s="11" t="s">
         <v>279</v>
       </c>
       <c r="H66" s="2" t="s">
@@ -8424,10 +8469,10 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="F67" s="5">
+      <c r="F67" s="4">
         <v>124070618735034</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="G67" s="11" t="s">
         <v>281</v>
       </c>
       <c r="H67" s="2" t="s">
@@ -8451,10 +8496,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="4">
         <v>82229267783572</v>
       </c>
-      <c r="G68" s="8" t="s">
+      <c r="G68" s="11" t="s">
         <v>283</v>
       </c>
       <c r="H68" s="2" t="s">
@@ -8478,10 +8523,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F69" s="5">
+      <c r="F69" s="4">
         <v>90764663625426</v>
       </c>
-      <c r="G69" s="8" t="s">
+      <c r="G69" s="11" t="s">
         <v>285</v>
       </c>
       <c r="H69" s="2" t="s">
@@ -8505,10 +8550,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F70" s="5">
+      <c r="F70" s="4">
         <v>89592774326120</v>
       </c>
-      <c r="G70" s="8" t="s">
+      <c r="G70" s="11" t="s">
         <v>287</v>
       </c>
       <c r="H70" s="2" t="s">
@@ -8532,10 +8577,10 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F71" s="4">
         <v>96498729983354</v>
       </c>
-      <c r="G71" s="8" t="s">
+      <c r="G71" s="11" t="s">
         <v>289</v>
       </c>
       <c r="H71" s="2" t="s">
@@ -8559,10 +8604,10 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="4">
         <v>137402232463633</v>
       </c>
-      <c r="G72" s="8" t="s">
+      <c r="G72" s="11" t="s">
         <v>291</v>
       </c>
       <c r="H72" s="2" t="s">
@@ -8586,10 +8631,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>15</v>
       </c>
-      <c r="F73" s="5">
+      <c r="F73" s="4">
         <v>79717469784936</v>
       </c>
-      <c r="G73" s="8" t="s">
+      <c r="G73" s="11" t="s">
         <v>293</v>
       </c>
       <c r="H73" s="2" t="s">
@@ -8613,10 +8658,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F74" s="5">
+      <c r="F74" s="4">
         <v>86646811474956</v>
       </c>
-      <c r="G74" s="8" t="s">
+      <c r="G74" s="11" t="s">
         <v>295</v>
       </c>
       <c r="H74" s="2" t="s">
@@ -8640,10 +8685,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F75" s="5">
+      <c r="F75" s="4">
         <v>128217347353354</v>
       </c>
-      <c r="G75" s="8" t="s">
+      <c r="G75" s="11" t="s">
         <v>297</v>
       </c>
       <c r="H75" s="2" t="s">
@@ -8667,10 +8712,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="4">
         <v>126321668579357</v>
       </c>
-      <c r="G76" s="8" t="s">
+      <c r="G76" s="11" t="s">
         <v>299</v>
       </c>
       <c r="H76" s="2" t="s">
@@ -8694,10 +8739,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>16</v>
       </c>
-      <c r="F77" s="5">
+      <c r="F77" s="4">
         <v>98351529529203</v>
       </c>
-      <c r="G77" s="8" t="s">
+      <c r="G77" s="11" t="s">
         <v>301</v>
       </c>
       <c r="H77" s="2" t="s">
@@ -8721,10 +8766,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F78" s="5">
+      <c r="F78" s="4">
         <v>81048668172712</v>
       </c>
-      <c r="G78" s="8" t="s">
+      <c r="G78" s="11" t="s">
         <v>303</v>
       </c>
       <c r="H78" s="2" t="s">
@@ -8748,10 +8793,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F79" s="5">
+      <c r="F79" s="4">
         <v>127615544859575</v>
       </c>
-      <c r="G79" s="8" t="s">
+      <c r="G79" s="11" t="s">
         <v>305</v>
       </c>
       <c r="H79" s="2" t="s">
@@ -8775,10 +8820,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="4">
         <v>70656304136373</v>
       </c>
-      <c r="G80" s="8" t="s">
+      <c r="G80" s="11" t="s">
         <v>307</v>
       </c>
       <c r="H80" s="2" t="s">
@@ -8802,10 +8847,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>17</v>
       </c>
-      <c r="F81" s="5">
+      <c r="F81" s="4">
         <v>134424174805013</v>
       </c>
-      <c r="G81" s="8" t="s">
+      <c r="G81" s="11" t="s">
         <v>309</v>
       </c>
       <c r="H81" s="2" t="s">
@@ -8829,10 +8874,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F82" s="5">
+      <c r="F82" s="4">
         <v>127255485663084</v>
       </c>
-      <c r="G82" s="8" t="s">
+      <c r="G82" s="11" t="s">
         <v>311</v>
       </c>
       <c r="H82" s="2" t="s">
@@ -8856,10 +8901,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F83" s="5">
+      <c r="F83" s="4">
         <v>134027683373658</v>
       </c>
-      <c r="G83" s="8" t="s">
+      <c r="G83" s="11" t="s">
         <v>313</v>
       </c>
       <c r="H83" s="2" t="s">
@@ -8883,10 +8928,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F84" s="5">
+      <c r="F84" s="4">
         <v>112447657334137</v>
       </c>
-      <c r="G84" s="8" t="s">
+      <c r="G84" s="11" t="s">
         <v>315</v>
       </c>
       <c r="H84" s="2" t="s">
@@ -8910,10 +8955,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>18</v>
       </c>
-      <c r="F85" s="5">
+      <c r="F85" s="4">
         <v>104595008892706</v>
       </c>
-      <c r="G85" s="8" t="s">
+      <c r="G85" s="11" t="s">
         <v>317</v>
       </c>
       <c r="H85" s="2" t="s">
@@ -8937,10 +8982,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F86" s="5">
+      <c r="F86" s="4">
         <v>82759045606098</v>
       </c>
-      <c r="G86" s="8" t="s">
+      <c r="G86" s="11" t="s">
         <v>319</v>
       </c>
       <c r="H86" s="2" t="s">
@@ -8964,10 +9009,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F87" s="5">
+      <c r="F87" s="4">
         <v>105620837789519</v>
       </c>
-      <c r="G87" s="8" t="s">
+      <c r="G87" s="11" t="s">
         <v>321</v>
       </c>
       <c r="H87" s="2" t="s">
@@ -8991,10 +9036,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F88" s="5">
+      <c r="F88" s="4">
         <v>111024567754480</v>
       </c>
-      <c r="G88" s="8" t="s">
+      <c r="G88" s="11" t="s">
         <v>323</v>
       </c>
       <c r="H88" s="2" t="s">
@@ -9018,10 +9063,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>19</v>
       </c>
-      <c r="F89" s="5">
+      <c r="F89" s="4">
         <v>137153989969007</v>
       </c>
-      <c r="G89" s="8" t="s">
+      <c r="G89" s="11" t="s">
         <v>325</v>
       </c>
       <c r="H89" s="2" t="s">
@@ -9045,10 +9090,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F90" s="5">
+      <c r="F90" s="4">
         <v>74496996195913</v>
       </c>
-      <c r="G90" s="8" t="s">
+      <c r="G90" s="11" t="s">
         <v>327</v>
       </c>
       <c r="H90" s="2" t="s">
@@ -9072,10 +9117,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F91" s="5">
+      <c r="F91" s="4">
         <v>132785860315163</v>
       </c>
-      <c r="G91" s="8" t="s">
+      <c r="G91" s="11" t="s">
         <v>329</v>
       </c>
       <c r="H91" s="2" t="s">
@@ -9099,10 +9144,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F92" s="5">
+      <c r="F92" s="4">
         <v>117198962948319</v>
       </c>
-      <c r="G92" s="8" t="s">
+      <c r="G92" s="11" t="s">
         <v>331</v>
       </c>
       <c r="H92" s="2" t="s">
@@ -9126,10 +9171,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>20</v>
       </c>
-      <c r="F93" s="5">
+      <c r="F93" s="4">
         <v>124449160476895</v>
       </c>
-      <c r="G93" s="8" t="s">
+      <c r="G93" s="11" t="s">
         <v>333</v>
       </c>
       <c r="H93" s="2" t="s">
@@ -9153,10 +9198,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F94" s="5">
+      <c r="F94" s="4">
         <v>125887863438527</v>
       </c>
-      <c r="G94" s="8" t="s">
+      <c r="G94" s="11" t="s">
         <v>335</v>
       </c>
       <c r="H94" s="2" t="s">
@@ -9180,10 +9225,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F95" s="5">
+      <c r="F95" s="4">
         <v>137692564728429</v>
       </c>
-      <c r="G95" s="8" t="s">
+      <c r="G95" s="11" t="s">
         <v>337</v>
       </c>
       <c r="H95" s="2" t="s">
@@ -9207,10 +9252,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F96" s="5">
+      <c r="F96" s="4">
         <v>82350951870220</v>
       </c>
-      <c r="G96" s="8" t="s">
+      <c r="G96" s="11" t="s">
         <v>339</v>
       </c>
       <c r="H96" s="2" t="s">
@@ -9234,10 +9279,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>21</v>
       </c>
-      <c r="F97" s="5">
+      <c r="F97" s="4">
         <v>133019385929561</v>
       </c>
-      <c r="G97" s="8" t="s">
+      <c r="G97" s="11" t="s">
         <v>341</v>
       </c>
       <c r="H97" s="2" t="s">
@@ -9261,10 +9306,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F98" s="5">
+      <c r="F98" s="4">
         <v>82714807302588</v>
       </c>
-      <c r="G98" s="8" t="s">
+      <c r="G98" s="11" t="s">
         <v>343</v>
       </c>
       <c r="H98" s="2" t="s">
@@ -9288,10 +9333,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F99" s="5">
+      <c r="F99" s="4">
         <v>120409278538446</v>
       </c>
-      <c r="G99" s="8" t="s">
+      <c r="G99" s="11" t="s">
         <v>345</v>
       </c>
       <c r="H99" s="2" t="s">
@@ -9315,10 +9360,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F100" s="5">
+      <c r="F100" s="4">
         <v>136303201068741</v>
       </c>
-      <c r="G100" s="8" t="s">
+      <c r="G100" s="11" t="s">
         <v>347</v>
       </c>
       <c r="H100" s="2" t="s">
@@ -9342,10 +9387,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>22</v>
       </c>
-      <c r="F101" s="5">
+      <c r="F101" s="4">
         <v>76724781858184</v>
       </c>
-      <c r="G101" s="8" t="s">
+      <c r="G101" s="11" t="s">
         <v>349</v>
       </c>
       <c r="H101" s="2" t="s">
@@ -9369,10 +9414,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F102" s="5">
+      <c r="F102" s="4">
         <v>120125979830927</v>
       </c>
-      <c r="G102" s="8" t="s">
+      <c r="G102" s="11" t="s">
         <v>351</v>
       </c>
       <c r="H102" s="2" t="s">
@@ -9396,10 +9441,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F103" s="5">
+      <c r="F103" s="4">
         <v>86921870572603</v>
       </c>
-      <c r="G103" s="8" t="s">
+      <c r="G103" s="11" t="s">
         <v>353</v>
       </c>
       <c r="H103" s="2" t="s">
@@ -9423,10 +9468,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F104" s="5">
+      <c r="F104" s="4">
         <v>126355990231048</v>
       </c>
-      <c r="G104" s="8" t="s">
+      <c r="G104" s="11" t="s">
         <v>355</v>
       </c>
       <c r="H104" s="2" t="s">
@@ -9450,10 +9495,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>23</v>
       </c>
-      <c r="F105" s="5">
+      <c r="F105" s="4">
         <v>72326444062448</v>
       </c>
-      <c r="G105" s="8" t="s">
+      <c r="G105" s="11" t="s">
         <v>357</v>
       </c>
       <c r="H105" s="2" t="s">
@@ -9477,10 +9522,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F106" s="5">
+      <c r="F106" s="4">
         <v>72257499044823</v>
       </c>
-      <c r="G106" s="8" t="s">
+      <c r="G106" s="11" t="s">
         <v>359</v>
       </c>
       <c r="H106" s="2" t="s">
@@ -9504,10 +9549,10 @@
         <f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</f>
         <v>24</v>
       </c>
-      <c r="F107" s="5">
+      <c r="F107" s="4">
         <v>74695865349139</v>
       </c>
-      <c r="G107" s="8" t="s">
+      <c r="G107" s="11" t="s">
         <v>361</v>
       </c>
       <c r="H107" s="2" t="s">
@@ -9530,10 +9575,10 @@
       <c r="E108" s="1">
         <v>24</v>
       </c>
-      <c r="F108" s="5">
+      <c r="F108" s="4">
         <v>98358488442985</v>
       </c>
-      <c r="G108" s="8" t="s">
+      <c r="G108" s="11" t="s">
         <v>363</v>
       </c>
       <c r="H108" s="2" t="s">
@@ -9557,10 +9602,10 @@
       <c r="E109" s="1">
         <v>24</v>
       </c>
-      <c r="F109" s="5">
+      <c r="F109" s="4">
         <v>113636295509693</v>
       </c>
-      <c r="G109" s="8" t="s">
+      <c r="G109" s="11" t="s">
         <v>365</v>
       </c>
       <c r="H109" s="2" t="s">
@@ -9584,10 +9629,10 @@
       <c r="E110" s="1">
         <v>25</v>
       </c>
-      <c r="F110" s="5">
+      <c r="F110" s="4">
         <v>114047124407739</v>
       </c>
-      <c r="G110" s="8" t="s">
+      <c r="G110" s="11" t="s">
         <v>367</v>
       </c>
       <c r="H110" s="2" t="s">
@@ -9611,10 +9656,10 @@
       <c r="E111" s="1">
         <v>25</v>
       </c>
-      <c r="F111" s="5">
+      <c r="F111" s="4">
         <v>95771403493939</v>
       </c>
-      <c r="G111" s="8" t="s">
+      <c r="G111" s="11" t="s">
         <v>369</v>
       </c>
       <c r="H111" s="2" t="s">
@@ -9638,10 +9683,10 @@
       <c r="E112" s="1">
         <v>25</v>
       </c>
-      <c r="F112" s="5">
+      <c r="F112" s="4">
         <v>140393673870516</v>
       </c>
-      <c r="G112" s="8" t="s">
+      <c r="G112" s="11" t="s">
         <v>371</v>
       </c>
       <c r="H112" s="2" t="s">
@@ -9665,10 +9710,10 @@
       <c r="E113" s="1">
         <v>25</v>
       </c>
-      <c r="F113" s="5">
+      <c r="F113" s="4">
         <v>123109322631502</v>
       </c>
-      <c r="G113" s="8" t="s">
+      <c r="G113" s="11" t="s">
         <v>373</v>
       </c>
       <c r="H113" s="2" t="s">
@@ -9692,10 +9737,10 @@
       <c r="E114" s="1">
         <v>26</v>
       </c>
-      <c r="F114" s="5">
+      <c r="F114" s="4">
         <v>98614967981417</v>
       </c>
-      <c r="G114" s="8" t="s">
+      <c r="G114" s="11" t="s">
         <v>375</v>
       </c>
       <c r="H114" s="2" t="s">
@@ -9719,10 +9764,10 @@
       <c r="E115" s="1">
         <v>26</v>
       </c>
-      <c r="F115" s="5">
+      <c r="F115" s="4">
         <v>127369769981706</v>
       </c>
-      <c r="G115" s="8" t="s">
+      <c r="G115" s="11" t="s">
         <v>377</v>
       </c>
       <c r="H115" s="2" t="s">
@@ -9746,10 +9791,10 @@
       <c r="E116" s="1">
         <v>26</v>
       </c>
-      <c r="F116" s="5">
+      <c r="F116" s="4">
         <v>134574393827781</v>
       </c>
-      <c r="G116" s="8" t="s">
+      <c r="G116" s="11" t="s">
         <v>379</v>
       </c>
       <c r="H116" s="2" t="s">
@@ -9773,10 +9818,10 @@
       <c r="E117" s="1">
         <v>26</v>
       </c>
-      <c r="F117" s="5">
+      <c r="F117" s="4">
         <v>130258203281991</v>
       </c>
-      <c r="G117" s="8" t="s">
+      <c r="G117" s="11" t="s">
         <v>381</v>
       </c>
       <c r="H117" s="2" t="s">
@@ -9800,10 +9845,10 @@
       <c r="E118" s="1">
         <v>27</v>
       </c>
-      <c r="F118" s="5">
+      <c r="F118" s="4">
         <v>93953823085119</v>
       </c>
-      <c r="G118" s="8" t="s">
+      <c r="G118" s="11" t="s">
         <v>383</v>
       </c>
       <c r="H118" s="2" t="s">
@@ -9827,10 +9872,10 @@
       <c r="E119" s="1">
         <v>27</v>
       </c>
-      <c r="F119" s="5">
+      <c r="F119" s="4">
         <v>109802560542166</v>
       </c>
-      <c r="G119" s="8" t="s">
+      <c r="G119" s="11" t="s">
         <v>385</v>
       </c>
       <c r="H119" s="2" t="s">
@@ -9854,10 +9899,10 @@
       <c r="E120" s="1">
         <v>27</v>
       </c>
-      <c r="F120" s="5">
+      <c r="F120" s="4">
         <v>130989494782889</v>
       </c>
-      <c r="G120" s="8" t="s">
+      <c r="G120" s="11" t="s">
         <v>387</v>
       </c>
       <c r="H120" s="2" t="s">
@@ -9881,10 +9926,10 @@
       <c r="E121" s="1">
         <v>27</v>
       </c>
-      <c r="F121" s="5">
+      <c r="F121" s="4">
         <v>129408716253336</v>
       </c>
-      <c r="G121" s="8" t="s">
+      <c r="G121" s="11" t="s">
         <v>389</v>
       </c>
       <c r="H121" s="2" t="s">
@@ -9908,10 +9953,10 @@
       <c r="E122" s="1">
         <v>28</v>
       </c>
-      <c r="F122" s="5">
+      <c r="F122" s="4">
         <v>127772866805590</v>
       </c>
-      <c r="G122" s="8" t="s">
+      <c r="G122" s="11" t="s">
         <v>391</v>
       </c>
       <c r="H122" s="2" t="s">
@@ -9935,10 +9980,10 @@
       <c r="E123" s="1">
         <v>28</v>
       </c>
-      <c r="F123" s="5">
+      <c r="F123" s="4">
         <v>91938109188463</v>
       </c>
-      <c r="G123" s="8" t="s">
+      <c r="G123" s="11" t="s">
         <v>393</v>
       </c>
       <c r="H123" s="2" t="s">
@@ -9962,10 +10007,10 @@
       <c r="E124" s="1">
         <v>28</v>
       </c>
-      <c r="F124" s="5">
+      <c r="F124" s="4">
         <v>85077262752129</v>
       </c>
-      <c r="G124" s="8" t="s">
+      <c r="G124" s="11" t="s">
         <v>395</v>
       </c>
       <c r="H124" s="2" t="s">
@@ -9980,7 +10025,7 @@
       <c r="B125" s="1">
         <v>122</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="11" t="s">
         <v>396</v>
       </c>
       <c r="D125" s="1">
@@ -9989,10 +10034,10 @@
       <c r="E125" s="1">
         <v>28</v>
       </c>
-      <c r="F125" s="5">
+      <c r="F125" s="4">
         <v>140335958193244</v>
       </c>
-      <c r="G125" s="8" t="s">
+      <c r="G125" s="11" t="s">
         <v>397</v>
       </c>
       <c r="H125" s="2" t="s">
@@ -10006,7 +10051,7 @@
       <c r="B126" s="1">
         <v>123</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C126" s="11" t="s">
         <v>398</v>
       </c>
       <c r="D126" s="1">
@@ -10015,10 +10060,10 @@
       <c r="E126" s="1">
         <v>29</v>
       </c>
-      <c r="F126" s="5">
+      <c r="F126" s="4">
         <v>86732012145983</v>
       </c>
-      <c r="G126" s="8" t="s">
+      <c r="G126" s="11" t="s">
         <v>399</v>
       </c>
       <c r="H126" s="2" t="s">
@@ -10032,7 +10077,7 @@
       <c r="B127" s="1">
         <v>124</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="11" t="s">
         <v>400</v>
       </c>
       <c r="D127" s="1">
@@ -10041,10 +10086,10 @@
       <c r="E127" s="1">
         <v>29</v>
       </c>
-      <c r="F127" s="5">
+      <c r="F127" s="4">
         <v>78044122276865</v>
       </c>
-      <c r="G127" s="8" t="s">
+      <c r="G127" s="11" t="s">
         <v>401</v>
       </c>
       <c r="H127" s="2" t="s">
@@ -10058,7 +10103,7 @@
       <c r="B128" s="1">
         <v>125</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="11" t="s">
         <v>402</v>
       </c>
       <c r="D128" s="1">
@@ -10067,10 +10112,10 @@
       <c r="E128" s="1">
         <v>29</v>
       </c>
-      <c r="F128" s="5">
+      <c r="F128" s="4">
         <v>114974638199136</v>
       </c>
-      <c r="G128" s="8" t="s">
+      <c r="G128" s="11" t="s">
         <v>403</v>
       </c>
       <c r="H128" s="2" t="s">
@@ -10084,7 +10129,7 @@
       <c r="B129" s="1">
         <v>126</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="11" t="s">
         <v>404</v>
       </c>
       <c r="D129" s="1">
@@ -10093,10 +10138,10 @@
       <c r="E129" s="1">
         <v>29</v>
       </c>
-      <c r="F129" s="5">
+      <c r="F129" s="4">
         <v>83652207307759</v>
       </c>
-      <c r="G129" s="8" t="s">
+      <c r="G129" s="11" t="s">
         <v>405</v>
       </c>
       <c r="H129" s="2" t="s">
@@ -10110,7 +10155,7 @@
       <c r="B130" s="1">
         <v>127</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="11" t="s">
         <v>406</v>
       </c>
       <c r="D130" s="1">
@@ -10119,10 +10164,10 @@
       <c r="E130" s="1">
         <v>30</v>
       </c>
-      <c r="F130" s="5">
+      <c r="F130" s="4">
         <v>131787091355052</v>
       </c>
-      <c r="G130" s="8" t="s">
+      <c r="G130" s="11" t="s">
         <v>407</v>
       </c>
       <c r="H130" s="2" t="s">
@@ -10136,7 +10181,7 @@
       <c r="B131" s="1">
         <v>128</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="11" t="s">
         <v>408</v>
       </c>
       <c r="D131" s="1">
@@ -10145,10 +10190,10 @@
       <c r="E131" s="1">
         <v>30</v>
       </c>
-      <c r="F131" s="5">
+      <c r="F131" s="4">
         <v>99348381699835</v>
       </c>
-      <c r="G131" s="8" t="s">
+      <c r="G131" s="11" t="s">
         <v>409</v>
       </c>
       <c r="H131" s="2" t="s">
@@ -10162,7 +10207,7 @@
       <c r="B132" s="1">
         <v>129</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="11" t="s">
         <v>410</v>
       </c>
       <c r="D132" s="1">
@@ -10171,10 +10216,10 @@
       <c r="E132" s="1">
         <v>30</v>
       </c>
-      <c r="F132" s="5">
+      <c r="F132" s="4">
         <v>75412160560516</v>
       </c>
-      <c r="G132" s="8" t="s">
+      <c r="G132" s="11" t="s">
         <v>411</v>
       </c>
       <c r="H132" s="2" t="s">
@@ -10188,7 +10233,7 @@
       <c r="B133" s="1">
         <v>130</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="11" t="s">
         <v>412</v>
       </c>
       <c r="D133" s="1">
@@ -10197,10 +10242,10 @@
       <c r="E133" s="1">
         <v>30</v>
       </c>
-      <c r="F133" s="5">
+      <c r="F133" s="4">
         <v>105475505052937</v>
       </c>
-      <c r="G133" s="8" t="s">
+      <c r="G133" s="11" t="s">
         <v>413</v>
       </c>
       <c r="H133" s="2" t="s">
@@ -10214,7 +10259,7 @@
       <c r="B134" s="1">
         <v>131</v>
       </c>
-      <c r="C134" s="8" t="s">
+      <c r="C134" s="11" t="s">
         <v>414</v>
       </c>
       <c r="D134" s="1">
@@ -10223,10 +10268,10 @@
       <c r="E134" s="1">
         <v>31</v>
       </c>
-      <c r="F134" s="5">
+      <c r="F134" s="4">
         <v>125484119033793</v>
       </c>
-      <c r="G134" s="8" t="s">
+      <c r="G134" s="11" t="s">
         <v>415</v>
       </c>
       <c r="H134" s="2" t="s">
@@ -10240,7 +10285,7 @@
       <c r="B135" s="1">
         <v>132</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="11" t="s">
         <v>416</v>
       </c>
       <c r="D135" s="1">
@@ -10249,10 +10294,10 @@
       <c r="E135" s="1">
         <v>31</v>
       </c>
-      <c r="F135" s="5">
+      <c r="F135" s="4">
         <v>140608831780254</v>
       </c>
-      <c r="G135" s="8" t="s">
+      <c r="G135" s="11" t="s">
         <v>417</v>
       </c>
       <c r="H135" s="2" t="s">
@@ -10266,7 +10311,7 @@
       <c r="B136" s="1">
         <v>133</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="C136" s="11" t="s">
         <v>418</v>
       </c>
       <c r="D136" s="1">
@@ -10275,10 +10320,10 @@
       <c r="E136" s="1">
         <v>31</v>
       </c>
-      <c r="F136" s="5">
+      <c r="F136" s="4">
         <v>124177358025481</v>
       </c>
-      <c r="G136" s="8" t="s">
+      <c r="G136" s="11" t="s">
         <v>419</v>
       </c>
       <c r="H136" s="2" t="s">
@@ -10292,7 +10337,7 @@
       <c r="B137" s="1">
         <v>134</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="11" t="s">
         <v>420</v>
       </c>
       <c r="D137" s="1">
@@ -10301,10 +10346,10 @@
       <c r="E137" s="1">
         <v>31</v>
       </c>
-      <c r="F137" s="5">
+      <c r="F137" s="4">
         <v>129385390119523</v>
       </c>
-      <c r="G137" s="8" t="s">
+      <c r="G137" s="11" t="s">
         <v>421</v>
       </c>
       <c r="H137" s="2" t="s">
@@ -10318,7 +10363,7 @@
       <c r="B138" s="1">
         <v>135</v>
       </c>
-      <c r="C138" s="8" t="s">
+      <c r="C138" s="11" t="s">
         <v>422</v>
       </c>
       <c r="D138" s="1">
@@ -10327,10 +10372,10 @@
       <c r="E138" s="1">
         <v>32</v>
       </c>
-      <c r="F138" s="5">
+      <c r="F138" s="4">
         <v>84940520003035</v>
       </c>
-      <c r="G138" s="8" t="s">
+      <c r="G138" s="11" t="s">
         <v>423</v>
       </c>
       <c r="H138" s="2" t="s">
@@ -10344,7 +10389,7 @@
       <c r="B139" s="1">
         <v>136</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="11" t="s">
         <v>424</v>
       </c>
       <c r="D139" s="1">
@@ -10353,10 +10398,10 @@
       <c r="E139" s="1">
         <v>32</v>
       </c>
-      <c r="F139" s="5">
+      <c r="F139" s="4">
         <v>90031364711610</v>
       </c>
-      <c r="G139" s="8" t="s">
+      <c r="G139" s="11" t="s">
         <v>425</v>
       </c>
       <c r="H139" s="2" t="s">
@@ -10370,7 +10415,7 @@
       <c r="B140" s="1">
         <v>137</v>
       </c>
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="11" t="s">
         <v>426</v>
       </c>
       <c r="D140" s="1">
@@ -10379,10 +10424,10 @@
       <c r="E140" s="1">
         <v>32</v>
       </c>
-      <c r="F140" s="5">
+      <c r="F140" s="4">
         <v>84418341821320</v>
       </c>
-      <c r="G140" s="8" t="s">
+      <c r="G140" s="11" t="s">
         <v>427</v>
       </c>
       <c r="H140" s="2" t="s">
@@ -10396,7 +10441,7 @@
       <c r="B141" s="1">
         <v>138</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="11" t="s">
         <v>428</v>
       </c>
       <c r="D141" s="1">
@@ -10405,10 +10450,10 @@
       <c r="E141" s="1">
         <v>32</v>
       </c>
-      <c r="F141" s="5">
+      <c r="F141" s="4">
         <v>130255705800444</v>
       </c>
-      <c r="G141" s="8" t="s">
+      <c r="G141" s="11" t="s">
         <v>429</v>
       </c>
       <c r="H141" s="2" t="s">
@@ -10422,7 +10467,7 @@
       <c r="B142" s="1">
         <v>139</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="11" t="s">
         <v>430</v>
       </c>
       <c r="D142" s="1">
@@ -10431,10 +10476,10 @@
       <c r="E142" s="1">
         <v>33</v>
       </c>
-      <c r="F142" s="5">
+      <c r="F142" s="4">
         <v>123568265278671</v>
       </c>
-      <c r="G142" s="8" t="s">
+      <c r="G142" s="11" t="s">
         <v>431</v>
       </c>
       <c r="H142" s="2" t="s">
@@ -10448,7 +10493,7 @@
       <c r="B143" s="1">
         <v>140</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="11" t="s">
         <v>432</v>
       </c>
       <c r="D143" s="1">
@@ -10457,10 +10502,10 @@
       <c r="E143" s="1">
         <v>33</v>
       </c>
-      <c r="F143" s="5">
+      <c r="F143" s="4">
         <v>75689117044416</v>
       </c>
-      <c r="G143" s="8" t="s">
+      <c r="G143" s="11" t="s">
         <v>433</v>
       </c>
       <c r="H143" s="2" t="s">
@@ -10474,7 +10519,7 @@
       <c r="B144" s="1">
         <v>141</v>
       </c>
-      <c r="C144" s="8" t="s">
+      <c r="C144" s="11" t="s">
         <v>434</v>
       </c>
       <c r="D144" s="1">
@@ -10483,10 +10528,10 @@
       <c r="E144" s="1">
         <v>33</v>
       </c>
-      <c r="F144" s="5">
+      <c r="F144" s="4">
         <v>92309488435591</v>
       </c>
-      <c r="G144" s="8" t="s">
+      <c r="G144" s="11" t="s">
         <v>435</v>
       </c>
       <c r="H144" s="2" t="s">
@@ -10500,7 +10545,7 @@
       <c r="B145" s="1">
         <v>142</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="11" t="s">
         <v>436</v>
       </c>
       <c r="D145" s="1">
@@ -10509,10 +10554,10 @@
       <c r="E145" s="1">
         <v>33</v>
       </c>
-      <c r="F145" s="5">
+      <c r="F145" s="4">
         <v>106319308889290</v>
       </c>
-      <c r="G145" s="8" t="s">
+      <c r="G145" s="11" t="s">
         <v>437</v>
       </c>
       <c r="H145" s="2" t="s">
@@ -10526,7 +10571,7 @@
       <c r="B146" s="1">
         <v>143</v>
       </c>
-      <c r="C146" s="8" t="s">
+      <c r="C146" s="11" t="s">
         <v>438</v>
       </c>
       <c r="D146" s="1">
@@ -10535,10 +10580,10 @@
       <c r="E146" s="1">
         <v>34</v>
       </c>
-      <c r="F146" s="5">
+      <c r="F146" s="4">
         <v>123120949699520</v>
       </c>
-      <c r="G146" s="8" t="s">
+      <c r="G146" s="11" t="s">
         <v>439</v>
       </c>
       <c r="H146" s="2" t="s">
@@ -10552,7 +10597,7 @@
       <c r="B147" s="1">
         <v>144</v>
       </c>
-      <c r="C147" s="8" t="s">
+      <c r="C147" s="11" t="s">
         <v>440</v>
       </c>
       <c r="D147" s="1">
@@ -10561,10 +10606,10 @@
       <c r="E147" s="1">
         <v>34</v>
       </c>
-      <c r="F147" s="5">
+      <c r="F147" s="4">
         <v>111674856010497</v>
       </c>
-      <c r="G147" s="8" t="s">
+      <c r="G147" s="11" t="s">
         <v>441</v>
       </c>
       <c r="H147" s="2" t="s">
@@ -10578,7 +10623,7 @@
       <c r="B148" s="1">
         <v>145</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="C148" s="11" t="s">
         <v>442</v>
       </c>
       <c r="D148" s="1">
@@ -10587,10 +10632,10 @@
       <c r="E148" s="1">
         <v>34</v>
       </c>
-      <c r="F148" s="5">
+      <c r="F148" s="4">
         <v>118080816505555</v>
       </c>
-      <c r="G148" s="8" t="s">
+      <c r="G148" s="11" t="s">
         <v>443</v>
       </c>
       <c r="H148" s="2" t="s">
@@ -10604,7 +10649,7 @@
       <c r="B149" s="1">
         <v>146</v>
       </c>
-      <c r="C149" s="8" t="s">
+      <c r="C149" s="11" t="s">
         <v>444</v>
       </c>
       <c r="D149" s="1">
@@ -10613,10 +10658,10 @@
       <c r="E149" s="1">
         <v>34</v>
       </c>
-      <c r="F149" s="5">
+      <c r="F149" s="4">
         <v>105021574817966</v>
       </c>
-      <c r="G149" s="8" t="s">
+      <c r="G149" s="11" t="s">
         <v>445</v>
       </c>
       <c r="H149" s="2" t="s">
@@ -10630,7 +10675,7 @@
       <c r="B150" s="1">
         <v>147</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C150" s="11" t="s">
         <v>446</v>
       </c>
       <c r="D150" s="1">
@@ -10639,10 +10684,10 @@
       <c r="E150" s="1">
         <v>35</v>
       </c>
-      <c r="F150" s="5">
+      <c r="F150" s="4">
         <v>72690180103558</v>
       </c>
-      <c r="G150" s="8" t="s">
+      <c r="G150" s="11" t="s">
         <v>447</v>
       </c>
       <c r="H150" s="2" t="s">
@@ -10656,7 +10701,7 @@
       <c r="B151" s="1">
         <v>148</v>
       </c>
-      <c r="C151" s="8" t="s">
+      <c r="C151" s="11" t="s">
         <v>448</v>
       </c>
       <c r="D151" s="1">
@@ -10665,10 +10710,10 @@
       <c r="E151" s="1">
         <v>35</v>
       </c>
-      <c r="F151" s="5">
+      <c r="F151" s="4">
         <v>94914272618995</v>
       </c>
-      <c r="G151" s="8" t="s">
+      <c r="G151" s="11" t="s">
         <v>449</v>
       </c>
       <c r="H151" s="2" t="s">
@@ -10692,156 +10737,156 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="10" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="2" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>452</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="10" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="3" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="10" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A4" s="7">
+      <c r="A4" s="10">
         <v>1</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="10">
         <v>2</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="10">
         <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A5" s="7">
+      <c r="A5" s="10">
         <v>2</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="10">
         <v>4</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="10">
         <v>151</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A6" s="7">
+      <c r="A6" s="10">
         <v>3</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="10">
         <v>8</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="10">
         <v>152</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A7" s="7">
+      <c r="A7" s="10">
         <v>4</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="10">
         <v>16</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="10">
         <v>153</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A8" s="7">
+      <c r="A8" s="10">
         <v>5</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="10">
         <v>32</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="10">
         <v>154</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A9" s="7">
+      <c r="A9" s="10">
         <v>6</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="10">
         <v>64</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="10">
         <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="15" customHeight="1" spans="1:3">
-      <c r="A10" s="7">
+      <c r="A10" s="10">
         <v>7</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="10">
         <v>128</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="10">
         <v>156</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A11" s="7">
+      <c r="A11" s="10">
         <v>8</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="10">
         <v>256</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="10">
         <v>157</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A12" s="7">
+      <c r="A12" s="10">
         <v>9</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="10">
         <v>512</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="10">
         <v>158</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A13" s="7">
+      <c r="A13" s="10">
         <v>10</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="10">
         <v>1024</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="10">
         <v>159</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="16.5" spans="1:3">
-      <c r="A14" s="7">
+      <c r="A14" s="10">
         <v>11</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="10">
         <v>2048</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="10">
         <v>160</v>
       </c>
     </row>
@@ -10859,18 +10904,20 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="38.6333333333333" customWidth="1"/>
-    <col min="3" max="4" width="23.3833333333333" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="22.9333333333333" customWidth="1"/>
-    <col min="7" max="7" width="55" customWidth="1"/>
-    <col min="8" max="8" width="44.5583333333333" customWidth="1"/>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="38.6333333333333" style="5" customWidth="1"/>
+    <col min="3" max="4" width="23.3833333333333" style="5" customWidth="1"/>
+    <col min="5" max="5" width="28" style="5" customWidth="1"/>
+    <col min="6" max="6" width="22.9333333333333" style="5" customWidth="1"/>
+    <col min="7" max="7" width="55" style="5" customWidth="1"/>
+    <col min="8" max="8" width="44.5583333333333" style="5" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="16.5" spans="1:9">
+    <row r="1" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>54</v>
       </c>
@@ -10896,7 +10943,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" customFormat="1" ht="16.5" spans="1:9">
+    <row r="2" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -10922,7 +10969,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="16.5" spans="1:9">
+    <row r="3" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>63</v>
       </c>
@@ -10948,7 +10995,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="16.5" spans="1:9">
+    <row r="4" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -10965,15 +11012,15 @@
         <v>1</v>
       </c>
       <c r="F4" s="1"/>
-      <c r="G4">
+      <c r="G4" s="5">
         <v>99853650045862</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="I4" s="6"/>
+      <c r="I4" s="7"/>
     </row>
-    <row r="5" customFormat="1" ht="16.5" spans="1:9">
+    <row r="5" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -10990,15 +11037,15 @@
         <v>39</v>
       </c>
       <c r="F5" s="1"/>
-      <c r="G5">
+      <c r="G5" s="5">
         <v>116225665846279</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="I5" s="6"/>
+      <c r="I5" s="7"/>
     </row>
-    <row r="6" customFormat="1" ht="16.5" spans="1:9">
+    <row r="6" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -11015,15 +11062,15 @@
         <v>450</v>
       </c>
       <c r="F6" s="1"/>
-      <c r="G6">
+      <c r="G6" s="5">
         <v>136956773152573</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="I6" s="6"/>
+      <c r="I6" s="7"/>
     </row>
-    <row r="7" customFormat="1" ht="16.5" spans="1:9">
+    <row r="7" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -11040,15 +11087,15 @@
         <v>3282</v>
       </c>
       <c r="F7" s="1"/>
-      <c r="G7">
+      <c r="G7" s="5">
         <v>97553870039023</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="I7" s="6"/>
+      <c r="I7" s="7"/>
     </row>
-    <row r="8" customFormat="1" ht="16.5" spans="1:9">
+    <row r="8" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -11058,22 +11105,22 @@
       <c r="C8" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="29" t="s">
         <v>470</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="29" t="s">
         <v>471</v>
       </c>
       <c r="F8" s="1"/>
-      <c r="G8">
+      <c r="G8" s="5">
         <v>118090700645855</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="I8" s="6"/>
+      <c r="I8" s="7"/>
     </row>
-    <row r="9" customFormat="1" ht="16.5" spans="1:9">
+    <row r="9" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -11083,22 +11130,22 @@
       <c r="C9" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="29" t="s">
         <v>474</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="29" t="s">
         <v>475</v>
       </c>
       <c r="F9" s="1"/>
-      <c r="G9">
+      <c r="G9" s="5">
         <v>138508042210191</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="I9" s="6"/>
+      <c r="I9" s="7"/>
     </row>
-    <row r="10" customFormat="1" ht="16.5" spans="1:9">
+    <row r="10" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -11108,22 +11155,22 @@
       <c r="C10" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="29" t="s">
         <v>478</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="29" t="s">
         <v>479</v>
       </c>
       <c r="F10" s="1"/>
-      <c r="G10">
+      <c r="G10" s="5">
         <v>78371166922896</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="I10" s="6"/>
+      <c r="I10" s="7"/>
     </row>
-    <row r="11" customFormat="1" ht="16.5" spans="1:9">
+    <row r="11" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -11133,22 +11180,22 @@
       <c r="C11" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="29" t="s">
         <v>482</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="29" t="s">
         <v>483</v>
       </c>
       <c r="F11" s="1"/>
-      <c r="G11">
+      <c r="G11" s="5">
         <v>132966760008713</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="6" t="s">
         <v>484</v>
       </c>
-      <c r="I11" s="6"/>
+      <c r="I11" s="7"/>
     </row>
-    <row r="12" customFormat="1" ht="16.5" spans="1:9">
+    <row r="12" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -11158,22 +11205,22 @@
       <c r="C12" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="29" t="s">
         <v>486</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="29" t="s">
         <v>487</v>
       </c>
       <c r="F12" s="1"/>
-      <c r="G12">
+      <c r="G12" s="5">
         <v>133927008310944</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="6" t="s">
         <v>488</v>
       </c>
-      <c r="I12" s="6"/>
+      <c r="I12" s="7"/>
     </row>
-    <row r="13" customFormat="1" ht="16.5" spans="1:9">
+    <row r="13" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -11183,22 +11230,22 @@
       <c r="C13" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="29" t="s">
         <v>490</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="29" t="s">
         <v>491</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="G13">
+      <c r="G13" s="5">
         <v>98415179467911</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="6" t="s">
         <v>492</v>
       </c>
-      <c r="I13" s="6"/>
+      <c r="I13" s="7"/>
     </row>
-    <row r="14" customFormat="1" ht="16.5" spans="1:9">
+    <row r="14" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -11208,22 +11255,22 @@
       <c r="C14" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="29" t="s">
         <v>494</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="29" t="s">
         <v>495</v>
       </c>
       <c r="F14" s="1"/>
-      <c r="G14">
+      <c r="G14" s="5">
         <v>79276409476682</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="I14" s="6"/>
+      <c r="I14" s="7"/>
     </row>
-    <row r="15" customFormat="1" ht="16.5" spans="1:9">
+    <row r="15" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -11233,22 +11280,22 @@
       <c r="C15" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="29" t="s">
         <v>498</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="29" t="s">
         <v>499</v>
       </c>
       <c r="F15" s="1"/>
-      <c r="G15">
+      <c r="G15" s="5">
         <v>86184044773576</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="I15" s="6"/>
+      <c r="I15" s="7"/>
     </row>
-    <row r="16" customFormat="1" ht="16.5" spans="1:9">
+    <row r="16" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -11258,22 +11305,22 @@
       <c r="C16" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="29" t="s">
         <v>502</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E16" s="29" t="s">
         <v>503</v>
       </c>
       <c r="F16" s="1"/>
-      <c r="G16">
+      <c r="G16" s="5">
         <v>85964386896273</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="6" t="s">
         <v>504</v>
       </c>
-      <c r="I16" s="6"/>
+      <c r="I16" s="7"/>
     </row>
-    <row r="17" customFormat="1" ht="16.5" spans="1:9">
+    <row r="17" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -11283,22 +11330,22 @@
       <c r="C17" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="29" t="s">
         <v>506</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="E17" s="29" t="s">
         <v>507</v>
       </c>
       <c r="F17" s="1"/>
-      <c r="G17">
+      <c r="G17" s="5">
         <v>121813166897471</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="I17" s="6"/>
+      <c r="I17" s="7"/>
     </row>
-    <row r="18" customFormat="1" ht="16.5" spans="1:9">
+    <row r="18" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -11308,22 +11355,22 @@
       <c r="C18" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="29" t="s">
         <v>510</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="E18" s="29" t="s">
         <v>511</v>
       </c>
       <c r="F18" s="1"/>
-      <c r="G18">
+      <c r="G18" s="5">
         <v>107669574278873</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="I18" s="6"/>
+      <c r="I18" s="7"/>
     </row>
-    <row r="19" customFormat="1" ht="16.5" spans="1:9">
+    <row r="19" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -11333,22 +11380,22 @@
       <c r="C19" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="29" t="s">
         <v>514</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="E19" s="29" t="s">
         <v>515</v>
       </c>
       <c r="F19" s="1"/>
-      <c r="G19">
+      <c r="G19" s="5">
         <v>98723580431394</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="6" t="s">
         <v>516</v>
       </c>
-      <c r="I19" s="6"/>
+      <c r="I19" s="7"/>
     </row>
-    <row r="20" customFormat="1" ht="16.5" spans="1:9">
+    <row r="20" s="5" customFormat="1" ht="16.5" spans="1:9">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -11358,20 +11405,20 @@
       <c r="C20" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="29" t="s">
         <v>518</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="29" t="s">
         <v>519</v>
       </c>
       <c r="F20" s="1"/>
-      <c r="G20">
+      <c r="G20" s="5">
         <v>126241505230536</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="6" t="s">
         <v>520</v>
       </c>
-      <c r="I20" s="6"/>
+      <c r="I20" s="7"/>
     </row>
     <row r="21" ht="16.5" spans="1:9">
       <c r="A21" s="1">
@@ -11383,20 +11430,20 @@
       <c r="C21" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="29" t="s">
         <v>522</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="29" t="s">
         <v>523</v>
       </c>
       <c r="F21" s="1"/>
-      <c r="G21">
+      <c r="G21" s="5">
         <v>78092021290844</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="6" t="s">
         <v>524</v>
       </c>
-      <c r="I21" s="6"/>
+      <c r="I21" s="7"/>
     </row>
     <row r="22" ht="16.5" spans="1:9">
       <c r="A22" s="1">
@@ -11408,20 +11455,20 @@
       <c r="C22" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="29" t="s">
         <v>526</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="29" t="s">
         <v>527</v>
       </c>
       <c r="F22" s="1"/>
-      <c r="G22">
+      <c r="G22" s="5">
         <v>138731887343821</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="I22" s="6"/>
+      <c r="I22" s="7"/>
     </row>
     <row r="23" ht="16.5" spans="1:9">
       <c r="A23" s="1">
@@ -11433,20 +11480,158 @@
       <c r="C23" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="29" t="s">
         <v>530</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="29" t="s">
         <v>531</v>
       </c>
       <c r="F23" s="1"/>
-      <c r="G23">
+      <c r="G23" s="5">
         <v>113127149166000</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="I23" s="6"/>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" ht="16.5" spans="1:9">
+      <c r="A24" s="1">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>121</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>533</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>122188029381990</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:9">
+      <c r="A25" s="1">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>122</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="D25" s="5">
+        <v>2</v>
+      </c>
+      <c r="E25" s="5">
+        <v>2</v>
+      </c>
+      <c r="G25">
+        <v>111918297845046</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:9">
+      <c r="A26" s="1">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>123</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="D26" s="5">
+        <v>3</v>
+      </c>
+      <c r="E26" s="5">
+        <v>3</v>
+      </c>
+      <c r="G26">
+        <v>131796875082030</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:9">
+      <c r="A27" s="1">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>124</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="D27" s="5">
+        <v>4</v>
+      </c>
+      <c r="E27" s="5">
+        <v>4</v>
+      </c>
+      <c r="G27">
+        <v>135291300946209</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:9">
+      <c r="A28" s="1">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>125</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="D28" s="5">
+        <v>5</v>
+      </c>
+      <c r="E28" s="5">
+        <v>5</v>
+      </c>
+      <c r="G28">
+        <v>135059340240171</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:9">
+      <c r="A29" s="1">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>126</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="D29" s="5">
+        <v>6</v>
+      </c>
+      <c r="E29" s="5">
+        <v>6</v>
+      </c>
+      <c r="G29">
+        <v>138711849822666</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>544</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11493,10 +11678,10 @@
         <v>56</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11504,7 +11689,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>146</v>
@@ -11565,7 +11750,7 @@
         <v>101</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -11581,7 +11766,7 @@
         <v>88151748923443</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11592,7 +11777,7 @@
         <v>102</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="D5" s="1">
         <v>2</v>
@@ -11608,7 +11793,7 @@
         <v>130646097070957</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11619,7 +11804,7 @@
         <v>103</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="D6" s="1">
         <v>3</v>
@@ -11635,7 +11820,7 @@
         <v>86124893237823</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11646,7 +11831,7 @@
         <v>104</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="D7" s="1">
         <v>4</v>
@@ -11662,7 +11847,7 @@
         <v>117901666423784</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11673,7 +11858,7 @@
         <v>105</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="D8" s="1">
         <v>5</v>
@@ -11689,7 +11874,7 @@
         <v>133168932011408</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11700,7 +11885,7 @@
         <v>106</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D9" s="1">
         <v>6</v>
@@ -11716,7 +11901,7 @@
         <v>71089861609803</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11727,7 +11912,7 @@
         <v>107</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="D10" s="1">
         <v>7</v>
@@ -11743,7 +11928,7 @@
         <v>71622349623563</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11754,7 +11939,7 @@
         <v>108</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="D11" s="1">
         <v>8</v>
@@ -11770,7 +11955,7 @@
         <v>126547452796781</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11781,7 +11966,7 @@
         <v>109</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="D12" s="1">
         <v>9</v>
@@ -11796,7 +11981,7 @@
         <v>111693433253936</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:1024 1025:16384">
@@ -11807,7 +11992,7 @@
         <v>110</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="D13" s="1">
         <v>10</v>
@@ -11823,7 +12008,7 @@
         <v>126721700266409</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -28209,7 +28394,7 @@
         <v>111</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="D14" s="1">
         <v>11</v>
@@ -28225,7 +28410,7 @@
         <v>92711027530571</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -44611,7 +44796,7 @@
         <v>112</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="D15" s="1">
         <v>12</v>
@@ -44627,7 +44812,7 @@
         <v>140129159429440</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -61013,7 +61198,7 @@
         <v>113</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="D16" s="1">
         <v>13</v>
@@ -61029,7 +61214,7 @@
         <v>125903398380406</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:9">
@@ -61040,7 +61225,7 @@
         <v>114</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="D17" s="1">
         <v>14</v>
@@ -61056,7 +61241,7 @@
         <v>110859814667398</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:9">
@@ -61067,7 +61252,7 @@
         <v>115</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="D18" s="1">
         <v>15</v>
@@ -61083,7 +61268,7 @@
         <v>71778195177377</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:9">
@@ -61094,7 +61279,7 @@
         <v>116</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="D19" s="1">
         <v>16</v>
@@ -61110,7 +61295,7 @@
         <v>82261970902739</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:9">
@@ -61121,7 +61306,7 @@
         <v>117</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="D20" s="1">
         <v>17</v>
@@ -61137,7 +61322,7 @@
         <v>84969691879555</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:9">
@@ -61148,7 +61333,7 @@
         <v>118</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="D21" s="1">
         <v>18</v>
@@ -61163,7 +61348,7 @@
         <v>135431835703650</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:9">
@@ -61174,7 +61359,7 @@
         <v>119</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="D22" s="1">
         <v>19</v>
@@ -61189,7 +61374,7 @@
         <v>84363202598659</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:9">
@@ -61200,7 +61385,7 @@
         <v>120</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="D23" s="1">
         <v>20</v>
@@ -61215,7 +61400,7 @@
         <v>140502552004582</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:9">
@@ -61226,7 +61411,7 @@
         <v>121</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="D24" s="1">
         <v>21</v>
@@ -61241,7 +61426,7 @@
         <v>110544423490869</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:9">
@@ -61252,7 +61437,7 @@
         <v>122</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="D25" s="1">
         <v>22</v>
@@ -61267,7 +61452,7 @@
         <v>88436670368181</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:9">
@@ -61278,7 +61463,7 @@
         <v>123</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="D26" s="1">
         <v>23</v>
@@ -61293,7 +61478,7 @@
         <v>101523513603326</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:9">
@@ -61304,7 +61489,7 @@
         <v>124</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="D27" s="1">
         <v>24</v>
@@ -61319,7 +61504,7 @@
         <v>117557339704806</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:9">
@@ -61330,7 +61515,7 @@
         <v>125</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="D28" s="1">
         <v>25</v>
@@ -61345,7 +61530,7 @@
         <v>94281665600637</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -15,12 +15,11 @@
     <s:sheet name="CommonConfig" sheetId="2" state="visible" r:id="rId2"/>
     <s:sheet name="TrainingFieldData" sheetId="3" state="visible" r:id="rId3"/>
     <s:sheet name="AreaConfig" sheetId="4" state="visible" r:id="rId4"/>
-    <s:sheet name="AreaRefreshData" sheetId="5" state="visible" r:id="rId5"/>
-    <s:sheet name="ItemData" sheetId="6" state="visible" r:id="rId6"/>
-    <s:sheet name="TrainingRateConfig" sheetId="7" state="visible" r:id="rId7"/>
-    <s:sheet name="ToolConfig" sheetId="8" state="visible" r:id="rId8"/>
-    <s:sheet name="AuraConfig" sheetId="9" state="visible" r:id="rId9"/>
-    <s:sheet name="LevelConfig" sheetId="10" state="visible" r:id="rId10"/>
+    <s:sheet name="ItemData" sheetId="5" state="visible" r:id="rId5"/>
+    <s:sheet name="TrainingRateConfig" sheetId="6" state="visible" r:id="rId6"/>
+    <s:sheet name="ToolConfig" sheetId="7" state="visible" r:id="rId7"/>
+    <s:sheet name="AuraConfig" sheetId="8" state="visible" r:id="rId8"/>
+    <s:sheet name="LevelConfig" sheetId="9" state="visible" r:id="rId9"/>
   </s:sheets>
   <s:definedNames>
     <s:definedName name="CurveBaseExp">_xlfn.LAMBDA(_xlpm.Multiplier,_xlpm.x,_xlpm.p,_xlpm.Multiplier*POWER(_xlpm.p,_xlpm.x))</s:definedName>
@@ -1480,952 +1479,6 @@
 </s:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:sheetPr>
-    <s:outlinePr summaryBelow="1" summaryRight="1"/>
-    <s:pageSetUpPr/>
-  </s:sheetPr>
-  <s:dimension ref="A1:E55"/>
-  <s:sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
-  <s:cols>
-    <s:col width="19.3611111111111" customWidth="1" style="28" min="1" max="1"/>
-    <s:col width="18.9814814814815" customWidth="1" style="28" min="2" max="2"/>
-    <s:col width="42.9814814814815" customWidth="1" style="28" min="3" max="3"/>
-  </s:cols>
-  <s:sheetData>
-    <s:row r="1" ht="15.6" customHeight="1" s="28">
-      <s:c r="A1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>关卡Id</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>草血量</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C1" s="1" t="inlineStr">
-        <s:is>
-          <s:t>颜色</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="2" ht="15.6" customHeight="1" s="28">
-      <s:c r="A2" s="1" t="inlineStr">
-        <s:is>
-          <s:t>LevelKey</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B2" s="1" t="inlineStr">
-        <s:is>
-          <s:t>GrassClumpsHP</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C2" s="1" t="inlineStr">
-        <s:is>
-          <s:t>Texture</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="3" ht="15.6" customHeight="1" s="28">
-      <s:c r="A3" s="1" t="inlineStr">
-        <s:is>
-          <s:t>string</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B3" s="1" t="inlineStr">
-        <s:is>
-          <s:t>number</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C3" s="1" t="inlineStr">
-        <s:is>
-          <s:t>string</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="4">
-      <s:c r="A4" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_1</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B4" s="2" t="n">
-        <s:v>29</s:v>
-      </s:c>
-      <s:c r="C4" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground1.png</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D4" s="2" t="n"/>
-      <s:c r="E4" s="2" t="n"/>
-    </s:row>
-    <s:row r="5">
-      <s:c r="A5" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_2</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B5" s="2" t="n">
-        <s:v>122</s:v>
-      </s:c>
-      <s:c r="C5" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground2.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="6">
-      <s:c r="A6" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_3</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B6" s="2" t="n">
-        <s:v>520</s:v>
-      </s:c>
-      <s:c r="C6" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground3.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="7">
-      <s:c r="A7" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_4</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B7" s="2" t="n">
-        <s:v>2176</s:v>
-      </s:c>
-      <s:c r="C7" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground4.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="8">
-      <s:c r="A8" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_5</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B8" s="2" t="n">
-        <s:v>9101</s:v>
-      </s:c>
-      <s:c r="C8" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground5.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="9">
-      <s:c r="A9" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_6</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B9" s="26" t="inlineStr">
-        <s:is>
-          <s:t>3.80e+4</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C9" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground6.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="10">
-      <s:c r="A10" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_7</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B10" s="26" t="inlineStr">
-        <s:is>
-          <s:t>1.59e+5</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C10" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground7.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="11">
-      <s:c r="A11" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_8</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B11" s="26" t="inlineStr">
-        <s:is>
-          <s:t>6.64e+5</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C11" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground8.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="12">
-      <s:c r="A12" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_9</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B12" s="26" t="inlineStr">
-        <s:is>
-          <s:t>2.77e+6</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C12" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground9.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="13">
-      <s:c r="A13" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_10</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B13" s="26" t="inlineStr">
-        <s:is>
-          <s:t>1.16e+7</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C13" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground10.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="14">
-      <s:c r="A14" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_11</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B14" s="26" t="inlineStr">
-        <s:is>
-          <s:t>4.84e+7</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C14" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground11.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="15">
-      <s:c r="A15" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_12</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B15" s="26" t="inlineStr">
-        <s:is>
-          <s:t>2.02e+8</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C15" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground12.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="16">
-      <s:c r="A16" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World1.Level_13</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B16" s="26" t="inlineStr">
-        <s:is>
-          <s:t>8.44e+8</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C16" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground13.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="17">
-      <s:c r="A17" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_14</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B17" s="26" t="inlineStr">
-        <s:is>
-          <s:t>3.53e+9</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C17" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground14.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="18">
-      <s:c r="A18" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_15</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B18" s="26" t="inlineStr">
-        <s:is>
-          <s:t>1.47e+10</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C18" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground15.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="19">
-      <s:c r="A19" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_16</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B19" s="26" t="inlineStr">
-        <s:is>
-          <s:t>6.15e+10</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C19" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground16.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="20">
-      <s:c r="A20" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_17</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B20" s="26" t="inlineStr">
-        <s:is>
-          <s:t>2.57e+11</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C20" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground17.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="21">
-      <s:c r="A21" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_18</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B21" s="26" t="inlineStr">
-        <s:is>
-          <s:t>1.07e+12</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C21" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground18.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="22">
-      <s:c r="A22" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_19</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B22" s="26" t="inlineStr">
-        <s:is>
-          <s:t>4.48e+12</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C22" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground19.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="23">
-      <s:c r="A23" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_20</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B23" s="26" t="inlineStr">
-        <s:is>
-          <s:t>1.87e+13</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C23" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground20.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="24">
-      <s:c r="A24" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_21</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B24" s="26" t="inlineStr">
-        <s:is>
-          <s:t>7.82e+13</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C24" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground21.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="25">
-      <s:c r="A25" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_22</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B25" s="26" t="inlineStr">
-        <s:is>
-          <s:t>3.27e+14</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C25" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground22.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="26">
-      <s:c r="A26" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_23</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B26" s="26" t="inlineStr">
-        <s:is>
-          <s:t>1.37e+15</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C26" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground23.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="27">
-      <s:c r="A27" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_24</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B27" s="26" t="inlineStr">
-        <s:is>
-          <s:t>5.70e+15</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C27" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground24.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="28">
-      <s:c r="A28" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_25</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B28" s="26" t="inlineStr">
-        <s:is>
-          <s:t>2.38e+16</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C28" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground25.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="29">
-      <s:c r="A29" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World2.Level_26</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B29" s="26" t="inlineStr">
-        <s:is>
-          <s:t>9.95e+16</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C29" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground26.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="30">
-      <s:c r="A30" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_27</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B30" s="26" t="inlineStr">
-        <s:is>
-          <s:t>4.16e+17</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C30" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground27.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="31">
-      <s:c r="A31" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_28</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B31" s="26" t="inlineStr">
-        <s:is>
-          <s:t>1.74e+18</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C31" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground28.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="32">
-      <s:c r="A32" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_29</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B32" s="26" t="inlineStr">
-        <s:is>
-          <s:t>7.25e+18</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C32" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground29.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="33">
-      <s:c r="A33" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_30</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B33" s="26" t="inlineStr">
-        <s:is>
-          <s:t>3.03e+19</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C33" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground30.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="34">
-      <s:c r="A34" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_31</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B34" s="26" t="inlineStr">
-        <s:is>
-          <s:t>1.27e+20</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C34" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground31.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="35">
-      <s:c r="A35" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_32</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B35" s="26" t="inlineStr">
-        <s:is>
-          <s:t>5.29e+20</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C35" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground32.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="36">
-      <s:c r="A36" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_33</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B36" s="26" t="inlineStr">
-        <s:is>
-          <s:t>2.21e+21</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C36" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground33.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="37">
-      <s:c r="A37" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_34</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B37" s="26" t="inlineStr">
-        <s:is>
-          <s:t>9.23e+21</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C37" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground34.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="38">
-      <s:c r="A38" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_35</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B38" s="26" t="inlineStr">
-        <s:is>
-          <s:t>3.85e+22</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C38" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground35.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="39">
-      <s:c r="A39" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_36</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B39" s="26" t="inlineStr">
-        <s:is>
-          <s:t>1.61e+23</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C39" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground36.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="40">
-      <s:c r="A40" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_37</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B40" s="26" t="inlineStr">
-        <s:is>
-          <s:t>6.73e+23</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C40" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground37.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="41">
-      <s:c r="A41" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_38</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B41" s="26" t="inlineStr">
-        <s:is>
-          <s:t>2.81e+24</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C41" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground38.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="42">
-      <s:c r="A42" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World3.Level_39</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B42" s="26" t="inlineStr">
-        <s:is>
-          <s:t>1.17e+25</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C42" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground39.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="43">
-      <s:c r="A43" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_40</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B43" s="27" t="inlineStr">
-        <s:is>
-          <s:t>4.90e+25</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C43" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground40.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="44">
-      <s:c r="A44" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_41</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B44" s="27" t="inlineStr">
-        <s:is>
-          <s:t>2.05e+26</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C44" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground41.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="45">
-      <s:c r="A45" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_42</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B45" s="27" t="inlineStr">
-        <s:is>
-          <s:t>8.55e+26</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C45" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground42.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="46">
-      <s:c r="A46" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_43</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B46" s="27" t="inlineStr">
-        <s:is>
-          <s:t>3.57e+27</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C46" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground43.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="47">
-      <s:c r="A47" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_44</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B47" s="27" t="inlineStr">
-        <s:is>
-          <s:t>1.49e+28</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C47" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground44.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="48">
-      <s:c r="A48" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_45</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B48" s="27" t="inlineStr">
-        <s:is>
-          <s:t>6.24e+28</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C48" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground45.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="49">
-      <s:c r="A49" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_46</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B49" s="27" t="inlineStr">
-        <s:is>
-          <s:t>2.60e+29</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C49" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground46.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="50">
-      <s:c r="A50" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_47</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B50" s="27" t="inlineStr">
-        <s:is>
-          <s:t>1.09e+30</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C50" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground47.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="51">
-      <s:c r="A51" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_48</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B51" s="27" t="inlineStr">
-        <s:is>
-          <s:t>4.54e+30</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C51" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground48.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="52">
-      <s:c r="A52" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_49</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B52" s="27" t="inlineStr">
-        <s:is>
-          <s:t>1.90e+31</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C52" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground49.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="53">
-      <s:c r="A53" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_50</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B53" s="27" t="inlineStr">
-        <s:is>
-          <s:t>7.93e+31</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C53" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground50.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="54">
-      <s:c r="A54" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_51</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B54" s="27" t="inlineStr">
-        <s:is>
-          <s:t>3.31e+32</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C54" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground51.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="55">
-      <s:c r="A55" s="2" t="inlineStr">
-        <s:is>
-          <s:t>World4.Level_52</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B55" s="27" t="inlineStr">
-        <s:is>
-          <s:t>1.38e+33</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C55" s="2" t="inlineStr">
-        <s:is>
-          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground52.png</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-  </s:sheetData>
-  <s:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</s:worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:sheetPr>
@@ -4196,1051 +3249,7 @@
     <s:outlinePr summaryBelow="1" summaryRight="1"/>
     <s:pageSetUpPr/>
   </s:sheetPr>
-  <s:dimension ref="A1:E58"/>
-  <s:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="27.6" outlineLevelCol="4"/>
-  <s:cols>
-    <s:col width="25.1759259259259" customWidth="1" style="9" min="1" max="1"/>
-    <s:col width="13.5740740740741" customWidth="1" style="9" min="2" max="2"/>
-    <s:col width="127.138888888889" customWidth="1" style="9" min="3" max="3"/>
-    <s:col width="49" customWidth="1" style="9" min="4" max="4"/>
-    <s:col width="92.962962962963" customWidth="1" style="10" min="5" max="5"/>
-    <s:col width="9" customWidth="1" style="9" min="6" max="16384"/>
-  </s:cols>
-  <s:sheetData>
-    <s:row r="1">
-      <s:c r="A1" s="11" t="inlineStr">
-        <s:is>
-          <s:t>索引</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B1" s="11" t="inlineStr">
-        <s:is>
-          <s:t>组ID</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C1" s="11" t="inlineStr">
-        <s:is>
-          <s:t>刷新ID(根据类型填写)</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D1" s="11" t="inlineStr">
-        <s:is>
-          <s:t>刷新对象类型</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="E1" s="10" t="inlineStr">
-        <s:is>
-          <s:t>含义</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="2">
-      <s:c r="A2" s="11" t="inlineStr">
-        <s:is>
-          <s:t>Index</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B2" s="11" t="inlineStr">
-        <s:is>
-          <s:t>AreaId</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C2" s="11" t="inlineStr">
-        <s:is>
-          <s:t>RewardPool</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D2" s="11" t="inlineStr">
-        <s:is>
-          <s:t>ObjectType</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="3">
-      <s:c r="A3" s="11" t="inlineStr">
-        <s:is>
-          <s:t>number</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="B3" s="11" t="inlineStr">
-        <s:is>
-          <s:t>number</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C3" s="11" t="inlineStr">
-        <s:is>
-          <s:t>vec2_array</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D3" s="11" t="inlineStr">
-        <s:is>
-          <s:t>string</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="4">
-      <s:c r="A4" s="11" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="B4" s="11" t="n">
-        <s:v>1</s:v>
-      </s:c>
-      <s:c r="C4" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{1, 35}, {2, 30}, {3, 20}, {4, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D4" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="5">
-      <s:c r="A5" s="11" t="n">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="B5" s="11" t="n">
-        <s:v>2</s:v>
-      </s:c>
-      <s:c r="C5" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{5, 35}, {6, 30}, {7, 20}, {8, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D5" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="6">
-      <s:c r="A6" s="11" t="n">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="B6" s="11" t="n">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="C6" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{9, 35}, {10, 30}, {11, 20}, {12, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D6" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="7">
-      <s:c r="A7" s="11" t="n">
-        <s:v>4</s:v>
-      </s:c>
-      <s:c r="B7" s="11" t="n">
-        <s:v>4</s:v>
-      </s:c>
-      <s:c r="C7" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{13, 35}, {14, 30}, {15, 20}, {16, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D7" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="8">
-      <s:c r="A8" s="11" t="n">
-        <s:v>5</s:v>
-      </s:c>
-      <s:c r="B8" s="11" t="n">
-        <s:v>5</s:v>
-      </s:c>
-      <s:c r="C8" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{17, 35}, {18, 30}, {19, 20}, {20, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D8" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="9">
-      <s:c r="A9" s="11" t="n">
-        <s:v>6</s:v>
-      </s:c>
-      <s:c r="B9" s="11" t="n">
-        <s:v>6</s:v>
-      </s:c>
-      <s:c r="C9" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{21, 35}, {22, 30}, {23, 20}, {24, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D9" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="10">
-      <s:c r="A10" s="11" t="n">
-        <s:v>7</s:v>
-      </s:c>
-      <s:c r="B10" s="11" t="n">
-        <s:v>7</s:v>
-      </s:c>
-      <s:c r="C10" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{25, 35}, {26, 30}, {27, 20}, {28, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D10" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="11">
-      <s:c r="A11" s="11" t="n">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="B11" s="11" t="n">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="C11" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{29, 35}, {30, 30}, {31, 20}, {32, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D11" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="12">
-      <s:c r="A12" s="11" t="n">
-        <s:v>9</s:v>
-      </s:c>
-      <s:c r="B12" s="11" t="n">
-        <s:v>9</s:v>
-      </s:c>
-      <s:c r="C12" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{33, 35}, {34, 30}, {35, 20}, {36, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D12" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="13">
-      <s:c r="A13" s="11" t="n">
-        <s:v>10</s:v>
-      </s:c>
-      <s:c r="B13" s="11" t="n">
-        <s:v>10</s:v>
-      </s:c>
-      <s:c r="C13" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{37, 35}, {38, 30}, {39, 20}, {40, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D13" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="14">
-      <s:c r="A14" s="11" t="n">
-        <s:v>11</s:v>
-      </s:c>
-      <s:c r="B14" s="11" t="n">
-        <s:v>11</s:v>
-      </s:c>
-      <s:c r="C14" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{41, 35}, {42, 30}, {43, 20}, {44, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D14" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="15">
-      <s:c r="A15" s="11" t="n">
-        <s:v>12</s:v>
-      </s:c>
-      <s:c r="B15" s="11" t="n">
-        <s:v>12</s:v>
-      </s:c>
-      <s:c r="C15" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{45, 35}, {46, 30}, {47, 20}, {48, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D15" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="16">
-      <s:c r="A16" s="11" t="n">
-        <s:v>13</s:v>
-      </s:c>
-      <s:c r="B16" s="11" t="n">
-        <s:v>13</s:v>
-      </s:c>
-      <s:c r="C16" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{49, 35}, {50, 30}, {51, 20}, {52, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D16" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="17">
-      <s:c r="A17" s="11" t="n">
-        <s:v>14</s:v>
-      </s:c>
-      <s:c r="B17" s="11" t="n">
-        <s:v>14</s:v>
-      </s:c>
-      <s:c r="C17" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{53, 35}, {54, 30}, {55, 20}, {56, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D17" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="18">
-      <s:c r="A18" s="11" t="n">
-        <s:v>15</s:v>
-      </s:c>
-      <s:c r="B18" s="11" t="n">
-        <s:v>15</s:v>
-      </s:c>
-      <s:c r="C18" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{57, 35}, {58, 30}, {59, 20}, {60, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D18" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="19">
-      <s:c r="A19" s="11" t="n">
-        <s:v>16</s:v>
-      </s:c>
-      <s:c r="B19" s="11" t="n">
-        <s:v>16</s:v>
-      </s:c>
-      <s:c r="C19" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{61, 35}, {62, 30}, {63, 20}, {64, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D19" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="20">
-      <s:c r="A20" s="11" t="n">
-        <s:v>17</s:v>
-      </s:c>
-      <s:c r="B20" s="11" t="n">
-        <s:v>17</s:v>
-      </s:c>
-      <s:c r="C20" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{65, 35}, {66, 30}, {67, 20}, {68, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D20" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="21">
-      <s:c r="A21" s="11" t="n">
-        <s:v>18</s:v>
-      </s:c>
-      <s:c r="B21" s="11" t="n">
-        <s:v>18</s:v>
-      </s:c>
-      <s:c r="C21" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{69, 35}, {70, 30}, {71, 20}, {72, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D21" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="22">
-      <s:c r="A22" s="11" t="n">
-        <s:v>19</s:v>
-      </s:c>
-      <s:c r="B22" s="11" t="n">
-        <s:v>19</s:v>
-      </s:c>
-      <s:c r="C22" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{73, 35}, {74, 30}, {75, 20}, {76, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D22" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="23">
-      <s:c r="A23" s="11" t="n">
-        <s:v>20</s:v>
-      </s:c>
-      <s:c r="B23" s="11" t="n">
-        <s:v>20</s:v>
-      </s:c>
-      <s:c r="C23" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{77, 35}, {78, 30}, {79, 20}, {80, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D23" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="24">
-      <s:c r="A24" s="11" t="n">
-        <s:v>21</s:v>
-      </s:c>
-      <s:c r="B24" s="11" t="n">
-        <s:v>21</s:v>
-      </s:c>
-      <s:c r="C24" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{81, 35}, {82, 30}, {83, 20}, {84, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D24" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="25">
-      <s:c r="A25" s="11" t="n">
-        <s:v>22</s:v>
-      </s:c>
-      <s:c r="B25" s="11" t="n">
-        <s:v>22</s:v>
-      </s:c>
-      <s:c r="C25" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{85, 35}, {86, 30}, {87, 20}, {88, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D25" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="26">
-      <s:c r="A26" s="11" t="n">
-        <s:v>23</s:v>
-      </s:c>
-      <s:c r="B26" s="11" t="n">
-        <s:v>23</s:v>
-      </s:c>
-      <s:c r="C26" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{89, 35}, {90, 30}, {91, 20}, {92, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D26" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="27">
-      <s:c r="A27" s="11" t="n">
-        <s:v>24</s:v>
-      </s:c>
-      <s:c r="B27" s="11" t="n">
-        <s:v>24</s:v>
-      </s:c>
-      <s:c r="C27" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{93, 35}, {94, 30}, {95, 20}, {96, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D27" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="28">
-      <s:c r="A28" s="11" t="n">
-        <s:v>25</s:v>
-      </s:c>
-      <s:c r="B28" s="11" t="n">
-        <s:v>25</s:v>
-      </s:c>
-      <s:c r="C28" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{97, 35}, {98, 30}, {99, 20}, {100, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D28" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="29">
-      <s:c r="A29" s="11" t="n">
-        <s:v>26</s:v>
-      </s:c>
-      <s:c r="B29" s="11" t="n">
-        <s:v>26</s:v>
-      </s:c>
-      <s:c r="C29" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{101, 35}, {102, 30}, {103, 20}, {104, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D29" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="30">
-      <s:c r="A30" s="11" t="n">
-        <s:v>27</s:v>
-      </s:c>
-      <s:c r="B30" s="11" t="n">
-        <s:v>27</s:v>
-      </s:c>
-      <s:c r="C30" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{105, 35}, {106, 30}, {107, 20}, {108, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D30" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="31">
-      <s:c r="A31" s="11" t="n">
-        <s:v>28</s:v>
-      </s:c>
-      <s:c r="B31" s="11" t="n">
-        <s:v>28</s:v>
-      </s:c>
-      <s:c r="C31" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{109, 35}, {110, 30}, {111, 20}, {112, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D31" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="32">
-      <s:c r="A32" s="11" t="n">
-        <s:v>29</s:v>
-      </s:c>
-      <s:c r="B32" s="11" t="n">
-        <s:v>29</s:v>
-      </s:c>
-      <s:c r="C32" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{113, 35}, {114, 30}, {115, 20}, {116, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D32" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="33">
-      <s:c r="A33" s="11" t="n">
-        <s:v>30</s:v>
-      </s:c>
-      <s:c r="B33" s="11" t="n">
-        <s:v>30</s:v>
-      </s:c>
-      <s:c r="C33" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{117, 35}, {118, 30}, {119, 20}, {120, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D33" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="34">
-      <s:c r="A34" s="11" t="n">
-        <s:v>31</s:v>
-      </s:c>
-      <s:c r="B34" s="11" t="n">
-        <s:v>31</s:v>
-      </s:c>
-      <s:c r="C34" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{121, 35}, {122, 30}, {123, 20}, {124, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D34" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="35">
-      <s:c r="A35" s="11" t="n">
-        <s:v>32</s:v>
-      </s:c>
-      <s:c r="B35" s="11" t="n">
-        <s:v>32</s:v>
-      </s:c>
-      <s:c r="C35" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{125, 35}, {126, 30}, {127, 20}, {128, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D35" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="36">
-      <s:c r="A36" s="11" t="n">
-        <s:v>33</s:v>
-      </s:c>
-      <s:c r="B36" s="11" t="n">
-        <s:v>33</s:v>
-      </s:c>
-      <s:c r="C36" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{129, 35}, {130, 30}, {131, 20}, {132, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D36" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="37">
-      <s:c r="A37" s="11" t="n">
-        <s:v>34</s:v>
-      </s:c>
-      <s:c r="B37" s="11" t="n">
-        <s:v>34</s:v>
-      </s:c>
-      <s:c r="C37" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{133, 35}, {134, 30}, {135, 20}, {136, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D37" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="38">
-      <s:c r="A38" s="11" t="n">
-        <s:v>35</s:v>
-      </s:c>
-      <s:c r="B38" s="11" t="n">
-        <s:v>35</s:v>
-      </s:c>
-      <s:c r="C38" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{137, 35}, {138, 30}, {139, 20}, {140, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D38" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="39">
-      <s:c r="A39" s="11" t="n">
-        <s:v>36</s:v>
-      </s:c>
-      <s:c r="B39" s="11" t="n">
-        <s:v>36</s:v>
-      </s:c>
-      <s:c r="C39" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{141, 35}, {142, 30}, {143, 20}, {144, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D39" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="40">
-      <s:c r="A40" s="11" t="n">
-        <s:v>37</s:v>
-      </s:c>
-      <s:c r="B40" s="11" t="n">
-        <s:v>37</s:v>
-      </s:c>
-      <s:c r="C40" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{145, 35}, {146, 30}, {147, 20}, {148, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D40" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="41">
-      <s:c r="A41" s="11" t="n">
-        <s:v>38</s:v>
-      </s:c>
-      <s:c r="B41" s="11" t="n">
-        <s:v>38</s:v>
-      </s:c>
-      <s:c r="C41" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{149, 35}, {150, 30}, {151, 20}, {152, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D41" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="42">
-      <s:c r="A42" s="11" t="n">
-        <s:v>39</s:v>
-      </s:c>
-      <s:c r="B42" s="11" t="n">
-        <s:v>39</s:v>
-      </s:c>
-      <s:c r="C42" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{153, 35}, {154, 30}, {155, 20}, {156, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D42" s="11" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="43">
-      <s:c r="A43" s="12" t="n">
-        <s:v>40</s:v>
-      </s:c>
-      <s:c r="B43" s="12" t="n">
-        <s:v>40</s:v>
-      </s:c>
-      <s:c r="C43" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{157, 35}, {158, 30}, {159, 20}, {160, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D43" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="44">
-      <s:c r="A44" s="12" t="n">
-        <s:v>41</s:v>
-      </s:c>
-      <s:c r="B44" s="12" t="n">
-        <s:v>41</s:v>
-      </s:c>
-      <s:c r="C44" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{161, 35}, {162, 30}, {163, 20}, {164, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D44" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="45">
-      <s:c r="A45" s="12" t="n">
-        <s:v>42</s:v>
-      </s:c>
-      <s:c r="B45" s="12" t="n">
-        <s:v>42</s:v>
-      </s:c>
-      <s:c r="C45" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{165, 35}, {166, 30}, {167, 20}, {168, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D45" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="46">
-      <s:c r="A46" s="12" t="n">
-        <s:v>43</s:v>
-      </s:c>
-      <s:c r="B46" s="12" t="n">
-        <s:v>43</s:v>
-      </s:c>
-      <s:c r="C46" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{169, 35}, {170, 30}, {171, 20}, {172, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D46" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="47">
-      <s:c r="A47" s="12" t="n">
-        <s:v>44</s:v>
-      </s:c>
-      <s:c r="B47" s="12" t="n">
-        <s:v>44</s:v>
-      </s:c>
-      <s:c r="C47" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{173, 35}, {174, 30}, {175, 20}, {176, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D47" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="48">
-      <s:c r="A48" s="12" t="n">
-        <s:v>45</s:v>
-      </s:c>
-      <s:c r="B48" s="12" t="n">
-        <s:v>45</s:v>
-      </s:c>
-      <s:c r="C48" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{177, 35}, {178, 30}, {179, 20}, {180, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D48" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="49">
-      <s:c r="A49" s="12" t="n">
-        <s:v>46</s:v>
-      </s:c>
-      <s:c r="B49" s="12" t="n">
-        <s:v>46</s:v>
-      </s:c>
-      <s:c r="C49" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{181, 35}, {182, 30}, {183, 20}, {184, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D49" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="50">
-      <s:c r="A50" s="12" t="n">
-        <s:v>47</s:v>
-      </s:c>
-      <s:c r="B50" s="12" t="n">
-        <s:v>47</s:v>
-      </s:c>
-      <s:c r="C50" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{185, 35}, {186, 30}, {187, 20}, {188, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D50" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="51">
-      <s:c r="A51" s="12" t="n">
-        <s:v>48</s:v>
-      </s:c>
-      <s:c r="B51" s="12" t="n">
-        <s:v>48</s:v>
-      </s:c>
-      <s:c r="C51" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{189, 35}, {190, 30}, {191, 20}, {192, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D51" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="52">
-      <s:c r="A52" s="12" t="n">
-        <s:v>49</s:v>
-      </s:c>
-      <s:c r="B52" s="12" t="n">
-        <s:v>49</s:v>
-      </s:c>
-      <s:c r="C52" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{193, 35}, {194, 30}, {195, 20}, {196, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D52" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="53">
-      <s:c r="A53" s="12" t="n">
-        <s:v>50</s:v>
-      </s:c>
-      <s:c r="B53" s="12" t="n">
-        <s:v>50</s:v>
-      </s:c>
-      <s:c r="C53" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{197, 35}, {198, 30}, {199, 20}, {200, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D53" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="54">
-      <s:c r="A54" s="12" t="n">
-        <s:v>51</s:v>
-      </s:c>
-      <s:c r="B54" s="12" t="n">
-        <s:v>51</s:v>
-      </s:c>
-      <s:c r="C54" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{201, 35}, {202, 30}, {203, 20}, {204, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D54" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="55">
-      <s:c r="A55" s="12" t="n">
-        <s:v>52</s:v>
-      </s:c>
-      <s:c r="B55" s="12" t="n">
-        <s:v>52</s:v>
-      </s:c>
-      <s:c r="C55" s="12" t="inlineStr">
-        <s:is>
-          <s:t>{205, 35}, {206, 30}, {207, 20}, {208, 15},</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D55" s="12" t="inlineStr">
-        <s:is>
-          <s:t>SItemObjectClass</s:t>
-        </s:is>
-      </s:c>
-    </s:row>
-    <s:row r="56">
-      <s:c r="A56" s="12" t="n"/>
-      <s:c r="B56" s="12" t="n"/>
-      <s:c r="C56" s="12" t="n"/>
-      <s:c r="D56" s="12" t="n"/>
-    </s:row>
-    <s:row r="57">
-      <s:c r="A57" s="12" t="n"/>
-      <s:c r="B57" s="12" t="n"/>
-      <s:c r="C57" s="12" t="n"/>
-      <s:c r="D57" s="12" t="n"/>
-    </s:row>
-    <s:row r="58">
-      <s:c r="C58" s="12" t="n"/>
-    </s:row>
-  </s:sheetData>
-  <s:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</s:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:sheetPr>
-    <s:outlinePr summaryBelow="1" summaryRight="1"/>
-    <s:pageSetUpPr/>
-  </s:sheetPr>
-  <s:dimension ref="A1:L151"/>
+  <s:dimension ref="A1:K151"/>
   <s:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <s:cols>
     <s:col width="18" customWidth="1" style="2" min="2" max="2"/>
@@ -5270,25 +3279,20 @@
       </s:c>
       <s:c r="D1" s="1" t="inlineStr">
         <s:is>
-          <s:t>价格</s:t>
+          <s:t>道具品质</s:t>
         </s:is>
       </s:c>
       <s:c r="E1" s="1" t="inlineStr">
         <s:is>
-          <s:t>道具品质</s:t>
+          <s:t>图标ID</s:t>
         </s:is>
       </s:c>
       <s:c r="F1" s="1" t="inlineStr">
         <s:is>
-          <s:t>图标ID</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G1" s="1" t="inlineStr">
-        <s:is>
           <s:t>模型ID</s:t>
         </s:is>
       </s:c>
-      <s:c r="H1" s="2" t="inlineStr">
+      <s:c r="G1" s="2" t="inlineStr">
         <s:is>
           <s:t>模型类型</s:t>
         </s:is>
@@ -5312,25 +3316,20 @@
       </s:c>
       <s:c r="D2" s="1" t="inlineStr">
         <s:is>
-          <s:t>Pirce</s:t>
+          <s:t>Quality</s:t>
         </s:is>
       </s:c>
       <s:c r="E2" s="1" t="inlineStr">
         <s:is>
-          <s:t>Quality</s:t>
+          <s:t>IconId</s:t>
         </s:is>
       </s:c>
       <s:c r="F2" s="1" t="inlineStr">
         <s:is>
-          <s:t>IconId</s:t>
+          <s:t>DisplayModelId</s:t>
         </s:is>
       </s:c>
       <s:c r="G2" s="1" t="inlineStr">
-        <s:is>
-          <s:t>DisplayModelId</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="H2" s="1" t="inlineStr">
         <s:is>
           <s:t>ModelType</s:t>
         </s:is>
@@ -5359,20 +3358,15 @@
       </s:c>
       <s:c r="E3" s="1" t="inlineStr">
         <s:is>
-          <s:t>number</s:t>
+          <s:t>string</s:t>
         </s:is>
       </s:c>
       <s:c r="F3" s="1" t="inlineStr">
         <s:is>
-          <s:t>string</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="G3" s="1" t="inlineStr">
-        <s:is>
           <s:t>string_option</s:t>
         </s:is>
       </s:c>
-      <s:c r="H3" s="2" t="inlineStr">
+      <s:c r="G3" s="2" t="inlineStr">
         <s:is>
           <s:t>string</s:t>
         </s:is>
@@ -5390,22 +3384,19 @@
           <s:t>打火机</s:t>
         </s:is>
       </s:c>
-      <s:c r="D4" s="1" t="n">
-        <s:v>3</s:v>
-      </s:c>
-      <s:c r="E4" s="1">
+      <s:c r="D4" s="1">
         <s:f>CEILING(A4/4,1)</s:f>
         <s:v>1</s:v>
       </s:c>
-      <s:c r="F4" s="4" t="n">
+      <s:c r="E4" s="4" t="n">
         <s:v>113244405937302</s:v>
       </s:c>
-      <s:c r="G4" s="5" t="inlineStr">
+      <s:c r="F4" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_001_Nail</s:t>
         </s:is>
       </s:c>
-      <s:c r="H4" s="2" t="inlineStr">
+      <s:c r="G4" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -5423,28 +3414,25 @@
           <s:t>矿泉水</s:t>
         </s:is>
       </s:c>
-      <s:c r="D5" s="1" t="n">
-        <s:v>4</s:v>
-      </s:c>
-      <s:c r="E5" s="1">
+      <s:c r="D5" s="1">
         <s:f>CEILING(A5/4,1)</s:f>
         <s:v>1</s:v>
       </s:c>
-      <s:c r="F5" s="4" t="n">
+      <s:c r="E5" s="4" t="n">
         <s:v>105711056874756</s:v>
       </s:c>
-      <s:c r="G5" s="5" t="inlineStr">
+      <s:c r="F5" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_002_Pill</s:t>
         </s:is>
       </s:c>
-      <s:c r="H5" s="2" t="inlineStr">
+      <s:c r="G5" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H5" s="3" t="n"/>
       <s:c r="I5" s="3" t="n"/>
-      <s:c r="J5" s="3" t="n"/>
     </s:row>
     <s:row r="6" ht="15.6" customHeight="1" s="28">
       <s:c r="A6" s="1" t="n">
@@ -5458,28 +3446,25 @@
           <s:t>纯净水</s:t>
         </s:is>
       </s:c>
-      <s:c r="D6" s="1" t="n">
-        <s:v>6</s:v>
-      </s:c>
-      <s:c r="E6" s="1">
+      <s:c r="D6" s="1">
         <s:f>CEILING(A6/4,1)</s:f>
         <s:v>1</s:v>
       </s:c>
-      <s:c r="F6" s="4" t="n">
+      <s:c r="E6" s="4" t="n">
         <s:v>82693303214454</s:v>
       </s:c>
-      <s:c r="G6" s="5" t="inlineStr">
+      <s:c r="F6" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_003_Capsule</s:t>
         </s:is>
       </s:c>
-      <s:c r="H6" s="2" t="inlineStr">
+      <s:c r="G6" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H6" s="3" t="n"/>
       <s:c r="I6" s="3" t="n"/>
-      <s:c r="J6" s="3" t="n"/>
     </s:row>
     <s:row r="7" ht="15.6" customHeight="1" s="28">
       <s:c r="A7" s="1" t="n">
@@ -5493,28 +3478,25 @@
           <s:t>苏打水</s:t>
         </s:is>
       </s:c>
-      <s:c r="D7" s="1" t="n">
-        <s:v>8</s:v>
-      </s:c>
-      <s:c r="E7" s="1">
+      <s:c r="D7" s="1">
         <s:f>CEILING(A7/4,1)</s:f>
         <s:v>1</s:v>
       </s:c>
-      <s:c r="F7" s="4" t="n">
+      <s:c r="E7" s="4" t="n">
         <s:v>102504658102706</s:v>
       </s:c>
-      <s:c r="G7" s="5" t="inlineStr">
+      <s:c r="F7" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_004_Battery01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H7" s="2" t="inlineStr">
+      <s:c r="G7" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H7" s="3" t="n"/>
       <s:c r="I7" s="3" t="n"/>
-      <s:c r="J7" s="3" t="n"/>
     </s:row>
     <s:row r="8" ht="15.6" customFormat="1" customHeight="1" s="3">
       <s:c r="A8" s="1" t="n">
@@ -5528,22 +3510,19 @@
           <s:t>水桶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D8" s="1" t="n">
-        <s:v>13</s:v>
-      </s:c>
-      <s:c r="E8" s="1">
+      <s:c r="D8" s="1">
         <s:f>CEILING(A8/4,1)</s:f>
         <s:v>2</s:v>
       </s:c>
-      <s:c r="F8" s="4" t="n">
+      <s:c r="E8" s="4" t="n">
         <s:v>83069096807916</s:v>
       </s:c>
-      <s:c r="G8" s="5" t="inlineStr">
+      <s:c r="F8" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_005_Battery02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H8" s="2" t="inlineStr">
+      <s:c r="G8" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -5561,27 +3540,24 @@
           <s:t>玻璃瓶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D9" s="1" t="n">
-        <s:v>20</s:v>
-      </s:c>
-      <s:c r="E9" s="1">
+      <s:c r="D9" s="1">
         <s:f>CEILING(A9/4,1)</s:f>
         <s:v>2</s:v>
       </s:c>
-      <s:c r="F9" s="4" t="n">
+      <s:c r="E9" s="4" t="n">
         <s:v>80534536398974</s:v>
       </s:c>
-      <s:c r="G9" s="5" t="inlineStr">
+      <s:c r="F9" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_006_Biscuit01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H9" s="2" t="inlineStr">
+      <s:c r="G9" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I9" s="3" t="n"/>
+      <s:c r="H9" s="3" t="n"/>
     </s:row>
     <s:row r="10" ht="15.6" customHeight="1" s="28">
       <s:c r="A10" s="1" t="n">
@@ -5595,27 +3571,24 @@
           <s:t>啤酒瓶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D10" s="1" t="n">
-        <s:v>30</s:v>
-      </s:c>
-      <s:c r="E10" s="1">
+      <s:c r="D10" s="1">
         <s:f>CEILING(A10/4,1)</s:f>
         <s:v>2</s:v>
       </s:c>
-      <s:c r="F10" s="4" t="n">
+      <s:c r="E10" s="4" t="n">
         <s:v>74246671448525</s:v>
       </s:c>
-      <s:c r="G10" s="5" t="inlineStr">
+      <s:c r="F10" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_007_Biscuit02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H10" s="2" t="inlineStr">
+      <s:c r="G10" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I10" s="3" t="n"/>
+      <s:c r="H10" s="3" t="n"/>
     </s:row>
     <s:row r="11" ht="15.6" customHeight="1" s="28">
       <s:c r="A11" s="1" t="n">
@@ -5629,27 +3602,24 @@
           <s:t>红酒瓶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D11" s="1" t="n">
-        <s:v>38</s:v>
-      </s:c>
-      <s:c r="E11" s="1">
+      <s:c r="D11" s="1">
         <s:f>CEILING(A11/4,1)</s:f>
         <s:v>2</s:v>
       </s:c>
-      <s:c r="F11" s="4" t="n">
+      <s:c r="E11" s="4" t="n">
         <s:v>71499702430100</s:v>
       </s:c>
-      <s:c r="G11" s="5" t="inlineStr">
+      <s:c r="F11" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_008_Biscuit03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H11" s="2" t="inlineStr">
+      <s:c r="G11" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I11" s="3" t="n"/>
+      <s:c r="H11" s="3" t="n"/>
     </s:row>
     <s:row r="12" ht="15.6" customFormat="1" customHeight="1" s="3">
       <s:c r="A12" s="1" t="n">
@@ -5663,22 +3633,19 @@
           <s:t>香槟瓶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D12" s="1" t="n">
-        <s:v>63</s:v>
-      </s:c>
-      <s:c r="E12" s="1">
+      <s:c r="D12" s="1">
         <s:f>CEILING(A12/4,1)</s:f>
         <s:v>3</s:v>
       </s:c>
-      <s:c r="F12" s="4" t="n">
+      <s:c r="E12" s="4" t="n">
         <s:v>122909083001205</s:v>
       </s:c>
-      <s:c r="G12" s="5" t="inlineStr">
+      <s:c r="F12" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_009_Chocolate01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H12" s="2" t="inlineStr">
+      <s:c r="G12" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -5696,22 +3663,19 @@
           <s:t>收藏酒瓶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D13" s="1" t="n">
-        <s:v>100</s:v>
-      </s:c>
-      <s:c r="E13" s="1">
+      <s:c r="D13" s="1">
         <s:f>CEILING(A13/4,1)</s:f>
         <s:v>3</s:v>
       </s:c>
-      <s:c r="F13" s="4" t="n">
+      <s:c r="E13" s="4" t="n">
         <s:v>128658267266293</s:v>
       </s:c>
-      <s:c r="G13" s="5" t="inlineStr">
+      <s:c r="F13" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_010_Chocolate02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H13" s="2" t="inlineStr">
+      <s:c r="G13" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -5729,22 +3693,19 @@
           <s:t>钢钉</s:t>
         </s:is>
       </s:c>
-      <s:c r="D14" s="1" t="n">
-        <s:v>150</s:v>
-      </s:c>
-      <s:c r="E14" s="1">
+      <s:c r="D14" s="1">
         <s:f>CEILING(A14/4,1)</s:f>
         <s:v>3</s:v>
       </s:c>
-      <s:c r="F14" s="4" t="n">
+      <s:c r="E14" s="4" t="n">
         <s:v>134748387119946</s:v>
       </s:c>
-      <s:c r="G14" s="5" t="inlineStr">
+      <s:c r="F14" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_011_Chocolate_Drink</s:t>
         </s:is>
       </s:c>
-      <s:c r="H14" s="2" t="inlineStr">
+      <s:c r="G14" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -5762,22 +3723,19 @@
           <s:t>药片</s:t>
         </s:is>
       </s:c>
-      <s:c r="D15" s="1" t="n">
-        <s:v>188</s:v>
-      </s:c>
-      <s:c r="E15" s="1">
+      <s:c r="D15" s="1">
         <s:f>CEILING(A15/4,1)</s:f>
         <s:v>3</s:v>
       </s:c>
-      <s:c r="F15" s="4" t="n">
+      <s:c r="E15" s="4" t="n">
         <s:v>131559815185521</s:v>
       </s:c>
-      <s:c r="G15" s="5" t="inlineStr">
+      <s:c r="F15" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_012_Honey01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H15" s="2" t="inlineStr">
+      <s:c r="G15" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -5795,30 +3753,27 @@
           <s:t>曲奇</s:t>
         </s:is>
       </s:c>
-      <s:c r="D16" s="1" t="n">
-        <s:v>313</s:v>
-      </s:c>
-      <s:c r="E16" s="1">
+      <s:c r="D16" s="1">
         <s:f>CEILING(A16/4,1)</s:f>
         <s:v>4</s:v>
       </s:c>
-      <s:c r="F16" s="4" t="n">
+      <s:c r="E16" s="4" t="n">
         <s:v>135406755438948</s:v>
       </s:c>
-      <s:c r="G16" s="5" t="inlineStr">
+      <s:c r="F16" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_013_Honey02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H16" s="2" t="inlineStr">
+      <s:c r="G16" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H16" s="3" t="n"/>
       <s:c r="I16" s="3" t="n"/>
       <s:c r="J16" s="3" t="n"/>
       <s:c r="K16" s="3" t="n"/>
-      <s:c r="L16" s="3" t="n"/>
     </s:row>
     <s:row r="17" ht="15.6" customHeight="1" s="28">
       <s:c r="A17" s="1" t="n">
@@ -5832,30 +3787,27 @@
           <s:t>苏打饼</s:t>
         </s:is>
       </s:c>
-      <s:c r="D17" s="1" t="n">
-        <s:v>500</s:v>
-      </s:c>
-      <s:c r="E17" s="1">
+      <s:c r="D17" s="1">
         <s:f>CEILING(A17/4,1)</s:f>
         <s:v>4</s:v>
       </s:c>
-      <s:c r="F17" s="4" t="n">
+      <s:c r="E17" s="4" t="n">
         <s:v>128433990441931</s:v>
       </s:c>
-      <s:c r="G17" s="5" t="inlineStr">
+      <s:c r="F17" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_014_Jam01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H17" s="2" t="inlineStr">
+      <s:c r="G17" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H17" s="3" t="n"/>
       <s:c r="I17" s="3" t="n"/>
       <s:c r="J17" s="3" t="n"/>
       <s:c r="K17" s="3" t="n"/>
-      <s:c r="L17" s="3" t="n"/>
     </s:row>
     <s:row r="18" ht="15.6" customHeight="1" s="28">
       <s:c r="A18" s="1" t="n">
@@ -5869,30 +3821,27 @@
           <s:t>夹心饼</s:t>
         </s:is>
       </s:c>
-      <s:c r="D18" s="1" t="n">
-        <s:v>750</s:v>
-      </s:c>
-      <s:c r="E18" s="1">
+      <s:c r="D18" s="1">
         <s:f>CEILING(A18/4,1)</s:f>
         <s:v>4</s:v>
       </s:c>
-      <s:c r="F18" s="4" t="n">
+      <s:c r="E18" s="4" t="n">
         <s:v>86357992624263</s:v>
       </s:c>
-      <s:c r="G18" s="5" t="inlineStr">
+      <s:c r="F18" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_015_Jam02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H18" s="2" t="inlineStr">
+      <s:c r="G18" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H18" s="3" t="n"/>
       <s:c r="I18" s="3" t="n"/>
       <s:c r="J18" s="3" t="n"/>
       <s:c r="K18" s="3" t="n"/>
-      <s:c r="L18" s="3" t="n"/>
     </s:row>
     <s:row r="19" ht="15.6" customHeight="1" s="28">
       <s:c r="A19" s="1" t="n">
@@ -5906,30 +3855,27 @@
           <s:t>黑巧克力</s:t>
         </s:is>
       </s:c>
-      <s:c r="D19" s="1" t="n">
-        <s:v>938</s:v>
-      </s:c>
-      <s:c r="E19" s="1">
+      <s:c r="D19" s="1">
         <s:f>CEILING(A19/4,1)</s:f>
         <s:v>4</s:v>
       </s:c>
-      <s:c r="F19" s="4" t="n">
+      <s:c r="E19" s="4" t="n">
         <s:v>96128137486525</s:v>
       </s:c>
-      <s:c r="G19" s="5" t="inlineStr">
+      <s:c r="F19" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_016_Water01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H19" s="2" t="inlineStr">
+      <s:c r="G19" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H19" s="3" t="n"/>
       <s:c r="I19" s="3" t="n"/>
       <s:c r="J19" s="3" t="n"/>
       <s:c r="K19" s="3" t="n"/>
-      <s:c r="L19" s="3" t="n"/>
     </s:row>
     <s:row r="20" ht="15.6" customHeight="1" s="28">
       <s:c r="A20" s="1" t="n">
@@ -5943,30 +3889,27 @@
           <s:t>牛奶巧克力</s:t>
         </s:is>
       </s:c>
-      <s:c r="D20" s="1" t="n">
-        <s:v>1563</s:v>
-      </s:c>
-      <s:c r="E20" s="1">
+      <s:c r="D20" s="1">
         <s:f>CEILING(A20/4,1)</s:f>
         <s:v>5</s:v>
       </s:c>
-      <s:c r="F20" s="4" t="n">
+      <s:c r="E20" s="4" t="n">
         <s:v>131913492630514</s:v>
       </s:c>
-      <s:c r="G20" s="5" t="inlineStr">
+      <s:c r="F20" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_017_Water02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H20" s="2" t="inlineStr">
+      <s:c r="G20" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H20" s="3" t="n"/>
       <s:c r="I20" s="3" t="n"/>
       <s:c r="J20" s="3" t="n"/>
       <s:c r="K20" s="3" t="n"/>
-      <s:c r="L20" s="3" t="n"/>
     </s:row>
     <s:row r="21" ht="15.6" customHeight="1" s="28">
       <s:c r="A21" s="1" t="n">
@@ -5980,30 +3923,27 @@
           <s:t>可可饮料</s:t>
         </s:is>
       </s:c>
-      <s:c r="D21" s="1" t="n">
-        <s:v>2500</s:v>
-      </s:c>
-      <s:c r="E21" s="1">
+      <s:c r="D21" s="1">
         <s:f>CEILING(A21/4,1)</s:f>
         <s:v>5</s:v>
       </s:c>
-      <s:c r="F21" s="4" t="n">
+      <s:c r="E21" s="4" t="n">
         <s:v>119579899338192</s:v>
       </s:c>
-      <s:c r="G21" s="5" t="inlineStr">
+      <s:c r="F21" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_018_Water03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H21" s="2" t="inlineStr">
+      <s:c r="G21" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H21" s="3" t="n"/>
       <s:c r="I21" s="3" t="n"/>
       <s:c r="J21" s="3" t="n"/>
       <s:c r="K21" s="3" t="n"/>
-      <s:c r="L21" s="3" t="n"/>
     </s:row>
     <s:row r="22" ht="15.6" customHeight="1" s="28">
       <s:c r="A22" s="1" t="n">
@@ -6017,30 +3957,27 @@
           <s:t>蜂蜜</s:t>
         </s:is>
       </s:c>
-      <s:c r="D22" s="1" t="n">
-        <s:v>3750</s:v>
-      </s:c>
-      <s:c r="E22" s="1">
+      <s:c r="D22" s="1">
         <s:f>CEILING(A22/4,1)</s:f>
         <s:v>5</s:v>
       </s:c>
-      <s:c r="F22" s="4" t="n">
+      <s:c r="E22" s="4" t="n">
         <s:v>82472089572732</s:v>
       </s:c>
-      <s:c r="G22" s="5" t="inlineStr">
+      <s:c r="F22" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_019_Waterbottle01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H22" s="2" t="inlineStr">
+      <s:c r="G22" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H22" s="3" t="n"/>
       <s:c r="I22" s="3" t="n"/>
       <s:c r="J22" s="3" t="n"/>
       <s:c r="K22" s="3" t="n"/>
-      <s:c r="L22" s="3" t="n"/>
     </s:row>
     <s:row r="23" ht="15.6" customHeight="1" s="28">
       <s:c r="A23" s="1" t="n">
@@ -6054,30 +3991,27 @@
           <s:t>野蜂蜜</s:t>
         </s:is>
       </s:c>
-      <s:c r="D23" s="1" t="n">
-        <s:v>4688</s:v>
-      </s:c>
-      <s:c r="E23" s="1">
+      <s:c r="D23" s="1">
         <s:f>CEILING(A23/4,1)</s:f>
         <s:v>5</s:v>
       </s:c>
-      <s:c r="F23" s="4" t="n">
+      <s:c r="E23" s="4" t="n">
         <s:v>104108852156434</s:v>
       </s:c>
-      <s:c r="G23" s="5" t="inlineStr">
+      <s:c r="F23" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_020_Waterbottle02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H23" s="2" t="inlineStr">
+      <s:c r="G23" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H23" s="3" t="n"/>
       <s:c r="I23" s="3" t="n"/>
       <s:c r="J23" s="3" t="n"/>
       <s:c r="K23" s="3" t="n"/>
-      <s:c r="L23" s="3" t="n"/>
     </s:row>
     <s:row r="24" ht="15.6" customHeight="1" s="28">
       <s:c r="A24" s="1" t="n">
@@ -6091,30 +4025,27 @@
           <s:t>草莓酱</s:t>
         </s:is>
       </s:c>
-      <s:c r="D24" s="1" t="n">
-        <s:v>7800</s:v>
-      </s:c>
-      <s:c r="E24" s="1">
+      <s:c r="D24" s="1">
         <s:f>CEILING(A24/4,1)</s:f>
         <s:v>6</s:v>
       </s:c>
-      <s:c r="F24" s="4" t="n">
+      <s:c r="E24" s="4" t="n">
         <s:v>79005623120233</s:v>
       </s:c>
-      <s:c r="G24" s="5" t="inlineStr">
+      <s:c r="F24" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_021_Bottle01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H24" s="2" t="inlineStr">
+      <s:c r="G24" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H24" s="3" t="n"/>
       <s:c r="I24" s="3" t="n"/>
       <s:c r="J24" s="3" t="n"/>
       <s:c r="K24" s="3" t="n"/>
-      <s:c r="L24" s="3" t="n"/>
     </s:row>
     <s:row r="25" ht="15.6" customHeight="1" s="28">
       <s:c r="A25" s="1" t="n">
@@ -6128,30 +4059,27 @@
           <s:t>蓝莓酱</s:t>
         </s:is>
       </s:c>
-      <s:c r="D25" s="1" t="n">
-        <s:v>12480</s:v>
-      </s:c>
-      <s:c r="E25" s="1">
+      <s:c r="D25" s="1">
         <s:f>CEILING(A25/4,1)</s:f>
         <s:v>6</s:v>
       </s:c>
-      <s:c r="F25" s="4" t="n">
+      <s:c r="E25" s="4" t="n">
         <s:v>97611938478078</s:v>
       </s:c>
-      <s:c r="G25" s="5" t="inlineStr">
+      <s:c r="F25" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_022_Bottle02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H25" s="2" t="inlineStr">
+      <s:c r="G25" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H25" s="3" t="n"/>
       <s:c r="I25" s="3" t="n"/>
       <s:c r="J25" s="3" t="n"/>
       <s:c r="K25" s="3" t="n"/>
-      <s:c r="L25" s="3" t="n"/>
     </s:row>
     <s:row r="26" ht="15.6" customHeight="1" s="28">
       <s:c r="A26" s="1" t="n">
@@ -6165,30 +4093,27 @@
           <s:t>肉罐头</s:t>
         </s:is>
       </s:c>
-      <s:c r="D26" s="1" t="n">
-        <s:v>18720</s:v>
-      </s:c>
-      <s:c r="E26" s="1">
+      <s:c r="D26" s="1">
         <s:f>CEILING(A26/4,1)</s:f>
         <s:v>6</s:v>
       </s:c>
-      <s:c r="F26" s="4" t="n">
+      <s:c r="E26" s="4" t="n">
         <s:v>81806655827798</s:v>
       </s:c>
-      <s:c r="G26" s="5" t="inlineStr">
+      <s:c r="F26" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_023_Bottle03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H26" s="2" t="inlineStr">
+      <s:c r="G26" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H26" s="3" t="n"/>
       <s:c r="I26" s="3" t="n"/>
       <s:c r="J26" s="3" t="n"/>
       <s:c r="K26" s="3" t="n"/>
-      <s:c r="L26" s="3" t="n"/>
     </s:row>
     <s:row r="27" ht="15.6" customHeight="1" s="28">
       <s:c r="A27" s="1" t="n">
@@ -6202,30 +4127,27 @@
           <s:t>鱼罐头</s:t>
         </s:is>
       </s:c>
-      <s:c r="D27" s="1" t="n">
-        <s:v>23400</s:v>
-      </s:c>
-      <s:c r="E27" s="1">
+      <s:c r="D27" s="1">
         <s:f>CEILING(A27/4,1)</s:f>
         <s:v>6</s:v>
       </s:c>
-      <s:c r="F27" s="4" t="n">
+      <s:c r="E27" s="4" t="n">
         <s:v>105716218867716</s:v>
       </s:c>
-      <s:c r="G27" s="5" t="inlineStr">
+      <s:c r="F27" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_024_Bottle04</s:t>
         </s:is>
       </s:c>
-      <s:c r="H27" s="2" t="inlineStr">
+      <s:c r="G27" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H27" s="3" t="n"/>
       <s:c r="I27" s="3" t="n"/>
       <s:c r="J27" s="3" t="n"/>
       <s:c r="K27" s="3" t="n"/>
-      <s:c r="L27" s="3" t="n"/>
     </s:row>
     <s:row r="28" ht="15.6" customHeight="1" s="28">
       <s:c r="A28" s="1" t="n">
@@ -6239,30 +4161,27 @@
           <s:t>水果罐头</s:t>
         </s:is>
       </s:c>
-      <s:c r="D28" s="1" t="n">
-        <s:v>39050</s:v>
-      </s:c>
-      <s:c r="E28" s="1">
+      <s:c r="D28" s="1">
         <s:f>CEILING(A28/4,1)</s:f>
         <s:v>7</s:v>
       </s:c>
-      <s:c r="F28" s="4" t="n">
+      <s:c r="E28" s="4" t="n">
         <s:v>128411546772202</s:v>
       </s:c>
-      <s:c r="G28" s="5" t="inlineStr">
+      <s:c r="F28" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_025_Bottle05</s:t>
         </s:is>
       </s:c>
-      <s:c r="H28" s="2" t="inlineStr">
+      <s:c r="G28" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H28" s="3" t="n"/>
       <s:c r="I28" s="3" t="n"/>
       <s:c r="J28" s="3" t="n"/>
       <s:c r="K28" s="3" t="n"/>
-      <s:c r="L28" s="3" t="n"/>
     </s:row>
     <s:row r="29" ht="15.6" customHeight="1" s="28">
       <s:c r="A29" s="1" t="n">
@@ -6276,30 +4195,27 @@
           <s:t>午餐肉</s:t>
         </s:is>
       </s:c>
-      <s:c r="D29" s="1" t="n">
-        <s:v>62480</s:v>
-      </s:c>
-      <s:c r="E29" s="1">
+      <s:c r="D29" s="1">
         <s:f>CEILING(A29/4,1)</s:f>
         <s:v>7</s:v>
       </s:c>
-      <s:c r="F29" s="4" t="n">
+      <s:c r="E29" s="4" t="n">
         <s:v>139465058617680</s:v>
       </s:c>
-      <s:c r="G29" s="5" t="inlineStr">
+      <s:c r="F29" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_026_Can01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H29" s="2" t="inlineStr">
+      <s:c r="G29" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H29" s="3" t="n"/>
       <s:c r="I29" s="3" t="n"/>
       <s:c r="J29" s="3" t="n"/>
       <s:c r="K29" s="3" t="n"/>
-      <s:c r="L29" s="3" t="n"/>
     </s:row>
     <s:row r="30" ht="15.6" customHeight="1" s="28">
       <s:c r="A30" s="1" t="n">
@@ -6313,30 +4229,27 @@
           <s:t>豆子罐头</s:t>
         </s:is>
       </s:c>
-      <s:c r="D30" s="1" t="n">
-        <s:v>93720</s:v>
-      </s:c>
-      <s:c r="E30" s="1">
+      <s:c r="D30" s="1">
         <s:f>CEILING(A30/4,1)</s:f>
         <s:v>7</s:v>
       </s:c>
-      <s:c r="F30" s="4" t="n">
+      <s:c r="E30" s="4" t="n">
         <s:v>81737011057690</s:v>
       </s:c>
-      <s:c r="G30" s="5" t="inlineStr">
+      <s:c r="F30" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_027_Can02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H30" s="2" t="inlineStr">
+      <s:c r="G30" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H30" s="3" t="n"/>
       <s:c r="I30" s="3" t="n"/>
       <s:c r="J30" s="3" t="n"/>
       <s:c r="K30" s="3" t="n"/>
-      <s:c r="L30" s="3" t="n"/>
     </s:row>
     <s:row r="31" ht="15.6" customHeight="1" s="28">
       <s:c r="A31" s="1" t="n">
@@ -6350,30 +4263,27 @@
           <s:t>军粮罐头</s:t>
         </s:is>
       </s:c>
-      <s:c r="D31" s="1" t="n">
-        <s:v>117150</s:v>
-      </s:c>
-      <s:c r="E31" s="1">
+      <s:c r="D31" s="1">
         <s:f>CEILING(A31/4,1)</s:f>
         <s:v>7</s:v>
       </s:c>
-      <s:c r="F31" s="4" t="n">
+      <s:c r="E31" s="4" t="n">
         <s:v>81445862907930</s:v>
       </s:c>
-      <s:c r="G31" s="5" t="inlineStr">
+      <s:c r="F31" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_028_Can03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H31" s="2" t="inlineStr">
+      <s:c r="G31" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H31" s="3" t="n"/>
       <s:c r="I31" s="3" t="n"/>
       <s:c r="J31" s="3" t="n"/>
       <s:c r="K31" s="3" t="n"/>
-      <s:c r="L31" s="3" t="n"/>
     </s:row>
     <s:row r="32" ht="15.6" customHeight="1" s="28">
       <s:c r="A32" s="1" t="n">
@@ -6387,30 +4297,27 @@
           <s:t>高级罐头</s:t>
         </s:is>
       </s:c>
-      <s:c r="D32" s="1" t="n">
-        <s:v>195500</s:v>
-      </s:c>
-      <s:c r="E32" s="1">
+      <s:c r="D32" s="1">
         <s:f>CEILING(A32/4,1)</s:f>
         <s:v>8</s:v>
       </s:c>
-      <s:c r="F32" s="4" t="n">
+      <s:c r="E32" s="4" t="n">
         <s:v>123098432383687</s:v>
       </s:c>
-      <s:c r="G32" s="5" t="inlineStr">
+      <s:c r="F32" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_029_Can04</s:t>
         </s:is>
       </s:c>
-      <s:c r="H32" s="2" t="inlineStr">
+      <s:c r="G32" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H32" s="3" t="n"/>
       <s:c r="I32" s="3" t="n"/>
       <s:c r="J32" s="3" t="n"/>
       <s:c r="K32" s="3" t="n"/>
-      <s:c r="L32" s="3" t="n"/>
     </s:row>
     <s:row r="33" ht="15.6" customFormat="1" customHeight="1" s="3">
       <s:c r="A33" s="1" t="n">
@@ -6424,22 +4331,19 @@
           <s:t>清洁剂</s:t>
         </s:is>
       </s:c>
-      <s:c r="D33" s="1" t="n">
-        <s:v>312800</s:v>
-      </s:c>
-      <s:c r="E33" s="1">
+      <s:c r="D33" s="1">
         <s:f>CEILING(A33/4,1)</s:f>
         <s:v>8</s:v>
       </s:c>
-      <s:c r="F33" s="4" t="n">
+      <s:c r="E33" s="4" t="n">
         <s:v>131796260838154</s:v>
       </s:c>
-      <s:c r="G33" s="5" t="inlineStr">
+      <s:c r="F33" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_030_Can05</s:t>
         </s:is>
       </s:c>
-      <s:c r="H33" s="2" t="inlineStr">
+      <s:c r="G33" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6457,22 +4361,19 @@
           <s:t>漂白水</s:t>
         </s:is>
       </s:c>
-      <s:c r="D34" s="1" t="n">
-        <s:v>469200</s:v>
-      </s:c>
-      <s:c r="E34" s="1">
+      <s:c r="D34" s="1">
         <s:f>CEILING(A34/4,1)</s:f>
         <s:v>8</s:v>
       </s:c>
-      <s:c r="F34" s="4" t="n">
+      <s:c r="E34" s="4" t="n">
         <s:v>116376878683736</s:v>
       </s:c>
-      <s:c r="G34" s="5" t="inlineStr">
+      <s:c r="F34" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_031_Can06</s:t>
         </s:is>
       </s:c>
-      <s:c r="H34" s="2" t="inlineStr">
+      <s:c r="G34" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6490,22 +4391,19 @@
           <s:t>润滑油</s:t>
         </s:is>
       </s:c>
-      <s:c r="D35" s="1" t="n">
-        <s:v>586500</s:v>
-      </s:c>
-      <s:c r="E35" s="1">
+      <s:c r="D35" s="1">
         <s:f>CEILING(A35/4,1)</s:f>
         <s:v>8</s:v>
       </s:c>
-      <s:c r="F35" s="4" t="n">
+      <s:c r="E35" s="4" t="n">
         <s:v>100558097057142</s:v>
       </s:c>
-      <s:c r="G35" s="5" t="inlineStr">
+      <s:c r="F35" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_032_Can07</s:t>
         </s:is>
       </s:c>
-      <s:c r="H35" s="2" t="inlineStr">
+      <s:c r="G35" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6523,30 +4421,27 @@
           <s:t>小油壶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D36" s="1" t="n">
-        <s:v>975000</s:v>
-      </s:c>
-      <s:c r="E36" s="1">
+      <s:c r="D36" s="1">
         <s:f>CEILING(A36/4,1)</s:f>
         <s:v>9</s:v>
       </s:c>
-      <s:c r="F36" s="4" t="n">
+      <s:c r="E36" s="4" t="n">
         <s:v>92332707761527</s:v>
       </s:c>
-      <s:c r="G36" s="5" t="inlineStr">
+      <s:c r="F36" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_033_Medicine_bottle01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H36" s="2" t="inlineStr">
+      <s:c r="G36" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H36" s="3" t="n"/>
       <s:c r="I36" s="3" t="n"/>
       <s:c r="J36" s="3" t="n"/>
       <s:c r="K36" s="3" t="n"/>
-      <s:c r="L36" s="3" t="n"/>
     </s:row>
     <s:row r="37" ht="15.6" customFormat="1" customHeight="1" s="3">
       <s:c r="A37" s="1" t="n">
@@ -6560,22 +4455,19 @@
           <s:t>运动水壶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D37" s="1" t="n">
-        <s:v>1560000</s:v>
-      </s:c>
-      <s:c r="E37" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D37" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>6</s:v>
       </s:c>
-      <s:c r="F37" s="4" t="n">
+      <s:c r="E37" s="4" t="n">
         <s:v>108895787734224</s:v>
       </s:c>
-      <s:c r="G37" s="5" t="inlineStr">
+      <s:c r="F37" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_034_Medicine_bottle02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H37" s="2" t="inlineStr">
+      <s:c r="G37" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6593,22 +4485,19 @@
           <s:t>军用水壶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D38" s="1" t="n">
-        <s:v>2340000</s:v>
-      </s:c>
-      <s:c r="E38" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D38" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>7</s:v>
       </s:c>
-      <s:c r="F38" s="4" t="n">
+      <s:c r="E38" s="4" t="n">
         <s:v>95471681056681</s:v>
       </s:c>
-      <s:c r="G38" s="5" t="inlineStr">
+      <s:c r="F38" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_035_Injection</s:t>
         </s:is>
       </s:c>
-      <s:c r="H38" s="2" t="inlineStr">
+      <s:c r="G38" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6626,30 +4515,27 @@
           <s:t>机油壶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D39" s="1" t="n">
-        <s:v>2925000</s:v>
-      </s:c>
-      <s:c r="E39" s="1">
+      <s:c r="D39" s="1">
         <s:f>CEILING(A39/4,1)</s:f>
         <s:v>9</s:v>
       </s:c>
-      <s:c r="F39" s="4" t="n">
+      <s:c r="E39" s="4" t="n">
         <s:v>104955598295323</s:v>
       </s:c>
-      <s:c r="G39" s="5" t="inlineStr">
+      <s:c r="F39" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_036_InjectionA</s:t>
         </s:is>
       </s:c>
-      <s:c r="H39" s="2" t="inlineStr">
+      <s:c r="G39" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H39" s="3" t="n"/>
       <s:c r="I39" s="3" t="n"/>
       <s:c r="J39" s="3" t="n"/>
       <s:c r="K39" s="3" t="n"/>
-      <s:c r="L39" s="3" t="n"/>
     </s:row>
     <s:row r="40" ht="15.6" customHeight="1" s="28">
       <s:c r="A40" s="1" t="n">
@@ -6663,30 +4549,27 @@
           <s:t>燃油罐</s:t>
         </s:is>
       </s:c>
-      <s:c r="D40" s="1" t="n">
-        <s:v>4885000</s:v>
-      </s:c>
-      <s:c r="E40" s="1">
+      <s:c r="D40" s="1">
         <s:f>CEILING(A40/4,1)</s:f>
         <s:v>10</s:v>
       </s:c>
-      <s:c r="F40" s="4" t="n">
+      <s:c r="E40" s="4" t="n">
         <s:v>103175883366340</s:v>
       </s:c>
-      <s:c r="G40" s="5" t="inlineStr">
+      <s:c r="F40" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_037_First_aid_Kit_Bandage</s:t>
         </s:is>
       </s:c>
-      <s:c r="H40" s="2" t="inlineStr">
+      <s:c r="G40" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
+      <s:c r="H40" s="3" t="n"/>
       <s:c r="I40" s="3" t="n"/>
       <s:c r="J40" s="3" t="n"/>
       <s:c r="K40" s="3" t="n"/>
-      <s:c r="L40" s="3" t="n"/>
     </s:row>
     <s:row r="41" ht="15.6" customFormat="1" customHeight="1" s="3">
       <s:c r="A41" s="1" t="n">
@@ -6700,22 +4583,19 @@
           <s:t>礼帽</s:t>
         </s:is>
       </s:c>
-      <s:c r="D41" s="1" t="n">
-        <s:v>7816000</s:v>
-      </s:c>
-      <s:c r="E41" s="1">
+      <s:c r="D41" s="1">
         <s:f>CEILING(A41/4,1)</s:f>
         <s:v>10</s:v>
       </s:c>
-      <s:c r="F41" s="4" t="n">
+      <s:c r="E41" s="4" t="n">
         <s:v>114247164745798</s:v>
       </s:c>
-      <s:c r="G41" s="5" t="inlineStr">
+      <s:c r="F41" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_038_Lv</s:t>
         </s:is>
       </s:c>
-      <s:c r="H41" s="2" t="inlineStr">
+      <s:c r="G41" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6733,22 +4613,19 @@
           <s:t>棒球帽</s:t>
         </s:is>
       </s:c>
-      <s:c r="D42" s="1" t="n">
-        <s:v>11724000</s:v>
-      </s:c>
-      <s:c r="E42" s="1">
+      <s:c r="D42" s="1">
         <s:f>CEILING(A42/4,1)</s:f>
         <s:v>10</s:v>
       </s:c>
-      <s:c r="F42" s="4" t="n">
+      <s:c r="E42" s="4" t="n">
         <s:v>86017047390182</s:v>
       </s:c>
-      <s:c r="G42" s="5" t="inlineStr">
+      <s:c r="F42" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_039_First_aid_Kit01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H42" s="2" t="inlineStr">
+      <s:c r="G42" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6766,22 +4643,19 @@
           <s:t>墨镜</s:t>
         </s:is>
       </s:c>
-      <s:c r="D43" s="1" t="n">
-        <s:v>14655000</s:v>
-      </s:c>
-      <s:c r="E43" s="1">
+      <s:c r="D43" s="1">
         <s:f>CEILING(A43/4,1)</s:f>
         <s:v>10</s:v>
       </s:c>
-      <s:c r="F43" s="4" t="n">
+      <s:c r="E43" s="4" t="n">
         <s:v>81373582816266</s:v>
       </s:c>
-      <s:c r="G43" s="5" t="inlineStr">
+      <s:c r="F43" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_040_First_aid_Kit02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H43" s="2" t="inlineStr">
+      <s:c r="G43" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6799,22 +4673,19 @@
           <s:t>太阳镜</s:t>
         </s:is>
       </s:c>
-      <s:c r="D44" s="1" t="n">
-        <s:v>24400000</s:v>
-      </s:c>
-      <s:c r="E44" s="1">
+      <s:c r="D44" s="1">
         <s:f>CEILING(A44/4,1)</s:f>
         <s:v>11</s:v>
       </s:c>
-      <s:c r="F44" s="4" t="n">
+      <s:c r="E44" s="4" t="n">
         <s:v>132788281080826</s:v>
       </s:c>
-      <s:c r="G44" s="5" t="inlineStr">
+      <s:c r="F44" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_041_First_aid_Kit03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H44" s="2" t="inlineStr">
+      <s:c r="G44" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6832,22 +4703,19 @@
           <s:t>护目镜</s:t>
         </s:is>
       </s:c>
-      <s:c r="D45" s="1" t="n">
-        <s:v>39040000</s:v>
-      </s:c>
-      <s:c r="E45" s="1">
+      <s:c r="D45" s="1">
         <s:f>CEILING(A45/4,1)</s:f>
         <s:v>11</s:v>
       </s:c>
-      <s:c r="F45" s="4" t="n">
+      <s:c r="E45" s="4" t="n">
         <s:v>95162444285252</s:v>
       </s:c>
-      <s:c r="G45" s="5" t="inlineStr">
+      <s:c r="F45" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_042_Detergent</s:t>
         </s:is>
       </s:c>
-      <s:c r="H45" s="2" t="inlineStr">
+      <s:c r="G45" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6865,22 +4733,19 @@
           <s:t>战术风镜</s:t>
         </s:is>
       </s:c>
-      <s:c r="D46" s="1" t="n">
-        <s:v>58560000</s:v>
-      </s:c>
-      <s:c r="E46" s="1">
+      <s:c r="D46" s="1">
         <s:f>CEILING(A46/4,1)</s:f>
         <s:v>11</s:v>
       </s:c>
-      <s:c r="F46" s="4" t="n">
+      <s:c r="E46" s="4" t="n">
         <s:v>95953438126479</s:v>
       </s:c>
-      <s:c r="G46" s="5" t="inlineStr">
+      <s:c r="F46" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_043_Bleach</s:t>
         </s:is>
       </s:c>
-      <s:c r="H46" s="2" t="inlineStr">
+      <s:c r="G46" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6898,22 +4763,19 @@
           <s:t>口罩</s:t>
         </s:is>
       </s:c>
-      <s:c r="D47" s="1" t="n">
-        <s:v>73200000</s:v>
-      </s:c>
-      <s:c r="E47" s="1">
+      <s:c r="D47" s="1">
         <s:f>CEILING(A47/4,1)</s:f>
         <s:v>11</s:v>
       </s:c>
-      <s:c r="F47" s="4" t="n">
+      <s:c r="E47" s="4" t="n">
         <s:v>112039222887887</s:v>
       </s:c>
-      <s:c r="G47" s="5" t="inlineStr">
+      <s:c r="F47" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_044_WD40</s:t>
         </s:is>
       </s:c>
-      <s:c r="H47" s="2" t="inlineStr">
+      <s:c r="G47" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6931,22 +4793,19 @@
           <s:t>防毒面具</s:t>
         </s:is>
       </s:c>
-      <s:c r="D48" s="1" t="n">
-        <s:v>122000000</s:v>
-      </s:c>
-      <s:c r="E48" s="1">
+      <s:c r="D48" s="1">
         <s:f>CEILING(A48/4,1)</s:f>
         <s:v>12</s:v>
       </s:c>
-      <s:c r="F48" s="4" t="n">
+      <s:c r="E48" s="4" t="n">
         <s:v>95377459606647</s:v>
       </s:c>
-      <s:c r="G48" s="5" t="inlineStr">
+      <s:c r="F48" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_045_Pipe</s:t>
         </s:is>
       </s:c>
-      <s:c r="H48" s="2" t="inlineStr">
+      <s:c r="G48" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6964,22 +4823,19 @@
           <s:t>战术面具</s:t>
         </s:is>
       </s:c>
-      <s:c r="D49" s="1" t="n">
-        <s:v>195200000</s:v>
-      </s:c>
-      <s:c r="E49" s="1">
+      <s:c r="D49" s="1">
         <s:f>CEILING(A49/4,1)</s:f>
         <s:v>12</s:v>
       </s:c>
-      <s:c r="F49" s="4" t="n">
+      <s:c r="E49" s="4" t="n">
         <s:v>113983796605688</s:v>
       </s:c>
-      <s:c r="G49" s="5" t="inlineStr">
+      <s:c r="F49" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_046_Zippo</s:t>
         </s:is>
       </s:c>
-      <s:c r="H49" s="2" t="inlineStr">
+      <s:c r="G49" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -6997,22 +4853,19 @@
           <s:t>皮靴</s:t>
         </s:is>
       </s:c>
-      <s:c r="D50" s="1" t="n">
-        <s:v>292800000</s:v>
-      </s:c>
-      <s:c r="E50" s="1">
+      <s:c r="D50" s="1">
         <s:f>CEILING(A50/4,1)</s:f>
         <s:v>12</s:v>
       </s:c>
-      <s:c r="F50" s="4" t="n">
+      <s:c r="E50" s="4" t="n">
         <s:v>117157716541352</s:v>
       </s:c>
-      <s:c r="G50" s="5" t="inlineStr">
+      <s:c r="F50" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_047_Oilcan01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H50" s="2" t="inlineStr">
+      <s:c r="G50" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7030,22 +4883,19 @@
           <s:t>雨靴</s:t>
         </s:is>
       </s:c>
-      <s:c r="D51" s="1" t="n">
-        <s:v>366000000</s:v>
-      </s:c>
-      <s:c r="E51" s="1">
+      <s:c r="D51" s="1">
         <s:f>CEILING(A51/4,1)</s:f>
         <s:v>12</s:v>
       </s:c>
-      <s:c r="F51" s="4" t="n">
+      <s:c r="E51" s="4" t="n">
         <s:v>100893051807474</s:v>
       </s:c>
-      <s:c r="G51" s="5" t="inlineStr">
+      <s:c r="F51" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_048_Oilcan02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H51" s="2" t="inlineStr">
+      <s:c r="G51" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7063,22 +4913,19 @@
           <s:t>登山靴</s:t>
         </s:is>
       </s:c>
-      <s:c r="D52" s="1" t="n">
-        <s:v>610000000</s:v>
-      </s:c>
-      <s:c r="E52" s="1">
+      <s:c r="D52" s="1">
         <s:f>CEILING(A52/4,1)</s:f>
         <s:v>13</s:v>
       </s:c>
-      <s:c r="F52" s="4" t="n">
+      <s:c r="E52" s="4" t="n">
         <s:v>137999782231090</s:v>
       </s:c>
-      <s:c r="G52" s="5" t="inlineStr">
+      <s:c r="F52" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_049_Oilcan03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H52" s="2" t="inlineStr">
+      <s:c r="G52" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7096,22 +4943,19 @@
           <s:t>军靴</s:t>
         </s:is>
       </s:c>
-      <s:c r="D53" s="1" t="n">
-        <s:v>976000000</s:v>
-      </s:c>
-      <s:c r="E53" s="1">
+      <s:c r="D53" s="1">
         <s:f>CEILING(A53/4,1)</s:f>
         <s:v>13</s:v>
       </s:c>
-      <s:c r="F53" s="4" t="n">
+      <s:c r="E53" s="4" t="n">
         <s:v>127007149281218</s:v>
       </s:c>
-      <s:c r="G53" s="5" t="inlineStr">
+      <s:c r="F53" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_050_Mobilephone</s:t>
         </s:is>
       </s:c>
-      <s:c r="H53" s="2" t="inlineStr">
+      <s:c r="G53" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7129,22 +4973,19 @@
           <s:t>防弹背心</s:t>
         </s:is>
       </s:c>
-      <s:c r="D54" s="1" t="n">
-        <s:v>1464000000</s:v>
-      </s:c>
-      <s:c r="E54" s="1">
+      <s:c r="D54" s="1">
         <s:f>CEILING(A54/4,1)</s:f>
         <s:v>13</s:v>
       </s:c>
-      <s:c r="F54" s="4" t="n">
+      <s:c r="E54" s="4" t="n">
         <s:v>85273469740405</s:v>
       </s:c>
-      <s:c r="G54" s="5" t="inlineStr">
+      <s:c r="F54" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_051_Watch01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H54" s="2" t="inlineStr">
+      <s:c r="G54" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7162,22 +5003,19 @@
           <s:t>重型护甲</s:t>
         </s:is>
       </s:c>
-      <s:c r="D55" s="1" t="n">
-        <s:v>1830000000</s:v>
-      </s:c>
-      <s:c r="E55" s="1">
+      <s:c r="D55" s="1">
         <s:f>CEILING(A55/4,1)</s:f>
         <s:v>13</s:v>
       </s:c>
-      <s:c r="F55" s="4" t="n">
+      <s:c r="E55" s="4" t="n">
         <s:v>85750403977754</s:v>
       </s:c>
-      <s:c r="G55" s="5" t="inlineStr">
+      <s:c r="F55" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_052_IdentificationTag</s:t>
         </s:is>
       </s:c>
-      <s:c r="H55" s="2" t="inlineStr">
+      <s:c r="G55" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7195,22 +5033,19 @@
           <s:t>工地头盔</s:t>
         </s:is>
       </s:c>
-      <s:c r="D56" s="1" t="n">
-        <s:v>3050000000</s:v>
-      </s:c>
-      <s:c r="E56" s="1">
+      <s:c r="D56" s="1">
         <s:f>CEILING(A56/4,1)</s:f>
         <s:v>14</s:v>
       </s:c>
-      <s:c r="F56" s="4" t="n">
+      <s:c r="E56" s="4" t="n">
         <s:v>87658125570749</s:v>
       </s:c>
-      <s:c r="G56" s="5" t="inlineStr">
+      <s:c r="F56" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_053_Compass</s:t>
         </s:is>
       </s:c>
-      <s:c r="H56" s="2" t="inlineStr">
+      <s:c r="G56" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7228,22 +5063,19 @@
           <s:t>骑行头盔</s:t>
         </s:is>
       </s:c>
-      <s:c r="D57" s="1" t="n">
-        <s:v>4880000000</s:v>
-      </s:c>
-      <s:c r="E57" s="1">
+      <s:c r="D57" s="1">
         <s:f>CEILING(A57/4,1)</s:f>
         <s:v>14</s:v>
       </s:c>
-      <s:c r="F57" s="4" t="n">
+      <s:c r="E57" s="4" t="n">
         <s:v>71386503893388</s:v>
       </s:c>
-      <s:c r="G57" s="5" t="inlineStr">
+      <s:c r="F57" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_054_CompassA</s:t>
         </s:is>
       </s:c>
-      <s:c r="H57" s="2" t="inlineStr">
+      <s:c r="G57" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7261,22 +5093,19 @@
           <s:t>防暴头盔</s:t>
         </s:is>
       </s:c>
-      <s:c r="D58" s="1" t="n">
-        <s:v>7320000000</s:v>
-      </s:c>
-      <s:c r="E58" s="1">
+      <s:c r="D58" s="1">
         <s:f>CEILING(A58/4,1)</s:f>
         <s:v>14</s:v>
       </s:c>
-      <s:c r="F58" s="4" t="n">
+      <s:c r="E58" s="4" t="n">
         <s:v>117660867991736</s:v>
       </s:c>
-      <s:c r="G58" s="5" t="inlineStr">
+      <s:c r="F58" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_055_Hat</s:t>
         </s:is>
       </s:c>
-      <s:c r="H58" s="2" t="inlineStr">
+      <s:c r="G58" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7294,22 +5123,19 @@
           <s:t>战术头盔</s:t>
         </s:is>
       </s:c>
-      <s:c r="D59" s="1" t="n">
-        <s:v>9150000000</s:v>
-      </s:c>
-      <s:c r="E59" s="1">
+      <s:c r="D59" s="1">
         <s:f>CEILING(A59/4,1)</s:f>
         <s:v>14</s:v>
       </s:c>
-      <s:c r="F59" s="4" t="n">
+      <s:c r="E59" s="4" t="n">
         <s:v>75602786825729</s:v>
       </s:c>
-      <s:c r="G59" s="5" t="inlineStr">
+      <s:c r="F59" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_056_Cap_A_0</s:t>
         </s:is>
       </s:c>
-      <s:c r="H59" s="2" t="inlineStr">
+      <s:c r="G59" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7327,22 +5153,19 @@
           <s:t>小背包</s:t>
         </s:is>
       </s:c>
-      <s:c r="D60" s="1" t="n">
-        <s:v>15250000000</s:v>
-      </s:c>
-      <s:c r="E60" s="1">
+      <s:c r="D60" s="1">
         <s:f>CEILING(A60/4,1)</s:f>
         <s:v>15</s:v>
       </s:c>
-      <s:c r="F60" s="4" t="n">
+      <s:c r="E60" s="4" t="n">
         <s:v>97494295137425</s:v>
       </s:c>
-      <s:c r="G60" s="5" t="inlineStr">
+      <s:c r="F60" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_057_Sunglass01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H60" s="2" t="inlineStr">
+      <s:c r="G60" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7360,22 +5183,19 @@
           <s:t>登山包</s:t>
         </s:is>
       </s:c>
-      <s:c r="D61" s="1" t="n">
-        <s:v>24400000000</s:v>
-      </s:c>
-      <s:c r="E61" s="1">
+      <s:c r="D61" s="1">
         <s:f>CEILING(A61/4,1)</s:f>
         <s:v>15</s:v>
       </s:c>
-      <s:c r="F61" s="4" t="n">
+      <s:c r="E61" s="4" t="n">
         <s:v>121387106380169</s:v>
       </s:c>
-      <s:c r="G61" s="5" t="inlineStr">
+      <s:c r="F61" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_058_Sunglass02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H61" s="2" t="inlineStr">
+      <s:c r="G61" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7393,22 +5213,19 @@
           <s:t>军用背包</s:t>
         </s:is>
       </s:c>
-      <s:c r="D62" s="1" t="n">
-        <s:v>36600000000</s:v>
-      </s:c>
-      <s:c r="E62" s="1">
+      <s:c r="D62" s="1">
         <s:f>CEILING(A62/4,1)</s:f>
         <s:v>15</s:v>
       </s:c>
-      <s:c r="F62" s="4" t="n">
+      <s:c r="E62" s="4" t="n">
         <s:v>77703154963129</s:v>
       </s:c>
-      <s:c r="G62" s="5" t="inlineStr">
+      <s:c r="F62" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_059_Goggle</s:t>
         </s:is>
       </s:c>
-      <s:c r="H62" s="2" t="inlineStr">
+      <s:c r="G62" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7426,22 +5243,19 @@
           <s:t>铁锅</s:t>
         </s:is>
       </s:c>
-      <s:c r="D63" s="1" t="n">
-        <s:v>45750000000</s:v>
-      </s:c>
-      <s:c r="E63" s="1">
+      <s:c r="D63" s="1">
         <s:f>CEILING(A63/4,1)</s:f>
         <s:v>15</s:v>
       </s:c>
-      <s:c r="F63" s="4" t="n">
+      <s:c r="E63" s="4" t="n">
         <s:v>82745313217810</s:v>
       </s:c>
-      <s:c r="G63" s="5" t="inlineStr">
+      <s:c r="F63" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_060_GoggleA</s:t>
         </s:is>
       </s:c>
-      <s:c r="H63" s="2" t="inlineStr">
+      <s:c r="G63" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7459,22 +5273,19 @@
           <s:t>木锤</s:t>
         </s:is>
       </s:c>
-      <s:c r="D64" s="1" t="n">
-        <s:v>76500000000</s:v>
-      </s:c>
-      <s:c r="E64" s="1">
+      <s:c r="D64" s="1">
         <s:f>CEILING(A64/4,1)</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="F64" s="4" t="n">
+      <s:c r="E64" s="4" t="n">
         <s:v>78702263483439</s:v>
       </s:c>
-      <s:c r="G64" s="5" t="inlineStr">
+      <s:c r="F64" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_061_MaskA</s:t>
         </s:is>
       </s:c>
-      <s:c r="H64" s="2" t="inlineStr">
+      <s:c r="G64" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7492,22 +5303,19 @@
           <s:t>铁锤</s:t>
         </s:is>
       </s:c>
-      <s:c r="D65" s="1" t="n">
-        <s:v>122400000000</s:v>
-      </s:c>
-      <s:c r="E65" s="1">
+      <s:c r="D65" s="1">
         <s:f>CEILING(A65/4,1)</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="F65" s="4" t="n">
+      <s:c r="E65" s="4" t="n">
         <s:v>103252845267522</s:v>
       </s:c>
-      <s:c r="G65" s="5" t="inlineStr">
+      <s:c r="F65" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_062_GasMask01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H65" s="2" t="inlineStr">
+      <s:c r="G65" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7525,22 +5333,19 @@
           <s:t>大锤</s:t>
         </s:is>
       </s:c>
-      <s:c r="D66" s="1" t="n">
-        <s:v>183600000000</s:v>
-      </s:c>
-      <s:c r="E66" s="1">
+      <s:c r="D66" s="1">
         <s:f>CEILING(A66/4,1)</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="F66" s="4" t="n">
+      <s:c r="E66" s="4" t="n">
         <s:v>93380659059014</s:v>
       </s:c>
-      <s:c r="G66" s="5" t="inlineStr">
+      <s:c r="F66" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_063_GasMask02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H66" s="2" t="inlineStr">
+      <s:c r="G66" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7558,22 +5363,19 @@
           <s:t>扳手</s:t>
         </s:is>
       </s:c>
-      <s:c r="D67" s="1" t="n">
-        <s:v>229500000000</s:v>
-      </s:c>
-      <s:c r="E67" s="1">
+      <s:c r="D67" s="1">
         <s:f>CEILING(A67/4,1)</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="F67" s="4" t="n">
+      <s:c r="E67" s="4" t="n">
         <s:v>124070618735034</s:v>
       </s:c>
-      <s:c r="G67" s="5" t="inlineStr">
+      <s:c r="F67" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_064_Boots01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H67" s="2" t="inlineStr">
+      <s:c r="G67" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7591,22 +5393,19 @@
           <s:t>活动扳手</s:t>
         </s:is>
       </s:c>
-      <s:c r="D68" s="1" t="n">
-        <s:v>381500000000</s:v>
-      </s:c>
-      <s:c r="E68" s="1">
+      <s:c r="D68" s="1">
         <s:f>CEILING(A68/4,1)</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="F68" s="4" t="n">
+      <s:c r="E68" s="4" t="n">
         <s:v>82229267783572</s:v>
       </s:c>
-      <s:c r="G68" s="5" t="inlineStr">
+      <s:c r="F68" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_065_Boots02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H68" s="2" t="inlineStr">
+      <s:c r="G68" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7624,22 +5423,19 @@
           <s:t>管钳</s:t>
         </s:is>
       </s:c>
-      <s:c r="D69" s="1" t="n">
-        <s:v>610400000000</s:v>
-      </s:c>
-      <s:c r="E69" s="1">
+      <s:c r="D69" s="1">
         <s:f>CEILING(A69/4,1)</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="F69" s="4" t="n">
+      <s:c r="E69" s="4" t="n">
         <s:v>90764663625426</s:v>
       </s:c>
-      <s:c r="G69" s="5" t="inlineStr">
+      <s:c r="F69" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_066_Boots03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H69" s="2" t="inlineStr">
+      <s:c r="G69" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7657,22 +5453,19 @@
           <s:t>工兵铲</s:t>
         </s:is>
       </s:c>
-      <s:c r="D70" s="1" t="n">
-        <s:v>915600000000</s:v>
-      </s:c>
-      <s:c r="E70" s="1">
+      <s:c r="D70" s="1">
         <s:f>CEILING(A70/4,1)</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="F70" s="4" t="n">
+      <s:c r="E70" s="4" t="n">
         <s:v>89592774326120</s:v>
       </s:c>
-      <s:c r="G70" s="5" t="inlineStr">
+      <s:c r="F70" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_067_Boots04</s:t>
         </s:is>
       </s:c>
-      <s:c r="H70" s="2" t="inlineStr">
+      <s:c r="G70" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7690,22 +5483,19 @@
           <s:t>铁锹</s:t>
         </s:is>
       </s:c>
-      <s:c r="D71" s="1" t="n">
-        <s:v>1144500000000</s:v>
-      </s:c>
-      <s:c r="E71" s="1">
+      <s:c r="D71" s="1">
         <s:f>CEILING(A71/4,1)</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="F71" s="4" t="n">
+      <s:c r="E71" s="4" t="n">
         <s:v>96498729983354</s:v>
       </s:c>
-      <s:c r="G71" s="5" t="inlineStr">
+      <s:c r="F71" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_068_BulletproofJacket01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H71" s="2" t="inlineStr">
+      <s:c r="G71" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7723,22 +5513,19 @@
           <s:t>十字镐</s:t>
         </s:is>
       </s:c>
-      <s:c r="D72" s="1" t="n">
-        <s:v>1905000000000</s:v>
-      </s:c>
-      <s:c r="E72" s="1">
+      <s:c r="D72" s="1">
         <s:f>CEILING(A72/4,1)</s:f>
         <s:v>18</s:v>
       </s:c>
-      <s:c r="F72" s="4" t="n">
+      <s:c r="E72" s="4" t="n">
         <s:v>137402232463633</s:v>
       </s:c>
-      <s:c r="G72" s="5" t="inlineStr">
+      <s:c r="F72" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_069_BulletproofJacket02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H72" s="2" t="inlineStr">
+      <s:c r="G72" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7756,22 +5543,19 @@
           <s:t>胶囊</s:t>
         </s:is>
       </s:c>
-      <s:c r="D73" s="1" t="n">
-        <s:v>3048000000000</s:v>
-      </s:c>
-      <s:c r="E73" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D73" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>15</s:v>
       </s:c>
-      <s:c r="F73" s="4" t="n">
+      <s:c r="E73" s="4" t="n">
         <s:v>79717469784936</s:v>
       </s:c>
-      <s:c r="G73" s="5" t="inlineStr">
+      <s:c r="F73" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_070_Helmet01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H73" s="2" t="inlineStr">
+      <s:c r="G73" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7789,22 +5573,19 @@
           <s:t>干电池</s:t>
         </s:is>
       </s:c>
-      <s:c r="D74" s="1" t="n">
-        <s:v>4572000000000</s:v>
-      </s:c>
-      <s:c r="E74" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D74" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="F74" s="4" t="n">
+      <s:c r="E74" s="4" t="n">
         <s:v>86646811474956</s:v>
       </s:c>
-      <s:c r="G74" s="5" t="inlineStr">
+      <s:c r="F74" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_071_Helmet02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H74" s="2" t="inlineStr">
+      <s:c r="G74" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7822,22 +5603,19 @@
           <s:t>强力电池</s:t>
         </s:is>
       </s:c>
-      <s:c r="D75" s="1" t="n">
-        <s:v>5715000000000</s:v>
-      </s:c>
-      <s:c r="E75" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D75" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="F75" s="4" t="n">
+      <s:c r="E75" s="4" t="n">
         <s:v>128217347353354</s:v>
       </s:c>
-      <s:c r="G75" s="5" t="inlineStr">
+      <s:c r="F75" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_072_Helmet03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H75" s="2" t="inlineStr">
+      <s:c r="G75" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7855,22 +5633,19 @@
           <s:t>药瓶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D76" s="1" t="n">
-        <s:v>9550000000000</s:v>
-      </s:c>
-      <s:c r="E76" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D76" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="F76" s="4" t="n">
+      <s:c r="E76" s="4" t="n">
         <s:v>126321668579357</s:v>
       </s:c>
-      <s:c r="G76" s="5" t="inlineStr">
+      <s:c r="F76" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_073_Helmet04</s:t>
         </s:is>
       </s:c>
-      <s:c r="H76" s="2" t="inlineStr">
+      <s:c r="G76" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7888,22 +5663,19 @@
           <s:t>急救药瓶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D77" s="1" t="n">
-        <s:v>15280000000000</s:v>
-      </s:c>
-      <s:c r="E77" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D77" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="F77" s="4" t="n">
+      <s:c r="E77" s="4" t="n">
         <s:v>98351529529203</s:v>
       </s:c>
-      <s:c r="G77" s="5" t="inlineStr">
+      <s:c r="F77" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_074_Bag01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H77" s="2" t="inlineStr">
+      <s:c r="G77" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7921,22 +5693,19 @@
           <s:t>注射器</s:t>
         </s:is>
       </s:c>
-      <s:c r="D78" s="1" t="n">
-        <s:v>22920000000000</s:v>
-      </s:c>
-      <s:c r="E78" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D78" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="F78" s="4" t="n">
+      <s:c r="E78" s="4" t="n">
         <s:v>81048668172712</s:v>
       </s:c>
-      <s:c r="G78" s="5" t="inlineStr">
+      <s:c r="F78" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_075_Bag02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H78" s="2" t="inlineStr">
+      <s:c r="G78" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7954,22 +5723,19 @@
           <s:t>强化针</s:t>
         </s:is>
       </s:c>
-      <s:c r="D79" s="1" t="n">
-        <s:v>28650000000000</s:v>
-      </s:c>
-      <s:c r="E79" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D79" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="F79" s="4" t="n">
+      <s:c r="E79" s="4" t="n">
         <s:v>127615544859575</s:v>
       </s:c>
-      <s:c r="G79" s="5" t="inlineStr">
+      <s:c r="F79" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_076_Bag03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H79" s="2" t="inlineStr">
+      <s:c r="G79" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -7987,22 +5753,19 @@
           <s:t>医用绷带</s:t>
         </s:is>
       </s:c>
-      <s:c r="D80" s="1" t="n">
-        <s:v>47700000000000</s:v>
-      </s:c>
-      <s:c r="E80" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D80" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="F80" s="4" t="n">
+      <s:c r="E80" s="4" t="n">
         <s:v>70656304136373</s:v>
       </s:c>
-      <s:c r="G80" s="5" t="inlineStr">
+      <s:c r="F80" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_077_Box01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H80" s="2" t="inlineStr">
+      <s:c r="G80" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8020,22 +5783,19 @@
           <s:t>绿色徽章</s:t>
         </s:is>
       </s:c>
-      <s:c r="D81" s="1" t="n">
-        <s:v>76320000000000</s:v>
-      </s:c>
-      <s:c r="E81" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D81" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="F81" s="4" t="n">
+      <s:c r="E81" s="4" t="n">
         <s:v>134424174805013</s:v>
       </s:c>
-      <s:c r="G81" s="5" t="inlineStr">
+      <s:c r="F81" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_078_Box02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H81" s="2" t="inlineStr">
+      <s:c r="G81" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8053,22 +5813,19 @@
           <s:t>急救包</s:t>
         </s:is>
       </s:c>
-      <s:c r="D82" s="1" t="n">
-        <s:v>114480000000000</s:v>
-      </s:c>
-      <s:c r="E82" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D82" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>18</s:v>
       </s:c>
-      <s:c r="F82" s="4" t="n">
+      <s:c r="E82" s="4" t="n">
         <s:v>127255485663084</s:v>
       </s:c>
-      <s:c r="G82" s="5" t="inlineStr">
+      <s:c r="F82" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_079_Box03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H82" s="2" t="inlineStr">
+      <s:c r="G82" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8086,22 +5843,19 @@
           <s:t>医疗箱</s:t>
         </s:is>
       </s:c>
-      <s:c r="D83" s="1" t="n">
-        <s:v>143100000000000</s:v>
-      </s:c>
-      <s:c r="E83" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D83" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>18</s:v>
       </s:c>
-      <s:c r="F83" s="4" t="n">
+      <s:c r="E83" s="4" t="n">
         <s:v>134027683373658</s:v>
       </s:c>
-      <s:c r="G83" s="5" t="inlineStr">
+      <s:c r="F83" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_080_Pot01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H83" s="2" t="inlineStr">
+      <s:c r="G83" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8119,22 +5873,19 @@
           <s:t>高级医疗箱</s:t>
         </s:is>
       </s:c>
-      <s:c r="D84" s="1" t="n">
-        <s:v>238500000000000</s:v>
-      </s:c>
-      <s:c r="E84" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D84" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>18</s:v>
       </s:c>
-      <s:c r="F84" s="4" t="n">
+      <s:c r="E84" s="4" t="n">
         <s:v>112447657334137</s:v>
       </s:c>
-      <s:c r="G84" s="5" t="inlineStr">
+      <s:c r="F84" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_081_Drum01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H84" s="2" t="inlineStr">
+      <s:c r="G84" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8152,22 +5903,19 @@
           <s:t>钢管</s:t>
         </s:is>
       </s:c>
-      <s:c r="D85" s="1" t="n">
-        <s:v>381600000000000</s:v>
-      </s:c>
-      <s:c r="E85" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D85" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>18</s:v>
       </s:c>
-      <s:c r="F85" s="4" t="n">
+      <s:c r="E85" s="4" t="n">
         <s:v>104595008892706</s:v>
       </s:c>
-      <s:c r="G85" s="5" t="inlineStr">
+      <s:c r="F85" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_082_Drum02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H85" s="2" t="inlineStr">
+      <s:c r="G85" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8185,22 +5933,19 @@
           <s:t>手机</s:t>
         </s:is>
       </s:c>
-      <s:c r="D86" s="1" t="n">
-        <s:v>572400000000000</s:v>
-      </s:c>
-      <s:c r="E86" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D86" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>19</s:v>
       </s:c>
-      <s:c r="F86" s="4" t="n">
+      <s:c r="E86" s="4" t="n">
         <s:v>82759045606098</s:v>
       </s:c>
-      <s:c r="G86" s="5" t="inlineStr">
+      <s:c r="F86" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_083_Drum03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H86" s="2" t="inlineStr">
+      <s:c r="G86" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8218,22 +5963,19 @@
           <s:t>手表</s:t>
         </s:is>
       </s:c>
-      <s:c r="D87" s="1" t="n">
-        <s:v>715500000000000</s:v>
-      </s:c>
-      <s:c r="E87" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D87" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>19</s:v>
       </s:c>
-      <s:c r="F87" s="4" t="n">
+      <s:c r="E87" s="4" t="n">
         <s:v>105620837789519</s:v>
       </s:c>
-      <s:c r="G87" s="5" t="inlineStr">
+      <s:c r="F87" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_084_Drum04</s:t>
         </s:is>
       </s:c>
-      <s:c r="H87" s="2" t="inlineStr">
+      <s:c r="G87" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8251,22 +5993,19 @@
           <s:t>身份牌</s:t>
         </s:is>
       </s:c>
-      <s:c r="D88" s="1" t="n">
-        <s:v>1190000000000000</s:v>
-      </s:c>
-      <s:c r="E88" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D88" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>19</s:v>
       </s:c>
-      <s:c r="F88" s="4" t="n">
+      <s:c r="E88" s="4" t="n">
         <s:v>111024567754480</s:v>
       </s:c>
-      <s:c r="G88" s="5" t="inlineStr">
+      <s:c r="F88" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_085_Drum05</s:t>
         </s:is>
       </s:c>
-      <s:c r="H88" s="2" t="inlineStr">
+      <s:c r="G88" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8284,22 +6023,19 @@
           <s:t>指南针</s:t>
         </s:is>
       </s:c>
-      <s:c r="D89" s="1" t="n">
-        <s:v>1904000000000000</s:v>
-      </s:c>
-      <s:c r="E89" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D89" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>19</s:v>
       </s:c>
-      <s:c r="F89" s="4" t="n">
+      <s:c r="E89" s="4" t="n">
         <s:v>137153989969007</s:v>
       </s:c>
-      <s:c r="G89" s="5" t="inlineStr">
+      <s:c r="F89" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_086_Propane</s:t>
         </s:is>
       </s:c>
-      <s:c r="H89" s="2" t="inlineStr">
+      <s:c r="G89" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8317,22 +6053,19 @@
           <s:t>军用罗盘</s:t>
         </s:is>
       </s:c>
-      <s:c r="D90" s="1" t="n">
-        <s:v>2856000000000000</s:v>
-      </s:c>
-      <s:c r="E90" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D90" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>20</s:v>
       </s:c>
-      <s:c r="F90" s="4" t="n">
+      <s:c r="E90" s="4" t="n">
         <s:v>74496996195913</s:v>
       </s:c>
-      <s:c r="G90" s="5" t="inlineStr">
+      <s:c r="F90" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_087_RopeA</s:t>
         </s:is>
       </s:c>
-      <s:c r="H90" s="2" t="inlineStr">
+      <s:c r="G90" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8350,22 +6083,19 @@
           <s:t>木箱</s:t>
         </s:is>
       </s:c>
-      <s:c r="D91" s="1" t="n">
-        <s:v>3570000000000000</s:v>
-      </s:c>
-      <s:c r="E91" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D91" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>20</s:v>
       </s:c>
-      <s:c r="F91" s="4" t="n">
+      <s:c r="E91" s="4" t="n">
         <s:v>132785860315163</s:v>
       </s:c>
-      <s:c r="G91" s="5" t="inlineStr">
+      <s:c r="F91" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_088_Wire</s:t>
         </s:is>
       </s:c>
-      <s:c r="H91" s="2" t="inlineStr">
+      <s:c r="G91" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8383,22 +6113,19 @@
           <s:t>工具箱</s:t>
         </s:is>
       </s:c>
-      <s:c r="D92" s="1" t="n">
-        <s:v>5950000000000000</s:v>
-      </s:c>
-      <s:c r="E92" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D92" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>20</s:v>
       </s:c>
-      <s:c r="F92" s="4" t="n">
+      <s:c r="E92" s="4" t="n">
         <s:v>117198962948319</s:v>
       </s:c>
-      <s:c r="G92" s="5" t="inlineStr">
+      <s:c r="F92" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_089_Walkie_Talkie</s:t>
         </s:is>
       </s:c>
-      <s:c r="H92" s="2" t="inlineStr">
+      <s:c r="G92" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8416,22 +6143,19 @@
           <s:t>补给箱</s:t>
         </s:is>
       </s:c>
-      <s:c r="D93" s="1" t="n">
-        <s:v>9520000000000000</s:v>
-      </s:c>
-      <s:c r="E93" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D93" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>20</s:v>
       </s:c>
-      <s:c r="F93" s="4" t="n">
+      <s:c r="E93" s="4" t="n">
         <s:v>124449160476895</s:v>
       </s:c>
-      <s:c r="G93" s="5" t="inlineStr">
+      <s:c r="F93" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_090_Walkie_TalkieA</s:t>
         </s:is>
       </s:c>
-      <s:c r="H93" s="2" t="inlineStr">
+      <s:c r="G93" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8449,22 +6173,19 @@
           <s:t>油桶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D94" s="1" t="n">
-        <s:v>1.428e+16</s:v>
-      </s:c>
-      <s:c r="E94" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D94" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>21</s:v>
       </s:c>
-      <s:c r="F94" s="4" t="n">
+      <s:c r="E94" s="4" t="n">
         <s:v>125887863438527</s:v>
       </s:c>
-      <s:c r="G94" s="5" t="inlineStr">
+      <s:c r="F94" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_091_Flashlight01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H94" s="2" t="inlineStr">
+      <s:c r="G94" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8482,22 +6203,19 @@
           <s:t>储物桶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D95" s="1" t="n">
-        <s:v>1.785e+16</s:v>
-      </s:c>
-      <s:c r="E95" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D95" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>21</s:v>
       </s:c>
-      <s:c r="F95" s="4" t="n">
+      <s:c r="E95" s="4" t="n">
         <s:v>137692564728429</s:v>
       </s:c>
-      <s:c r="G95" s="5" t="inlineStr">
+      <s:c r="F95" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_092_HeadLantern</s:t>
         </s:is>
       </s:c>
-      <s:c r="H95" s="2" t="inlineStr">
+      <s:c r="G95" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8515,22 +6233,19 @@
           <s:t>密封桶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D96" s="1" t="n">
-        <s:v>2.98e+16</s:v>
-      </s:c>
-      <s:c r="E96" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D96" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>21</s:v>
       </s:c>
-      <s:c r="F96" s="4" t="n">
+      <s:c r="E96" s="4" t="n">
         <s:v>82350951870220</s:v>
       </s:c>
-      <s:c r="G96" s="5" t="inlineStr">
+      <s:c r="F96" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_093_Lantern</s:t>
         </s:is>
       </s:c>
-      <s:c r="H96" s="2" t="inlineStr">
+      <s:c r="G96" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8548,22 +6263,19 @@
           <s:t>大铁桶</s:t>
         </s:is>
       </s:c>
-      <s:c r="D97" s="1" t="n">
-        <s:v>4.768e+16</s:v>
-      </s:c>
-      <s:c r="E97" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D97" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>21</s:v>
       </s:c>
-      <s:c r="F97" s="4" t="n">
+      <s:c r="E97" s="4" t="n">
         <s:v>133019385929561</s:v>
       </s:c>
-      <s:c r="G97" s="5" t="inlineStr">
+      <s:c r="F97" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_094_Telescope01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H97" s="2" t="inlineStr">
+      <s:c r="G97" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8581,22 +6293,19 @@
           <s:t>煤气罐</s:t>
         </s:is>
       </s:c>
-      <s:c r="D98" s="1" t="n">
-        <s:v>7.152e+16</s:v>
-      </s:c>
-      <s:c r="E98" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D98" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>22</s:v>
       </s:c>
-      <s:c r="F98" s="4" t="n">
+      <s:c r="E98" s="4" t="n">
         <s:v>82714807302588</s:v>
       </s:c>
-      <s:c r="G98" s="5" t="inlineStr">
+      <s:c r="F98" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_095_Telescope02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H98" s="2" t="inlineStr">
+      <s:c r="G98" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8614,22 +6323,19 @@
           <s:t>粗绳</s:t>
         </s:is>
       </s:c>
-      <s:c r="D99" s="1" t="n">
-        <s:v>8.94e+16</s:v>
-      </s:c>
-      <s:c r="E99" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D99" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>22</s:v>
       </s:c>
-      <s:c r="F99" s="4" t="n">
+      <s:c r="E99" s="4" t="n">
         <s:v>120409278538446</s:v>
       </s:c>
-      <s:c r="G99" s="5" t="inlineStr">
+      <s:c r="F99" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_096_Hammer01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H99" s="2" t="inlineStr">
+      <s:c r="G99" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8647,22 +6353,19 @@
           <s:t>电线</s:t>
         </s:is>
       </s:c>
-      <s:c r="D100" s="1" t="n">
-        <s:v>1.49e+17</s:v>
-      </s:c>
-      <s:c r="E100" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D100" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>22</s:v>
       </s:c>
-      <s:c r="F100" s="4" t="n">
+      <s:c r="E100" s="4" t="n">
         <s:v>136303201068741</s:v>
       </s:c>
-      <s:c r="G100" s="5" t="inlineStr">
+      <s:c r="F100" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_097_Hammer02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H100" s="2" t="inlineStr">
+      <s:c r="G100" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8680,22 +6383,19 @@
           <s:t>对讲机</s:t>
         </s:is>
       </s:c>
-      <s:c r="D101" s="1" t="n">
-        <s:v>2.384e+17</s:v>
-      </s:c>
-      <s:c r="E101" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D101" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>22</s:v>
       </s:c>
-      <s:c r="F101" s="4" t="n">
+      <s:c r="E101" s="4" t="n">
         <s:v>76724781858184</s:v>
       </s:c>
-      <s:c r="G101" s="5" t="inlineStr">
+      <s:c r="F101" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_098_Hammer03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H101" s="2" t="inlineStr">
+      <s:c r="G101" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8713,22 +6413,19 @@
           <s:t>军用电台</s:t>
         </s:is>
       </s:c>
-      <s:c r="D102" s="1" t="n">
-        <s:v>3.576e+17</s:v>
-      </s:c>
-      <s:c r="E102" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D102" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>23</s:v>
       </s:c>
-      <s:c r="F102" s="4" t="n">
+      <s:c r="E102" s="4" t="n">
         <s:v>120125979830927</s:v>
       </s:c>
-      <s:c r="G102" s="5" t="inlineStr">
+      <s:c r="F102" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_099_Wrench01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H102" s="2" t="inlineStr">
+      <s:c r="G102" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8746,22 +6443,19 @@
           <s:t>手电筒</s:t>
         </s:is>
       </s:c>
-      <s:c r="D103" s="1" t="n">
-        <s:v>4.47e+17</s:v>
-      </s:c>
-      <s:c r="E103" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D103" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>23</s:v>
       </s:c>
-      <s:c r="F103" s="4" t="n">
+      <s:c r="E103" s="4" t="n">
         <s:v>86921870572603</s:v>
       </s:c>
-      <s:c r="G103" s="5" t="inlineStr">
+      <s:c r="F103" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_100_Wrench02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H103" s="2" t="inlineStr">
+      <s:c r="G103" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8779,22 +6473,19 @@
           <s:t>头灯</s:t>
         </s:is>
       </s:c>
-      <s:c r="D104" s="1" t="n">
-        <s:v>7.45e+17</s:v>
-      </s:c>
-      <s:c r="E104" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D104" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>23</s:v>
       </s:c>
-      <s:c r="F104" s="4" t="n">
+      <s:c r="E104" s="4" t="n">
         <s:v>126355990231048</s:v>
       </s:c>
-      <s:c r="G104" s="5" t="inlineStr">
+      <s:c r="F104" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_101_Wrench03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H104" s="2" t="inlineStr">
+      <s:c r="G104" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8812,22 +6503,19 @@
           <s:t>提灯</s:t>
         </s:is>
       </s:c>
-      <s:c r="D105" s="1" t="n">
-        <s:v>1.192e+18</s:v>
-      </s:c>
-      <s:c r="E105" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D105" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>23</s:v>
       </s:c>
-      <s:c r="F105" s="4" t="n">
+      <s:c r="E105" s="4" t="n">
         <s:v>72326444062448</s:v>
       </s:c>
-      <s:c r="G105" s="5" t="inlineStr">
+      <s:c r="F105" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_102_Shovel01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H105" s="2" t="inlineStr">
+      <s:c r="G105" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8845,22 +6533,19 @@
           <s:t>望远镜</s:t>
         </s:is>
       </s:c>
-      <s:c r="D106" s="1" t="n">
-        <s:v>1.788e+18</s:v>
-      </s:c>
-      <s:c r="E106" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D106" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>24</s:v>
       </s:c>
-      <s:c r="F106" s="4" t="n">
+      <s:c r="E106" s="4" t="n">
         <s:v>72257499044823</s:v>
       </s:c>
-      <s:c r="G106" s="5" t="inlineStr">
+      <s:c r="F106" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_103_Shovel02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H106" s="2" t="inlineStr">
+      <s:c r="G106" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8878,22 +6563,19 @@
           <s:t>高倍望远镜</s:t>
         </s:is>
       </s:c>
-      <s:c r="D107" s="1" t="n">
-        <s:v>2.235e+18</s:v>
-      </s:c>
-      <s:c r="E107" s="1">
-        <s:f>INT((ROW()-ROW(ItemData!$E$14))/4)+1</s:f>
+      <s:c r="D107" s="1">
+        <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>24</s:v>
       </s:c>
-      <s:c r="F107" s="4" t="n">
+      <s:c r="E107" s="4" t="n">
         <s:v>74695865349139</s:v>
       </s:c>
-      <s:c r="G107" s="5" t="inlineStr">
+      <s:c r="F107" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_104_Pickax</s:t>
         </s:is>
       </s:c>
-      <s:c r="H107" s="2" t="inlineStr">
+      <s:c r="G107" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -8912,25 +6594,22 @@
         </s:is>
       </s:c>
       <s:c r="D108" s="1" t="n">
-        <s:v>3.725e+18</s:v>
-      </s:c>
-      <s:c r="E108" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="F108" s="4" t="n">
+      <s:c r="E108" s="4" t="n">
         <s:v>98358488442985</s:v>
       </s:c>
-      <s:c r="G108" s="5" t="inlineStr">
+      <s:c r="F108" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_105_GolfClub</s:t>
         </s:is>
       </s:c>
-      <s:c r="H108" s="2" t="inlineStr">
+      <s:c r="G108" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I108" s="3" t="n"/>
+      <s:c r="H108" s="3" t="n"/>
     </s:row>
     <s:row r="109" ht="15.6" customHeight="1" s="28">
       <s:c r="A109" s="1" t="n">
@@ -8945,25 +6624,22 @@
         </s:is>
       </s:c>
       <s:c r="D109" s="1" t="n">
-        <s:v>5.96e+18</s:v>
-      </s:c>
-      <s:c r="E109" s="1" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="F109" s="4" t="n">
+      <s:c r="E109" s="4" t="n">
         <s:v>113636295509693</s:v>
       </s:c>
-      <s:c r="G109" s="5" t="inlineStr">
+      <s:c r="F109" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_106_Hockey</s:t>
         </s:is>
       </s:c>
-      <s:c r="H109" s="2" t="inlineStr">
+      <s:c r="G109" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I109" s="3" t="n"/>
+      <s:c r="H109" s="3" t="n"/>
     </s:row>
     <s:row r="110" ht="15.6" customHeight="1" s="28">
       <s:c r="A110" s="1" t="n">
@@ -8978,25 +6654,22 @@
         </s:is>
       </s:c>
       <s:c r="D110" s="1" t="n">
-        <s:v>8.94e+18</s:v>
-      </s:c>
-      <s:c r="E110" s="1" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="F110" s="4" t="n">
+      <s:c r="E110" s="4" t="n">
         <s:v>114047124407739</s:v>
       </s:c>
-      <s:c r="G110" s="5" t="inlineStr">
+      <s:c r="F110" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_107_Bat01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H110" s="2" t="inlineStr">
+      <s:c r="G110" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I110" s="3" t="n"/>
+      <s:c r="H110" s="3" t="n"/>
     </s:row>
     <s:row r="111" ht="15.6" customHeight="1" s="28">
       <s:c r="A111" s="1" t="n">
@@ -9011,25 +6684,22 @@
         </s:is>
       </s:c>
       <s:c r="D111" s="1" t="n">
-        <s:v>1.1175e+19</s:v>
-      </s:c>
-      <s:c r="E111" s="1" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="F111" s="4" t="n">
+      <s:c r="E111" s="4" t="n">
         <s:v>95771403493939</s:v>
       </s:c>
-      <s:c r="G111" s="5" t="inlineStr">
+      <s:c r="F111" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_108_Bat02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H111" s="2" t="inlineStr">
+      <s:c r="G111" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I111" s="3" t="n"/>
+      <s:c r="H111" s="3" t="n"/>
     </s:row>
     <s:row r="112" ht="15.6" customHeight="1" s="28">
       <s:c r="A112" s="1" t="n">
@@ -9044,25 +6714,22 @@
         </s:is>
       </s:c>
       <s:c r="D112" s="1" t="n">
-        <s:v>1.865e+19</s:v>
-      </s:c>
-      <s:c r="E112" s="1" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="F112" s="4" t="n">
+      <s:c r="E112" s="4" t="n">
         <s:v>140393673870516</s:v>
       </s:c>
-      <s:c r="G112" s="5" t="inlineStr">
+      <s:c r="F112" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_109_Bat03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H112" s="2" t="inlineStr">
+      <s:c r="G112" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I112" s="3" t="n"/>
+      <s:c r="H112" s="3" t="n"/>
     </s:row>
     <s:row r="113" ht="15.6" customHeight="1" s="28">
       <s:c r="A113" s="1" t="n">
@@ -9077,25 +6744,22 @@
         </s:is>
       </s:c>
       <s:c r="D113" s="1" t="n">
-        <s:v>2.984e+19</s:v>
-      </s:c>
-      <s:c r="E113" s="1" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="F113" s="4" t="n">
+      <s:c r="E113" s="4" t="n">
         <s:v>123109322631502</s:v>
       </s:c>
-      <s:c r="G113" s="5" t="inlineStr">
+      <s:c r="F113" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_110_Bat04</s:t>
         </s:is>
       </s:c>
-      <s:c r="H113" s="2" t="inlineStr">
+      <s:c r="G113" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I113" s="3" t="n"/>
+      <s:c r="H113" s="3" t="n"/>
     </s:row>
     <s:row r="114" ht="15.6" customHeight="1" s="28">
       <s:c r="A114" s="1" t="n">
@@ -9110,25 +6774,22 @@
         </s:is>
       </s:c>
       <s:c r="D114" s="1" t="n">
-        <s:v>4.476e+19</s:v>
-      </s:c>
-      <s:c r="E114" s="1" t="n">
         <s:v>26</s:v>
       </s:c>
-      <s:c r="F114" s="4" t="n">
+      <s:c r="E114" s="4" t="n">
         <s:v>98614967981417</s:v>
       </s:c>
-      <s:c r="G114" s="5" t="inlineStr">
+      <s:c r="F114" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_111_ElectricSaw</s:t>
         </s:is>
       </s:c>
-      <s:c r="H114" s="2" t="inlineStr">
+      <s:c r="G114" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I114" s="3" t="n"/>
+      <s:c r="H114" s="3" t="n"/>
     </s:row>
     <s:row r="115" ht="15.6" customHeight="1" s="28">
       <s:c r="A115" s="1" t="n">
@@ -9143,25 +6804,22 @@
         </s:is>
       </s:c>
       <s:c r="D115" s="1" t="n">
-        <s:v>5.595e+19</s:v>
-      </s:c>
-      <s:c r="E115" s="1" t="n">
         <s:v>26</s:v>
       </s:c>
-      <s:c r="F115" s="4" t="n">
+      <s:c r="E115" s="4" t="n">
         <s:v>127369769981706</s:v>
       </s:c>
-      <s:c r="G115" s="5" t="inlineStr">
+      <s:c r="F115" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_112_Ax01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H115" s="2" t="inlineStr">
+      <s:c r="G115" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I115" s="3" t="n"/>
+      <s:c r="H115" s="3" t="n"/>
     </s:row>
     <s:row r="116" ht="15.6" customHeight="1" s="28">
       <s:c r="A116" s="1" t="n">
@@ -9176,25 +6834,22 @@
         </s:is>
       </s:c>
       <s:c r="D116" s="1" t="n">
-        <s:v>9.3e+19</s:v>
-      </s:c>
-      <s:c r="E116" s="1" t="n">
         <s:v>26</s:v>
       </s:c>
-      <s:c r="F116" s="4" t="n">
+      <s:c r="E116" s="4" t="n">
         <s:v>134574393827781</s:v>
       </s:c>
-      <s:c r="G116" s="5" t="inlineStr">
+      <s:c r="F116" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_113_Ax02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H116" s="2" t="inlineStr">
+      <s:c r="G116" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I116" s="3" t="n"/>
+      <s:c r="H116" s="3" t="n"/>
     </s:row>
     <s:row r="117" ht="15.6" customHeight="1" s="28">
       <s:c r="A117" s="1" t="n">
@@ -9209,25 +6864,22 @@
         </s:is>
       </s:c>
       <s:c r="D117" s="1" t="n">
-        <s:v>1.488e+20</s:v>
-      </s:c>
-      <s:c r="E117" s="1" t="n">
         <s:v>26</s:v>
       </s:c>
-      <s:c r="F117" s="4" t="n">
+      <s:c r="E117" s="4" t="n">
         <s:v>130258203281991</s:v>
       </s:c>
-      <s:c r="G117" s="5" t="inlineStr">
+      <s:c r="F117" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_114_Ax03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H117" s="2" t="inlineStr">
+      <s:c r="G117" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I117" s="3" t="n"/>
+      <s:c r="H117" s="3" t="n"/>
     </s:row>
     <s:row r="118" ht="15.6" customHeight="1" s="28">
       <s:c r="A118" s="1" t="n">
@@ -9242,25 +6894,22 @@
         </s:is>
       </s:c>
       <s:c r="D118" s="1" t="n">
-        <s:v>2.232e+20</s:v>
-      </s:c>
-      <s:c r="E118" s="1" t="n">
         <s:v>27</s:v>
       </s:c>
-      <s:c r="F118" s="4" t="n">
+      <s:c r="E118" s="4" t="n">
         <s:v>93953823085119</s:v>
       </s:c>
-      <s:c r="G118" s="5" t="inlineStr">
+      <s:c r="F118" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_115_Knife01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H118" s="2" t="inlineStr">
+      <s:c r="G118" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I118" s="3" t="n"/>
+      <s:c r="H118" s="3" t="n"/>
     </s:row>
     <s:row r="119" ht="15.6" customHeight="1" s="28">
       <s:c r="A119" s="1" t="n">
@@ -9275,25 +6924,22 @@
         </s:is>
       </s:c>
       <s:c r="D119" s="1" t="n">
-        <s:v>2.79e+20</s:v>
-      </s:c>
-      <s:c r="E119" s="1" t="n">
         <s:v>27</s:v>
       </s:c>
-      <s:c r="F119" s="4" t="n">
+      <s:c r="E119" s="4" t="n">
         <s:v>109802560542166</s:v>
       </s:c>
-      <s:c r="G119" s="5" t="inlineStr">
+      <s:c r="F119" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_116_Knife02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H119" s="2" t="inlineStr">
+      <s:c r="G119" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I119" s="3" t="n"/>
+      <s:c r="H119" s="3" t="n"/>
     </s:row>
     <s:row r="120" ht="15.6" customHeight="1" s="28">
       <s:c r="A120" s="1" t="n">
@@ -9308,25 +6954,22 @@
         </s:is>
       </s:c>
       <s:c r="D120" s="1" t="n">
-        <s:v>4.655e+20</s:v>
-      </s:c>
-      <s:c r="E120" s="1" t="n">
         <s:v>27</s:v>
       </s:c>
-      <s:c r="F120" s="4" t="n">
+      <s:c r="E120" s="4" t="n">
         <s:v>130989494782889</s:v>
       </s:c>
-      <s:c r="G120" s="5" t="inlineStr">
+      <s:c r="F120" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_117_Knife03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H120" s="2" t="inlineStr">
+      <s:c r="G120" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I120" s="3" t="n"/>
+      <s:c r="H120" s="3" t="n"/>
     </s:row>
     <s:row r="121" ht="15.6" customHeight="1" s="28">
       <s:c r="A121" s="1" t="n">
@@ -9341,25 +6984,22 @@
         </s:is>
       </s:c>
       <s:c r="D121" s="1" t="n">
-        <s:v>7.448e+20</s:v>
-      </s:c>
-      <s:c r="E121" s="1" t="n">
         <s:v>27</s:v>
       </s:c>
-      <s:c r="F121" s="4" t="n">
+      <s:c r="E121" s="4" t="n">
         <s:v>129408716253336</s:v>
       </s:c>
-      <s:c r="G121" s="5" t="inlineStr">
+      <s:c r="F121" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_118_Knife04</s:t>
         </s:is>
       </s:c>
-      <s:c r="H121" s="2" t="inlineStr">
+      <s:c r="G121" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I121" s="3" t="n"/>
+      <s:c r="H121" s="3" t="n"/>
     </s:row>
     <s:row r="122" ht="15.6" customHeight="1" s="28">
       <s:c r="A122" s="1" t="n">
@@ -9374,25 +7014,22 @@
         </s:is>
       </s:c>
       <s:c r="D122" s="1" t="n">
-        <s:v>1.1172e+21</s:v>
-      </s:c>
-      <s:c r="E122" s="1" t="n">
         <s:v>28</s:v>
       </s:c>
-      <s:c r="F122" s="4" t="n">
+      <s:c r="E122" s="4" t="n">
         <s:v>127772866805590</s:v>
       </s:c>
-      <s:c r="G122" s="5" t="inlineStr">
+      <s:c r="F122" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_119_Knife05</s:t>
         </s:is>
       </s:c>
-      <s:c r="H122" s="2" t="inlineStr">
+      <s:c r="G122" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I122" s="3" t="n"/>
+      <s:c r="H122" s="3" t="n"/>
     </s:row>
     <s:row r="123" ht="15.6" customHeight="1" s="28">
       <s:c r="A123" s="1" t="n">
@@ -9407,25 +7044,22 @@
         </s:is>
       </s:c>
       <s:c r="D123" s="1" t="n">
-        <s:v>1.3965e+21</s:v>
-      </s:c>
-      <s:c r="E123" s="1" t="n">
         <s:v>28</s:v>
       </s:c>
-      <s:c r="F123" s="4" t="n">
+      <s:c r="E123" s="4" t="n">
         <s:v>91938109188463</s:v>
       </s:c>
-      <s:c r="G123" s="5" t="inlineStr">
+      <s:c r="F123" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_120_Knife06</s:t>
         </s:is>
       </s:c>
-      <s:c r="H123" s="2" t="inlineStr">
+      <s:c r="G123" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I123" s="3" t="n"/>
+      <s:c r="H123" s="3" t="n"/>
     </s:row>
     <s:row r="124" ht="15.6" customHeight="1" s="28">
       <s:c r="A124" s="1" t="n">
@@ -9440,25 +7074,22 @@
         </s:is>
       </s:c>
       <s:c r="D124" s="1" t="n">
-        <s:v>2.33e+21</s:v>
-      </s:c>
-      <s:c r="E124" s="1" t="n">
         <s:v>28</s:v>
       </s:c>
-      <s:c r="F124" s="4" t="n">
+      <s:c r="E124" s="4" t="n">
         <s:v>85077262752129</s:v>
       </s:c>
-      <s:c r="G124" s="5" t="inlineStr">
+      <s:c r="F124" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_121_Ironmace</s:t>
         </s:is>
       </s:c>
-      <s:c r="H124" s="2" t="inlineStr">
+      <s:c r="G124" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
       </s:c>
-      <s:c r="I124" s="3" t="n"/>
+      <s:c r="H124" s="3" t="n"/>
     </s:row>
     <s:row r="125" ht="15.6" customHeight="1" s="28">
       <s:c r="A125" s="1" t="n">
@@ -9473,20 +7104,17 @@
         </s:is>
       </s:c>
       <s:c r="D125" s="1" t="n">
-        <s:v>3.728e+21</s:v>
-      </s:c>
-      <s:c r="E125" s="1" t="n">
         <s:v>28</s:v>
       </s:c>
-      <s:c r="F125" s="4" t="n">
+      <s:c r="E125" s="4" t="n">
         <s:v>140335958193244</s:v>
       </s:c>
-      <s:c r="G125" s="5" t="inlineStr">
+      <s:c r="F125" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_122_Dynamite01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H125" s="2" t="inlineStr">
+      <s:c r="G125" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9505,20 +7133,17 @@
         </s:is>
       </s:c>
       <s:c r="D126" s="1" t="n">
-        <s:v>5.592e+21</s:v>
-      </s:c>
-      <s:c r="E126" s="1" t="n">
         <s:v>29</s:v>
       </s:c>
-      <s:c r="F126" s="4" t="n">
+      <s:c r="E126" s="4" t="n">
         <s:v>86732012145983</s:v>
       </s:c>
-      <s:c r="G126" s="5" t="inlineStr">
+      <s:c r="F126" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_123_Dynamite02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H126" s="2" t="inlineStr">
+      <s:c r="G126" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9537,20 +7162,17 @@
         </s:is>
       </s:c>
       <s:c r="D127" s="1" t="n">
-        <s:v>6.990000000000001e+21</s:v>
-      </s:c>
-      <s:c r="E127" s="1" t="n">
         <s:v>29</s:v>
       </s:c>
-      <s:c r="F127" s="4" t="n">
+      <s:c r="E127" s="4" t="n">
         <s:v>78044122276865</s:v>
       </s:c>
-      <s:c r="G127" s="5" t="inlineStr">
+      <s:c r="F127" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_124_Dynamite03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H127" s="2" t="inlineStr">
+      <s:c r="G127" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9569,20 +7191,17 @@
         </s:is>
       </s:c>
       <s:c r="D128" s="1" t="n">
-        <s:v>1.165e+22</s:v>
-      </s:c>
-      <s:c r="E128" s="1" t="n">
         <s:v>29</s:v>
       </s:c>
-      <s:c r="F128" s="4" t="n">
+      <s:c r="E128" s="4" t="n">
         <s:v>114974638199136</s:v>
       </s:c>
-      <s:c r="G128" s="5" t="inlineStr">
+      <s:c r="F128" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_125_Grenade01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H128" s="2" t="inlineStr">
+      <s:c r="G128" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9601,20 +7220,17 @@
         </s:is>
       </s:c>
       <s:c r="D129" s="1" t="n">
-        <s:v>1.864e+22</s:v>
-      </s:c>
-      <s:c r="E129" s="1" t="n">
         <s:v>29</s:v>
       </s:c>
-      <s:c r="F129" s="4" t="n">
+      <s:c r="E129" s="4" t="n">
         <s:v>83652207307759</s:v>
       </s:c>
-      <s:c r="G129" s="5" t="inlineStr">
+      <s:c r="F129" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_126_Grenade02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H129" s="2" t="inlineStr">
+      <s:c r="G129" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9633,20 +7249,17 @@
         </s:is>
       </s:c>
       <s:c r="D130" s="1" t="n">
-        <s:v>2.796e+22</s:v>
-      </s:c>
-      <s:c r="E130" s="1" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="F130" s="4" t="n">
+      <s:c r="E130" s="4" t="n">
         <s:v>131787091355052</s:v>
       </s:c>
-      <s:c r="G130" s="5" t="inlineStr">
+      <s:c r="F130" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_127_Grenade03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H130" s="2" t="inlineStr">
+      <s:c r="G130" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9665,20 +7278,17 @@
         </s:is>
       </s:c>
       <s:c r="D131" s="1" t="n">
-        <s:v>3.495e+22</s:v>
-      </s:c>
-      <s:c r="E131" s="1" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="F131" s="4" t="n">
+      <s:c r="E131" s="4" t="n">
         <s:v>99348381699835</s:v>
       </s:c>
-      <s:c r="G131" s="5" t="inlineStr">
+      <s:c r="F131" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_128_Mine</s:t>
         </s:is>
       </s:c>
-      <s:c r="H131" s="2" t="inlineStr">
+      <s:c r="G131" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9697,20 +7307,17 @@
         </s:is>
       </s:c>
       <s:c r="D132" s="1" t="n">
-        <s:v>5.8e+22</s:v>
-      </s:c>
-      <s:c r="E132" s="1" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="F132" s="4" t="n">
+      <s:c r="E132" s="4" t="n">
         <s:v>75412160560516</s:v>
       </s:c>
-      <s:c r="G132" s="5" t="inlineStr">
+      <s:c r="F132" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_129_Trap</s:t>
         </s:is>
       </s:c>
-      <s:c r="H132" s="2" t="inlineStr">
+      <s:c r="G132" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9729,20 +7336,17 @@
         </s:is>
       </s:c>
       <s:c r="D133" s="1" t="n">
-        <s:v>9.28e+22</s:v>
-      </s:c>
-      <s:c r="E133" s="1" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="F133" s="4" t="n">
+      <s:c r="E133" s="4" t="n">
         <s:v>105475505052937</s:v>
       </s:c>
-      <s:c r="G133" s="5" t="inlineStr">
+      <s:c r="F133" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_130_Bullet01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H133" s="2" t="inlineStr">
+      <s:c r="G133" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9761,20 +7365,17 @@
         </s:is>
       </s:c>
       <s:c r="D134" s="1" t="n">
-        <s:v>1.392e+23</s:v>
-      </s:c>
-      <s:c r="E134" s="1" t="n">
         <s:v>31</s:v>
       </s:c>
-      <s:c r="F134" s="4" t="n">
+      <s:c r="E134" s="4" t="n">
         <s:v>125484119033793</s:v>
       </s:c>
-      <s:c r="G134" s="5" t="inlineStr">
+      <s:c r="F134" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_131_Bullet02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H134" s="2" t="inlineStr">
+      <s:c r="G134" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9793,20 +7394,17 @@
         </s:is>
       </s:c>
       <s:c r="D135" s="1" t="n">
-        <s:v>1.74e+23</s:v>
-      </s:c>
-      <s:c r="E135" s="1" t="n">
         <s:v>31</s:v>
       </s:c>
-      <s:c r="F135" s="4" t="n">
+      <s:c r="E135" s="4" t="n">
         <s:v>140608831780254</s:v>
       </s:c>
-      <s:c r="G135" s="5" t="inlineStr">
+      <s:c r="F135" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_132_Bullet03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H135" s="2" t="inlineStr">
+      <s:c r="G135" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9825,20 +7423,17 @@
         </s:is>
       </s:c>
       <s:c r="D136" s="1" t="n">
-        <s:v>2.91e+23</s:v>
-      </s:c>
-      <s:c r="E136" s="1" t="n">
         <s:v>31</s:v>
       </s:c>
-      <s:c r="F136" s="4" t="n">
+      <s:c r="E136" s="4" t="n">
         <s:v>124177358025481</s:v>
       </s:c>
-      <s:c r="G136" s="5" t="inlineStr">
+      <s:c r="F136" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_133_Bullet04</s:t>
         </s:is>
       </s:c>
-      <s:c r="H136" s="2" t="inlineStr">
+      <s:c r="G136" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9857,20 +7452,17 @@
         </s:is>
       </s:c>
       <s:c r="D137" s="1" t="n">
-        <s:v>4.656e+23</s:v>
-      </s:c>
-      <s:c r="E137" s="1" t="n">
         <s:v>31</s:v>
       </s:c>
-      <s:c r="F137" s="4" t="n">
+      <s:c r="E137" s="4" t="n">
         <s:v>129385390119523</s:v>
       </s:c>
-      <s:c r="G137" s="5" t="inlineStr">
+      <s:c r="F137" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_134_Bullet05</s:t>
         </s:is>
       </s:c>
-      <s:c r="H137" s="2" t="inlineStr">
+      <s:c r="G137" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9889,20 +7481,17 @@
         </s:is>
       </s:c>
       <s:c r="D138" s="1" t="n">
-        <s:v>6.984000000000001e+23</s:v>
-      </s:c>
-      <s:c r="E138" s="1" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="F138" s="4" t="n">
+      <s:c r="E138" s="4" t="n">
         <s:v>84940520003035</s:v>
       </s:c>
-      <s:c r="G138" s="5" t="inlineStr">
+      <s:c r="F138" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_135_Bullet06</s:t>
         </s:is>
       </s:c>
-      <s:c r="H138" s="2" t="inlineStr">
+      <s:c r="G138" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9921,20 +7510,17 @@
         </s:is>
       </s:c>
       <s:c r="D139" s="1" t="n">
-        <s:v>8.73e+23</s:v>
-      </s:c>
-      <s:c r="E139" s="1" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="F139" s="4" t="n">
+      <s:c r="E139" s="4" t="n">
         <s:v>90031364711610</s:v>
       </s:c>
-      <s:c r="G139" s="5" t="inlineStr">
+      <s:c r="F139" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_136_Bullet07</s:t>
         </s:is>
       </s:c>
-      <s:c r="H139" s="2" t="inlineStr">
+      <s:c r="G139" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9953,20 +7539,17 @@
         </s:is>
       </s:c>
       <s:c r="D140" s="1" t="n">
-        <s:v>1.455e+24</s:v>
-      </s:c>
-      <s:c r="E140" s="1" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="F140" s="4" t="n">
+      <s:c r="E140" s="4" t="n">
         <s:v>84418341821320</s:v>
       </s:c>
-      <s:c r="G140" s="5" t="inlineStr">
+      <s:c r="F140" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_137_Cartridge</s:t>
         </s:is>
       </s:c>
-      <s:c r="H140" s="2" t="inlineStr">
+      <s:c r="G140" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -9985,20 +7568,17 @@
         </s:is>
       </s:c>
       <s:c r="D141" s="1" t="n">
-        <s:v>2.328e+24</s:v>
-      </s:c>
-      <s:c r="E141" s="1" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="F141" s="4" t="n">
+      <s:c r="E141" s="4" t="n">
         <s:v>130255705800444</s:v>
       </s:c>
-      <s:c r="G141" s="5" t="inlineStr">
+      <s:c r="F141" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_138_Gun01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H141" s="2" t="inlineStr">
+      <s:c r="G141" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -10017,20 +7597,17 @@
         </s:is>
       </s:c>
       <s:c r="D142" s="1" t="n">
-        <s:v>3.492e+24</s:v>
-      </s:c>
-      <s:c r="E142" s="1" t="n">
         <s:v>33</s:v>
       </s:c>
-      <s:c r="F142" s="4" t="n">
+      <s:c r="E142" s="4" t="n">
         <s:v>123568265278671</s:v>
       </s:c>
-      <s:c r="G142" s="5" t="inlineStr">
+      <s:c r="F142" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_139_Gun02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H142" s="2" t="inlineStr">
+      <s:c r="G142" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -10049,20 +7626,17 @@
         </s:is>
       </s:c>
       <s:c r="D143" s="1" t="n">
-        <s:v>4.365e+24</s:v>
-      </s:c>
-      <s:c r="E143" s="1" t="n">
         <s:v>33</s:v>
       </s:c>
-      <s:c r="F143" s="4" t="n">
+      <s:c r="E143" s="4" t="n">
         <s:v>75689117044416</s:v>
       </s:c>
-      <s:c r="G143" s="5" t="inlineStr">
+      <s:c r="F143" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_140_Rifle01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H143" s="2" t="inlineStr">
+      <s:c r="G143" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -10081,20 +7655,17 @@
         </s:is>
       </s:c>
       <s:c r="D144" s="1" t="n">
-        <s:v>7.3e+24</s:v>
-      </s:c>
-      <s:c r="E144" s="1" t="n">
         <s:v>33</s:v>
       </s:c>
-      <s:c r="F144" s="4" t="n">
+      <s:c r="E144" s="4" t="n">
         <s:v>92309488435591</s:v>
       </s:c>
-      <s:c r="G144" s="5" t="inlineStr">
+      <s:c r="F144" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_141_Rifle02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H144" s="2" t="inlineStr">
+      <s:c r="G144" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -10113,20 +7684,17 @@
         </s:is>
       </s:c>
       <s:c r="D145" s="1" t="n">
-        <s:v>1.168e+25</s:v>
-      </s:c>
-      <s:c r="E145" s="1" t="n">
         <s:v>33</s:v>
       </s:c>
-      <s:c r="F145" s="4" t="n">
+      <s:c r="E145" s="4" t="n">
         <s:v>106319308889290</s:v>
       </s:c>
-      <s:c r="G145" s="5" t="inlineStr">
+      <s:c r="F145" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_142_Rifle03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H145" s="2" t="inlineStr">
+      <s:c r="G145" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -10145,20 +7713,17 @@
         </s:is>
       </s:c>
       <s:c r="D146" s="1" t="n">
-        <s:v>1.752e+25</s:v>
-      </s:c>
-      <s:c r="E146" s="1" t="n">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="F146" s="4" t="n">
+      <s:c r="E146" s="4" t="n">
         <s:v>123120949699520</s:v>
       </s:c>
-      <s:c r="G146" s="5" t="inlineStr">
+      <s:c r="F146" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_143_Rifle04</s:t>
         </s:is>
       </s:c>
-      <s:c r="H146" s="2" t="inlineStr">
+      <s:c r="G146" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -10177,20 +7742,17 @@
         </s:is>
       </s:c>
       <s:c r="D147" s="1" t="n">
-        <s:v>2.19e+25</s:v>
-      </s:c>
-      <s:c r="E147" s="1" t="n">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="F147" s="4" t="n">
+      <s:c r="E147" s="4" t="n">
         <s:v>111674856010497</s:v>
       </s:c>
-      <s:c r="G147" s="5" t="inlineStr">
+      <s:c r="F147" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_144_Rifle05</s:t>
         </s:is>
       </s:c>
-      <s:c r="H147" s="2" t="inlineStr">
+      <s:c r="G147" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -10209,20 +7771,17 @@
         </s:is>
       </s:c>
       <s:c r="D148" s="1" t="n">
-        <s:v>3.64e+25</s:v>
-      </s:c>
-      <s:c r="E148" s="1" t="n">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="F148" s="4" t="n">
+      <s:c r="E148" s="4" t="n">
         <s:v>118080816505555</s:v>
       </s:c>
-      <s:c r="G148" s="5" t="inlineStr">
+      <s:c r="F148" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_145_MachineGun01</s:t>
         </s:is>
       </s:c>
-      <s:c r="H148" s="2" t="inlineStr">
+      <s:c r="G148" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -10241,20 +7800,17 @@
         </s:is>
       </s:c>
       <s:c r="D149" s="1" t="n">
-        <s:v>5.824e+25</s:v>
-      </s:c>
-      <s:c r="E149" s="1" t="n">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="F149" s="4" t="n">
+      <s:c r="E149" s="4" t="n">
         <s:v>105021574817966</s:v>
       </s:c>
-      <s:c r="G149" s="5" t="inlineStr">
+      <s:c r="F149" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_146_MachineGun02</s:t>
         </s:is>
       </s:c>
-      <s:c r="H149" s="2" t="inlineStr">
+      <s:c r="G149" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -10273,20 +7829,17 @@
         </s:is>
       </s:c>
       <s:c r="D150" s="1" t="n">
-        <s:v>8.736000000000001e+25</s:v>
-      </s:c>
-      <s:c r="E150" s="1" t="n">
         <s:v>35</s:v>
       </s:c>
-      <s:c r="F150" s="4" t="n">
+      <s:c r="E150" s="4" t="n">
         <s:v>72690180103558</s:v>
       </s:c>
-      <s:c r="G150" s="5" t="inlineStr">
+      <s:c r="F150" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_147_MachineGun03</s:t>
         </s:is>
       </s:c>
-      <s:c r="H150" s="2" t="inlineStr">
+      <s:c r="G150" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -10305,20 +7858,17 @@
         </s:is>
       </s:c>
       <s:c r="D151" s="1" t="n">
-        <s:v>1.092e+26</s:v>
-      </s:c>
-      <s:c r="E151" s="1" t="n">
         <s:v>35</s:v>
       </s:c>
-      <s:c r="F151" s="4" t="n">
+      <s:c r="E151" s="4" t="n">
         <s:v>94914272618995</s:v>
       </s:c>
-      <s:c r="G151" s="5" t="inlineStr">
+      <s:c r="F151" s="5" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_148_MachineGun04</s:t>
         </s:is>
       </s:c>
-      <s:c r="H151" s="2" t="inlineStr">
+      <s:c r="G151" s="2" t="inlineStr">
         <s:is>
           <s:t>Item</s:t>
         </s:is>
@@ -10329,7 +7879,7 @@
 </s:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <s:sheetPr>
     <s:outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10524,7 +8074,7 @@
 </s:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11480,7 +9030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -61534,4 +59084,950 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:sheetPr>
+    <s:outlinePr summaryBelow="1" summaryRight="1"/>
+    <s:pageSetUpPr/>
+  </s:sheetPr>
+  <s:dimension ref="A1:E55"/>
+  <s:sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <s:cols>
+    <s:col width="19.3611111111111" customWidth="1" style="28" min="1" max="1"/>
+    <s:col width="18.9814814814815" customWidth="1" style="28" min="2" max="2"/>
+    <s:col width="42.9814814814815" customWidth="1" style="28" min="3" max="3"/>
+  </s:cols>
+  <s:sheetData>
+    <s:row r="1" ht="15.6" customHeight="1" s="28">
+      <s:c r="A1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>关卡Id</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>草血量</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C1" s="1" t="inlineStr">
+        <s:is>
+          <s:t>颜色</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="2" ht="15.6" customHeight="1" s="28">
+      <s:c r="A2" s="1" t="inlineStr">
+        <s:is>
+          <s:t>LevelKey</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B2" s="1" t="inlineStr">
+        <s:is>
+          <s:t>GrassClumpsHP</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C2" s="1" t="inlineStr">
+        <s:is>
+          <s:t>Texture</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="3" ht="15.6" customHeight="1" s="28">
+      <s:c r="A3" s="1" t="inlineStr">
+        <s:is>
+          <s:t>string</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B3" s="1" t="inlineStr">
+        <s:is>
+          <s:t>number</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C3" s="1" t="inlineStr">
+        <s:is>
+          <s:t>string</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="4">
+      <s:c r="A4" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_1</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B4" s="2" t="n">
+        <s:v>29</s:v>
+      </s:c>
+      <s:c r="C4" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground1.png</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D4" s="2" t="n"/>
+      <s:c r="E4" s="2" t="n"/>
+    </s:row>
+    <s:row r="5">
+      <s:c r="A5" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_2</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B5" s="2" t="n">
+        <s:v>122</s:v>
+      </s:c>
+      <s:c r="C5" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground2.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="6">
+      <s:c r="A6" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_3</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B6" s="2" t="n">
+        <s:v>520</s:v>
+      </s:c>
+      <s:c r="C6" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground3.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="7">
+      <s:c r="A7" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_4</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B7" s="2" t="n">
+        <s:v>2176</s:v>
+      </s:c>
+      <s:c r="C7" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground4.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="8">
+      <s:c r="A8" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_5</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B8" s="2" t="n">
+        <s:v>9101</s:v>
+      </s:c>
+      <s:c r="C8" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground5.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="9">
+      <s:c r="A9" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_6</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B9" s="26" t="inlineStr">
+        <s:is>
+          <s:t>3.80e+4</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C9" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground6.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="10">
+      <s:c r="A10" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_7</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B10" s="26" t="inlineStr">
+        <s:is>
+          <s:t>1.59e+5</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C10" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground7.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="11">
+      <s:c r="A11" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_8</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B11" s="26" t="inlineStr">
+        <s:is>
+          <s:t>6.64e+5</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C11" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground8.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="12">
+      <s:c r="A12" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_9</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B12" s="26" t="inlineStr">
+        <s:is>
+          <s:t>2.77e+6</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C12" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground9.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="13">
+      <s:c r="A13" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_10</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B13" s="26" t="inlineStr">
+        <s:is>
+          <s:t>1.16e+7</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C13" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground10.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="14">
+      <s:c r="A14" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_11</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B14" s="26" t="inlineStr">
+        <s:is>
+          <s:t>4.84e+7</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C14" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground11.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="15">
+      <s:c r="A15" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_12</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B15" s="26" t="inlineStr">
+        <s:is>
+          <s:t>2.02e+8</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C15" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground12.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="16">
+      <s:c r="A16" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World1.Level_13</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B16" s="26" t="inlineStr">
+        <s:is>
+          <s:t>8.44e+8</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C16" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground13.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="17">
+      <s:c r="A17" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_14</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B17" s="26" t="inlineStr">
+        <s:is>
+          <s:t>3.53e+9</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C17" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground14.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="18">
+      <s:c r="A18" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_15</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B18" s="26" t="inlineStr">
+        <s:is>
+          <s:t>1.47e+10</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C18" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground15.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="19">
+      <s:c r="A19" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_16</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B19" s="26" t="inlineStr">
+        <s:is>
+          <s:t>6.15e+10</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C19" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground16.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="20">
+      <s:c r="A20" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_17</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B20" s="26" t="inlineStr">
+        <s:is>
+          <s:t>2.57e+11</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C20" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground17.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="21">
+      <s:c r="A21" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_18</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B21" s="26" t="inlineStr">
+        <s:is>
+          <s:t>1.07e+12</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C21" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground18.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="22">
+      <s:c r="A22" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_19</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B22" s="26" t="inlineStr">
+        <s:is>
+          <s:t>4.48e+12</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C22" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground19.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="23">
+      <s:c r="A23" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_20</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B23" s="26" t="inlineStr">
+        <s:is>
+          <s:t>1.87e+13</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C23" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground20.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="24">
+      <s:c r="A24" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_21</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B24" s="26" t="inlineStr">
+        <s:is>
+          <s:t>7.82e+13</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C24" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground21.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="25">
+      <s:c r="A25" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_22</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B25" s="26" t="inlineStr">
+        <s:is>
+          <s:t>3.27e+14</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C25" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground22.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="26">
+      <s:c r="A26" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_23</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B26" s="26" t="inlineStr">
+        <s:is>
+          <s:t>1.37e+15</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C26" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground23.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="27">
+      <s:c r="A27" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_24</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B27" s="26" t="inlineStr">
+        <s:is>
+          <s:t>5.70e+15</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C27" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground24.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="28">
+      <s:c r="A28" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_25</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B28" s="26" t="inlineStr">
+        <s:is>
+          <s:t>2.38e+16</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C28" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground25.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="29">
+      <s:c r="A29" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World2.Level_26</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B29" s="26" t="inlineStr">
+        <s:is>
+          <s:t>9.95e+16</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C29" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground26.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="30">
+      <s:c r="A30" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_27</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B30" s="26" t="inlineStr">
+        <s:is>
+          <s:t>4.16e+17</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C30" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground27.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="31">
+      <s:c r="A31" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_28</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B31" s="26" t="inlineStr">
+        <s:is>
+          <s:t>1.74e+18</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C31" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground28.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="32">
+      <s:c r="A32" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_29</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B32" s="26" t="inlineStr">
+        <s:is>
+          <s:t>7.25e+18</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C32" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground29.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="33">
+      <s:c r="A33" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_30</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B33" s="26" t="inlineStr">
+        <s:is>
+          <s:t>3.03e+19</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C33" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground30.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="34">
+      <s:c r="A34" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_31</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B34" s="26" t="inlineStr">
+        <s:is>
+          <s:t>1.27e+20</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C34" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground31.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="35">
+      <s:c r="A35" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_32</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B35" s="26" t="inlineStr">
+        <s:is>
+          <s:t>5.29e+20</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C35" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground32.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="36">
+      <s:c r="A36" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_33</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B36" s="26" t="inlineStr">
+        <s:is>
+          <s:t>2.21e+21</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C36" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground33.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="37">
+      <s:c r="A37" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_34</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B37" s="26" t="inlineStr">
+        <s:is>
+          <s:t>9.23e+21</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C37" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground34.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="38">
+      <s:c r="A38" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_35</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B38" s="26" t="inlineStr">
+        <s:is>
+          <s:t>3.85e+22</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C38" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground35.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="39">
+      <s:c r="A39" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_36</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B39" s="26" t="inlineStr">
+        <s:is>
+          <s:t>1.61e+23</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C39" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground36.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="40">
+      <s:c r="A40" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_37</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B40" s="26" t="inlineStr">
+        <s:is>
+          <s:t>6.73e+23</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C40" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground37.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="41">
+      <s:c r="A41" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_38</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B41" s="26" t="inlineStr">
+        <s:is>
+          <s:t>2.81e+24</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C41" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground38.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="42">
+      <s:c r="A42" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World3.Level_39</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B42" s="26" t="inlineStr">
+        <s:is>
+          <s:t>1.17e+25</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C42" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground39.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="43">
+      <s:c r="A43" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_40</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B43" s="27" t="inlineStr">
+        <s:is>
+          <s:t>4.90e+25</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C43" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground40.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="44">
+      <s:c r="A44" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_41</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B44" s="27" t="inlineStr">
+        <s:is>
+          <s:t>2.05e+26</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C44" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground41.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="45">
+      <s:c r="A45" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_42</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B45" s="27" t="inlineStr">
+        <s:is>
+          <s:t>8.55e+26</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C45" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground42.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="46">
+      <s:c r="A46" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_43</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B46" s="27" t="inlineStr">
+        <s:is>
+          <s:t>3.57e+27</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C46" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground43.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="47">
+      <s:c r="A47" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_44</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B47" s="27" t="inlineStr">
+        <s:is>
+          <s:t>1.49e+28</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C47" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground44.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="48">
+      <s:c r="A48" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_45</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B48" s="27" t="inlineStr">
+        <s:is>
+          <s:t>6.24e+28</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C48" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground45.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="49">
+      <s:c r="A49" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_46</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B49" s="27" t="inlineStr">
+        <s:is>
+          <s:t>2.60e+29</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C49" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground46.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="50">
+      <s:c r="A50" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_47</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B50" s="27" t="inlineStr">
+        <s:is>
+          <s:t>1.09e+30</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C50" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground47.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="51">
+      <s:c r="A51" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_48</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B51" s="27" t="inlineStr">
+        <s:is>
+          <s:t>4.54e+30</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C51" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground48.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="52">
+      <s:c r="A52" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_49</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B52" s="27" t="inlineStr">
+        <s:is>
+          <s:t>1.90e+31</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C52" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground49.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="53">
+      <s:c r="A53" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_50</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B53" s="27" t="inlineStr">
+        <s:is>
+          <s:t>7.93e+31</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C53" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground50.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="54">
+      <s:c r="A54" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_51</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B54" s="27" t="inlineStr">
+        <s:is>
+          <s:t>3.31e+32</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C54" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground51.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="55">
+      <s:c r="A55" s="2" t="inlineStr">
+        <s:is>
+          <s:t>World4.Level_52</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B55" s="27" t="inlineStr">
+        <s:is>
+          <s:t>1.38e+33</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C55" s="2" t="inlineStr">
+        <s:is>
+          <s:t>sandboxId://Model/Block/SegmenteGrassClump/Ground52.png</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+  </s:sheetData>
+  <s:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</s:worksheet>
 </file>
--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -1817,14 +1817,44 @@
       </s:c>
     </s:row>
     <s:row r="19" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B19" s="12" t="n"/>
-      <s:c r="C19" s="12" t="n"/>
-      <s:c r="D19" s="13" t="n"/>
+      <s:c r="A19" s="12" t="inlineStr">
+        <s:is>
+          <s:t>string,bool</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B19" s="12" t="inlineStr">
+        <s:is>
+          <s:t>AnalyticsEnabled</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C19" s="12" t="b">
+        <s:v>1</s:v>
+      </s:c>
+      <s:c r="D19" s="13" t="inlineStr">
+        <s:is>
+          <s:t>Analytics reporting enabled. Developer accounts are always excluded.</s:t>
+        </s:is>
+      </s:c>
     </s:row>
     <s:row r="20" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B20" s="12" t="n"/>
-      <s:c r="C20" s="12" t="n"/>
-      <s:c r="D20" s="13" t="n"/>
+      <s:c r="A20" s="12" t="inlineStr">
+        <s:is>
+          <s:t>string,number_array</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B20" s="12" t="inlineStr">
+        <s:is>
+          <s:t>AnalyticsExcludedUserIds</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C20" s="12" t="n">
+        <s:v>2563885143</s:v>
+      </s:c>
+      <s:c r="D20" s="13" t="inlineStr">
+        <s:is>
+          <s:t>Excluded developer/test account UserIds, comma-separated numbers.</s:t>
+        </s:is>
+      </s:c>
     </s:row>
     <s:row r="21" ht="24.6" customFormat="1" customHeight="1" s="11">
       <s:c r="B21" s="12" t="n"/>

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -8,7 +8,7 @@
   </ns1:AlternateContent>
   <s:workbookPr/>
   <s:bookViews>
-    <s:workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="642" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
+    <s:workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="642" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </s:bookViews>
   <s:sheets>
     <s:sheet name="Rule" sheetId="1" state="visible" r:id="rId1"/>
@@ -44,7 +44,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <s:styleSheet xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:numFmts count="0"/>
+  <s:numFmts count="1">
+    <s:numFmt numFmtId="164" formatCode="0_ "/>
+  </s:numFmts>
   <s:fonts count="27">
     <s:font>
       <s:name val="宋体"/>
@@ -690,7 +692,7 @@
       <s:alignment vertical="center"/>
     </s:xf>
   </s:cellStyleXfs>
-  <s:cellXfs count="24">
+  <s:cellXfs count="28">
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <s:alignment vertical="center"/>
     </s:xf>
@@ -701,8 +703,11 @@
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <s:alignment horizontal="center" vertical="center"/>
     </s:xf>
-    <s:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <s:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <s:alignment vertical="center"/>
+    </s:xf>
+    <s:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <s:alignment horizontal="center" vertical="center"/>
     </s:xf>
     <s:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <s:alignment horizontal="center" vertical="center"/>
@@ -714,6 +719,9 @@
       <s:alignment horizontal="center" vertical="center" wrapText="1"/>
     </s:xf>
     <s:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <s:alignment vertical="center"/>
+    </s:xf>
+    <s:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <s:alignment vertical="center"/>
     </s:xf>
     <s:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -735,9 +743,6 @@
       <s:alignment horizontal="center"/>
     </s:xf>
     <s:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <s:alignment horizontal="left"/>
-    </s:xf>
-    <s:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <s:alignment horizontal="center" vertical="center" wrapText="1"/>
     </s:xf>
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -752,6 +757,9 @@
     <s:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <s:alignment vertical="center"/>
     </s:xf>
+    <s:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <s:alignment vertical="center"/>
+    </s:xf>
     <s:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <s:alignment horizontal="center" vertical="center"/>
     </s:xf>
@@ -760,6 +768,12 @@
     </s:xf>
     <s:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <s:alignment vertical="center"/>
+    </s:xf>
+    <s:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <s:alignment vertical="center"/>
+    </s:xf>
+    <s:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <s:alignment horizontal="center" vertical="center"/>
     </s:xf>
   </s:cellXfs>
   <s:cellStyles count="49">
@@ -1156,96 +1170,96 @@
   </s:cols>
   <s:sheetData>
     <s:row r="1">
-      <s:c r="A1" s="17" t="inlineStr">
+      <s:c r="A1" s="18" t="inlineStr">
         <s:is>
           <s:t>子配置键</s:t>
         </s:is>
       </s:c>
-      <s:c r="B1" s="17" t="inlineStr">
+      <s:c r="B1" s="18" t="inlineStr">
         <s:is>
           <s:t>子配置键类型</s:t>
         </s:is>
       </s:c>
-      <s:c r="C1" s="17" t="inlineStr">
+      <s:c r="C1" s="18" t="inlineStr">
         <s:is>
           <s:t>子配置读取类型</s:t>
         </s:is>
       </s:c>
-      <s:c r="D1" s="17" t="inlineStr">
+      <s:c r="D1" s="18" t="inlineStr">
         <s:is>
           <s:t>子配置内的key类型</s:t>
         </s:is>
       </s:c>
-      <s:c r="E1" s="17" t="inlineStr">
+      <s:c r="E1" s="18" t="inlineStr">
         <s:is>
           <s:t>对应页签</s:t>
         </s:is>
       </s:c>
-      <s:c r="F1" s="17" t="inlineStr">
+      <s:c r="F1" s="18" t="inlineStr">
         <s:is>
           <s:t>含义</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="2">
-      <s:c r="A2" s="17" t="inlineStr">
+      <s:c r="A2" s="18" t="inlineStr">
         <s:is>
           <s:t>CommonConfig</s:t>
         </s:is>
       </s:c>
-      <s:c r="B2" s="17" t="inlineStr">
+      <s:c r="B2" s="18" t="inlineStr">
         <s:is>
           <s:t>string</s:t>
         </s:is>
       </s:c>
-      <s:c r="C2" s="17" t="inlineStr">
+      <s:c r="C2" s="18" t="inlineStr">
         <s:is>
           <s:t>table</s:t>
         </s:is>
       </s:c>
-      <s:c r="D2" s="17" t="inlineStr">
+      <s:c r="D2" s="18" t="inlineStr">
         <s:is>
           <s:t>Key</s:t>
         </s:is>
       </s:c>
-      <s:c r="E2" s="18" t="inlineStr">
+      <s:c r="E2" s="19" t="inlineStr">
         <s:is>
           <s:t>CommonConfig</s:t>
         </s:is>
       </s:c>
-      <s:c r="F2" s="17" t="inlineStr">
+      <s:c r="F2" s="18" t="inlineStr">
         <s:is>
           <s:t>通用数据</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="3" ht="26" customHeight="1" s="1">
-      <s:c r="A3" s="17" t="inlineStr">
+      <s:c r="A3" s="18" t="inlineStr">
         <s:is>
           <s:t>TrainingFieldData</s:t>
         </s:is>
       </s:c>
-      <s:c r="B3" s="17" t="inlineStr">
+      <s:c r="B3" s="18" t="inlineStr">
         <s:is>
           <s:t>string</s:t>
         </s:is>
       </s:c>
-      <s:c r="C3" s="17" t="inlineStr">
+      <s:c r="C3" s="18" t="inlineStr">
         <s:is>
           <s:t>struct</s:t>
         </s:is>
       </s:c>
-      <s:c r="D3" s="17" t="inlineStr">
+      <s:c r="D3" s="18" t="inlineStr">
         <s:is>
           <s:t>Index</s:t>
         </s:is>
       </s:c>
-      <s:c r="E3" s="19" t="inlineStr">
+      <s:c r="E3" s="20" t="inlineStr">
         <s:is>
           <s:t>TrainingFieldData</s:t>
         </s:is>
       </s:c>
-      <s:c r="F3" s="17" t="inlineStr">
+      <s:c r="F3" s="18" t="inlineStr">
         <s:is>
           <s:t>训练场地数据</s:t>
         </s:is>
@@ -1304,7 +1318,7 @@
           <s:t>Index</s:t>
         </s:is>
       </s:c>
-      <s:c r="E5" s="20" t="inlineStr">
+      <s:c r="E5" s="21" t="inlineStr">
         <s:is>
           <s:t>TrainingRateConfig</s:t>
         </s:is>
@@ -1366,7 +1380,7 @@
           <s:t>Index</s:t>
         </s:is>
       </s:c>
-      <s:c r="E8" s="20" t="inlineStr">
+      <s:c r="E8" s="21" t="inlineStr">
         <s:is>
           <s:t>ItemData</s:t>
         </s:is>
@@ -1398,7 +1412,7 @@
           <s:t>Index</s:t>
         </s:is>
       </s:c>
-      <s:c r="E9" s="20" t="inlineStr">
+      <s:c r="E9" s="21" t="inlineStr">
         <s:is>
           <s:t>AreaConfig</s:t>
         </s:is>
@@ -1461,479 +1475,480 @@
   <s:dimension ref="A1:G36"/>
   <s:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <s:cols>
-    <s:col width="44.175" customWidth="1" style="11" min="1" max="1"/>
-    <s:col width="71.35833333333331" customWidth="1" style="11" min="2" max="2"/>
-    <s:col width="123.558333333333" customWidth="1" style="11" min="3" max="3"/>
-    <s:col width="82.8666666666667" customWidth="1" style="11" min="4" max="4"/>
-    <s:col width="9" customWidth="1" style="11" min="5" max="6"/>
-    <s:col width="81.18333333333329" customWidth="1" style="11" min="7" max="7"/>
-    <s:col width="9" customWidth="1" style="11" min="8" max="16384"/>
+    <s:col width="44.175" customWidth="1" style="13" min="1" max="1"/>
+    <s:col width="71.35833333333331" customWidth="1" style="13" min="2" max="2"/>
+    <s:col width="123.558333333333" customWidth="1" style="13" min="3" max="3"/>
+    <s:col width="82.8666666666667" customWidth="1" style="13" min="4" max="4"/>
+    <s:col width="9" customWidth="1" style="13" min="5" max="6"/>
+    <s:col width="81.18333333333329" customWidth="1" style="13" min="7" max="7"/>
+    <s:col width="9" customWidth="1" style="13" min="8" max="16384"/>
   </s:cols>
   <s:sheetData>
-    <s:row r="1" ht="22.25" customFormat="1" customHeight="1" s="11">
-      <s:c r="A1" s="12" t="inlineStr">
+    <s:row r="1" ht="22.25" customFormat="1" customHeight="1" s="13">
+      <s:c r="A1" s="14" t="inlineStr">
         <s:is>
           <s:t>KeyType, ValueType</s:t>
         </s:is>
       </s:c>
-      <s:c r="B1" s="12" t="inlineStr">
+      <s:c r="B1" s="14" t="inlineStr">
         <s:is>
           <s:t>类型</s:t>
         </s:is>
       </s:c>
-      <s:c r="C1" s="12" t="inlineStr">
+      <s:c r="C1" s="14" t="inlineStr">
         <s:is>
           <s:t>字符串通用</s:t>
         </s:is>
       </s:c>
-      <s:c r="D1" s="13" t="inlineStr">
+      <s:c r="D1" s="15" t="inlineStr">
         <s:is>
           <s:t>描述函数含义</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="2" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B2" s="12" t="n"/>
-      <s:c r="C2" s="12" t="n"/>
-      <s:c r="D2" s="13" t="n"/>
+    <s:row r="2" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B2" s="14" t="n"/>
+      <s:c r="C2" s="14" t="n"/>
+      <s:c r="D2" s="15" t="n"/>
     </s:row>
-    <s:row r="3" ht="91" customFormat="1" customHeight="1" s="11">
-      <s:c r="A3" s="12" t="inlineStr">
+    <s:row r="3" ht="91" customFormat="1" customHeight="1" s="13">
+      <s:c r="A3" s="14" t="inlineStr">
         <s:is>
           <s:t>string,kv_string</s:t>
         </s:is>
       </s:c>
-      <s:c r="B3" s="12" t="inlineStr">
+      <s:c r="B3" s="14" t="inlineStr">
         <s:is>
           <s:t>TrainingLevelUpCurve</s:t>
         </s:is>
       </s:c>
-      <s:c r="C3" s="12" t="inlineStr">
+      <s:c r="C3" s="14" t="inlineStr">
         <s:is>
           <s:t>Type=Power,M=1,P=2</s:t>
         </s:is>
       </s:c>
-      <s:c r="D3" s="13" t="n"/>
+      <s:c r="D3" s="14" t="n"/>
     </s:row>
-    <s:row r="4" ht="60" customFormat="1" customHeight="1" s="11">
-      <s:c r="A4" s="12" t="inlineStr">
+    <s:row r="4" ht="60" customFormat="1" customHeight="1" s="13">
+      <s:c r="A4" s="14" t="inlineStr">
         <s:is>
           <s:t>string,kv_string</s:t>
         </s:is>
       </s:c>
-      <s:c r="B4" s="12" t="inlineStr">
+      <s:c r="B4" s="14" t="inlineStr">
         <s:is>
           <s:t>RebirthConsumeCurve</s:t>
         </s:is>
       </s:c>
-      <s:c r="C4" s="12" t="inlineStr">
+      <s:c r="C4" s="14" t="inlineStr">
         <s:is>
           <s:t>Type=Power,M=1,P=3</s:t>
         </s:is>
       </s:c>
-      <s:c r="D4" s="13" t="n"/>
-      <s:c r="E4" s="12" t="n"/>
-      <s:c r="F4" s="12" t="n"/>
-      <s:c r="G4" s="12" t="n"/>
+      <s:c r="D4" s="14" t="n"/>
+      <s:c r="E4" s="14" t="n"/>
+      <s:c r="F4" s="14" t="n"/>
+      <s:c r="G4" s="14" t="n"/>
     </s:row>
-    <s:row r="5" ht="60" customFormat="1" customHeight="1" s="11">
-      <s:c r="A5" s="12" t="inlineStr">
+    <s:row r="5" ht="60" customFormat="1" customHeight="1" s="13">
+      <s:c r="A5" s="14" t="inlineStr">
         <s:is>
           <s:t>string, number</s:t>
         </s:is>
       </s:c>
-      <s:c r="B5" s="12" t="inlineStr">
+      <s:c r="B5" s="14" t="inlineStr">
         <s:is>
           <s:t>TrainingLevelToStrength</s:t>
         </s:is>
       </s:c>
-      <s:c r="C5" s="12" t="n">
+      <s:c r="C5" s="14" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="D5" s="13" t="n"/>
+      <s:c r="D5" s="14" t="n"/>
     </s:row>
-    <s:row r="6" ht="60" customFormat="1" customHeight="1" s="11">
-      <s:c r="A6" s="12" t="inlineStr">
+    <s:row r="6" ht="60" customFormat="1" customHeight="1" s="13">
+      <s:c r="A6" s="14" t="inlineStr">
         <s:is>
           <s:t>string,kv_string</s:t>
         </s:is>
       </s:c>
-      <s:c r="B6" s="12" t="inlineStr">
+      <s:c r="B6" s="14" t="inlineStr">
         <s:is>
           <s:t>RebirthTrainingRate</s:t>
         </s:is>
       </s:c>
-      <s:c r="C6" s="12" t="inlineStr">
+      <s:c r="C6" s="14" t="inlineStr">
         <s:is>
           <s:t>Type=Power,M=1,P=2</s:t>
         </s:is>
       </s:c>
-      <s:c r="D6" s="13" t="n"/>
-      <s:c r="E6" s="12" t="n"/>
-      <s:c r="F6" s="12" t="n"/>
-      <s:c r="G6" s="12" t="n"/>
+      <s:c r="D6" s="14" t="n"/>
+      <s:c r="E6" s="14" t="n"/>
+      <s:c r="F6" s="14" t="n"/>
+      <s:c r="G6" s="14" t="n"/>
     </s:row>
-    <s:row r="7" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A7" s="14" t="inlineStr">
+    <s:row r="7" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A7" s="16" t="inlineStr">
         <s:is>
           <s:t>string,kv_string</s:t>
         </s:is>
       </s:c>
-      <s:c r="B7" s="14" t="inlineStr">
+      <s:c r="B7" s="16" t="inlineStr">
         <s:is>
           <s:t>RebirthMoneyRate</s:t>
         </s:is>
       </s:c>
-      <s:c r="C7" s="14" t="inlineStr">
+      <s:c r="C7" s="16" t="inlineStr">
         <s:is>
           <s:t>Type=Power,M=1,P=2</s:t>
         </s:is>
       </s:c>
-      <s:c r="D7" s="15" t="n"/>
-      <s:c r="E7" s="15" t="n"/>
-      <s:c r="F7" s="15" t="n"/>
-      <s:c r="G7" s="15" t="n"/>
+      <s:c r="D7" s="16" t="n"/>
+      <s:c r="E7" s="16" t="n"/>
+      <s:c r="F7" s="16" t="n"/>
+      <s:c r="G7" s="16" t="n"/>
     </s:row>
-    <s:row r="8" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A8" s="14" t="inlineStr">
+    <s:row r="8" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A8" s="16" t="inlineStr">
         <s:is>
           <s:t>string,kv_string</s:t>
         </s:is>
       </s:c>
-      <s:c r="B8" s="14" t="inlineStr">
+      <s:c r="B8" s="16" t="inlineStr">
         <s:is>
           <s:t>InviteFriendData</s:t>
         </s:is>
       </s:c>
-      <s:c r="C8" s="14" t="inlineStr">
+      <s:c r="C8" s="16" t="inlineStr">
         <s:is>
           <s:t>MaxCount=4, AddRate=0.25, CD=300</s:t>
         </s:is>
       </s:c>
-      <s:c r="D8" s="15" t="inlineStr">
+      <s:c r="D8" s="16" t="inlineStr">
         <s:is>
           <s:t>最好倍率数量, 每个好友的额外倍率, 提示CD时间</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="9" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A9" s="14" t="inlineStr">
+    <s:row r="9" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A9" s="16" t="inlineStr">
         <s:is>
           <s:t>string,kv_string</s:t>
         </s:is>
       </s:c>
-      <s:c r="B9" s="14" t="inlineStr">
+      <s:c r="B9" s="16" t="inlineStr">
         <s:is>
           <s:t>ItemData</s:t>
         </s:is>
       </s:c>
-      <s:c r="C9" s="14" t="inlineStr">
+      <s:c r="C9" s="16" t="inlineStr">
         <s:is>
           <s:t>TimeSurvivel=30, LuckSurvivelTime=30,LuckRefreshInterval=90</s:t>
         </s:is>
       </s:c>
-      <s:c r="D9" s="15" t="inlineStr">
+      <s:c r="D9" s="16" t="inlineStr">
         <s:is>
           <s:t>数据表</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="10" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A10" s="12" t="inlineStr">
+    <s:row r="10" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A10" s="14" t="inlineStr">
         <s:is>
           <s:t>string,kv_string</s:t>
         </s:is>
       </s:c>
-      <s:c r="B10" s="12" t="inlineStr">
+      <s:c r="B10" s="14" t="inlineStr">
         <s:is>
           <s:t>CollectionData</s:t>
         </s:is>
       </s:c>
-      <s:c r="C10" s="12" t="inlineStr">
+      <s:c r="C10" s="14" t="inlineStr">
         <s:is>
           <s:t>UnlockCount=10,TrainingRate=0.25</s:t>
         </s:is>
       </s:c>
-      <s:c r="D10" s="13" t="n"/>
-      <s:c r="E10" s="12" t="n"/>
-      <s:c r="F10" s="12" t="n"/>
-      <s:c r="G10" s="12" t="n"/>
+      <s:c r="D10" s="14" t="n"/>
+      <s:c r="E10" s="14" t="n"/>
+      <s:c r="F10" s="14" t="n"/>
+      <s:c r="G10" s="14" t="n"/>
     </s:row>
-    <s:row r="11" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A11" s="12" t="inlineStr">
+    <s:row r="11" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A11" s="14" t="inlineStr">
         <s:is>
           <s:t>string,kv_string</s:t>
         </s:is>
       </s:c>
-      <s:c r="B11" s="12" t="inlineStr">
+      <s:c r="B11" s="14" t="inlineStr">
         <s:is>
           <s:t>OfflineReward</s:t>
         </s:is>
       </s:c>
-      <s:c r="C11" s="12" t="inlineStr">
+      <s:c r="C11" s="14" t="inlineStr">
         <s:is>
           <s:t>Time=14400, Rate= 0.25, VIPRate=0.5</s:t>
         </s:is>
       </s:c>
-      <s:c r="D11" s="13" t="n"/>
-      <s:c r="E11" s="12" t="n"/>
-      <s:c r="F11" s="12" t="n"/>
-      <s:c r="G11" s="12" t="n"/>
+      <s:c r="D11" s="14" t="n"/>
+      <s:c r="E11" s="14" t="n"/>
+      <s:c r="F11" s="14" t="n"/>
+      <s:c r="G11" s="14" t="n"/>
     </s:row>
-    <s:row r="12" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A12" s="12" t="inlineStr">
+    <s:row r="12" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A12" s="14" t="inlineStr">
         <s:is>
           <s:t>string,kv_string</s:t>
         </s:is>
       </s:c>
-      <s:c r="B12" s="12" t="inlineStr">
+      <s:c r="B12" s="14" t="inlineStr">
         <s:is>
           <s:t>LoginData</s:t>
         </s:is>
       </s:c>
-      <s:c r="C12" s="12" t="inlineStr">
+      <s:c r="C12" s="14" t="inlineStr">
         <s:is>
           <s:t>GemCount=5</s:t>
         </s:is>
       </s:c>
-      <s:c r="D12" s="13" t="n"/>
-      <s:c r="E12" s="12" t="n"/>
-      <s:c r="F12" s="12" t="n"/>
-      <s:c r="G12" s="12" t="n"/>
+      <s:c r="D12" s="14" t="n"/>
+      <s:c r="E12" s="14" t="n"/>
+      <s:c r="F12" s="14" t="n"/>
+      <s:c r="G12" s="14" t="n"/>
     </s:row>
-    <s:row r="13" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A13" s="12" t="inlineStr">
+    <s:row r="13" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A13" s="14" t="inlineStr">
         <s:is>
           <s:t>string,kv_string</s:t>
         </s:is>
       </s:c>
-      <s:c r="B13" s="12" t="inlineStr">
+      <s:c r="B13" s="14" t="inlineStr">
         <s:is>
           <s:t>GiftData</s:t>
         </s:is>
       </s:c>
-      <s:c r="C13" s="16" t="inlineStr">
-        <s:is>
-          <s:t>Gem=5,Count=5,Time=10</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="D13" s="13" t="n"/>
-      <s:c r="E13" s="13" t="n"/>
-      <s:c r="F13" s="13" t="n"/>
-      <s:c r="G13" s="13" t="n"/>
+      <s:c r="C13" s="17" t="inlineStr">
+        <s:is>
+          <s:t>Gem=5,Count=1,Time=600</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D13" s="14" t="n"/>
+      <s:c r="E13" s="14" t="n"/>
+      <s:c r="F13" s="14" t="n"/>
+      <s:c r="G13" s="14" t="n"/>
     </s:row>
-    <s:row r="14" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A14" s="12" t="inlineStr">
+    <s:row r="14" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A14" s="14" t="inlineStr">
         <s:is>
           <s:t>string,number_array</s:t>
         </s:is>
       </s:c>
-      <s:c r="B14" s="12" t="inlineStr">
+      <s:c r="B14" s="14" t="inlineStr">
         <s:is>
           <s:t>ToyPriceRateRange</s:t>
         </s:is>
       </s:c>
-      <s:c r="C14" s="12" t="inlineStr">
+      <s:c r="C14" s="14" t="inlineStr">
         <s:is>
           <s:t>0.5,1.5</s:t>
         </s:is>
       </s:c>
-      <s:c r="D14" s="13" t="n"/>
+      <s:c r="D14" s="14" t="n"/>
     </s:row>
-    <s:row r="15" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A15" s="12" t="inlineStr">
+    <s:row r="15" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A15" s="14" t="inlineStr">
         <s:is>
           <s:t>string,number</s:t>
         </s:is>
       </s:c>
-      <s:c r="B15" s="12" t="inlineStr">
+      <s:c r="B15" s="14" t="inlineStr">
         <s:is>
           <s:t>ToyCandidateCount</s:t>
         </s:is>
       </s:c>
-      <s:c r="C15" s="12" t="n">
+      <s:c r="C15" s="14" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="D15" s="13" t="n"/>
+      <s:c r="D15" s="14" t="n"/>
     </s:row>
-    <s:row r="16" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A16" s="0" t="inlineStr">
+    <s:row r="16" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A16" s="3" t="inlineStr">
         <s:is>
           <s:t>string,number</s:t>
         </s:is>
       </s:c>
-      <s:c r="B16" s="12" t="inlineStr">
+      <s:c r="B16" s="14" t="inlineStr">
         <s:is>
           <s:t>ToyItemsPerStage</s:t>
         </s:is>
       </s:c>
-      <s:c r="C16" s="12" t="n">
+      <s:c r="C16" s="14" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="D16" s="13" t="n"/>
+      <s:c r="D16" s="14" t="n"/>
     </s:row>
-    <s:row r="17" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A17" s="12" t="inlineStr">
+    <s:row r="17" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A17" s="14" t="inlineStr">
         <s:is>
           <s:t>string,number</s:t>
         </s:is>
       </s:c>
-      <s:c r="B17" s="12" t="inlineStr">
+      <s:c r="B17" s="14" t="inlineStr">
         <s:is>
           <s:t>ToyRefreshRatio</s:t>
         </s:is>
       </s:c>
-      <s:c r="C17" s="12">
+      <s:c r="C17" s="14">
         <s:f>1/3</s:f>
         <s:v>0.333333333333333</s:v>
       </s:c>
-      <s:c r="D17" s="13" t="inlineStr">
+      <s:c r="D17" s="14" t="inlineStr">
         <s:is>
           <s:t>Occupied stone count = floor(total stones * ratio).</s:t>
         </s:is>
       </s:c>
-      <s:c r="E17" s="12" t="n"/>
-      <s:c r="F17" s="12" t="n"/>
-      <s:c r="G17" s="12" t="n"/>
+      <s:c r="E17" s="14" t="n"/>
+      <s:c r="F17" s="14" t="n"/>
+      <s:c r="G17" s="14" t="n"/>
     </s:row>
-    <s:row r="18" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A18" s="12" t="inlineStr">
+    <s:row r="18" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A18" s="14" t="inlineStr">
         <s:is>
           <s:t>string,number</s:t>
         </s:is>
       </s:c>
-      <s:c r="B18" s="12" t="inlineStr">
+      <s:c r="B18" s="14" t="inlineStr">
         <s:is>
           <s:t>ToyLuckyCount</s:t>
         </s:is>
       </s:c>
-      <s:c r="C18" s="12" t="n">
+      <s:c r="C18" s="14" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D18" s="13" t="inlineStr">
+      <s:c r="D18" s="14" t="inlineStr">
         <s:is>
           <s:t>Fixed lucky count included in occupied stones, capped by occupied count.</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="19" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A19" s="12" t="inlineStr">
+    <s:row r="19" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A19" s="14" t="inlineStr">
         <s:is>
           <s:t>string,bool</s:t>
         </s:is>
       </s:c>
-      <s:c r="B19" s="12" t="inlineStr">
+      <s:c r="B19" s="14" t="inlineStr">
         <s:is>
           <s:t>AnalyticsEnabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="C19" s="12" t="b">
+      <s:c r="C19" s="14" t="b">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="D19" s="13" t="inlineStr">
+      <s:c r="D19" s="14" t="inlineStr">
         <s:is>
           <s:t>Analytics reporting enabled. Developer accounts are always excluded.</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="20" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="A20" s="12" t="inlineStr">
+    <s:row r="20" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A20" s="14" t="inlineStr">
         <s:is>
           <s:t>string,number_array</s:t>
         </s:is>
       </s:c>
-      <s:c r="B20" s="12" t="inlineStr">
+      <s:c r="B20" s="14" t="inlineStr">
         <s:is>
           <s:t>AnalyticsExcludedUserIds</s:t>
         </s:is>
       </s:c>
-      <s:c r="C20" s="12" t="n">
-        <s:v>2563885143</s:v>
-      </s:c>
-      <s:c r="D20" s="13" t="inlineStr">
+      <s:c r="C20" s="14" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="D20" s="14" t="inlineStr">
         <s:is>
           <s:t>Excluded developer/test account UserIds, comma-separated numbers.</s:t>
         </s:is>
       </s:c>
     </s:row>
-    <s:row r="21" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B21" s="12" t="n"/>
-      <s:c r="C21" s="12" t="n"/>
-      <s:c r="D21" s="13" t="n"/>
+    <s:row r="21" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="A21" s="2" t="n"/>
+      <s:c r="B21" s="14" t="n"/>
+      <s:c r="C21" s="14" t="n"/>
+      <s:c r="D21" s="14" t="n"/>
     </s:row>
-    <s:row r="22" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B22" s="12" t="n"/>
-      <s:c r="C22" s="12" t="n"/>
-      <s:c r="D22" s="13" t="n"/>
+    <s:row r="22" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B22" s="14" t="n"/>
+      <s:c r="C22" s="14" t="n"/>
+      <s:c r="D22" s="15" t="n"/>
     </s:row>
-    <s:row r="23" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B23" s="12" t="n"/>
-      <s:c r="C23" s="12" t="n"/>
-      <s:c r="D23" s="13" t="n"/>
+    <s:row r="23" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B23" s="14" t="n"/>
+      <s:c r="C23" s="14" t="n"/>
+      <s:c r="D23" s="15" t="n"/>
     </s:row>
-    <s:row r="24" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B24" s="12" t="n"/>
-      <s:c r="C24" s="12" t="n"/>
-      <s:c r="D24" s="13" t="n"/>
+    <s:row r="24" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B24" s="14" t="n"/>
+      <s:c r="C24" s="14" t="n"/>
+      <s:c r="D24" s="15" t="n"/>
     </s:row>
-    <s:row r="25" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B25" s="12" t="n"/>
-      <s:c r="C25" s="12" t="n"/>
-      <s:c r="D25" s="13" t="n"/>
+    <s:row r="25" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B25" s="14" t="n"/>
+      <s:c r="C25" s="14" t="n"/>
+      <s:c r="D25" s="15" t="n"/>
     </s:row>
-    <s:row r="26" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B26" s="12" t="n"/>
-      <s:c r="C26" s="12" t="n"/>
-      <s:c r="D26" s="13" t="n"/>
+    <s:row r="26" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B26" s="14" t="n"/>
+      <s:c r="C26" s="14" t="n"/>
+      <s:c r="D26" s="15" t="n"/>
     </s:row>
-    <s:row r="27" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="C27" s="12" t="n"/>
-      <s:c r="D27" s="13" t="n"/>
+    <s:row r="27" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="C27" s="14" t="n"/>
+      <s:c r="D27" s="15" t="n"/>
     </s:row>
-    <s:row r="28" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B28" s="12" t="n"/>
-      <s:c r="C28" s="12" t="n"/>
-      <s:c r="D28" s="13" t="n"/>
+    <s:row r="28" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B28" s="14" t="n"/>
+      <s:c r="C28" s="14" t="n"/>
+      <s:c r="D28" s="15" t="n"/>
     </s:row>
-    <s:row r="29" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B29" s="12" t="n"/>
-      <s:c r="C29" s="12" t="n"/>
-      <s:c r="D29" s="13" t="n"/>
+    <s:row r="29" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B29" s="14" t="n"/>
+      <s:c r="C29" s="14" t="n"/>
+      <s:c r="D29" s="15" t="n"/>
     </s:row>
-    <s:row r="30" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B30" s="12" t="n"/>
-      <s:c r="C30" s="12" t="n"/>
-      <s:c r="D30" s="13" t="n"/>
+    <s:row r="30" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B30" s="14" t="n"/>
+      <s:c r="C30" s="14" t="n"/>
+      <s:c r="D30" s="15" t="n"/>
     </s:row>
-    <s:row r="31" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B31" s="12" t="n"/>
-      <s:c r="C31" s="12" t="n"/>
-      <s:c r="D31" s="13" t="n"/>
+    <s:row r="31" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B31" s="14" t="n"/>
+      <s:c r="C31" s="14" t="n"/>
+      <s:c r="D31" s="15" t="n"/>
     </s:row>
-    <s:row r="32" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B32" s="12" t="n"/>
-      <s:c r="C32" s="12" t="n"/>
-      <s:c r="D32" s="13" t="n"/>
+    <s:row r="32" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B32" s="14" t="n"/>
+      <s:c r="C32" s="14" t="n"/>
+      <s:c r="D32" s="15" t="n"/>
     </s:row>
-    <s:row r="33" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B33" s="12" t="n"/>
-      <s:c r="C33" s="12" t="n"/>
-      <s:c r="D33" s="13" t="n"/>
+    <s:row r="33" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B33" s="14" t="n"/>
+      <s:c r="C33" s="14" t="n"/>
+      <s:c r="D33" s="15" t="n"/>
     </s:row>
-    <s:row r="34" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B34" s="12" t="n"/>
-      <s:c r="C34" s="12" t="n"/>
-      <s:c r="D34" s="13" t="n"/>
+    <s:row r="34" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B34" s="14" t="n"/>
+      <s:c r="C34" s="14" t="n"/>
+      <s:c r="D34" s="15" t="n"/>
     </s:row>
-    <s:row r="35" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B35" s="12" t="n"/>
-      <s:c r="C35" s="12" t="n"/>
-      <s:c r="D35" s="13" t="n"/>
+    <s:row r="35" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B35" s="14" t="n"/>
+      <s:c r="C35" s="14" t="n"/>
+      <s:c r="D35" s="15" t="n"/>
     </s:row>
-    <s:row r="36" ht="24.6" customFormat="1" customHeight="1" s="11">
-      <s:c r="B36" s="12" t="n"/>
-      <s:c r="C36" s="12" t="n"/>
-      <s:c r="D36" s="13" t="n"/>
+    <s:row r="36" ht="24.6" customFormat="1" customHeight="1" s="13">
+      <s:c r="B36" s="14" t="n"/>
+      <s:c r="C36" s="14" t="n"/>
+      <s:c r="D36" s="15" t="n"/>
     </s:row>
   </s:sheetData>
   <s:mergeCells count="28">
@@ -2167,1075 +2182,1075 @@
   <s:dimension ref="A1:E55"/>
   <s:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="22.5" outlineLevelCol="4"/>
   <s:cols>
-    <s:col width="37.75" customWidth="1" style="9" min="1" max="2"/>
+    <s:col width="37.75" customWidth="1" style="11" min="1" max="2"/>
     <s:col width="33.0833333333333" customWidth="1" style="1" min="3" max="3"/>
     <s:col width="40.4416666666667" customWidth="1" style="1" min="4" max="5"/>
   </s:cols>
   <s:sheetData>
     <s:row r="1" ht="22.2" customHeight="1" s="1">
-      <s:c r="A1" s="10" t="inlineStr">
+      <s:c r="A1" s="12" t="inlineStr">
         <s:is>
           <s:t>索引</s:t>
         </s:is>
       </s:c>
-      <s:c r="B1" s="10" t="inlineStr">
+      <s:c r="B1" s="12" t="inlineStr">
         <s:is>
           <s:t>组ID</s:t>
         </s:is>
       </s:c>
-      <s:c r="C1" s="10" t="inlineStr">
+      <s:c r="C1" s="12" t="inlineStr">
         <s:is>
           <s:t>Deprecated: use CommonConfig.ToyRefreshRatio</s:t>
         </s:is>
       </s:c>
-      <s:c r="D1" s="10" t="inlineStr">
+      <s:c r="D1" s="12" t="inlineStr">
         <s:is>
           <s:t>Deprecated: use CommonConfig.ToyLuckyCount</s:t>
         </s:is>
       </s:c>
-      <s:c r="E1" s="10" t="inlineStr">
+      <s:c r="E1" s="12" t="inlineStr">
         <s:is>
           <s:t>幸运刷新倍率</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="2" ht="22.2" customHeight="1" s="1">
-      <s:c r="A2" s="10" t="inlineStr">
+      <s:c r="A2" s="12" t="inlineStr">
         <s:is>
           <s:t>Index</s:t>
         </s:is>
       </s:c>
-      <s:c r="B2" s="10" t="inlineStr">
+      <s:c r="B2" s="12" t="inlineStr">
         <s:is>
           <s:t>AreaId</s:t>
         </s:is>
       </s:c>
-      <s:c r="C2" s="10" t="inlineStr">
+      <s:c r="C2" s="12" t="inlineStr">
         <s:is>
           <s:t>NormalRefreshCount</s:t>
         </s:is>
       </s:c>
-      <s:c r="D2" s="10" t="inlineStr">
+      <s:c r="D2" s="12" t="inlineStr">
         <s:is>
           <s:t>LuckRefreshCount</s:t>
         </s:is>
       </s:c>
-      <s:c r="E2" s="10" t="inlineStr">
+      <s:c r="E2" s="12" t="inlineStr">
         <s:is>
           <s:t>LuckRefreshRate</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="3" ht="22.2" customHeight="1" s="1">
-      <s:c r="A3" s="10" t="inlineStr">
+      <s:c r="A3" s="12" t="inlineStr">
         <s:is>
           <s:t>number</s:t>
         </s:is>
       </s:c>
-      <s:c r="B3" s="10" t="inlineStr">
+      <s:c r="B3" s="12" t="inlineStr">
         <s:is>
           <s:t>number</s:t>
         </s:is>
       </s:c>
-      <s:c r="C3" s="10" t="inlineStr">
+      <s:c r="C3" s="12" t="inlineStr">
         <s:is>
           <s:t>number_option</s:t>
         </s:is>
       </s:c>
-      <s:c r="D3" s="10" t="inlineStr">
+      <s:c r="D3" s="12" t="inlineStr">
         <s:is>
           <s:t>number_option</s:t>
         </s:is>
       </s:c>
-      <s:c r="E3" s="10" t="inlineStr">
+      <s:c r="E3" s="12" t="inlineStr">
         <s:is>
           <s:t>number_array_option</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="4" ht="22.2" customHeight="1" s="1">
-      <s:c r="A4" s="10" t="n">
+      <s:c r="A4" s="12" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="B4" s="10" t="n">
+      <s:c r="B4" s="12" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="C4" s="10" t="n">
+      <s:c r="C4" s="12" t="n">
         <s:v>80</s:v>
       </s:c>
-      <s:c r="D4" s="10" t="n">
+      <s:c r="D4" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E4" s="10" t="inlineStr">
+      <s:c r="E4" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="5" ht="22.2" customHeight="1" s="1">
-      <s:c r="A5" s="10" t="n">
+      <s:c r="A5" s="12" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="B5" s="10" t="n">
+      <s:c r="B5" s="12" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="C5" s="10" t="n">
+      <s:c r="C5" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D5" s="10" t="n">
+      <s:c r="D5" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E5" s="10" t="inlineStr">
+      <s:c r="E5" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="6" ht="22.2" customHeight="1" s="1">
-      <s:c r="A6" s="10" t="n">
+      <s:c r="A6" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="B6" s="10" t="n">
+      <s:c r="B6" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="C6" s="10" t="n">
+      <s:c r="C6" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D6" s="10" t="n">
+      <s:c r="D6" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E6" s="10" t="inlineStr">
+      <s:c r="E6" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="7" ht="22.2" customHeight="1" s="1">
-      <s:c r="A7" s="10" t="n">
+      <s:c r="A7" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="B7" s="10" t="n">
+      <s:c r="B7" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="C7" s="10" t="n">
+      <s:c r="C7" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D7" s="10" t="n">
+      <s:c r="D7" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E7" s="10" t="inlineStr">
+      <s:c r="E7" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="8" ht="22.2" customHeight="1" s="1">
-      <s:c r="A8" s="10" t="n">
+      <s:c r="A8" s="12" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="B8" s="10" t="n">
+      <s:c r="B8" s="12" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="C8" s="10" t="n">
+      <s:c r="C8" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D8" s="10" t="n">
+      <s:c r="D8" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E8" s="10" t="inlineStr">
+      <s:c r="E8" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="9" ht="22.2" customHeight="1" s="1">
-      <s:c r="A9" s="10" t="n">
+      <s:c r="A9" s="12" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="B9" s="10" t="n">
+      <s:c r="B9" s="12" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="C9" s="10" t="n">
+      <s:c r="C9" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D9" s="10" t="n">
+      <s:c r="D9" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E9" s="10" t="inlineStr">
+      <s:c r="E9" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="10" ht="22.2" customHeight="1" s="1">
-      <s:c r="A10" s="10" t="n">
+      <s:c r="A10" s="12" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="B10" s="10" t="n">
+      <s:c r="B10" s="12" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="C10" s="10" t="n">
+      <s:c r="C10" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D10" s="10" t="n">
+      <s:c r="D10" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E10" s="10" t="inlineStr">
+      <s:c r="E10" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="11" ht="22.2" customHeight="1" s="1">
-      <s:c r="A11" s="10" t="n">
+      <s:c r="A11" s="12" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="B11" s="10" t="n">
+      <s:c r="B11" s="12" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="C11" s="10" t="n">
+      <s:c r="C11" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D11" s="10" t="n">
+      <s:c r="D11" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E11" s="10" t="inlineStr">
+      <s:c r="E11" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="12" ht="22.2" customHeight="1" s="1">
-      <s:c r="A12" s="10" t="n">
+      <s:c r="A12" s="12" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="B12" s="10" t="n">
+      <s:c r="B12" s="12" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="C12" s="10" t="n">
+      <s:c r="C12" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D12" s="10" t="n">
+      <s:c r="D12" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E12" s="10" t="inlineStr">
+      <s:c r="E12" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="13" ht="22.2" customHeight="1" s="1">
-      <s:c r="A13" s="10" t="n">
+      <s:c r="A13" s="12" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="B13" s="10" t="n">
+      <s:c r="B13" s="12" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="C13" s="10" t="n">
+      <s:c r="C13" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D13" s="10" t="n">
+      <s:c r="D13" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E13" s="10" t="inlineStr">
+      <s:c r="E13" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="14" ht="22.2" customHeight="1" s="1">
-      <s:c r="A14" s="10" t="n">
+      <s:c r="A14" s="12" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="B14" s="10" t="n">
+      <s:c r="B14" s="12" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="C14" s="10" t="n">
+      <s:c r="C14" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D14" s="10" t="n">
+      <s:c r="D14" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E14" s="10" t="inlineStr">
+      <s:c r="E14" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="15" ht="22.2" customHeight="1" s="1">
-      <s:c r="A15" s="10" t="n">
+      <s:c r="A15" s="12" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="B15" s="10" t="n">
+      <s:c r="B15" s="12" t="n">
         <s:v>12</s:v>
       </s:c>
-      <s:c r="C15" s="10" t="n">
+      <s:c r="C15" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D15" s="10" t="n">
+      <s:c r="D15" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E15" s="10" t="inlineStr">
+      <s:c r="E15" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="16" ht="22.2" customHeight="1" s="1">
-      <s:c r="A16" s="10" t="n">
+      <s:c r="A16" s="12" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="B16" s="10" t="n">
+      <s:c r="B16" s="12" t="n">
         <s:v>13</s:v>
       </s:c>
-      <s:c r="C16" s="10" t="n">
+      <s:c r="C16" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D16" s="10" t="n">
+      <s:c r="D16" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E16" s="10" t="inlineStr">
+      <s:c r="E16" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="17" ht="22.2" customHeight="1" s="1">
-      <s:c r="A17" s="10" t="n">
+      <s:c r="A17" s="12" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="B17" s="10" t="n">
+      <s:c r="B17" s="12" t="n">
         <s:v>14</s:v>
       </s:c>
-      <s:c r="C17" s="10" t="n">
+      <s:c r="C17" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D17" s="10" t="n">
+      <s:c r="D17" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E17" s="10" t="inlineStr">
+      <s:c r="E17" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="18" ht="22.2" customHeight="1" s="1">
-      <s:c r="A18" s="10" t="n">
+      <s:c r="A18" s="12" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="B18" s="10" t="n">
+      <s:c r="B18" s="12" t="n">
         <s:v>15</s:v>
       </s:c>
-      <s:c r="C18" s="10" t="n">
+      <s:c r="C18" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D18" s="10" t="n">
+      <s:c r="D18" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E18" s="10" t="inlineStr">
+      <s:c r="E18" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="19" ht="22.2" customHeight="1" s="1">
-      <s:c r="A19" s="10" t="n">
+      <s:c r="A19" s="12" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="B19" s="10" t="n">
+      <s:c r="B19" s="12" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="C19" s="10" t="n">
+      <s:c r="C19" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D19" s="10" t="n">
+      <s:c r="D19" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E19" s="10" t="inlineStr">
+      <s:c r="E19" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="20" ht="22.2" customHeight="1" s="1">
-      <s:c r="A20" s="10" t="n">
+      <s:c r="A20" s="12" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="B20" s="10" t="n">
+      <s:c r="B20" s="12" t="n">
         <s:v>17</s:v>
       </s:c>
-      <s:c r="C20" s="10" t="n">
+      <s:c r="C20" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D20" s="10" t="n">
+      <s:c r="D20" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E20" s="10" t="inlineStr">
+      <s:c r="E20" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="21" ht="22.2" customHeight="1" s="1">
-      <s:c r="A21" s="10" t="n">
+      <s:c r="A21" s="12" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="B21" s="10" t="n">
+      <s:c r="B21" s="12" t="n">
         <s:v>18</s:v>
       </s:c>
-      <s:c r="C21" s="10" t="n">
+      <s:c r="C21" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D21" s="10" t="n">
+      <s:c r="D21" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E21" s="10" t="inlineStr">
+      <s:c r="E21" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="22" ht="22.2" customHeight="1" s="1">
-      <s:c r="A22" s="10" t="n">
+      <s:c r="A22" s="12" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="B22" s="10" t="n">
+      <s:c r="B22" s="12" t="n">
         <s:v>19</s:v>
       </s:c>
-      <s:c r="C22" s="10" t="n">
+      <s:c r="C22" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D22" s="10" t="n">
+      <s:c r="D22" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E22" s="10" t="inlineStr">
+      <s:c r="E22" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="23" ht="22.2" customHeight="1" s="1">
-      <s:c r="A23" s="10" t="n">
+      <s:c r="A23" s="12" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="B23" s="10" t="n">
+      <s:c r="B23" s="12" t="n">
         <s:v>20</s:v>
       </s:c>
-      <s:c r="C23" s="10" t="n">
+      <s:c r="C23" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D23" s="10" t="n">
+      <s:c r="D23" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E23" s="10" t="inlineStr">
+      <s:c r="E23" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="24" ht="22.2" customHeight="1" s="1">
-      <s:c r="A24" s="10" t="n">
+      <s:c r="A24" s="12" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="B24" s="10" t="n">
+      <s:c r="B24" s="12" t="n">
         <s:v>21</s:v>
       </s:c>
-      <s:c r="C24" s="10" t="n">
+      <s:c r="C24" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D24" s="10" t="n">
+      <s:c r="D24" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E24" s="10" t="inlineStr">
+      <s:c r="E24" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="25" ht="22.2" customHeight="1" s="1">
-      <s:c r="A25" s="10" t="n">
+      <s:c r="A25" s="12" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="B25" s="10" t="n">
+      <s:c r="B25" s="12" t="n">
         <s:v>22</s:v>
       </s:c>
-      <s:c r="C25" s="10" t="n">
+      <s:c r="C25" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D25" s="10" t="n">
+      <s:c r="D25" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E25" s="10" t="inlineStr">
+      <s:c r="E25" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="26" ht="22.2" customHeight="1" s="1">
-      <s:c r="A26" s="10" t="n">
+      <s:c r="A26" s="12" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="B26" s="10" t="n">
+      <s:c r="B26" s="12" t="n">
         <s:v>23</s:v>
       </s:c>
-      <s:c r="C26" s="10" t="n">
+      <s:c r="C26" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D26" s="10" t="n">
+      <s:c r="D26" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E26" s="10" t="inlineStr">
+      <s:c r="E26" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="27" ht="22.2" customHeight="1" s="1">
-      <s:c r="A27" s="10" t="n">
+      <s:c r="A27" s="12" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="B27" s="10" t="n">
+      <s:c r="B27" s="12" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="C27" s="10" t="n">
+      <s:c r="C27" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D27" s="10" t="n">
+      <s:c r="D27" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E27" s="10" t="inlineStr">
+      <s:c r="E27" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="28" ht="22.2" customHeight="1" s="1">
-      <s:c r="A28" s="10" t="n">
+      <s:c r="A28" s="12" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="B28" s="10" t="n">
+      <s:c r="B28" s="12" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="C28" s="10" t="n">
+      <s:c r="C28" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D28" s="10" t="n">
+      <s:c r="D28" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E28" s="10" t="inlineStr">
+      <s:c r="E28" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="29" ht="22.2" customHeight="1" s="1">
-      <s:c r="A29" s="10" t="n">
+      <s:c r="A29" s="12" t="n">
         <s:v>26</s:v>
       </s:c>
-      <s:c r="B29" s="10" t="n">
+      <s:c r="B29" s="12" t="n">
         <s:v>26</s:v>
       </s:c>
-      <s:c r="C29" s="10" t="n">
+      <s:c r="C29" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D29" s="10" t="n">
+      <s:c r="D29" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E29" s="10" t="inlineStr">
+      <s:c r="E29" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="30" ht="22.2" customHeight="1" s="1">
-      <s:c r="A30" s="10" t="n">
+      <s:c r="A30" s="12" t="n">
         <s:v>27</s:v>
       </s:c>
-      <s:c r="B30" s="10" t="n">
+      <s:c r="B30" s="12" t="n">
         <s:v>27</s:v>
       </s:c>
-      <s:c r="C30" s="10" t="n">
+      <s:c r="C30" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D30" s="10" t="n">
+      <s:c r="D30" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E30" s="10" t="inlineStr">
+      <s:c r="E30" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="31" ht="22.2" customHeight="1" s="1">
-      <s:c r="A31" s="10" t="n">
+      <s:c r="A31" s="12" t="n">
         <s:v>28</s:v>
       </s:c>
-      <s:c r="B31" s="10" t="n">
+      <s:c r="B31" s="12" t="n">
         <s:v>28</s:v>
       </s:c>
-      <s:c r="C31" s="10" t="n">
+      <s:c r="C31" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D31" s="10" t="n">
+      <s:c r="D31" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E31" s="10" t="inlineStr">
+      <s:c r="E31" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="32" ht="22.2" customHeight="1" s="1">
-      <s:c r="A32" s="10" t="n">
+      <s:c r="A32" s="12" t="n">
         <s:v>29</s:v>
       </s:c>
-      <s:c r="B32" s="10" t="n">
+      <s:c r="B32" s="12" t="n">
         <s:v>29</s:v>
       </s:c>
-      <s:c r="C32" s="10" t="n">
+      <s:c r="C32" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D32" s="10" t="n">
+      <s:c r="D32" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E32" s="10" t="inlineStr">
+      <s:c r="E32" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="33" ht="22.2" customHeight="1" s="1">
-      <s:c r="A33" s="10" t="n">
+      <s:c r="A33" s="12" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="B33" s="10" t="n">
+      <s:c r="B33" s="12" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="C33" s="10" t="n">
+      <s:c r="C33" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D33" s="10" t="n">
+      <s:c r="D33" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E33" s="10" t="inlineStr">
+      <s:c r="E33" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="34" ht="22.2" customHeight="1" s="1">
-      <s:c r="A34" s="10" t="n">
+      <s:c r="A34" s="12" t="n">
         <s:v>31</s:v>
       </s:c>
-      <s:c r="B34" s="10" t="n">
+      <s:c r="B34" s="12" t="n">
         <s:v>31</s:v>
       </s:c>
-      <s:c r="C34" s="10" t="n">
+      <s:c r="C34" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D34" s="10" t="n">
+      <s:c r="D34" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E34" s="10" t="inlineStr">
+      <s:c r="E34" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="35" ht="22.2" customHeight="1" s="1">
-      <s:c r="A35" s="10" t="n">
+      <s:c r="A35" s="12" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="B35" s="10" t="n">
+      <s:c r="B35" s="12" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="C35" s="10" t="n">
+      <s:c r="C35" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D35" s="10" t="n">
+      <s:c r="D35" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E35" s="10" t="inlineStr">
+      <s:c r="E35" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="36" ht="22.2" customHeight="1" s="1">
-      <s:c r="A36" s="10" t="n">
+      <s:c r="A36" s="12" t="n">
         <s:v>33</s:v>
       </s:c>
-      <s:c r="B36" s="10" t="n">
+      <s:c r="B36" s="12" t="n">
         <s:v>33</s:v>
       </s:c>
-      <s:c r="C36" s="10" t="n">
+      <s:c r="C36" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D36" s="10" t="n">
+      <s:c r="D36" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E36" s="10" t="inlineStr">
+      <s:c r="E36" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="37" ht="22.2" customHeight="1" s="1">
-      <s:c r="A37" s="10" t="n">
+      <s:c r="A37" s="12" t="n">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="B37" s="10" t="n">
+      <s:c r="B37" s="12" t="n">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="C37" s="10" t="n">
+      <s:c r="C37" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D37" s="10" t="n">
+      <s:c r="D37" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E37" s="10" t="inlineStr">
+      <s:c r="E37" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="38" ht="22.2" customHeight="1" s="1">
-      <s:c r="A38" s="10" t="n">
+      <s:c r="A38" s="12" t="n">
         <s:v>35</s:v>
       </s:c>
-      <s:c r="B38" s="10" t="n">
+      <s:c r="B38" s="12" t="n">
         <s:v>35</s:v>
       </s:c>
-      <s:c r="C38" s="10" t="n">
+      <s:c r="C38" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D38" s="10" t="n">
+      <s:c r="D38" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E38" s="10" t="inlineStr">
+      <s:c r="E38" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="39" ht="22.2" customHeight="1" s="1">
-      <s:c r="A39" s="10" t="n">
+      <s:c r="A39" s="12" t="n">
         <s:v>36</s:v>
       </s:c>
-      <s:c r="B39" s="10" t="n">
+      <s:c r="B39" s="12" t="n">
         <s:v>36</s:v>
       </s:c>
-      <s:c r="C39" s="10" t="n">
+      <s:c r="C39" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D39" s="10" t="n">
+      <s:c r="D39" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E39" s="10" t="inlineStr">
+      <s:c r="E39" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="40" ht="22.2" customHeight="1" s="1">
-      <s:c r="A40" s="10" t="n">
+      <s:c r="A40" s="12" t="n">
         <s:v>37</s:v>
       </s:c>
-      <s:c r="B40" s="10" t="n">
+      <s:c r="B40" s="12" t="n">
         <s:v>37</s:v>
       </s:c>
-      <s:c r="C40" s="10" t="n">
+      <s:c r="C40" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D40" s="10" t="n">
+      <s:c r="D40" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E40" s="10" t="inlineStr">
+      <s:c r="E40" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="41" ht="22.2" customHeight="1" s="1">
-      <s:c r="A41" s="10" t="n">
+      <s:c r="A41" s="12" t="n">
         <s:v>38</s:v>
       </s:c>
-      <s:c r="B41" s="10" t="n">
+      <s:c r="B41" s="12" t="n">
         <s:v>38</s:v>
       </s:c>
-      <s:c r="C41" s="10" t="n">
+      <s:c r="C41" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D41" s="10" t="n">
+      <s:c r="D41" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E41" s="10" t="inlineStr">
+      <s:c r="E41" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="42" ht="22.2" customHeight="1" s="1">
-      <s:c r="A42" s="10" t="n">
+      <s:c r="A42" s="12" t="n">
         <s:v>39</s:v>
       </s:c>
-      <s:c r="B42" s="10" t="n">
+      <s:c r="B42" s="12" t="n">
         <s:v>39</s:v>
       </s:c>
-      <s:c r="C42" s="10" t="n">
+      <s:c r="C42" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D42" s="10" t="n">
+      <s:c r="D42" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E42" s="10" t="inlineStr">
+      <s:c r="E42" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="43" ht="22.2" customHeight="1" s="1">
-      <s:c r="A43" s="10" t="n">
+      <s:c r="A43" s="12" t="n">
         <s:v>40</s:v>
       </s:c>
-      <s:c r="B43" s="10" t="n">
+      <s:c r="B43" s="12" t="n">
         <s:v>40</s:v>
       </s:c>
-      <s:c r="C43" s="10" t="n">
+      <s:c r="C43" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D43" s="10" t="n">
+      <s:c r="D43" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E43" s="10" t="inlineStr">
+      <s:c r="E43" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="44" ht="22.2" customHeight="1" s="1">
-      <s:c r="A44" s="10" t="n">
+      <s:c r="A44" s="12" t="n">
         <s:v>41</s:v>
       </s:c>
-      <s:c r="B44" s="10" t="n">
+      <s:c r="B44" s="12" t="n">
         <s:v>41</s:v>
       </s:c>
-      <s:c r="C44" s="10" t="n">
+      <s:c r="C44" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D44" s="10" t="n">
+      <s:c r="D44" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E44" s="10" t="inlineStr">
+      <s:c r="E44" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="45" ht="22.2" customHeight="1" s="1">
-      <s:c r="A45" s="10" t="n">
+      <s:c r="A45" s="12" t="n">
         <s:v>42</s:v>
       </s:c>
-      <s:c r="B45" s="10" t="n">
+      <s:c r="B45" s="12" t="n">
         <s:v>42</s:v>
       </s:c>
-      <s:c r="C45" s="10" t="n">
+      <s:c r="C45" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D45" s="10" t="n">
+      <s:c r="D45" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E45" s="10" t="inlineStr">
+      <s:c r="E45" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="46" ht="22.2" customHeight="1" s="1">
-      <s:c r="A46" s="10" t="n">
+      <s:c r="A46" s="12" t="n">
         <s:v>43</s:v>
       </s:c>
-      <s:c r="B46" s="10" t="n">
+      <s:c r="B46" s="12" t="n">
         <s:v>43</s:v>
       </s:c>
-      <s:c r="C46" s="10" t="n">
+      <s:c r="C46" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D46" s="10" t="n">
+      <s:c r="D46" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E46" s="10" t="inlineStr">
+      <s:c r="E46" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="47" ht="22.2" customHeight="1" s="1">
-      <s:c r="A47" s="10" t="n">
+      <s:c r="A47" s="12" t="n">
         <s:v>44</s:v>
       </s:c>
-      <s:c r="B47" s="10" t="n">
+      <s:c r="B47" s="12" t="n">
         <s:v>44</s:v>
       </s:c>
-      <s:c r="C47" s="10" t="n">
+      <s:c r="C47" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D47" s="10" t="n">
+      <s:c r="D47" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E47" s="10" t="inlineStr">
+      <s:c r="E47" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="48" ht="22.2" customHeight="1" s="1">
-      <s:c r="A48" s="10" t="n">
+      <s:c r="A48" s="12" t="n">
         <s:v>45</s:v>
       </s:c>
-      <s:c r="B48" s="10" t="n">
+      <s:c r="B48" s="12" t="n">
         <s:v>45</s:v>
       </s:c>
-      <s:c r="C48" s="10" t="n">
+      <s:c r="C48" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D48" s="10" t="n">
+      <s:c r="D48" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E48" s="10" t="inlineStr">
+      <s:c r="E48" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="49" ht="22.2" customHeight="1" s="1">
-      <s:c r="A49" s="10" t="n">
+      <s:c r="A49" s="12" t="n">
         <s:v>46</s:v>
       </s:c>
-      <s:c r="B49" s="10" t="n">
+      <s:c r="B49" s="12" t="n">
         <s:v>46</s:v>
       </s:c>
-      <s:c r="C49" s="10" t="n">
+      <s:c r="C49" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D49" s="10" t="n">
+      <s:c r="D49" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E49" s="10" t="inlineStr">
+      <s:c r="E49" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="50" ht="22.2" customHeight="1" s="1">
-      <s:c r="A50" s="10" t="n">
+      <s:c r="A50" s="12" t="n">
         <s:v>47</s:v>
       </s:c>
-      <s:c r="B50" s="10" t="n">
+      <s:c r="B50" s="12" t="n">
         <s:v>47</s:v>
       </s:c>
-      <s:c r="C50" s="10" t="n">
+      <s:c r="C50" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D50" s="10" t="n">
+      <s:c r="D50" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E50" s="10" t="inlineStr">
+      <s:c r="E50" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="51" ht="22.2" customHeight="1" s="1">
-      <s:c r="A51" s="10" t="n">
+      <s:c r="A51" s="12" t="n">
         <s:v>48</s:v>
       </s:c>
-      <s:c r="B51" s="10" t="n">
+      <s:c r="B51" s="12" t="n">
         <s:v>48</s:v>
       </s:c>
-      <s:c r="C51" s="10" t="n">
+      <s:c r="C51" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D51" s="10" t="n">
+      <s:c r="D51" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E51" s="10" t="inlineStr">
+      <s:c r="E51" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="52" ht="22.2" customHeight="1" s="1">
-      <s:c r="A52" s="10" t="n">
+      <s:c r="A52" s="12" t="n">
         <s:v>49</s:v>
       </s:c>
-      <s:c r="B52" s="10" t="n">
+      <s:c r="B52" s="12" t="n">
         <s:v>49</s:v>
       </s:c>
-      <s:c r="C52" s="10" t="n">
+      <s:c r="C52" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D52" s="10" t="n">
+      <s:c r="D52" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E52" s="10" t="inlineStr">
+      <s:c r="E52" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="53" ht="22.2" customHeight="1" s="1">
-      <s:c r="A53" s="10" t="n">
+      <s:c r="A53" s="12" t="n">
         <s:v>50</s:v>
       </s:c>
-      <s:c r="B53" s="10" t="n">
+      <s:c r="B53" s="12" t="n">
         <s:v>50</s:v>
       </s:c>
-      <s:c r="C53" s="10" t="n">
+      <s:c r="C53" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D53" s="10" t="n">
+      <s:c r="D53" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E53" s="10" t="inlineStr">
+      <s:c r="E53" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="54" ht="22.2" customHeight="1" s="1">
-      <s:c r="A54" s="10" t="n">
+      <s:c r="A54" s="12" t="n">
         <s:v>51</s:v>
       </s:c>
-      <s:c r="B54" s="10" t="n">
+      <s:c r="B54" s="12" t="n">
         <s:v>51</s:v>
       </s:c>
-      <s:c r="C54" s="10" t="n">
+      <s:c r="C54" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D54" s="10" t="n">
+      <s:c r="D54" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E54" s="10" t="inlineStr">
+      <s:c r="E54" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="55" ht="22.2" customHeight="1" s="1">
-      <s:c r="A55" s="10" t="n">
+      <s:c r="A55" s="12" t="n">
         <s:v>52</s:v>
       </s:c>
-      <s:c r="B55" s="10" t="n">
+      <s:c r="B55" s="12" t="n">
         <s:v>52</s:v>
       </s:c>
-      <s:c r="C55" s="10" t="n">
+      <s:c r="C55" s="12" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="D55" s="10" t="n">
+      <s:c r="D55" s="12" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E55" s="10" t="inlineStr">
+      <s:c r="E55" s="12" t="inlineStr">
         <s:is>
           <s:t>2.5,3</s:t>
         </s:is>
@@ -3391,10 +3406,12 @@
         <s:f>CEILING(A4/4,1)</s:f>
         <s:v>1</s:v>
       </s:c>
-      <s:c r="E4" s="4" t="n">
-        <s:v>113244405937302</s:v>
-      </s:c>
-      <s:c r="F4" s="5" t="inlineStr">
+      <s:c r="E4" s="22" t="inlineStr">
+        <s:is>
+          <s:t>113244405937302</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F4" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_001_Nail</s:t>
         </s:is>
@@ -3421,10 +3438,12 @@
         <s:f>CEILING(A5/4,1)</s:f>
         <s:v>1</s:v>
       </s:c>
-      <s:c r="E5" s="4" t="n">
-        <s:v>105711056874756</s:v>
-      </s:c>
-      <s:c r="F5" s="5" t="inlineStr">
+      <s:c r="E5" s="22" t="inlineStr">
+        <s:is>
+          <s:t>105711056874756</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F5" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_002_Pill</s:t>
         </s:is>
@@ -3452,10 +3471,12 @@
         <s:f>CEILING(A6/4,1)</s:f>
         <s:v>1</s:v>
       </s:c>
-      <s:c r="E6" s="4" t="n">
-        <s:v>82693303214454</s:v>
-      </s:c>
-      <s:c r="F6" s="5" t="inlineStr">
+      <s:c r="E6" s="22" t="inlineStr">
+        <s:is>
+          <s:t>82693303214454</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F6" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_003_Capsule</s:t>
         </s:is>
@@ -3483,10 +3504,12 @@
         <s:f>CEILING(A7/4,1)</s:f>
         <s:v>1</s:v>
       </s:c>
-      <s:c r="E7" s="4" t="n">
-        <s:v>102504658102706</s:v>
-      </s:c>
-      <s:c r="F7" s="5" t="inlineStr">
+      <s:c r="E7" s="22" t="inlineStr">
+        <s:is>
+          <s:t>102504658102706</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F7" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_004_Battery01</s:t>
         </s:is>
@@ -3514,10 +3537,10 @@
         <s:f>CEILING(A8/4,1)</s:f>
         <s:v>2</s:v>
       </s:c>
-      <s:c r="E8" s="4" t="n">
+      <s:c r="E8" s="26" t="n">
         <s:v>83069096807916</s:v>
       </s:c>
-      <s:c r="F8" s="5" t="inlineStr">
+      <s:c r="F8" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_005_Battery02</s:t>
         </s:is>
@@ -3544,10 +3567,10 @@
         <s:f>CEILING(A9/4,1)</s:f>
         <s:v>2</s:v>
       </s:c>
-      <s:c r="E9" s="4" t="n">
+      <s:c r="E9" s="26" t="n">
         <s:v>80534536398974</s:v>
       </s:c>
-      <s:c r="F9" s="5" t="inlineStr">
+      <s:c r="F9" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_006_Biscuit01</s:t>
         </s:is>
@@ -3575,10 +3598,10 @@
         <s:f>CEILING(A10/4,1)</s:f>
         <s:v>2</s:v>
       </s:c>
-      <s:c r="E10" s="4" t="n">
+      <s:c r="E10" s="26" t="n">
         <s:v>74246671448525</s:v>
       </s:c>
-      <s:c r="F10" s="5" t="inlineStr">
+      <s:c r="F10" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_007_Biscuit02</s:t>
         </s:is>
@@ -3606,10 +3629,10 @@
         <s:f>CEILING(A11/4,1)</s:f>
         <s:v>2</s:v>
       </s:c>
-      <s:c r="E11" s="4" t="n">
+      <s:c r="E11" s="26" t="n">
         <s:v>71499702430100</s:v>
       </s:c>
-      <s:c r="F11" s="5" t="inlineStr">
+      <s:c r="F11" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_008_Biscuit03</s:t>
         </s:is>
@@ -3637,10 +3660,10 @@
         <s:f>CEILING(A12/4,1)</s:f>
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E12" s="4" t="n">
+      <s:c r="E12" s="26" t="n">
         <s:v>122909083001205</s:v>
       </s:c>
-      <s:c r="F12" s="5" t="inlineStr">
+      <s:c r="F12" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_009_Chocolate01</s:t>
         </s:is>
@@ -3667,10 +3690,10 @@
         <s:f>CEILING(A13/4,1)</s:f>
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E13" s="4" t="n">
+      <s:c r="E13" s="26" t="n">
         <s:v>128658267266293</s:v>
       </s:c>
-      <s:c r="F13" s="5" t="inlineStr">
+      <s:c r="F13" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_010_Chocolate02</s:t>
         </s:is>
@@ -3697,10 +3720,10 @@
         <s:f>CEILING(A14/4,1)</s:f>
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E14" s="4" t="n">
+      <s:c r="E14" s="26" t="n">
         <s:v>134748387119946</s:v>
       </s:c>
-      <s:c r="F14" s="5" t="inlineStr">
+      <s:c r="F14" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_011_Chocolate_Drink</s:t>
         </s:is>
@@ -3727,10 +3750,10 @@
         <s:f>CEILING(A15/4,1)</s:f>
         <s:v>3</s:v>
       </s:c>
-      <s:c r="E15" s="4" t="n">
+      <s:c r="E15" s="26" t="n">
         <s:v>131559815185521</s:v>
       </s:c>
-      <s:c r="F15" s="5" t="inlineStr">
+      <s:c r="F15" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_012_Honey01</s:t>
         </s:is>
@@ -3757,10 +3780,10 @@
         <s:f>CEILING(A16/4,1)</s:f>
         <s:v>4</s:v>
       </s:c>
-      <s:c r="E16" s="4" t="n">
+      <s:c r="E16" s="26" t="n">
         <s:v>135406755438948</s:v>
       </s:c>
-      <s:c r="F16" s="5" t="inlineStr">
+      <s:c r="F16" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_013_Honey02</s:t>
         </s:is>
@@ -3788,10 +3811,10 @@
         <s:f>CEILING(A17/4,1)</s:f>
         <s:v>4</s:v>
       </s:c>
-      <s:c r="E17" s="4" t="n">
+      <s:c r="E17" s="26" t="n">
         <s:v>128433990441931</s:v>
       </s:c>
-      <s:c r="F17" s="5" t="inlineStr">
+      <s:c r="F17" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_014_Jam01</s:t>
         </s:is>
@@ -3819,10 +3842,10 @@
         <s:f>CEILING(A18/4,1)</s:f>
         <s:v>4</s:v>
       </s:c>
-      <s:c r="E18" s="4" t="n">
+      <s:c r="E18" s="26" t="n">
         <s:v>86357992624263</s:v>
       </s:c>
-      <s:c r="F18" s="5" t="inlineStr">
+      <s:c r="F18" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_015_Jam02</s:t>
         </s:is>
@@ -3850,10 +3873,10 @@
         <s:f>CEILING(A19/4,1)</s:f>
         <s:v>4</s:v>
       </s:c>
-      <s:c r="E19" s="4" t="n">
+      <s:c r="E19" s="26" t="n">
         <s:v>96128137486525</s:v>
       </s:c>
-      <s:c r="F19" s="5" t="inlineStr">
+      <s:c r="F19" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_016_Water01</s:t>
         </s:is>
@@ -3881,10 +3904,10 @@
         <s:f>CEILING(A20/4,1)</s:f>
         <s:v>5</s:v>
       </s:c>
-      <s:c r="E20" s="4" t="n">
+      <s:c r="E20" s="26" t="n">
         <s:v>131913492630514</s:v>
       </s:c>
-      <s:c r="F20" s="5" t="inlineStr">
+      <s:c r="F20" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_017_Water02</s:t>
         </s:is>
@@ -3912,10 +3935,10 @@
         <s:f>CEILING(A21/4,1)</s:f>
         <s:v>5</s:v>
       </s:c>
-      <s:c r="E21" s="4" t="n">
+      <s:c r="E21" s="26" t="n">
         <s:v>119579899338192</s:v>
       </s:c>
-      <s:c r="F21" s="5" t="inlineStr">
+      <s:c r="F21" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_018_Water03</s:t>
         </s:is>
@@ -3943,10 +3966,10 @@
         <s:f>CEILING(A22/4,1)</s:f>
         <s:v>5</s:v>
       </s:c>
-      <s:c r="E22" s="4" t="n">
+      <s:c r="E22" s="26" t="n">
         <s:v>82472089572732</s:v>
       </s:c>
-      <s:c r="F22" s="5" t="inlineStr">
+      <s:c r="F22" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_019_Waterbottle01</s:t>
         </s:is>
@@ -3974,10 +3997,10 @@
         <s:f>CEILING(A23/4,1)</s:f>
         <s:v>5</s:v>
       </s:c>
-      <s:c r="E23" s="4" t="n">
+      <s:c r="E23" s="26" t="n">
         <s:v>104108852156434</s:v>
       </s:c>
-      <s:c r="F23" s="5" t="inlineStr">
+      <s:c r="F23" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_020_Waterbottle02</s:t>
         </s:is>
@@ -4005,10 +4028,10 @@
         <s:f>CEILING(A24/4,1)</s:f>
         <s:v>6</s:v>
       </s:c>
-      <s:c r="E24" s="4" t="n">
+      <s:c r="E24" s="26" t="n">
         <s:v>79005623120233</s:v>
       </s:c>
-      <s:c r="F24" s="5" t="inlineStr">
+      <s:c r="F24" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_021_Bottle01</s:t>
         </s:is>
@@ -4036,10 +4059,10 @@
         <s:f>CEILING(A25/4,1)</s:f>
         <s:v>6</s:v>
       </s:c>
-      <s:c r="E25" s="4" t="n">
+      <s:c r="E25" s="26" t="n">
         <s:v>97611938478078</s:v>
       </s:c>
-      <s:c r="F25" s="5" t="inlineStr">
+      <s:c r="F25" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_022_Bottle02</s:t>
         </s:is>
@@ -4067,10 +4090,10 @@
         <s:f>CEILING(A26/4,1)</s:f>
         <s:v>6</s:v>
       </s:c>
-      <s:c r="E26" s="4" t="n">
+      <s:c r="E26" s="26" t="n">
         <s:v>81806655827798</s:v>
       </s:c>
-      <s:c r="F26" s="5" t="inlineStr">
+      <s:c r="F26" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_023_Bottle03</s:t>
         </s:is>
@@ -4098,10 +4121,10 @@
         <s:f>CEILING(A27/4,1)</s:f>
         <s:v>6</s:v>
       </s:c>
-      <s:c r="E27" s="4" t="n">
+      <s:c r="E27" s="26" t="n">
         <s:v>105716218867716</s:v>
       </s:c>
-      <s:c r="F27" s="5" t="inlineStr">
+      <s:c r="F27" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_024_Bottle04</s:t>
         </s:is>
@@ -4129,10 +4152,10 @@
         <s:f>CEILING(A28/4,1)</s:f>
         <s:v>7</s:v>
       </s:c>
-      <s:c r="E28" s="4" t="n">
+      <s:c r="E28" s="26" t="n">
         <s:v>128411546772202</s:v>
       </s:c>
-      <s:c r="F28" s="5" t="inlineStr">
+      <s:c r="F28" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_025_Bottle05</s:t>
         </s:is>
@@ -4160,10 +4183,10 @@
         <s:f>CEILING(A29/4,1)</s:f>
         <s:v>7</s:v>
       </s:c>
-      <s:c r="E29" s="4" t="n">
+      <s:c r="E29" s="26" t="n">
         <s:v>139465058617680</s:v>
       </s:c>
-      <s:c r="F29" s="5" t="inlineStr">
+      <s:c r="F29" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_026_Can01</s:t>
         </s:is>
@@ -4191,10 +4214,10 @@
         <s:f>CEILING(A30/4,1)</s:f>
         <s:v>7</s:v>
       </s:c>
-      <s:c r="E30" s="4" t="n">
+      <s:c r="E30" s="26" t="n">
         <s:v>81737011057690</s:v>
       </s:c>
-      <s:c r="F30" s="5" t="inlineStr">
+      <s:c r="F30" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_027_Can02</s:t>
         </s:is>
@@ -4222,10 +4245,10 @@
         <s:f>CEILING(A31/4,1)</s:f>
         <s:v>7</s:v>
       </s:c>
-      <s:c r="E31" s="4" t="n">
+      <s:c r="E31" s="26" t="n">
         <s:v>81445862907930</s:v>
       </s:c>
-      <s:c r="F31" s="5" t="inlineStr">
+      <s:c r="F31" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_028_Can03</s:t>
         </s:is>
@@ -4253,10 +4276,10 @@
         <s:f>CEILING(A32/4,1)</s:f>
         <s:v>8</s:v>
       </s:c>
-      <s:c r="E32" s="4" t="n">
+      <s:c r="E32" s="26" t="n">
         <s:v>123098432383687</s:v>
       </s:c>
-      <s:c r="F32" s="5" t="inlineStr">
+      <s:c r="F32" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_029_Can04</s:t>
         </s:is>
@@ -4284,10 +4307,10 @@
         <s:f>CEILING(A33/4,1)</s:f>
         <s:v>8</s:v>
       </s:c>
-      <s:c r="E33" s="4" t="n">
+      <s:c r="E33" s="26" t="n">
         <s:v>131796260838154</s:v>
       </s:c>
-      <s:c r="F33" s="5" t="inlineStr">
+      <s:c r="F33" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_030_Can05</s:t>
         </s:is>
@@ -4314,10 +4337,10 @@
         <s:f>CEILING(A34/4,1)</s:f>
         <s:v>8</s:v>
       </s:c>
-      <s:c r="E34" s="4" t="n">
+      <s:c r="E34" s="26" t="n">
         <s:v>116376878683736</s:v>
       </s:c>
-      <s:c r="F34" s="5" t="inlineStr">
+      <s:c r="F34" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_031_Can06</s:t>
         </s:is>
@@ -4344,10 +4367,10 @@
         <s:f>CEILING(A35/4,1)</s:f>
         <s:v>8</s:v>
       </s:c>
-      <s:c r="E35" s="4" t="n">
+      <s:c r="E35" s="26" t="n">
         <s:v>100558097057142</s:v>
       </s:c>
-      <s:c r="F35" s="5" t="inlineStr">
+      <s:c r="F35" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_032_Can07</s:t>
         </s:is>
@@ -4374,10 +4397,10 @@
         <s:f>CEILING(A36/4,1)</s:f>
         <s:v>9</s:v>
       </s:c>
-      <s:c r="E36" s="4" t="n">
+      <s:c r="E36" s="26" t="n">
         <s:v>92332707761527</s:v>
       </s:c>
-      <s:c r="F36" s="5" t="inlineStr">
+      <s:c r="F36" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_033_Medicine_bottle01</s:t>
         </s:is>
@@ -4405,10 +4428,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>6</s:v>
       </s:c>
-      <s:c r="E37" s="4" t="n">
+      <s:c r="E37" s="26" t="n">
         <s:v>108895787734224</s:v>
       </s:c>
-      <s:c r="F37" s="5" t="inlineStr">
+      <s:c r="F37" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_034_Medicine_bottle02</s:t>
         </s:is>
@@ -4435,10 +4458,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>7</s:v>
       </s:c>
-      <s:c r="E38" s="4" t="n">
+      <s:c r="E38" s="26" t="n">
         <s:v>95471681056681</s:v>
       </s:c>
-      <s:c r="F38" s="5" t="inlineStr">
+      <s:c r="F38" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_035_Injection</s:t>
         </s:is>
@@ -4465,10 +4488,10 @@
         <s:f>CEILING(A39/4,1)</s:f>
         <s:v>9</s:v>
       </s:c>
-      <s:c r="E39" s="4" t="n">
+      <s:c r="E39" s="26" t="n">
         <s:v>104955598295323</s:v>
       </s:c>
-      <s:c r="F39" s="5" t="inlineStr">
+      <s:c r="F39" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_036_InjectionA</s:t>
         </s:is>
@@ -4496,10 +4519,10 @@
         <s:f>CEILING(A40/4,1)</s:f>
         <s:v>10</s:v>
       </s:c>
-      <s:c r="E40" s="4" t="n">
+      <s:c r="E40" s="26" t="n">
         <s:v>103175883366340</s:v>
       </s:c>
-      <s:c r="F40" s="5" t="inlineStr">
+      <s:c r="F40" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_037_First_aid_Kit_Bandage</s:t>
         </s:is>
@@ -4527,10 +4550,10 @@
         <s:f>CEILING(A41/4,1)</s:f>
         <s:v>10</s:v>
       </s:c>
-      <s:c r="E41" s="4" t="n">
+      <s:c r="E41" s="26" t="n">
         <s:v>114247164745798</s:v>
       </s:c>
-      <s:c r="F41" s="5" t="inlineStr">
+      <s:c r="F41" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_038_Lv</s:t>
         </s:is>
@@ -4557,10 +4580,10 @@
         <s:f>CEILING(A42/4,1)</s:f>
         <s:v>10</s:v>
       </s:c>
-      <s:c r="E42" s="4" t="n">
+      <s:c r="E42" s="26" t="n">
         <s:v>86017047390182</s:v>
       </s:c>
-      <s:c r="F42" s="5" t="inlineStr">
+      <s:c r="F42" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_039_First_aid_Kit01</s:t>
         </s:is>
@@ -4587,10 +4610,10 @@
         <s:f>CEILING(A43/4,1)</s:f>
         <s:v>10</s:v>
       </s:c>
-      <s:c r="E43" s="4" t="n">
+      <s:c r="E43" s="26" t="n">
         <s:v>81373582816266</s:v>
       </s:c>
-      <s:c r="F43" s="5" t="inlineStr">
+      <s:c r="F43" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_040_First_aid_Kit02</s:t>
         </s:is>
@@ -4617,10 +4640,10 @@
         <s:f>CEILING(A44/4,1)</s:f>
         <s:v>11</s:v>
       </s:c>
-      <s:c r="E44" s="4" t="n">
+      <s:c r="E44" s="26" t="n">
         <s:v>132788281080826</s:v>
       </s:c>
-      <s:c r="F44" s="5" t="inlineStr">
+      <s:c r="F44" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_041_First_aid_Kit03</s:t>
         </s:is>
@@ -4647,10 +4670,10 @@
         <s:f>CEILING(A45/4,1)</s:f>
         <s:v>11</s:v>
       </s:c>
-      <s:c r="E45" s="4" t="n">
+      <s:c r="E45" s="26" t="n">
         <s:v>95162444285252</s:v>
       </s:c>
-      <s:c r="F45" s="5" t="inlineStr">
+      <s:c r="F45" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_042_Detergent</s:t>
         </s:is>
@@ -4677,10 +4700,10 @@
         <s:f>CEILING(A46/4,1)</s:f>
         <s:v>11</s:v>
       </s:c>
-      <s:c r="E46" s="4" t="n">
+      <s:c r="E46" s="26" t="n">
         <s:v>95953438126479</s:v>
       </s:c>
-      <s:c r="F46" s="5" t="inlineStr">
+      <s:c r="F46" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_043_Bleach</s:t>
         </s:is>
@@ -4707,10 +4730,10 @@
         <s:f>CEILING(A47/4,1)</s:f>
         <s:v>11</s:v>
       </s:c>
-      <s:c r="E47" s="4" t="n">
+      <s:c r="E47" s="26" t="n">
         <s:v>112039222887887</s:v>
       </s:c>
-      <s:c r="F47" s="5" t="inlineStr">
+      <s:c r="F47" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_044_WD40</s:t>
         </s:is>
@@ -4737,10 +4760,10 @@
         <s:f>CEILING(A48/4,1)</s:f>
         <s:v>12</s:v>
       </s:c>
-      <s:c r="E48" s="4" t="n">
+      <s:c r="E48" s="26" t="n">
         <s:v>95377459606647</s:v>
       </s:c>
-      <s:c r="F48" s="5" t="inlineStr">
+      <s:c r="F48" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_045_Pipe</s:t>
         </s:is>
@@ -4767,10 +4790,10 @@
         <s:f>CEILING(A49/4,1)</s:f>
         <s:v>12</s:v>
       </s:c>
-      <s:c r="E49" s="4" t="n">
+      <s:c r="E49" s="26" t="n">
         <s:v>113983796605688</s:v>
       </s:c>
-      <s:c r="F49" s="5" t="inlineStr">
+      <s:c r="F49" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_046_Zippo</s:t>
         </s:is>
@@ -4797,10 +4820,10 @@
         <s:f>CEILING(A50/4,1)</s:f>
         <s:v>12</s:v>
       </s:c>
-      <s:c r="E50" s="4" t="n">
+      <s:c r="E50" s="26" t="n">
         <s:v>117157716541352</s:v>
       </s:c>
-      <s:c r="F50" s="5" t="inlineStr">
+      <s:c r="F50" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_047_Oilcan01</s:t>
         </s:is>
@@ -4827,10 +4850,10 @@
         <s:f>CEILING(A51/4,1)</s:f>
         <s:v>12</s:v>
       </s:c>
-      <s:c r="E51" s="4" t="n">
+      <s:c r="E51" s="26" t="n">
         <s:v>100893051807474</s:v>
       </s:c>
-      <s:c r="F51" s="5" t="inlineStr">
+      <s:c r="F51" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_048_Oilcan02</s:t>
         </s:is>
@@ -4857,10 +4880,10 @@
         <s:f>CEILING(A52/4,1)</s:f>
         <s:v>13</s:v>
       </s:c>
-      <s:c r="E52" s="4" t="n">
+      <s:c r="E52" s="26" t="n">
         <s:v>137999782231090</s:v>
       </s:c>
-      <s:c r="F52" s="5" t="inlineStr">
+      <s:c r="F52" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_049_Oilcan03</s:t>
         </s:is>
@@ -4887,10 +4910,10 @@
         <s:f>CEILING(A53/4,1)</s:f>
         <s:v>13</s:v>
       </s:c>
-      <s:c r="E53" s="4" t="n">
+      <s:c r="E53" s="26" t="n">
         <s:v>127007149281218</s:v>
       </s:c>
-      <s:c r="F53" s="5" t="inlineStr">
+      <s:c r="F53" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_050_Mobilephone</s:t>
         </s:is>
@@ -4917,10 +4940,10 @@
         <s:f>CEILING(A54/4,1)</s:f>
         <s:v>13</s:v>
       </s:c>
-      <s:c r="E54" s="4" t="n">
+      <s:c r="E54" s="26" t="n">
         <s:v>85273469740405</s:v>
       </s:c>
-      <s:c r="F54" s="5" t="inlineStr">
+      <s:c r="F54" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_051_Watch01</s:t>
         </s:is>
@@ -4947,10 +4970,10 @@
         <s:f>CEILING(A55/4,1)</s:f>
         <s:v>13</s:v>
       </s:c>
-      <s:c r="E55" s="4" t="n">
+      <s:c r="E55" s="26" t="n">
         <s:v>85750403977754</s:v>
       </s:c>
-      <s:c r="F55" s="5" t="inlineStr">
+      <s:c r="F55" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_052_IdentificationTag</s:t>
         </s:is>
@@ -4977,10 +5000,10 @@
         <s:f>CEILING(A56/4,1)</s:f>
         <s:v>14</s:v>
       </s:c>
-      <s:c r="E56" s="4" t="n">
+      <s:c r="E56" s="26" t="n">
         <s:v>87658125570749</s:v>
       </s:c>
-      <s:c r="F56" s="5" t="inlineStr">
+      <s:c r="F56" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_053_Compass</s:t>
         </s:is>
@@ -5007,10 +5030,10 @@
         <s:f>CEILING(A57/4,1)</s:f>
         <s:v>14</s:v>
       </s:c>
-      <s:c r="E57" s="4" t="n">
+      <s:c r="E57" s="26" t="n">
         <s:v>71386503893388</s:v>
       </s:c>
-      <s:c r="F57" s="5" t="inlineStr">
+      <s:c r="F57" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_054_CompassA</s:t>
         </s:is>
@@ -5037,10 +5060,10 @@
         <s:f>CEILING(A58/4,1)</s:f>
         <s:v>14</s:v>
       </s:c>
-      <s:c r="E58" s="4" t="n">
+      <s:c r="E58" s="26" t="n">
         <s:v>117660867991736</s:v>
       </s:c>
-      <s:c r="F58" s="5" t="inlineStr">
+      <s:c r="F58" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_055_Hat</s:t>
         </s:is>
@@ -5067,10 +5090,10 @@
         <s:f>CEILING(A59/4,1)</s:f>
         <s:v>14</s:v>
       </s:c>
-      <s:c r="E59" s="4" t="n">
+      <s:c r="E59" s="26" t="n">
         <s:v>75602786825729</s:v>
       </s:c>
-      <s:c r="F59" s="5" t="inlineStr">
+      <s:c r="F59" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_056_Cap_A_0</s:t>
         </s:is>
@@ -5097,10 +5120,10 @@
         <s:f>CEILING(A60/4,1)</s:f>
         <s:v>15</s:v>
       </s:c>
-      <s:c r="E60" s="4" t="n">
+      <s:c r="E60" s="26" t="n">
         <s:v>97494295137425</s:v>
       </s:c>
-      <s:c r="F60" s="5" t="inlineStr">
+      <s:c r="F60" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_057_Sunglass01</s:t>
         </s:is>
@@ -5127,10 +5150,10 @@
         <s:f>CEILING(A61/4,1)</s:f>
         <s:v>15</s:v>
       </s:c>
-      <s:c r="E61" s="4" t="n">
+      <s:c r="E61" s="26" t="n">
         <s:v>121387106380169</s:v>
       </s:c>
-      <s:c r="F61" s="5" t="inlineStr">
+      <s:c r="F61" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_058_Sunglass02</s:t>
         </s:is>
@@ -5157,10 +5180,10 @@
         <s:f>CEILING(A62/4,1)</s:f>
         <s:v>15</s:v>
       </s:c>
-      <s:c r="E62" s="4" t="n">
+      <s:c r="E62" s="26" t="n">
         <s:v>77703154963129</s:v>
       </s:c>
-      <s:c r="F62" s="5" t="inlineStr">
+      <s:c r="F62" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_059_Goggle</s:t>
         </s:is>
@@ -5187,10 +5210,10 @@
         <s:f>CEILING(A63/4,1)</s:f>
         <s:v>15</s:v>
       </s:c>
-      <s:c r="E63" s="4" t="n">
+      <s:c r="E63" s="26" t="n">
         <s:v>82745313217810</s:v>
       </s:c>
-      <s:c r="F63" s="5" t="inlineStr">
+      <s:c r="F63" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_060_GoggleA</s:t>
         </s:is>
@@ -5217,10 +5240,10 @@
         <s:f>CEILING(A64/4,1)</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="E64" s="4" t="n">
+      <s:c r="E64" s="26" t="n">
         <s:v>78702263483439</s:v>
       </s:c>
-      <s:c r="F64" s="5" t="inlineStr">
+      <s:c r="F64" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_061_MaskA</s:t>
         </s:is>
@@ -5247,10 +5270,10 @@
         <s:f>CEILING(A65/4,1)</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="E65" s="4" t="n">
+      <s:c r="E65" s="26" t="n">
         <s:v>103252845267522</s:v>
       </s:c>
-      <s:c r="F65" s="5" t="inlineStr">
+      <s:c r="F65" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_062_GasMask01</s:t>
         </s:is>
@@ -5277,10 +5300,10 @@
         <s:f>CEILING(A66/4,1)</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="E66" s="4" t="n">
+      <s:c r="E66" s="26" t="n">
         <s:v>93380659059014</s:v>
       </s:c>
-      <s:c r="F66" s="5" t="inlineStr">
+      <s:c r="F66" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_063_GasMask02</s:t>
         </s:is>
@@ -5307,10 +5330,10 @@
         <s:f>CEILING(A67/4,1)</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="E67" s="4" t="n">
+      <s:c r="E67" s="26" t="n">
         <s:v>124070618735034</s:v>
       </s:c>
-      <s:c r="F67" s="5" t="inlineStr">
+      <s:c r="F67" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_064_Boots01</s:t>
         </s:is>
@@ -5337,10 +5360,10 @@
         <s:f>CEILING(A68/4,1)</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="E68" s="4" t="n">
+      <s:c r="E68" s="26" t="n">
         <s:v>82229267783572</s:v>
       </s:c>
-      <s:c r="F68" s="5" t="inlineStr">
+      <s:c r="F68" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_065_Boots02</s:t>
         </s:is>
@@ -5367,10 +5390,10 @@
         <s:f>CEILING(A69/4,1)</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="E69" s="4" t="n">
+      <s:c r="E69" s="26" t="n">
         <s:v>90764663625426</s:v>
       </s:c>
-      <s:c r="F69" s="5" t="inlineStr">
+      <s:c r="F69" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_066_Boots03</s:t>
         </s:is>
@@ -5397,10 +5420,10 @@
         <s:f>CEILING(A70/4,1)</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="E70" s="4" t="n">
+      <s:c r="E70" s="26" t="n">
         <s:v>89592774326120</s:v>
       </s:c>
-      <s:c r="F70" s="5" t="inlineStr">
+      <s:c r="F70" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_067_Boots04</s:t>
         </s:is>
@@ -5427,10 +5450,10 @@
         <s:f>CEILING(A71/4,1)</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="E71" s="4" t="n">
+      <s:c r="E71" s="26" t="n">
         <s:v>96498729983354</s:v>
       </s:c>
-      <s:c r="F71" s="5" t="inlineStr">
+      <s:c r="F71" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_068_BulletproofJacket01</s:t>
         </s:is>
@@ -5457,10 +5480,10 @@
         <s:f>CEILING(A72/4,1)</s:f>
         <s:v>18</s:v>
       </s:c>
-      <s:c r="E72" s="4" t="n">
+      <s:c r="E72" s="26" t="n">
         <s:v>137402232463633</s:v>
       </s:c>
-      <s:c r="F72" s="5" t="inlineStr">
+      <s:c r="F72" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_069_BulletproofJacket02</s:t>
         </s:is>
@@ -5487,10 +5510,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>15</s:v>
       </s:c>
-      <s:c r="E73" s="4" t="n">
+      <s:c r="E73" s="26" t="n">
         <s:v>79717469784936</s:v>
       </s:c>
-      <s:c r="F73" s="5" t="inlineStr">
+      <s:c r="F73" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_070_Helmet01</s:t>
         </s:is>
@@ -5517,10 +5540,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="E74" s="4" t="n">
+      <s:c r="E74" s="26" t="n">
         <s:v>86646811474956</s:v>
       </s:c>
-      <s:c r="F74" s="5" t="inlineStr">
+      <s:c r="F74" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_071_Helmet02</s:t>
         </s:is>
@@ -5547,10 +5570,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="E75" s="4" t="n">
+      <s:c r="E75" s="26" t="n">
         <s:v>128217347353354</s:v>
       </s:c>
-      <s:c r="F75" s="5" t="inlineStr">
+      <s:c r="F75" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_072_Helmet03</s:t>
         </s:is>
@@ -5577,10 +5600,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="E76" s="4" t="n">
+      <s:c r="E76" s="26" t="n">
         <s:v>126321668579357</s:v>
       </s:c>
-      <s:c r="F76" s="5" t="inlineStr">
+      <s:c r="F76" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_073_Helmet04</s:t>
         </s:is>
@@ -5607,10 +5630,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>16</s:v>
       </s:c>
-      <s:c r="E77" s="4" t="n">
+      <s:c r="E77" s="26" t="n">
         <s:v>98351529529203</s:v>
       </s:c>
-      <s:c r="F77" s="5" t="inlineStr">
+      <s:c r="F77" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_074_Bag01</s:t>
         </s:is>
@@ -5637,10 +5660,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="E78" s="4" t="n">
+      <s:c r="E78" s="26" t="n">
         <s:v>81048668172712</s:v>
       </s:c>
-      <s:c r="F78" s="5" t="inlineStr">
+      <s:c r="F78" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_075_Bag02</s:t>
         </s:is>
@@ -5667,10 +5690,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="E79" s="4" t="n">
+      <s:c r="E79" s="26" t="n">
         <s:v>127615544859575</s:v>
       </s:c>
-      <s:c r="F79" s="5" t="inlineStr">
+      <s:c r="F79" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_076_Bag03</s:t>
         </s:is>
@@ -5697,10 +5720,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="E80" s="4" t="n">
+      <s:c r="E80" s="26" t="n">
         <s:v>70656304136373</s:v>
       </s:c>
-      <s:c r="F80" s="5" t="inlineStr">
+      <s:c r="F80" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_077_Box01</s:t>
         </s:is>
@@ -5727,10 +5750,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>17</s:v>
       </s:c>
-      <s:c r="E81" s="4" t="n">
+      <s:c r="E81" s="26" t="n">
         <s:v>134424174805013</s:v>
       </s:c>
-      <s:c r="F81" s="5" t="inlineStr">
+      <s:c r="F81" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_078_Box02</s:t>
         </s:is>
@@ -5757,10 +5780,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>18</s:v>
       </s:c>
-      <s:c r="E82" s="4" t="n">
+      <s:c r="E82" s="26" t="n">
         <s:v>127255485663084</s:v>
       </s:c>
-      <s:c r="F82" s="5" t="inlineStr">
+      <s:c r="F82" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_079_Box03</s:t>
         </s:is>
@@ -5787,10 +5810,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>18</s:v>
       </s:c>
-      <s:c r="E83" s="4" t="n">
+      <s:c r="E83" s="26" t="n">
         <s:v>134027683373658</s:v>
       </s:c>
-      <s:c r="F83" s="5" t="inlineStr">
+      <s:c r="F83" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_080_Pot01</s:t>
         </s:is>
@@ -5817,10 +5840,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>18</s:v>
       </s:c>
-      <s:c r="E84" s="4" t="n">
+      <s:c r="E84" s="26" t="n">
         <s:v>112447657334137</s:v>
       </s:c>
-      <s:c r="F84" s="5" t="inlineStr">
+      <s:c r="F84" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_081_Drum01</s:t>
         </s:is>
@@ -5847,10 +5870,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>18</s:v>
       </s:c>
-      <s:c r="E85" s="4" t="n">
+      <s:c r="E85" s="26" t="n">
         <s:v>104595008892706</s:v>
       </s:c>
-      <s:c r="F85" s="5" t="inlineStr">
+      <s:c r="F85" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_082_Drum02</s:t>
         </s:is>
@@ -5877,10 +5900,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>19</s:v>
       </s:c>
-      <s:c r="E86" s="4" t="n">
+      <s:c r="E86" s="26" t="n">
         <s:v>82759045606098</s:v>
       </s:c>
-      <s:c r="F86" s="5" t="inlineStr">
+      <s:c r="F86" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_083_Drum03</s:t>
         </s:is>
@@ -5907,10 +5930,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>19</s:v>
       </s:c>
-      <s:c r="E87" s="4" t="n">
+      <s:c r="E87" s="26" t="n">
         <s:v>105620837789519</s:v>
       </s:c>
-      <s:c r="F87" s="5" t="inlineStr">
+      <s:c r="F87" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_084_Drum04</s:t>
         </s:is>
@@ -5937,10 +5960,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>19</s:v>
       </s:c>
-      <s:c r="E88" s="4" t="n">
+      <s:c r="E88" s="26" t="n">
         <s:v>111024567754480</s:v>
       </s:c>
-      <s:c r="F88" s="5" t="inlineStr">
+      <s:c r="F88" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_085_Drum05</s:t>
         </s:is>
@@ -5967,10 +5990,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>19</s:v>
       </s:c>
-      <s:c r="E89" s="4" t="n">
+      <s:c r="E89" s="26" t="n">
         <s:v>137153989969007</s:v>
       </s:c>
-      <s:c r="F89" s="5" t="inlineStr">
+      <s:c r="F89" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_086_Propane</s:t>
         </s:is>
@@ -5997,10 +6020,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>20</s:v>
       </s:c>
-      <s:c r="E90" s="4" t="n">
+      <s:c r="E90" s="26" t="n">
         <s:v>74496996195913</s:v>
       </s:c>
-      <s:c r="F90" s="5" t="inlineStr">
+      <s:c r="F90" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_087_RopeA</s:t>
         </s:is>
@@ -6027,10 +6050,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>20</s:v>
       </s:c>
-      <s:c r="E91" s="4" t="n">
+      <s:c r="E91" s="26" t="n">
         <s:v>132785860315163</s:v>
       </s:c>
-      <s:c r="F91" s="5" t="inlineStr">
+      <s:c r="F91" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_088_Wire</s:t>
         </s:is>
@@ -6057,10 +6080,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>20</s:v>
       </s:c>
-      <s:c r="E92" s="4" t="n">
+      <s:c r="E92" s="26" t="n">
         <s:v>117198962948319</s:v>
       </s:c>
-      <s:c r="F92" s="5" t="inlineStr">
+      <s:c r="F92" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_089_Walkie_Talkie</s:t>
         </s:is>
@@ -6087,10 +6110,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>20</s:v>
       </s:c>
-      <s:c r="E93" s="4" t="n">
+      <s:c r="E93" s="26" t="n">
         <s:v>124449160476895</s:v>
       </s:c>
-      <s:c r="F93" s="5" t="inlineStr">
+      <s:c r="F93" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_090_Walkie_TalkieA</s:t>
         </s:is>
@@ -6117,10 +6140,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>21</s:v>
       </s:c>
-      <s:c r="E94" s="4" t="n">
+      <s:c r="E94" s="26" t="n">
         <s:v>125887863438527</s:v>
       </s:c>
-      <s:c r="F94" s="5" t="inlineStr">
+      <s:c r="F94" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_091_Flashlight01</s:t>
         </s:is>
@@ -6147,10 +6170,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>21</s:v>
       </s:c>
-      <s:c r="E95" s="4" t="n">
+      <s:c r="E95" s="26" t="n">
         <s:v>137692564728429</s:v>
       </s:c>
-      <s:c r="F95" s="5" t="inlineStr">
+      <s:c r="F95" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_092_HeadLantern</s:t>
         </s:is>
@@ -6177,10 +6200,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>21</s:v>
       </s:c>
-      <s:c r="E96" s="4" t="n">
+      <s:c r="E96" s="26" t="n">
         <s:v>82350951870220</s:v>
       </s:c>
-      <s:c r="F96" s="5" t="inlineStr">
+      <s:c r="F96" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_093_Lantern</s:t>
         </s:is>
@@ -6207,10 +6230,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>21</s:v>
       </s:c>
-      <s:c r="E97" s="4" t="n">
+      <s:c r="E97" s="26" t="n">
         <s:v>133019385929561</s:v>
       </s:c>
-      <s:c r="F97" s="5" t="inlineStr">
+      <s:c r="F97" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_094_Telescope01</s:t>
         </s:is>
@@ -6237,10 +6260,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>22</s:v>
       </s:c>
-      <s:c r="E98" s="4" t="n">
+      <s:c r="E98" s="26" t="n">
         <s:v>82714807302588</s:v>
       </s:c>
-      <s:c r="F98" s="5" t="inlineStr">
+      <s:c r="F98" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_095_Telescope02</s:t>
         </s:is>
@@ -6267,10 +6290,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>22</s:v>
       </s:c>
-      <s:c r="E99" s="4" t="n">
+      <s:c r="E99" s="26" t="n">
         <s:v>120409278538446</s:v>
       </s:c>
-      <s:c r="F99" s="5" t="inlineStr">
+      <s:c r="F99" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_096_Hammer01</s:t>
         </s:is>
@@ -6297,10 +6320,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>22</s:v>
       </s:c>
-      <s:c r="E100" s="4" t="n">
+      <s:c r="E100" s="26" t="n">
         <s:v>136303201068741</s:v>
       </s:c>
-      <s:c r="F100" s="5" t="inlineStr">
+      <s:c r="F100" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_097_Hammer02</s:t>
         </s:is>
@@ -6327,10 +6350,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>22</s:v>
       </s:c>
-      <s:c r="E101" s="4" t="n">
+      <s:c r="E101" s="26" t="n">
         <s:v>76724781858184</s:v>
       </s:c>
-      <s:c r="F101" s="5" t="inlineStr">
+      <s:c r="F101" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_098_Hammer03</s:t>
         </s:is>
@@ -6357,10 +6380,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>23</s:v>
       </s:c>
-      <s:c r="E102" s="4" t="n">
+      <s:c r="E102" s="26" t="n">
         <s:v>120125979830927</s:v>
       </s:c>
-      <s:c r="F102" s="5" t="inlineStr">
+      <s:c r="F102" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_099_Wrench01</s:t>
         </s:is>
@@ -6387,10 +6410,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>23</s:v>
       </s:c>
-      <s:c r="E103" s="4" t="n">
+      <s:c r="E103" s="26" t="n">
         <s:v>86921870572603</s:v>
       </s:c>
-      <s:c r="F103" s="5" t="inlineStr">
+      <s:c r="F103" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_100_Wrench02</s:t>
         </s:is>
@@ -6417,10 +6440,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>23</s:v>
       </s:c>
-      <s:c r="E104" s="4" t="n">
+      <s:c r="E104" s="26" t="n">
         <s:v>126355990231048</s:v>
       </s:c>
-      <s:c r="F104" s="5" t="inlineStr">
+      <s:c r="F104" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_101_Wrench03</s:t>
         </s:is>
@@ -6447,10 +6470,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>23</s:v>
       </s:c>
-      <s:c r="E105" s="4" t="n">
+      <s:c r="E105" s="26" t="n">
         <s:v>72326444062448</s:v>
       </s:c>
-      <s:c r="F105" s="5" t="inlineStr">
+      <s:c r="F105" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_102_Shovel01</s:t>
         </s:is>
@@ -6477,10 +6500,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>24</s:v>
       </s:c>
-      <s:c r="E106" s="4" t="n">
+      <s:c r="E106" s="26" t="n">
         <s:v>72257499044823</s:v>
       </s:c>
-      <s:c r="F106" s="5" t="inlineStr">
+      <s:c r="F106" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_103_Shovel02</s:t>
         </s:is>
@@ -6507,10 +6530,10 @@
         <s:f>INT((ROW()-ROW(ItemData!$D$14))/4)+1</s:f>
         <s:v>24</s:v>
       </s:c>
-      <s:c r="E107" s="4" t="n">
+      <s:c r="E107" s="26" t="n">
         <s:v>74695865349139</s:v>
       </s:c>
-      <s:c r="F107" s="5" t="inlineStr">
+      <s:c r="F107" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_104_Pickax</s:t>
         </s:is>
@@ -6536,10 +6559,10 @@
       <s:c r="D108" s="2" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="E108" s="4" t="n">
+      <s:c r="E108" s="26" t="n">
         <s:v>98358488442985</s:v>
       </s:c>
-      <s:c r="F108" s="5" t="inlineStr">
+      <s:c r="F108" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_105_GolfClub</s:t>
         </s:is>
@@ -6566,10 +6589,10 @@
       <s:c r="D109" s="2" t="n">
         <s:v>24</s:v>
       </s:c>
-      <s:c r="E109" s="4" t="n">
+      <s:c r="E109" s="26" t="n">
         <s:v>113636295509693</s:v>
       </s:c>
-      <s:c r="F109" s="5" t="inlineStr">
+      <s:c r="F109" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_106_Hockey</s:t>
         </s:is>
@@ -6596,10 +6619,10 @@
       <s:c r="D110" s="2" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="E110" s="4" t="n">
+      <s:c r="E110" s="26" t="n">
         <s:v>114047124407739</s:v>
       </s:c>
-      <s:c r="F110" s="5" t="inlineStr">
+      <s:c r="F110" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_107_Bat01</s:t>
         </s:is>
@@ -6626,10 +6649,10 @@
       <s:c r="D111" s="2" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="E111" s="4" t="n">
+      <s:c r="E111" s="26" t="n">
         <s:v>95771403493939</s:v>
       </s:c>
-      <s:c r="F111" s="5" t="inlineStr">
+      <s:c r="F111" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_108_Bat02</s:t>
         </s:is>
@@ -6656,10 +6679,10 @@
       <s:c r="D112" s="2" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="E112" s="4" t="n">
+      <s:c r="E112" s="26" t="n">
         <s:v>140393673870516</s:v>
       </s:c>
-      <s:c r="F112" s="5" t="inlineStr">
+      <s:c r="F112" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_109_Bat03</s:t>
         </s:is>
@@ -6686,10 +6709,10 @@
       <s:c r="D113" s="2" t="n">
         <s:v>25</s:v>
       </s:c>
-      <s:c r="E113" s="4" t="n">
+      <s:c r="E113" s="26" t="n">
         <s:v>123109322631502</s:v>
       </s:c>
-      <s:c r="F113" s="5" t="inlineStr">
+      <s:c r="F113" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_110_Bat04</s:t>
         </s:is>
@@ -6716,10 +6739,10 @@
       <s:c r="D114" s="2" t="n">
         <s:v>26</s:v>
       </s:c>
-      <s:c r="E114" s="4" t="n">
+      <s:c r="E114" s="26" t="n">
         <s:v>98614967981417</s:v>
       </s:c>
-      <s:c r="F114" s="5" t="inlineStr">
+      <s:c r="F114" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_111_ElectricSaw</s:t>
         </s:is>
@@ -6746,10 +6769,10 @@
       <s:c r="D115" s="2" t="n">
         <s:v>26</s:v>
       </s:c>
-      <s:c r="E115" s="4" t="n">
+      <s:c r="E115" s="26" t="n">
         <s:v>127369769981706</s:v>
       </s:c>
-      <s:c r="F115" s="5" t="inlineStr">
+      <s:c r="F115" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_112_Ax01</s:t>
         </s:is>
@@ -6776,10 +6799,10 @@
       <s:c r="D116" s="2" t="n">
         <s:v>26</s:v>
       </s:c>
-      <s:c r="E116" s="4" t="n">
+      <s:c r="E116" s="26" t="n">
         <s:v>134574393827781</s:v>
       </s:c>
-      <s:c r="F116" s="5" t="inlineStr">
+      <s:c r="F116" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_113_Ax02</s:t>
         </s:is>
@@ -6806,10 +6829,10 @@
       <s:c r="D117" s="2" t="n">
         <s:v>26</s:v>
       </s:c>
-      <s:c r="E117" s="4" t="n">
+      <s:c r="E117" s="26" t="n">
         <s:v>130258203281991</s:v>
       </s:c>
-      <s:c r="F117" s="5" t="inlineStr">
+      <s:c r="F117" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_114_Ax03</s:t>
         </s:is>
@@ -6836,10 +6859,10 @@
       <s:c r="D118" s="2" t="n">
         <s:v>27</s:v>
       </s:c>
-      <s:c r="E118" s="4" t="n">
+      <s:c r="E118" s="26" t="n">
         <s:v>93953823085119</s:v>
       </s:c>
-      <s:c r="F118" s="5" t="inlineStr">
+      <s:c r="F118" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_115_Knife01</s:t>
         </s:is>
@@ -6866,10 +6889,10 @@
       <s:c r="D119" s="2" t="n">
         <s:v>27</s:v>
       </s:c>
-      <s:c r="E119" s="4" t="n">
+      <s:c r="E119" s="26" t="n">
         <s:v>109802560542166</s:v>
       </s:c>
-      <s:c r="F119" s="5" t="inlineStr">
+      <s:c r="F119" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_116_Knife02</s:t>
         </s:is>
@@ -6896,10 +6919,10 @@
       <s:c r="D120" s="2" t="n">
         <s:v>27</s:v>
       </s:c>
-      <s:c r="E120" s="4" t="n">
+      <s:c r="E120" s="26" t="n">
         <s:v>130989494782889</s:v>
       </s:c>
-      <s:c r="F120" s="5" t="inlineStr">
+      <s:c r="F120" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_117_Knife03</s:t>
         </s:is>
@@ -6926,10 +6949,10 @@
       <s:c r="D121" s="2" t="n">
         <s:v>27</s:v>
       </s:c>
-      <s:c r="E121" s="4" t="n">
+      <s:c r="E121" s="26" t="n">
         <s:v>129408716253336</s:v>
       </s:c>
-      <s:c r="F121" s="5" t="inlineStr">
+      <s:c r="F121" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_118_Knife04</s:t>
         </s:is>
@@ -6956,10 +6979,10 @@
       <s:c r="D122" s="2" t="n">
         <s:v>28</s:v>
       </s:c>
-      <s:c r="E122" s="4" t="n">
+      <s:c r="E122" s="26" t="n">
         <s:v>127772866805590</s:v>
       </s:c>
-      <s:c r="F122" s="5" t="inlineStr">
+      <s:c r="F122" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_119_Knife05</s:t>
         </s:is>
@@ -6986,10 +7009,10 @@
       <s:c r="D123" s="2" t="n">
         <s:v>28</s:v>
       </s:c>
-      <s:c r="E123" s="4" t="n">
+      <s:c r="E123" s="26" t="n">
         <s:v>91938109188463</s:v>
       </s:c>
-      <s:c r="F123" s="5" t="inlineStr">
+      <s:c r="F123" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_120_Knife06</s:t>
         </s:is>
@@ -7016,10 +7039,10 @@
       <s:c r="D124" s="2" t="n">
         <s:v>28</s:v>
       </s:c>
-      <s:c r="E124" s="4" t="n">
+      <s:c r="E124" s="26" t="n">
         <s:v>85077262752129</s:v>
       </s:c>
-      <s:c r="F124" s="5" t="inlineStr">
+      <s:c r="F124" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_121_Ironmace</s:t>
         </s:is>
@@ -7038,7 +7061,7 @@
       <s:c r="B125" s="2" t="n">
         <s:v>122</s:v>
       </s:c>
-      <s:c r="C125" s="5" t="inlineStr">
+      <s:c r="C125" s="6" t="inlineStr">
         <s:is>
           <s:t>炸药罐</s:t>
         </s:is>
@@ -7046,10 +7069,10 @@
       <s:c r="D125" s="2" t="n">
         <s:v>28</s:v>
       </s:c>
-      <s:c r="E125" s="4" t="n">
+      <s:c r="E125" s="26" t="n">
         <s:v>140335958193244</s:v>
       </s:c>
-      <s:c r="F125" s="5" t="inlineStr">
+      <s:c r="F125" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_122_Dynamite01</s:t>
         </s:is>
@@ -7067,7 +7090,7 @@
       <s:c r="B126" s="2" t="n">
         <s:v>123</s:v>
       </s:c>
-      <s:c r="C126" s="5" t="inlineStr">
+      <s:c r="C126" s="6" t="inlineStr">
         <s:is>
           <s:t>捆装炸药</s:t>
         </s:is>
@@ -7075,10 +7098,10 @@
       <s:c r="D126" s="2" t="n">
         <s:v>29</s:v>
       </s:c>
-      <s:c r="E126" s="4" t="n">
+      <s:c r="E126" s="26" t="n">
         <s:v>86732012145983</s:v>
       </s:c>
-      <s:c r="F126" s="5" t="inlineStr">
+      <s:c r="F126" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_123_Dynamite02</s:t>
         </s:is>
@@ -7096,7 +7119,7 @@
       <s:c r="B127" s="2" t="n">
         <s:v>124</s:v>
       </s:c>
-      <s:c r="C127" s="5" t="inlineStr">
+      <s:c r="C127" s="6" t="inlineStr">
         <s:is>
           <s:t>遥控炸弹</s:t>
         </s:is>
@@ -7104,10 +7127,10 @@
       <s:c r="D127" s="2" t="n">
         <s:v>29</s:v>
       </s:c>
-      <s:c r="E127" s="4" t="n">
+      <s:c r="E127" s="26" t="n">
         <s:v>78044122276865</s:v>
       </s:c>
-      <s:c r="F127" s="5" t="inlineStr">
+      <s:c r="F127" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_124_Dynamite03</s:t>
         </s:is>
@@ -7125,7 +7148,7 @@
       <s:c r="B128" s="2" t="n">
         <s:v>125</s:v>
       </s:c>
-      <s:c r="C128" s="5" t="inlineStr">
+      <s:c r="C128" s="6" t="inlineStr">
         <s:is>
           <s:t>圆形手雷</s:t>
         </s:is>
@@ -7133,10 +7156,10 @@
       <s:c r="D128" s="2" t="n">
         <s:v>29</s:v>
       </s:c>
-      <s:c r="E128" s="4" t="n">
+      <s:c r="E128" s="26" t="n">
         <s:v>114974638199136</s:v>
       </s:c>
-      <s:c r="F128" s="5" t="inlineStr">
+      <s:c r="F128" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_125_Grenade01</s:t>
         </s:is>
@@ -7154,7 +7177,7 @@
       <s:c r="B129" s="2" t="n">
         <s:v>126</s:v>
       </s:c>
-      <s:c r="C129" s="5" t="inlineStr">
+      <s:c r="C129" s="6" t="inlineStr">
         <s:is>
           <s:t>高爆手雷</s:t>
         </s:is>
@@ -7162,10 +7185,10 @@
       <s:c r="D129" s="2" t="n">
         <s:v>29</s:v>
       </s:c>
-      <s:c r="E129" s="4" t="n">
+      <s:c r="E129" s="26" t="n">
         <s:v>83652207307759</s:v>
       </s:c>
-      <s:c r="F129" s="5" t="inlineStr">
+      <s:c r="F129" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_126_Grenade02</s:t>
         </s:is>
@@ -7183,7 +7206,7 @@
       <s:c r="B130" s="2" t="n">
         <s:v>127</s:v>
       </s:c>
-      <s:c r="C130" s="5" t="inlineStr">
+      <s:c r="C130" s="6" t="inlineStr">
         <s:is>
           <s:t>等离子手雷</s:t>
         </s:is>
@@ -7191,10 +7214,10 @@
       <s:c r="D130" s="2" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="E130" s="4" t="n">
+      <s:c r="E130" s="26" t="n">
         <s:v>131787091355052</s:v>
       </s:c>
-      <s:c r="F130" s="5" t="inlineStr">
+      <s:c r="F130" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_127_Grenade03</s:t>
         </s:is>
@@ -7212,7 +7235,7 @@
       <s:c r="B131" s="2" t="n">
         <s:v>128</s:v>
       </s:c>
-      <s:c r="C131" s="5" t="inlineStr">
+      <s:c r="C131" s="6" t="inlineStr">
         <s:is>
           <s:t>感应地雷</s:t>
         </s:is>
@@ -7220,10 +7243,10 @@
       <s:c r="D131" s="2" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="E131" s="4" t="n">
+      <s:c r="E131" s="26" t="n">
         <s:v>99348381699835</s:v>
       </s:c>
-      <s:c r="F131" s="5" t="inlineStr">
+      <s:c r="F131" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_128_Mine</s:t>
         </s:is>
@@ -7241,7 +7264,7 @@
       <s:c r="B132" s="2" t="n">
         <s:v>129</s:v>
       </s:c>
-      <s:c r="C132" s="5" t="inlineStr">
+      <s:c r="C132" s="6" t="inlineStr">
         <s:is>
           <s:t>捕兽夹</s:t>
         </s:is>
@@ -7249,10 +7272,10 @@
       <s:c r="D132" s="2" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="E132" s="4" t="n">
+      <s:c r="E132" s="26" t="n">
         <s:v>75412160560516</s:v>
       </s:c>
-      <s:c r="F132" s="5" t="inlineStr">
+      <s:c r="F132" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_129_Trap</s:t>
         </s:is>
@@ -7270,7 +7293,7 @@
       <s:c r="B133" s="2" t="n">
         <s:v>130</s:v>
       </s:c>
-      <s:c r="C133" s="5" t="inlineStr">
+      <s:c r="C133" s="6" t="inlineStr">
         <s:is>
           <s:t>手枪子弹</s:t>
         </s:is>
@@ -7278,10 +7301,10 @@
       <s:c r="D133" s="2" t="n">
         <s:v>30</s:v>
       </s:c>
-      <s:c r="E133" s="4" t="n">
+      <s:c r="E133" s="26" t="n">
         <s:v>105475505052937</s:v>
       </s:c>
-      <s:c r="F133" s="5" t="inlineStr">
+      <s:c r="F133" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_130_Bullet01</s:t>
         </s:is>
@@ -7299,7 +7322,7 @@
       <s:c r="B134" s="2" t="n">
         <s:v>131</s:v>
       </s:c>
-      <s:c r="C134" s="5" t="inlineStr">
+      <s:c r="C134" s="6" t="inlineStr">
         <s:is>
           <s:t>手枪弹药</s:t>
         </s:is>
@@ -7307,10 +7330,10 @@
       <s:c r="D134" s="2" t="n">
         <s:v>31</s:v>
       </s:c>
-      <s:c r="E134" s="4" t="n">
+      <s:c r="E134" s="26" t="n">
         <s:v>125484119033793</s:v>
       </s:c>
-      <s:c r="F134" s="5" t="inlineStr">
+      <s:c r="F134" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_131_Bullet02</s:t>
         </s:is>
@@ -7328,7 +7351,7 @@
       <s:c r="B135" s="2" t="n">
         <s:v>132</s:v>
       </s:c>
-      <s:c r="C135" s="5" t="inlineStr">
+      <s:c r="C135" s="6" t="inlineStr">
         <s:is>
           <s:t>整箱弹药</s:t>
         </s:is>
@@ -7336,10 +7359,10 @@
       <s:c r="D135" s="2" t="n">
         <s:v>31</s:v>
       </s:c>
-      <s:c r="E135" s="4" t="n">
+      <s:c r="E135" s="26" t="n">
         <s:v>140608831780254</s:v>
       </s:c>
-      <s:c r="F135" s="5" t="inlineStr">
+      <s:c r="F135" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_132_Bullet03</s:t>
         </s:is>
@@ -7357,7 +7380,7 @@
       <s:c r="B136" s="2" t="n">
         <s:v>133</s:v>
       </s:c>
-      <s:c r="C136" s="5" t="inlineStr">
+      <s:c r="C136" s="6" t="inlineStr">
         <s:is>
           <s:t>盒装弹药</s:t>
         </s:is>
@@ -7365,10 +7388,10 @@
       <s:c r="D136" s="2" t="n">
         <s:v>31</s:v>
       </s:c>
-      <s:c r="E136" s="4" t="n">
+      <s:c r="E136" s="26" t="n">
         <s:v>124177358025481</s:v>
       </s:c>
-      <s:c r="F136" s="5" t="inlineStr">
+      <s:c r="F136" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_133_Bullet04</s:t>
         </s:is>
@@ -7386,7 +7409,7 @@
       <s:c r="B137" s="2" t="n">
         <s:v>134</s:v>
       </s:c>
-      <s:c r="C137" s="5" t="inlineStr">
+      <s:c r="C137" s="6" t="inlineStr">
         <s:is>
           <s:t>直式弹匣</s:t>
         </s:is>
@@ -7394,10 +7417,10 @@
       <s:c r="D137" s="2" t="n">
         <s:v>31</s:v>
       </s:c>
-      <s:c r="E137" s="4" t="n">
+      <s:c r="E137" s="26" t="n">
         <s:v>129385390119523</s:v>
       </s:c>
-      <s:c r="F137" s="5" t="inlineStr">
+      <s:c r="F137" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_134_Bullet05</s:t>
         </s:is>
@@ -7415,7 +7438,7 @@
       <s:c r="B138" s="2" t="n">
         <s:v>135</s:v>
       </s:c>
-      <s:c r="C138" s="5" t="inlineStr">
+      <s:c r="C138" s="6" t="inlineStr">
         <s:is>
           <s:t>弯式弹匣</s:t>
         </s:is>
@@ -7423,10 +7446,10 @@
       <s:c r="D138" s="2" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="E138" s="4" t="n">
+      <s:c r="E138" s="26" t="n">
         <s:v>84940520003035</s:v>
       </s:c>
-      <s:c r="F138" s="5" t="inlineStr">
+      <s:c r="F138" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_135_Bullet06</s:t>
         </s:is>
@@ -7444,7 +7467,7 @@
       <s:c r="B139" s="2" t="n">
         <s:v>136</s:v>
       </s:c>
-      <s:c r="C139" s="5" t="inlineStr">
+      <s:c r="C139" s="6" t="inlineStr">
         <s:is>
           <s:t>霰弹盒</s:t>
         </s:is>
@@ -7452,10 +7475,10 @@
       <s:c r="D139" s="2" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="E139" s="4" t="n">
+      <s:c r="E139" s="26" t="n">
         <s:v>90031364711610</s:v>
       </s:c>
-      <s:c r="F139" s="5" t="inlineStr">
+      <s:c r="F139" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_136_Bullet07</s:t>
         </s:is>
@@ -7473,7 +7496,7 @@
       <s:c r="B140" s="2" t="n">
         <s:v>137</s:v>
       </s:c>
-      <s:c r="C140" s="5" t="inlineStr">
+      <s:c r="C140" s="6" t="inlineStr">
         <s:is>
           <s:t>军用弹药箱</s:t>
         </s:is>
@@ -7481,10 +7504,10 @@
       <s:c r="D140" s="2" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="E140" s="4" t="n">
+      <s:c r="E140" s="26" t="n">
         <s:v>84418341821320</s:v>
       </s:c>
-      <s:c r="F140" s="5" t="inlineStr">
+      <s:c r="F140" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_137_Cartridge</s:t>
         </s:is>
@@ -7502,7 +7525,7 @@
       <s:c r="B141" s="2" t="n">
         <s:v>138</s:v>
       </s:c>
-      <s:c r="C141" s="5" t="inlineStr">
+      <s:c r="C141" s="6" t="inlineStr">
         <s:is>
           <s:t>左轮手枪</s:t>
         </s:is>
@@ -7510,10 +7533,10 @@
       <s:c r="D141" s="2" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="E141" s="4" t="n">
+      <s:c r="E141" s="26" t="n">
         <s:v>130255705800444</s:v>
       </s:c>
-      <s:c r="F141" s="5" t="inlineStr">
+      <s:c r="F141" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_138_Gun01</s:t>
         </s:is>
@@ -7531,7 +7554,7 @@
       <s:c r="B142" s="2" t="n">
         <s:v>139</s:v>
       </s:c>
-      <s:c r="C142" s="5" t="inlineStr">
+      <s:c r="C142" s="6" t="inlineStr">
         <s:is>
           <s:t>单发手枪</s:t>
         </s:is>
@@ -7539,10 +7562,10 @@
       <s:c r="D142" s="2" t="n">
         <s:v>33</s:v>
       </s:c>
-      <s:c r="E142" s="4" t="n">
+      <s:c r="E142" s="26" t="n">
         <s:v>123568265278671</s:v>
       </s:c>
-      <s:c r="F142" s="5" t="inlineStr">
+      <s:c r="F142" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_139_Gun02</s:t>
         </s:is>
@@ -7560,7 +7583,7 @@
       <s:c r="B143" s="2" t="n">
         <s:v>140</s:v>
       </s:c>
-      <s:c r="C143" s="5" t="inlineStr">
+      <s:c r="C143" s="6" t="inlineStr">
         <s:is>
           <s:t>短管突击步枪</s:t>
         </s:is>
@@ -7568,10 +7591,10 @@
       <s:c r="D143" s="2" t="n">
         <s:v>33</s:v>
       </s:c>
-      <s:c r="E143" s="4" t="n">
+      <s:c r="E143" s="26" t="n">
         <s:v>75689117044416</s:v>
       </s:c>
-      <s:c r="F143" s="5" t="inlineStr">
+      <s:c r="F143" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_140_Rifle01</s:t>
         </s:is>
@@ -7589,7 +7612,7 @@
       <s:c r="B144" s="2" t="n">
         <s:v>141</s:v>
       </s:c>
-      <s:c r="C144" s="5" t="inlineStr">
+      <s:c r="C144" s="6" t="inlineStr">
         <s:is>
           <s:t>战术突击步枪</s:t>
         </s:is>
@@ -7597,10 +7620,10 @@
       <s:c r="D144" s="2" t="n">
         <s:v>33</s:v>
       </s:c>
-      <s:c r="E144" s="4" t="n">
+      <s:c r="E144" s="26" t="n">
         <s:v>92309488435591</s:v>
       </s:c>
-      <s:c r="F144" s="5" t="inlineStr">
+      <s:c r="F144" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_141_Rifle02</s:t>
         </s:is>
@@ -7618,7 +7641,7 @@
       <s:c r="B145" s="2" t="n">
         <s:v>142</s:v>
       </s:c>
-      <s:c r="C145" s="5" t="inlineStr">
+      <s:c r="C145" s="6" t="inlineStr">
         <s:is>
           <s:t>木托突击步枪</s:t>
         </s:is>
@@ -7626,10 +7649,10 @@
       <s:c r="D145" s="2" t="n">
         <s:v>33</s:v>
       </s:c>
-      <s:c r="E145" s="4" t="n">
+      <s:c r="E145" s="26" t="n">
         <s:v>106319308889290</s:v>
       </s:c>
-      <s:c r="F145" s="5" t="inlineStr">
+      <s:c r="F145" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_142_Rifle03</s:t>
         </s:is>
@@ -7647,7 +7670,7 @@
       <s:c r="B146" s="2" t="n">
         <s:v>143</s:v>
       </s:c>
-      <s:c r="C146" s="5" t="inlineStr">
+      <s:c r="C146" s="6" t="inlineStr">
         <s:is>
           <s:t>战斗霰弹枪</s:t>
         </s:is>
@@ -7655,10 +7678,10 @@
       <s:c r="D146" s="2" t="n">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="E146" s="4" t="n">
+      <s:c r="E146" s="26" t="n">
         <s:v>123120949699520</s:v>
       </s:c>
-      <s:c r="F146" s="5" t="inlineStr">
+      <s:c r="F146" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_143_Rifle04</s:t>
         </s:is>
@@ -7676,7 +7699,7 @@
       <s:c r="B147" s="2" t="n">
         <s:v>144</s:v>
       </s:c>
-      <s:c r="C147" s="5" t="inlineStr">
+      <s:c r="C147" s="6" t="inlineStr">
         <s:is>
           <s:t>狙击步枪</s:t>
         </s:is>
@@ -7684,10 +7707,10 @@
       <s:c r="D147" s="2" t="n">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="E147" s="4" t="n">
+      <s:c r="E147" s="26" t="n">
         <s:v>111674856010497</s:v>
       </s:c>
-      <s:c r="F147" s="5" t="inlineStr">
+      <s:c r="F147" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_144_Rifle05</s:t>
         </s:is>
@@ -7705,7 +7728,7 @@
       <s:c r="B148" s="2" t="n">
         <s:v>145</s:v>
       </s:c>
-      <s:c r="C148" s="5" t="inlineStr">
+      <s:c r="C148" s="6" t="inlineStr">
         <s:is>
           <s:t>冲锋枪</s:t>
         </s:is>
@@ -7713,10 +7736,10 @@
       <s:c r="D148" s="2" t="n">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="E148" s="4" t="n">
+      <s:c r="E148" s="26" t="n">
         <s:v>118080816505555</s:v>
       </s:c>
-      <s:c r="F148" s="5" t="inlineStr">
+      <s:c r="F148" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_145_MachineGun01</s:t>
         </s:is>
@@ -7734,7 +7757,7 @@
       <s:c r="B149" s="2" t="n">
         <s:v>146</s:v>
       </s:c>
-      <s:c r="C149" s="5" t="inlineStr">
+      <s:c r="C149" s="6" t="inlineStr">
         <s:is>
           <s:t>消音冲锋枪</s:t>
         </s:is>
@@ -7742,10 +7765,10 @@
       <s:c r="D149" s="2" t="n">
         <s:v>34</s:v>
       </s:c>
-      <s:c r="E149" s="4" t="n">
+      <s:c r="E149" s="26" t="n">
         <s:v>105021574817966</s:v>
       </s:c>
-      <s:c r="F149" s="5" t="inlineStr">
+      <s:c r="F149" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_146_MachineGun02</s:t>
         </s:is>
@@ -7763,7 +7786,7 @@
       <s:c r="B150" s="2" t="n">
         <s:v>147</s:v>
       </s:c>
-      <s:c r="C150" s="5" t="inlineStr">
+      <s:c r="C150" s="6" t="inlineStr">
         <s:is>
           <s:t>微型冲锋枪</s:t>
         </s:is>
@@ -7771,10 +7794,10 @@
       <s:c r="D150" s="2" t="n">
         <s:v>35</s:v>
       </s:c>
-      <s:c r="E150" s="4" t="n">
+      <s:c r="E150" s="26" t="n">
         <s:v>72690180103558</s:v>
       </s:c>
-      <s:c r="F150" s="5" t="inlineStr">
+      <s:c r="F150" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_147_MachineGun03</s:t>
         </s:is>
@@ -7792,7 +7815,7 @@
       <s:c r="B151" s="2" t="n">
         <s:v>148</s:v>
       </s:c>
-      <s:c r="C151" s="5" t="inlineStr">
+      <s:c r="C151" s="6" t="inlineStr">
         <s:is>
           <s:t>木托冲锋枪</s:t>
         </s:is>
@@ -7800,10 +7823,10 @@
       <s:c r="D151" s="2" t="n">
         <s:v>35</s:v>
       </s:c>
-      <s:c r="E151" s="4" t="n">
+      <s:c r="E151" s="26" t="n">
         <s:v>94914272618995</s:v>
       </s:c>
-      <s:c r="F151" s="5" t="inlineStr">
+      <s:c r="F151" s="6" t="inlineStr">
         <s:is>
           <s:t>game.ReplicatedStorage.Assets.ItemModel.Y1_148_MachineGun04</s:t>
         </s:is>
@@ -7833,174 +7856,174 @@
   </s:cols>
   <s:sheetData>
     <s:row r="1" ht="15.6" customHeight="1" s="1">
-      <s:c r="A1" s="8" t="inlineStr">
+      <s:c r="A1" s="9" t="inlineStr">
         <s:is>
           <s:t>索引</s:t>
         </s:is>
       </s:c>
-      <s:c r="B1" s="8" t="inlineStr">
+      <s:c r="B1" s="9" t="inlineStr">
         <s:is>
           <s:t>倍率</s:t>
         </s:is>
       </s:c>
-      <s:c r="C1" s="8" t="inlineStr">
+      <s:c r="C1" s="9" t="inlineStr">
         <s:is>
           <s:t>购买ID</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="2" ht="15.6" customHeight="1" s="1">
-      <s:c r="A2" s="8" t="inlineStr">
+      <s:c r="A2" s="9" t="inlineStr">
         <s:is>
           <s:t>Index</s:t>
         </s:is>
       </s:c>
-      <s:c r="B2" s="8" t="inlineStr">
+      <s:c r="B2" s="9" t="inlineStr">
         <s:is>
           <s:t>Rate</s:t>
         </s:is>
       </s:c>
-      <s:c r="C2" s="8" t="inlineStr">
+      <s:c r="C2" s="9" t="inlineStr">
         <s:is>
           <s:t>GemGoodsId</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="3" ht="15.6" customHeight="1" s="1">
-      <s:c r="A3" s="8" t="inlineStr">
+      <s:c r="A3" s="9" t="inlineStr">
         <s:is>
           <s:t>number</s:t>
         </s:is>
       </s:c>
-      <s:c r="B3" s="8" t="inlineStr">
+      <s:c r="B3" s="9" t="inlineStr">
         <s:is>
           <s:t>number</s:t>
         </s:is>
       </s:c>
-      <s:c r="C3" s="8" t="inlineStr">
+      <s:c r="C3" s="9" t="inlineStr">
         <s:is>
           <s:t>number</s:t>
         </s:is>
       </s:c>
     </s:row>
     <s:row r="4" ht="15.6" customHeight="1" s="1">
-      <s:c r="A4" s="8" t="n">
+      <s:c r="A4" s="9" t="n">
         <s:v>1</s:v>
       </s:c>
-      <s:c r="B4" s="8" t="n">
+      <s:c r="B4" s="9" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="C4" s="8" t="n">
+      <s:c r="C4" s="9" t="n">
         <s:v>150</s:v>
       </s:c>
     </s:row>
     <s:row r="5" ht="15.6" customHeight="1" s="1">
-      <s:c r="A5" s="8" t="n">
+      <s:c r="A5" s="9" t="n">
         <s:v>2</s:v>
       </s:c>
-      <s:c r="B5" s="8" t="n">
+      <s:c r="B5" s="9" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="C5" s="8" t="n">
+      <s:c r="C5" s="9" t="n">
         <s:v>151</s:v>
       </s:c>
     </s:row>
     <s:row r="6" ht="15.6" customHeight="1" s="1">
-      <s:c r="A6" s="8" t="n">
+      <s:c r="A6" s="9" t="n">
         <s:v>3</s:v>
       </s:c>
-      <s:c r="B6" s="8" t="n">
+      <s:c r="B6" s="9" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="C6" s="8" t="n">
+      <s:c r="C6" s="9" t="n">
         <s:v>152</s:v>
       </s:c>
     </s:row>
     <s:row r="7" ht="15.6" customHeight="1" s="1">
-      <s:c r="A7" s="8" t="n">
+      <s:c r="A7" s="9" t="n">
         <s:v>4</s:v>
       </s:c>
-      <s:c r="B7" s="8" t="n">
+      <s:c r="B7" s="9" t="n">
         <s:v>16</s:v>
       </s:c>
-      <s:c r="C7" s="8" t="n">
+      <s:c r="C7" s="9" t="n">
         <s:v>153</s:v>
       </s:c>
     </s:row>
     <s:row r="8" ht="15.6" customHeight="1" s="1">
-      <s:c r="A8" s="8" t="n">
+      <s:c r="A8" s="9" t="n">
         <s:v>5</s:v>
       </s:c>
-      <s:c r="B8" s="8" t="n">
+      <s:c r="B8" s="9" t="n">
         <s:v>32</s:v>
       </s:c>
-      <s:c r="C8" s="8" t="n">
+      <s:c r="C8" s="9" t="n">
         <s:v>154</s:v>
       </s:c>
     </s:row>
     <s:row r="9" ht="15.6" customHeight="1" s="1">
-      <s:c r="A9" s="8" t="n">
+      <s:c r="A9" s="9" t="n">
         <s:v>6</s:v>
       </s:c>
-      <s:c r="B9" s="8" t="n">
+      <s:c r="B9" s="9" t="n">
         <s:v>64</s:v>
       </s:c>
-      <s:c r="C9" s="8" t="n">
+      <s:c r="C9" s="9" t="n">
         <s:v>155</s:v>
       </s:c>
     </s:row>
     <s:row r="10" ht="15" customHeight="1" s="1">
-      <s:c r="A10" s="8" t="n">
+      <s:c r="A10" s="9" t="n">
         <s:v>7</s:v>
       </s:c>
-      <s:c r="B10" s="8" t="n">
+      <s:c r="B10" s="9" t="n">
         <s:v>128</s:v>
       </s:c>
-      <s:c r="C10" s="8" t="n">
+      <s:c r="C10" s="9" t="n">
         <s:v>156</s:v>
       </s:c>
     </s:row>
     <s:row r="11" ht="15.6" customHeight="1" s="1">
-      <s:c r="A11" s="8" t="n">
+      <s:c r="A11" s="9" t="n">
         <s:v>8</s:v>
       </s:c>
-      <s:c r="B11" s="8" t="n">
+      <s:c r="B11" s="9" t="n">
         <s:v>256</s:v>
       </s:c>
-      <s:c r="C11" s="8" t="n">
+      <s:c r="C11" s="9" t="n">
         <s:v>157</s:v>
       </s:c>
     </s:row>
     <s:row r="12" ht="15.6" customHeight="1" s="1">
-      <s:c r="A12" s="8" t="n">
+      <s:c r="A12" s="9" t="n">
         <s:v>9</s:v>
       </s:c>
-      <s:c r="B12" s="8" t="n">
+      <s:c r="B12" s="9" t="n">
         <s:v>512</s:v>
       </s:c>
-      <s:c r="C12" s="8" t="n">
+      <s:c r="C12" s="9" t="n">
         <s:v>158</s:v>
       </s:c>
     </s:row>
     <s:row r="13" ht="15.6" customHeight="1" s="1">
-      <s:c r="A13" s="8" t="n">
+      <s:c r="A13" s="9" t="n">
         <s:v>10</s:v>
       </s:c>
-      <s:c r="B13" s="8" t="n">
+      <s:c r="B13" s="9" t="n">
         <s:v>1024</s:v>
       </s:c>
-      <s:c r="C13" s="8" t="n">
+      <s:c r="C13" s="9" t="n">
         <s:v>159</s:v>
       </s:c>
     </s:row>
     <s:row r="14" ht="15.6" customHeight="1" s="1">
-      <s:c r="A14" s="8" t="n">
+      <s:c r="A14" s="9" t="n">
         <s:v>11</s:v>
       </s:c>
-      <s:c r="B14" s="8" t="n">
+      <s:c r="B14" s="9" t="n">
         <s:v>2048</s:v>
       </s:c>
-      <s:c r="C14" s="8" t="n">
+      <s:c r="C14" s="9" t="n">
         <s:v>160</s:v>
       </s:c>
     </s:row>
@@ -8167,7 +8190,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>WornWoodenPickaxe</t>
+          <t>Worn Wooden Pickaxe</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -8177,15 +8200,15 @@
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="27" t="n">
         <v>99853650045862</v>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["01WornWoodenPickaxe"]</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n"/>
+      <c r="I4" s="7" t="n"/>
     </row>
     <row r="5" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A5" s="2" t="n">
@@ -8196,7 +8219,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HeavyWoodenHammer</t>
+          <t>Heavy Wooden Hammer</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -8206,15 +8229,15 @@
         <v>39</v>
       </c>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="27" t="n">
         <v>116225665846279</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["02HeavyWoodenHammer"]</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n"/>
+      <c r="I5" s="7" t="n"/>
     </row>
     <row r="6" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A6" s="2" t="n">
@@ -8225,7 +8248,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>CrudeSilverPickaxe</t>
+          <t>Crude Silver Pickaxe</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -8235,15 +8258,15 @@
         <v>450</v>
       </c>
       <c r="F6" s="2" t="n"/>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="27" t="n">
         <v>136956773152573</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["03CrudeSilverPickaxe"]</t>
         </is>
       </c>
-      <c r="I6" s="6" t="n"/>
+      <c r="I6" s="7" t="n"/>
     </row>
     <row r="7" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A7" s="2" t="n">
@@ -8254,7 +8277,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CrudeSilverHammer</t>
+          <t>Crude Silver Hammer</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -8264,15 +8287,15 @@
         <v>3282</v>
       </c>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="27" t="n">
         <v>97553870039023</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["04CrudeSilverHammer"]</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="7" t="n"/>
     </row>
     <row r="8" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A8" s="2" t="n">
@@ -8283,29 +8306,29 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ReinforcedIronPickaxe</t>
+          <t>Reinforced Iron Pickaxe</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>3.50e+4</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>1.90e+4</t>
         </is>
       </c>
       <c r="F8" s="2" t="n"/>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="27" t="n">
         <v>118090700645855</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["05ReinforcedIronPickaxe"]</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n"/>
+      <c r="I8" s="7" t="n"/>
     </row>
     <row r="9" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A9" s="2" t="n">
@@ -8316,29 +8339,29 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ReinforcedIronHammer</t>
+          <t>Reinforced Iron Hammer</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>2.53e+5</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>9.55e+4</t>
         </is>
       </c>
       <c r="F9" s="2" t="n"/>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="27" t="n">
         <v>138508042210191</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["06ReinforcedIronHammer"]</t>
         </is>
       </c>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="7" t="n"/>
     </row>
     <row r="10" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A10" s="2" t="n">
@@ -8349,29 +8372,29 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>FineSteelMiningPickaxe</t>
+          <t>Fine Steel Mining Pickaxe</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>1.89e+6</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>4.42e+5</t>
         </is>
       </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="27" t="n">
         <v>78371166922896</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["07FineSteelMiningPickaxe"]</t>
         </is>
       </c>
-      <c r="I10" s="6" t="n"/>
+      <c r="I10" s="7" t="n"/>
     </row>
     <row r="11" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A11" s="2" t="n">
@@ -8382,29 +8405,29 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>FineSteelMaul</t>
+          <t>Fine Steel Maul</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>1.22e+7</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>1.93e+6</t>
         </is>
       </c>
       <c r="F11" s="2" t="n"/>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="27" t="n">
         <v>132966760008713</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["08FineSteelMaul"]</t>
         </is>
       </c>
-      <c r="I11" s="6" t="n"/>
+      <c r="I11" s="7" t="n"/>
     </row>
     <row r="12" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A12" s="2" t="n">
@@ -8415,29 +8438,29 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>BrassMechanicalPickaxe</t>
+          <t>Brass Mechanical Pickaxe</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>7.62e+7</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>8.10e+6</t>
         </is>
       </c>
       <c r="F12" s="2" t="n"/>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="27" t="n">
         <v>133927008310944</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["09BrassMechanicalPickaxe"]</t>
         </is>
       </c>
-      <c r="I12" s="6" t="n"/>
+      <c r="I12" s="7" t="n"/>
     </row>
     <row r="13" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A13" s="2" t="n">
@@ -8448,29 +8471,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>BrassMechanicalHammer</t>
+          <t>Brass Mechanical Hammer</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>4.65e+8</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>3.31e+7</t>
         </is>
       </c>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="27" t="n">
         <v>98415179467911</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["10BrassMechanicalHammer"]</t>
         </is>
       </c>
-      <c r="I13" s="6" t="n"/>
+      <c r="I13" s="7" t="n"/>
     </row>
     <row r="14" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A14" s="2" t="n">
@@ -8481,29 +8504,29 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ObsidianBattlePickaxe</t>
+          <t>Obsidian Battle Pickaxe</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>2.78e+9</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>1.33e+8</t>
         </is>
       </c>
       <c r="F14" s="2" t="n"/>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="27" t="n">
         <v>79276409476682</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["11ObsidianBattlePickaxe"]</t>
         </is>
       </c>
-      <c r="I14" s="6" t="n"/>
+      <c r="I14" s="7" t="n"/>
     </row>
     <row r="15" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A15" s="2" t="n">
@@ -8514,29 +8537,29 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ObsidianGreatHammer</t>
+          <t>Obsidian Great Hammer</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>1.64e+10</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>5.25e+8</t>
         </is>
       </c>
       <c r="F15" s="2" t="n"/>
-      <c r="G15" s="3" t="n">
+      <c r="G15" s="27" t="n">
         <v>86184044773576</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["12ObsidianGreatHammer"]</t>
         </is>
       </c>
-      <c r="I15" s="6" t="n"/>
+      <c r="I15" s="7" t="n"/>
     </row>
     <row r="16" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A16" s="2" t="n">
@@ -8547,29 +8570,29 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EmeraldGuardianPickaxe</t>
+          <t>Emerald Guardian Pickaxe</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>9.55e+10</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>2.05e+9</t>
         </is>
       </c>
       <c r="F16" s="2" t="n"/>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="27" t="n">
         <v>85964386896273</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["13EmeraldGuardianPickaxe"]</t>
         </is>
       </c>
-      <c r="I16" s="6" t="n"/>
+      <c r="I16" s="7" t="n"/>
     </row>
     <row r="17" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A17" s="2" t="n">
@@ -8580,29 +8603,29 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EmeraldGuardianHammer</t>
+          <t>Emerald Guardian Hammer</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>5.49e+11</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>7.99e+9</t>
         </is>
       </c>
       <c r="F17" s="2" t="n"/>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="27" t="n">
         <v>121813166897471</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["14EmeraldGuardianHammer"]</t>
         </is>
       </c>
-      <c r="I17" s="6" t="n"/>
+      <c r="I17" s="7" t="n"/>
     </row>
     <row r="18" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A18" s="2" t="n">
@@ -8613,29 +8636,29 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>RedCrystalForgePickaxe</t>
+          <t>Red Crystal Forge Pickaxe</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>3.13e+12</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>3.10e+10</t>
         </is>
       </c>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="27" t="n">
         <v>107669574278873</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["15RedCrystalForgePickaxe"]</t>
         </is>
       </c>
-      <c r="I18" s="6" t="n"/>
+      <c r="I18" s="7" t="n"/>
     </row>
     <row r="19" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A19" s="2" t="n">
@@ -8646,29 +8669,29 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>RedCrystalForgeHammer</t>
+          <t>Red Crystal Forge Hammer</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>1.77e+13</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>1.20e+11</t>
         </is>
       </c>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="27" t="n">
         <v>98723580431394</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["16RedCrystalForgeHammer"]</t>
         </is>
       </c>
-      <c r="I19" s="6" t="n"/>
+      <c r="I19" s="7" t="n"/>
     </row>
     <row r="20" ht="15.6" customFormat="1" customHeight="1" s="3">
       <c r="A20" s="2" t="n">
@@ -8679,29 +8702,29 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>IceBlueStarCrystalPickaxe</t>
+          <t>Ice-Blue Star Crystal Pickaxe</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>9.93e+13</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>4.62e+11</t>
         </is>
       </c>
       <c r="F20" s="2" t="n"/>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="27" t="n">
         <v>126241505230536</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["17IceBlueStarCrystalPickaxe"]</t>
         </is>
       </c>
-      <c r="I20" s="6" t="n"/>
+      <c r="I20" s="7" t="n"/>
     </row>
     <row r="21" ht="15.6" customHeight="1" s="1">
       <c r="A21" s="2" t="n">
@@ -8712,29 +8735,29 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>IceBlueStarCrystalHammer</t>
+          <t>Ice-Blue Star Crystal Hammer</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>5.54e+14</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>1.78e+12</t>
         </is>
       </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="27" t="n">
         <v>78092021290844</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["18IceBlueStarCrystalHammer"]</t>
         </is>
       </c>
-      <c r="I21" s="6" t="n"/>
+      <c r="I21" s="7" t="n"/>
     </row>
     <row r="22" ht="15.6" customHeight="1" s="1">
       <c r="A22" s="2" t="n">
@@ -8745,29 +8768,29 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>GildedCrownPickaxe</t>
+          <t>Gilded Crown Pickaxe</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>3.07e+15</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>6.90e+12</t>
         </is>
       </c>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="3" t="n">
+      <c r="G22" s="27" t="n">
         <v>138731887343821</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["19GildedCrownPickaxe"]</t>
         </is>
       </c>
-      <c r="I22" s="6" t="n"/>
+      <c r="I22" s="7" t="n"/>
     </row>
     <row r="23" ht="15.6" customHeight="1" s="1">
       <c r="A23" s="2" t="n">
@@ -8778,29 +8801,29 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>GildedCrownGreatHammer</t>
+          <t>Gilded Crown Great Hammer</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>1.69e+16</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>2.67e+13</t>
         </is>
       </c>
       <c r="F23" s="2" t="n"/>
-      <c r="G23" s="3" t="n">
+      <c r="G23" s="27" t="n">
         <v>113127149166000</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.BlockMeshs.Tools["20GildedCrownGreatHammer"]</t>
         </is>
       </c>
-      <c r="I23" s="6" t="n"/>
+      <c r="I23" s="7" t="n"/>
     </row>
     <row r="24" ht="15.6" customHeight="1" s="1">
       <c r="A24" s="2" t="n">
@@ -8811,7 +8834,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>DeepSeaAnchorHammer</t>
+          <t>Deep Sea Anchor Hammer</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -8820,10 +8843,8 @@
       <c r="E24" s="3" t="n">
         <v>80100000000000</v>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>96227746339558</t>
-        </is>
+      <c r="G24" s="27" t="n">
+        <v>96227746339558</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -8840,7 +8861,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>DeepSeaHookPickaxe</t>
+          <t>Deep Sea Hook Pickaxe</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -8849,10 +8870,8 @@
       <c r="E25" s="3" t="n">
         <v>240000000000000</v>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>134869410236813</t>
-        </is>
+      <c r="G25" s="27" t="n">
+        <v>134869410236813</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -8869,7 +8888,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>DesertColossusBoneHammer</t>
+          <t>Desert Colossus Bone Hammer</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -8878,10 +8897,8 @@
       <c r="E26" s="3" t="n">
         <v>720000000000000</v>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>121268665996978</t>
-        </is>
+      <c r="G26" s="27" t="n">
+        <v>121268665996978</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
@@ -8898,7 +8915,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>SandKingFangPickaxe</t>
+          <t>Sand King Fang Pickaxe</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -8907,10 +8924,8 @@
       <c r="E27" s="3" t="n">
         <v>2160000000000000</v>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>89972874141623</t>
-        </is>
+      <c r="G27" s="27" t="n">
+        <v>89972874141623</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
@@ -8927,7 +8942,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>AmethystStarRingHammer</t>
+          <t>Amethyst Star Ring Hammer</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -8936,10 +8951,8 @@
       <c r="E28" s="3" t="n">
         <v>6480000000000000</v>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>88597169256101</t>
-        </is>
+      <c r="G28" s="27" t="n">
+        <v>88597169256101</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
@@ -8956,7 +8969,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>AmethystStarRingPickaxe</t>
+          <t>Amethyst Star Ring Pickaxe</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
@@ -8965,10 +8978,8 @@
       <c r="E29" s="3" t="n">
         <v>1.94e+16</v>
       </c>
-      <c r="G29" s="22" t="inlineStr">
-        <is>
-          <t>85002040484327</t>
-        </is>
+      <c r="G29" s="27" t="n">
+        <v>85002040484327</v>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
@@ -8983,9 +8994,9 @@
       <c r="B30" s="2" t="n">
         <v>127</v>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>HolyCrownPickaxe</t>
+          <t>Holy Crown Pickaxe</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
@@ -8994,10 +9005,10 @@
       <c r="E30" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="27" t="n">
         <v>122188029381990</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["01-holy-crown-pickaxe"]</t>
         </is>
@@ -9010,9 +9021,9 @@
       <c r="B31" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>HolyCrownHammer</t>
+          <t>Holy Crown Hammer</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
@@ -9021,10 +9032,10 @@
       <c r="E31" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G31" s="27" t="n">
         <v>111918297845046</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["02-holy-crown-hammer"]</t>
         </is>
@@ -9037,9 +9048,9 @@
       <c r="B32" s="2" t="n">
         <v>129</v>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>DragonFlamePickaxe</t>
+          <t>Dragon Flame Pickaxe</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
@@ -9048,10 +9059,10 @@
       <c r="E32" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="G32" s="3" t="n">
+      <c r="G32" s="27" t="n">
         <v>131796875082030</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["03-dragon-flame-pickaxe"]</t>
         </is>
@@ -9064,9 +9075,9 @@
       <c r="B33" s="2" t="n">
         <v>130</v>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>DragonFlameHammer</t>
+          <t>Dragon Flame Hammer</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
@@ -9075,10 +9086,10 @@
       <c r="E33" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="G33" s="3" t="n">
+      <c r="G33" s="27" t="n">
         <v>135291300946209</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["04-dragon-flame-hammer"]</t>
         </is>
@@ -9091,9 +9102,9 @@
       <c r="B34" s="2" t="n">
         <v>131</v>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>ThunderPickaxe</t>
+          <t>Thunder Pickaxe</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
@@ -9102,10 +9113,10 @@
       <c r="E34" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="G34" s="27" t="n">
         <v>135059340240171</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["05-thunder-pickaxe"]</t>
         </is>
@@ -9118,9 +9129,9 @@
       <c r="B35" s="2" t="n">
         <v>132</v>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>ThunderHammer</t>
+          <t>Thunder Hammer</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
@@ -9129,242 +9140,242 @@
       <c r="E35" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="G35" s="27" t="n">
         <v>138711849822666</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" s="6" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["06-thunder-hammer"]</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="C36" s="0" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>EasternCloudsPickaxe</t>
+          <t>Eastern Clouds Pickaxe</t>
         </is>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D36" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="E36" s="0" t="n">
+      <c r="E36" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="G36" s="0" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>103077185243615</t>
         </is>
       </c>
-      <c r="H36" s="0" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["07-eastern-clouds-pickaxe"]</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="0" t="n">
+      <c r="A37" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="C37" s="0" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>EasternCloudsHammer</t>
+          <t>Eastern Clouds Hammer</t>
         </is>
       </c>
-      <c r="D37" s="0" t="n">
+      <c r="D37" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E37" s="0" t="n">
+      <c r="E37" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G37" s="0" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>119720961929827</t>
         </is>
       </c>
-      <c r="H37" s="0" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["08-eastern-clouds-hammer"]</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C38" s="0" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>ForestGuardianPickaxe</t>
+          <t>Forest Guardian Pickaxe</t>
         </is>
       </c>
-      <c r="D38" s="0" t="n">
+      <c r="D38" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G38" s="0" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>104288707111612</t>
         </is>
       </c>
-      <c r="H38" s="0" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["09-forest-guardian-pickaxe"]</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="C39" s="0" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>ForestGuardianHammer</t>
+          <t>Forest Guardian Hammer</t>
         </is>
       </c>
-      <c r="D39" s="0" t="n">
+      <c r="D39" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="G39" s="0" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>93955605202823</t>
         </is>
       </c>
-      <c r="H39" s="0" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["10-forest-guardian-hammer"]</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="0" t="n">
+      <c r="A40" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="C40" s="0" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>IceCrystalPickaxe</t>
+          <t>Ice Crystal Pickaxe</t>
         </is>
       </c>
-      <c r="D40" s="0" t="n">
+      <c r="D40" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="E40" s="0" t="n">
+      <c r="E40" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="G40" s="0" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>94920898798936</t>
         </is>
       </c>
-      <c r="H40" s="0" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["11-ice-crystal-pickaxe"]</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="0" t="n">
+      <c r="A41" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="C41" s="0" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>IceCrystalHammer</t>
+          <t>Ice Crystal Hammer</t>
         </is>
       </c>
-      <c r="D41" s="0" t="n">
+      <c r="D41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="E41" s="0" t="n">
+      <c r="E41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="G41" s="0" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>98900726428144</t>
         </is>
       </c>
-      <c r="H41" s="0" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["12-ice-crystal-hammer"]</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="0" t="n">
+      <c r="A42" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C42" s="0" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>ShadowDemonPickaxe</t>
+          <t>Shadow Demon Pickaxe</t>
         </is>
       </c>
-      <c r="D42" s="0" t="n">
+      <c r="D42" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="E42" s="0" t="n">
+      <c r="E42" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="G42" s="0" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>97673689505764</t>
         </is>
       </c>
-      <c r="H42" s="0" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["13-shadow-demon-pickaxe"]</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="0" t="n">
+      <c r="A43" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C43" s="0" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>ShadowDemonHammer</t>
+          <t>Shadow Demon Hammer</t>
         </is>
       </c>
-      <c r="D43" s="0" t="n">
+      <c r="D43" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="E43" s="0" t="n">
+      <c r="E43" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="G43" s="0" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>133737570876290</t>
         </is>
       </c>
-      <c r="H43" s="0" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>game.ReplicatedStorage.Assets.AITools["14-shadow-demon-hammer"]</t>
         </is>
@@ -9557,7 +9568,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n"/>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="26" t="n">
         <v>88151748923443</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -9588,7 +9599,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="n"/>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="26" t="n">
         <v>130646097070957</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9619,7 +9630,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="2" t="n"/>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="26" t="n">
         <v>86124893237823</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -9650,7 +9661,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="2" t="n"/>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="26" t="n">
         <v>117901666423784</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -9681,7 +9692,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="2" t="n"/>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="26" t="n">
         <v>133168932011408</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9712,7 +9723,7 @@
         <v>6</v>
       </c>
       <c r="G9" s="3" t="n"/>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="26" t="n">
         <v>71089861609803</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -9743,7 +9754,7 @@
         <v>7</v>
       </c>
       <c r="G10" s="3" t="n"/>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="26" t="n">
         <v>71622349623563</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -9774,7 +9785,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="3" t="n"/>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="26" t="n">
         <v>126547452796781</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -9804,7 +9815,7 @@
       <c r="F12" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="26" t="n">
         <v>111693433253936</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -9835,7 +9846,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="n"/>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="26" t="n">
         <v>126721700266409</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -26241,7 +26252,7 @@
         <v>11</v>
       </c>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="26" t="n">
         <v>92711027530571</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -42647,7 +42658,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="2" t="n"/>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="26" t="n">
         <v>140129159429440</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -59053,7 +59064,7 @@
         <v>13</v>
       </c>
       <c r="G16" s="2" t="n"/>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="26" t="n">
         <v>125903398380406</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -59084,7 +59095,7 @@
         <v>14</v>
       </c>
       <c r="G17" s="2" t="n"/>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="26" t="n">
         <v>110859814667398</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -59115,7 +59126,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="2" t="n"/>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="26" t="n">
         <v>71778195177377</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -59146,7 +59157,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="2" t="n"/>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="26" t="n">
         <v>82261970902739</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -59177,7 +59188,7 @@
         <v>17</v>
       </c>
       <c r="G20" s="2" t="n"/>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="26" t="n">
         <v>84969691879555</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -59207,7 +59218,7 @@
       <c r="F21" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="26" t="n">
         <v>135431835703650</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -59237,7 +59248,7 @@
       <c r="F22" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="26" t="n">
         <v>84363202598659</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -59267,7 +59278,7 @@
       <c r="F23" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="26" t="n">
         <v>140502552004582</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -59297,7 +59308,7 @@
       <c r="F24" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="26" t="n">
         <v>110544423490869</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -59327,7 +59338,7 @@
       <c r="F25" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="26" t="n">
         <v>88436670368181</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -59357,7 +59368,7 @@
       <c r="F26" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="26" t="n">
         <v>101523513603326</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -59387,7 +59398,7 @@
       <c r="F27" s="2" t="n">
         <v>24</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="26" t="n">
         <v>117557339704806</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -59417,7 +59428,7 @@
       <c r="F28" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="26" t="n">
         <v>94281665600637</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -59579,7 +59590,7 @@
           <s:t>World1.Level_6</s:t>
         </s:is>
       </s:c>
-      <s:c r="B9" s="22" t="inlineStr">
+      <s:c r="B9" s="24" t="inlineStr">
         <s:is>
           <s:t>3.80e+4</s:t>
         </s:is>
@@ -59596,7 +59607,7 @@
           <s:t>World1.Level_7</s:t>
         </s:is>
       </s:c>
-      <s:c r="B10" s="22" t="inlineStr">
+      <s:c r="B10" s="24" t="inlineStr">
         <s:is>
           <s:t>1.59e+5</s:t>
         </s:is>
@@ -59613,7 +59624,7 @@
           <s:t>World1.Level_8</s:t>
         </s:is>
       </s:c>
-      <s:c r="B11" s="22" t="inlineStr">
+      <s:c r="B11" s="24" t="inlineStr">
         <s:is>
           <s:t>6.64e+5</s:t>
         </s:is>
@@ -59630,7 +59641,7 @@
           <s:t>World1.Level_9</s:t>
         </s:is>
       </s:c>
-      <s:c r="B12" s="22" t="inlineStr">
+      <s:c r="B12" s="24" t="inlineStr">
         <s:is>
           <s:t>2.77e+6</s:t>
         </s:is>
@@ -59647,7 +59658,7 @@
           <s:t>World1.Level_10</s:t>
         </s:is>
       </s:c>
-      <s:c r="B13" s="22" t="inlineStr">
+      <s:c r="B13" s="24" t="inlineStr">
         <s:is>
           <s:t>1.16e+7</s:t>
         </s:is>
@@ -59664,7 +59675,7 @@
           <s:t>World1.Level_11</s:t>
         </s:is>
       </s:c>
-      <s:c r="B14" s="22" t="inlineStr">
+      <s:c r="B14" s="24" t="inlineStr">
         <s:is>
           <s:t>4.84e+7</s:t>
         </s:is>
@@ -59681,7 +59692,7 @@
           <s:t>World1.Level_12</s:t>
         </s:is>
       </s:c>
-      <s:c r="B15" s="22" t="inlineStr">
+      <s:c r="B15" s="24" t="inlineStr">
         <s:is>
           <s:t>2.02e+8</s:t>
         </s:is>
@@ -59698,7 +59709,7 @@
           <s:t>World1.Level_13</s:t>
         </s:is>
       </s:c>
-      <s:c r="B16" s="22" t="inlineStr">
+      <s:c r="B16" s="24" t="inlineStr">
         <s:is>
           <s:t>8.44e+8</s:t>
         </s:is>
@@ -59715,7 +59726,7 @@
           <s:t>World2.Level_14</s:t>
         </s:is>
       </s:c>
-      <s:c r="B17" s="22" t="inlineStr">
+      <s:c r="B17" s="24" t="inlineStr">
         <s:is>
           <s:t>3.53e+9</s:t>
         </s:is>
@@ -59732,7 +59743,7 @@
           <s:t>World2.Level_15</s:t>
         </s:is>
       </s:c>
-      <s:c r="B18" s="22" t="inlineStr">
+      <s:c r="B18" s="24" t="inlineStr">
         <s:is>
           <s:t>1.47e+10</s:t>
         </s:is>
@@ -59749,7 +59760,7 @@
           <s:t>World2.Level_16</s:t>
         </s:is>
       </s:c>
-      <s:c r="B19" s="22" t="inlineStr">
+      <s:c r="B19" s="24" t="inlineStr">
         <s:is>
           <s:t>6.15e+10</s:t>
         </s:is>
@@ -59766,7 +59777,7 @@
           <s:t>World2.Level_17</s:t>
         </s:is>
       </s:c>
-      <s:c r="B20" s="22" t="inlineStr">
+      <s:c r="B20" s="24" t="inlineStr">
         <s:is>
           <s:t>2.57e+11</s:t>
         </s:is>
@@ -59783,7 +59794,7 @@
           <s:t>World2.Level_18</s:t>
         </s:is>
       </s:c>
-      <s:c r="B21" s="22" t="inlineStr">
+      <s:c r="B21" s="24" t="inlineStr">
         <s:is>
           <s:t>1.07e+12</s:t>
         </s:is>
@@ -59800,7 +59811,7 @@
           <s:t>World2.Level_19</s:t>
         </s:is>
       </s:c>
-      <s:c r="B22" s="22" t="inlineStr">
+      <s:c r="B22" s="24" t="inlineStr">
         <s:is>
           <s:t>4.48e+12</s:t>
         </s:is>
@@ -59817,7 +59828,7 @@
           <s:t>World2.Level_20</s:t>
         </s:is>
       </s:c>
-      <s:c r="B23" s="22" t="inlineStr">
+      <s:c r="B23" s="24" t="inlineStr">
         <s:is>
           <s:t>1.87e+13</s:t>
         </s:is>
@@ -59834,7 +59845,7 @@
           <s:t>World2.Level_21</s:t>
         </s:is>
       </s:c>
-      <s:c r="B24" s="22" t="inlineStr">
+      <s:c r="B24" s="24" t="inlineStr">
         <s:is>
           <s:t>7.82e+13</s:t>
         </s:is>
@@ -59851,7 +59862,7 @@
           <s:t>World2.Level_22</s:t>
         </s:is>
       </s:c>
-      <s:c r="B25" s="22" t="inlineStr">
+      <s:c r="B25" s="24" t="inlineStr">
         <s:is>
           <s:t>3.27e+14</s:t>
         </s:is>
@@ -59868,7 +59879,7 @@
           <s:t>World2.Level_23</s:t>
         </s:is>
       </s:c>
-      <s:c r="B26" s="22" t="inlineStr">
+      <s:c r="B26" s="24" t="inlineStr">
         <s:is>
           <s:t>1.37e+15</s:t>
         </s:is>
@@ -59885,7 +59896,7 @@
           <s:t>World2.Level_24</s:t>
         </s:is>
       </s:c>
-      <s:c r="B27" s="22" t="inlineStr">
+      <s:c r="B27" s="24" t="inlineStr">
         <s:is>
           <s:t>5.70e+15</s:t>
         </s:is>
@@ -59902,7 +59913,7 @@
           <s:t>World2.Level_25</s:t>
         </s:is>
       </s:c>
-      <s:c r="B28" s="22" t="inlineStr">
+      <s:c r="B28" s="24" t="inlineStr">
         <s:is>
           <s:t>2.38e+16</s:t>
         </s:is>
@@ -59919,7 +59930,7 @@
           <s:t>World2.Level_26</s:t>
         </s:is>
       </s:c>
-      <s:c r="B29" s="22" t="inlineStr">
+      <s:c r="B29" s="24" t="inlineStr">
         <s:is>
           <s:t>9.95e+16</s:t>
         </s:is>
@@ -59936,7 +59947,7 @@
           <s:t>World3.Level_27</s:t>
         </s:is>
       </s:c>
-      <s:c r="B30" s="22" t="inlineStr">
+      <s:c r="B30" s="24" t="inlineStr">
         <s:is>
           <s:t>4.16e+17</s:t>
         </s:is>
@@ -59953,7 +59964,7 @@
           <s:t>World3.Level_28</s:t>
         </s:is>
       </s:c>
-      <s:c r="B31" s="22" t="inlineStr">
+      <s:c r="B31" s="24" t="inlineStr">
         <s:is>
           <s:t>1.74e+18</s:t>
         </s:is>
@@ -59970,7 +59981,7 @@
           <s:t>World3.Level_29</s:t>
         </s:is>
       </s:c>
-      <s:c r="B32" s="22" t="inlineStr">
+      <s:c r="B32" s="24" t="inlineStr">
         <s:is>
           <s:t>7.25e+18</s:t>
         </s:is>
@@ -59987,7 +59998,7 @@
           <s:t>World3.Level_30</s:t>
         </s:is>
       </s:c>
-      <s:c r="B33" s="22" t="inlineStr">
+      <s:c r="B33" s="24" t="inlineStr">
         <s:is>
           <s:t>3.03e+19</s:t>
         </s:is>
@@ -60004,7 +60015,7 @@
           <s:t>World3.Level_31</s:t>
         </s:is>
       </s:c>
-      <s:c r="B34" s="22" t="inlineStr">
+      <s:c r="B34" s="24" t="inlineStr">
         <s:is>
           <s:t>1.27e+20</s:t>
         </s:is>
@@ -60021,7 +60032,7 @@
           <s:t>World3.Level_32</s:t>
         </s:is>
       </s:c>
-      <s:c r="B35" s="22" t="inlineStr">
+      <s:c r="B35" s="24" t="inlineStr">
         <s:is>
           <s:t>5.29e+20</s:t>
         </s:is>
@@ -60038,7 +60049,7 @@
           <s:t>World3.Level_33</s:t>
         </s:is>
       </s:c>
-      <s:c r="B36" s="22" t="inlineStr">
+      <s:c r="B36" s="24" t="inlineStr">
         <s:is>
           <s:t>2.21e+21</s:t>
         </s:is>
@@ -60055,7 +60066,7 @@
           <s:t>World3.Level_34</s:t>
         </s:is>
       </s:c>
-      <s:c r="B37" s="22" t="inlineStr">
+      <s:c r="B37" s="24" t="inlineStr">
         <s:is>
           <s:t>9.23e+21</s:t>
         </s:is>
@@ -60072,7 +60083,7 @@
           <s:t>World3.Level_35</s:t>
         </s:is>
       </s:c>
-      <s:c r="B38" s="22" t="inlineStr">
+      <s:c r="B38" s="24" t="inlineStr">
         <s:is>
           <s:t>3.85e+22</s:t>
         </s:is>
@@ -60089,7 +60100,7 @@
           <s:t>World3.Level_36</s:t>
         </s:is>
       </s:c>
-      <s:c r="B39" s="22" t="inlineStr">
+      <s:c r="B39" s="24" t="inlineStr">
         <s:is>
           <s:t>1.61e+23</s:t>
         </s:is>
@@ -60106,7 +60117,7 @@
           <s:t>World3.Level_37</s:t>
         </s:is>
       </s:c>
-      <s:c r="B40" s="22" t="inlineStr">
+      <s:c r="B40" s="24" t="inlineStr">
         <s:is>
           <s:t>6.73e+23</s:t>
         </s:is>
@@ -60123,7 +60134,7 @@
           <s:t>World3.Level_38</s:t>
         </s:is>
       </s:c>
-      <s:c r="B41" s="22" t="inlineStr">
+      <s:c r="B41" s="24" t="inlineStr">
         <s:is>
           <s:t>2.81e+24</s:t>
         </s:is>
@@ -60140,7 +60151,7 @@
           <s:t>World3.Level_39</s:t>
         </s:is>
       </s:c>
-      <s:c r="B42" s="22" t="inlineStr">
+      <s:c r="B42" s="24" t="inlineStr">
         <s:is>
           <s:t>1.17e+25</s:t>
         </s:is>
@@ -60157,7 +60168,7 @@
           <s:t>World4.Level_40</s:t>
         </s:is>
       </s:c>
-      <s:c r="B43" s="23" t="inlineStr">
+      <s:c r="B43" s="25" t="inlineStr">
         <s:is>
           <s:t>4.90e+25</s:t>
         </s:is>
@@ -60174,7 +60185,7 @@
           <s:t>World4.Level_41</s:t>
         </s:is>
       </s:c>
-      <s:c r="B44" s="23" t="inlineStr">
+      <s:c r="B44" s="25" t="inlineStr">
         <s:is>
           <s:t>2.05e+26</s:t>
         </s:is>
@@ -60191,7 +60202,7 @@
           <s:t>World4.Level_42</s:t>
         </s:is>
       </s:c>
-      <s:c r="B45" s="23" t="inlineStr">
+      <s:c r="B45" s="25" t="inlineStr">
         <s:is>
           <s:t>8.55e+26</s:t>
         </s:is>
@@ -60208,7 +60219,7 @@
           <s:t>World4.Level_43</s:t>
         </s:is>
       </s:c>
-      <s:c r="B46" s="23" t="inlineStr">
+      <s:c r="B46" s="25" t="inlineStr">
         <s:is>
           <s:t>3.57e+27</s:t>
         </s:is>
@@ -60225,7 +60236,7 @@
           <s:t>World4.Level_44</s:t>
         </s:is>
       </s:c>
-      <s:c r="B47" s="23" t="inlineStr">
+      <s:c r="B47" s="25" t="inlineStr">
         <s:is>
           <s:t>1.49e+28</s:t>
         </s:is>
@@ -60242,7 +60253,7 @@
           <s:t>World4.Level_45</s:t>
         </s:is>
       </s:c>
-      <s:c r="B48" s="23" t="inlineStr">
+      <s:c r="B48" s="25" t="inlineStr">
         <s:is>
           <s:t>6.24e+28</s:t>
         </s:is>
@@ -60259,7 +60270,7 @@
           <s:t>World4.Level_46</s:t>
         </s:is>
       </s:c>
-      <s:c r="B49" s="23" t="inlineStr">
+      <s:c r="B49" s="25" t="inlineStr">
         <s:is>
           <s:t>2.60e+29</s:t>
         </s:is>
@@ -60276,7 +60287,7 @@
           <s:t>World4.Level_47</s:t>
         </s:is>
       </s:c>
-      <s:c r="B50" s="23" t="inlineStr">
+      <s:c r="B50" s="25" t="inlineStr">
         <s:is>
           <s:t>1.09e+30</s:t>
         </s:is>
@@ -60293,7 +60304,7 @@
           <s:t>World4.Level_48</s:t>
         </s:is>
       </s:c>
-      <s:c r="B51" s="23" t="inlineStr">
+      <s:c r="B51" s="25" t="inlineStr">
         <s:is>
           <s:t>4.54e+30</s:t>
         </s:is>
@@ -60310,7 +60321,7 @@
           <s:t>World4.Level_49</s:t>
         </s:is>
       </s:c>
-      <s:c r="B52" s="23" t="inlineStr">
+      <s:c r="B52" s="25" t="inlineStr">
         <s:is>
           <s:t>1.90e+31</s:t>
         </s:is>
@@ -60327,7 +60338,7 @@
           <s:t>World4.Level_50</s:t>
         </s:is>
       </s:c>
-      <s:c r="B53" s="23" t="inlineStr">
+      <s:c r="B53" s="25" t="inlineStr">
         <s:is>
           <s:t>7.93e+31</s:t>
         </s:is>
@@ -60344,7 +60355,7 @@
           <s:t>World4.Level_51</s:t>
         </s:is>
       </s:c>
-      <s:c r="B54" s="23" t="inlineStr">
+      <s:c r="B54" s="25" t="inlineStr">
         <s:is>
           <s:t>3.31e+32</s:t>
         </s:is>
@@ -60361,7 +60372,7 @@
           <s:t>World4.Level_52</s:t>
         </s:is>
       </s:c>
-      <s:c r="B55" s="23" t="inlineStr">
+      <s:c r="B55" s="25" t="inlineStr">
         <s:is>
           <s:t>1.38e+33</s:t>
         </s:is>

--- a/配置文档/GameConfig.xlsx
+++ b/配置文档/GameConfig.xlsx
@@ -3399,7 +3399,7 @@
       </s:c>
       <s:c r="C4" s="2" t="inlineStr">
         <s:is>
-          <s:t>打火机</s:t>
+          <s:t>Steel Nail</s:t>
         </s:is>
       </s:c>
       <s:c r="D4" s="2">
@@ -3431,7 +3431,7 @@
       </s:c>
       <s:c r="C5" s="2" t="inlineStr">
         <s:is>
-          <s:t>矿泉水</s:t>
+          <s:t>Tablet</s:t>
         </s:is>
       </s:c>
       <s:c r="D5" s="2">
@@ -3464,7 +3464,7 @@
       </s:c>
       <s:c r="C6" s="2" t="inlineStr">
         <s:is>
-          <s:t>纯净水</s:t>
+          <s:t>Capsule</s:t>
         </s:is>
       </s:c>
       <s:c r="D6" s="2">
@@ -3497,7 +3497,7 @@
       </s:c>
       <s:c r="C7" s="2" t="inlineStr">
         <s:is>
-          <s:t>苏打水</s:t>
+          <s:t>Dry Cell Battery</s:t>
         </s:is>
       </s:c>
       <s:c r="D7" s="2">
@@ -3530,7 +3530,7 @@
       </s:c>
       <s:c r="C8" s="2" t="inlineStr">
         <s:is>
-          <s:t>水桶</s:t>
+          <s:t>9V Battery</s:t>
         </s:is>
       </s:c>
       <s:c r="D8" s="2">
@@ -3560,7 +3560,7 @@
       </s:c>
       <s:c r="C9" s="2" t="inlineStr">
         <s:is>
-          <s:t>玻璃瓶</s:t>
+          <s:t>Crackers</s:t>
         </s:is>
       </s:c>
       <s:c r="D9" s="2">
@@ -3591,7 +3591,7 @@
       </s:c>
       <s:c r="C10" s="2" t="inlineStr">
         <s:is>
-          <s:t>啤酒瓶</s:t>
+          <s:t>Sandwich Crackers</s:t>
         </s:is>
       </s:c>
       <s:c r="D10" s="2">
@@ -3622,7 +3622,7 @@
       </s:c>
       <s:c r="C11" s="2" t="inlineStr">
         <s:is>
-          <s:t>红酒瓶</s:t>
+          <s:t>Packaged Crackers</s:t>
         </s:is>
       </s:c>
       <s:c r="D11" s="2">
@@ -3653,7 +3653,7 @@
       </s:c>
       <s:c r="C12" s="2" t="inlineStr">
         <s:is>
-          <s:t>香槟瓶</s:t>
+          <s:t>Chocolate Stick</s:t>
         </s:is>
       </s:c>
       <s:c r="D12" s="2">
@@ -3683,7 +3683,7 @@
       </s:c>
       <s:c r="C13" s="2" t="inlineStr">
         <s:is>
-          <s:t>收藏酒瓶</s:t>
+          <s:t>Chocolate Bar</s:t>
         </s:is>
       </s:c>
       <s:c r="D13" s="2">
@@ -3713,7 +3713,7 @@
       </s:c>
       <s:c r="C14" s="2" t="inlineStr">
         <s:is>
-          <s:t>钢钉</s:t>
+          <s:t>Chocolate Drink</s:t>
         </s:is>
       </s:c>
       <s:c r="D14" s="2">
@@ -3743,7 +3743,7 @@
       </s:c>
       <s:c r="C15" s="2" t="inlineStr">
         <s:is>
-          <s:t>药片</s:t>
+          <s:t>Honey Jar</s:t>
         </s:is>
       </s:c>
       <s:c r="D15" s="2">
@@ -3773,7 +3773,7 @@
       </s:c>
       <s:c r="C16" s="2" t="inlineStr">
         <s:is>
-          <s:t>曲奇</s:t>
+          <s:t>Open Honey Jar</s:t>
         </s:is>
       </s:c>
       <s:c r="D16" s="2">
@@ -3804,7 +3804,7 @@
       </s:c>
       <s:c r="C17" s="2" t="inlineStr">
         <s:is>
-          <s:t>苏打饼</s:t>
+          <s:t>Jam Jar</s:t>
         </s:is>
       </s:c>
       <s:c r="D17" s="2">
@@ -3835,7 +3835,7 @@
       </s:c>
       <s:c r="C18" s="2" t="inlineStr">
         <s:is>
-          <s:t>夹心饼</s:t>
+          <s:t>Open Jam Jar</s:t>
         </s:is>
       </s:c>
       <s:c r="D18" s="2">
@@ -3866,7 +3866,7 @@
       </s:c>
       <s:c r="C19" s="2" t="inlineStr">
         <s:is>
-          <s:t>黑巧克力</s:t>
+          <s:t>Bottled Water</s:t>
         </s:is>
       </s:c>
       <s:c r="D19" s="2">
@@ -3897,7 +3897,7 @@
       </s:c>
       <s:c r="C20" s="2" t="inlineStr">
         <s:is>
-          <s:t>牛奶巧克力</s:t>
+          <s:t>Water Bottle with Handle</s:t>
         </s:is>
       </s:c>
       <s:c r="D20" s="2">
@@ -3928,7 +3928,7 @@
       </s:c>
       <s:c r="C21" s="2" t="inlineStr">
         <s:is>
-          <s:t>可可饮料</s:t>
+          <s:t>Large Water Bottle</s:t>
         </s:is>
       </s:c>
       <s:c r="D21" s="2">
@@ -3959,7 +3959,7 @@
       </s:c>
       <s:c r="C22" s="2" t="inlineStr">
         <s:is>
-          <s:t>蜂蜜</s:t>
+          <s:t>Black Canteen</s:t>
         </s:is>
       </s:c>
       <s:c r="D22" s="2">
@@ -3990,7 +3990,7 @@
       </s:c>
       <s:c r="C23" s="2" t="inlineStr">
         <s:is>
-          <s:t>野蜂蜜</s:t>
+          <s:t>Military Canteen</s:t>
         </s:is>
       </s:c>
       <s:c r="D23" s="2">
@@ -4021,7 +4021,7 @@
       </s:c>
       <s:c r="C24" s="2" t="inlineStr">
         <s:is>
-          <s:t>草莓酱</s:t>
+          <s:t>Glass Bottle</s:t>
         </s:is>
       </s:c>
       <s:c r="D24" s="2">
@@ -4052,7 +4052,7 @@
       </s:c>
       <s:c r="C25" s="2" t="inlineStr">
         <s:is>
-          <s:t>蓝莓酱</s:t>
+          <s:t>Round Bottle</s:t>
         </s:is>
       </s:c>
       <s:c r="D25" s="2">
@@ -4083,7 +4083,7 @@
       </s:c>
       <s:c r="C26" s="2" t="inlineStr">
         <s:is>
-          <s:t>肉罐头</s:t>
+          <s:t>Broken Bottle</s:t>
         </s:is>
       </s:c>
       <s:c r="D26" s="2">
@@ -4114,7 +4114,7 @@
       </s:c>
       <s:c r="C27" s="2" t="inlineStr">
         <s:is>
-          <s:t>鱼罐头</s:t>
+          <s:t>Square Bottle</s:t>
         </s:is>
       </s:c>
       <s:c r="D27" s="2">
@@ -4145,7 +4145,7 @@
       </s:c>
       <s:c r="C28" s="2" t="inlineStr">
         <s:is>
-          <s:t>水果罐头</s:t>
+          <s:t>Beer Bottle</s:t>
         </s:is>
       </s:c>
       <s:c r="D28" s="2">
@@ -4176,7 +4176,7 @@
       </s:c>
       <s:c r="C29" s="2" t="inlineStr">
         <s:is>
-          <s:t>午餐肉</s:t>
+          <s:t>Canned Peas</s:t>
         </s:is>
       </s:c>
       <s:c r="D29" s="2">
@@ -4207,7 +4207,7 @@
       </s:c>
       <s:c r="C30" s="2" t="inlineStr">
         <s:is>
-          <s:t>豆子罐头</s:t>
+          <s:t>Open Can of Peas</s:t>
         </s:is>
       </s:c>
       <s:c r="D30" s="2">
@@ -4238,7 +4238,7 @@
       </s:c>
       <s:c r="C31" s="2" t="inlineStr">
         <s:is>
-          <s:t>军粮罐头</s:t>
+          <s:t>Canned Fish</s:t>
         </s:is>
       </s:c>
       <s:c r="D31" s="2">
@@ -4269,7 +4269,7 @@
       </s:c>
       <s:c r="C32" s="2" t="inlineStr">
         <s:is>
-          <s:t>高级罐头</s:t>
+          <s:t>Open Can of Fish</s:t>
         </s:is>
       </s:c>
       <s:c r="D32" s="2">
@@ -4300,7 +4300,7 @@
       </s:c>
       <s:c r="C33" s="2" t="inlineStr">
         <s:is>
-          <s:t>清洁剂</s:t>
+          <s:t>Canned Beans</s:t>
         </s:is>
       </s:c>
       <s:c r="D33" s="2">
@@ -4330,7 +4330,7 @@
       </s:c>
       <s:c r="C34" s="2" t="inlineStr">
         <s:is>
-          <s:t>漂白水</s:t>
+          <s:t>Open Can of Beans</s:t>
         </s:is>
       </s:c>
       <s:c r="D34" s="2">
@@ -4360,7 +4360,7 @@
       </s:c>
       <s:c r="C35" s="2" t="inlineStr">
         <s:is>
-          <s:t>润滑油</s:t>
+          <s:t>Canned Drink</s:t>
         </s:is>
       </s:c>
       <s:c r="D35" s="2">
@@ -4390,7 +4390,7 @@
       </s:c>
       <s:c r="C36" s="2" t="inlineStr">
         <s:is>
-          <s:t>小油壶</s:t>
+          <s:t>Medicine Bottle</s:t>
         </s:is>
       </s:c>
       <s:c r="D36" s="2">
@@ -4421,7 +4421,7 @@
       </s:c>
       <s:c r="C37" s="2" t="inlineStr">
         <s:is>
-          <s:t>运动水壶</s:t>
+          <s:t>Pill Organizer</s:t>
         </s:is>
       </s:c>
       <s:c r="D37" s="2">
@@ -4451,7 +4451,7 @@
       </s:c>
       <s:c r="C38" s="2" t="inlineStr">
         <s:is>
-          <s:t>军用水壶</s:t>
+          <s:t>Syringe</s:t>
         </s:is>
       </s:c>
       <s:c r="D38" s="2">
@@ -4481,7 +4481,7 @@
       </s:c>
       <s:c r="C39" s="2" t="inlineStr">
         <s:is>
-          <s:t>机油壶</s:t>
+          <s:t>Auto-Injector</s:t>
         </s:is>
       </s:c>
       <s:c r="D39" s="2">
@@ -4512,7 +4512,7 @@
       </s:c>
       <s:c r="C40" s="2" t="inlineStr">
         <s:is>
-          <s:t>燃油罐</s:t>
+          <s:t>Bandage Roll</s:t>
         </s:is>
       </s:c>
       <s:c r="D40" s="2">
@@ -4543,7 +4543,7 @@
       </s:c>
       <s:c r="C41" s="2" t="inlineStr">
         <s:is>
-          <s:t>礼帽</s:t>
+          <s:t>IV Bag</s:t>
         </s:is>
       </s:c>
       <s:c r="D41" s="2">
@@ -4573,7 +4573,7 @@
       </s:c>
       <s:c r="C42" s="2" t="inlineStr">
         <s:is>
-          <s:t>棒球帽</s:t>
+          <s:t>First Aid Bag</s:t>
         </s:is>
       </s:c>
       <s:c r="D42" s="2">
@@ -4603,7 +4603,7 @@
       </s:c>
       <s:c r="C43" s="2" t="inlineStr">
         <s:is>
-          <s:t>墨镜</s:t>
+          <s:t>First Aid Kit</s:t>
         </s:is>
       </s:c>
       <s:c r="D43" s="2">
@@ -4633,7 +4633,7 @@
       </s:c>
       <s:c r="C44" s="2" t="inlineStr">
         <s:is>
-          <s:t>太阳镜</s:t>
+          <s:t>Medical Case</s:t>
         </s:is>
       </s:c>
       <s:c r="D44" s="2">
@@ -4663,7 +4663,7 @@
       </s:c>
       <s:c r="C45" s="2" t="inlineStr">
         <s:is>
-          <s:t>护目镜</s:t>
+          <s:t>Cleaning Spray</s:t>
         </s:is>
       </s:c>
       <s:c r="D45" s="2">
@@ -4693,7 +4693,7 @@
       </s:c>
       <s:c r="C46" s="2" t="inlineStr">
         <s:is>
-          <s:t>战术风镜</s:t>
+          <s:t>Bleach</s:t>
         </s:is>
       </s:c>
       <s:c r="D46" s="2">
@@ -4723,7 +4723,7 @@
       </s:c>
       <s:c r="C47" s="2" t="inlineStr">
         <s:is>
-          <s:t>口罩</s:t>
+          <s:t>Lubricant Spray</s:t>
         </s:is>
       </s:c>
       <s:c r="D47" s="2">
@@ -4753,7 +4753,7 @@
       </s:c>
       <s:c r="C48" s="2" t="inlineStr">
         <s:is>
-          <s:t>防毒面具</s:t>
+          <s:t>Metal Pipe</s:t>
         </s:is>
       </s:c>
       <s:c r="D48" s="2">
@@ -4783,7 +4783,7 @@
       </s:c>
       <s:c r="C49" s="2" t="inlineStr">
         <s:is>
-          <s:t>战术面具</s:t>
+          <s:t>Flip-Top Lighter</s:t>
         </s:is>
       </s:c>
       <s:c r="D49" s="2">
@@ -4813,7 +4813,7 @@
       </s:c>
       <s:c r="C50" s="2" t="inlineStr">
         <s:is>
-          <s:t>皮靴</s:t>
+          <s:t>Red Fuel Can</s:t>
         </s:is>
       </s:c>
       <s:c r="D50" s="2">
@@ -4843,7 +4843,7 @@
       </s:c>
       <s:c r="C51" s="2" t="inlineStr">
         <s:is>
-          <s:t>雨靴</s:t>
+          <s:t>Green Fuel Can</s:t>
         </s:is>
       </s:c>
       <s:c r="D51" s="2">
@@ -4873,7 +4873,7 @@
       </s:c>
       <s:c r="C52" s="2" t="inlineStr">
         <s:is>
-          <s:t>登山靴</s:t>
+          <s:t>Jerry Can</s:t>
         </s:is>
       </s:c>
       <s:c r="D52" s="2">
@@ -4903,7 +4903,7 @@
       </s:c>
       <s:c r="C53" s="2" t="inlineStr">
         <s:is>
-          <s:t>军靴</s:t>
+          <s:t>Smartphone</s:t>
         </s:is>
       </s:c>
       <s:c r="D53" s="2">
@@ -4933,7 +4933,7 @@
       </s:c>
       <s:c r="C54" s="2" t="inlineStr">
         <s:is>
-          <s:t>防弹背心</s:t>
+          <s:t>Stopwatch</s:t>
         </s:is>
       </s:c>
       <s:c r="D54" s="2">
@@ -4963,7 +4963,7 @@
       </s:c>
       <s:c r="C55" s="2" t="inlineStr">
         <s:is>
-          <s:t>重型护甲</s:t>
+          <s:t>Pet ID Tag</s:t>
         </s:is>
       </s:c>
       <s:c r="D55" s="2">
@@ -4993,7 +4993,7 @@
       </s:c>
       <s:c r="C56" s="2" t="inlineStr">
         <s:is>
-          <s:t>工地头盔</s:t>
+          <s:t>Compass</s:t>
         </s:is>
       </s:c>
       <s:c r="D56" s="2">
@@ -5023,7 +5023,7 @@
       </s:c>
       <s:c r="C57" s="2" t="inlineStr">
         <s:is>
-          <s:t>骑行头盔</s:t>
+          <s:t>Folding Compass</s:t>
         </s:is>
       </s:c>
       <s:c r="D57" s="2">
@@ -5053,7 +5053,7 @@
       </s:c>
       <s:c r="C58" s="2" t="inlineStr">
         <s:is>
-          <s:t>防暴头盔</s:t>
+          <s:t>Fedora</s:t>
         </s:is>
       </s:c>
       <s:c r="D58" s="2">
@@ -5083,7 +5083,7 @@
       </s:c>
       <s:c r="C59" s="2" t="inlineStr">
         <s:is>
-          <s:t>战术头盔</s:t>
+          <s:t>Baseball Cap</s:t>
         </s:is>
       </s:c>
       <s:c r="D59" s="2">
@@ -5113,7 +5113,7 @@
       </s:c>
       <s:c r="C60" s="2" t="inlineStr">
         <s:is>
-          <s:t>小背包</s:t>
+          <s:t>Gold-Framed Sunglasses</s:t>
         </s:is>
       </s:c>
       <s:c r="D60" s="2">
@@ -5143,7 +5143,7 @@
       </s:c>
       <s:c r="C61" s="2" t="inlineStr">
         <s:is>
-          <s:t>登山包</s:t>
+          <s:t>Sunglasses</s:t>
         </s:is>
       </s:c>
       <s:c r="D61" s="2">
@@ -5173,7 +5173,7 @@
       </s:c>
       <s:c r="C62" s="2" t="inlineStr">
         <s:is>
-          <s:t>军用背包</s:t>
+          <s:t>Safety Goggles</s:t>
         </s:is>
       </s:c>
       <s:c r="D62" s="2">
@@ -5203,7 +5203,7 @@
       </s:c>
       <s:c r="C63" s="2" t="inlineStr">
         <s:is>
-          <s:t>铁锅</s:t>
+          <s:t>Tactical Goggles</s:t>
         </s:is>
       </s:c>
       <s:c r="D63" s="2">
@@ -5233,7 +5233,7 @@
       </s:c>
       <s:c r="C64" s="2" t="inlineStr">
         <s:is>
-          <s:t>木锤</s:t>
+          <s:t>Dust Mask</s:t>
         </s:is>
       </s:c>
       <s:c r="D64" s="2">
@@ -5263,7 +5263,7 @@
       </s:c>
       <s:c r="C65" s="2" t="inlineStr">
         <s:is>
-          <s:t>铁锤</s:t>
+          <s:t>Half-Face Respirator</s:t>
         </s:is>
       </s:c>
       <s:c r="D65" s="2">
@@ -5293,7 +5293,7 @@
       </s:c>
       <s:c r="C66" s="2" t="inlineStr">
         <s:is>
-          <s:t>大锤</s:t>
+          <s:t>Gas Mask</s:t>
         </s:is>
       </s:c>
       <s:c r="D66" s="2">
@@ -5323,7 +5323,7 @@
       </s:c>
       <s:c r="C67" s="2" t="inlineStr">
         <s:is>
-          <s:t>扳手</s:t>
+          <s:t>Brown Boots</s:t>
         </s:is>
       </s:c>
       <s:c r="D67" s="2">
@@ -5353,7 +5353,7 @@
       </s:c>
       <s:c r="C68" s="2" t="inlineStr">
         <s:is>
-          <s:t>活动扳手</s:t>
+          <s:t>Black Boots</s:t>
         </s:is>
       </s:c>
       <s:c r="D68" s="2">
@@ -5383,7 +5383,7 @@
       </s:c>
       <s:c r="C69" s="2" t="inlineStr">
         <s:is>
-          <s:t>管钳</s:t>
+          <s:t>Rubber Boots</s:t>
         </s:is>
       </s:c>
       <s:c r="D69" s="2">
@@ -5413,7 +5413,7 @@
       </s:c>
       <s:c r="C70" s="2" t="inlineStr">
         <s:is>
-          <s:t>工兵铲</s:t>
+          <s:t>Leather Shoes</s:t>
         </s:is>
       </s:c>
       <s:c r="D70" s="2">
@@ -5443,7 +5443,7 @@
       </s:c>
       <s:c r="C71" s="2" t="inlineStr">
         <s:is>
-          <s:t>铁锹</s:t>
+          <s:t>Bulletproof Vest</s:t>
         </s:is>
       </s:c>
       <s:c r="D71" s="2">
@@ -5473,7 +5473,7 @@
       </s:c>
       <s:c r="C72" s="2" t="inlineStr">
         <s:is>
-          <s:t>十字镐</s:t>
+          <s:t>Heavy Armor Vest</s:t>
         </s:is>
       </s:c>
       <s:c r="D72" s="2">
@@ -5503,7 +5503,7 @@
       </s:c>
       <s:c r="C73" s="2" t="inlineStr">
         <s:is>
-          <s:t>胶囊</s:t>
+          <s:t>Helmet with Goggles</s:t>
         </s:is>
       </s:c>
       <s:c r="D73" s="2">
@@ -5533,7 +5533,7 @@
       </s:c>
       <s:c r="C74" s="2" t="inlineStr">
         <s:is>
-          <s:t>干电池</s:t>
+          <s:t>Combat Helmet</s:t>
         </s:is>
       </s:c>
       <s:c r="D74" s="2">
@@ -5563,7 +5563,7 @@
       </s:c>
       <s:c r="C75" s="2" t="inlineStr">
         <s:is>
-          <s:t>强力电池</s:t>
+          <s:t>Riot Helmet</s:t>
         </s:is>
       </s:c>
       <s:c r="D75" s="2">
@@ -5593,7 +5593,7 @@
       </s:c>
       <s:c r="C76" s="2" t="inlineStr">
         <s:is>
-          <s:t>药瓶</s:t>
+          <s:t>Tactical Helmet</s:t>
         </s:is>
       </s:c>
       <s:c r="D76" s="2">
@@ -5623,7 +5623,7 @@
       </s:c>
       <s:c r="C77" s="2" t="inlineStr">
         <s:is>
-          <s:t>急救药瓶</s:t>
+          <s:t>Multi-Pocket Backpack</s:t>
         </s:is>
       </s:c>
       <s:c r="D77" s="2">
@@ -5653,7 +5653,7 @@
       </s:c>
       <s:c r="C78" s="2" t="inlineStr">
         <s:is>
-          <s:t>注射器</s:t>
+          <s:t>Tactical Backpack</s:t>
         </s:is>
       </s:c>
       <s:c r="D78" s="2">
@@ -5683,7 +5683,7 @@
       </s:c>
       <s:c r="C79" s="2" t="inlineStr">
         <s:is>
-          <s:t>强化针</s:t>
+          <s:t>Large Tactical Backpack</s:t>
         </s:is>
       </s:c>
       <s:c r="D79" s="2">
@@ -5713,7 +5713,7 @@
       </s:c>
       <s:c r="C80" s="2" t="inlineStr">
         <s:is>
-          <s:t>医用绷带</s:t>
+          <s:t>Toolbox</s:t>
         </s:is>
       </s:c>
       <s:c r="D80" s="2">
@@ -5743,7 +5743,7 @@
       </s:c>
       <s:c r="C81" s="2" t="inlineStr">
         <s:is>
-          <s:t>绿色徽章</s:t>
+          <s:t>Supply Case</s:t>
         </s:is>
       </s:c>
       <s:c r="D81" s="2">
@@ -5773,7 +5773,7 @@
       </s:c>
       <s:c r="C82" s="2" t="inlineStr">
         <s:is>
-          <s:t>急救包</s:t>
+          <s:t>Equipment Case</s:t>
         </s:is>
       </s:c>
       <s:c r="D82" s="2">
@@ -5803,7 +5803,7 @@
       </s:c>
       <s:c r="C83" s="2" t="inlineStr">
         <s:is>
-          <s:t>医疗箱</s:t>
+          <s:t>Cooking Pot</s:t>
         </s:is>
       </s:c>
       <s:c r="D83" s="2">
@@ -5833,7 +5833,7 @@
       </s:c>
       <s:c r="C84" s="2" t="inlineStr">
         <s:is>
-          <s:t>高级医疗箱</s:t>
+          <s:t>Red Barrel</s:t>
         </s:is>
       </s:c>
       <s:c r="D84" s="2">
@@ -5863,7 +5863,7 @@
       </s:c>
       <s:c r="C85" s="2" t="inlineStr">
         <s:is>
-          <s:t>钢管</s:t>
+          <s:t>Blue Barrel</s:t>
         </s:is>
       </s:c>
       <s:c r="D85" s="2">
@@ -5893,7 +5893,7 @@
       </s:c>
       <s:c r="C86" s="2" t="inlineStr">
         <s:is>
-          <s:t>手机</s:t>
+          <s:t>Sealed Drum</s:t>
         </s:is>
       </s:c>
       <s:c r="D86" s="2">
@@ -5923,7 +5923,7 @@
       </s:c>
       <s:c r="C87" s="2" t="inlineStr">
         <s:is>
-          <s:t>手表</s:t>
+          <s:t>Blue Steel Drum</s:t>
         </s:is>
       </s:c>
       <s:c r="D87" s="2">
@@ -5953,7 +5953,7 @@
       </s:c>
       <s:c r="C88" s="2" t="inlineStr">
         <s:is>
-          <s:t>身份牌</s:t>
+          <s:t>Hazardous Materials Drum</s:t>
         </s:is>
       </s:c>
       <s:c r="D88" s="2">
@@ -5983,7 +5983,7 @@
       </s:c>
       <s:c r="C89" s="2" t="inlineStr">
         <s:is>
-          <s:t>指南针</s:t>
+          <s:t>Propane Tank</s:t>
         </s:is>
       </s:c>
       <s:c r="D89" s="2">
@@ -6013,7 +6013,7 @@
       </s:c>
       <s:c r="C90" s="2" t="inlineStr">
         <s:is>
-          <s:t>军用罗盘</s:t>
+          <s:t>Rope</s:t>
         </s:is>
       </s:c>
       <s:c r="D90" s="2">
@@ -6043,7 +6043,7 @@
       </s:c>
       <s:c r="C91" s="2" t="inlineStr">
         <s:is>
-          <s:t>木箱</s:t>
+          <s:t>Wire Coil</s:t>
         </s:is>
       </s:c>
       <s:c r="D91" s="2">
@@ -6073,7 +6073,7 @@
       </s:c>
       <s:c r="C92" s="2" t="inlineStr">
         <s:is>
-          <s:t>工具箱</s:t>
+          <s:t>Walkie-Talkie</s:t>
         </s:is>
       </s:c>
       <s:c r="D92" s="2">
@@ -6103,7 +6103,7 @@
       </s:c>
       <s:c r="C93" s="2" t="inlineStr">
         <s:is>
-          <s:t>补给箱</s:t>
+          <s:t>Field Radio</s:t>
         </s:is>
       </s:c>
       <s:c r="D93" s="2">
@@ -6133,7 +6133,7 @@
       </s:c>
       <s:c r="C94" s="2" t="inlineStr">
         <s:is>
-          <s:t>油桶</s:t>
+          <s:t>Flashlight</s:t>
         </s:is>
       </s:c>
       <s:c r="D94" s="2">
@@ -6163,7 +6163,7 @@
       </s:c>
       <s:c r="C95" s="2" t="inlineStr">
         <s:is>
-          <s:t>储物桶</s:t>
+          <s:t>Headlamp</s:t>
         </s:is>
       </s:c>
       <s:c r="D95" s="2">
@@ -6193,7 +6193,7 @@
       </s:c>
       <s:c r="C96" s="2" t="inlineStr">
         <s:is>
-          <s:t>密封桶</s:t>
+          <s:t>Lantern</s:t>
         </s:is>
       </s:c>
       <s:c r="D96" s="2">
@@ -6223,7 +6223,7 @@
       </s:c>
       <s:c r="C97" s="2" t="inlineStr">
         <s:is>
-          <s:t>大铁桶</s:t>
+          <s:t>Telescope</s:t>
         </s:is>
       </s:c>
       <s:c r="D97" s="2">
@@ -6253,7 +6253,7 @@
       </s:c>
       <s:c r="C98" s="2" t="inlineStr">
         <s:is>
-          <s:t>煤气罐</s:t>
+          <s:t>Binoculars</s:t>
         </s:is>
       </s:c>
       <s:c r="D98" s="2">
@@ -6283,7 +6283,7 @@
       </s:c>
       <s:c r="C99" s="2" t="inlineStr">
         <s:is>
-          <s:t>粗绳</s:t>
+          <s:t>Claw Hammer</s:t>
         </s:is>
       </s:c>
       <s:c r="D99" s="2">
@@ -6313,7 +6313,7 @@
       </s:c>
       <s:c r="C100" s="2" t="inlineStr">
         <s:is>
-          <s:t>电线</s:t>
+          <s:t>Hammer</s:t>
         </s:is>
       </s:c>
       <s:c r="D100" s="2">
@@ -6343,7 +6343,7 @@
       </s:c>
       <s:c r="C101" s="2" t="inlineStr">
         <s:is>
-          <s:t>对讲机</s:t>
+          <s:t>Sledgehammer</s:t>
         </s:is>
       </s:c>
       <s:c r="D101" s="2">
@@ -6373,7 +6373,7 @@
       </s:c>
       <s:c r="C102" s="2" t="inlineStr">
         <s:is>
-          <s:t>军用电台</s:t>
+          <s:t>Adjustable Wrench</s:t>
         </s:is>
       </s:c>
       <s:c r="D102" s="2">
@@ -6403,7 +6403,7 @@
       </s:c>
       <s:c r="C103" s="2" t="inlineStr">
         <s:is>
-          <s:t>手电筒</s:t>
+          <s:t>Pipe Wrench</s:t>
         </s:is>
       </s:c>
       <s:c r="D103" s="2">
@@ -6433,7 +6433,7 @@
       </s:c>
       <s:c r="C104" s="2" t="inlineStr">
         <s:is>
-          <s:t>头灯</s:t>
+          <s:t>Crowbar</s:t>
         </s:is>
       </s:c>
       <s:c r="D104" s="2">
@@ -6463,7 +6463,7 @@
       </s:c>
       <s:c r="C105" s="2" t="inlineStr">
         <s:is>
-          <s:t>提灯</s:t>
+          <s:t>Entrenching Shovel</s:t>
         </s:is>
       </s:c>
       <s:c r="D105" s="2">
@@ -6493,7 +6493,7 @@
       </s:c>
       <s:c r="C106" s="2" t="inlineStr">
         <s:is>
-          <s:t>望远镜</s:t>
+          <s:t>Shovel</s:t>
         </s:is>
       </s:c>
       <s:c r="D106" s="2">
@@ -6523,7 +6523,7 @@
       </s:c>
       <s:c r="C107" s="2" t="inlineStr">
         <s:is>
-          <s:t>高倍望远镜</s:t>
+          <s:t>Pickaxe</s:t>
         </s:is>
       </s:c>
       <s:c r="D107" s="2">
@@ -6553,7 +6553,7 @@
       </s:c>
       <s:c r="C108" s="2" t="inlineStr">
         <s:is>
-          <s:t>高尔夫球杆</s:t>
+          <s:t>Croquet Mallet</s:t>
         </s:is>
       </s:c>
       <s:c r="D108" s="2" t="n">
@@ -6583,7 +6583,7 @@
       </s:c>
       <s:c r="C109" s="2" t="inlineStr">
         <s:is>
-          <s:t>冰球杆</s:t>
+          <s:t>Hockey Stick</s:t>
         </s:is>
       </s:c>
       <s:c r="D109" s="2" t="n">
@@ -6613,7 +6613,7 @@
       </s:c>
       <s:c r="C110" s="2" t="inlineStr">
         <s:is>
-          <s:t>木棒</s:t>
+          <s:t>Wooden Baseball Bat</s:t>
         </s:is>
       </s:c>
       <s:c r="D110" s="2" t="n">
@@ -6643,7 +6643,7 @@
       </s:c>
       <s:c r="C111" s="2" t="inlineStr">
         <s:is>
-          <s:t>球棒</s:t>
+          <s:t>Metal Baseball Bat</s:t>
         </s:is>
       </s:c>
       <s:c r="D111" s="2" t="n">
@@ -6673,7 +6673,7 @@
       </s:c>
       <s:c r="C112" s="2" t="inlineStr">
         <s:is>
-          <s:t>铁棒</s:t>
+          <s:t>Spiked Metal Bat</s:t>
         </s:is>
       </s:c>
       <s:c r="D112" s="2" t="n">
@@ -6703,7 +6703,7 @@
       </s:c>
       <s:c r="C113" s="2" t="inlineStr">
         <s:is>
-          <s:t>战术棍</s:t>
+          <s:t>Nailed Wooden Bat</s:t>
         </s:is>
       </s:c>
       <s:c r="D113" s="2" t="n">
@@ -6733,7 +6733,7 @@
       </s:c>
       <s:c r="C114" s="2" t="inlineStr">
         <s:is>
-          <s:t>电锯</s:t>
+          <s:t>Chainsaw</s:t>
         </s:is>
       </s:c>
       <s:c r="D114" s="2" t="n">
@@ -6763,7 +6763,7 @@
       </s:c>
       <s:c r="C115" s="2" t="inlineStr">
         <s:is>
-          <s:t>木斧</s:t>
+          <s:t>Hatchet</s:t>
         </s:is>
       </s:c>
       <s:c r="D115" s="2" t="n">
@@ -6793,7 +6793,7 @@
       </s:c>
       <s:c r="C116" s="2" t="inlineStr">
         <s:is>
-          <s:t>消防斧</s:t>
+          <s:t>Chopping Axe</s:t>
         </s:is>
       </s:c>
       <s:c r="D116" s="2" t="n">
@@ -6823,7 +6823,7 @@
       </s:c>
       <s:c r="C117" s="2" t="inlineStr">
         <s:is>
-          <s:t>战斧</s:t>
+          <s:t>Double-Bladed Battle Axe</s:t>
         </s:is>
       </s:c>
       <s:c r="D117" s="2" t="n">
@@ -6853,7 +6853,7 @@
       </s:c>
       <s:c r="C118" s="2" t="inlineStr">
         <s:is>
-          <s:t>小刀</s:t>
+          <s:t>Knife</s:t>
         </s:is>
       </s:c>
       <s:c r="D118" s="2" t="n">
@@ -6883,7 +6883,7 @@
       </s:c>
       <s:c r="C119" s="2" t="inlineStr">
         <s:is>
-          <s:t>猎刀</s:t>
+          <s:t>Hunting Knife</s:t>
         </s:is>
       </s:c>
       <s:c r="D119" s="2" t="n">
@@ -6913,7 +6913,7 @@
       </s:c>
       <s:c r="C120" s="2" t="inlineStr">
         <s:is>
-          <s:t>军刀</s:t>
+          <s:t>Knuckle Knife</s:t>
         </s:is>
       </s:c>
       <s:c r="D120" s="2" t="n">
@@ -6943,7 +6943,7 @@
       </s:c>
       <s:c r="C121" s="2" t="inlineStr">
         <s:is>
-          <s:t>开山刀</s:t>
+          <s:t>Karambit</s:t>
         </s:is>
       </s:c>
       <s:c r="D121" s="2" t="n">
@@ -6973,7 +6973,7 @@
       </s:c>
       <s:c r="C122" s="2" t="inlineStr">
         <s:is>
-          <s:t>匕首</s:t>
+          <s:t>Cleaver</s:t>
         </s:is>
       </s:c>
       <s:c r="D122" s="2" t="n">
@@ -7003,7 +7003,7 @@
       </s:c>
       <s:c r="C123" s="2" t="inlineStr">
         <s:is>
-          <s:t>战术刀</s:t>
+          <s:t>Machete</s:t>
         </s:is>
       </s:c>
       <s:c r="D123" s="2" t="n">
@@ -7033,7 +7033,7 @@
       </s:c>
       <s:c r="C124" s="2" t="inlineStr">
         <s:is>
-          <s:t>狼牙棒</s:t>
+          <s:t>Spiked Mace</s:t>
         </s:is>
       </s:c>
       <s:c r="D124" s="2" t="n">
@@ -7063,7 +7063,7 @@
       </s:c>
       <s:c r="C125" s="6" t="inlineStr">
         <s:is>
-          <s:t>炸药罐</s:t>
+          <s:t>Dynamite Stick</s:t>
         </s:is>
       </s:c>
       <s:c r="D125" s="2" t="n">
@@ -7092,7 +7092,7 @@
       </s:c>
       <s:c r="C126" s="6" t="inlineStr">
         <s:is>
-          <s:t>捆装炸药</s:t>
+          <s:t>Dynamite Bundle</s:t>
         </s:is>
       </s:c>
       <s:c r="D126" s="2" t="n">
@@ -7121,7 +7121,7 @@
       </s:c>
       <s:c r="C127" s="6" t="inlineStr">
         <s:is>
-          <s:t>遥控炸弹</s:t>
+          <s:t>Dynamite with Detonator</s:t>
         </s:is>
       </s:c>
       <s:c r="D127" s="2" t="n">
@@ -7150,7 +7150,7 @@
       </s:c>
       <s:c r="C128" s="6" t="inlineStr">
         <s:is>
-          <s:t>圆形手雷</s:t>
+          <s:t>Round Grenade</s:t>
         </s:is>
       </s:c>
       <s:c r="D128" s="2" t="n">
@@ -7179,7 +7179,7 @@
       </s:c>
       <s:c r="C129" s="6" t="inlineStr">
         <s:is>
-          <s:t>高爆手雷</s:t>
+          <s:t>Canister Grenade</s:t>
         </s:is>
       </s:c>
       <s:c r="D129" s="2" t="n">
@@ -7208,7 +7208,7 @@
       </s:c>
       <s:c r="C130" s="6" t="inlineStr">
         <s:is>
-          <s:t>等离子手雷</s:t>
+          <s:t>Energy Grenade</s:t>
         </s:is>
       </s:c>
       <s:c r="D130" s="2" t="n">
@@ -7237,7 +7237,7 @@
       </s:c>
       <s:c r="C131" s="6" t="inlineStr">
         <s:is>
-          <s:t>感应地雷</s:t>
+          <s:t>Land Mine</s:t>
         </s:is>
       </s:c>
       <s:c r="D131" s="2" t="n">
@@ -7266,7 +7266,7 @@
       </s:c>
       <s:c r="C132" s="6" t="inlineStr">
         <s:is>
-          <s:t>捕兽夹</s:t>
+          <s:t>Bear Trap</s:t>
         </s:is>
       </s:c>
       <s:c r="D132" s="2" t="n">
@@ -7295,7 +7295,7 @@
       </s:c>
       <s:c r="C133" s="6" t="inlineStr">
         <s:is>
-          <s:t>手枪子弹</s:t>
+          <s:t>Pistol Round</s:t>
         </s:is>
       </s:c>
       <s:c r="D133" s="2" t="n">
@@ -7324,7 +7324,7 @@
       </s:c>
       <s:c r="C134" s="6" t="inlineStr">
         <s:is>
-          <s:t>手枪弹药</s:t>
+          <s:t>Pistol Ammo</s:t>
         </s:is>
       </s:c>
       <s:c r="D134" s="2" t="n">
@@ -7353,7 +7353,7 @@
       </s:c>
       <s:c r="C135" s="6" t="inlineStr">
         <s:is>
-          <s:t>整箱弹药</s:t>
+          <s:t>Ammo Crate</s:t>
         </s:is>
       </s:c>
       <s:c r="D135" s="2" t="n">
@@ -7382,7 +7382,7 @@
       </s:c>
       <s:c r="C136" s="6" t="inlineStr">
         <s:is>
-          <s:t>盒装弹药</s:t>
+          <s:t>Boxed Ammo</s:t>
         </s:is>
       </s:c>
       <s:c r="D136" s="2" t="n">
@@ -7411,7 +7411,7 @@
       </s:c>
       <s:c r="C137" s="6" t="inlineStr">
         <s:is>
-          <s:t>直式弹匣</s:t>
+          <s:t>Straight Magazine</s:t>
         </s:is>
       </s:c>
       <s:c r="D137" s="2" t="n">
@@ -7440,7 +7440,7 @@
       </s:c>
       <s:c r="C138" s="6" t="inlineStr">
         <s:is>
-          <s:t>弯式弹匣</s:t>
+          <s:t>Curved Magazine</s:t>
         </s:is>
       </s:c>
       <s:c r="D138" s="2" t="n">
@@ -7469,7 +7469,7 @@
       </s:c>
       <s:c r="C139" s="6" t="inlineStr">
         <s:is>
-          <s:t>霰弹盒</s:t>
+          <s:t>Pellet Box</s:t>
         </s:is>
       </s:c>
       <s:c r="D139" s="2" t="n">
@@ -7498,7 +7498,7 @@
       </s:c>
       <s:c r="C140" s="6" t="inlineStr">
         <s:is>
-          <s:t>军用弹药箱</s:t>
+          <s:t>Military Ammo Can</s:t>
         </s:is>
       </s:c>
       <s:c r="D140" s="2" t="n">
@@ -7527,7 +7527,7 @@
       </s:c>
       <s:c r="C141" s="6" t="inlineStr">
         <s:is>
-          <s:t>左轮手枪</s:t>
+          <s:t>Revolver</s:t>
         </s:is>
       </s:c>
       <s:c r="D141" s="2" t="n">
@@ -7556,7 +7556,7 @@
       </s:c>
       <s:c r="C142" s="6" t="inlineStr">
         <s:is>
-          <s:t>单发手枪</s:t>
+          <s:t>Single-Shot Pistol</s:t>
         </s:is>
       </s:c>
       <s:c r="D142" s="2" t="n">
@@ -7585,7 +7585,7 @@
       </s:c>
       <s:c r="C143" s="6" t="inlineStr">
         <s:is>
-          <s:t>短管突击步枪</s:t>
+          <s:t>Short-Barreled Assault Rifle</s:t>
         </s:is>
       </s:c>
       <s:c r="D143" s="2" t="n">
@@ -7614,7 +7614,7 @@
       </s:c>
       <s:c r="C144" s="6" t="inlineStr">
         <s:is>
-          <s:t>战术突击步枪</s:t>
+          <s:t>Folding-Stock Assault Rifle</s:t>
         </s:is>
       </s:c>
       <s:c r="D144" s="2" t="n">
@@ -7643,7 +7643,7 @@
       </s:c>
       <s:c r="C145" s="6" t="inlineStr">
         <s:is>
-          <s:t>木托突击步枪</s:t>
+          <s:t>Wooden-Stock Assault Rifle</s:t>
         </s:is>
       </s:c>
       <s:c r="D145" s="2" t="n">
@@ -7672,7 +7672,7 @@
       </s:c>
       <s:c r="C146" s="6" t="inlineStr">
         <s:is>
-          <s:t>战斗霰弹枪</s:t>
+          <s:t>Grenade Launcher</s:t>
         </s:is>
       </s:c>
       <s:c r="D146" s="2" t="n">
@@ -7701,7 +7701,7 @@
       </s:c>
       <s:c r="C147" s="6" t="inlineStr">
         <s:is>
-          <s:t>狙击步枪</s:t>
+          <s:t>Sniper Rifle</s:t>
         </s:is>
       </s:c>
       <s:c r="D147" s="2" t="n">
@@ -7730,7 +7730,7 @@
       </s:c>
       <s:c r="C148" s="6" t="inlineStr">
         <s:is>
-          <s:t>冲锋枪</s:t>
+          <s:t>Submachine Gun</s:t>
         </s:is>
       </s:c>
       <s:c r="D148" s="2" t="n">
@@ -7759,7 +7759,7 @@
       </s:c>
       <s:c r="C149" s="6" t="inlineStr">
         <s:is>
-          <s:t>消音冲锋枪</s:t>
+          <s:t>Suppressed Submachine Gun</s:t>
         </s:is>
       </s:c>
       <s:c r="D149" s="2" t="n">
@@ -7788,7 +7788,7 @@
       </s:c>
       <s:c r="C150" s="6" t="inlineStr">
         <s:is>
-          <s:t>微型冲锋枪</s:t>
+          <s:t>Compact Submachine Gun</s:t>
         </s:is>
       </s:c>
       <s:c r="D150" s="2" t="n">
@@ -7817,7 +7817,7 @@
       </s:c>
       <s:c r="C151" s="6" t="inlineStr">
         <s:is>
-          <s:t>木托冲锋枪</s:t>
+          <s:t>Wooden-Stock Submachine Gun</s:t>
         </s:is>
       </s:c>
       <s:c r="D151" s="2" t="n">
